--- a/top_100_reels_meta_ads_guiones.xlsx
+++ b/top_100_reels_meta_ads_guiones.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Top 100 Meta Ads" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Resumen y método" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bonus marketing general" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +54,12 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -124,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -169,6 +176,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,7 +545,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -9975,7 +9985,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="96" customWidth="1" min="2" max="2"/>
@@ -10257,4 +10267,5692 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>OJO: estos NO hablan de Meta Ads (marketing general, marcas, otras plataformas). Van de bonus por sus vistas altas — sirven para estudiar ganchos y formatos virales, no como contenido de pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Creador</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Vistas</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Duración (seg)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Descripción (qué habla)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Guion completo en español</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Cómo está hecho</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Nivel de producción</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Por qué funcionó</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>¿Replicable con poca producción?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="88" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>8700000</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7646475816993295647</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney presenta un 'árbol de decisión' para evaluar si conviene invertir en anuncios de Snapchat en 2026, con datos de audiencia, anuncios dinámicos de producto y tasas de intención de compra. Es contenido patrocinado (#ad) en partnership con Snapchat.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>¿Vale la pena considerar los anuncios de Snapchat en 2026? Hablemos de eso. La verdad armé este árbol de decisiones para que lo recorramos juntos, porque sé lo que están pensando. 'Pero Dara, nadie usa Snapchat.' Falso. Snapchat tiene esta percepción de ser una plataforma que ya pasó su mejor momento. Pero la cosa es así: los marketers de crecimiento inteligentes saben que esto es una oportunidad y un moat (una ventaja competitiva defendible) para el tipo de negocio correcto. Así que vamos a repasar si esto es para vos. Número uno, considerá tu demografía. Snapchat llega al 75% de toda la gente en Estados Unidos. El 80% de la audiencia de Snapchat tiene más de dieciocho años. La mitad de los usuarios de Snapchat tiene 25 años o más, y un tercio tiene 35 años o más. Y de hecho es su segmento de más rápido crecimiento. El usuario promedio abre la plataforma 30 veces por día. Y número dos: sus anuncios dinámicos de producto son excelentes, así que si tenés múltiples SKUs [productos] y estás buscando alcance neto nuevo, es una decisión obvia. Y número tres, esto es lo que más me sorprende a mí: los usuarios de Snapchat, en conjunto, tienen una tasa de intención de compra 1,7 veces más alta que Meta o YouTube. Y son cinco veces más propensos a tomar acción después de ver un anuncio en la plataforma, comparado con las otras. Bueno, gente, yo creo que los anuncios de Snapchat volvieron, pero cuéntenme en los comentarios qué piensan ustedes.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Selfie / talking head estilo vlog (cámara en mano, se ve el brazo sosteniendo un micrófono lavalier), con gráficos animados a pantalla completa superpuestos (árbol de decisión con preguntas y sistema de puntos; mapa de EE.UU. cubierto con el logo de Snapchat y la estadística '75%'), subtítulos nativos tipo caption de TikTok (blanco con sombra, centrados en la parte inferior) sincronizados con el habla, corte a un ejemplo real de anuncio de producto (RoseSkinCo) como caso ilustrativo, locación tipo baño/casa con buena luz e iluminación cuidada, vestimenta casual (top negro).</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de pregunta directa + objeción anticipada del espectador ('pero Dara, nadie usa Snapchat... Falso') que genera curiosidad y contradice la creencia común; estructura de lista numerada con datos concretos (75%, 1,7x, 5x) que dan autoridad; formato de herramienta práctica ('árbol de decisión') que aporta valor utilizable más allá del video; cierre con pregunta abierta que invita a comentar.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>no — requiere diseño gráfico/motion (árbol de decisión animado) y es pauta patrocinada de marca, no es solo cámara y edición casera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="88" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>325000</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7661407989231897887</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell analiza la estrategia de marketing y lanzamiento de MAC Energy, la bebida energética de Conor McGregor, explicando cómo combinan la atención de la 'semana de pelea' con Amazon, TikTok Shop, retail y un ejército de creadores.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Conor McGregor acaba de lanzar MAC Energy, y este podría ser uno de los lanzamientos de marca de celebridad más agresivos del año. Porque esto no es solo el lanzamiento de una bebida energética. Esto es una toma de atención total durante la semana de la pelea. El 'Mac' volvió, y toda la estrategia está apilada alrededor de un momento masivo: el regreso de Conor. Conferencias de prensa en Las Vegas, carteles publicitarios, jets privados, Amazon, TikTok Shop, retail, anuncios de Facebook, creadores de contenido, y algunos de los nombres más grandes del rubro: Ryan García, Ashton Hall, Real Tarzan [?], atletas, peleadores, páginas de MMA, personalidades de podcasts y cuentas de comentario de páginas de creadores. La mayoría de las marcas lanzan un producto y después tratan de comprar atención. MAC Energy ya tiene la atención. Cada entrevista, clip viral, conferencia de prensa, momento, comentario: 'el Mac volvió' se convierte en el titular, se convierte en combustible para la marca. Y ese es el primer movimiento: convertir la pelea en el embudo (funnel). Después siembran esa demanda en el triángulo perfecto. Esta es la estrategia: Amazon captura la intención de compra, TikTok Shop genera descubrimiento liderado por creadores, el retail aporta prueba social y velocidad de estantería, y el sitio web mantiene simple el recorrido de compra. Eso importa porque las marcas de celebridades usualmente generan expectativa y después pierden gente por un camino de compra confuso. MAC Energy está haciendo lo opuesto. Y acá se pone todavía más loco: esto no son solo unos posteos de influencers. Esto es un ejército de creadores. Muestreo en TikTok Shop con unboxings de degustación, contenido de gimnasio, reacciones de la semana de pelea, contenido callejero, clips de podcasts, reseñas de creadores. Cada creador se convierte en distribución hoy para la marca, y en creatividad para mañana. Después, en Facebook, lanzan un 'war room' creativo: videos con IA, anuncios de sabores, ediciones de hype de Conor, anuncios enfocados en Amazon, anuncios de retail, clips de la semana de pelea. Cientos de ángulos alimentando al algoritmo para ver qué es lo que realmente vende. Si un clip de la semana de pelea se hace viral, se convierte en anuncio. Si un video de un creador despega, se convierte en anuncio. Si un sabor empieza a ganar en Amazon, se convierte en un ángulo de anuncio. Si la gente empieza a discutir en los comentarios, eso también se convierte en anuncio. Y como Meta ya les estaba dando problemas con la cuenta publicitaria, armaron cuentas publicitarias de respaldo y páginas de respaldo para un camino de lanzamiento en paralelo. Así que si a una cuenta le ponen una restricción, el lanzamiento no se detiene ahí. Este es el flywheel [rueda de inercia]: Conor consigue la atención, Amazon la captura, TikTok Shop genera el ejército de creadores, los anuncios de Facebook escalan los ángulos ganadores, y el retail captura el desborde. Esto no es una celebridad poniendo su nombre en una lata. Esto es una historia de regreso, un evento mediático de semana de pelea, un motor de creadores, una jugada de velocidad en Amazon, una estrategia de prueba en retail y una máquina de anuncios de Facebook, todo pasando al mismo tiempo. MAC Energy está lanzando el manual de jugadas de los campeones, y esto podría convertirse en uno de los lanzamientos de CPG [bienes de consumo] más rápidos del año. Comenten 'Mac' para aprender cómo lo hicimos.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Formato 'reacción'/talking head en un recuadro pequeño abajo de la pantalla (estudio casero con micrófono de podcast), con imágenes de fondo a pantalla completa que cambian según el tema (foto oscura de Conor McGregor, foto de conferencia de prensa con las latas del producto de fondo, captura de pantalla del Meta Ads Manager mostrando una restricción de cuenta publicitaria), remera negra lisa, sin gráficos animados, edición basada en cortes de imagen fija por tema.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de noticia/actualidad con nombre famoso (Conor McGregor) + promesa de 'uno de los lanzamientos más agresivos del año'; estructura de desglose paso a paso de una estrategia real (caso de estudio); gatillo de autoridad ('así lo hicimos nosotros') y curiosidad por ver el detrás de escena de una marca de celebridad.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo necesita cámara/mic básico, capturas de pantalla e imágenes de internet, sin edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="88" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Gary Vaynerchuk (GaryVee)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>209100</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@garyvee/video/7628306384462925069</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento de una entrevista/podcast donde Gary Vaynerchuk (GaryVee) explica su estrategia de marketing para 2026: crear múltiples cuentas nuevas, postear contenido orgánico en volumen masivo y usar el algoritmo para detectar qué contenido potenciar con pauta paga.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Acá está la clave del marketing en 2026: es todo social orgánico, son varias cuentas. Si yo fuera ustedes, crearía un usuario de TikTok que todavía no existe, en @ninguno por favor, al especial de Netflix de Mark [?], dos cuentas nuevas y estás posteando ahí de forma orgánica como un loco de mierda, ¿entendido? Acá está la clave: cuando consigue muchas vistas orgánicas hay que discutir eso, ¿le ponés medios pagos atrás? Lo recortás y lo ponés en otro lado. Usá los algoritmos a tu favor, el algoritmo de cada uno tiene una correlación directa y completa con lo que está interactuando, buscando y mirando. Sí, pero no querés curar para el algoritmo porque eso te va a cambiar... correcto, correcto, en realidad es al revés, tenés toda la razón. Bueno, vos solo querés hacer eso de postear en cantidad [?] a escala, eso significa 50 posteos por semana, no uno. Oh, wow.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Formato entrevista/podcast en estudio: plano medio de Gary Vaynerchuk sentado con micrófono de brazo articulado, remera con logo bajo capucha negra, fondo con pared de cuadros/retratos enmarcados (set del programa) y otra persona sentada detrás/al costado. Cartel de título fijo arriba ("The 2026 Marketing Blueprint"). Subtítulos en pantalla con palabra clave resaltada en amarillo. Es un recorte de una conversación más larga (long-form). Formato vertical.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con cartel de autoridad/actualidad ('El plan de marketing 2026') que promete una fórmula orientada al futuro inmediato. Estructura: afirmación tajante ('acá está la clave') + framework accionable (cuentas nuevas, volumen de posteo, dejar que el algoritmo indique qué pagar) + validación cruzada con el interlocutor que refuerza la idea. Gatillos: autoridad reconocida del entrevistado + promesa de framework + urgencia de estar al día para el año próximo.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>sí + el rodaje (cámara fija + texto superpuesto) es barato, pero gran parte del peso del video depende de tener ya un podcast propio y un invitado con autoridad reconocida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="88" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>143800</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7623478096884256013</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento de una sesión de consultoría en vivo (formato 'hot seat') donde Alex Hormozi entrevista a un empresario que vende servicios de gestión a consorcios de oficinas, y le explica que sus verdaderos clientes no son esos consorcios sino los brokers y desarrolladores que los derivan.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Vendo servicios de gestión a los miembros de la comisión directiva de asociaciones de propietarios de zonas comerciales, pensalo como un consorcio pero para oficinas. Bueno, la empresa factura 1.8 millones y a mí me paga 625.000 al año. Bueno, y me exige trabajar unos noventa minutos por semana. Bueno, ¿cuántos de estos consorcios (HOA) tenés? Ciento cuarenta y siete. Bueno, ¿cómo conseguiste esos ciento cuarenta y siete que tenés? Boca en boca, de manera desordenada, de parte de brokers, de desarrolladores, a veces de algún propietario dentro de una asociación que tenemos. Básicamente lo que pasó de casualidad con los brokers originales lo tenemos que hacer pasar a propósito, así que tenemos que ser deliberados en esa experiencia del cliente y verlos a ellos como el verdadero cliente. La primera vez que aprendí esto fue con Alan, el software que teníamos. Yo pensaba que los dueños de negocios físicos cuyos leads trabajábamos y a quienes les respondíamos eran nuestros clientes, y eso no era cierto. Los clientes reales son los dueños de agencia que trajeron a esos clientes, que pusieron nuestro producto bajo su propia marca (white label) para atender a la pyme. Tus tipos del consorcio no son el cliente; los brokers y tus COI (centros de influencia) son el cliente, y todo tu marketing tiene que apuntar a ellos. Pensalos en términos de cuál es su recorrido como cliente, cuál es su experiencia, cuál es el punto de activación, cómo los vuelvo a enganchar de manera constante, ¿organizo eventos para ellos?, ¿de qué maneras puedo servirles para que siempre sientan reciprocidad hacia mí? Eso es lo que yo haría como estrategia general. Y creo que si tenés toda una semana de horas disponible ahora mismo, te ponés súper agresivo con eso, y probablemente eso sería lo que yo haría durante 40 horas a la semana.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de un evento en vivo (conferencia de marca 'Acquisition'), formato entrevista/Q&amp;A desde el escenario: Alex Hormozi de pie con fondo violeta de marca, y cortes a miembros del público parados con micrófono respondiendo. Pantalla dividida verticalmente en dos mitades (escenario arriba, público abajo) en algunos frames. Subtítulos blancos quemados en pantalla con palabras en negrita/color. Cortes rápidos entre cámaras, vestimenta informal. Formato vertical, editado a partir de una grabación más larga.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de curiosidad inmediato por el título ('Ayudando a una agencia de gestión de propiedades a conseguir más clientes') que promete resolver un caso real. Estructura de caso real: cifras concretas (1.8 millones de facturación, 625.000 de paga, 147 consorcios) que dan autoridad y aspiracionalidad, seguidas de un diagnóstico contraintuitivo sobre quién es 'el verdadero cliente', y cierre con un plan de acción concreto. Gatillos: caso real con números + autoridad del consultor + revelación contraintuitiva.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>sí + el motor del formato (charla real de consultoría con cifras concretas y subtítulos) se puede grabar por Zoom o celular; lo difícil de igualar es conseguir casos reales con esos números.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>112800</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7662080307570511134</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell compara las estrategias de marketing de dos marcas de suplementos, Lemme y Goli, usando datos de la biblioteca de anuncios de Facebook y de ventas en TikTok Shop para definir cuál tiene mejor ejecución.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>¿De quién es mejor el marketing, de Lemme o de Goli? Lemme tiene 380 anuncios activos en Facebook. Publicitan en varios idiomas para llegar a mercados masivos. También están corriendo anuncios de colaboración paga porque saben que esos pueden superar en rendimiento a los anuncios tradicionales entre un 15 y un 30%. Eso es un salto enorme. Y combinan credibilidad de celebridades, desgloses completos de marca, y UGC [contenido generado por usuarios] sin parar. Pero después mirás a Goli. Goli tiene 3.000 anuncios activos en Facebook. ¿3.000? Eso es absolutamente ridículo. Es casi diez veces el volumen de Lemme en ese punto. No están probando solo unos pocos formatos, están probando prácticamente cada formato, ángulo, gancho, audiencia y oferta imaginable. Lemme manda el tráfico a páginas de producto personalizadas enfocadas fuertemente solo en suscripciones. ¿Por qué? Porque no quieren una sola compra. Quieren que el cliente pague todos los meses, aumentando la retención y el valor de vida del cliente a escala. Goli toma un enfoque completamente distinto. Lideran con combos (bundles) diseñados para que los clientes compren más productos en el primerísimo pedido. Eso genera un AOV [ticket promedio] más alto, un ROAS [retorno sobre la inversión publicitaria] más fuerte, y les da más margen para inundar el mercado con gasto publicitario. Ahora, en TikTok Shop es donde esto se pone completamente insano. Lemme tiene más de 19.000 afiliados que publicaron más de 86.000 videos, y pasaron de cero a 20 millones de dólares en solo unos meses en TikTok Shop. Ese nivel de crecimiento es casi inaudito. Los números de Goli son todavía más difíciles de comprender. Generaron más de 146 millones de dólares en TikTok Shop. 87.000 creadores con más de 662.000 videos publicados. Eso es casi ocho videos por creador. Es absolutamente alucinante. Ambas marcas entienden que TikTok Shop no es solo un canal de ventas. Es un motor de distribución masivo que impulsa el retail, los anuncios pagos, el reconocimiento de marca, todo el ecosistema de marketing junto. Entonces, ¿de quién es realmente mejor el marketing? ¿De Lemme, que está despegando ahora mismo? ¿O de Goli, que se convirtió en un gigante absoluto?</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, capturas de pantalla a pantalla completa (Facebook Ads Library, gráfico comparando precios de compra única vs. suscripción, dashboard de TikTok Shop de Goli con métricas), con anotaciones en rojo (flechas y recuadros) resaltando cifras clave, remera clara lisa, fondo neutro tipo oficina/casa.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Formato de comparación ('versus') que genera enganche por definir un 'ganador'; cifras extremas y sorprendentes (3.000 anuncios activos, $146 millones en TikTok Shop) que generan incredulidad y curiosidad; estructura clara punto por punto (ads, embudo web, TikTok Shop); cierre abierto pidiendo opinión que impulsa comentarios.</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo requiere capturas de pantalla de herramientas gratuitas (Ads Library, dashboards públicos) y edición simple con anotaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>93400</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7629619182321093902</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Sesión de consultoría en vivo donde Alex Hormozi le explica a los dueños de una marca de e-commerce (facturando unos 3 millones al año) por qué su plan de armar un portafolio de marcas para vender no va a funcionar sin patente o marca propia, y describe el 'loop' que conecta la promesa de marketing con el producto.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Vendemos productos de e-commerce. Tiene como cuatro meses. Así que estamos en un ritmo de facturación anual de unos tres millones. ¿Cuántos SKU tenés? Cuatro. ¿Es todo la misma marca? No. Bueno, ¿qué tan grande querés que sea esto? El objetivo es tener un portafolio de, digamos, cuatro o cinco marcas, para poder vender (hacer exit) en un par de años. Bueno, yo tengo esta conversación cada semana con alguien que hace e-commerce, y es casi siempre la misma: 'me gustaría tener un portafolio de un puñado de productos que eventualmente pueda vender algún día'. La verdad es que todavía no vi a nadie lograr eso. Ustedes ahora mismo manejan un negocio de arbitraje de medios, y funciona muy bien hasta cerca de los 10 millones. Bueno. Y después va a dejar de funcionar bien rápidamente. A medida que sigan escalando, su CAC (costo de adquisición de cliente) va a seguir subiendo, sus márgenes brutos se van a achicar, y eso se va a poner frustrante. Después también van a tener problemas de cadena de suministro, que se van a volver una carga. También van a tener imitaciones ('dupes'): si empiezan a ir muy bien, alguien los va a undercutear en precio y listar en Amazon y todo eso. ¿Tienen alguna patente proyectada para alguno de estos productos? La habilidad que a ustedes les falta va a ser la marca, y la marca también se completa con el producto. Claro. O sea, eso es lo que cierra el círculo de la marca: hacemos esta promesa increíble, tenemos todas estas asociaciones geniales, la gente hace la compra, y después el producto o refuerza la marca o la destruye. Y si refuerza la marca, entonces el círculo continúa y se vuelve un ciclo virtuoso. Y así es como pasás de ser cualquier tienda de e-commerce que hace arbitraje de medios a ser un nombre reconocido que podés vender no solo por 50 millones, sino tal vez por 500 millones. Así que o tienen algún tipo de patente que realmente puedan proteger y un equipo legal que la pueda hacer cumplir, o construyen una marca. Te estoy hablando con total honestidad. Sí, prefiero ahorrarte un par de años.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato que la serie de Hormozi: grabación de evento en vivo, escenario con fondo violeta de marca, Hormozi de pie con musculosa gesticulando mucho con las manos, cortes a jóvenes del público parados con micrófono respondiendo. Subtítulos blancos con palabras en negrita quemados en pantalla. Cartel de fondo con logo del evento parcialmente visible. Formato vertical, cortes entre cámara de escenario y cámara de público.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Gancho conceptual desde el título fijo ('El marketing hace promesas. El producto cumple promesas. Producto - marketing = Marca'), una fórmula memorable antes de arrancar. Estructura: caso real con cifras (3 millones de facturación, 4 SKU) → predicción de fracaso basada en patrones ya vistos por el consultor → framework claro y citable sobre cómo se construye una marca. Gatillos: autoridad + fórmula memorable + advertencia que genera urgencia + caso real con números.</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>sí + el formato (consultoría real con cifras y una frase-fórmula al inicio) se puede grabar en una videollamada con buen audio y subtítulos, sin necesidad de escenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7623114793200766222</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Sesión de consultoría en vivo donde Alex Hormozi ayuda al dueño de una agencia que produce comerciales con inteligencia artificial a subir drásticamente sus precios, señalando que está subvaluando su servicio y que el uso de IA debería ser un secreto de costos, no el argumento de venta.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Hacemos comerciales con IA. Ajá. Y este año estamos en 250 mil, básicamente a 25 mil cada uno. ¿Y en avisos? ¿Cobrás 25.000 por esos avisos? Sí. La puta madre, che. Bueno, nuestro precio, a donde queremos llegar, es 50 mil. Así que nuestra propuesta de valor de venta es, viste, arrancamos anclando el precio en que un comercial de televisión normal sale 500 mil. La idea inicial era que somos una décima parte del precio, a 50 mil. En la misma industria, con la misma pericia, calidad y fidelidad. Yo diría que estamos como en 18 mil en cuanto al costo real de un comercial de 30 segundos. En cuanto al costo, no creo que la IA tenga nada de especial. La gente quiere clientes. Ya sea que yo tenga un palo en llamas que agito y vienen los clientes, señales de humo, el muñeco inflable bailarín de esos que agitan los brazos, a nadie le importa, ¿no? Mientras consigan clientes. Es más, casi preferiría que el hecho de que usás IA sea un secreto. Preferiría venderlo por 500 mil y que te cueste 18, y ya está, buenísimo.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato de la serie: evento en vivo, Hormozi en escenario con musculosa y fondo violeta de marca, corte a un miembro del público (joven con notas en un cuaderno) parado con micrófono contando su caso. Subtítulos blancos en negrita quemados en pantalla, sincronizados con el habla. Formato vertical con cortes entre cámaras de escenario y de público.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con caso real sorprendente (una agencia de comerciales con IA subfacturando su propio valor) y reacción visceral del consultor que genera identificación inmediata. Estructura: cifra baja inicial (25 mil) → contraste con el punto de referencia de la industria (500 mil por un comercial tradicional) → reencuadre de precio con anclaje → remate con una idea contraintuitiva memorable (esconder que se usa IA en vez de venderla como diferencial). Gatillos: caso real + número concreto + revelación contraintuitiva + autoridad.</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>sí + el mismo mecanismo (mostrar un caso real de mal pricing y corregirlo en cámara) se puede grabar en una videollamada de consultoría sin necesidad de escenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Gary Vaynerchuk (GaryVee)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>48700</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@garyvee/video/7638691392759319821</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Clip corto de Gary Vaynerchuk hablando desde el escenario de un evento, resumiendo en pocos segundos su fórmula de marketing: hacer un buen video, targetearlo, conseguir alcance masivo y después remarketear con un llamado a la acción.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>¿Querés creer de verdad en cómo funciona el marketing? Hacé un video buenísimo, de la puta madre. Targeteálo [segmentalo] correctamente, conseguí que cientos de miles de personas vean una buena parte, y después volvé a impactarlos [remarketing] con un llamado a la acción, y mirá cuántos convierten. Vas a creer en el marketing por el resto de tu vida.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Metraje reciclado de una charla/keynote en vivo (no grabado específicamente para TikTok), cámara fija a media distancia, GaryVee de pie con micrófono en mano sobre un escenario con decoración de rayas rojas y blancas, pantalla con contenido detrás suyo, subtítulos blancos quemados frase por frase, apertura con una pantalla negra con la palabra 'believe' en tipografía elegante con efecto de brillo.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Formato ultra corto (11 segundos) que retiene hasta el final; gancho agresivo ('¿Querés creer de verdad...?' + lenguaje fuerte) que capta atención inmediata; autoridad del speaker (referente reconocido de marketing) hablando con convicción desde un escenario; consejo accionable condensado en una sola frase memorable.</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>sí — es solo reutilizar un fragmento de una charla ya grabada y agregar subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>40700</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7663136859421199646</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell compara el marketing de dos marcas de belleza/skincare, Reale Actives (vinculada a la creadora Alex Earl) y Prequel, analizando por qué Prequel está ganando pese a que Reale Actives tiene una influencer con mucha más audiencia.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>¿De quién es mejor el marketing, de Reale Actives o de Prequel? Esta honestamente me sorprendió. Reale Actives tiene una de las ventajas de creadores más grandes del mundo: Alex Earl. Y sin embargo, solo están corriendo 27 anuncios de Facebook. Usan anuncios de producto, anuncios de características, reseñas, antes y después, y estadísticas de marca, predominantemente. Pero, ¿dónde está el UGC? ¿Dónde están los creadores? ¿Dónde están los anuncios con influencers? ¿Y por qué la audiencia de Alex Earl no se está convirtiendo en un ejército de creadores? Esa es la oportunidad perdida más grande en este momento. Ahora miren a Prequel. Están corriendo 130 anuncios activos en Facebook. UGC, anuncios tipo historia, combos, recorridos de producto, ángulos de problema-solución, ganchos de viaje, ofertas de temporada. Y cada anuncio se siente nativo y es completamente distinto de la web. Reale Actives manda el tráfico a una página de producto cargada de texto, sin oferta especial, sin imágenes de desglose de producto, y casi sin contenido de creadores fuera de la propia Alex. El sitio de Prequel está construido para convertir: educación de producto, combos con descuento, ventas cruzadas y ventas adicionales en el carrito. Todo está diseñado para maximizar el AOV [ticket promedio]. Pero acá viene la parte más loca: en TikTok Shop, Reale Actives ni siquiera está. ¿Cómo es posible? Alex Earl se hizo famosa en TikTok. Tiene una de las audiencias más grandes de la plataforma. Esta marca debería ser una de las TikTok Shops de más rápido crecimiento de internet. En cambio, Prequel es la que está dominando: 677.000 productos vendidos, 39.000 reseñas de cinco estrellas, y 62.000 clientes recurrentes. Miles de creadores están vendiendo sus productos todos los días. Están apostando exactamente a lo que funciona. Reale Actives tiene una de las ventajas de creadores más grandes de la categoría de belleza, si la activaran. Pero Prequel tiene el mejor sistema de marketing y el equipo de ejecución real detrás. Pero cuéntenme, ¿quién creen que está ganando?</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, fondo de estantería de productos verdes desenfocado al inicio, capturas de pantalla de anuncios (Facebook Ads Library) y de página de producto con anotaciones en rojo (recuadros, subrayados), remera clara lisa, estudio/casa con buena luz.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de contraste inesperado ('esta me shockeó') combinado con una celebridad conocida (Alex Earl) que genera curiosidad sobre por qué no está ganando pese a su ventaja; estructura de desglose por canal (Facebook ads, web, TikTok Shop) con datos concretos (677.000 productos vendidos); pregunta final que invita a debatir en comentarios.</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>sí — mismo formato reutilizable de capturas de pantalla y talking head, sin producción cara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="88" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>37000</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7651622337745390879</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell muestra cómo usó la IA Claude para crear un sitio de Shopify completo y optimizado para conversión en pocos minutos, a partir de escanear un sitio existente y aplicar un 'manual' de tasa de conversión.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Claude es absolutamente una locura. Ahora podés crear sitios completos de Shopify en minutos. Primero, le hacés crear un kit de marca. Segundo, le hacés escanear tu producto, el lenguaje, la oferta, la audiencia, y las objeciones de los clientes, todo a partir de tu sitio actual. Tercero, lo pasás por este manual de tasa de conversión que tengo acá. Después diseña y ejecuta el sitio web por vos. Miren nomás el sitio que armamos usándolo. Cubre psicología del comprador, encuadre del problema, ofertas de credibilidad, marcos de tasa de conversión, ventas adicionales, ventas cruzadas, recorridos completos de producto, y mucho más. Y literalmente te lleva de una tienda básica de Shopify a un sitio web perfecto y de alta conversión en menos de 10 minutos. Comenten 'Claude' y les mando la estrategia completa.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, imagen de apertura con el logo de Claude y una modelo haciendo un gesto de corazón con las manos sobre fondo violeta, captura de pantalla de una conversación de texto con Claude (salida del modelo), captura de una página de producto resultante (Koochi Wash) con anotación en rojo, remera negra.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de novedad tecnológica con promesa extrema ('sitios completos de Shopify en minutos'); demostración de caso real (capturas del resultado) que aporta prueba; estructura de pasos numerados fácil de seguir; llamado a la acción con recompensa (estrategia completa) a cambio de comentar.</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo necesita capturas de pantalla de la herramienta y cámara básica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Gary Vaynerchuk (GaryVee)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>34100</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@garyvee/video/7648438344526875918</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento de una entrevista/podcast con Gary Vaynerchuk hablando sobre su 'blueprint de marketing 2026': crear múltiples cuentas nuevas en redes, postear contenido orgánico a gran escala, y usar el rendimiento orgánico para decidir dónde meter pauta paga.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Acá está la clave del marketing en 2026. Es todo social, orgánico. Son múltiples cuentas. Si yo fuera ustedes, creo un usuario de TikTok que todavía no existe. [fragmento poco claro por ASR: 'At none to please at Marks Netflix special' ?]. Dos cuentas nuevas y estás posteando orgánicamente ahí como loco, carajo. Entendido. Acá está la clave: cuando consigue muchas vistas orgánicas, eso hay que discutirlo. ¿Le ponés medios pagos atrás? ¿Lo recortás [clip] y lo ponés en otro lado? Usá los algoritmos a tu favor. El algoritmo de cada uno tiene una correlación directa y completa con lo que están interactuando, buscando y mirando. Sí, pero no... no querés curar para el algoritmo, porque eso te va a cambiar el... Correcto. Correcto. En realidad es al revés. Tenés toda la razón. Bueno. Vos querés solamente hacer tu 'shitpost' [contenido de bajo esfuerzo, posteado sin filtro] a escala. Eso significa 50 posteos por semana, no uno. Oh, wow. Wow.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Formato entrevista/podcast, sentados en un estudio con una pared de fotos enmarcadas de fondo, gráfico de título fijo en la parte superior de la pantalla ('The 2026 Marketing Blueprint'), subtítulos blancos quemados palabra clave por palabra clave, micrófono de brazo articulado visible, remera con estampa y gorra.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Formato de conversación con intercambio dinámico entre dos personas que se siente auténtico y no guionado; autoridad reconocida del entrevistado; consejo contraintuitivo (crear cuentas que 'todavía no existen', 'no curar para el algoritmo') que genera curiosidad; ritmo ágil con subtítulos grandes que permiten seguirlo sin audio.</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>no — requiere un estudio de podcast con set, iluminación y gráfico de título editado, no es un formato casero simple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>28800</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7647921690407750943</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell desglosa la estrategia de posicionamiento de marca de Bite (pasta dental en pastillas) que factura 8 millones de dólares al año, basada en sustentabilidad, estética y contenido de creadores en vez de los mensajes tradicionales de cuidado bucal.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>La genial estrategia de posicionamiento de marca de Bite, de ocho millones de dólares al año, es algo que casi todas las marcas de e-commerce se están perdiendo ahora mismo. La mayoría de las marcas de cuidado bucal hacen marketing en torno al aliento fresco, dientes más blancos, protección contra caries. Bite fue en una dirección completamente distinta: sustentabilidad, estética, ingredientes, estilo de vida, ser anti-pasta-dental-grande y no competir con Colgate por 'mejor pasta dental'. Crearon una categoría completamente nueva: pastillas de pasta dental (toothpaste tablets). De repente el producto se volvió más compartible, más interesante, más premium, más amigable para el contenido, y especialmente amigable para los creadores. Y acá es donde la estrategia se pone genial. Su producto se ve distinto, lo que significa que cada video de un creador automáticamente va a captar atención en el feed. Por eso sus anuncios de TikTok y Meta funcionan tan bien ahora. Después le suman branding limpio y minimalista, mensajes eco-friendly, estética de lujo, ofertas de suscripción, UGC, contenido de creadores, y atractivo visual para la mesada del baño. Convirtieron la pasta dental en una marca de estilo de vida, porque cuando sos dueño del posicionamiento, podés cobrar más, escalar más fácil, conseguir un CAC [costo de adquisición de cliente] más bajo, aumentar tu retención y dominar la atención sin depender de descuentos. Comenten 'bite' [?] y les mando mi manual de posicionamiento de marca.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, con clips de contenido tipo UGC de fondo (una mujer usando el producto frente al espejo del baño, un unboxing sobre una mesa con una planta de fondo, un primer plano sosteniendo el frasco junto a un cepillo de dientes), subtítulos parciales quemados en los clips de fondo, remera negra.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de cifra concreta ('estrategia genial de 8 millones de dólares al año') + promesa de que 'casi todas las marcas se están perdiendo esto'; estructura de contraste (lo que hacen todos vs. lo que hizo Bite) fácil de seguir; ejemplos visuales reales del producto/contenido de creadores que respaldan el argumento; cierre con incentivo para comentar y recibir más información.</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>sí — reutiliza clips de UGC ya existentes de la marca, sin producción propia cara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7623479735972056334</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Sesión de consultoría en vivo donde Alex Hormozi le explica al dueño de una agencia que arma equipos de ventas (14 millones de facturación) que su freno para llegar a 100 millones es un problema de precios, y describe el 'ciclo virtuoso' de subir precios en negocios de servicios para poder contratar mejor talento.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Armamos equipos de ventas para empresas. Estamos justo por debajo de los 14 millones. Este año nos gustaría llegar a 100 millones. Hicimos los números: la cantidad de liderazgo y de cumplimiento (fulfillment) que necesitaríamos para esos clientes no sería rentable. Seguramente tengas un problema de precios. Lo que termina pasando en todos los negocios de servicios, especialmente B2B, es que el precio sigue subiendo. Y así es como funciona, porque a medida que perseguís clientes más grandes y más numerosos, cobrás primas cada vez más grandes. Y ese es el ciclo virtuoso de los servicios. Siempre tenés una restricción de oferta si estás en servicios, si sos bueno. Y por eso subís tu precio, y entonces podés incorporar más jugadores A porque te los podés permitir. Eso aumenta tu reputación, aumenta la demanda, lo que te permite conseguir más jugadores A. Y así pasás de pagarle a gente de 100.000 dólares, a 250.000, a gente de un millón de dólares al año, a gente de varios millones de dólares al año. Ahí es donde termina yendo.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato de la serie: escenario de evento en vivo con fondo violeta de marca, Hormozi con musculosa gesticulando con las manos mientras se mueve por el escenario, corte a un joven del público de perfil hablando al micrófono. Subtítulos blancos en negrita quemados en pantalla. Formato vertical, cortes entre cámaras.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con caso aspiracional (agencia que ya factura 14 millones y quiere llegar a 100) que genera autoridad instantánea al consultor al señalar un problema que el dueño no había visto. Estructura: objetivo grande declarado → diagnóstico directo y seguro → explicación de un principio generalizable ('el ciclo virtuoso de los servicios') aplicable a cualquier negocio de servicios que mira el video. Gatillos: caso real con cifras grandes + autoridad + framework generalizable y memorable.</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>sí + se puede lograr el mismo efecto grabando una consultoría real por videollamada con audio limpio y subtítulos, sin necesidad de escenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7668490573732465933</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi responde en formato preguntas y respuestas a una consulta de la audiencia sobre cómo vender una marca de streetwear (producto no esencial) en un país en desarrollo donde la prioridad de la gente es cubrir necesidades básicas.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>¿Cómo venderías una marca de streetwear en un país en desarrollo, donde la mayoría de la gente prioriza necesidades básicas como la comida? ¿Cómo generás suficiente valor y deseo para que gasten en ropa no esencial? Muy buena pregunta, señora. Eh, yo creo que la pregunta que estás haciendo es: ¿cómo vendés paraguas en el desierto? Entonces, no querés... el requisito número uno para que haya demanda es una multitud hambrienta. Tenés que tener gente que lo quiera. Vos no querés crear demanda, querés canalizar demanda. Ahora bien, hay dos escenarios en los que veo que este modelo podría funcionar. El modelo número uno es venderle a los ricos. Y con esto me refiero a que capaz tenés un país en desarrollo con mucha gente pobre, pero hay gente adinerada, y esa gente adinerada quiere que todo el mundo sepa que son ricos. Entonces ahí tenés una audiencia, una porción mucho más chica, pero hay gente dispuesta a pagar un precio premium para demostrar que tiene estatus en esa comunidad. Tu marca de streetwear está bien así, probablemente vaya a tener que ser premium y estar dirigida a la gente que tiene la plata, en lugar de tratar de convencer a gente que no tiene plata de gastar dinero que no tiene. Yo no quiero educar a toda una audiencia sobre por qué mi producto tiene valor. Prefiero encontrar lo que ya quieren y después resolvérselo de una forma nueva.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en primer plano fijo, fondo negro liso tipo estudio, remera musculosa blanca con logo 'ACQUISITION.COM', micrófono de podcast visible sobre la mesa, subtítulos blancos grandes quemados en pantalla, sin cortes de edición ni gráficos adicionales, plano único sostenido.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de pregunta real de audiencia (formato Q&amp;A que genera identificación); analogía memorable y contraintuitiva ('¿cómo vendés paraguas en el desierto?'); autoridad reconocida del entrevistado en negocios; respuesta estructurada en un framework simple (dos escenarios posibles) fácil de recordar y repetir.</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo requiere una cámara, buena luz y un micrófono, sin edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>22500</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7662765037668388126</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell da su predicción de marketing para 2026 sobre la tensión entre lo analógico y lo digital, argumentando que el marketing físico/humano (cartas, eventos, packaging) se va a volver la 'capa de confianza' que complementa a la distribución digital.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Predicciones de marketing para 2026. Analógico versus digital. Lo analógico va a ser lo digital [?]. Y sé que suena una locura, porque todo el mundo habla de IA, todo el mundo habla de automatización, todo el mundo habla de más anuncios, más embudos, más emails y más contenido. Pero acá está el patrón. Disrupción [?]. Cuando todo se vuelve digital, lo que se siente físico se vuelve premium. Y cuando cada marca usa IA, la marca que se siente humana se destaca. Cuando cada empresa manda emails automatizados, la nota escrita a mano se recuerda. Y cuando cada lanzamiento de producto pasa online, el evento presencial se siente mágico. Y cuando cada anuncio se ve pulido, el contenido crudo del fundador detrás de escena gana. Por eso el marketing analógico está volviendo. No porque lo digital esté muerto, sino porque lo digital sigue siendo el motor, pero lo analógico se está convirtiendo en la capa de confianza. Correo físico, cartas del fundador, insertos impresos, eventos VIP, activaciones en retail, pop-ups, encuentros de comunidad, packaging de producto, regalos para clientes, contenido detrás de escena, momentos del mundo real que la gente realmente recuerda. Las marcas que ganen en 2026 no van a ser las que elijan entre analógico o digital. Van a ser las que combinen ambos. Lo digital genera el alcance, lo analógico genera la relación. Lo digital consigue el clic, lo analógico crea el recuerdo. Lo digital escala la atención, y lo analógico construye confianza. Confianza: ese es el cambio. Las marcas que dependen de uno solo de los dos se van a sentir cada vez más reemplazables. Las marcas que suman experiencias del mundo real al recorrido del cliente se van a sentir imposibles de copiar. Así que mi predicción para 2026 es simple: la próxima ola del marketing no es más digital. Es distribución digital con confianza analógica. Cuéntenme en los comentarios qué piensan.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, imágenes de fondo ilustrativas que cambian según el punto (un rostro femenino generado/filtrado por IA con el texto en pantalla 'This is AI', una foto tipo editorial de una mujer en la playa, un video de un joven bebiendo de una lata en un festival al aire libre con amigos), remera negra.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de predicción contraintuitiva ('lo analógico va a ser lo digital') que genera curiosidad inmediata; estructura de contrastes repetidos ('cuando todo es X, Y se vuelve premium') fácil de seguir y citar; ejemplos visuales concretos (IA vs. momentos reales) que refuerzan el argumento; cierre con pregunta de opinión.</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo necesita imágenes de stock/redes y talking head, sin producción cara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="88" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>20200</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7644195232329796895</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell enumera siete predicciones de marketing para 2026 dirigidas a marcas de consumo masivo (CPG): volumen de creadores, TikTok Shop como motor de descubrimiento, marcas lideradas por fundadores, IA para escalar creatividad, y marcas que se convierten en compañías de medios.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Mis predicciones de marketing para 2026 para marcas de CPG [bienes de consumo masivo]. Número uno: el volumen de creadores va a importar más que el contenido pulido. Las marcas más grandes van a dejar de obsesionarse con anuncios perfectos y se van a enfocar en producir miles de piezas de creadores cada mes. Las marcas con más velocidad de contenido van a ganar. Número dos: TikTok Shop se va a convertir en el motor número uno de descubrimiento de producto, va a impulsar la demanda en retail, aumentar las ventas en Amazon, generar creatividades para Meta, y potenciar la búsqueda de marca. El efecto halo se va a volver imposible de ignorar. Número tres: las marcas lideradas por fundadores van a dominar la atención. Los consumidores hoy confían más en personas que en marcas. Los fundadores que se convierten en la cara del contenido van a superar ampliamente a las marcas de estilo corporativo. Número cuatro: los anuncios de Meta se van a ver cada vez menos como anuncios. Las creatividades que más conviertan se van a sentir nativas, educativas, grabadas por creadores [?], de baja producción, y pensadas primero para lo social. Los comerciales pulidos van a seguir perdiendo efectividad con el tiempo. Número cinco: la IA va a hacer explotar la producción creativa. Las marcas ganadoras no van a usar la IA para reemplazar creadores. La van a usar para generar conceptos, iterar ganchos, crear estadísticas, testear ángulos, lanzar más rápido, generar más UGC, y multiplicar el contenido de creadores. La velocidad creativa se va a convertir en la ventaja competitiva más grande del e-commerce. Número seis: la economía de suscripción más retención va a separar a los ganadores de los perdedores. Las marcas con un LTV [valor de vida del cliente] fuerte se van a poder dar el lujo de gastar más que todos los demás, lo que significa que los combos, membresías, reposición, comunidad y ofertas de continuidad van a volverse todavía más importantes. Número siete: las marcas se convierten en compañías de medios. Las marcas de CPG más grandes en 2026 no se van a sentir como empresas de productos. Se van a sentir como marcas de entretenimiento, marcas educativas, redes de creadores, comunidades. La atención se está convirtiendo en el activo más valioso del e-commerce y del mundo. Pero cuéntenme qué piensan.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, imágenes de fondo que cambian con cada punto numerado (primer plano de labios tipo anuncio UGC de belleza, mujer en una cocina abriendo un producto, captura de un artículo de Forbes sobre la marca AG1), remera negra.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Formato de lista numerada (7 predicciones) que promete valor denso y fácil de consumir; autoridad por hablar en base a datos y tendencias del sector; variedad visual constante (una imagen distinta por punto) que evita que el video se sienta monótono; cierre con pregunta de opinión para generar comentarios.</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo requiere un guion con datos/opinión propia y clips o capturas de apoyo, sin producción cara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>19300</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7623473944162520333</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Sesión de consultoría en vivo donde Alex Hormozi ayuda al dueño de una agencia de contenido white-label para firmas de relaciones públicas (estancada en 1.5 millones de facturación durante cinco años) a diagnosticar que su estructura de precios está mal calibrada: muy alta para la mayoría de sus clientes y muy baja para los mejores.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Vendo servicios de medios bajo marca blanca (white label) a firmas de relaciones públicas. Estuvimos estancados en 1.5 millones durante cinco años. Las agencias vienen a vos. Sí. Y después ponen tu servicio bajo su propia marca y le venden tu producto a otra gente. Exactamente eso. ¿Tenés la misma cantidad de agencias vendiendo tu producto este año que el año pasado, y el año anterior, y el anterior a ese? Tenemos bastante rotación (churn), en general. ¿Se dan de baja porque no usan los artículos o porque los artículos no son buenos? Porque no los usan. Probablemente necesites un nivel más bajo que tenga algún componente de uso agregado. Podría ser algo así como 199 al mes más 100 por artículo. Tenés que estar lo suficientemente bajo para que no se den de baja en sus meses malos. Y ese es el problema de fondo, creo: que tenés un precio demasiado alto para la mayoría de tus clientes, y demasiado bajo para aquellos con los que vas a maximizar tu ganancia.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato de la serie: evento en vivo, fondo de cortina negra con logo del evento, un hombre del público con lanyard/acreditación parado hablando al micrófono mientras cuenta su caso (Hormozi se escucha preguntar desde fuera de plano en este segmento). Subtítulos blancos en negrita quemados en pantalla. Formato vertical.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de caso real con tensión (negocio 'estancado' cinco años en la misma cifra) que genera empatía inmediata en cualquier dueño de negocio frenado. Estructura de diagnóstico por preguntas (rotación de clientes, motivo del churn) al estilo interrogatorio, hasta llegar a la causa raíz, y cierre con una solución de pricing concreta y aplicable. Gatillos: caso real + estancamiento relatable + autoridad + solución concreta.</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>sí + el mecanismo central (diagnóstico de negocio real en una charla grabada con subtítulos) no requiere escenario, se puede hacer con una videollamada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>15400</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7646799950600359199</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell explica cómo TikTok Shop 'salvó' a Sprinter, la marca de bebidas de Kylie Jenner, al pasar de una estrategia de lanzamiento tradicional centrada en la celebridad a una impulsada por contenido masivo de creadores.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>La marca de Kylie Jenner, Sprinter, acaba de ser salvada por TikTok Shop. ¿Por qué? Porque lanzó como una marca de celebridad tradicional. Al principio, el marketing estaba muy enfocado en visuales de la celebridad, expectativa de lanzamiento, campañas pulidas, y el branding de Kylie. Pero eso solo ya no funciona como antes, porque la atención se corrió de las celebridades a los creadores. Y ahí es donde TikTok Shop cambió completamente el juego. Esto es lo que empezó a pasar: en lugar de que la gente vea anuncios pulidos, las marcas ahora usan TikTok para inundar los feeds con degustaciones, contenido de 'noche de chicas', reposiciones de stock, videos rankeando sabores, reseñas casuales de creadores. Y ahora su producto se sintió más cultural que corporativo. Ese es el desbloqueo. TikTok Shop funciona porque los creadores normalizan los productos a través de la repetición. Y las marcas de bebidas se benefician especialmente de esto porque son altamente sociales, estéticamente visuales, fáciles de reseñar, y motivadas por la compra impulsiva. Un solo video de un creador puede hacer que una bebida se sienta instantáneamente de moda, viral, socialmente aprobada, y que valga la pena probar. Y TikTok Shop comprime todo este embudo -descubrimiento, prueba social, checkout y compra- todo dentro de un mismo feed. Por eso es tan poderoso. Y acá está el cambio de estrategia más grande: TikTok Shop está ayudando a las marcas de celebridades a pasar de ser productos de propiedad de una celebridad a productos de distribución por creadores. Esa es una diferencia enorme, porque los ecosistemas de creadores escalan muchísimo mejor que el hype de una celebridad sola. Pero cuéntenme qué piensan: ¿se van a convertir en la próxima gran marca?</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, clips de fondo tipo lifestyle/fiesta (grupo de mujeres en una salida nocturna bajo luces de neón, primer plano de alguien tomando de una lata de Sprinter) y una captura de pantalla del checkout de compra del producto (con Apple Pay), remera negra.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de nombre famoso (Kylie Jenner) + palabra 'salvada' que genera curiosidad sobre qué pasó; estructura de antes/después (marketing tradicional que no funcionó vs. TikTok Shop que sí); explicación del mecanismo (por qué funcionan los creadores) que aporta aprendizaje aplicable; cierre con pregunta abierta.</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo usa clips existentes de redes y una captura de pantalla, sin producción propia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7647543637399588126</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell resume lo que dijo el co-fundador de Bloom Nutrition sobre su estrategia en TikTok Shop: miles de creadores por mes, uso de la herramienta GMV Max, y cómo el éxito en TikTok genera un 'efecto halo' que dispara las ventas en Amazon y Target.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>¿Vieron lo que dijo el co-fundador de Bloom sobre TikTok Shop? Es una de las oportunidades más grandes en este momento. Dijo que escalaron a cifras altas de siete dígitos por mes en TikTok, con más de 30.000 videos de creadores publicados cada mes. Eso es una locura. Su objetivo ni siquiera es solo vender en TikTok Shop. Están usando TikTok Shop para aumentar las ventas en Amazon, la velocidad en Target, el rendimiento de los anuncios de Meta, el volumen de búsqueda de marca, y la demanda en retail, para conseguir el efecto halo. Paso 1: incorporan cientos de afiliados todos los días. Le dan a los clientes libertad creativa completa en lugar de controlar excesivamente el mensaje. ¿Por qué? Porque los creadores descubren ángulos que a las marcas nunca se les ocurrirían. Paso 2: siembra masiva de creadores [creator seeding]. Los mejores operadores de TikTok Shop están enviando producto a entre 2.000 y 5.000 creadores por mes como mínimo, porque TikTok premia el volumen creativo. Por eso la mayoría de las marcas fracasan: intentan escalar con cinco creadores. Las marcas más grandes trabajan con miles. Paso 3: activar GMV Max. Solo Bloom dijo que su GMV Max genera un estimado del 60 al 70% del GMV [valor bruto de mercancía] total de su cuenta. Esta es la parte que la mayoría de las marcas no entiende: GMV Max automáticamente toma los videos de afiliados, el contenido orgánico, los anuncios pagos, los posteos de creadores, y empuja a los de mejor rendimiento. A escala, TikTok literalmente se convierte en una máquina automatizada de compra de medios para vos. Paso 4: usar TikTok Shop como motor de efecto halo. Bloom dijo que un sabor de San Valentín se agotó en 24 horas y provocó que las ventas en Amazon aumentaran 10 veces en un solo día. Otro producto aumentó las búsquedas de marca en Amazon en un 40% e impulsó las ventas en Target un 30% semana tras semana. Tiene sentido, estamos viendo lo mismo. TikTok Shop no solo genera compras dentro de TikTok. Genera demanda en todos lados: Amazon, retail, sitio web, anuncios de Meta, búsquedas de Google, y mucho más. Paso 5: reciclar los videos ganadores de TikTok Shop convirtiéndolos en anuncios de Meta. De repente tenés cientos de anuncios UGC: prueba social, mayor autoridad, creatividades con CAC [costo de adquisición] más bajo, volumen de testeo constante. Y las marcas más grandes no usan TikTok Shop como un marketplace. Lo usan como una capa de infraestructura de adquisición de clientes. Comenten 'shop' para conseguir la estrategia completa.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro pequeño abajo, imagen de apertura tipo captura de video/entrevista con el texto 'over 30,000 videos published' sobre fondo rosa y logo de TikTok Shop, clip de una creadora con auriculares al aire libre sosteniendo el producto frente a cámara, foto de un exhibidor de latas Bloom sabor manzana, remera negra.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de cita/declaración de un cofundador real ('¿vieron lo que dijo...?') que da autoridad y actualidad; estructura de pasos numerados (5 pasos) que se siente accionable; cifras impactantes (30.000 videos/mes, ventas 10x en un día) que generan asombro; cierre con incentivo para comentar y recibir la estrategia completa.</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>sí — reutiliza clips de creadores y capturas existentes, sin filmación propia costosa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Alex Hormozi</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ahormozi/video/7669294663844580621</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento de una consultoría/llamada estilo pregunta y respuesta donde el dueño de un proveedor de apoyo para discapacidad en Australia (negocio con precio topeado por el gobierno) pregunta cómo debería estructurar ingresos y márgenes para poder vender su empresa, y recibe consejos concretos sobre cómo generar margen y volverla más atractiva para la venta.</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Yo manejo un proveedor de apoyo para discapacidad en Australia. Es un esquema financiado por el gobierno, con precio topeado, altos requisitos de cumplimiento normativo, no podés facturar por adelantado. El año pasado facturamos un millón y medio, con márgenes brutos del 30%. Este año estamos achicando para enfocarnos en el público objetivo, porque antes aceptaba plata de cualquiera y era una pesadilla. Mi pregunta es: ¿cómo tendrían que verse los ingresos, el margen neto y el organigrama para poder venderla? ¿Y vale la pena? Sí. Bueno, desde la perspectiva de qué tan vendible es, digamos que podés vender cualquier negocio. La pregunta es a quién se lo querés vender y a qué precio, o a qué múltiplo. Así que tenés que pensarlo al revés, partiendo del objetivo. Por ejemplo, yo podría comprarte el negocio hoy por cero dólares, para ponerlo como un extremo hipotético. Entonces, más específicamente, ¿qué resultado querés? Sí, me encantaría venderlo por 500 mil dólares. Y si pudiera hacerlo en los próximos dos años, sería increíble. Servicio recurrente. Recurrente, sí. ¿Es pegajoso, en el sentido de que retenés a la gente de un año al otro? Sí, más o menos. La gente se queda alrededor de 12 meses. Bueno, entonces no es pegajoso, porque se van. Bien. Eso es lo que va a hacer que el negocio sea más viable. Además, lo va a convertir en algo que capaz no vas a querer vender, porque el objetivo de construir un negocio vendible es construir algo que no quieras vender, porque genera mucha plata. Ese es el objetivo. Bueno, entonces 500 mil dólares. Dijiste que tenés 30% de margen bruto. ¿Cuál es el margen neto? El margen neto ahora mismo es prácticamente nada. Empecé... sí, empecé otro negocio, y eso absorbió todo. Bueno, si no hubieras empezado el otro negocio, ¿cuál hubiera sido el margen si no hubieras fundido toda la plata? Doce y medio por ciento. Bien. Que en realidad, si tu margen bruto es 30, hacer doce y medio no está mal, relativamente. Sí creo que con 30% de margen bruto es muy difícil hacer funcionar un negocio. Y cuando tenés precios fijados por el gobierno, tenés dos opciones disponibles. Opción uno: vender un 'seguro plus', es decir, hacer lo que está cubierto por el gobierno más otras cosas si el cliente las quiere, que parte de la gente está dispuesta a pagar de su bolsillo. Y eso puede generar una diferencia material en la ganancia neta del negocio. Entonces, aunque solo el 10% de la gente esté dispuesta a pagar, digamos, un 50% más, eso duplica la ganancia del negocio. Opción B, y podés hacer las dos juntas, dicho sea de paso: cuando tenés un negocio con precio topeado, tenés que crear margen desde la base, lo que significa que tenés que cortar todos los gastos, absolutamente todo. Si el objetivo fueran 500 mil, yo diría: voy a hacer costo más margen en el frente, voy a recortar margen atrás, y voy a tratar de ver qué puedo hacer para que la gente se quede dos o tres años. Si lográs esas tres cosas, probablemente recreés el margen que tenías, y ahí vas a poder vender la empresa.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Plano fijo único, estilo videollamada/consultoría grabada: hombre con gorra puesta al revés, barba grande, camisa a cuadros, sentado a una mesa de madera con el celular apoyado, fondo negro liso. Subtítulos incrustados en cada frame con palabras clave en negrita (números como '30%', '10%'). No se ven cortes de cámara ni gráficos adicionales en los frames muestreados: estética cruda de llamada de consultoría/podcast.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: pregunta real de un oyente con cifras concretas de su propio negocio (1.5 millones de ingresos, 30% de margen), que genera identificación inmediata en dueños de negocios de servicios. Estructura: formato pregunta-respuesta de consultoría en vivo, pensando en voz alta y llegando a un marco replicable (opción A/opción B). Gatillo: autoridad (experto reconocido resolviendo un caso real) + caso real con números + utilidad práctica inmediata (framework aplicable a cualquier negocio con precio topeado).</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo necesita grabar una consulta o llamada real (Zoom/Riverside) con buena luz y subtitularla, sin edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>10900</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7637531758681967903</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Análisis de la estrategia de marca de Prequel, marca de skincare que facturó 18 millones de dólares desde su lanzamiento, mostrando cómo combina volumen de UGC, marketing educativo, crecimiento product-led y omnipresencia en canales para construir una comunidad tipo 'culto' alrededor de la marca.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Prequel facturó 18 millones de dólares desde su lanzamiento y es una de las marcas de skincare de más rápido crecimiento en este momento. Prequel no solo está escalando, está construyendo un culto. Así es como lo lograron. No dependieron de un solo canal de venta. Construyeron un motor de obsesión multicanal. Primero, volumen creativo, con UGC constante inundando los feeds. Ganchos únicos usando los mismos beneficios y los mismos resultados en cada video. Lo repiten hasta que se vuelve innegable. Segundo, marketing basado en educación primero. No solo venden productos, crean 'insiders' desglosando los ingredientes, desmintiendo mitos comunes, haciendo que el cliente se sienta más inteligente que el resto. Así es como convertís compradores en creyentes. La tercera cosa es el crecimiento tipo 'product-led'. Este producto realmente pega cuando alguien lo prueba. No solo les gusta, lo comentan online. Y así es como el boca en boca se potencia. Cuarto, dominación de la distribución. Están en todos lados a donde vaya tu atención. Están en TikTok, en Meta, orgánico, pago. No los descubrís una sola vez, los ves en todos lados al mismo tiempo. Eso no es marketing, es directamente omnipresencia. Esto es lo que a la mayoría de las marcas se les escapa. No solo están corriendo anuncios, están reforzando la identidad de su usuario. Cada video empuja la misma visión del mundo, cada comentario construye comunidad, y cada cliente siente que forma parte. Así es como se construyen las marcas de culto. No son solo clientes, son un grupo de gente que cree en lo mismo. Y así es como escalás a ocho cifras rápido. Comentá 'cult' y te mando mi guía para construir tu propia marca tipo culto.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Formato split-screen: mitad superior alterna entre b-roll de aplicación de un producto de skincare (primer plano de piel, texto 'SOOTHING CREAM ABSORBS EASILY'), una captura tipo making-of/entrevista rotulada 'Nerding out with Dr. Sam / Gleanser + Glycolic' con recuadro rojo de énfasis, y una captura de la biblioteca de anuncios de Meta mostrando la página de 'Prequel Skin' con conteo de anuncios activos (~45 results) y una flecha roja de señalización; mitad inferior es el mismo presentador de remera clara y campera oscura hablando a cámara con micrófono de podcast. Subtítulos incrustados sincronizados con el guion.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: cifra concreta (18 millones de dólares) + palabra polémica/llamativa ('cult', culto) que genera curiosidad. Estructura: cuatro pilares numerados (volumen creativo, educación, product-led growth, omnipresencia) con una síntesis conceptual al cierre ('no son clientes, son creyentes'). Gatillo: número concreto + curiosidad + investigación real mostrada en pantalla (Meta Ads Library) que da sensación de autoridad; CTA de comentario ('cult').</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>sí + requiere investigar la marca (Meta Ads Library es gratis) y conseguir algo de b-roll del producto, sin equipo caro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7641609837616401695</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Video que presenta cinco formatos de anuncios (paid partnership, estilo notas del iPhone, DMs falsos de iPhone, historias POV de Instagram y desgloses con imágenes de IA) que, según el creador, están usando las marcas de más rápido crecimiento porque ya no parecen publicidad tradicional.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Las marcas de más rápido crecimiento online están usando estos cinco formatos de anuncios ahora mismo, y lo más loco es que la mayoría ni siquiera parecen anuncios. El primero son los anuncios de paid partnership (colaboración paga). Las marcas se asocian con creadores porque la confianza convierte mejor que los comerciales pulidos. Ahora se siente nativo, se siente orgánico y se siente creíble. El creador se convierte en el puente entre la audiencia y el producto. Es un formato que se puede escalar infinitamente: sumás más creadores y conseguís más contenido sin tener que hacer vos mismo los rodajes. Es increíble. Segundo, los anuncios estilo 'nota'. Están explotando ahora mismo. Las marcas literalmente hacen anuncios que parecen capturas de pantalla de la app de Notas del iPhone, o una simple lista de recordatorios. ¿Por qué? Porque se siente educativo, es de baja presión y es fácil de consumir, casi como si un amigo te recomendara algo casualmente. El tercero son los DM tipo iPhone, probablemente uno de los formatos de mayor conversión que estamos corriendo ahora mismo. Son hilos de mensajes de texto falsos, capturas de iMessage, conversaciones naturales: 'Ok, estaba equivocada con estas gomitas'. Ese formato funciona porque se siente real, no está guionado, no es corporativo, es solo una captura de pantalla en tu chat. El cuarto son los anuncios estilo historia POV de Instagram. Parecen alguien subiendo casualmente a su historia, sacándole una foto al producto que acaba de recibir, mostrando el producto en la vida real, con sus opiniones rápidas, sus reacciones rápidas, qué piensa del producto. Y se mezcla en el feed en lugar de interrumpirlo. Por eso la retención es tan alta. Quinto, los anuncios de desglose con imágenes de IA. Esto está explotando ahora mismo porque las marcas los pueden hacer increíblemente rápido. Hacés visuales con IA: gráficos educativos, antes y después, desgloses de ingredientes, explicaciones de problema-solución, e imágenes de un solo producto con cientos de variaciones de anuncios. Las marcas más grandes ya no dependen de un solo anuncio, están construyendo ecosistemas creativos enteros alrededor de estos formatos. Así es como las marcas están escalando en 2026: más variaciones, más contenido nativo, más confianza, más datos para el algoritmo. Si querés conseguir estos cinco formatos exactos, comentá 'creative' y te mando la herramienta.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Formato listicle con evidencia visual real: para cada uno de los 5 formatos de anuncio se muestra una captura de pantalla de un ejemplo real (biblioteca de anuncios de Meta con la página 'Prequel Skin', un 'swipe file' estilo Pinterest con un anuncio de la marca rhode, una captura de un hilo de iMessage falso de 'The Absorption Company' promocionando un producto GLP-1) en la mitad superior, mientras el presentador narra en la mitad inferior. Edición con muchos cortes de pantalla acorde al ritmo de la enumeración.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: promesa de que hay anuncios 'que ni siquiera parecen anuncios', apelando a la curiosidad y a un cambio de paradigma. Estructura: listicle de 5 formatos, cada uno con nombre, por qué funciona y ejemplo visual real. Gatillo: número concreto (5), curiosidad, utilidad práctica inmediata (framework copiable) + evidencia real en pantalla; CTA de comentario ('creative').</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>sí + se arma con capturas de pantalla reales de anuncios (Meta Ads Library es gratis) y un guion tipo listicle, sin filmación elaborada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7659800682131737886</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>El creador analiza por qué la marca de estilo de vida de Meghan Markle, As Ever, está fallando pese a la fama de su fundadora, señalando falta de sistema de marketing, línea de productos dispersa y la salida de Netflix como inversor.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Por qué la marca de celebridad de Meghan Markle está en problemas. No todas las marcas de celebridades despegan. Y la marca de Meghan Markle, As Ever, es una clase magistral de cómo una atención masiva igual puede convertirse en un desastre de marketing. Esta es la Duquesa de Sussex. Tenía reconocimiento global, un programa de Netflix, millones de personas mirando, y productos que inicialmente se agotaron. Uno pensaría que esta marca sería absolutamente imparable, pero después todo empezó a desmoronarse. El contenido en redes sociales se siente más como una página de estilo de vida personal que como un verdadero motor de crecimiento de contenido. No hay una máquina publicitaria masiva inundando el mercado. El sitio web se ve hermoso, pero no está agresivamente optimizado para convertir, aumentar el valor promedio de pedido, impulsar suscripciones, o poder convertir gente a escala. La línea de productos se siente dispersa. Hay mermelada, té, vino, velas. ¿Qué tienen que ver todas esas cosas entre sí? No hay un producto estrella obvio ni una razón clara para que los clientes vuelvan. Y ahí llegó la señal de alerta más grande de todas. Netflix terminó su alianza de inversión con As Ever. Esto es absolutamente impactante. Tenían a una de las compañías de medios más grandes del mundo ayudando a lanzar esta marca, y ahora Meghan tiene que hacerla crecer de forma independiente. Este es el verdadero problema. Que la fama te dé atención no garantiza automáticamente que construyas retención, ingresos recurrentes, adquisición paga o distribución escalable. As Ever no tenía un problema de reconocimiento. Tenía un problema de sistemas. Porque ni el fundador más famoso del mundo puede salvar una marca sin la infraestructura para convertirla en un motor de adquisición que genere ventas predecibles. Y eso es... [el video se corta acá]</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Selfie/talking head con micrófono de podcast en mano, hablando a cámara en lo que parece una cocina o living con flores y frascos de mermelada de fondo. En otros frames aparece recortado por croma sobre capturas de pantalla del sitio web de la marca As Ever y una foto de Meghan Markle, como si estuviera parado delante de esas imágenes. No se ven subtítulos de texto agregados por el editor en los frames capturados. Cortes entre el video de él hablando y las capturas superpuestas de pantalla/fotos.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con pregunta contraintuitiva sobre una celebridad global (Meghan Markle) que 'está fracasando' pese a fama y recursos, lo que genera curiosidad inmediata y algo de polémica. Usa autoridad de análisis de marketing con evidencia concreta (falta de ads, línea de producto dispersa, salida de Netflix) en una estructura de problema, evidencia, causa raíz y lección generalizable.</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo necesita cámara, micrófono y capturas de pantalla de la marca analizada, sin edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>9602</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7663051854296796438</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Reacción/análisis a la noticia de la quiebra de Prime Hydration (la marca de bebidas de Logan Paul y KSI), explicando que el éxito inicial basado en hype y fama de los fundadores no se supo adaptar con el tiempo hacia una estrategia de marketing más racional.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Prime Hydration quebró. ¿Te sorprende? KSI y Logan Paul facturaron más de 1200 millones de dólares en sus primeros 18 meses de negocio. Todo construido sobre el hype, la atención, y el poder de las marcas personales de los fundadores. Fallaron fundamentalmente en adaptar su estrategia de marketing. Apalancarse en Logan Paul y KSI al principio funcionó mejor de lo que cualquiera se hubiera imaginado. Lo pasearon en una gira mundial como si fuera un recital, y trataron los anuncios de puntos de venta como lanzamientos de ropa (drops). Casualmente, yo también generé más de 1200 millones de dólares para mis clientes en los últimos 11 años. Esto es lo que tienen que hacer: necesitan pasar del hype y la promoción agresiva a construir el vínculo de por qué deberías comprarlo, creando una lógica detrás del propósito. Digo, ellos patrocinan algunos de los clubes deportivos más grandes del planeta, y a los atletas y creadores más grandes también. Pero más allá del título llamativo, no lograron mostrar a los atletas realmente usando y beneficiándose del producto. El hype solo puede sostener hasta cierto punto. Es hora de adaptarse o morir, Prime.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Formato de reacción a noticia: mitad superior es una captura de un artículo periodístico real (sección Finance/Business, titular sobre la quiebra de la empresa australiana de Prime, con foto y firma del autor, fecha 10 de julio de 2026); mitad inferior es un hombre (pelo canoso/entradas, remera polo azul, sosteniendo un objeto pequeño en la mano) hablando a cámara. Subtítulos incrustados sincronizados con el guion ('did over', 'concert', 'sponsored').</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: noticia de actualidad/polémica ('Prime Hydration quebró. ¿Te sorprende?') sobre una marca masiva de celebridades reconocidas (Logan Paul, KSI). Estructura: contraste entre lo que funcionó (hype inicial) y lo que falló (no adaptar el mensaje), cerrado con un consejo concreto y un juego de palabras final. Gatillo: actualidad/polémica + autoridad (menciona resultados propios de 1200 millones de dólares) + número concreto.</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo necesita encontrar una noticia de negocios viral y grabar una opinión de experto en selfie, presupuesto mínimo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>9346</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7649037945722113310</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Explica un framework de 5 pasos para construir un 'ecosistema de distribución' de marca (Meta Ads, Google, Amazon/TikTok Shop, retail online y retail físico) donde cada canal potencia al siguiente.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Esta es la jugada de distribución que a toda marca le está faltando ahora mismo. Las marcas más grandes ya no están construyendo un solo canal de venta. Están construyendo un ecosistema de distribución. Y cada canal alimenta al siguiente. Acá va exactamente cómo funciona. La mayoría de las marcas arrancan con Meta Ads hacia Shopify. Ahí es donde empiezan, porque Meta te da feedback rápido. Te da datos de conversión, testeo de creatividades, insights de audiencia y validación de oferta. Y es consistente. Básicamente es tu motor de testeo para lanzar y escalar cosas. Y una vez que encontrás el producto y el mensaje ganador, todo lo demás se vuelve más fácil. Después del paso dos, Google captura la demanda. Después de que Meta empieza a escalar, la gente empieza a buscar tu marca online: los nombres de tus productos, tus reseñas, tus comparaciones. Y ahora la búsqueda de Google se convierte en una máquina de captura de demanda. Por eso el volumen de búsqueda de marca importa tanto cuando estás corriendo anuncios. Meta crea demanda. Google captura esa demanda. Hay una diferencia enorme. Paso 3: sumás Amazon y TikTok Shop para amplificar tu distribución. Acá es donde las marcas empiezan a multiplicar puntos de contacto. Amazon te da confianza, envío rápido, poder de ranking, acumulación de reseñas e intención de compra de marketplace. TikTok Shop te da distribución por creadores, escala de afiliados, descubrimiento viral, prueba social y velocidad de contenido. Entonces ahora los clientes te ven en todos lados. Y acá está la parte importante: TikTok Shop muchas veces impulsa directamente las ventas de Amazon, y Amazon muchas veces impulsa la confianza en el retail. Y el retail impulsa las tasas de conversión de Meta. Todo se potencia junto una vez que empezás a integrar esto. Paso 4: lanzás distribución mayorista y de retail online. Una vez que la marca tiene demanda, los retailers empiezan a prestarte atención. Entonces ahora entrás a Walmart online, Target online, GNC, CVS, cadenas regionales y retailers especializados. Por qué esto importa: porque la distribución en retail empieza a generar legitimidad. Y los clientes empiezan a pensar, si está en Target, tiene que ser real y tiene que funcionar. Esa confianza sola mejora el rendimiento en todos tus canales. Los anuncios de Meta convierten mejor, las tasas de conversión de Amazon suben. El contenido de creadores [?] rinde más fuerte. La búsqueda de marca crece, el retail se convierte en marketing. Y ahí empieza el desborde. No es solo el paso de ventas. Número 5: distribución en retail físico. Acá es donde las marcas se vuelven dominantes. Ahora el cliente te ve en todos lados: en Meta, creadores de TikTok, listados de Amazon, Google, góndolas de Target, Walmart, muchísimo más, todo al mismo tiempo. Ese nivel de omnipresencia crea memoria de marca. Y una vez que eso empieza a pasar, tu CAC [costo de adquisición; en el audio se oye 'cache'] empieza a bajar, porque el cliente ya sabe quién sos antes incluso de hacer clic. Este es el cambio más grande que está pasando en e-commerce ahora mismo. Las marcas ganadoras ya no dependen de un solo canal. Están construyendo modelos de distribución interconectados donde cada plataforma fortalece a la siguiente. Así es como las marcas de consumo masivo [CPG, en el audio se oye 'CBG'] modernas escalan a nueve cifras al año. Comentá 'CPG' y te mando la estrategia completa.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Talking head/selfie con micrófono, con gráficos animados superpuestos sobre fondo blanco con textura de puntos: logos de marcas reales (Bloom, RYSE, Olly) e íconos de Meta, Shopify, Amazon, Google y Target conectados con flechas. Estilo explicativo con diagramas de flujo simples que ilustran cada paso del embudo de distribución.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de FOMO ('esto se le está escapando a toda marca') más promesa de framework accionable numerado (pasos 1 a 5), con marcas reales como ejemplo y beneficios cuantificables percibidos, cerrando con CTA de comentario para generar leads. La estructura paso a paso con gráficos sostiene la atención pese a la duración larga (140 seg).</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>no + requiere diseño de motion graphics/diagramas personalizados que exige más tiempo y habilidad de edición que un video parado hablando a cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>8623</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7625663762128784671</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney, estratega creativa publicitaria, presenta en formato 'qué haría yo si trabajara en esta marca' un análisis de la biblioteca de anuncios de Oats Overnight (avena overnight) y propone estrategias de partnership con creadores y segmentación de audiencia basada en reseñas de clientes.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Esto es lo que hago como estratega creativa en Oats Overnight: uso 'cloud co-work' [?, transcripción ambigua, posible herramienta de IA] para correr un análisis de su biblioteca de anuncios (ads library), y vi que de los 206 anuncios activos que tienen ahora mismo, solo el 15% son anuncios de partnership (colaboración con creadores); bastante bajo para una marca de su tamaño, y no les está yendo tan bien. Así que hay dos estrategias que probaría para que los anuncios de partnership funcionen mejor para ellos. Número uno: su contenido de 'warehouse' (depósito) está funcionando buenísimo, así que en realidad querría crear una página completamente separada donde podamos dar de alta anuncios solo para el equipo de warehouse, porque es como fruta al alcance de la mano. Y después querría trabajar con creadores millennials mayores y de la generación X que sean parte de familias trabajadoras, pensá en enfermeras, docentes, obreros de la construcción. Sus creadores top ahora mismo están yendo por los ángulos de fitness y proteína, y se sienten como creadores 'profesionales'; sin embargo, su creativo de anuncio con mejor rendimiento en realidad se enfoca en la idea de la 'mañana súper ocupada', así que querría trabajar con creadores que realmente vivan eso. Por último, de las personas (perfiles de cliente) que generé a partir de todas sus reseñas, noté que las que buscaban saciedad ('fullness') en realidad aparecían menos, pero tenían la mayor intensidad emocional en sus reseñas, así que querría poner a prueba este insight combinándolo con la persona que más apareció en todas las reseñas: la 'buscadora de consuelo' (comfort craver). Están obsesionadas con todos los distintos perfiles de sabor, también son muy nostálgicas, y los beneficios para la salud de Oats Overnight son como algo secundario para ellas. Así que querría hacer una serie de estáticos y videos para ver si podemos desbloquear aún más a esa audiencia súper cargada emocionalmente. Avísenme qué marca debería hacer después.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Talking head selfie en interior (living/cocina con estantería, plantas y trípode de fondo), sosteniendo un micrófono inalámbrico tipo cápsula. Sobre la parte superior de la pantalla se superpone una captura/mockup de un dashboard de análisis ('Oats Overnight Ad Library Analysis' con métricas: 206 anuncios, 32, 79%) a modo de gráfico ilustrativo. Subtítulos en pantalla. Formato vertical, plano fijo con imagen de pantalla superpuesta en la mitad superior.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de autoridad y utilidad inmediata: se posiciona como especialista mostrando trabajo real y gratuito ('esto es lo que haría yo') para una marca conocida, generando curiosidad de 'aprender del ejemplo real' y prueba social (analiza datos reales, no teoría). Estructura clara en pasos numerados con cifras concretas (206 anuncios, 15%) que dan credibilidad analítica, y cierre con llamado a la interacción que genera comentarios y contenido en serie. Gatillos: autoridad + caso real con datos + formato de serie + utilidad práctica para otros marketers.</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo requiere cámara de celular, un micrófono barato y capturas de pantalla de herramientas de análisis reales o simuladas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>8514</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7665002675112512798</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Compara las estrategias de TikTok Shop de dos marcas de bebidas energéticas, Bum Energy y Ghost: volumen de ventas, tasa de recompra, ejército de creadores/afiliados y estrategia de sabores como motor de contenido.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>¿Quién tiene mejor marketing en TikTok Shop, Bum Energy o Ghost? Las dos marcas la están rompiendo totalmente. Bum Energy vendió más de 36.000 productos en TikTok Shop. Son partners oficiales con la insignia de tienda oficial, tienen un 18% [?, en el audio '18 repeat purchasers'] de compradores recurrentes, y están sumados básicamente a todos los programas de TikTok Shop que te puedas imaginar: cupones, ofertas especiales, promoción inteligente, campañas de vendedor, descuentos para seguidores. Saben que si alguien sigue la cuenta, es más probable que le compre. Esa simple acción de un clic. Pero acá está lo que hace peligrosa a Bum Energy: tienen un ejército de creadores. Miles de influencers están empujando su producto con reseñas de producto, pruebas de sabor, contenido de gimnasio, videos de entrenamiento, videos de reacción, packs de sabores, comparaciones, desgloses de producto, y contenido educativo sobre bebidas energéticas. Y los comentarios están haciendo la mitad de la venta. La gente debate los sabores, la gente pregunta cuál sabe mejor, la gente dice que necesita probarlo. Así es exactamente como TikTok Shop impulsa las compras por impulso. Ahora mirá a Ghost. Ghost lleva años en el mercado, pero en TikTok Shop se sigue moviendo con un volumen serio. Más de 61.000 bebidas vendidas, 86.000 productos vendidos en total, pero solo un 14% [?, en el audio '14 repeat shop buyers'] de compradores recurrentes en la tienda. Y eso te dice la estrategia ahí mismo. Están usando TikTok Shop para impulsar una adquisición masiva de clientes nuevos, porque Ghost ya tiene distribución minorista en todos lados. Entonces cada venta en TikTok Shop no solo genera ingresos, genera reconocimiento de marca alrededor del producto. Genera prueba de producto. Genera impulso. Genera un efecto halo en toda la marca. Y su estrategia de sabores es genial: Welch's, Warheads, sabores ácidos, frambuesa azul, alianzas de sabores limitados una locura que hacen que la gente quiera probar el producto de inmediato. Y los creadores convierten eso en contenido de sabores: pruebas de sabor, hallazgos en tienda, videos de entrenamiento, clips de podcast, comparaciones de producto, rankings de sabores, reacciones en el punto de venta. Así que Bum Energy está construyendo uno de los motores de creadores nativos de TikTok Shop más fuertes, pero Ghost está usando TikTok Shop como una máquina de reconocimiento de embudo completo que se derrama hacia el retail. Las dos están ganando. Las dos entienden la distribución liderada por creadores. Las dos saben que TikTok Shop no es solo un canal de ventas. Es un motor de contenido, un motor de creadores, y un motor de demanda para el retail, todo al mismo tiempo. Pero, ¿quién pensás que lo está haciendo mejor, Bum Energy o Ghost?</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Talking head con micrófono, superpuesto sobre capturas de pantalla reales de la tienda de TikTok (perfil de Bum Energy con insignia oficial y métricas de ventas), video de manos mostrando el producto físico (lata/pote de Bum) con subtítulo de una palabra ('THOUGHTS'), y clip de otro creador sosteniendo un envase de Ghost en un gimnasio con cartel 'No excuses' de fondo y fragmento de subtítulo ('...LLY HAS'). Mezcla de screen recording, clips de video de terceros y presentador a cámara.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de comparación directa entre dos marcas del mismo nicho que invita al debate. Aporta cifras concretas de ventas y recompra como prueba de autoridad, y usa evidencia visual (capturas de la tienda, clips de creadores) para reforzar cada punto. Cierra pidiendo la opinión del espectador, lo que fomenta comentarios.</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>sí + requiere investigar datos públicos de TikTok Shop y grabarse comentando capturas y clips ya existentes de las marcas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="88" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Gary Vaynerchuk (GaryVee)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>6936</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@garyvee/video/7665774955149282574</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento de podcast donde Gary Vaynerchuk defiende que la cantidad de contenido producido es un ingrediente clave -y subestimado por orgullo- para lograr una pieza que 'rompa', más allá de la calidad.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>La cantidad es una parte secreta de la ecuación que nadie que tenga orgullo quiere admitir que es verdad. Existe este conflicto inherente entre calidad y cantidad que tantos artistas e individuos con ideología quieren sostener. Pero la verdad es que la cantidad es un ingrediente increíble para lograr un quiebre. Son de verdad los turnos al bate para hacer la pieza de contenido que te cambia la vida. Y yo creo mucho en eso. Ahora bien, mucha gente va a hacer[?] 10.000 piezas de mierda y nunca lo va a lograr. La calidad tiene que ser parte de la ecuación. Pero esto lo vas a apreciar: la calidad es subjetiva. ¿Qué es lindo? ¿Qué es atractivo? ¿Qué es divertido? ¿No? La cantidad no lo es.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast con estética de estudio: hombre sentado en sillón de cuero, gorra negra, luz ambiente azul/púrpura, micrófono de brazo (boom) visible, pies apoyados en un banquito, en lo que parece una entrevista o programa grabado. Título fijo superpuesto ('Why Quantity Beats Quality (Most Of The Time)') más subtítulos dinámicos palabra por palabra sincronizados con el habla, típico de un recorte de podcast largo editado para formato corto.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: afirmación contraintuitiva que contradice una creencia común y 'orgullosa' de los creadores ('la cantidad es lo que nadie quiere admitir'). Estructura: tesis, matiz (la calidad también importa) y una frase filosófica memorable de cierre ('la calidad es subjetiva, la cantidad no'). Gatillo: polémica/contraintuitivo + autoridad de una figura reconocida del marketing + lenguaje directo y crudo que genera impacto.</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>sí + alcanza con una opinión fuerte y contraintuitiva grabada con celular y buen audio, aunque la estética de estudio con luces de color eleva un poco el piso de producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>4636</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670086856104496398</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial rápido que explica cómo usar la transcripción de una video sales letter (VSL) como insumo para que una IA (ChatGPT o Claude) genere una secuencia de emails de seguimiento que conviertan leads en llamadas agendadas.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Es muy útil si tenés un activo fundacional realmente sólido, como una video sales letter (VSL), que después podés usar para escribir tu email. Tomá la transcripción de esa video sales letter, la ponés adentro de ChatGPT o Claude, y le decís: 'quiero que me escribas una secuencia de emails de tres a cinco días para alguien que se suscribió a esta video sales letter pero no agendó una llamada para hablar conmigo'. Y ahora tiene el contexto de cuáles son tus puntos de dolor, deseos, etcétera, y lo va a volcar en esa secuencia de emails. Así, la persona pasa por las mismas cosas que te están consiguiendo llamadas agendadas en la VSL, pero ahora vas a empezar a conseguir llamadas agendadas desde los emails también. Yo uso la transcripción de mi video sales letter para escribir mis anuncios con IA, para escribir mis campañas de email, para escribir un montón de cosas, porque sé que en definitiva eso me funcionó en el pasado. Así que simplemente quiero extrapolarlo a cualquier otro medio que estemos usando.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Formato split-screen: mitad superior es el presentador (hombre con barba, remera blanca, micrófono inalámbrico solapa) hablando a cámara en lo que parece una habitación de hotel (cama con acolchado blanco, veladores, cuadro en la pared); mitad inferior muestra un diagrama dibujado a mano en una hoja de papel ('New Subscriber Sequence' con cajas para Intro, Case study/CTA y CTA, unidas por flechas). Subtítulos incrustados sincronizados con el guion.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: promesa de un 'truco' concreto de IA con resultado tangible ('convertir tu VSL en emails que convierten'). Estructura: instrucción paso a paso replicable (transcript → prompt → secuencia de emails) apoyada en un diagrama simple dibujado a mano. Gatillo: utilidad práctica inmediata + atajo/curiosidad + autoridad de experiencia personal.</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo necesita celular, papel y lapicera para el diagrama, y una cuenta de ChatGPT o Claude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>4592</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670084775046057229</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento de podcast donde un fundador que facturó 35 millones de dólares cuenta cómo aceptar invitaciones a eventos y podcasts, en lugar de rechazarlas, le generó una cadena de oportunidades de networking que describe como 'ponerse en una zona de suerte'.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Se me hizo muy fácil pensar 'no necesito ir a una mascarada, no necesito ir a hablar en este evento'. Pero una de las cosas que no estaba calculando ahí es la exposición de hablar con gente de distintos orígenes, con distintos negocios. Y cuando estoy hablando con esta gente, pensaba 'ah, mirá, tu problema más grande es la adquisición de clientes, yo soy realmente bueno en eso'. Y, ¿cómo hago para unir estas dos cosas? Ryan Pena, que es un emprendedor bastante grande en el espacio del e-learning para la gente. Ah, no, me llamó pidiéndome ayuda con su material de marketing. Y le di una mano. Y me dice 'che, tenés que venir al podcast, estoy en Las Vegas'. Y entonces fui a ese podcast. Mientras estaba ahí, entré a otros cuatro podcasts más, y me invitaron a hablar en un evento en California. Y después conseguí la oportunidad de hablar en el evento de Ryan en julio. A partir de ahí, es como que esa única decisión de ponerte, entre comillas, en una zona de suerte donde la suerte puede pasar, después expandió todo lo demás. Creo que la gente subestima ese aspecto de la colaboración. Creo que puede ser absolutamente enorme para destrabar el próximo nivel.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast/entrevista: dos personas en un estudio con micrófonos de marca 'W' sobre pie, fondo con una planta de flores rojas y luz ambiente violeta/rosa; se alterna entre plano dividido de ambos participantes y primeros planos individuales de quien habla (remera/camisa borravino). Título superpuesto con la cifra del entrevistado (founder de 35 millones de dólares que revela cómo 'tener suerte' en los negocios) y subtítulos incrustados sincronizados palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: cifra grande del entrevistado (35 millones de dólares) + palabra en tensión entre comillas ('lucky') que promete revelar que la suerte se puede fabricar. Estructura: anécdota personal con nombres y hechos concretos (Ryan Pena, podcasts, evento de julio) que ilustra la tesis. Gatillo: caso real + autoridad + reformulación de una idea abstracta (suerte) en algo accionable (exposición/colaboración).</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>sí + es una entrevista tipo podcast donde el guion es simplemente contar una anécdota real, aunque el estudio con micrófonos e iluminación de marca sube algo el piso de producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>4544</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670084499983666446</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Video de consejo de marketing que argumenta que el error más común de los dueños de negocio es sobrecomplicar su mensaje, y que la oferta se debe comunicar de forma extremadamente simple en los primeros segundos.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>En el marketing, en los anuncios y en el embudo, en realidad querés que sea absurdamente simple. Entonces no querés decir 'vamos a hacer coaching y consultoría, vas a tener acceso a todas estas llamadas'. Simplemente querés decir 'che, si sos esta persona, te vamos a poner un asistente virtual en tu negocio, y si no te lo hace crecer, no pagás'. No querés meterte en 'hay acceso a llamadas de coaching y a Slack y te vamos a ayudar', porque la verdad es que es demasiada información para que alguien entienda quién sos, y lo que realmente quieren es meterte en una caja. Bien, ¿es un coach o es una agencia de colocación, una agencia de reclutamiento? Como dije antes, tenés de tres a cinco segundos, así que no lo arruines tratando de sonar súper único. El marketing no es para eso.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Formato split-screen con dos videollamadas/grabaciones distintas: arriba, un hombre en un living (remera clara, puerta de madera, TV de fondo); abajo, otro hombre con anteojos y remera negra en una silla de oficina con panel acústico, cerca de un micrófono tipo boom con espuma. Título fijo superpuesto ('The worst marketing mistake 90% of business owners make') y subtítulos incrustados sincronizados, estilo entrevista/podcast a control remoto.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: cifra de alarma ('el 90% de los dueños de negocio comete este error'). Estructura: contraste entre un mensaje complicado (malo) y un mensaje 'estúpidamente simple' (bueno), con la regla de los 3-5 segundos como justificación. Gatillo: miedo a estar cometiendo el error común + número concreto + utilidad práctica inmediata.</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>sí + alcanza con una videollamada grabada entre dos personas y subtítulos automáticos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>4540</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670086375588367630</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Reflexión de un emprendedor sobre cómo los resultados de hoy (ventas, llamadas) casi siempre son consecuencia de decisiones tomadas 60 o 90 días atrás, y no de lo que se hace en el día a día inmediato.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>En mi experiencia, lo que suelo hacer es... digamos que hacemos algo y funciona muy bien. Empezamos a conseguir muchas llamadas o empezamos a conseguir muchas ventas. Pienso que es el ajuste que hicimos lo que nos está ayudando a escalar. Pero en realidad fue algo que hicimos hace 60 días o 90 días. Y eso me pasó una o dos veces. Pienso 'ah, estamos consiguiendo todas estas ventas por esto que hicimos ahora'. Pero en realidad, estamos consiguiendo todas estas ventas por cosas que hicimos hace 60 días. Mucha gente piensa 'voy a hacer esto hoy, y mañana va a terminar siendo el resultado de lo que hice hoy'. Pero casi siempre, la vida que estamos viviendo hoy, las experiencias que estamos teniendo hoy, vienen de decisiones que tomamos como mínimo 90 días atrás. Y la vida que estás viviendo hoy también viene de las decisiones que tomaste hace dos años, tres años, cinco años.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato de estudio tipo podcast que otros videos del canal (micrófono de marca 'W' sobre pie, fondo con planta de flores rojas, luz violeta ambiente): un hombre con remera/camisa borravino habla a cámara en plano medio fijo. Subtítulos incrustados palabra por palabra ('Working', 'right here.', 'the experiences').</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: cifra de contradicción tomada del título del video ('el 95% de los emprendedores está equivocado sobre esto'). Estructura: reflexión personal con ejemplo concreto (ventas de hoy explicadas por decisiones de 60-90 días atrás) que reformula la relación causa-efecto en los negocios. Gatillo: contraintuitivo + autoridad + introspección relatable para cualquier dueño de negocio.</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>sí + es una anécdota personal grabada en un estudio simple con buen micrófono, sin edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>4503</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7657206796494359839</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Video que presenta un framework de estrategia creativa para 2026 basado en definir personas/arquetipos de cliente, ángulos de mensaje, diversidad de formatos con creadores y landing pages únicas armadas rápidamente con Replit, usando como caso de éxito la venta de una marca por mil millones de dólares.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Una cosa: que se rompa el rendimiento de tu creatividad en realidad no tiene nada que ver con la pieza publicitaria en sí, tiene que ver con esto. Este es el framework para una estrategia creativa ganadora en 2026. Empieza con las personas: ¿cuáles son los arquetipos de tu cliente? ¿Cuáles son sus puntos de dolor, sus deseos? ¿Cómo les tenés que hablar? ¿Y cuáles son los grandes ángulos alrededor de los cuales querés desarrollar la creatividad? Y después, el siguiente nivel es asegurarte de tener un rango diverso de formatos creativos, incluyendo creadores. Como mínimo, para tus grandes ángulos creativos, vas a necesitar asegurarte de tener este tipo de formatos: un rango de activaciones con creadores, y video prescriptivo y contenido estático en cada punto del embudo. Y finalmente, lo que yo no suelo escuchar que los estrategas creativos mencionen: la landing page. Este es el verdadero final de la experiencia creativa, no solo cuando termina el anuncio. Por eso las marcas necesitan tener una experiencia de landing page única para sus mayores aprendizajes creativos. Y por lejos, la forma más fácil que encontré para hacer landing pages al vuelo es con Replit. Listicles, quizzes, y landing pages estilo overview se pueden pensar y lanzar en el mismo día. Lo que significa que, si sos estratega creativo, en realidad está en tu poder hacer esto. Grüns[?] se vendió hace poco por 1000 millones de dólares, y de hecho usan este mismo framework para sus mayores aprendizajes creativos. Sabían a quién venderle, qué tipos de formatos creativos hacer, y qué tipos de creadores deberían usar. Y sabían cómo cerrar esa experiencia con una landing page adecuada, que ahora se puede hacer en menos de media hora con Replit, lo cual es increíble. Sean honestos, estrategas creativos: ¿con qué frecuencia piensan en landing pages? Cuéntenme.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Formato split-screen: mitad superior muestra, en un momento, un gráfico/infografía diseñada ('CREATIVE STRATEGY 2026 — Framework' con columnas de personas, ángulos y niveles de embudo terminando en landing pages) y, en otro momento, una captura de resultados de búsqueda/noticias sobre la adquisición de la marca Grüns por Unilever por 1200 millones de dólares; mitad inferior es la presentadora (pelo pelirrojo, aros dorados, top negro) hablando a cámara con un micrófono inalámbrico solapa, en un living con sillón y almohadones.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: afirmación contraintuitiva ('lo que rompe tu rendimiento creativo no tiene nada que ver con la pieza publicitaria en sí'). Estructura: framework de 4 pasos (personas, ángulos, formatos, landing pages) ejemplificado con una infografía y un caso real de una marca vendida por mil millones de dólares. Gatillo: contraintuitivo + framework accionable + caso real de gran escala + pregunta final para generar comentarios.</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>sí + necesita armar una infografía simple (se puede hacer gratis en Canva) y apoyarse en un caso real de referencia, pero no requiere equipo caro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>4473</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7668715792929705229</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de una charla/taller en pizarra donde se explica un sistema de KPIs en cascada, desde la plata nueva a nivel CEO hasta métricas específicas para editores de video corto y compradores de medios.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Generalmente, la forma en la que querés distribuir los KPI en tu empresa es empezar desde arriba del todo e ir bajando de a poco. El KPI de tu director de medios podría ser la cantidad de alcance único que estás consiguiendo por mes. Entonces el diseñador gráfico está pensando: ¿cómo hago una pieza[?] que me consiga más alcance único para nuestro departamento, para que podamos ayudar a la empresa en general? El KPI, que es plata nueva, estamos en el nivel en el que lo tiene el CEO, lo tienen los directores, y la capa de abajo también lo tiene. Para nuestros editores de formato corto, es la cantidad de shorts publicados por día. Ese es el KPI para ellos, que lleva al KPI de compra de medios, que es alcance orgánico único, que lleva al KPI de marketing, que son llamadas agendadas de forma orgánica, que lleva al KPI de la empresa, que es plata nueva entrando. Y así es como te asegurás de que todos estén remando para el mismo lado.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de una charla/taller en vivo: un hombre (remera blanca con logo 'Scaling ___') parado frente a una pizarra blanca con anotaciones y diagramas a mano sobre KPIs, con una laptop en primer plano y cortinas oscuras de fondo (sala de conferencia/salón de evento). Un solo plano fijo de cámara, subtítulos incrustados en negrita blanca con palabras clave destacadas ('KPI').</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Gancho visual/textual directo ('robate nuestro sistema de KPIs de 8 cifras'), con la palabra 'robate/steal' apelando a obtener gratis algo valioso. Estructura: explica la cascada de KPIs desde arriba (CEO) hacia abajo (roles específicos), con ejemplos concretos por puesto. Gatillo: utilidad práctica directa + autoridad (resultado de 8 cifras) + sensación de estar accediendo a información interna/exclusiva.</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>sí + alcanza con grabar una charla o reunión real frente a una pizarra con el celular, sin edición elaborada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>4460</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7667259303132220685</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala explica por qué la marca es la ventaja competitiva más fuerte frente a la publicidad paga, porque es lo único que la competencia no puede copiar y permite cobrar precios más altos.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Creo que hay un cambio enorme en el mercado ahora mismo, de la publicidad paga tradicional al contenido orgánico. Construir comunidades, que la gente te conozca, le gustes y confíe en vos, y construir una marca. Fijate en todos los grandes, los que la están rompiendo -y no me pongo en esa categoría-, pero todos se están moviendo hacia el contenido orgánico online. Y de nuevo, cuando hablamos de qué te hace diferente de tus competidores: si es solo el material de tu curso, no alcanza. Si es solo tu servicio, no alcanza. Si es tu marca, algo que literalmente lleva años construir, ahí empezamos a hablar de algo que la gente no puede copiar. Nadie puede ser vos, o nadie puede ser tu marca. Y eso te permite vender cosas que están, entre comillas, "comoditizadas", pero otra gente las compra a un precio más alto del que pagarían si las consiguieran en otro lado.</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Talking head filmado de pie en lo que parece un evento o taller en vivo (cortinas oscuras, ventana con luz natural detrás), remera blanca con logo "Scaling School", gesticula mucho con las manos. Al inicio hay una placa de título con texto grande en negro sobre fondo claro y la palabra clave resaltada en naranja/dorado ("branding"). Luego subtítulos progresivos palabra por palabra en blanco/negro con contorno, tipografía bold. Un solo plano, cámara vertical fija.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Arranca con una afirmación de cambio de paradigma en el mercado (de anuncios pagos a contenido orgánico), que combina curiosidad con autoridad de alguien que ya trabaja con negocios grandes. Estructura en contraste: lo commoditizable (curso, servicio) versus lo inimitable (la marca), y cierra con el beneficio concreto de poder cobrar más. El gatillo es el argumento contraintuitivo (la marca vale más que el producto) reforzado con autoridad.</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo necesita cámara, un guion con una idea contraintuitiva y buenos subtítulos; no requiere edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>4436</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7666145935050673422</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala cuenta cómo detectó que su equipo de ventas estaba atrayendo al tipo de cliente equivocado y explica la técnica de "reverse engineering" a partir de los mejores clientes para ajustar todo el mensaje de ventas, anuncios y redes.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Le pregunté a mi equipo de ventas: ¿cuáles fueron sus llamadas de venta favoritas de los últimos 30 días? Como, ¿quiénes son? Tipo, si pudiera hacer que cada llamada de venta fuera igual a esta persona, amaría mi trabajo, y bueno, optimizamos en base a eso. Hicimos esto hace poco. Le pedí a mi director de ventas que lo hiciera, y lo hizo durante todo el mes de junio. Y estaba mirando los datos ahí y pensé: ¿estás seguro de que esto es correcto? Porque en junio lanzamos una oferta nueva para ayudar a lanzar ofertas a, eh, ese tipo de gente. Expertos que necesitan lanzar una oferta online. Y pensé: no, no, no. Nosotros creamos esa oferta -de la que voy a hablar más adelante- solo para capitalizar a todos esos principiantes que sí pasan por mis embudos. Pero no quiero atraer a más gente así. Esas no son las mejores personas para trabajar. Quiero trabajar con gente que ya la está rompiendo, y ayudarlos a romperla todavía más. Entonces, en su primer documento -y no es que lo esté criticando, les estoy mostrando lo que a ustedes les podría pasar- si simplemente toman todas sus llamadas de venta y todos sus clientes, van a conseguir más de lo mismo que ya tienen. Pero a menos que amen absolutamente cada llamada de venta que toman y cada cliente que consiguen, tienen que elegir a dedo a los mejores. Aunque sean solo cinco o diez. Elijan a dedo a los mejores absolutos y después construyan todo de manera reversa a partir de ellos. Entonces, ¿qué dice tu carta de ventas en video? ¿Qué dice el copy de tu anuncio? ¿Qué dice tu video de YouTube? ¿Qué dice la bio de tu Instagram? Todo eso tiene que estar apuntando exactamente a esa persona.</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Talking head de pie detrás de un atril/mesa de madera con una MacBook, botella de agua y celular sobre la mesa, pared blanca lisa de fondo, remera polo verde oscuro y pantalón chino claro. Subtítulos progresivos palabra por palabra en blanco/negro. Plano fijo, sin cortes visibles, cámara vertical.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Abre con una anécdota concreta y curiosa (le pregunta a su equipo de ventas cuáles son sus llamadas favoritas), con un giro donde descubre que su propia oferta atraía al cliente equivocado. Estructura de caso real, seguido de autocrítica (vulnerabilidad/autenticidad) y cierre con un framework accionable (reverse engineering de mejores clientes) aplicado a canales concretos. El gatillo es el storytelling personal combinado con un método replicable.</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>sí — alcanza con una cámara fija, un escritorio y una anécdota real bien contada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>4414</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7666146063555890445</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala explica que la causa más común de que un negocio no escale es la falta de métricas y seguimiento riguroso de los anuncios, usando el ejemplo de clientes que apagan campañas sin saber por qué dejaron de funcionar.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Una de las grandes razones por las que la gente no escala. Y a esta altura ya trabajamos con un par de miles de dueños de negocio ayudándolos a escalar tal cual están, porque simplemente no conocen sus números. No te puedo decir la cantidad de veces que me subo a una llamada con un cliente y me dicen: "ah, veníamos probando esta estrategia de anuncios, pero dejó de funcionar". Y yo les digo, buenísimo, metámonos más profundo en por qué dejó de funcionar, porque muchas veces hasta la podemos revivir. Entonces, ¿por qué dejó de funcionar? "Ah, y bueno, dejamos de recibir tantas llamadas agendadas". Bien, ¿aumentó tu costo por clic? ¿Bajó tu tasa de clics? ¿Fue la conversión de tu opt-in? ¿La conversión de lead a reserva? ¿Pasó algo con los setters? Y me dicen: "ah, la verdad que no sé. No lo miré tan a fondo. Directamente apagamos los anuncios". Y muchas veces no tienen ningún tipo de seguimiento ni de métricas implementadas. Y para poder escalar la inversión, tenés que tener un seguimiento implacable.</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Selfie/talking head sentado en un home office, estantería de fondo con libros, planta y lámpara decorativa, micrófono profesional de podcast grande a cuadro, remera clara, pulsera dorada, sostiene un lápiz/stylus sobre una tablet. Subtítulos progresivos palabra por palabra en blanco con contorno negro. Plano fijo cerrado.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Empieza con una estadística de autoridad (trabajaron con miles de dueños de negocio) y va directo al dolor del público objetivo (por qué no escalás). Estructura de diagnóstico del problema seguido de un diálogo reconstruido tipo caso real con un cliente, y cierra con una frase memorable ("ruthless tracking"/seguimiento implacable). El gatillo combina autoridad con caso real dialogado.</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo necesita cámara, un micrófono decente y una anécdota o caso real de cliente reconstruido en diálogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>4413</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7666145793962741005</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala advierte que los resultados de un anuncio siempre empeoran a medida que se escala la inversión, y recomienda mantener un margen de rentabilidad muy alto al principio para absorber ese deterioro.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Los números que ves al principio, cuando arrancás corriendo esos anuncios con un par de cientos de dólares por día de inversión, nunca van a ser los mismos números que vas a tener cuando estés en dos, tres, cuatro, cinco, diez mil dólares de inversión. Casi siempre empeora a medida que escalás. Tu costo por clic va a subir. Tu costo por mil impresiones va a subir. Puede que tu tasa de clics baje porque Facebook se lo empieza a mostrar a una audiencia cada vez más fría. Tu tasa de opt-in va a bajar, tu tasa de reservas va a bajar. La gente ya vio el mensaje varias veces. El anuncio se fatiga, y uno entre un millón de factores distintos va a hacer que tus campañas publicitarias funcionen peor que cuando arrancaste. Entonces esa es otra gran lección: cuando recién estás corriendo las campañas y conseguís tu primera venta, pero apenas estás en el punto de equilibrio con la campaña publicitaria, no salgas corriendo a tratar de escalarla de inmediato, porque necesitás asegurarte de ser exageradamente rentable al principio, para que cuando escales y esos números finalmente empiecen a jugar en tu contra, todavía tengas, digamos, un margen de error del 30% en todo el negocio.</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Mismo set que el video anterior: home office con estantería de fondo (libros, planta, lámpara), micrófono de podcast grande a cuadro, talking head selfie sentado, remera clara. Subtítulos progresivos palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Gancho contraintuitivo directo ("los números del principio nunca van a ser los mismos cuando escalás") que toca el miedo/expectativa de quien recién arranca con anuncios. Estructura de lista de métricas que empeoran, seguida de una advertencia y un consejo concreto (mantener 30% de margen). El gatillo es la alerta más la cifra concreta de margen de seguridad.</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>sí — mismo formato hogareño de bajo costo, sin cortes ni gráficos adicionales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="88" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>4403</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7668716077114739982</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala cuenta por qué exige cobrar entre 2.000 y 3.000 dólares de pago inicial a sus clientes, priorizando calidad de cliente sobre cerrar cualquier venta, dado el aumento de costos a medida que se escala.</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Necesitás estar cobrando al menos entre 2 y 3 mil dólares por adelantado, porque a medida que escalás, los costos de publicidad van a aumentar, los costos del equipo de ventas van a aumentar, los costos de back-end y de cumplimiento van a aumentar. Y estamos en el punto en el que preferimos decirle que no a una venta que sería de 2.000 dólares por adelantado antes que decirle que sí y después tener que pelear para cobrar esa plata, o encima terminar poniendo dinero de nuestro bolsillo. Y esto se relaciona con mucho de lo que hablamos ayer sobre la visión a largo plazo de tu empresa. Así que le dije que no a los 2.000 dólares para poder seguir diciéndole que sí a los de tres, cinco, ocho mil dólares.</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Talking head sentado en un ambiente tipo depósito o garage con estanterías industriales de fondo, remera blanca escote V con logo tenue, sostiene una tablet/anotador, reloj. Placa de título al inicio con texto grande en negro sobre fondo blanco y palabra clave resaltada en dorado ("Charge more upfront for better clients"), luego subtítulos progresivos palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Frase directa con cifra concreta desde el segundo uno ("necesitás cobrar entre 2 y 3 mil dólares por adelantado"). Estructura de regla, justificación de costos crecientes y ejemplo real de una decisión polémica (decirle que no a una venta de 2.000 para poder decirle que sí a ventas más grandes). El gatillo es la cifra concreta combinada con una postura firme/polémica.</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>sí — video de 30 segundos a cámara fija, sin edición ni gráficos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="88" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>4387</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@neilpatel/video/7639715989571079437</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel muestra un dato de que el 90% de las páginas citadas por ChatGPT rankean mal en Google, y usa el caso de un cliente número uno en Google pero sin citas de IA por no tener presencia fuera de su propio sitio.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Acá hay una parte que realmente debería llamarte la atención. El 90% de las páginas que cita ChatGPT están en la posición 21 o más abajo en Google. Lo vi de primera mano con clientes. Una marca que estaba en el puesto número 1 para su palabra clave principal, con un SEO sólido, con gran autoridad de dominio, cero citas de IA, porque todo el contenido que produjeron alguna vez vivió únicamente en su propio sitio web. Nunca construyeron presencia en ningún otro lado. Las marcas a las que la IA menciona de manera consistente son una historia completamente distinta.</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida horizontal: arriba, un gráfico/captura de pantalla tipo dashboard de datos con una fuente citada; abajo, talking head contra una pared con textura de rayas rojas/negras, sweater gris, micrófono de podcast profesional a cuadro. Subtítulos progresivos centrados. Fondo de marca cuidado y buena iluminación tipo estudio.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Estadística sorprendente en los primeros segundos (90% de las páginas citadas por ChatGPT rankean mal en Google), reforzada con un gráfico. Estructura de dato duro seguido de un caso real de cliente que contrasta ranking #1 en Google con cero citas de IA, y cierre con la conclusión sobre necesitar presencia fuera del propio sitio. El gatillo combina el número sorprendente con autoridad (Neil Patel como referente de SEO) y un caso real.</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>no del todo — el gancho depende de datos y gráficos propios (citas de IA, rankings) que requieren herramientas de SEO pagas para igualar el mismo nivel de impacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="88" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>4369</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7668715915395075342</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala explica por qué hay que separar las campañas publicitarias de imágenes y de video en vez de mezclarlas, porque cada plataforma las prioriza distinto y así se puede duplicar la inversión total.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Las plataformas de anuncios tratan las imágenes y los videos de manera muy distinta. Por ejemplo, Facebook casi siempre va a priorizar las imágenes por sobre los videos, e Instagram casi siempre va a priorizar los videos por sobre las imágenes. O al menos esa fue mi experiencia hasta ahora. Entonces es muy importante que estés creando múltiples campañas distintas, una para videos y otra para imágenes. Y vas a ver que esto pasa muchas veces a medida que hablamos de esto, incluso cuando lleguemos a las campañas de escalado. Y la otra razón por la que me gustan tanto las imágenes como los videos es porque, de nuevo, mucha gente piensa: "ah, mi problema más grande es que no logro conseguir una campaña ganadora". Pero el problema más grande en realidad es cómo hago para gastar más en esa campaña ganadora. Y cuanto más testeo puedas hacer y más creativos publicitarios ganadores tengas, más presupuesto vas a poder ponerle atrás. Entonces, al separar entre videos e imágenes, no estás tratando de repartir el mismo presupuesto entre una imagen o un video. Vas a poder básicamente duplicar la inversión publicitaria. Digamos, 2.000 dólares por día yendo a tus videos ganadores y 2.000 dólares por día yendo a tus imágenes ganadoras, lo que significa que podés gastar 4.000 dólares por día.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Mismo home office/selfie setup que otros videos de este creador (estantería con libros y planta, micrófono de podcast, remera clara), talking head sentado, subtítulos progresivos palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Afirmación directa sobre una creencia poco conocida de las plataformas ("tratan imágenes y videos muy distinto"). Estructura de comparación Facebook vs Instagram, reencuadre del verdadero problema (no conseguir un ganador sino poder gastar más en él) y ejemplo numérico de cómo duplicar el gasto. El gatillo es el tip técnico específico combinado con el reencuadre de una creencia común.</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>sí — talking head simple sin edición; el valor está en el guion técnico, no en la producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="88" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670084877919816973</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento tipo entrevista/podcast donde Ravi Abuvala explica por qué elegir un nicho de mercado demasiado chico (como agendamiento solo para coaches) encarece los anuncios, y recomienda apuntar a un mercado más amplio para mantener bajo el costo por llamada.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Con los anuncios, en la práctica, necesitás un mercado total direccionable (TAM) lo suficientemente grande para que los anuncios tengan sentido, para poder mantener bajo tu costo por llamada agendada. El problema es que si nos ponemos tan específicos como, por ejemplo, "agendamiento de citas solo para coaches", ese TAM es relativamente chico. Y entonces va a ser muy difícil aumentar la inversión publicitaria ahí. Mientras que si hablamos de coaching, cursos, comunidades, agencias, negocios basados en servicios, todos esos caen dentro de la misma bolsa. Y eso le permite a tus anuncios -y si queremos ponernos técnicos, a tu CPM- mantenerse relativamente bajo, para que puedas escalar y, digamos, conseguir un costo por llamada agendada de 100 a 200 dólares.</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida vertical con dos videollamadas/clips apilados, formato entrevista o podcast a dos cámaras: arriba un hombre sentado en un living con puerta y TV de fondo; abajo otro hombre con anteojos en un ambiente con luz púrpura/azul tenue. Placa de título con texto grande en negro y blanco al inicio ("This mistake is killing 90% of your ad budget"), subtítulos progresivos debajo.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Placa de texto con cifra fuerte de entrada ("esto está matando el 90% de tu presupuesto") y formato de entrevista/conversación que da sensación de autenticidad. Estructura de problema (nicho muy chico) seguida de explicación técnica (TAM, CPM) y objetivo numérico concreto (costo por llamada). El gatillo es la cifra de alarma en el título combinada con el formato conversación.</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>sí — si ya se graba un podcast o una llamada, solo hay que recortar el fragmento y titularlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="88" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>4334</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670086089331313934</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala explica su proceso semanal de testeo de anuncios usando IA (ChatGPT/Claude) para generar variaciones de un anuncio ganador con pequeños cambios visuales, y así volver a escalar sin que el algoritmo lo trate como creativo repetido.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Por lo general, lo que testeo todas las semanas son principalmente tres ángulos de anuncio distintos. El primer ángulo va a ser un ángulo ganador. La semana pasada testeé un montón de anuncios. La semana anterior a esa también testeé un montón de anuncios y, obviamente, hubo un ganador entre ellos. Entonces agarro ese ganador, lo pongo dentro de ChatGPT -o Claude- y le digo: quiero crear otro anuncio parecido a este, dame los guiones. Y después grabo ese mismo anuncio pero con un fondo distinto. Capaz estoy caminando en vez de sentado en mi escritorio. Capaz estoy jugando pádel en vez de caminando. Capaz estoy usando una remera distinta. La idea es que se vea apenas un poco distinto del anterior, lo suficientemente distinto como para que el algoritmo lo vea como un creativo publicitario diferente, entre en fase de aprendizaje y pueda escalar a partir de ahí.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Mismo home office/selfie setup (estantería, planta, micrófono de podcast), pero suma como recurso visual una hoja escrita a mano que sostiene a cámara ("Testing / Tuesday / Claude") como apoyo del guion. Subtítulos progresivos palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Promesa de rutina/proceso revelado ("lo que testeo cada semana") que apela a la curiosidad por ver el detrás de escena. Estructura de rutina semanal seguida de un método paso a paso concreto (tomar el ganador, pedirle variaciones a la IA, regrabar con cambios mínimos) y la explicación de por qué funciona con el algoritmo. El gatillo combina curiosidad por el proceso con utilidad práctica inmediata y un prop visual (el cartel escrito a mano).</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>sí — solo requiere un celular, una hoja escrita a mano y acceso a ChatGPT o Claude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="88" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>4304</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670816095451745550</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>El creador cuenta una anécdota de podcast: un consejo de Dan Martell sobre que tu mayor fortaleza también es tu mayor debilidad, aplicado a su propia tendencia a sistematizar todo, ilustrado con un mastermind improvisado que organizó en París.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Dan Martell estuvo en mi podcast hace unas semanas y dijo algo tan de pasada... Estaba hablando de que lo que sea que sea tu mayor fortaleza ahora mismo, probablemente también es tu mayor debilidad. Y entonces me dice: 'vos sos un tipo súper de sistemas, y eso probablemente también es tu mayor debilidad al mismo tiempo'. Y yo pensé: 'la puta, tiene toda la razón'. Cuando estaba hablando con Ali ayer, me dice: '¿este mastermind es tu mastermind de nivel más alto? ¿Estás invitando a esta gente acá?' Y yo le dije: 'no, la verdad es que estoy en París y dije, armemos este mastermind y divirtámonos con esto'. Es gracioso porque le estaba explicando cómo antes yo necesitaba tener sistemas para todo, de la A a la Z, mientras que este mastermind fue bastante improvisado [?, en el audio 'pretty ad hawk'] y la pasamos genial. Además nos dio ganancias el mastermind. Hay algunas personas que conozco que van a seguir trabajando con nosotros.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Formato entrevista/podcast en video: un frame es talking head de cerca hablando a un micrófono de podcast, con texto superpuesto ('Dan Martell gave me advice that blew my mind') y debajo una foto de contexto (dos personas con un libro de Dan Martell, 'Buy Back Your...'). Otro frame muestra pantalla dividida en dos (formato entrevista, dos personas hablando, cada una en su recuadro). Subtítulos palabra por palabra en blanco sobre fondo oscuro con una planta detrás.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de autoridad por asociación ('Dan Martell me dio un consejo que me voló la cabeza') que apela a la reputación de una figura reconocida en el nicho de negocios/coaching. Formato de anécdota personal más reflexión, que genera identificación y curiosidad por saber cuál fue el consejo.</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>sí + aprovecha grabaciones de podcast ya existentes, solo requiere edición de clips y subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="88" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>4294</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7667260590976535821</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Fragmento tipo entrevista/podcast donde Ravi Abuvala cuenta cómo, analizando 16.000 llamadas de venta, descubrió que consumir contenido (sobre todo de YouTube) antes de agendar dispara la tasa de asistencia hasta un 88%.</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>La mayoría de las veces, las tasas bajas de asistencia tienen que ver más con el tema del contenido que con los aspectos técnicos en sí. En julio de 2023, nuestra tasa de asistencia se había desplomado al 30%. Y, como te imaginarás, cuando estás gastando la cantidad de plata que gastamos en anuncios y tenés la nómina de sueldos que tengo yo, se vuelve bastante molesto y bastante costoso tener una tasa de asistencia tan baja. Así que hice un análisis de 16.000 llamadas de venta a través de Hyros [?]. Y miré las atribuciones. Y, por lejos, como dije antes, la gran mayoría de la gente que efectivamente se presentaba a la llamada, en algún momento había consumido algo de mi contenido, sobre todo de YouTube. Si tomaba, de esas 16.000 llamadas de venta, solamente a la gente que había pasado por YouTube, tenía una tasa de asistencia del 88%. Entonces necesitan pasar por unas cuantas horas de contenido antes de agendar una llamada. Necesitan saber por qué van a subirse a la llamada, necesitan valorar la llamada. Así que tenés que asegurarte de que estén entusiasmados para eso. Y la única manera de lograrlo es preparando el terreno antes de la llamada.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida vertical tipo entrevista/podcast a dos cámaras: arriba un hombre con auriculares grandes contra una estantería con libros; abajo otro hombre con gorra trucker y remera clara frente a un micrófono de podcast grande, con planta de fondo. Placa de título con texto grande, parte resaltada en dorado ("88% show up rate came from this one thing"), luego subtítulos progresivos.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Título con cifra puntual y curiosidad ("88% de asistencia vino de esto"), en formato entrevista que da autenticidad. Estructura de problema histórico (30% de asistencia en 2023), investigación propia (análisis de 16.000 llamadas), hallazgo (el consumo de contenido dispara la asistencia) y conclusión accionable (preparar el terreno antes del call). El gatillo combina cifra concreta con caso de estudio con datos propios.</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>sí — si ya hay una entrevista o podcast grabado, solo hace falta recortar y subtitular el fragmento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="88" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>4287</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7667260792441441550</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Consejo de ventas: reducir la cantidad de recordatorios antes de una llamada agendada (de 18 a 3) mejora la tasa de asistencia, usando mensajes personalizados generados con ChatGPT a nombre del vendedor.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Cuando finalmente reservan la llamada... Acá van algunos tips rápidos que aprendí, en base a los datos que investigamos. Primero que nada, irónicamente, cuantos menos recordatorios hagas, mejor. Cuando reservé una llamada para hablar con nuestra propia empresa, hice como un 'cliente incógnito' de nuestra propia empresa, por así decirlo, para ver cómo era la experiencia. Recibí 18 recordatorios en tres días, entre mensajes de texto, emails, y después los coordinadores de citas y el vendedor. O sea, yo dirijo la empresa y ni yo mismo quería presentarme a mi propia llamada de ventas. Era demasiado insistente, y como que nos sacaba autoridad [frame]. Nos hacía ver un poco desesperados por la llamada de ventas. Así que hay una relación inversa entre la cantidad de recordatorios que mandás y la tasa de asistencia que tenés. Entonces la bajamos a tres recordatorios. Se ven personalizados. Usamos ChatGPT de parte del vendedor y les pedimos que respondan. Entonces parece algo legítimo, directamente de parte del vendedor. Eso calma todo.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Formato podcast/entrevista a dos cámaras en pantalla dividida verticalmente, ambos con auriculares tipo headset: uno con estantería de libros de fondo, otro con fondo de living/plantas y gorra. Subtítulos blancos palabra por palabra centrados en pantalla, con la frase gancho inicial destacada en negro sobre blanco ('This small mistake is killing your show rate').</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de 'error pequeño con consecuencia grande' en el título más un dato contraintuitivo (menos recordatorios da mejor resultado) presentado como hallazgo basado en un experimento propio ('secret shopped'), lo que da autoridad. Formato de consejo táctico y accionable en poco tiempo.</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo requiere grabar una conversación tipo podcast con cámara básica y agregar subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="88" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>4248</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670084187734494477</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Un fundador cuenta por qué contrató a propósito a un director de operaciones sin experiencia en su industria (ex-Nike) y por qué ser la persona más inteligente de tu empresa termina siendo un techo para el crecimiento del negocio.</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Cuando contraté a mi director de operaciones, él había trabajado en Nike. Contraté a propósito a alguien de afuera del mundo del coaching/e-learning. Llegaba y me decía: 'che, tenés que cambiar esto, tenés que cambiar aquello, tenés que hacer esto de otra manera'. Y yo literalmente nunca había pensado en algunas de las cosas de las que hablaba. Y nunca lo hubiera pensado, porque a nadie lo entrenan en eso dentro de nuestra industria. No hay nada que mate un negocio más rápido que vos siendo la persona más inteligente de tu empresa. Así que si la base de conocimiento de tu empresa tiene como techo a vos, y todos los que están debajo tuyo están tomando órdenes tuyas, nunca vas a poder crecer. Siempre vas a estar limitado por vos mismo.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Talking head de pie en una sala tipo oficina/sala de reuniones con pizarra blanca (con anotaciones) detrás, laptop apoyada en una mesa/atril en primer plano, cortina oscura de fondo. Subtítulos blancos palabra por palabra centrados, con la frase gancho inicial destacada en negro sobre blanco ('8-Figure founder shares his hiring secret').</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de autoridad numérica en el título ('fundador de 8 cifras') más promesa de secreto revelado, seguido de una anécdota concreta y personal (contratar a alguien de Nike) que ilustra una lección de negocios memorable y aplicable ('no seas el más inteligente de tu empresa').</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo requiere grabarse hablando en una sala con pizarra y agregar subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="88" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>4186</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7667259397323721998</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>El creador explica por qué el contenido orgánico en YouTube convierte mejor y genera menos reembolsos que la publicidad fría de tope de embudo, porque los espectadores llegan ya educados sobre su método.</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Nuestra nueva estrategia es llevar contenido a todos lados, hacia nuestro canal de YouTube. Si logro que alguien consuma unas horas de contenido mío, es muy probable que compre, y va a comprar, y va a volver a comprar. Notamos la tendencia de que todo el mundo venía de YouTube, pero acá seguía corriendo un montón de anuncios fríos de tope de embudo al mismo tiempo, y en realidad no estaba enfocado en YouTube. Fue bastante gracioso, porque cuando miramos los datos, los anuncios fríos de tope de embudo son de donde vienen los pedidos de reembolso, los contracargos. En cambio, aunque fuera un ciclo de venta más largo, la gente que venía de YouTube era literalmente un batazo seguro. Y la gente que venía de YouTube también ya sabía bien cómo ser mis clientes. Ya sabían quién era yo. Entonces, se sumaban y nosotros teníamos que hacer, solo para dar un ejemplo, digamos un 20% del trabajo para conseguirles un resultado 10 veces mejor que el que lográbamos con alguien que venía de anuncios fríos, porque a esos había que enseñarles nuestras estrategias de escalamiento desde cero.</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Talking head de pie en la misma sala tipo oficina/sala de reuniones con pizarra blanca y laptop en primer plano que en la fila 110 (mismo set y misma persona). Subtítulos blancos palabra por palabra, frase gancho inicial destacada en negro sobre blanco ('Why content sells better than ads').</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de afirmación contraintuitiva en el título ('por qué el contenido vende mejor que los anuncios') que desafía la sabiduría convencional de marketing pago, reforzado con datos internos comparativos (reembolsos vs. conversión, '20% del trabajo para un resultado 10x') que dan autoridad.</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>sí + mismo formato reutilizable de grabarse hablando con pizarra de fondo y subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="88" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>4142</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7668715658724543758</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Técnica de contratación: hacer 40 entrevistas para un puesto nunca antes cubierto (director de operaciones) para aprender el rango salarial, las responsabilidades y los KPIs típicos del rol antes de decidir a quién contratar.</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Cuando contraté a un director senior de operaciones, nunca antes había contratado para ese puesto, así que lo único que hice fue hacer 40 entrevistas y preguntar: '¿qué hace bueno a un director de marketing?', o '¿cuáles son tus roles y responsabilidades típicas?'. Y después de entrevistar a 40 personas, te vas haciendo una idea de qué hacen los buenos y qué hacen los malos. Y les preguntaba: '¿cuál es tu KPI número uno como director senior de operaciones?'. Y eventualmente, como después del entrevistado número 15, empezás a llegar a las reuniones un poco más preparado que la persona a la que estás entrevistando, y también te vas haciendo una idea de los planes de compensación. Al final de mi primera entrevista con cada uno, siempre pregunto: '¿cuánto te gustaría ganar si cumplís los objetivos?'. Yo no sabía, en nuestra industria, cuánto se le paga a un director de marketing, cuánto se le paga a un director senior de operaciones. Después de entrevistar a 40 personas, te hacés una idea del rango, y también mirás tu presupuesto de nómina según lo que tenés reflejado en tu directorio, y decidís en base a eso. La respuesta corta es: un buen coordinador de citas es alguien a quien le vas a decir: 'che, no sé qué es un buen coordinador de citas, tengo una base de datos donde me entran 10 leads nuevos todos los días, no tengo tecnología ni un proceso armado, ¿qué harías para empezar a agendar citas esta semana?'. Y ves qué te contesta.</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato y set que las filas 110 y 111 (talking head de pie con pizarra blanca y laptop en primer plano, cortina oscura de fondo). Subtítulos blancos palabra por palabra centrados en pantalla.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de resultado concreto y cuantificado en el título ('este truco de contratación me ahorró 6 cifras en malas contrataciones') más un método replicable y detallado (40 entrevistas como forma de calibrarse antes de contratar), que aporta valor táctico inmediato.</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>sí + mismo formato reutilizable de grabarse hablando con pizarra de fondo y subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="88" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>4088</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@neilpatel/video/7642406355197824270</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel explica que en vez de competir por palabras clave genéricas y muy disputadas, apunta a keywords de cola larga muy específicas usando Ubersuggest e IA, lo que le permitió construir millones de visitas mensuales.</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>No puedo creer que les esté contando esto, porque es literalmente cómo construí mi tráfico hasta millones de visitas por mes. Pero la mayoría de ustedes están persiguiendo las palabras clave equivocadas. Todos van detrás de los términos grandes: "marketing", "SEO", "cómo hacer dinero", millones de búsquedas por mes, y después se preguntan por qué están en la página 47 de Google. Están compitiendo contra sitios con diez años de autoridad y miles de backlinks. No van a ganar esa pelea, al menos no ahora. Esto es lo que hice yo en cambio: dejé de ir detrás de las palabras clave obvias y empecé a apuntar a las específicas. No "email marketing", sino "los mejores asuntos de email para agentes inmobiliarios". Esa es una conversación que casi nadie está teniendo. Y si hacés eso con miles de palabras clave, te vas a dar cuenta de que podés generar un montón de tráfico, y la inteligencia artificial hasta te puede ayudar. Así que estos son los pasos que sigo: entro a Ubersuggest.com, escribo una palabra clave relacionada con mi rubro, y me muestra todas las preguntas que la gente está tipeando en ChatGPT ahora mismo. Después voy y creo contenido en base a esas palabras clave usando su "AI Write" (redactor con inteligencia artificial). Arrancá con eso y vas a empezar a generar todavía más tráfico.</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Talking head (hombre pelado, sweater/camisa oscura, fondo claro liso) combinado con gráficos superpuestos: capturas de pantalla de métricas de tráfico tipo dashboard y listas de texto en negrita con viñetas rojas. En otro tramo, screen recording de navegador (Ubersuggest.com) con la cámara del presentador insertada como "burbuja" webcam sobre la pantalla. Subtítulos progresivos.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Confesión/secreto como gancho ("no puedo creer que les esté contando esto") sumado a prueba de autoridad (millones de visitas propias). Estructura de mito (competir por keywords grandes) versus método alternativo (long-tail), con pasos concretos demostrados en pantalla usando una herramienta real. El gatillo es el efecto "secreto revelado" combinado con autoridad numérica y demo visual del proceso.</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>parcial — el guion y la lógica de keywords son replicables sin costo, pero mostrar datos reales de tráfico propio y gráficos requiere autoridad previa y herramientas de pago.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="88" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>3758</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7642437656084892959</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney comparte tres pruebas de locución con inteligencia artificial (ElevenLabs) que usó en anuncios que generaron más de 125.000 dólares para un cliente: susurro en el gancho, cambio de género de voz y test de manejo de objeciones con distintas voces.</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Bueno, cada uno de estos anuncios le generó a mi cliente más de 125 mil dólares en ingresos, y todos tenían algo en común. ¿Pueden adivinar qué es? Bueno, usamos locución de ElevenLabs (11 Labs) en cada uno de ellos. Así que acá van tres de mis iteraciones de locución favoritas para que puedan generarles todavía más ingresos a sus clientes. Número uno: cambiar la locución a un susurro. Honestamente, con solo hacer esto en el gancho inicial, le da una onda ASMR increíble, que realmente mejora el rendimiento. Y número dos: cambiar el género de la locución. De hecho, en este caso cambiamos de una locución femenina a una masculina. Y si bien nuestra intención inicial era apuntar a un nuevo público -o sea, hombres-, terminamos igual entregándole el anuncio principalmente a mujeres de alto poder adquisitivo con esta locución. Pero igual generó mejor rendimiento. Y ahora que tenemos este aprendizaje, es algo que queremos usar en un futuro anuncio en conjunto con un creador de contenido. Y número tres: hacer un test de manejo de objeciones usando tres voces distintas que representen a tres de tus principales personas (perfiles de cliente). Usando ElevenLabs vas a poder personalizar la voz según edad, género e incluso dialecto, para poder generar más diversidad creativa en tus cuentas publicitarias y, en definitiva, mejor rendimiento. Así que cuéntenme en los comentarios: ¿ya están usando ElevenLabs? Y si no, ¿por qué no?</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Talking head (mujer con blazer gris, aros, cabello recogido) de pie en un living/loft moderno con cocina y luces colgantes de fondo, sostiene un micrófono inalámbrico con espuma antiviento. Se superponen tarjetas de texto (título numerado sobre fondo amarillo) y una captura de pantalla borrosa de métricas de un dashboard publicitario (spend, ROAS, purchase value). Subtítulos progresivos.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Cifra de resultado concreta desde el inicio ("cada uno de estos anuncios generó más de 125 mil dólares") combinada con pregunta de intriga ("¿adivinás qué tenían en común?"). Estructura de lista numerada de tres tácticas con ejemplo real de cada una, incluyendo un dato contraintuitivo (cambiar a voz masculina terminó igual llegando a mujeres). El gatillo combina cifra de revenue, formato de lista numerada y el giro inesperado dentro del ejemplo dos.</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>sí en el concepto (lista numerada + talking head + herramienta de IA accesible), aunque el gancho depende de tener datos reales de resultados de un cliente propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="88" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7660561341396143391</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney (estratega creativa) da su 'hot take' a estrategas creativos junior: nadie te debe nada, tenés que construir tu propio camino, y lo ilustra con el ejemplo personal de haber rechazado una entrevista de trabajo por no ofrecerle el sueldo que pedía.</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Mi ‘hot take’ más incómodo para estrategas creativos es que en realidad nadie te debe nada. Las marcas y las agencias no te deben un puesto de entrada bien pago para que puedas aprender estas habilidades. Y los fundadores no te deben un sueldo de seis cifras solo porque hiciste un par de anuncios ganadores. Y esto tengo que recordármelo a mí misma todo el tiempo. Yo no te debo una guía gratuita paso a paso de cómo hacer este trabajo fácilmente. Se vuelve mucho más liberador cuando te das cuenta de que vos sos quien controla tu propio destino y podés elegir invertir en capacitaciones y en mentores. Podés elegir remarla, acumular experiencia y demostrar tu valor. Creo que todo el que realmente tiene mucho éxito en esta industria, posta [?], pasa por una temporada de remarla en serio. Si todavía no pasaste por una, probablemente por eso estás batallando. Y lo bueno de tener este tipo de responsabilidad radical es que podés elegir con quién trabajar y asegurarte de que tus valores realmente estén alineados. Te voy a ser sincera al 100%: lo de la plata es súper real. De hecho, hace como seis meses tuve una entrevista de trabajo, y no nos poníamos de acuerdo en el tipo de sueldo como para siquiera seguir la conversación después de la primera entrevista. Básicamente dije: ‘che, si no me van a pagar 300 mil, entonces no tenemos que tener esta conversación’. Así que no la tuvimos. Y me acuerdo de irme de esa conversación pensando: guau, eso fue un poco corto de miras de su parte. Yo podría simplemente hacer un anuncio y eso compensaría de sobra ese sueldo extra que no me quisieron pagar. Después me tomé un momento y pensé: mierda, están totalmente en su derecho de no querer pagar esa banda salarial. Realmente creo que por eso casi todos los estrategas creativos que conozco que tienen mucho éxito y que de verdad entienden esta industria, en algún momento terminan yendo por su cuenta: arman su propia agencia, se vuelven consultores, arman su propia marca. Se dan cuenta de que tienen tanto poder de negociación en sus habilidades que finalmente no termina de alinearse con lo que las empresas quieren pagar por su trabajo. Y en vez de quejarse, arrancan su propio proyecto y se hacen cargo de lo que realmente quieren.</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Selfie/talking head en primer plano, luz natural suave, fondo interior (pared verde clara, mueble bajo con marco de foto, sillón). Viste musculosa de encaje color crudo, pelo suelto. Usa auriculares con cable blanco a modo de micrófono. Subtítulos automáticos blancos con contorno negro, centrados abajo, sincronizados palabra por palabra. Toma continua a cámara, sin cortes ni gráficos adicionales.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: 'hot take' incomodo y directo (nadie te debe nada) que genera friccion/curiosidad desde el segundo uno. Estructura: afirmacion provocadora, argumentacion con ejemplos, anecdota personal concreta (entrevista de 300K) y cierre aspiracional. Gatillo: polemica/opinion impopular + autoridad de experiencia personal + caso real con cifra.</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>sí, solo necesita celular, buena luz natural y auriculares con micrófono; cero edición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="88" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>3133</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@neilpatel/video/7663838353892085006</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel explica que la mayoría de las marcas hace mal el marketing con creadores: en vez de gastar todo en un influencer grande, conviene repartir el presupuesto entre 3 a 5 creadores más chicos que estén en la etapa de 'interés' del comprador, citando el caso de una marca de belleza que facturó decenas de millones vía afiliados.</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Había una marca de belleza popular que facturó decenas de millones en TikTok Shop, y la gran mayoría vino de creadores afiliados, no de su propia cuenta, no de anuncios pagos. Entonces, ¿los creadores no son algo ‘lindo tener’? Son el canal. La pregunta es cómo los desplegar. Y casi todo el mundo lo hace al revés. Le pagan a un creador grande para generar reconocimiento de marca, el que tenga más seguidores que puedan pagar. Pero en la etapa de reconocimiento (awareness), un creador te ahorra cerca del 5% del tiempo del recorrido del cliente. En la etapa de interés, cuando alguien ya está considerando un producto como el tuyo, un 39%. Ese es todo el juego. Tu presupuesto de creadores mueve la aguja en el medio, no en la parte de arriba. Así que no lo tires todo en un nombre gigante. Repartilo entre tres o cinco creadores más chicos que realmente vivan en tu categoría, desplegados donde la gente ya se está decidiendo, y mirá lo que hace ahora una recomendación real. A largo plazo, necesitás escalar eso a cientos, si no miles, de creadores. Eso es lo que están haciendo las empresas que generan millones, si no decenas de millones de dólares al año desde TikTok.</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en estudio con fondo gris liso, iluminación tipo softbox (reflejo de aro de luz en los ojos), sweater gris, micrófono de solapa. Abre simulando una pantalla de perfil de TikTok ('BeautyBrand', seguidores, botón Follow) para ilustrar el caso citado, corta a un gráfico de barras animado comparando etapas del funnel ('Influencer Content Acceleration Effect') y vuelve al talking head. Subtítulos blancos en negrita, palabra por palabra, centrados abajo. Producción con varios cortes y motion graphics.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: caso real impactante (marca de belleza que facturó decenas de millones solo con creadores afiliados). Estructura: mito común, luego dato que lo refuta (5% vs 39%), y recomendación táctica concreta (3 a 5 creadores chicos). Gatillo: cifra concreta + revelación contraintuitiva + autoridad del especialista en marketing.</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>sí, con salvedad: el guion y hablar a cámara son replicables sin presupuesto, pero para igualar el impacto conviene sumar algún gráfico simple (texto/flechas) en edición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="88" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>2806</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7659966626040728862</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney explica por qué, pese al miedo de que la IA elimine puestos junior, hay más demanda que nunca de estrategas creativos junior, dando tres razones: boom del boot camp de estrategia creativa de Motion, dificultad para contratar liderazgo, y sensación de 'derecho adquirido' en los roles medios/senior mal definidos.</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Te voy a ser sincera al 100%. Yo pensaba que la IA iba a eliminar los puestos junior este año. Entonces, ¿por qué es que literalmente nunca hubo tantas marcas contactándome para pedirme estrategas creativos junior? Tengo un par de hot takes sobre esto. Sí, el último es el más impopular. Número uno: el mercado de estrategas creativos junior está absolutamente saturado [de demanda]. Y creo que se debe en gran parte al boot camp de estrategia creativa de Motion que se hizo hace unos meses. De hecho, fijate en las tendencias de búsqueda de Google para 'estrategia creativa'. Esa es la campaña publicitaria que hizo Motion. Y número dos: hoy en día es realmente muy difícil contratar liderazgo en estrategia creativa. De hecho tuve varias conversaciones con otros operadores de agencias y gente que trabaja del lado de las marcas que están tratando de contratar un director de estrategia creativa. Y lo que están descubriendo es que la mejor experiencia —las mejores agencias o la mejor experiencia de marca— en realidad no se correlaciona con los mejores resultados. Muchas marcas se dieron cuenta de que, en realidad, es la fortaleza de tus sistemas y tus SOPs (procedimientos operativos estándar) lo que puede garantizar resultados más consistentes o mejores en un período más largo, en vez de ese mítico estratega creativo '10 sobre 10'. Y por último, y esta es la parte de la que me siento más incómoda hablando, porque yo quiero que los estrategas creativos generen riqueza, hagan su plata, tengan carreras prósperas —esa es la razón por la que tengo esta plataforma—. Sin embargo, noté que hay mucho sentido de derecho adquirido (entitlement) a la hora de contratar. Igual no creo que esto sea culpa de los estrategas creativos. Creo que los puestos de nivel medio a liderazgo están tan poco definidos claramente en nuestra industria que se hace muy difícil evaluarlos. ¿Cómo es un estratega creativo senior comparado con un director de estrategia creativa? ¿Versus alguien que está más en el nivel de VP de crecimiento? Creo que quienes más se benefician de esta confusión ahora mismo son los estrategas creativos junior. Así que si te interesa saber más sobre estos puestos de estrategia creativa junior, seguí mi cuenta. Voy a compartir más sobre esto mañana.</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Mismo setup selfie que la fila 046: interior con pared verde clara, sillón de fondo, pelo suelto, top a rayas azul/rosa/marrón. Sostiene y juega con el cable de los auriculares mientras habla. Subtítulos automáticos blancos con contorno, centrados abajo. Toma continua, sin cortes ni gráficos.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: contradicción con el miedo instalado ('la IA iba a matar los puestos junior') seguido de pregunta retórica intrigante. Estructura: listado numerado de tres 'hot takes' con la más polémica al final, cierre con gancho de continuidad ('mañana comparto más'). Gatillo: curiosidad + formato lista + autoridad (opera agencia) + cliffhanger para generar seguimiento.</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>sí, mismo formato selfie sin edición que la fila 046, solo cámara y buena luz natural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="88" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>2653</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@neilpatel/video/7655766383606631693</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel argumenta que las empresas pierden clientes no porque su trabajo sea malo sino porque no pueden competir manualmente con el volumen actual de mensajes de marketing, y propone automatizar con segmentación multicanal, citando cifras de HighLevel, la empresa con la que se asoció.</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Tus clientes reciben más mensajes de marketing en un día que los que recibían tus abuelos en un año. Vos y tu equipo no pueden competir con empresas multimillonarias a menos que sepan trabajar de forma más inteligente. Dejame explicarte. Las bandejas de entrada de email de todo el mundo están inundadas. Los feeds de redes sociales están saturados. El SMS está repartido entre seis plataformas. Las notificaciones push nunca paran. La persona promedio está expuesta a miles de mensajes de marketing por día. Si sos un marketer o dueño de un negocio tratando de competir con eso —mandando emails a mano, publicando en redes de a uno, haciendo seguimiento de leads manualmente— no estás perdiendo porque tu trabajo sea malo. Estás perdiendo porque la matemática es imposible. Entonces, ¿qué es lo que realmente funciona ahora? No es mandar más mensajes. Es volumen inteligente: el mensaje correcto, a la persona correcta, en el momento correcto, por el canal correcto. Automatizado y funcionando mientras dormís. Eso significa segmentar a los clientes según lo que realmente hicieron. Coordinar email, SMS y voz, todo en el mismo flujo, todo funcionando al mismo tiempo. Y para que esto sea concreto: HighLevel, una empresa con la que nos asociamos —solo sus usuarios ya están corriendo esta estrategia y mandan 1.860 millones de mensajes y generan 67 millones de leads nuevos cada mes. Eso no es una estadística de la plataforma. Eso es lo que están produciendo ahora mismo los operadores que corren volumen inteligente a escala. Construí un sistema que escale junto con el ruido.</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en interior prolijo (living/cocina con cuadro abstracto, mueble de madera), luz cálida, remera blanca y campera negra abierta, micrófono de solapa. Se intercalan gráficos: collage de logos de marcas grandes (Coca-Cola, Nissan, Google, McDonald's, etc.) superpuesto sobre su cara; tarjeta con lista de tareas manuales tachadas ('Sending emails one by one', etc.); logo animado de 'HighLevel'. Subtítulos blancos en negrita centrados. Varios cortes y motion graphics.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: comparación exagerada y relatable (más mensajes de marketing por día que tus abuelos en un año). Estructura problema-causa-solución-prueba: saturación de canales, por qué se pierde (no es calidad, es matemática), solución (volumen inteligente automatizado), prueba con cifra concreta (1.860 millones de mensajes). Gatillo: analogía sorprendente + número grande + solución práctica accionable.</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>sí, con salvedad: el discurso a cámara es replicable, pero el video suma varias tarjetas gráficas y montajes de logos que piden algo de edición extra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="88" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>2553</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7649689908218531094</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath analiza en vivo el comercial de Nike para el Mundial ('Flip the Script'), comentando la edición, el elenco de futbolistas y celebridades, y explica por qué el anuncio funciona al combinar referencias que atraen tanto al público futbolero núcleo como al casual.</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>El elenco [cast] es una demostración de poder (flex) grande de Nike, ¿eh? Es como una intro muy acelerada, con un montón pasando, muy cinemática, en cámara lenta, y después como que corta. Lindo. Ninguno de estos jugadores me escucha, ¿okey? Tenemos que controlar esto de alguna manera. Ya hay un montón de futbolistas súper conocidos. Y la gente conoce el fútbol. También ex futbolistas muy conocidos. 'Zlatan va a volver'. Ja ja ja. Están haciendo un buen trabajo enlazando las personalidades, porque eso de 'Zlatan va a volver' es una frase muy propia de Zlatan Ibrahimović. 'No, todavía no'. Esto es una linda mezcla total en términos de cómo se mostró. Como que la toma de cámara en la oficina, tenés a LeBron y a Cristiano Ronaldo. 'Los goats [los mejores de la historia] se despiden'. Es un poco una narrativa de cambio de guardia ahí. Apuesto a que lo van a dar vuelta en un segundo. No es la narrativa que Ronaldo va a querer. Ja ja ja. Sí, pensé que lo iban a dar vuelta enseguida. Como pieza de marketing, esto es muy divertido y creativo. Se ve divertido. Ja ja. Ted Lasso ahí. Muy lindo. O sea, una cantidad enorme de nombres conocidos de futbolistas actuales y del pasado. También grandes celebridades. Ja ja. Y como que las historias en... todas. Voy a saltear al pibe joven. Lindo. Cuando estás creando anuncios, una de las cosas que a menudo tratás de hacer —que a menudo tratamos de hacer— en la fase de planificación, es pensar: ¿podemos crear algo que le atraiga tanto a la audiencia casual como a la audiencia núcleo (core)? Porque si podés producir algo que les atraiga a ambos, tiene el potencial de rendir mejor que cualquier otra cosa. Nike es una marca, pero acá está más orientada al fútbol en el Mundial. Así que tienen un montón de lindos detalles para los fanáticos núcleo del fútbol e incluso para los casuales que entran y salen. Tienen figuras históricas ahí, como futbolistas históricos, y a la gente que es fanática núcleo del fútbol y sigue a esas personas le va a encantar eso. O sea, hay algo ahí para ellos, pero también hay cosas para audiencia nueva. Tienen otras personas externas al fútbol. Si no conocés a nadie [del fútbol], va a haber nombres ahí que vas a reconocer, y eso ayuda a atraerte. Está simplemente cortado, editado y filmado de una manera en la que la cinematografía es realmente buena, es visualmente atractivo, hay una historia, hay una narrativa, es emocionante, tiene ritmo rápido desde el arranque. Así que eso también va a ayudar a atraer a gran parte de esa audiencia nueva, o incluso a la audiencia casual. Pero bueno, eso es algo en lo que a menudo tenés que pensar cuando producís contenido de marketing: ¿hay algo que mantenga contenta a la gente súper 'core' pero que también enganche a tu audiencia [más amplia]? Creo que hicieron un muy buen trabajo con eso. Máxima puntuación para eso. Muy bien logrado.</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Formato de reacción dividida: parte superior muestra al presentador (remera polo azul, silla gamer negra, oficina/living con reloj de pared y cuadro con ícono de YouTube) mirando hacia abajo fuera de cuadro; parte inferior reproduce el comercial de Nike (jugadores de fútbol, pelota, estadio) que está comentando. Subtítulos blancos en la franja del medio. En otros momentos pasa a plano completo del presentador hablando directo a cámara, sin el video incrustado. Corte entre 'mirando la pantalla' y 'hablando a cámara'.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: comentario en caliente sobre un comercial reconocible de Nike para el Mundial, con reacciones genuinas (risas, sorpresa). Estructura: análisis 'play-by-play' del anuncio mientras se reproduce, seguido de la lección de marketing generalizable (atraer audiencia núcleo y casual a la vez). Gatillo: caso real de marca famosa + celebridades reconocibles + autoridad del analista publicitario.</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>sí, con salvedad: solo necesita el video ajeno más reacción hablada, pero requiere el comercial de referencia y editar la superposición pantalla/cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="88" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>2540</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7626743164648410399</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney cuenta cómo, tras recibir una crítica sobre que sus roadmaps creativos vivían en Google Sheets, usó Claude para generar el prompt ideal y el nuevo Agent 4 de Replit para 'vibe-codear' sin experiencia previa un dashboard funcional de agencia que rastrea el estado de las pruebas creativas de todos sus clientes. Video de partnership con Replit.</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Me sentí súper ofendida cuando recibí este comentario sobre mis mapas de ruta creativos, pero bueno, en realidad estaba enojada porque ella tenía razón, así que decidí hacer algo al respecto. Mis amigos de Replit [transcripto como 'Replex'] vieron lo que estaba pasando y me dijeron 'che, podés usar nuestro nuevo Agent 4 [transcripto como 'agent for release']', que en realidad despliega múltiples agentes para planificar, programar y diseñar varias cosas a la vez por vos. Pero la verdad es que yo nunca había programado con IA ('vibe coding'), y todavía estaba un poco asustada de que fuera demasiado técnico para mí. Entonces me acordé de lo mejor de la IA, que es que le podés preguntar a la IA cómo usar mejor la IA. Así que le mostré a Claude mi mapa de ruta creativo y le dije 'dame el mejor prompt que pueda usar dentro de Replit para que podamos hacer esto', y en cuestión de minutos tenía un prototipo funcionando que ahora estoy empezando a usar con mis clientes. Creé un dashboard de dueño de agencia donde puedo ver en qué estado están las pruebas (tests) en todos los clientes: cuáles se están demorando de mi lado, cuáles están trabadas por algo del lado del cliente, y cuáles ya se lanzaron [?, tramo incierto de la transcripción]. Esto me hizo sentir una total genia. Definitivamente voy a estar disfrutando este subidón por semanas, así que asegurate de revisar su nuevo Agent 4, porque uno puede simplemente hacer las cosas, así que hacelas.</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Talking head selfie en interior (estantería con plantas de fondo), sosteniendo micrófono inalámbrico tipo cápsula. Se superpone en la parte superior de pantalla una captura del dashboard/app que construyó ('Creative Roadmap', 'Overview', métricas de clientes). Subtítulos en pantalla. Formato vertical, mismo estilo consistente de la serie de la creadora (imagen de producto/pantalla arriba, cara hablando abajo); descripción incluye hashtag de partnership (#ReplitPartner).</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>Gancho narrativo con vulnerabilidad/anécdota personal (la criticaron, pero tenía razón) que genera identificación y curiosidad por saber qué hizo al respecto. Estructura de historia con arco completo: problema → duda/miedo técnico → solución con IA → resultado tangible (dashboard funcionando) → llamado a la acción hacia el producto patrocinador. Gatillos: storytelling personal/vulnerabilidad + curiosidad + demostración de resultado real + contenido patrocinado con caso de uso auténtico.</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>sí + es un talking head con capturas de pantalla del producto, solo requiere celular y micrófono; lo específico es tener acceso al partnership con el producto patrocinador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="88" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>2311</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@neilpatel/video/7656045476281650445</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel cuenta el caso real de un gran retailer de e-commerce que aumentó 45% las ventas (300 millones de dólares al año) con solo eliminar el botón obligatorio de 'Registrarse' y reemplazarlo por 'Continuar'.</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Un gran retailer de e-commerce tenía un problema de abandono de carrito. Trajeron a un investigador de UX llamado Jared Spool para averiguar por qué. Lo que encontró paralizó a todos en la sala. El 45% de sus clientes tenía múltiples cuentas en el mismo sitio y no podían recordar cuál habían usado. Las solicitudes de restablecimiento de contraseña llegaban a ciento sesenta mil por día. Un botón de 'Registrarse'. Ese era todo el problema. Estaba parado entre el cliente y la compra. Y millones de personas simplemente se iban. Sacaron el botón de registro y lo reemplazaron por una sola palabra: 'Continuar'. Agregaron una línea: 'No necesitás crear una cuenta para hacer compras en nuestro sitio'. Las ventas subieron 45%. Quince millones extra en el primer mes, trescientos millones en el primer año. ¿Era el botón de registro un requisito legal? No. ¿Lo exigía el procesador de pagos? No. Era una UX heredada de otra época. Y le costó 300 millones antes de que alguien finalmente preguntara: ¿por qué estaba ahí? Entonces, ¿cuánto vale tu versión de ese botón?</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en estudio con fondo de paneles acanalados color coral/rojo, luz pareja. Viste remera blanca con campera negra abierta, micrófono de solapa. Se insertan gráficos: foto pixelada de un hombre (Jared Spool) con etiqueta 'named'; burbuja de mensaje de chat con una pregunta retórica superpuesta ('Was that Register button legally required?'). Subtítulos blancos en negrita centrados abajo.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: intriga narrativa ('lo que encontró paralizó a todos en la sala') sobre un problema de conversión de un gran retailer. Estructura de caso de estudio: problema, investigación, hallazgo sorprendente (un botón), solución simple, resultado con cifras enormes (+45%, 300 millones). Gatillo: curiosidad + revelación + números concretos y grandes + pregunta final que involucra al espectador.</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>sí, con salvedad: el relato de caso funciona solo con cámara y buena luz, aunque el video suma gráficos (imagen pixelada, burbuja de chat) que piden edición extra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="88" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>2226</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7650897822996335894</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath, caminando en un centro turístico de montaña, cuenta que llegar a 1 millón de dólares de ingresos anuales no fue tan emocionante como esperaba, porque después de impuestos y costos queda mucho menos, y por eso subió su meta a 10 veces más.</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Llegar a un millón al año en ingresos no fue ni cerca de tan emocionante como pensé que iba a ser. Creo que cuando pensás 'ah, estoy generando un millón de dólares al año en mi negocio', pensás que eso sería mucho. Pero después empezás a desglosarlo y pensás: bueno, eso es facturación, no ganancia, así que hay que restar los costos. Incluso si tu negocio está brillantemente manejado con márgenes altos, probablemente estés hablando de un 30, 40% de eso. Entonces son 300, 400 mil. La mitad se va a ir al fisco. Si elegís retirar eso, es como que tenés un negocio de un millón de dólares al año y estás ganando 100 mil, y pensás: 'ok'. Empezás a darte cuenta de que, para que esto sea algo emocionante, tiene que ser 10 veces más. Y si de verdad quiero lograr mis objetivos, tenemos que estar haciendo algo así como 100 millones al año. Y básicamente movés esa meta mucho más alto de lo que en un principio pensabas que hacía falta.</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Selfie/vlog caminando al aire libre en un pueblo tipo centro de esquí (edificios de madera y piedra, pinos, comercios), luz de atardecer/amanecer. Viste campera roja y pantalón gris. Habla directo a cámara mientras camina y gesticula. Texto superpuesto grande estilo 'título' con la pregunta clave ('What does $1M a year look like in reality?') además del subtítulo automático de la palabra actual. Toma continua tipo caminata, sin cortes notorios.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: confesión personal que rompe expectativas (llegar a 1 millón no fue tan emocionante). Estructura: desglose numérico de por qué la cifra 'grande' se achica (costos, impuestos) y conclusión con meta más ambiciosa (10x). Gatillo: desmitificación de una cifra aspiracional + relato personal + formato caminata informal que da cercanía.</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>sí, se grabó caminando en la calle con el celular y texto simple superpuesto, muy fácil de replicar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="88" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>2117</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7664639468892146966</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Clip tipo entrevista/podcast con dos personas debatiendo si los anuncios en video o los estáticos generan más clics, explicando que los anuncios en video tienen mayor caída de audiencia y hay que compensarlo vendiendo la idea a lo largo de todo el video.</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Qué hace que un anuncio en video sea bueno, pero no un anuncio estático. Los anuncios en video siempre van a tener tasas de abandono más altas que los anuncios de imagen. La imagen la captas de inmediato, pero un porcentaje menor de gente va a llegar hasta el final de tu anuncio en video, comparado con la cantidad de gente que básicamente consume la imagen entera. Entonces compensás eso asegurándote de venderle bien a la gente a lo largo de todo ese recorrido.</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida en dos mitades horizontales: arriba un hombre con anteojos de sol y remera polo marrón, gesticulando, fondo de mar/costa con balaustrada de piedra; abajo otro hombre con anteojos recetados, barba y cadena, remera negra, mismo fondo costero. Parece contenido de podcast/entrevista reutilizado como clip corto. Subtítulos azules en negrita centrados en la unión de ambos cuadros.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: pregunta directa y útil para cualquier anunciante (video vs. estático, qué convierte más). Estructura: mini-explicación de por qué el video tiene más abandono y cómo compensarlo. Gatillo: formato de diálogo entre dos personas que suma autoridad + utilidad inmediata en formato muy corto (bite-size).</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>sí, con esfuerzo: requiere dos participantes y aprovechar un formato tipo entrevista/podcast ya grabado, pero no exige presupuesto de producción alto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="88" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>2084</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7667024216109108502</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista a Ben Heath sobre el presupuesto publicitario más grande que manejó (600.000 dólares por día) y cómo cambia el trabajo a ese nivel: fatiga creativa casi inmediata, decisiones por hora, y picos de gasto solo en fechas puntuales como Black Friday.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>¿Cuál es el presupuesto más grande que manejaste y qué cambia a ese nivel? El presupuesto más grande que manejé fue gastar cerca de 600.000 dólares por día. A ese nivel, la fatiga del creativo publicitario aparece casi de inmediato: estás evaluando resultados en horas, no en días, y mucho menos en semanas. Entonces la carga de trabajo que se necesita cuando estás gastando tanto sube muchísimo. Por suerte, si estás gastando tanto, probablemente sea porque las campañas están funcionando muy bien, y por lo tanto tenés la plata entrando como para poder pagar todo el material creativo extra. Trabajar con creadores e influencers para producir anuncios de partnership y cosas por el estilo. La otra cosa para tener en cuenta es que cuando estás gastando ese tipo de presupuesto, lo más probable es que estés alcanzando a una proporción realmente grande de tu mercado objetivo muy rápido. Así que es poco probable que puedas mantener eso indefinidamente. Este tipo de presupuestos normalmente se ven durante una semana en el Black Friday, el Cyber Monday, o para un evento de ofertas específico, algo así. Es muy raro que un negocio pueda mantener un presupuesto así durante mucho tiempo.</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Formato entrevista: hombre de perfil (no mira a cámara, mira hacia un costado como si hablara con un entrevistador fuera de cuadro), sentado en silla de metal plegable, al aire libre con fondo de pared de chapa acanalada gris, luz de sol dura lateral, remera polo verde, micrófono inalámbrico con pelusa (windscreen) prendido en el cuello. Subtítulos blancos en negrita centrados. Toma fija, sin cortes.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: pregunta directa sobre una cifra impresionante (el presupuesto más grande manejado). Estructura de entrevista pregunta-respuesta: cifra shock ($600.000/día), qué cambia a ese nivel (fatiga creativa, decisiones por hora), contexto de cuándo se usa (Black Friday). Gatillo: número extremo + formato entrevista + curiosidad sobre el detrás de escena de grandes cuentas.</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>sí, formato entrevista simple con una cámara y micrófono de solapa en una ubicación exterior sencilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="88" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>1965</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7662761746049830166</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath reacciona a un posteo de X que muestra que Nike lleva semanas sin stock de la camiseta de Noruega para el Mundial sin siquiera capturar los emails de la gente interesada, señalando que están perdiendo ingresos por no generar leads.</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Nike te está mostrando exactamente cómo NO manejar una situación de stock agotado. Miren esto. Noruega tuvo una racha casi increíble en el Mundial, pero aun así, estamos hablando de Nike, una empresa de 65 mil millones de dólares. Llevan casi tres semanas sin stock. Ahora bien, entender los cambios en la demanda de tus productos y mover montañas para asegurar el stock es parte del trabajo, ya seas Nike o un retailer independiente. Pero lo que es todavía peor es que ni siquiera están haciendo ningún tipo de generación de leads. Capturar el email de la gente, decirles que les vas a avisar cuando haya más stock disponible. Darles un incentivo, un descuento en un combo. Nike literalmente está dejando plata sobre la mesa. El hype de Noruega llegó y se fue. Esas tres semanas podrían haber sido extremadamente rentables. O, en el peor de los casos, podrían haber juntado los leads y revendido una parte de esas camisetas. O, mejor aún, podrían haber vendido combos más grandes.</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Formato 'reacción a pantalla': mitad superior muestra una captura de un posteo de X/Twitter (usuario dennis hegstad) con imagen de un producto de Nike y texto superpuesto 'Nike FLOP at the World Cup'; mitad inferior es la cámara del presentador (remera polo azul oscuro, fondo negro liso, colgante), hablando en formato picture-in-picture vertical. Subtítulos blancos en negrita sobre la franja inferior. La captura permanece fija mientras el presentador habla (mismo gráfico en los tres frames).</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: acusación directa a una marca reconocida ('Nike te muestra cómo NO manejar un sell out'). Estructura: evidencia visual (captura de tuit), diagnóstico del error, y qué deberían haber hecho distinto. Gatillo: polémica/crítica a marca grande y conocida + evidencia concreta (screenshot) + autoridad del especialista en conversión.</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>sí, solo requiere grabarse reaccionando a un tuit/captura de pantalla con el celular, cero producción adicional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="88" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7667358660410019102</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney comparte sus formas favoritas de usar IA esa semana: ChatGPT/Codex para automatizar reportes creativos, automatizaciones con Claude para vigilar Slack y redactar emails, y la herramienta 'Runneth' de Motion para analizar bibliotecas de anuncios y comparar el desempeño de marcas.</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Tengo una amiga estratega creativa que cobra 8 mil dólares por una auditoría creativa, y las marcas la aman. Sacan un montón de valor de ella. Pero dijo algo una locura, que fue que, por culpa de la IA, en realidad le está llevando dos o tres veces más tiempo hacer estos reportes, porque tiene muchísimos más datos e insights para analizar. Y yo pensé: '¡por fin alguien lo dijo!'. Porque últimamente he estado sintiendo como una fatiga en la que pienso: 'ah, pero ¿y este insight tan fascinante? ¿Encaja esto en mi hipótesis general?'. Y bueno, dicho esto, siento que estoy llegando a un muy buen lugar en mi recorrido con la IA. Últimamente estuve usando Codex para hacer los decks para clientes y tener eso completamente automatizado. Voy a compartir eso muy pronto. También estoy usando Claude para crear un montón de automatizaciones que me avisan todos los días, sacando a la luz mensajes importantes de Slack, escribiendo borradores de emails. Contenta de compartir eso también. Y también estuve usando bastante la herramienta Runneth de Motion últimamente, y tengo que decir que mi equipo está obsesionado. Les voy a dar algunos ejemplos de las formas en que la usé en las últimas semanas. Número uno: estamos actualmente incorporando una marca nueva, y tenía algunas preguntas puntuales, del tipo 'me pregunto si alguna vez corrieron anuncios en español' o 'me pregunto si alguna vez usaron contenido UGC (generado por usuarios)', y usando Runneth pude hacer esas preguntas directamente en Slack y que me diera una respuesta definitiva de sí o no para los últimos 365 días. Lo que también me encanta es que pudo hacer algunos reportes de investigación muy copados, en los que confío mucho más que en las otras automatizaciones que hice en el pasado. Porque Runneth en realidad puede mirar los videos dentro de la biblioteca de anuncios, o incluso los videos que vos le subís, ¿no? Muchas veces estos LLMs en realidad solo miran la transcripción. Pero no, Runneth realmente está mirando esos videos cuadro por cuadro y puede dar un análisis mucho más profundo de la pieza creativa en su conjunto. ¡No sé! Si algo de esto les suena interesante y quieren que profundice en algo, cuéntenme en los comentarios. Me estoy sintiendo muy bien con todo esto de la IA últimamente y me encantaría compartirlo.</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Selfie/talking head sentada en un puf/otomana en un living (piso de madera, puerta blanca al fondo, cuadro de paisaje con marco dorado, mueble bajo con parlante), remera celeste y short de raso rojo, aros dorados, sostiene un micrófono de mano tipo podcast. En distintos momentos se superpone una captura de pantalla de un chat estilo Slack con resumen de tareas ('MORNING SWEEP', emails) y luego una captura de un dashboard oscuro de análisis de anuncios (columnas 'Summary/What's Unusual/Personas/Creative/Static'). Subtítulos blancos en negrita arriba. Toma continua a cámara con gráficos superpuestos en momentos puntuales.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Gancho: anécdota contraintuitiva de una colega que cobra $8K y a la que la IA le lleva MÁS tiempo, no menos. Estructura: mini-lista de casos de uso concretos de herramientas de IA (Codex, Claude, Runneth) con ejemplos reales de preguntas hechas. Gatillo: cifra concreta + contraintuitivo + utilidad práctica (tips de herramientas) + pregunta final que invita a comentar.</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>sí, selfie hablado en el living de casa, sin edición compleja salvo pegar un par de capturas de pantalla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="88" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1904</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7660261653258177822</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Una creadora de contenido en Nueva York muestra un corcho (corkboard) gigante que le sobró al redecorar su oficina y lo ofrece de regalo a quien viva en la zona.</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Estoy redecorando mi oficina, y compré un corcho gigante. Esto. Esto es para dar una idea del tamaño. Esa puerta. Esto. Así de grande es esta cosa. Bueno, me mandaron dos, y si estás en la zona de Nueva York, me encantaría regalártelo. Y ya sé lo que estás pensando: corcho... da esta onda. No, da esta onda. Gracias.</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Selfie/talking head grabado con celular en un living luminoso (ventanales grandes, plantas de fondo), con un corte a plano más abierto donde se la ve de cuerpo entero sosteniendo el corcho para mostrar el tamaño. Viste un vestido de encaje crema, pelo recogido. Subtítulo quemado en pantalla en blanco negrita con contorno negro ('anyone in nyc want a big ass cork board?'). Sin gráficos ni cortes a otras escenas.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Gancho inmediato con la pregunta directa en pantalla (¿alguien en NYC quiere un corcho gigante?), estructura simple de mostrar el objeto + contexto + oferta, y el gatillo es el regalo real segmentado por ciudad (genera comentarios pidiéndolo) combinado con humor autoconsciente ('it's giving...').</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Sí, es un selfie casero sin edición compleja; el gancho es el regalo real, no la producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="88" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7663051404734434582</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath analiza en la calle una campaña de Uber para el Mundial que ofrece 30% de descuento a los hinchas del equipo perdedor, destacando el timing y la ejecución de la idea.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Uber acaba de ganar el Mundial. Bueno, si existiera una versión de marketing [del Mundial], sin dudas la ganaron. Es divertido, está pensado para que la gente comparta fotos, con un timing perfecto, y la oferta es buenísima. Los hinchas venían diciendo lo caro que salió el transporte en Nueva York durante el Mundial. Un código de 30% de descuento. Perfecto, 10 sobre 10. Uber, bien jugado.</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Talking head parado en una vereda de ciudad; de fondo se ve un camión con pantalla digital mostrando la promoción de Uber y una estructura/escultura blanca envuelta. Dos capas de texto superpuesto (una línea chica arriba y un titular grande abajo, con emoji), más una etiqueta 'World Cup'. Subtítulos blancos sincronizados palabra por palabra. Toma continua, sin cortes a otras escenas, ropa casual (polo).</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Hook con titular polémico-gracioso sobre el Mundial (Uber lastimó aún más a los hinchas de Inglaterra), estructura breve de elogio punto por punto (timing, shareability, oferta), y el gatillo es la actualidad deportiva combinada con humor y un caso real de marketing bien ejecutado.</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>Sí, es una grabación simple en la calle con el celular más un par de textos superpuestos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="88" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>1653</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665693455577845014</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath conversa con otro creador junto al mar sobre por qué pagar 135.000 dólares por un día de asesoría con Alex Hormozi puede tener sentido. El entrevistado explica que, al operar a una escala similar con su propia marca personal, un consejo tan específico justifica la inversión.</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Con Alex Hormozi en particular, construyó la mejor marca personal que se haya visto en el mundo de los negocios, rompiendo récords en todos lados. Y la está monetizando a un ritmo de cientos de millones de dólares por año. Así que gastás 135.000 dólares por un día con Alex Hormozi. Estoy operando a una escala en la que pagar por ese consejo tiene sentido. Creo que es una de las pocas personas en el mundo que podría darme un consejo muy específico para mi situación. Él llegó a donde yo quiero llegar. Lo hizo dentro de un rubro similar al mío. Yo construí un negocio a una escala más chica, basado en una marca personal. Yo monetizo una marca personal. Es como que creo que él va a poder darme consejos muy tácticos que, ojalá, hagan una gran diferencia.</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Conversación entre dos personas sentadas en un banco de piedra con vista al mar y veleros de fondo (locación tipo evento/resort). Edición en pantalla dividida que alterna entre los dos interlocutores hablando por separado. Subtítulos blancos negrita, con resaltado en caja de color para alguna frase clave. Vestimenta casual/business casual (polo, camisa, anteojos de sol), luz de día natural.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Abre con una cifra shockeante (135.000 dólares por un día), estructura de justificación de esa inversión, y el gatillo es la autoridad/status de Alex Hormozi combinado con un número concreto y extremo.</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>Sí, alcanza con una charla grabada en exteriores y un corte a dos planos; el valor está en el contenido, no en el equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="88" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1282</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7658382928216395038</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney reflexiona sobre su paso por Cannes Lions con clips de un panel donde habló del poder de los creadores. Cuenta cómo pasó de sentir vergüenza por una nota que la criticaba por enseñar publicidad en TikTok, a sentirse validada como creadora en el festival de este año.</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Esto es lo último que voy a decir sobre Cannes Lions. En el panel de Dark Room Villa, cuando dije que los creadores tienen el poder en la sala en este momento, fue algo muy, muy personal para mí, porque hace 18 meses, una publicación grande de publicidad que no voy a nombrar escribió una nota de porquería, un periodismo de mierda, donde mi nombre y mi trabajo fueron el chiste, que era: 'no podés aprender publicidad en TikTok'. Sentí tanta vergüenza que no creé contenido durante semanas después de eso. Así que estar en Cannes este año, donde los creadores fueron celebrados, donde los gatekeepers [los que controlan el acceso] nos sostuvieron la puerta abierta y nuestro trabajo fue validado, se sintió increíble. Trabajé en la industria publicitaria durante 10 años, hice contenido para anunciantes durante seis. Y a esta altura, todos sabemos cuál es la gran conclusión cliché de Cannes este año: che, los creadores son realmente importantes para el futuro de la publicidad. Y para los que creamos y consumimos contenido online, eso lo sabemos hace años. Pero para los gigantes de la industria, para la institución que se mueve lenta y que en realidad dirige este negocio, es algo nuevo, es novedoso, y vale la pena repetírselo. Para mí, lo que realmente me entusiasma es que, por un tiempo, ahora mismo, el poder está verdaderamente en manos de individuos de todo tipo de orígenes, de los que tenemos un punto de vista único y decidimos apretar 'publicar'. Así que un enorme gracias a Dark Room Villa por ser un refugio gigante para mi alma introvertida esta semana. Gracias a Orange John [?], Josh Levine y Matt de Whisper Flow por compartir su genialidad conmigo en el panel. Y muchísimas gracias a vos que te quedaste viendo hasta el final, porque, sí, escribí el guion un poco borracha en el avión de vuelta a casa. Los quiero. Chau.</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Video con narración en off sobre varias tomas de B-roll grabadas en un evento (aparenta ser Cannes Lions): ella hablando arriba de un escenario iluminado de rojo de noche con público filmando con celulares; caminando por una playa al atardecer con acreditación colgada; sentada en un banco de piedra bajo un gazebo con vista al mar. Textos grandes en amarillo negrita tipo 'quote card' superpuestos en los momentos clave, y subtítulos blancos estándar sincronizados con la voz en otras partes. Varios cambios de vestuario, lo que sugiere múltiples clips editados juntos.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Abre con una frase potente sobre poder (los creadores tienen el poder en la sala), estructura de storytelling personal (humillación pasada seguida de validación presente), y el gatillo es la vulnerabilidad/caso real combinado con un tema de actualidad de la industria (creadores vs. instituciones tradicionales).</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>Sí, aunque requiere planificación de varias tomas (B-roll) durante un evento real; la narración en off es lo que sostiene el video, no equipo caro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="88" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Neil Patel</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>1135</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@neilpatel/video/7655303772008189197</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Usa el caso de Tesla (de 2.000 a 20.000 millones de ingresos en 30 meses) para explicar un framework simple de auditoría de embudo: distinguir pasos 'requeridos' (legal, operativo o pedido por el cliente) de pasos 'heredados' que solo generan fricción.</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Tesla pasó de 2.000 millones a 20.000 millones de dólares en ingresos en menos de 30 meses. Una parte enorme de eso fue simplemente eliminar lo que nunca debió haber estado ahí. Y acá está el tema: no fue solo su checkout. Cada capa de su embudo tenía el mismo problema, y el tuyo también. Tenés que hacerte una sola pregunta: ¿este paso es realmente necesario, o simplemente lo heredamos? Necesario significa tres cosas: que sea legalmente requerido, que sea operativamente necesario, o que el cliente lo haya pedido específicamente. Heredado significa que alguien lo agregó en algún momento y nunca nadie tuvo el coraje de sacarlo.</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en estudio con fondo de paneles/rayas color salmón-naranja, formato vertical con motion graphics superpuestos: gráfico de línea estilo 'stock chart' verde con la cifra '$20' arriba y subtítulo 'in revenue' debajo; gráfico de embudo en rojo con subtítulo 'had the same'; ícono animado 'Legally required' con un martillo de juez. Cortes rápidos entre presentador y placas gráficas a pantalla completa.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con cifra impactante y caso de marca reconocida (Tesla, de 2 a 20 mil millones en 30 meses) que da autoridad y curiosidad inmediata. Framework simple y memorable (requerido vs. heredado) fácil de aplicar por el espectador a su propio negocio, reforzado visualmente con gráficos que sintetizan cada idea.</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>no + depende de motion graphics personalizados y un set de estudio de marca, más difícil de igualar sin herramientas de edición y diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="88" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>1117</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7652027052584979734</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath desglosa en puntos por qué el anuncio de Nike celebrando el título de los Knicks es una genialidad de marketing. Destaca el timing, la música, el product placement y el hecho de haber sido filmado en los festejos reales con hinchas auténticos.</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Hoy voy a analizar el nuevo anuncio de Nike que celebra el campeonato de los Knicks. Esto es una genialidad, y te cuento por qué. Primero, el timing: lo lanzaron al día siguiente [?], de alta producción [?]. Los anuncios así normalmente no son tan reactivos, pero este realmente se nutre del momento y los ayuda a apropiárselo. La elección de la música es increíble: es una canción sobre alguien que rechaza Miami o Hollywood para estar junto al Hudson. Los neoyorquinos están orgullosos de su ciudad, y esto juega justo con eso. Además, es lo único que se escucha: las imágenes muestran el caos típico de Nueva York, pero la música lo tapa por completo. Realmente quieren que sientas algo. Después, el product placement: Nike patrocina a la NBA desde hace nueve años, las dos marcas van de la mano. Nike no necesita hacer una venta agresiva, necesitan convertirse en la cultura y en el sentimiento del momento. La parte realmente genial es que en realidad lo filmaron durante los festejos reales: no hay sets ni actores, son personas reales celebrando el momento real. Capturaron la sensación que normalmente solo se logra con cine de alta producción, pero con hinchas crudos y auténticos. Y por último, el eslogan es genial: 'nunca durmieron, siempre soñaron'. Nueva York es la ciudad que nunca duerme, y lo mismo el equipo, que nunca abandonó el sueño de ganar el campeonato durante 54 años [?]. Y encaja perfectamente con el eslogan de Nike, 'impossible is nothing' [imposible no es nada] [?]. 10 sobre 10. Gran trabajo, Nike.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Talking head sentado a una mesa de living/cocina, luces colgantes y cuadro enmarcado de fondo, con micrófono clip en la remera (polo con franjas). En un momento la pantalla se divide: arriba sigue él hablando, abajo se inserta un clip del anuncio de Nike que está analizando (escena nocturna con tono verdoso). Subtítulos blancos negrita sincronizados palabra por palabra. Luz natural de ventana.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>Promete un análisis experto desde el inicio (esto es una genialidad y te digo por qué), estructura clara en puntos numerados (timing, música, product placement, autenticidad, tagline), y el gatillo es la actualidad deportiva sumada a la autoridad de marketing.</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Sí, es talking head casero más un clip del anuncio ya existente insertado, sin equipo profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="88" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7649716623909178646</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista callejera en formato 'blind ranking' en la que alguien ordena a ciegas, del 1 al 5, las mejores películas sobre negocios: Moneyball, El fundador, El lobo de Wall Street, La red social y La gran apuesta, justificando cada elección a medida que las va ubicando.</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>¿Querés armar un ranking a ciegas de las mejores películas de negocios? Moneyball. Me gusta Moneyball. No... el 3. Que quede en el medio. El fundador. Me parece que se enfocan demasiado en mostrarlo como el malo de la película, lo cual... bueno, como sea. Pero malos hay en todos lados. La parte que a mí me interesa es la historia de éxito increíble de McDonald's. Así que le voy a dar el puesto cuatro. El lobo de Wall Street. Ah, esa va en el puesto 1. Es tan entretenida, una locura. Me encanta que esté basada en una historia real. La ves y pensás: '¿en serio hicieron eso? ¿en serio hicieron eso?'. Así que sí. Puesto uno [?], La red social. Y me parece que La red social... seguramente se enfocan demasiado en la traición, ya sabés, entre Mark y los demás. No la querés poner en el puesto 5. Dale, entonces. Ponela en el puesto 2. La gran apuesta. Y ya me quedan cinco [?]. Cierto, a esa definitivamente la pondría más arriba. Para mí esa es probablemente el puesto 2. Antes de eso, lo único que me queda es el puesto cinco para La gran apuesta. Genial. La gran apuesta es muy interesante, la explican realmente bien. De nuevo, es otra basada en una historia real que pasó. Tengo edad suficiente como para acordarme de cuando pasó. Tiene que ir en el puesto 5, pero si pudiera, la cambiaría.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista en la vía pública (frente a un canal con arcos y balcones, set tipo The Venetian, Las Vegas). Encuadre plano medio del entrevistado parado con mochila, hablando hacia un entrevistador fuera de cuadro. Gráfico superpuesto sobre el pecho: miniaturas de pósters de las películas que se acomodan en 5 casilleros numerados y coloreados (verde, amarillo, amarillo, naranja, rojo) a medida que se completa el ranking. Subtítulos quemados abajo en blanco, mayúsculas, centrados. Luz natural de día, sin cortes de cámara visibles en los frames revisados.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de pregunta directa ('¿querés armar un ranking a ciegas?') que invita a la audiencia a jugar en su cabeza y comparar su propio orden. El formato de entrevista callejera + gráfico de ranking en vivo genera curiosidad progresiva por ver en qué termina el orden, y el tema (películas populares + ángulo de negocios) cruza dos audiencias distintas. El gatillo principal es la curiosidad por el resultado final y el mini-debate/justificación de cada elección.</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: solo necesita una persona con celular, preguntarle a alguien en la calle y armar el gráfico de casilleros numerados en una app de edición tipo CapCut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="88" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>984</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7664541099402218774</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Un consultor de ads propone una campaña hipotética para Spotify Premium centrada en 'momentos arruinados' por interrupciones publicitarias (subte, gimnasio, avión, fiesta), y explica por qué esa estrategia de criticar la propia versión gratuita solo funciona para una marca dominante como Spotify.</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Esto es lo que haría yo si estuviera manejando anuncios pagos para Spotify Premium. Los anuncios actuales son simplemente aburridos, y están vendiendo mucho más características que sensaciones. Así que armaría la campaña alrededor de una sola idea central: que Premium elimina los momentos que te arruinan la música. Mostraría a alguien en el subte sin señal, a alguien a mitad de un entrenamiento al que lo interrumpe un anuncio, a alguien en un vuelo que se olvidó de descargar música, a alguien organizando una fiesta a la que de repente le suena un anuncio. Y apuntarle a estos puntos de dolor hace que el mensaje sea mucho más fuerte. Cosas como '¿seguís siendo interrumpido? Probá Premium gratis por un mes'. Para que quede claro, esto es arriesgado, porque al hacer esto están criticando su propia versión gratuita. Así que no se lo recomendaría a una marca retadora. Pero Spotify sí lo puede hacer, porque no es una marca retadora. Son el gorila de 400 kilos [800 pound gorilla] del mundo del streaming de música. Se pueden dar el lujo de tomar un riesgo así.</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Talking head de pie junto a una pizarra/pantalla con logos de servicios de streaming de música (SoundCloud, YouTube Music, Deezer, Amazon Music, Tidal) y el logo de Spotify superpuesto en grande. Incluye un inserto de video dentro del video mostrando una escena de gimnasio para ilustrar el 'punto de dolor' de la interrupción. Subtítulos blancos palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de pregunta directa al espectador ('¿correrías esta campaña?') más formato de 'rediseño de campaña real' de una marca conocida (Spotify), que da autoridad de experto en ads y genera opinión/debate en comentarios. La idea creativa (dolor emocional en vez de features) es fácil de entender y memorable.</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>sí + alcanza con una pizarra o pantalla de apoyo y grabarse explicando la idea de campaña, aunque el inserto de video ilustrativo suma algo de producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="88" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>981</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7654580842609511702</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>En una entrevista callejera, un experto en ads responde qué consejo le daría a su yo de 23 años al empezar su agencia: delegar mucho antes en vez de acumular todos los roles del negocio (ventas, contabilidad, diseño web) él mismo.</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>¿Qué consejo le darías a tu yo de 23 años que recién estaba arrancando la agencia, en una sola frase? Hacer muchas menos de las tareas que yo hacía. Cuando recién empecé, y durante muchos años, yo era el departamento de ventas, entregables, generación de leads, administración de marca personal, el contador, yo escribía la política de privacidad del sitio web, yo hacía el diseño del sitio web. Hacía literalmente todo, viste. Y tuve que hacer eso al principio porque no tenía la plata para que no fuera así. Pero en vez de decir 'ah, ahora estoy ganando 100 mil al año, qué bueno', lo que debería haber hecho es mantener mi estilo de vida bien económico y reinvertir eso enseguida, en vez de esperar años, tener mucho más, antes de empezar a delegar todos esos roles. Porque para todos esos roles, hay alguien mejor que yo. A quien puedo convencer de que trabaje para mí y pagarle. En vez de ser yo el que hace todo en mi práctica personal. Me dije: hay una sola cosa que nadie más puede hacer por mí, pero todo lo demás debería estar haciéndolo alguien que sea mejor que yo en eso.</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista al aire libre en una locación turística con arquería histórica de fondo (estilo Palace of Fine Arts, San Francisco), entrevistado con remera polo. Texto superpuesto tipo titular en la parte superior ('$300M Founder Advice: Starting a business in your 20s? Do THIS') y subtítulos amarillos palabra por palabra más abajo. Cámara con poca profundidad de campo (fondo desenfocado), estilo entrevista de calle.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Formato de entrevista callejera con pregunta directa y personal ('¿qué le dirías a tu yo de 23 años?') que genera curiosidad y autenticidad. El titular superpuesto usa la cifra '$300M' como gancho de autoridad, y la respuesta ofrece una lección de negocios concreta y aplicable (delegar antes) con ejemplos específicos de tareas.</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>sí + requiere salir a grabar entrevistas en la calle con una sola cámara y agregar subtítulos, sin edición compleja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="88" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>972</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7649707042650787094</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>En una entrevista callejera, un experto en publicidad responde con qué titular de cinco palabras describiría a Tesla: 'mejores autos por menos plata', explicando la relación calidad-precio frente a la competencia.</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Si tuvieras que escribir un titular publicitario para Tesla con solo cinco palabras, ¿cuáles serían esas cinco palabras? Yo creo que sería 'mejores autos por menos plata'. La calidad de auto que obtenés cuando comprás un Tesla, comparada con lo que pagás, está muy por encima de la competencia en muchos casos. Si hace cinco años hubieras querido conseguir esa calidad de auto de otra marca, habrías estado pagando [?, en el audio 'playing'] mucho más. Creo que esa es la cosa número uno.</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista al aire libre en una locación turística con calesita y locales de feria de fondo (estilo muelle turístico/Pier 39, San Francisco), entrevistado con anteojos de sol y remera polo. Texto superpuesto tipo titular en la parte superior ('$300M Meta Ad Expert rebrands Tesla in 5 words') y subtítulos amarillos palabra por palabra. Mismo estilo de cámara con fondo desenfocado que la fila 117 (parece la misma sesión de entrevistas).</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>medio-alto</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Formato de reto con restricción concreta ('solo cinco palabras') que genera curiosidad inmediata sobre la respuesta. El titular superpuesto usa autoridad numérica ('$300M Meta Ad Expert') y el gancho de una marca muy conocida (Tesla) para maximizar el interés, en un video corto (19 seg) fácil de consumir completo.</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>sí + mismo formato reutilizable de entrevistas callejeras cortas con una sola pregunta y subtítulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="88" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>785</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7637404028070137118</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Una estratega creativa/de marketing repasa cronológicamente todos sus trabajos, edades y salarios iniciales hasta llegar a facturar 200.000 dólares con el lanzamiento de un curso online, y argumenta por qué la IA no amenaza sino que potencia a los creadores de cursos con marca personal.</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Este es cada trabajo que tuve en mi vida, mi edad y mi salario inicial. Comparto esto porque creo que los estrategas creativos están particularmente muy bien posicionados para cambiar sus vidas en cuestión de años, comparado con lo que a nuestros padres les hubiera llevado décadas lograr. La primera parte de mi carrera la pasé en el sector humanitario. Viví en África Occidental, India y Medio Oriente, que en teoría es el extremo opuesto de lo que hago ahora, que es publicidad. Y cuando me pasé al marketing, tuve algunos años difíciles. Me despidieron de este trabajo después de solo tres meses, y esta startup fracasó en apenas unos seis meses. Ahora, durante este trabajo, empecé a hacer tutoriales de compra de medios (media buying) en YouTube. Durante la pandemia yo no era la mejor media buyer del mundo, en realidad solo estaba enseñando lo que iba aprendiendo en tiempo real. Hice esto durante varios años y generaba un poco de ingresos de acá y de allá, pero el gran punto de quiebre para mí fue cuando lancé mi curso en Teachable. Hice 200 mil dólares solo con ese lanzamiento, lo cual es una locura. Y lo loco es que ahora creo que en realidad hay todavía más oportunidades para que los estrategas creativos triunfen, especialmente los que tienen su propio negocio. Y es gracioso, siempre me preguntan: '¿no te preocupa que otros estrategas creativos lancen cursos?'. Y yo pienso: no, ¿qué? Realmente creo que lo que la IA está eliminando son los cursos genéricos, los cursos que no tienen una cara o un nombre detrás. Y lo que está generando es este deseo cada vez mayor de entender cómo cada estratega creativo, individualmente, encara este trabajo. Yo voy a tener un enfoque de estrategia creativa distinto al de Sarah Levinger, al de Savannah Sanchez, al de Joanna Wallace. Y por eso creo que hay más que suficiente oportunidad para que los estrategas creativos tengan sus propios productos online. Pero tengo curiosidad, ¿ustedes qué piensan?</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Talking head selfie estilo vlog en un living/oficina hogareña (estantería, espejo, planta), con micrófono tipo shotgun sostenido en mano hacia la cámara, vestimenta formal (blazer). Gráfico superpuesto: tabla tipo spreadsheet (columnas Role, Organization, Compensation, Age) que lista su historial laboral, visible arriba mientras ella habla abajo. Otro frame muestra un recuadro picture-in-picture con un clip 'detrás de escena' de ella siendo filmada, superpuesto sobre una captura de un dashboard de anuncios. Subtítulos quemados en blanco, centrados abajo.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de curiosidad numérica: abre mostrando literalmente la tabla con cada salario que tuvo, algo que genera curiosidad inmediata (a todos les interesa espiar sueldos ajenos). Sigue una estructura de historia de superación (trabajos humanitarios mal pagos, despidos, fracasos) hasta un giro con cifra concreta (200K de un lanzamiento), lo que da autoridad. Cierra con pregunta abierta para generar comentarios y un ángulo contraintuitivo sobre IA que genera reacción entre otros creadores de cursos.</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: el gráfico de tabla de salarios se arma fácil en Canva o Google Sheets y todo se graba con el celular en casa; lo difícil de replicar es tener una historia con números reales y concretos para mostrar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="88" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7637148950180433168</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>El creador explica cómo usaría la inteligencia artificial si fuera adolescente hoy: como 'gimnasio mental' diario para aprender de negocios, prepararse para entrevistas y reflexionar antes de dormir, y cuenta que sus propios hijos, menores de 10 años, ya generan ingresos usando IA.</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Nadie les está enseñando a los adolescentes cómo usar la IA de verdad. Así que esto es lo que yo haría. Si yo fuera vos, usaría la IA como un gimnasio mental, y la usaría todos los días. Le pediría a ChatGPT que me explique distintos modelos de negocio haciendo de cuenta que es mi emprendedor favorito. Que me ayude a planificar el día, a prepararme para entrevistas de trabajo, a desglosar ideas grandes, o lo que sea que me interese. Mientras voy caminando a la escuela, estaría escuchando un podcast hecho con IA. En el almuerzo, estaría leyendo un caso de estudio de dos minutos sobre IA. Antes de dormir, estaría reflexionando con ChatGPT, pidiéndole que repase cosas como qué aprendí, qué es lo que todavía necesito que me expliquen, o qué es lo que no terminé de entender. Y miren, no estoy especulando: mis propios hijos ya están haciendo esto. Ya empezaron a aprender habilidades de alto valor. Ganaron plata y tienen miles de dólares ahorrados. Yo no les di ni un centavo, y todos tienen menos de 10 años. Simplemente empezaron temprano, se mantuvieron curiosos y usaron la IA como un mentor diseñado para ayudarlos a lograr prácticamente cualquier cosa que se propongan en serio. La buena noticia es que la mayoría de la gente de tu edad no está haciendo nada de esto. Así que si empezás ahora, no solo te vas a adelantar, vas a estar construyendo un superpoder que se va a ir multiplicando con el tiempo.</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en estudio oscuro (fondo negro con una guitarra eléctrica roja colgada y una planta), plano medio corto, sentado frente a un escritorio de madera oscura, remera negra lisa. Subtítulos quemados palabra por palabra estilo 'karaoke', tipografía gruesa amarilla con contorno/brillo negro, centrados sobre el pecho. Un solo ángulo de cámara fijo, sin cortes de escena ni gráficos adicionales en los frames revisados.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de afirmación polémica y de autoridad ('nadie le está enseñando esto a los adolescentes') que posiciona al creador como el que sí sabe. Estructura de lista de hábitos concretos y aplicables (caminando a la escuela, en el almuerzo, antes de dormir), fácil de seguir. Cierra con prueba social/autoridad personal (sus hijos menores de 10 ya ganan plata con esto) y una promesa de resultado compuesto a futuro, con gatillo de urgencia ('empezá ahora').</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: es un video de cámara fija hablando a cámara con subtítulos animados, fáciles de generar con CapCut u otra app gratuita, sin gráficos complejos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="88" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7641652246979104001</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Charla directa a cámara sobre un principio de venta/persuasión: la gente no cambia hasta que quedarse donde está duele más que cambiar; usa el ejemplo de alguien con un trabajo mediocre pero 'tolerable' para explicar cómo hacer emerger ese 'dolor latente' con una pregunta poderosa.</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>La mayoría de la gente no se mueve hasta que quedarse donde está se siente más doloroso que cambiar. Esa es la verdad. Y si querés vender más de lo que sea —tu servicio, tu curso, tu coaching—, tenés que aprender a generar ese momento de darse cuenta. Así que hagamos esto concreto. Pensá en alguien que tiene un trabajo de 9 a 5 decente. Gana una plata está bien. Su vida no es genial, pero tampoco se le está cayendo a pedazos. Va tirando. Pero por debajo de la superficie, odia los lunes. Se siente invisible en el trabajo. Scrollea sin pensar en el teléfono a la noche para distraerse del hecho de que su vida en realidad no se siente como su vida. Si le preguntás cómo le va, va a decir algo como 'sí, estoy bien, tirando'. Pero si le hacés una pregunta más poderosa, como '¿qué pasa si dentro de tres años seguís haciendo exactamente lo mismo?', silencio. Esa es la grieta, ese momento en el que el 'estar bien' deja de sentirse bien del todo. Eso es lo que llamamos dolor latente que se vuelve consciente. Siempre estuvo ahí, simplemente todavía no lo sabían. Y ahí es donde vos ajustás la tuerca. No para ser cruel, sino para mostrarles lo que es posible.</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Talking head, plano medio, sentado a un escritorio de madera, remera/chomba negra, fondo con un tablero de dardos y estantería desenfocados. Se intercalan pantallas completas negras con texto animado tipo tarjeta de cita ('That's the TRUTH' en blanco/celeste; 'SILENCE' en blanco con un ícono de figura tapándose la boca) que cortan el video para enfatizar frases clave, casi como diapositivas entre segmentos hablados. Subtítulos quemados con palabras clave resaltadas.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con afirmación tajante y contraintuitiva sobre comportamiento humano ('la gente no cambia hasta que...'), que funciona como una verdad universal fácil de asentir. Estructura de storytelling con un personaje genérico relatable (el del trabajo 9 a 5 'tolerable') y una pregunta retórica que genera tensión, seguida de una pausa dramática remarcada visualmente con una pantalla de texto ('SILENCE'). El gatillo es la identificación personal del espectador con la situación descripta.</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: solo requiere hablar a cámara y agregar un par de pantallas de texto negro entre tomas, editable en cualquier app de celular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="88" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7639437775430765831</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Explica el concepto psicológico de 'reactancia' (querer más algo cuando se lo restringe) con ejemplos cotidianos —un botón de 'no presionar', prohibiciones de la infancia— y lo aplica al marketing, contrastando la escasez falsa ('solo quedan 3 lugares') con la reactancia real, lograda haciendo que el cliente sienta que debe calificar para trabajar con la marca.</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Imaginate por un segundo que entrás a una habitación y hay un botón rojo grande con un cartel arriba que dice 'no presionar'. Bueno, ¿cuál es lo primero que querés hacer? Presionarlo. Obviamente, eso es la reactancia en acción. Pensá en cuando eras chico y tus padres te decían 'no entres a esa habitación'. Bueno, ¿cuál era lo primero que querías hacer? Entrar a esa habitación. No era porque la habitación fuera interesante, era porque alguien te dijo que no podías. Y en el momento en que alguien te restringe el acceso a algo —incluso algo que ni te importaba hace apenas unos segundos— tu cerebro lo percibe como una amenaza a tu libertad. Y las amenazas a la libertad disparan un impulso casi primitivo de restaurar esa libertad de inmediato. Esto es lo que muestra la investigación: allá por los años 60, el psicólogo Jack Bream [?, posiblemente Jack Brehm] descubrió algo fascinante sobre el comportamiento humano. Cuando las personas sienten que su libertad está siendo amenazada o limitada de cualquier manera, experimentan reactancia psicológica, que es una motivación intensa para restaurar esa libertad. En otras palabras, en el momento en que hacés que algo se sienta limitado, restringido o difícil de conseguir, la gente lo quiere más. Por eso los chicos quieren el juguete con el que está jugando su hermano. O por eso la gente quiere entrar al boliche exclusivo que tiene fila afuera. Y por eso los compradores quieren el producto que casi siempre está agotado. Pero acá es donde la mayoría de los dueños de negocios se equivocan por completo. Piensan que escasez significa decir 'me quedan solo tres lugares' o 'esta oferta vence el viernes'. Pero eso no es reactancia psicológica, eso generalmente es escasez falsa, y tus potenciales clientes la huelen a un kilómetro de distancia. La reactancia psicológica real ocurre cuando hacés que la gente sienta que necesita calificar para poder trabajar con vos.</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>El presentador (remera negra, plano medio-corto, mismo estudio oscuro con planta) aparece recortado dentro de un marco con esquinas redondeadas que flota sobre un fondo gris con grilla/cuadrícula, dejando bordes vacíos a los costados. Sobre el escritorio se ve un botón rojo grande tipo 'buzzer' de utilería, coherente con la historia que cuenta. Subtítulos quemados en blanco con palabras clave resaltadas en verde brillante.</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con escenario hipotético universal e identificable (el botón rojo de 'no presionar') que genera curiosidad inmediata y usa un prop físico real en cámara para reforzarlo. Estructura de ejemplo cotidiano → cita de autoridad científica (psicólogo de los años 60) → aplicación práctica al negocio → corrección de un error común ('la mayoría se equivoca'). El gatillo combina curiosidad, autoridad científica y la promesa de corregir un error extendido entre dueños de negocio.</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: el prop del botón rojo es opcional y barato de conseguir; el resto es hablar a cámara con edición de subtítulos animados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="88" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7662707329476922641</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Usando la metáfora del iceberg del Titanic, explica por qué el marketing basado solo en tácticas visibles (trends, hacks de redes) falla si no está construido sobre la psicología profunda de por qué compra la gente, y promociona una capacitación gratuita sobre el tema.</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>La mayoría de los dueños de negocios no fracasan porque su servicio sea malo. Fracasan porque su marketing está construido sobre tácticas superficiales en lugar de los disparadores psicológicos más profundos que son los que realmente impulsan las ventas. Suena un poco confuso, así que déjenme darles una mejor forma de pensarlo. Imaginate el Titanic. Al barco lo llamaban insumergible, pero todos sabemos cómo terminó esa historia. Todo el mundo se acuerda del iceberg. Pero lo que la mayoría se olvida es que no fue la parte de arriba, la que se veía en la superficie, la que causó el daño. Fue la enorme estructura oculta debajo del agua. Lo mismo pasa en marketing. Todo el mundo se enfoca en lo visible: hablan de trucos de redes sociales, del audio que está de moda, o de los asuntos de los emails. Esa es la punta del iceberg. Parece importante, capta la atención, pero no es lo que hace o rompe tu negocio. El verdadero poder vive debajo de la superficie. Ahí está la psicología detrás de por qué compra la gente, en qué confía y cómo toma decisiones. Y si ignorás esa parte, ninguna táctica te va a salvar. A este error yo lo llamo 'la trampa del Titanic'. Es fácil caer en ella: sale un video nuevo que se hace viral, entonces copiás el formato; alguien dice que tal funnel está funcionando, entonces también lo probás. Vas saltando de una cosa a la otra esperando que algo finalmente prenda. Ese tipo de marketing parece activo, pero no tiene dirección. No hay un mensaje central, no hay estructura, solo hay movimiento. Y esto es un problema grande porque el cerebro humano no está hecho para la complejidad. Por defecto, funciona con unos pocos instintos clave: buscar placer, evitar el dolor, conservar energía. Si tu mensaje no le habla a esos instintos [?], la gente simplemente lo ignora. No es personal, es solo cómo estamos programados. Y acá está la parte que a la mayoría se le pasa: podés seguir cada táctica a la perfección y aun así no va a funcionar si tu oferta no conecta a un nivel más profundo. Es como tirarle kétchup a tu receta de cookies con chips de chocolate porque algún influencer dijo que funciona bien. Que algo esté de moda no significa que tenga que estar en tu estrategia. Kétchup y cookies... eh, en cambio el marketing que funciona se siente natural, el mensaje llega y la gente presta atención, quiere saber más. Pero esto no pasa por accidente. Pasa cuando tu oferta le habla a la parte del cerebro que dice 'esto resuelve mi problema'. La buena noticia es que no necesitás una audiencia enorme para que esto funcione. Solo necesitás claridad. Tu contenido tiene que responder preguntas que la gente ya se está haciendo, en el lenguaje que ya usa. Y tu oferta tiene que sentirse como el paso siguiente más fácil, más seguro y más lógico para resolver su problema. Por eso dedico tanto tiempo a enseñar psicología en lugar de solo tácticas. Porque una vez que entendés qué es lo que la gente realmente está buscando, podés ajustar todo lo demás alrededor de eso: tus anuncios, tus landing pages, tus emails, todo empieza a rendir mejor. La verdad es que el éxito en marketing viene de la alineación, no de la actividad aleatoria, no del ruido. Necesitás un mensaje que conecte con cómo la gente realmente toma decisiones. Sin eso, tus tácticas son solo decoración superficial. Si venís haciendo el trabajo pero todavía no estás viendo resultados, probablemente sea por eso. No estás haciendo nada mal, simplemente estás construyendo tu estrategia sobre la parte equivocada del iceberg. Y si estás listo para pasar de un marketing superficial a algo que realmente funcione, tengo una capacitación gratuita que te guía por todo el sistema, y el link está en la descripción o en el link de la bio, para empezar por la psicología y construir todo lo demás a partir de ahí.</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Fuerte uso de motion graphics y material de archivo en lugar de talking head puro: metraje de archivo en blanco y negro del Titanic navegando de noche con textura de grano/ruido de película vieja y texto animado ('THE SHIP') en amarillo; ilustraciones vectoriales en tonos amarillo/negro de una silueta humana con traje y corbata ('THE HUMAN') y de esa misma silueta señalando a un público sentado ('MUCH TIME'). Tipografía en negrita con animaciones de aparición sincronizadas con la narración en off; no se ve al presentador hablando a cámara en los frames revisados.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Gancho contraintuitivo de autoridad ('no fracasan por el servicio, fracasan por esto otro') seguido de una metáfora visual poderosa y memorable (el iceberg del Titanic) que estructura todo el video. Estructura de storytelling con nombre propio para el error ('la trampa del Titanic'), concepto pegadizo y compartible. Combina autoridad, un caso cultural conocido por todos (el Titanic) y humor (el ejemplo del kétchup con cookies) como gatillos, y cierra con llamado a la acción hacia contenido gratuito.</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>no + nota: requiere metraje de archivo con licencia y animación vectorial personalizada; se podría abaratar con plantillas de motion graphics ya hechas, pero no es un simple video hablando a cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="88" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>578</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7663113511056264465</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>El creador cuenta cómo pasó de perseguir clientes con anuncios y DMs en frío sin éxito a usar una 'auditoría sigilosa' y tres disparadores psicológicos de retención, lo que llevó a su agencia a facturar entre 147.000 y 190.000 dólares mensuales recurrentes.</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Cuando arranqué mi negocio por primera vez, hice lo mismo que hace todo el mundo. Corrí anuncios, mandé DMs en frío, perseguí leads como si mi vida dependiera de eso. Y aun así no era suficiente. Después probé algo distinto: una pequeña auditoría discreta que no se sentía como venta, pero que conseguía clientes como loco. Ese único método me ayudó a construir mi agencia hasta superar los 147.000 dólares por mes. Sin anuncios, sin pitchear, sin outreach en frío. Pero acá está la cuestión: conseguir clientes es solo la mitad de la batalla. La plata de verdad está en lograr que esos clientes se queden a largo plazo. Miren, la mayoría de las agencias, coaches y profesionales de servicios pierden clientes cada tres meses. Yo era uno de ellos: firmaba un cliente, trabajaba duro, y después lo veía desaparecer a los 90 días. Era agotador. Pero todo cambió cuando descubrí dos cosas. Primero, un método que llamo 'la auditoría sigilosa' (stealth audit), que convierte clientes de alto valor discretamente. Segundo, tres disparadores psicológicos poderosos que mantenían a esos clientes contentos, que se quedaran y que siguieran pagando durante 18 meses o más. Juntos, estos dos sistemas me llevaron de ser un freelancer que la estaba peleando a construir una agencia que generaba entre 147 y 190 mil dólares por mes en ingresos recurrentes.</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Combina talking head con gráficos: un frame muestra íconos simples (Google Ads, un ícono de mensaje/DM, un imán de leads) con textos cortos debajo ('Ran Ads', 'Sent cold DMs') sobre fondo negro. Otro frame muestra al presentador en plano medio, remera negra, con un efecto de encuadre superpuesto (la misma imagen de fondo, desenfocada, detrás del recuadro principal), sentado a un escritorio con una taza y un reflector de estudio tipo fotográfico visible. Otro frame usa un ícono en forma de antifaz rojo con brillo neón y el texto 'Stealth Audit' sobre fondo negro con grilla. Subtítulos quemados con palabra clave resaltada en verde.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de identificación ('hice lo mismo que hace todo el mundo... y no alcanzaba') seguido de contraste con una solución simple y una cifra concreta y alta ($147.000/mes) que da autoridad y genera curiosidad sobre el método. Estructura de problema (perder clientes a los 90 días) → giro con nombre propio pegadizo para el método ('stealth audit') → resultado cuantificado. El gatillo principal es la cifra concreta de facturación combinada con la promesa de un método 'no obvio' y sin publicidad paga.</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: la base es hablar a cámara con textos e íconos simples superpuestos (disponibles gratis en Canva); el efecto de marco/blur de fondo pide un poco más de edición pero sigue siendo accesible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="88" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>571</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7656888890799836423</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Presenta un 'playbook' de siete pasos de marketing (conocer a la audiencia, mensaje claro, canales correctos, automatización, datos, contenido evergreen y fidelización) para escalar un negocio sin agotarse, y cierra promocionando el software HighLevel con una prueba gratuita de 30 días.</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Si querés hacer crecer tu negocio sin quemarte en el proceso, este es el playbook de marketing de siete pasos que usé para ayudar a miles de emprendedores a escalar, y lo podés aplicar empezando ahora mismo. Paso 1: conocé a tu audiencia. Entendé quiénes son, con qué luchan y qué es lo que realmente quieren. El buen marketing empieza con empatía, no con suposiciones. Paso 2: armá un mensaje claro. Hablale directamente a sus puntos de dolor. Mostrales que los entendés y que los podés ayudar. La conexión genera confianza, y la confianza impulsa las ventas. Paso 3: elegí los canales correctos. No trates de estar en todos lados. Averiguá dónde pasa el tiempo tu audiencia —Instagram, YouTube, email, donde sea— y metete de lleno ahí. Paso 4: construí una máquina de marketing. Automatizá tus seguimientos. Sistematizá tu flujo de leads. Así es como escalás sin trabajar 18 horas por día. Paso 5: seguí los datos. Fijate qué está funcionando realmente: tasas de conversión, tráfico, aperturas de email. Dejá que los números guíen tu próximo movimiento. Paso 6: creá contenido perenne (evergreen). Construí contenido que siga funcionando después de publicarlo. Pensá en videos tipo tutorial, lead magnets, secuencias de email automatizadas. Paso 7: cultivá la lealtad. La plata de verdad está en los clientes que vuelven. Seguí entregando valor y tu gente se va a quedar con vos. Ahora bien, si suena como mucho para manejar, es porque lo es, a menos que tengas un sistema que lo junte todo. Y por eso uso HighLevel. Tiene funnels automatizados, programación de contenido, seguimiento de datos en tiempo real, un CRM, herramientas de seguimiento y retención, y todo está disponible en un solo panel simple, en lugar de tratar de pegar con cinta 15 soluciones distintas. Y ahora mismo lo podés probar completamente gratis con una prueba de 30 días, además de conseguir todas mis plantillas listas para usar y lanzar rápido. Así que tocá el link en mi bio o en algún lugar cerca de este video y conseguí tu prueba gratis hoy. Este es tu mapa de ruta hacia un negocio que escala sin quemarte. Así que construyamos algo que dure.</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Video mixto: talking head en el mismo estudio oscuro (remera negra, dardos y estantería de fondo) con subtítulos amarillos en negrita; tarjetas de transición de fondo amarillo con formas onduladas animadas que anuncian cada paso numerado ('#5 TRACK THE DATA'); y una sección con capturas de pantalla desenfocadas de un dashboard de software (CRM, mensajes, secuencias de email) con la palabra 'TRACKING' superpuesta en amarillo, mostrando el producto HighLevel que se promociona. Se alternan tomas habladas con estas tarjetas gráficas de paso.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con promesa de resultado deseado y objeción resuelta desde el arranque ('crecer sin quemarte'), dirigido a un dolor común de emprendedores. Estructura de lista numerada clásica (7 pasos) fácil de seguir y recordar, con autoridad implícita ('usé esto para ayudar a miles de emprendedores'). Cierra con oferta comercial concreta (prueba gratis + plantillas) como llamado a la acción. El gatillo es el formato de lista/framework accionable combinado con la promesa de simplicidad.</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: el guion en lista numerada y las tarjetas de paso son fáciles de recrear con plantillas de CapCut/Canva; solo la parte final de captura de software específico requiere tener esa herramienta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="88" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>568</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7659073959643598096</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Explica una 'jerarquía del marketing' de cuatro niveles —trucos/hacks, tácticas, estrategia y psicología— y argumenta que la mayoría de los negocios fracasan porque se quedan estancados en los niveles más bajos en lugar de alinear su mensaje con la psicología real de la decisión de compra.</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Cuando los dueños de negocios me dicen que probaron de todo —publicar contenido, armar funnels, correr anuncios— pero que igual no consiguen tracción, generalmente encuentro el mismo problema: no están haciendo las cosas mal, están haciendo las cosas correctas en el orden equivocado. El marketing no es una sola jugada gigante, es un sistema por capas. Y si te salteás pasos o construís sobre bases débiles, todo el asunto se traba. La mejor forma que encontré de explicar esto es con la jerarquía del marketing. Tiene cuatro niveles, cada uno se construye sobre el anterior, y la mayoría de la gente se queda estancada en la base sin darse cuenta. En la base está el nivel 1: trucos y hacks. Ahí es donde vive la mayoría de los consejos de marketing que circulan online. Cosas como 'usá este sonido que está de moda' o 'publicá a las 9 de la mañana' o 'agregale esta línea a tu titular'. Claro que algo de eso funciona, pero es impredecible. Podés ver un pico de interacción y después desaparece por completo. Esto pasa porque estos trucos no están hechos para escalar, son solo ruido a menos que los ancles a algo más profundo. Después está el nivel 2: tácticas —funnels, lead magnets, campañas de anuncios, calendarios de contenido—, todas herramientas sólidas, pero el problema acá es la fragmentación. Tenés una buena secuencia de emails, pero tu landing page no está alineada con eso. Conseguís vistas en Instagram, pero nadie hace clic para pasar al siguiente paso. Cada parte individualmente puede ser fuerte, pero no están alineadas entre sí. Ahí es donde entra el nivel 3: estrategia. Acá es donde las piezas empiezan a trabajar juntas. Tu contenido lleva a tu oferta, tus emails refuerzan tu mensaje, tus anuncios traen gente que ya está lista para comprar. En este nivel ya no estás adivinando, estás guiando. Tenés estructura, tenés cierto impulso. Pero ni siquiera la estrategia te va a llevar lejos sin la capa de arriba, el nivel 4: psicología. Acá es donde todo cambia. Ya no estás solo organizando tu marketing, lo estás alineando con cómo la gente realmente toma decisiones de compra. En lugar de solo escribir titulares, estás conectando con lo que alguien necesita sentir antes de decir que sí. En lugar de simplemente tirar ofertas, las estás enmarcando de una manera que se siente segura, clara y fácil de elegir. No estás sumando presión, estás reduciendo resistencia. Y una vez que tu mensaje conecta en ese nivel, la gente se mueve más rápido, necesita menos convencimiento, porque ya cree que esta es la decisión correcta para ellos. Esto es lo que a la mayoría se le escapa. Piensan que la solución es un mejor anuncio o un mejor funnel, cuando en realidad están operando demasiado abajo en la jerarquía. La estrategia puede ser fuerte, las tácticas pueden estar bien puestas, pero si no estás anclado en la psicología de cómo la gente elige y actúa, nunca va a terminar de encastrar. Y terminás haciendo mucho más trabajo del necesario y consiguiendo menos a cambio. Por eso enseño esta jerarquía: te da un mapa, porque una vez que sabés dónde estás estancado, lo podés arreglar. Dejá de perseguir ideas al azar y empezá a construir algo que realmente mueva la aguja. Y cuanto más subís en la jerarquía, más fácil empieza a sentirse todo. Los leads llegan ya confiando en vos, las ventas suceden con menos resistencia, y tu mensaje se convierte en el que la gente recuerda. El marketing solo se siente difícil cuando estás estancado en la base. Llegá a la cima, y el sistema empieza a trabajar a tu favor, no en tu contra.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Video 100% animado, sin talking head visible: motion graphics con fondo degradado amarillo/negro y tipografía en negrita blanca/amarilla apareciendo en sincronía con la narración en off ('MARKETING GIANT' con ícono de megáfono, 'STRONG' con cuatro íconos de engranaje en círculos blancos, un grupo de siluetas vectoriales con traje formando una fila con el texto 'BETTER AD'). Estética de kinetic typography con paleta consistente amarillo/negro/dorado, íconos planos y siluetas ilustradas.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de diagnóstico común y relatable ('probé de todo y no funciona') que valida la frustración de la audiencia, seguido de una reformulación contraintuitiva ('no es que hagas las cosas mal, las hacés en el orden equivocado'). Estructura de framework jerárquico de 4 niveles con nombres claros, fácil de visualizar y recordar, que posiciona al creador como quien tiene 'el mapa' que otros no tienen. El gatillo es el marco conceptual claro combinado con la promesa de una causa raíz oculta del fracaso.</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>no + nota: es un video totalmente animado con ilustración vectorial e íconos personalizados, requiere herramientas y habilidades de motion design (o plantillas premium); no alcanza con grabarse hablando a cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="88" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>558</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7665797241055268104</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Video corto que explica el 'efecto del gradiente de la meta' (goal gradient effect): la tendencia humana a esforzarse más cuando se percibe estar cerca de completar un objetivo, usando el ejemplo de las barras de progreso y XP en los videojuegos, con la idea implícita de aplicarlo al marketing.</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Todo se trata de percepción. ¿Alguna vez jugaste un videojuego en el que te esforzás más cuando estás cerca de subir de nivel? Ya saben, cuando estás como en el 90% de la experiencia (XP), de repente no podés dejar de jugar. Eso es el 'efecto del gradiente de la meta' (goal gradient effect) en acción. Nosotros, como humanos, naturalmente aceleramos cuando podemos ver qué tan cerca estamos del próximo nivel. Los diseñadores de videojuegos saben esto desde hace décadas, y por eso te muestran barras de progreso, contadores de XP y porcentajes de logros.</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Combina talking head (mismo presentador, remera negra, fondo azulado con planta) con una captura/mockup de interfaz de videojuego oscura mostrando una barra de progreso 'LEVEL 9' al 9%, y una pantalla de texto negra con la frase 'Video game designers have known this for decades' en letra fina blanca/gris, más subtítulos quemados abajo con palabra clave resaltada en verde. Video muy corto (21 segundos) con una sola idea desarrollada a ritmo rápido.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Gancho conceptual ('todo se trata de percepción') combinado con una pregunta identificable para cualquiera que haya jugado videojuegos, lo que genera reconocimiento inmediato. Formato ultra corto con una sola idea clara, apoyada en un ejemplo visual (mockup de barra de progreso) fácil de entender de un vistazo. El gatillo es la curiosidad por el nombre técnico del fenómeno sumado a la familiaridad con videojuegos.</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: el mockup de interfaz de videojuego se puede simplificar o directamente omitir sin perder el mensaje central; lo esencial es la idea y el hablar a cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="88" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>535</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7654947618283408641</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Video corto de advertencia sobre cómo el cambio de Google hacia respuestas generadas por IA (en vez de resultados de búsqueda tradicionales) está dejando invisibles a los pequeños negocios que no aparecen en esas respuestas, y por qué la credibilidad ante el algoritmo importa más que solo tener buen contenido.</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Google acaba de hacer un cambio enorme, y ya está dejando atrás a miles de pequeños negocios. Y lo más loco es que la mayoría de los dueños de negocios ni siquiera se dieron cuenta. Esto es lo que cambió: la forma en que la gente descubre negocios online volvió a cambiar. La gente ya no está scrolleando los resultados de búsqueda. Ahora le pregunta directamente a la IA y consigue las respuestas al instante. Y si tu marca y tu negocio no aparecen en esas respuestas, bueno, es como si no existieran. Y ese cambio hizo que muchas de las tácticas de marketing habituales sean mucho menos efectivas. Por ejemplo, tener buen contenido por sí solo ya no alcanza. Y la visibilidad ahora depende de si el algoritmo ve a tu negocio como creíble o no.</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en el estudio habitual (fondo oscuro, guitarra roja, planta, remera negra) con subtítulos en negrita blanca/verde. Incluye una captura/mockup de una interfaz tipo chat de IA (similar a ChatGPT) mostrando el mensaje '¿Por dónde deberíamos empezar?' con un botón 'Best' resaltado, ilustrando el comportamiento de búsqueda que describe.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de alarma/urgencia con autoridad de marca reconocible ('Google acaba de hacer un cambio enorme') combinado con la afirmación de que 'nadie se dio cuenta todavía', lo que genera sensación de información privilegiada. Estructura breve de problema-consecuencia sin resolución completa, que genera intriga para buscar más contenido del autor. El gatillo es la urgencia/miedo a quedar obsoleto sumado a la novedad del tema (IA generativa reemplazando la búsqueda tradicional).</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: alcanza con hablar a cámara y agregar una captura de pantalla simple de un chat de IA como apoyo visual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="88" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>535</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7651250032909339905</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Consejo de copywriting: reemplazar mensajes genéricos ('ayudo a emprendedores a crecer') por descripciones específicas y creíbles con dolor, cambio y resultado concretos, ilustrado con un ejemplo de antes/después y tres preguntas guía para escribir mensajes más creíbles.</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>La mayoría del marketing suena pulido, pero no se siente personal. Y eso es un problema, porque si la gente no puede sentir tu mensaje, no va a confiar en él. Así que acá te muestro cómo arreglarlo: hacelo específico. En lugar de decir 'ayudo a emprendedores a hacer crecer su negocio con estrategias probadas', probá esto: 'trabajo con coaches que publican todos los días y aun así no consiguen leads; les ajustamos la mensajería y agendan sus primeras tres llamadas de venta en 7 días'. Eso es una imagen que la gente realmente puede visualizar. Y cuando la ven, empiezan a creer que también podría funcionar para ellos. Así que acá va tu regla: genérico es igual a olvidable, específico es igual a creíble. La próxima vez que escribas o grabes algo, preguntate: ¿en qué dolor exacto están? ¿qué cambio exacto hicimos? ¿qué resultado exacto surgió de eso? Sacá la paja y hacé que se sienta real. Porque cuando se siente real, la gente confía. Y la confianza es lo que impulsa la acción.</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en el estudio oscuro habitual (guitarra, planta, remera negra) con subtítulos en negrita blanca. Incluye un mockup de una ventana de redacción de email ('New Message') con el texto de ejemplo específico escrito ('I work with coaches who post every day and still get no leads...') y la frase clave 'AND BOOK' resaltada en amarillo con efecto de brillo, mostrando visualmente el mensaje específico que recomienda usar.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de contraste simple y accionable ('suena pulido pero no se siente personal') que apunta a un problema que casi todo emprendedor de contenido tiene. Estructura de antes/después con ejemplo concreto de copy (genérico vs. específico) copiable literalmente, y cierra con una regla memorable ('genérico es olvidable, específico es creíble') más tres preguntas guía aplicables de inmediato. El gatillo es la utilidad práctica inmediata sumada a un mini-framework fácil de recordar.</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: solo requiere hablar a cámara y mostrar el texto de ejemplo en pantalla, algo armable en cualquier editor de video gratuito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="88" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>533</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7649078484211371272</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Explica por qué los funnels de marketing simples funcionan mejor que los complicados (menos fricción, más fáciles de optimizar, escalan mejor), describe las tres etapas básicas de un funnel (conciencia, consideración, conversión) y termina promocionando el software HighLevel con prueba gratuita.</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Hablemos de funnels de marketing y de por qué el tuyo puede estar demasiado complicado. Un funnel es simplemente el recorrido que hace tu cliente desde 'nunca escuché hablar de vos' hasta 'no puedo esperar para comprarte'. Pero acá está el secreto: cuanto más simple sea tu funnel, mejor rinde. Y esto es por qué. Uno: menos fricción. Cuantos más pasos, más abandono. Los funnels simples hacen que sea fácil para la gente tomar acción rápido. Dos: es más fácil de optimizar. Con menos partes móviles, podés ver exactamente qué está funcionando y qué no. Después podés hacer ajustes inteligentes y mejorar el rendimiento en tiempo real. Tres: escala mejor. Cuando tu funnel es liviano, es fácil replicarlo, automatizarlo y crecer sin dolores de cabeza técnicos. La pregunta entonces es: ¿cómo es en realidad un funnel simple? Bueno, empieza con conciencia (awareness): la gente te descubre por redes sociales, blogs o anuncios; tu trabajo es mostrarles por qué debería importarles. Después, consideración: los vas calentando con valor —emails, testimonios, videos—; ahí estás construyendo confianza. Después, conversión: les das un próximo paso claro —agendar una llamada, registrarse, comprar ahora—. Estoy hablando de cero confusión, solo acción. Y si te estás preguntando cómo armar todo esto en la práctica, usá HighLevel. Es la forma más fácil de crear funnels automatizados que guían a los leads desde el conocimiento hasta la conversión, que los nutren con emails, videos o SMS, y que te ayudan a monitorear el rendimiento en cada paso. Y es simple, potente y escalable. Y con tu prueba gratis de 30 días, también conseguís mis plantillas de funnel y mi checklist de optimización para ayudarte a lanzar rápido. Así que si estás listo para dejar de pensar de más y empezar a convertir, tocá el link en mi bio o en algún lugar cerca de este video y conseguí tu prueba gratis hoy. Y construyamos un funnel que funcione incluso cuando vos no estás.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Video 100% animado, sin talking head en los frames revisados: motion graphics con la estética consistente amarillo/negro de la cuenta (siluetas vectoriales de figuras con traje, texto en negrita apareciendo en sincronía con la narración: 'NEVER HEARD OF YOU BEFORE' con silueta haciendo pulgar arriba, 'WHAT DOES A SIMPLE FUN[NEL]' con silueta encogiéndose de hombros, íconos de sobre de email y botón de play con la palabra 'EMAILS'). Narración en off sobre las animaciones.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de corrección de creencia común dirigido directo al dolor del espectador ('tu funnel puede estar demasiado complicado'), apela a quienes sienten que su marketing es complejo y no funciona. Estructura de lista de razones (3 motivos) + framework de 3 etapas (conciencia-consideración-conversión), fácil de aplicar y recordar. Cierra con oferta comercial concreta. El gatillo es la promesa de simplicidad frente a la sobrecarga que sienten los emprendedores con su propio marketing.</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>no + nota: la animación vectorial con siluetas e íconos personalizados requiere herramientas de motion design; no es solo grabarse hablando a cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="88" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>517</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7652762918974393617</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Presenta un framework de tres tipos de historias para el contenido —historia de origen, historia de un cliente exitoso e historia de visión— que en conjunto generan confianza, prueba y autoridad, para atraer clientes sin sonar 'vendedor'.</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>¿Querés generar confianza rápido sin sonar a que estás vendiendo? Bueno, usá este sistema de tres historias en todo tu contenido. Se llama 'la rueda del storytelling' (storytelling flywheel), y así es como se usa. Parte 1: tu historia de origen. Este es el 'por qué'. ¿Por qué hacés lo que hacés? Acá no trates de impresionar a nadie, solo sé real. Por ejemplo: yo construí mi primer sistema por frustración. Los leads se me escapaban entre las grietas y yo estaba quemado. No empecé esto porque ya lo tenía todo resuelto, empecé porque tenía que hacerlo. Hagas lo que hagas acá, mantenelo simple, porque esto es lo que construye conexión. Parte 2: una historia de victoria de un cliente. Elegí una situación real. ¿Qué problema tenía? ¿Qué cambió? ¿Y cuál fue el resultado? Por ejemplo: mi clienta publicaba todos los días y no conseguía leads. Le cambiamos los copies y el CTA, y esa semana agendó tres llamadas. La clave acá es enfocarse en resultados chicos y creíbles. No querés exagerar, solo mostrar lo que es posible. Parte 3: tu historia de visión. Esta muestra tu dirección. ¿Hacia dónde estás llevando a tus clientes? ¿Qué creés vos que es la mejor manera de hacer las cosas? Por ejemplo: yo creo que los dueños de negocios no deberían tener que trabajar a mil por hora las 24 horas los 7 días. El futuro es la automatización, los sistemas simples y un marketing más inteligente. Eso, amigo mío, es liderazgo, y eso es lo que genera compra. La clave acá, eso sí, es ir rotando estas historias en todo tu contenido. El origen construye confianza, las historias de clientes construyen prueba, y la visión construye autoridad. Así es como te convertís en alguien con quien la gente quiere trabajar.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Video 100% animado sin talking head visible en los frames: motion graphics con la misma estética amarilla de la cuenta —un rombo/diamante con la palabra 'CALLED', una tarjeta de transición con fondo ondulado anunciando 'PART 2: A CLIENT WIN STORY. PICK A REAL SITUATION.', y una silueta vectorial levantando una barra/mancuerna sobre un fondo de skyline urbano con el texto 'I BELIEVE'—. Tipografía en negrita blanca/dorada sincronizada con la narración en off.</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con pregunta directa a un deseo común ('generar confianza rápido sin sonar vendedor'), seguido de un framework con nombre propio memorable ('storytelling flywheel') dividido en 3 partes claras y numeradas, cada una con un ejemplo concreto aplicado a su propio negocio (autenticidad/caso real). El gatillo es la estructura de framework fácil de replicar sumada a los mini-casos reales que sirven de prueba.</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>no + nota: requiere animación vectorial y motion graphics personalizados; el guion en sí (las 3 historias) sería replicable hablando directo a cámara si no se dispone de esas herramientas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="88" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>505</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7642012743393971457</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Explica cómo generar 'reactancia psicológica real' haciendo que los potenciales clientes sientan que deben calificar/ser aprobados para trabajar con la marca, lo que invierte la dinámica de venta: en vez de perseguir clientes, estos empiezan a perseguir al vendedor.</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Hay un disparador psicológico que da vuelta completamente el juego de las ventas: en lugar de perseguir clientes, son ellos los que empiezan a perseguirte a vos. Cuando empecé a usar este disparador, los prospectos empezaron a decir cosas como '¿qué necesito hacer para trabajar con vos?'. Nada de perseguir, nada de seguimientos incómodos, solo demanda entrante (inbound). La reactancia psicológica real ocurre cuando hacés que la gente sienta que necesita calificar para poder trabajar con vos. Estás creando una selectividad real alrededor de con quién elegís trabajar. Y en el momento en que alguien siente que tal vez no califica, que tal vez no es lo suficientemente bueno para vos, bueno, su cerebro entra en modo acelerado tratando de probar que sí lo es. Cuando alguien percibe que está siendo evaluado o juzgado, automáticamente pasa de pensar '¿quiero esto?' a pensar '¿soy lo suficientemente bueno para esto?'. Y ese simple cambio, bueno, cambia todo, porque ahora son ellos los que están tratando de convencerte a vos, en lugar de que seas vos el que trata de convencerlos a ellos.</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en un estudio con fondo azulado y plantas (set distinto al de la guitarra roja), remera negra, subtítulos en negrita blanca con palabras clave en verde. Incluye una tarjeta de texto sobre fondo con grilla gris que cita una frase clave del guion ('Real psychological reactance happens when people feel like they [need to qualify]...' con una palabra resaltada en celeste), y un encuadre con la imagen del presentador duplicada (versión desenfocada de fondo detrás de un recuadro nítido), recurso visual similar al de otros videos de la cuenta.</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Gancho de promesa fuerte y contraintuitiva ('un disparador que da vuelta completamente el juego de las ventas... en vez de perseguir, te persiguen a vos'), apunta directo al dolor de tener que perseguir clientes. Estructura de causa (creás selectividad) → efecto psicológico (el cerebro entra en modo prueba) → resultado (inversión de roles en la conversación de venta). El gatillo combina autoridad/experiencia personal declarada y la promesa de una técnica que resuelve un problema doloroso y común.</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>sí + nota: es un video hablado a cámara con tarjetas de texto simples, reproducible con cualquier celular y una app de edición básica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="88" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>491</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7655690340350856466</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Un coach de marketing y ventas explica, a cámara, por qué justificar o defender el precio frente a un cliente es un error, y qué es lo que en realidad evalúan los clientes que pagan bien.</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>El momento en que defendés tu precio, admitís que necesita ser defendido. Y los clientes que realmente querés, los que pagan bien, respetan el trabajo y te dejan hacer lo que sabés hacer, esas personas no están esperando tu explicación. Ya saben lo que cuesta lo bueno, ya pagaron por algo premium antes. Lo que en realidad están observando es si titubeás, si te apurás a llenar el silencio, si empezás a retractarte apenas el aire se pone tenso, porque eso les dice todo lo que necesitan saber sobre si vos realmente creés en el número que acabás de decir.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en plano medio, cámara fija, hombre parado en interior con luz tenue y una planta de fondo (oficina o estudio casero), remera negra lisa. Subtítulos quemados en pantalla en mayúsculas blancas con palabras clave resaltadas en verde neón, animados palabra por palabra (estilo karaoke) sincronizados con el habla. Cartel de título fijo arriba de la pantalla ("STOP DEFENDING YOUR PRICE"). Toma continua, sin cortes de escena visibles. Formato vertical.</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Gancho inmediato con una afirmación contraintuitiva en el cartel fijo ("dejá de defender tu precio") que contradice la intuición común. Estructura de una sola idea desarrollada con tono de autoridad personal y que cierra con una revelación psicológica concreta (qué delata la inseguridad del vendedor). Gatillos: autoridad + contraintuición/polémica + tensión psicológica relatable para cualquiera que venda un servicio.</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo requiere cámara de celular, buena luz y una app de subtítulos automáticos; el valor está en el guion, no en la producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="88" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Adam Erhart</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialadamerhart/video/7641246328894278933</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>El mismo creador explica un 'gatillo psicológico' (la reactancia psicológica) que, según él, hace que los prospectos empiecen a perseguir al vendedor en vez de al revés, generando demanda entrante.</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Hay un gatillo psicológico que da vuelta por completo el juego de las ventas. En lugar de perseguir clientes, son ellos los que empiezan a perseguirte a vos. Cuando empecé a usar este gatillo, los prospectos empezaron a decir cosas como '¿qué necesito hacer para trabajar con vos?'. Nada de perseguir, nada de seguimientos incómodos, solo demanda entrante. La reactancia psicológica real ocurre cuando hacés sentir a la gente que necesita calificar para trabajar con vos. Estás creando una selectividad real sobre con quién elegís trabajar. Y en el momento en que alguien siente que tal vez no califica, que tal vez no es lo suficientemente bueno para vos, bueno, su cerebro se pone a mil tratando de demostrar que sí lo es. Cuando alguien percibe que está siendo evaluado o juzgado, automáticamente pasa de pensar '¿quiero esto?' a pensar '¿soy lo suficientemente bueno para esto?'. Y ese simple cambio, bueno, lo cambia todo, porque ahora son ellos los que están tratando de convencerte a vos, en lugar de vos tratando de convencerlos a ellos.</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato y escenario que la fila 091 (posible misma sesión de grabación): talking head en plano medio, hombre parado frente a una mesa de madera, luz azulada de fondo con planta, remera negra. Subtítulos blanco/amarillo/verde palabra por palabra tipo karaoke. Incluye un corte breve a una placa de texto cinético sobre fondo de grilla oscura que reemplaza momentáneamente el rostro para reforzar una frase clave. Formato vertical.</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Gancho con promesa concreta y exclusiva ('hay UN gatillo psicológico') que genera curiosidad inmediata. Estructura: promesa, resultado personal como prueba de autoridad ('cuando empecé a usarlo, los prospectos me decían...'), mecanismo psicológico explicado con un término técnico que da credibilidad ('reactancia psicológica'), y cierre con el cambio que resuelve el dolor del espectador (dejar de perseguir clientes). Gatillos: curiosidad + autoridad + mecanismo con nombre técnico.</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo requiere cámara y buena locución; el recurso de texto cinético se arma gratis con apps de edición como CapCut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="88" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Barry Hott</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EE.UU.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@barryhott/video/7650150683672317215</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Un consultor de ads reacciona con sarcasmo a la tendencia de creadores afiliados de TikTok Shop que repiten el mismo guion ('no compres esto salvo que esté en oferta') para promocionar decenas de productos distintos, y remata explicando por qué esa práctica perjudica a las marcas.</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>No compres los sticks de hidratación Fire Salt a menos que los vayas a comprar cuando estén en oferta, tocá el carrito y fijate si... No compres el Joy Spring, son sus sticks de humor con azafrán, a menos que los vayas a comprar cuando estén en oferta. No compres el Salt Air [?]. No compres los suplementos Snap. No compres el Happy, tocá el carrito para ver si... no compres las cosas de Marina [?]. No compres, no compres, no compres, no compres el, no, no compres el, no compres el, no compres el. No compres el hierro fundido. No compres el químico [?]. Vamos a estar tan... bueno, voy a estar, finalmente van a, bueno, voy a, bueno, no compres esto, no compres el desodorante de dos unidades. Así que finalmente pusieron, finalmente pusieron el limpiador pulidor Donkey Pro. Solo no vayas a ver tantas cadenas [?] en eso. No compres los desodorantes. No compres el Salt Purpose [?]. Así que finalmente pusieron el limpiador pulidor Donkey Pro. Creo que voy a tener que devolver... no compres el excelente [?]. No compres esta magia, vos solo querés... no compres el variety pack Built Puff a menos que agarres el limpiador de Mississippi. No puede llegar a menos que consigas el descuento secreto, tocá el carrito y necesitás ir finalmente por el doble descuento. Este es el aire [?], no compres el kit de lavado de autos Chemical Guys a menos que lo consigas con el doble descuento que salió hoy, tocá el carrito y conseguí una oferta relámpago. Bueno, o sea... esto no es bueno para tu marca.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Formato reacción/duet con grabación de pantalla: se ve el feed de TikTok (reloj del sistema, barra de búsqueda, tarjetas de producto visibles, como captura real) con distintas creadoras mostrando productos y repitiendo el mismo guion 'no compres X a menos que esté en oferta'; la cámara de reacción del autor aparece como recuadro pequeño en la esquina (primer plano de su cara con gorra con logo 'Make ugly ads'). Un frame muestra al autor con otra persona afuera en la calle (clip adicional insertado). Barras negras alrededor simulando grabación de pantalla de celular. Sin subtítulos propios agregados aparte de los que ya traen los clips originales.</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Gancho por indignación/sarcasmo desde el título ('ah, sí, buenísimo, pagále a afiliados para que le digan a tus clientes que solo compren cuando mi producto está descontado, genial'). Estructura de acumulación: mostrar muchísimos ejemplos reales seguidos del mismo guion dañino para que el espectador 'sienta' el problema por repetición, y cerrar con la conclusión de autoridad en marketing. Gatillos: polémica/indignación + humor sarcástico + evidencia acumulada dentro de la industria del marketing.</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>sí + solo necesita grabar pantalla de ejemplos reales y sumar una cámara de reacción, prácticamente sin producción.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId90"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/top_100_reels_meta_ads_guiones.xlsx
+++ b/top_100_reels_meta_ads_guiones.xlsx
@@ -76,7 +76,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,22 +101,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -161,10 +161,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -673,27 +673,27 @@
     </row>
     <row r="2" ht="88" customHeight="1">
       <c r="A2" s="2" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Mitch Barham (Beardpreneur)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -708,48 +708,48 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>5708</v>
+        <v>231400</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beardpreneur/video/7628243140423470349</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7618214625120767262</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Fragmento breve, con pinta de recorte de un podcast o transmision en vivo, donde Mitch da su opinion sobre la frecuencia publicitaria: dice que casi no le importa y que todo se reduce a los resultados; si un ad set 'evergreen' se agota, prefiere duplicarlo y refrescar la audiencia antes que matar la creatividad.</t>
+          <t>Chase Chappell presenta cómo conectar la herramienta de IA Manus a Meta Ads Manager para detectar la fatiga de creatividades en tiempo real y automatizar el contacto con creadores de UGC vía Instagram, armando lo que llama un 'motor de adquisición autooptimizante'.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>La frecuencia. Me importa y no me importa la frecuencia. Aun asi, o sea, volvemos a lo mismo. Es como, me importa pero no me importa. Es como una de las ultimas cosas que voy a mirar. La verdad es que todo se reduce a los resultados. Tipo, che, esto se esta cayendo. No esta funcionando. Estos anuncios la estaban rompiendo. ¿Okay? Dependiendo de la industria, del nicho, lo que hay que hacer es duplicar y refrescar la audiencia. Literalmente hice eso con un conjunto de anuncios de un fotografo de bodas el otro dia, donde era como, esto siempre funciona. Son evergreen, siempre funcionan. Entonces tipo, bueno, duplica el conjunto de anuncios y reinicialo, y veamos que pasa. Y por lo general vuelve a agarrar ritmo justo donde habia quedado.</t>
+          <t>Meta acaba de cambiar el marketing con IA para siempre. Acaban de adquirir Manus AI y ahora la podés sincronizar directamente con Meta Ads. Esto es automatización de IA a nivel de toma de decisiones. Acá está exactamente cómo funciona. Primero, conectás Manus AI a Meta Ads Manager, permitiéndole ver los datos de tu cuenta publicitaria en tiempo real. Segundo, le podés preguntar qué creatividades se están fatigando y te dice exactamente cuándo está cayendo la atención, cuándo la frecuencia se está disparando, y justo antes de que el rendimiento de tu cuenta esté por caer. Así sabés exactamente cuándo renovar tu contenido publicitario. Pero acá es donde se pone una locura. Podés configurar el agente de IA para que automatice por vos el contacto con creadores. Imaginate un bot potenciado por Meta contactando creadores de UGC por vos en Instagram, haciéndoles la propuesta, haciendo seguimiento, registrando las respuestas, organizando las entregas, y alimentando automáticamente esas creatividades nuevas de vuelta a tu cuenta publicitaria justo en el momento exacto en que más importa. Eso significa que tu pipeline creativo nunca se va a secar. Y se acabó el adivinar cuándo cambiar los anuncios, se acabó correr desesperado por contenido nuevo, y se acabaron los cuellos de botella creativos que matan la escala. Esto no es solo una herramienta de IA para reportes. Esto es un motor de adquisición autooptimizante. IA vigilando tus anuncios, IA prediciendo la fatiga, IA consiguiendo nuevos creadores, e IA manteniendo tu cuenta fresca. Si entendés de anuncios de Meta, sabés que lo creativo es el cuello de botella. Esto va a cambiar todo. Comentá 'Manus' y te doy el desglose exacto de cómo podés aprovecharlo antes que todos los demás.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>Arranca con un pequeno recuadro de video de esquinas redondeadas sobre un fondo animado de particulas/glow (plantilla tipo 'highlight' de clip automatico), despues corta a la imagen de camara web a pantalla completa. El poster de fondo ('NOBODY CARES, WORK HARDER') aparece espejado/invertido en varios frames, senal de grabacion sin corregir el volteo de la webcam. Subtitulos palabra por palabra, sin cortes de pantalla ni graficos: es talking head puro, con pinta de recorte de un video mas largo.</t>
+          <t>Encuadre: grabación de pantalla (screen recording) en modo oscuro con la cara del creador en un recuadro (PiP) en la parte inferior, formato podcast con micrófono. Subtítulos: no hay subtítulos quemados; el texto en pantalla es la interfaz de la app. Cortes: cortes entre distintas pantallas de la herramienta (menú de conectores, chat de la IA, dashboard). Gráficos: flechas rojas de énfasis dibujadas sobre la interfaz para guiar la mirada (se confirma en pantalla el nombre real de la herramienta, 'Manus 1.6 Lite'). Locación: fondo oscuro tipo estudio, sin locación física identificable.</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>Gancho de opinion contraintuitiva sobre un tema tecnico muy discutido en el nicho (la frecuencia del anuncio); estructura breve de anecdota real y concreta (el fotografo de bodas) que aporta credibilidad; gatillo de autoridad por experiencia practica, en un clip corto (36s) facil de consumir entero.</t>
+          <t>Gancho: afirmación exagerada de 'noticia' ('Meta acaba de cambiar el marketing con IA para siempre'), con emoji en el título. Estructura: anuncio de novedad, explicación paso a paso del mecanismo, escalada de expectativa ('acá es donde se pone una locura') y reencuadre ambicioso (no es una herramienta de reportes, es un motor de adquisición). Gatillo: FOMO por ser early adopter más un CTA con palabra clave en comentarios que dispara el algoritmo por engagement.</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>sí, es literalmente una camara fija sin edicion ni graficos, el formato mas barato del lote (ideal para recortar contenido largo como un podcast).</t>
+          <t>Sí, con matices — el formato (webcam + grabación de pantalla + flechas) es de bajo presupuesto, pero depende de tener acceso a la herramienta de IA mostrada y de estar atento a la novedad justo cuando es tendencia.</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -765,27 +765,27 @@
     </row>
     <row r="3" ht="88" customHeight="1">
       <c r="A3" s="2" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+        <v>71</v>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Mitch Barham (Beardpreneur)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -800,48 +800,48 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>4859</v>
+        <v>72700</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beardpreneur/video/7652781295931624718</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7603828023187492126</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Mitch explica por que, con Advantage+ dominando la entrega de anuncios en Meta, la segmentacion manual ya casi no importa: el verdadero 'targeting' ahora lo hace la creatividad (copy, imagen, video), al punto de poder nombrar explicitamente a la audiencia en la primera linea del anuncio.</t>
+          <t>Chase Chappell cuenta el caso de la marca Haus, que usa datos de TikTok Shop para identificar al 1% de creadores top, los suma a una comunidad de contenido y produce miles de anuncios de partnership, lo que según el video la llevó de 1 a 10 millones de dólares en un mes.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>Mira, la cosa es que tu segmentacion ya no importa. La creatividad lo hace todo. Y se que eso confunde a todo el mundo porque piensan '¿que carajo?'. Y te lo voy a explicar. Mira, en los ultimos seis meses, en realidad como 7, 8 meses, el... el algoritmo de Meta, todos tus anuncios, cambio drasticamente con todo el mundo siendo empujado hacia campanas de ventas Advantage Plus. Advantage Plus leads, campanas, tus audiencias Advantage Plus. No me importa si volves a intereses manuales, igual estas dentro de Advantage Plus. Va a salirse de cualquier parametro que le des. Ni siquiera lo usa realmente como una sugerencia para tu creatividad. Tu copy de anuncio, tu imagen y tus videos son los que hacen la segmentacion. Podes llegar incluso a nombrarlos explicitamente en la primera linea. Entonces, digamos que vendes productos para mascotas. 'Hola, duenos de mascotas, ¿tenes una mascota?'. Todos esos son creativos de apertura y ganchos de apertura que el sistema lee, conoce, interpreta, y despues le sirve tu anuncio a la gente correcta. Es alucinante. Pero esto es lo que hacemos con todos nuestros clientes y la estamos rompiendo por completo.</t>
+          <t>Esta marca se está apoderando de internet con UGC. Haus construyó un sistema usando datos de TikTok Shop en los que ya confían. Identifican al 1% superior de creadores que generan más ventas. Después los pasan a una comunidad de contenido armada para escalar. Esa misma comunidad produce creatividades sin parar para los anuncios de Meta. Ahora mismo están corriendo más de 11.000 anuncios de 'paid partnership club' [?] pagados. Eso significa testeo constante, iteración constante, y ganadores nuevos todo el tiempo. Esta estrategia está funcionando ahora mismo. En 2026. Y es la misma estrategia que los hizo escalar de un millón a diez millones de dólares en un solo mes. No en un año, no en un trimestre. En un mes. Datos de UGC, escala de comunidad. Ese es el nuevo playbook. Comentá 'UGC' y te mando la estrategia completa.</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>Talking head a media distancia (se ve el torso, gesticula con las manos), con un poster de fondo con frases motivacionales en letras grandes que aparece espejado/invertido en algunos frames (senal de flip horizontal no corregido). Titular gancho en texto blanco sobre fondo negro en el primer frame ('Ads On Facebook Failing? This is The Cause and Fix'), subtitulos dinamicos con palabras clave resaltadas en rosa/magenta. Toma continua sin cortes a pantalla ni graficos.</t>
+          <t>Encuadre: múltiples capas de video superpuestas (PiP dentro de PiP): clip selfie del fundador de la marca arriba, presentador de podcast hablando a un micrófono abajo. Subtítulos: etiqueta de texto tipo 'Haus Founder' con flecha roja señalando al fundador. Cortes: alterna entre el clip del fundador, capturas de Meta Ads Library y un dashboard de analítica con gráfico de ventas. Gráficos: flechas rojas de énfasis, capturas con métricas reales ('~11,000 results', '$10.9M Total sales', '107.9K%'). Locación: interior tipo living con micrófono de podcast.</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>Gancho de afirmacion contraintuitiva y polemica ('el targeting esta muerto'); estructura de explicacion causal ('te lo voy a explicar') con ejemplo concreto y accionable (nombrar a la audiencia en la primera linea del copy); gatillo de autoridad/prueba social al cerrar con 'esto es lo que hacemos con nuestros clientes y la rompemos'.</t>
+          <t>Gancho: afirmación de caso de éxito extremo ('esta marca se está apoderando de internet'). Estructura: formato de case study (quién, qué hicieron, prueba con capturas reales, resultado numérico). Gatillo: cifra específica y extrema (de 1 a 10 millones de dólares en un mes, no en un año) reforzada con capturas de pantalla reales como prueba social, más CTA con palabra clave.</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>sí, es solo una camara fija y opinion hablada, sin edicion ni graficos, uno de los formatos mas baratos de replicar.</t>
+          <t>No — depende de tener un caso de éxito real con datos de ventas documentados y varias capas de video (PiP, capturas, dashboard) editadas juntas.</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -857,32 +857,32 @@
     </row>
     <row r="4" ht="88" customHeight="1">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -892,48 +892,48 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>3940</v>
+        <v>47400</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7635737398961245462</t>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7647588481862012174</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell comparte, sobre un grafico fijo con voz en off, un insight de sus ultimas 90 dias en cuentas de anuncios: las creatividades estaticas estan empezando a convertir mejor que el video, posiblemente por la desconfianza creciente hacia contenido generado con IA y las voces genericas de UGC.</t>
+          <t>Caleb (mr.paidsocial) presenta un sistema gratuito, corrido con Claude Code, para crear y lanzar una cuenta de anuncios de Meta completa -imagenes, video UGC, hasta claymation- usando solo la voz, sin disenador ni editor. Cierra invitando a bajar un repo de GitHub gratis con todo el sistema.</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>Y lo que les puedo decir ahora mismo es que, en todas las cuentas de anuncios en las que estuve trabajando en los ultimos 90 dias, lo estatico esta empezando a rendir mejor que el video. Creo que lo que esta pasando es que hay demasiadas marcas haciendo contenido de IA malo, y muchos consumidores estan empezando a desconfiar de si el creativo que estan viendo fue generado por IA. Entonces, en mi opinion, creo que esta empezando a haber una falta de confianza con los creadores de video. Y encima de eso, muchas marcas estan yendo directamente con esta voz generica de influencer, tipo el creador UGC estandar, que no esta convirtiendo tan bien comparado con lo estatico. Esa es la tendencia que estoy viendo. Pero de cualquier manera, tenes que tener variacion aca.</t>
+          <t>¿Y si pudieras construir y lanzar una cuenta de anuncios de Meta completa? Docenas de anuncios de imagen, videos UGC que detienen el scroll, incluso anuncios estilo claymation usando nada mas que tu voz y Claude Code. Sin disenador, sin editor de video, sin VA, y sin tocar el Administrador de anuncios. Estoy a punto de hacer todo esto en vivo en este video, y te voy a dar el sistema exacto que voy a estar usando, gratis. Voy a tomar una foto de producto y convertirla en 30 anuncios de imagen en estilos totalmente distintos sin escribir un solo prompt. Despues te voy a mostrar como clonar cualquier anuncio que hayas visto por ahi, el ganador de un competidor, un anuncio random en tu feed, y reconstruirlo con tu propio producto en segundos. Despues pasamos a video. Te voy a mostrar el flujo de trabajo creativo completo de UGC con IA y como lograr una consistencia de personaje perfecta. Despues te voy a mostrar como podes agregar B-roll, efectos de sonido lo-fi, musica de fondo, voz en off. Todo lo que posiblemente agregarias a un video y tendrias que editar y publicar, lo podes hacer dentro de Claude Code. Sin abrir CapCut, sin Canva, sin Adobe, sin Final Cut Pro. Literalmente estas hablando con Claude como si fuera tu gerente creativo. Incluso voy a tomar un TikTok al azar y mostrarte como puedo recrearlo plano por plano usando uno de mis propios productos. Ademas te voy a mostrar como hacer anuncios estilo animacion que parezcan claymation o estilo Pixar. Y finalmente, te voy a mostrar mi parte favorita de todo este sistema. Lanzar los anuncios a tu cuenta de anuncios real sin tocar el Administrador de anuncios. Claude puede extraer todos los datos de tu cuenta de anuncios y aprender exactamente que esta funcionando. Y no solo eso, sino que puede escanear todos tus anuncios de imagen y video para entender con contexto perfecto de que deberia tratarse cada anuncio, y despues escribirte el copy de anuncio perfecto especifico para cada anuncio individual. Este sistema por si solo te va a ahorrar horas todos los dias y te va a dar el desbloqueo que necesitas para lanzar mas anuncios en tu cuenta hoy mismo. Y lo mejor de todo, esto vive en un repositorio de GitHub gratuito que construi y que podes conseguir en la descripcion de abajo. Si nunca usaste Claude Code y no tenes ni idea de como usar GitHub, no importa. Literalmente lo unico que tenes que hacer es agarrar el link que te dan, tirarlo en Claude Code, y el se encarga de toda la configuracion por vos. Asi que si corres anuncios de Meta o queres correr anuncios de Meta, este video es el cheat code que estabas esperando. Y este podria ser uno de los videos mas importantes que veas en todo el ano. Vamos a entrarle.</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>Video practicamente estatico: los tres frames muestreados (1, 3 y 5) son identicos, una sola imagen/grafico fijo con dos titulares en banners rojos ('Static Meta ads seem to be doing better on average than video right now' / 'Is this because of AI?') sobre una captura de pantalla de datos comparando video, estatico y carrusel. No hay talking head visible ni cortes; la voz en off es la unica fuente de dinamismo, sin locacion identificable (imagen tipo escritorio/Mac).</t>
+          <t>Talking head en primer plano (gorra, anteojos, luz azul/verde de fondo tipo home studio) intercalado con capturas de pantalla de un editor de codigo/chat de Claude Code y ejemplos de anuncios generados. Subtitulos dinamicos con palabras clave resaltadas en blanco sobre negro ('VOICE', 'PERFECT') con icono de forma de onda de audio. Cortes frecuentes entre camara y pantalla, sin locacion mas alla del escritorio/oficina del creador.</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>Gancho de dato de tendencia contraintuitivo y accionable para el nicho (estatico rinde mejor que video); estructura breve de opinion mas hipotesis (desconfianza hacia la IA); gatillo de pregunta polemica para generar debate en comentarios ('¿es por la IA?'), todo en un clip muy corto (39s).</t>
+          <t>Gancho de pregunta hipotetica + promesa de maximo valor ('el video de mas valor que hice'); estructura de lista de capacidades demostradas una por una en vivo (imagen, video, lanzamiento); gatillo de gratuidad y urgencia/FOMO (repo gratis, 'uno de los videos mas importantes que veas este ano') mas reduccion de friccion para quien nunca uso la herramienta.</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>sí, es practicamente solo un grafico de texto fijo con voz en off, el formato mas barato posible de producir.</t>
+          <t>sí, solo necesita camara/mic y grabacion de pantalla, sin equipo de produccion caro.</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -949,32 +949,32 @@
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -988,44 +988,44 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>3692</v>
+        <v>34600</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7650235356842986775</t>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7650195193890721038</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell explica cómo usa Claude (IA de Anthropic) para analizar reportes de campañas pagas de Meta y Google, detectando por ejemplo caídas de conversión causadas por tráfico de afiliados.</t>
+          <t>En formato 'todo lo que construi', Caleb muestra una serie de automatizaciones armadas con el nuevo modelo Fable 5 de Claude: dashboards de contenido, gestion de su comunidad de Skool, republicado de posts, email marketing, anuncios de Meta y hasta un programador de horarios de guarderia del gimnasio, todo controlado desde el celular.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>Vengo usando mucho Claude para ayudarme a analizar las campañas de anuncios pagos que estoy corriendo últimamente, y se volvió extremadamente valioso, porque lo que puedo hacer es sacar muchos reportes distintos de distintos canales y después cargárselos a Claude, darle contexto y hacerle las preguntas correctas, lo cual me ayuda a dirigir las campañas y los canales en la dirección correcta. Así que acá, por ejemplo, hay capturas de pantalla de un chat que tuve con Claude para una marca que venía teniendo problemas con la tasa de conversión, que estaba bajando, y tienen afiliados que están mandando un poco más de tráfico del que deberían, y eso está impactando en las campañas de meta ads. Entonces estamos tratando de entender por qué está pasando esto, qué tenemos que sacar, y como estos chicos no están usando nada como Triple Whale [?, en el audio "Triple L"] o Hyros [?, en el audio "high rise"], en realidad no tenemos nada con modelos de atribución ni con el solapamiento (overlap). Así que lo que hago acá es entrar a GA4 y exportar un archivo CSV que muestra el rendimiento del tráfico por campaña UTM y por fuente UTM, y después cargo información sobre meta, y exporto distintas tablas de meta: a nivel de campaña, a nivel de anuncios, incluso algo de la creatividad del anuncio. Y exportamos métricas como costo por clic, click through, CPMs; saco reportes de si el CPM subió o bajó en los últimos 12 meses. Y cuando empezás a juntar toda esta información, puede ser un poco difícil armar un análisis sólido que explique qué está pasando o qué no está pasando. Y ahí es donde entra Claude, porque podés cargarle todo esto. Y una vez que ya armó ese contexto, podés empezar a hacerle preguntas para tratar de entender qué está pasando. Y como pueden ver, Claude es realmente bueno para visualizar estos datos a lo largo del tiempo. Entonces acá podemos ver, por ejemplo, cómo se ve la convergencia [?, posiblemente "conversión"] a lo largo del tiempo con Google para esta campaña específica que estamos corriendo. Lo podemos comparar con Facebook y podemos hacer un montón de otras cosas más. Y esa es la belleza de usar IA en media buying. Yo no hago que la IA corra ninguna de las campañas ni las configure, pero la estoy usando ahora para analizar toda esta información. Y está llegando a un punto en el que, al final de cada semana, voy a empezar a cargarle reportes específicos a Claude, que después me va a dar un resumen de qué está pasando.</t>
+          <t>Esto es todo lo que construi en las ultimas 24 horas usando el nuevo modelo Fable 5 de Claude. Primero le hice construir este dashboard de contenido. Muestra mi cantidad total de seguidores en todos los canales sociales, la cantidad total de vistas. Aca tengo todos mis distintos canales con sus estadisticas. Un dashboard en vivo de mi contenido en cada canal de las ultimas 48 horas. O graficos increibles que muestran el volumen de publicaciones, la tendencia promedio en tres meses, la tasa de acierto de seguidores por publicacion, que es cuantos de mis videos se vuelven virales, contenido que funciono bien que no republique en otros canales. Toda una base de datos de biblioteca de contenido que muestra las vistas en cada canal donde publico mi contenido, y una vista de todos los acuerdos de marca que hice. Ah si, construi eso desde mi celular. Lo siguiente que tuve que hacer fue auditar mi comunidad de Skool y darme sugerencias sobre como hacer que la seccion de cursos fluya mejor. Asi que en realidad me construyo cursos nuevos, donde descargo todo mi contenido de Skool y volvio a subir todo por mi. Y ahora mismo esta literalmente tomando control de mi navegador en mi Mac Mini y subiendo miniaturas personalizadas a los nuevos cursos que creo para mi. Tambien puede hacer cosas como mandar DMs a la gente que esta por cancelar, crear eventos automaticamente en el calendario del grupo, y publicar automaticamente cosas como grabaciones grupales de Skool y oradores invitados en la seccion de cursos por mi. Todo esto es trabajo que normalmente tendria que pagarle a una VA para hacer, o que me llevaria horas cada semana. Ahora mismo lo tengo trabajando en un nuevo sistema de email para mi, asi que le hice investigar cada proveedor de email que existe y averiguar cuales tenian las mejores integraciones de API. Y va a encargarse de cambiar toda mi infraestructura de email de un proveedor a otro. Tengo a Fable 5 conectado a todos mis canales sociales para que pueda republicar contenido por mi. Asi que aca dije: publique un video en mi Instagram y quiero que lo republiques en TikTok y YouTube Shorts, y lo hizo. Tambien queria que escribiera un texto mas largo para LinkedIn y lo hizo por mi. Esta proxima es una locura. Le hice construir un programador automatico de cuidado infantil para el gimnasio al que voy. El gimnasio al que voy solo tiene como dos lugares de guarderia cada manana, y si no te despertas a las 6 am, simplemente no los conseguis. Asi que Fable 5 puede controlar mi navegador Chrome a las 6 de la manana y seleccionar automaticamente mis horarios preferidos para dejar a mi hijo en el gimnasio. Le hice rastrear todas mis finanzas y conciliar toda mi contabilidad entre lo personal y lo de mi negocio. Lo tengo publicando y creando anuncios para mi y mi cuenta de anuncios sin que yo tenga que entrar al Administrador de anuncios. Voy a crear anuncios tipo claymation y animaciones estilo Pixar. Tengo esta cosa integrada en practicamente cada aspecto de mi vida ahora mismo, tanto en mi negocio como en mi vida personal. Y lo tengo corriendo en esta Mac Mini, asi que literalmente puedo controlarlo desde cualquier lugar, desde mi celular. Lo que significa que si estoy manejando de vuelta a casa y quiero saber como va mi contenido, puedo simplemente hablarle por voz a Claude y me va a decir. O si tengo anuncios nuevos que necesitan publicarse, le puedo pedir que los publique por mi y lo va a hacer. ¿Cual es lo mas genial que construiste hasta ahora? Contame en los comentarios.</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>Sin talking head: fondo negro con título fijo en texto blanco ("How I'm using Claude with media buying"); debajo se muestra una captura de pantalla real de un chat/reporte sobre fondo blanco, y en un frame posterior se agrega un gráfico de líneas comparando canales. Se ve la barra de dock de macOS abajo, lo que sugiere una grabación de pantalla o edición simple tipo diapositivas con voz en off, sin subtítulos incrustados visibles en los frames capturados.</t>
+          <t>Talking head en oficina/casa con luces de colores (verde/rosa) y planta de fondo, banner de texto rojo fijo en la parte superior con el titulo 'EVERYTHING IVE BUILT USING FABLE 5', subtitulos dinamicos abajo. Intercalado con grabacion de escritorio/mano senalando un monitor con un dashboard real (seguidores de Facebook, YouTube, X). Cortes entre webcam y pantalla, estilo demo casera.</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Gancho de autoridad práctica ("cómo uso Claude para analizar campañas") sobre un dolor común del rubro (atribución confusa, afiliados inflando resultados), reforzado con prueba real (capturas de un chat/reporte real) en estructura de caso de uso paso a paso.</t>
+          <t>Gancho de curiosidad ('todo lo que construi en 24 horas'); estructura de catalogo de casos de uso variados y crecientes en sorpresa (dashboards, cursos, email, guarderia, finanzas, ads); gatillo de pregunta final que invita al comentario y fantasia aspiracional de un asistente todopoderoso que maneja todo el negocio.</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: solo requiere capturas de pantalla propias, una cuenta de Claude y una grabación de pantalla o edición básica de texto, sin cámara ni locación.</t>
+          <t>sí, el formato de grabacion es barato, aunque depende de tener ya varios sistemas y negocios digitales armados para poder mostrar tantos casos de uso.</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1041,32 +1041,32 @@
     </row>
     <row r="6" ht="88" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1076,48 +1076,48 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="J6" s="6" t="n">
-        <v>2569</v>
+        <v>29000</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7624497738855583008</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7624241425068166431</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>En formato de entrevista, Ben Heath responde cual es el error mas comun de los anunciantes en Meta Ads: no dejar en paz las campanas y tocarlas constantemente, lo que impide salir de la fase de aprendizaje y lleva a decisiones basadas en ruido en vez de datos.</t>
+          <t>Chase Chappell anuncia que Meta eliminara los pagos con tarjeta de credito para cuentas de anuncios de alto gasto a partir del 1 de abril, obligando a usar debito bancario o facturacion mensual, y advierte sobre el impacto en el flujo de caja de las marcas.</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>¿Cual es el error mas grande que ves que comete la gente en las campanas de anuncios de Meta? El error mas comun que veo que comete la gente en las cuentas de anuncios de Meta va a ser que la gente no puede dejar sus cuentas de anuncios en paz. Ajustando y testeando constantemente y metiendo un anuncio aca. Cuando hacen eso, nunca salen de la fase de aprendizaje. Nunca le dan tiempo a Meta para estabilizar las campanas. Ven resultados increiblemente volatiles. Le atribuyen mal los resultados a los cambios que acaban de hacer. Y puede no tener nada que ver con eso. Podria ser que de todas formas ibas a tener un buen dia o un mal dia. Entonces no estan tomando decisiones basadas en datos. Estan mucho mejor si simplemente le dan mas tiempo a las cosas, se dan un cronograma de optimizacion y dicen 'solo voy a ajustar mis campanas una vez cada siete dias, o una vez cada 10 dias', algo asi.</t>
+          <t>¿Escuchaste sobre esta nueva actualizacion de META? META acaba de hacer un movimiento que la mayoria de los anunciantes estan pasando completamente por alto. Estan eliminando silenciosamente los pagos con tarjeta de credito, especificamente para cuentas de anuncios de alto gasto. A partir del 1 de abril, o cambias a debito bancario o facturacion mensual, o tus anuncios se detienen. Se acabaron los puntos de la tarjeta. ¿Por que? Porque META ya no quiere pagar de 2 a 3% en comisiones de tarjeta de credito. Esto es una jugada de margen por parte de Meta. Pero es mas grande que eso. Estan ajustando el control sobre el flujo de caja, la verificacion de cuentas, y quien realmente puede escalar. A los anunciantes mas chicos, por ahora no los afecta [?, en el original 'They're on touch for now', probable error de reconocimiento por 'They're untouched for now'], pero a los grandes anunciantes: ahora estan jugando con las reglas de Meta, y aca es donde se pone real. Ahora estas pagando nominas, haciendo pedidos de inventario, y pagando una factura enorme de Meta a fin de mes, todo al mismo tiempo, sin colchon, sin demora, sin margen de maniobra. Esto no es una actualizacion de facturacion. Esto es una prueba de estres de flujo de caja. Las plataformas se estan poniendo mas estrictas y el juego se esta poniendo mas dificil. Asi que la pregunta real es: ¿puede tu negocio realmente sostener el flujo de caja?</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>Toma continua a camara en interior sencillo (paredes blancas, cuadro enmarcado, planta), microfono de podcast visible sobre la mesa; subtitulos blancos que siguen el audio palabra por palabra, sin graficos adicionales; formato de pregunta y respuesta tipo entrevista/podcast.</t>
+          <t>Produccion mas elaborada: combina un clip de video/cine de stock (hombre con anteojos de sol de perfil en un auto) con el logo de Meta superpuesto como gancho visual; sigue con un infografico a medida comparando linea de tiempo 'antes' (pago con tarjeta, periodo de 60 dias) vs 'despues' (facturacion, periodo de 30 dias) con emojis y flechas; cierra con un grafico simulando un estado de cuenta/factura de Meta ('Ads on Reels $50,000') con signos de exclamacion, y Chase hablando a camara con microfono de podcast sobre fondo negro.</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta directa ('What's the biggest mistake...?') que promete un error concreto a evitar; estructura de explicacion causa-efecto (tocar demasiado, nunca sale de fase de aprendizaje, decisiones mal atribuidas) con solucion accionable al final (ajustar cada 7-10 dias); gatillo de autoridad conversacional: se siente como consejo genuino de experto en vez de anuncio.</t>
+          <t>Gancho de pregunta mas novedad ('Have you heard of this new META update?'); estructura de que-por que-que implica con evidencia visual (linea de tiempo, factura simulada) que hace tangible un cambio abstracto de facturacion; gatillo de ansiedad financiera ('cash flow stress test') relevante para cualquier negocio que dependa de Meta Ads.</t>
         </is>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>si, solo requiere una camara, un microfono y responder una pregunta con criterio propio.</t>
+          <t>no, requiere metraje de stock/cine con licencia y al menos dos piezas de diseno grafico a medida (linea de tiempo y factura simulada), mas tiempo de edicion que el resto del lote.</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
     </row>
     <row r="7" ht="88" customHeight="1">
       <c r="A7" s="2" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1168,48 +1168,48 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1971</v>
+        <v>28900</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7646443420076068118</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7612660537196907806</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell comenta una tendencia que observa en sus cuentas de Meta Ads: el contenido estático está empezando a superar en rendimiento al video y al UGC generado con IA, por la creciente desconfianza de los consumidores hacia contenido con IA y voces genéricas de influencer.</t>
+          <t>Chase Chappell presenta una herramienta que permite 'copiar' el anuncio de cualquier competidor y obtener la plantilla creativa exacta (estructura, hook, formato, CTA) para recrearlo en minutos para la propia marca.</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>Lo que les puedo decir ahora mismo es que, en todas las cuentas de anuncios en las que estuve trabajando en los últimos 90 días, lo estático (static/imagen) está empezando a rendir mejor que el video. Creo que lo que está pasando es que hay demasiadas marcas haciendo mal contenido de IA, y muchos consumidores se están volviendo escépticos sobre si la creatividad que están viendo fue generada por IA. Entonces, en mi opinión, creo que está empezando a haber una falta de confianza con la creatividad en video [corregido de "video craves", error de reconocimiento]. Y encima de eso, muchas marcas están yendo directamente con esa voz genérica de influencer, como el típico creador de UGC estándar, que no está convirtiendo tan bien comparado con lo estático. Esa es la tendencia que estoy viendo. Pero de cualquier manera, tienen que tener variación acá. Deberían probar carruseles, estático, video, y ver qué les está funcionando a ustedes, en lugar de hacer solo estático.</t>
+          <t>Esta herramienta creativa cambia las reglas del juego. Si estás corriendo anuncios pagos ahora mismo, esto es una estrategia al límite de lo injusto. Con esta herramienta, literalmente podés 'swipear' (copiar) el anuncio de cualquier competidor y conseguir la plantilla creativa exacta para recrearlo. No es inspiración. No hay que adivinar la estructura y el formato real, ya sea un anuncio de reseña con beneficios, antes y después, testimonios de UGC, o anuncios basados en problema-solución. Ves qué formato están usando, cómo está armado el hook (gancho), dónde aparece la prueba, cómo está ubicado el CTA (llamado a la acción), y después literalmente te dan un botón de 'recrear' para tu marca en minutos. Así es como las marcas top se mueven más rápido que todas las demás. No están reinventando los anuncios, están replicando lo que ya funciona hoy y desplegándolo a escala. Ayuda a bajar la fatiga creativa, a testear más rápido, y a tener más anuncios ganadores. Así que si sos una marca seria escalando en 2026, este es el tipo de ventaja (leverage) que necesitás. Comentá 'creative' y te mando la herramienta.</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>Sin talking head: tarjeta de texto roja fija ("Static is beginning to out perform video and AI UGC and every other type of creative...") sobre una captura/grabación de pantalla de escritorio Mac con tres recuadros (Video, otro tipo poco legible, Carrusel) y texto pequeño ilegible. Los tres frames capturados son prácticamente idénticos, lo que sugiere una sola imagen fija sostenida con narración en off en vez de video en movimiento.</t>
+          <t>Encuadre: grabación de pantalla de una herramienta de plantillas publicitarias con el creador en recuadro inferior hablando a micrófono. Subtítulos: texto grande tipo 'hook' superpuesto ('Have you heard of this Meta Ad Creative Tool?'), y en otro frame texto de ejemplo de copy de anuncio en franjas blancas. Cortes: cambia entre distintas pantallas de la herramienta (dashboard de inicio, ejemplo de anuncio UGC de sábanas, menú de categorías/filtros). Gráficos: parte del nombre/logo de la marca de la herramienta aparece borroneado. Locación: sin locación física, foco en pantalla con fondo de estudio.</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta/tendencia contraintuitiva en el título ("¿alguien más nota que lo estático supera al video?") que interpela directamente a colegas del rubro, en formato corto de opinión/hot take de autoridad que invita al debate en comentarios.</t>
+          <t>Gancho: pregunta retórica con etiqueta de 'game changer' y emoji, apunta a la curiosidad sobre una herramienta desconocida. Estructura: promesa fuerte ('estrategia al límite de lo injusto'), demostración en pantalla del mecanismo, beneficios (menos fatiga creativa, testeo más rápido) y apela a la exclusividad ('así se mueven las marcas top'). Gatillo: combinación de FOMO más utilidad muy concreta (botón de 'recrear') más curiosidad por el nombre de la herramienta, que aparece parcialmente oculto.</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: solo necesita una tarjeta de texto con opinión y una captura de pantalla de fondo, sin cámara ni edición avanzada.</t>
+          <t>Sí, con matices — el formato (webcam + grabación de pantalla) es económico, pero requiere acceso a la herramienta de plantillas mostrada (probablemente paga).</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1225,32 +1225,32 @@
     </row>
     <row r="8" ht="88" customHeight="1">
       <c r="A8" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Mitch Barham (Beardpreneur)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1260,48 +1260,48 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1614</v>
+        <v>13400</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7642466201179884822</t>
+          <t>https://www.tiktok.com/@beardpreneur/video/7634698833859005709</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell explica la estrategia de 'partnership ads' (whitelisting) en Meta: contactar masivamente a microcreadores (de cientos a 10,000 seguidores) para correr anuncios pagos publicados directamente desde sus cuentas, generando prueba social, awareness y contenido auténtico acumulativo.</t>
+          <t>Mitch (beardpreneur) explica en 4 puntos el nuevo conector MCP de Meta Ads que permite gestionar campanas de Facebook Ads directamente desde Claude o ChatGPT sin necesidad de programar, y ofrece mandar el link a quien comente 'meta'.</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>Esta estrategia de meta ads nos está dando un crecimiento compuesto explosivo. Básicamente se trata de usar partnerships (asociaciones) en meta, que es cuando vas y buscás un montón de creadores de contenido o influencers y publicás en partnership con esas personas. Así que agarré esta captura de Google, y pueden ver acá, por ejemplo, en este anuncio de belleza, tenés el nombre del creador de contenido y después dice "con" (with), y después la marca. Y lo que estamos haciendo ahora mismo en algunas de estas marcas es contactar masivamente a microcreadores de contenido que se parecen a los clientes. O sea, no son gente que ya tiene muchos seguidores. Normalmente tienen desde un par de cientos hasta quizás 10,000 seguidores como máximo en Instagram. Y lo que hacemos es conseguir un buen volumen de gente hablando sobre el producto o servicio. Y después corremos lo que se llaman anuncios de partnership de meta. Algunos le dicen "whitelist ads" (anuncios de whitelisting). Entonces lo que hacemos es tener una campaña ahora mismo que tiene todos estos distintos anuncios de partnership. Básicamente es una campaña, un ad set. Y podés incluso hacerlo con targeting abierto/amplio (open broad), o podés usar exclusiones. Yo prefiero usar exclusiones porque esto funciona muy bien con el top of funnel. Y normalmente tenemos entre 5 y 25 anuncios dependiendo de cuánto presupuesto tengas. Y simplemente vas empujando a todos estos distintos creadores que están hablando de tu producto, pero corriendo los anuncios con ellos. Entonces básicamente parece una marca distinta en vez de solo ser tu marca. Y donde esto empieza a compensarse/multiplicarse (compound) es que, con el tiempo, terminás teniendo un par de cientos de creadores que publicaron sobre vos. Entonces cuando la gente busca tu marca, su contenido aparece. Tenés más prueba social, tenés creatividad publicitaria. Y obviamente estás construyendo reconocimiento (awareness) a través de su audiencia, porque ellos también están publicando sobre vos. Y en mi experiencia hasta ahora, lo que mejor funcionó es enfocarse en estos microcreadores de contenido, enfocarse en gente que se parece a tus clientes. No son creadores de contenido profesionales, no son influencers. Y ese estilo de contenido auténtico que conseguís de este tipo de persona está funcionando muy bien como anuncio. De nuevo, esta estrategia simplemente implica literalmente contactar gente, ofreciéndoles algún tipo de incentivo. Tal vez hacés una tarifa fija por posteo más producto gratis, o afiliación, lo que sea. Y a cambio, querés poder correr anuncios de partnership donde podés correr anuncios a través de su página, con esta creatividad. Eso es lo que está funcionando extremadamente bien ahora mismo en un par de marcas de e-commerce con las que estoy trabajando.</t>
+          <t>Vas a querer guardar esto para despues. Meta acaba de lanzar una actualizacion enorme que te permite manejar tus anuncios de Facebook directamente desde Claude o ChatGPT. Y aca van cuatro cosas que realmente necesitas saber sobre el conector MCP de Meta Ads. 1. No necesitas ser desarrollador para instalarlo. No hace falta configuracion de API ni programar nada. Literalmente solo lo conectas a tu herramienta de IA via MCP y listo. Desconfia del consejo que te da. Probablemente sea bastante parecido a un representante normal de Facebook que te da consejos malos. Pero si va a extraer tus insights reales de rendimiento de campana, datos de catalogo. Asi que la IA puede analizar realmente que esta funcionando y, ya sabes, darte ideas. Pero yo las tomaria con pinzas. Pero ahora tambien podes editar campanas en lenguaje natural en vez de andar clickeando por todos esos menus del Administrador de anuncios. Y le podes decir a la IA que directamente actualice tu conjunto de anuncios, cree una campana nueva, lo que quieras hacer. Por ultimo, funciona a traves de 4 canales. Podes usar tu IA para extraer insights de Meta y compararlos con tus otras plataformas, todo en un solo lugar. Si queres el link para instalar esto dentro de tu IA, deja la palabra 'meta' y te mando el link del MCP para que lo instales con tu Claude o tu ChatGPT.</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>Sin talking head propio: tarjeta de texto roja con título ("New Meta Ads Strategy For Explosive Compounding Growth") sobre capturas de pantalla de dos posts reales (Instagram y Facebook) de un partnership ad de belleza ("kaiblue with lakeur_beauty"), y una segunda tarjeta de texto con instrucción concreta ("Put all of the partner ads into one campaign/shopping campaign, use exclusions"). Formato slideshow de imágenes fijas con narración en off; se ve el dock de un iPhone/iPad abajo.</t>
+          <t>Formato de pantalla dividida: mitad superior es una captura de una pagina/anuncio oficial de Meta con el titular 'Introducing Meta Ads AI Connectors' y una ilustracion de personas en oficina; mitad inferior es el creador (barba larga, anteojos) hablando a camara sosteniendo un microfono. Subtitulos palabra por palabra quemados en el video, fondo neutro tipo estudio, sin locacion identificable mas alla de un espacio de grabacion cerrado.</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>Gancho de superlativo ("una de las mejores estrategias que estoy corriendo ahora") con promesa de crecimiento compuesto/explosivo, explicando paso a paso una táctica poco conocida (whitelisting con microcreadores) respaldada con un ejemplo visual real que da sensación de información privilegiada.</t>
+          <t>Gancho de noticia/autoridad ('Meta acaba de lanzar una actualizacion enorme'); estructura numerada de 4 datos clave, facil de seguir y de guardar; gatillo de reciprocidad con CTA claro (comentar la palabra clave para recibir el link), que ademas genera comentarios masivos.</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: no requiere producción propia, solo capturas de pantalla de ejemplo y narración en off; el costo real está en el trabajo de outreach a creadores, no en el video en sí.</t>
+          <t>sí, solo requiere un microfono y la captura de una pagina web oficial, con edicion simple de subtitulos y split-screen.</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="9" ht="88" customHeight="1">
       <c r="A9" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1352,48 +1352,48 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1236</v>
+        <v>12700</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7648727626592406806</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7634971114262908190</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell comparte en pantalla los resultados reales de una campaña ASC (Advantage+ Shopping) de Meta que está funcionando bien para una marca de e-commerce, mostrando métricas de alcance, frecuencia y costo por conversión.</t>
+          <t>Chase Chappell analiza si 'The Absorption Company' (marca de suplementos vinculada a Ian Somerhalder) tiene lo necesario para convertirse en la próxima gran marca, repasando su producto, su sitio web y su estrategia de distribución.</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>Quiero darles una actualización porque estoy usando campañas ASC ahora mismo, campañas de compras Advantage+, y en realidad están funcionando muy bien. Básicamente es una campaña abierta y amplia que usa optimización de presupuesto de campaña (CBO). Y en ese conjunto de anuncios tengo alrededor de 15 creativos. Y quiero mostrarles las métricas principales de los últimos 30 días acá. Como pueden ver, tuvimos un alcance de un millón de personas, que es bastante fuerte, pero la frecuencia es de 4x. Entonces naturalmente está haciendo retargeting de gente dentro de esta campaña. Y solo para darles más contexto, tengo otras campañas corriendo, que oculté acá, pero básicamente tengo una campaña de tope de embudo corriendo con exclusiones de quienes ya interactuaron con los anuncios y también visitaron el sitio web de esta marca. Y después tengo otra campaña que hace retargeting a clientes existentes, retargeting de tráfico y retargeting de interacción. Y esta es la campaña dominante en términos de gasto publicitario. Pueden ver que tuvimos 4.300 compras acá. Estamos usando cualquier creativo que haya funcionado bien, ya sea orgánicamente o en una campaña estándar de tope de embudo. Entonces, usualmente en esta cuenta, si estuvimos testeando un conjunto de anuncios que tuvo 20 o más conversiones a un costo razonable o mejor que el promedio, entonces duplicamos ese anuncio y lo corremos dentro de esta ASC. Esta es la única marca con la que estoy probando esto por ahora. Usualmente esta marca paga alrededor de $25 por conversión. Ahora mismo está en $18, y podría bajar más optimizando el creativo. Ahora, si vieron mis otros videos, sabrán que en realidad no fui fanático de ASC por un tiempo. Dejé de usarla porque encontré mucha evidencia que sugería que ya no eran confiables. Pero en este caso, hemos estado empujando fuerte una campaña de tope de embudo que está consiguiendo mucho tráfico nuevo. Entonces no me preocupa tanto esta relación de alcance a frecuencia. Y parece estar funcionando bastante bien. De hecho la vengo corriendo desde hace bastante tiempo. Pueden ver que tuvimos 21.000 compras de por vida, una frecuencia de por vida de [?] x, un CPA de $17,65 con casi $400.000 de gasto. Entonces recomendaría probar una campaña ASC, especialmente si sos de e-commerce y tenés múltiples SKUs y múltiples creativos. Probablemente solo haría esto cuando ya tengas una estructura de tope de embudo y fondo de embudo, y después agregues esto encima. Tenés que estar atento a esta frecuencia. Tenés que cuidarte del solapamiento de subastas (auction overlap). Pero como pueden ver, hay muchos datos acá y en Triple Whale [?] que respaldan que esta campaña está funcionando, y voy a seguir trabajando para seguir escalándola.</t>
+          <t>¿Es 'The Absorption Company' la próxima gran marca de suplementos? Tienen todos los ingredientes de una marca que va a explotar. Vamos a desglosarlo. Construyeron un producto que realmente se destaca: una formulación limpia con un diferenciador claro. Después construyeron un sitio que convierte en cada gatillo [trigger]: hay etiquetado de producto para guiar a los usuarios, suscripciones para impulsar el LTV [valor de vida del cliente], el sello 'elección de médicos' [?] para dar credibilidad, y desgloses respaldados por ciencia [?] para generar confianza, recomendaciones de expertos, y flujos de compra simples y prolijos. ¿Y la pieza clave? Posicionan el producto como una rutina diaria. Eso es lo que impulsa la retención. Después viene la distribución: están corriendo más de 150 anuncios de Facebook enfocados en problema-solución, educación, desgloses de producto, ciencia y resultados. Y no solo están vendiendo, están convenciendo. Y ahora están escalando en TikTok Shop. Eso significa más contenido, más alcance y más conversiones. Entonces, ¿pueden ser la próxima gran marca? Bueno, si siguen escalando su creatividad, siguen impulsando afiliados y maximizan su LTV, definitivamente están en el camino. Comenten 'growth' y les desgloso el manual completo.</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>Es prácticamente solo una grabación/captura de pantalla del panel de Meta Ads Manager en tema oscuro, con las métricas reales de la cuenta (Resultados, Alcance, Frecuencia, Costo por resultado, Presupuesto, Gasto, Impresiones, CPM); no aparece el presentador en cámara en los frames vistos, es voz en off narrando sobre el dashboard. Un cintillo de texto rojo fijo en la parte superior funciona de hook ('New insight on ASC Meta campaigns performing well'); se ve el dock de iOS en la parte inferior, sugiriendo una grabación de pantalla de dispositivo móvil pegada en formato vertical. Sin cortes de escena, sin gráficos adicionales, locación no aplica (solo pantalla).</t>
+          <t>Talking head en recuadro pequeño abajo, foto de producto (tres frascos de suplementos: CoQ10, Berberine, etc.) sobre fondo blanco tipo catálogo, capturas de pantalla del sitio web (sección 'Backed by Experts' con citas de médicos y catálogo de productos en TikTok Shop), campera oscura.</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>Gancho: actualización de un profesional compartiendo datos en vivo de su propia cuenta ('quiero darles una actualización'). Estructura: recorrido por cifras reales concretas (alcance, frecuencia, CPA, gasto total) que sirve de evidencia paso a paso. Gatillo: autoridad y transparencia (muestra números reales, incluso admite que antes dudaba de ASC), lo que genera confianza y comentarios de otros media buyers.</t>
+          <t>Gancho de pregunta especulativa ('¿es la próxima gran marca?') que invita a quedarse a ver la respuesta; estructura de checklist/desglose (producto, web, distribución) que da sensación de análisis riguroso; menciones de cifras y elementos de credibilidad (150+ anuncios, respaldo de expertos) que dan autoridad; cierre con incentivo para comentar.</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo necesita grabar la pantalla del Ads Manager propio y narrar, cero producción adicional.</t>
+          <t>sí — solo requiere fotos de producto y capturas de pantalla del sitio, sin producción cara.</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1409,32 +1409,32 @@
     </row>
     <row r="10" ht="88" customHeight="1">
       <c r="A10" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1444,48 +1444,48 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>896</v>
+        <v>11700</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7636364743753649440</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7636037201276505374</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath responde, en formato de preguntas y respuestas, cual es la mejor optimizacion de campana en Meta Ads entre leads, vistas de landing page o ventas, y cuando conviene elegir cada una.</t>
+          <t>Chase Chappell compara las estrategias de marketing de dos marcas de ropa deportiva, Rhone y Ten Thousand, analizando sus embudos de venta, presencia en retail y enfoque creativo (rendimiento a corto plazo vs. construcción de marca a largo plazo).</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>¿Cual es la mejor optimizacion? ¿Leads, vistas de landing page o ventas? Definitivamente no vistas de landing page. Y entre las otras dos, realmente depende de tu negocio. Entonces, te conviene ir con ventas si podes rastrear la conversion de compra, cuando alguien efectivamente hace una compra. Eh, particularmente si hay valores diferentes, y podes optimizar para compras de mayor valor. Personas que gastan mas cuando compran en tu tienda online, por ejemplo. Si no podes rastrear eso directamente, es decir, si hay un paso intermedio (la gente agenda una cotizacion gratis, una llamada o una consulta o algo asi), entonces te conviene mas ir con leads.</t>
+          <t>¿De quién es mejor el marketing, de Rhone o de Ten Thousand? Ambas marcas corren alrededor de 120 anuncios en Meta. Así que esto no se trata de volumen, se trata de cómo convierten la atención en ingresos. Rhone manda el tráfico directo a la página de producto. Ten Thousand manda el tráfico a la página de colección. Rhone elige un camino más rápido, con mayor intención y conversiones más directas. Pero acá es donde se pone interesante: el flujo de colección de Ten Thousand no es una debilidad, es una jugada de marca. Están dejando que los clientes exploren múltiples productos y múltiples puntos de entrada. Esto tiene más chances de encontrar el ajuste perfecto, y de hecho puede aumentar su AOV [ticket promedio] si la experiencia está bien calibrada. Ahora sumemos el retail: Rhone tiene más de 20 tiendas. Ten Thousand tiene cero. Rhone tiene presencia física. La confianza se construye offline, lo cual sin dudas ayuda a las conversiones online. Pero Ten Thousand es totalmente digital, lo que significa que cada dólar está obligado a rendir. Sin red de contención del retail. Es un juego distinto, y definitivamente es una presión distinta. Ahora miremos la estrategia creativa: Rhone apuesta a su rendimiento con UGC, ofertas de respuesta directa, conversiones rápidas. Ten Thousand apuesta a su marca con visuales prolijos, posicionamiento premium, un marketing menos agresivo y una percepción más controlada de quiénes son. Entonces, ¿qué está pasando realmente acá? Rhone está optimizando para ingresos inmediatos. Ten Thousand está optimizando para valor de marca a largo plazo. Entonces, ¿quién creen que está ganando? Cuéntenme abajo.</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>Toma continua al aire libre (silla puf sobre pasto, luz natural), Ben con anteojos de sol y ropa casual; subtitulos grandes en negrita que resaltan palabra por palabra lo que dice; pequenos iconos (personas, flecha, documento, apreton de manos) en las esquinas superiores, posiblemente indicando el tema o el formato de una entrevista/podcast reciclado como clip corto.</t>
+          <t>Talking head en recuadro pequeño abajo, clip de video de marca con overlay de texto (escena de tren/subte con logo cruzado y crédito 'Creative Director &amp; Co-Founder'), captura de pantalla del carrito de compra de Ten Thousand con anotación roja, captura de comentarios de Instagram de la cuenta de Rhone con recuadros rojos resaltando respuestas, campera oscura.</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>Pregunta directa como gancho ('What's the best optimization?'); respuesta corta, clara y accionable en menos de 31 segundos; gatillo de utilidad practica inmediata para cualquiera que gestione campanas.</t>
+          <t>Formato de comparación cabeza a cabeza que invita a 'elegir un bando'; estructura por variable (tráfico, retail, creatividad) fácil de seguir; conclusión con dos filosofías claras y opuestas (ingresos inmediatos vs. valor de marca a largo plazo) que deja algo memorable; cierre con pregunta de opinión.</t>
         </is>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>si, es una respuesta corta a camara con subtitulos, sin edicion compleja.</t>
+          <t>sí — solo necesita capturas de pantalla y clips públicos de las marcas, sin producción propia cara.</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1501,27 +1501,27 @@
     </row>
     <row r="11" ht="88" customHeight="1">
       <c r="A11" s="2" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Caleb Kruse (Mr. Paid Social)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,48 +1536,48 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J11" s="6" t="n">
-        <v>47400</v>
+        <v>11500</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.paidsocial/video/7647588481862012174</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7639758395595099422</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Caleb (mr.paidsocial) presenta un sistema gratuito, corrido con Claude Code, para crear y lanzar una cuenta de anuncios de Meta completa -imagenes, video UGC, hasta claymation- usando solo la voz, sin disenador ni editor. Cierra invitando a bajar un repo de GitHub gratis con todo el sistema.</t>
+          <t>Video de análisis de marca que desglosa la estrategia publicitaria y de retail de Vuori, la marca de indumentaria deportiva valuada en mil millones de dólares, explicando su volumen creativo, su juego de AOV/LTV y su expansión a tiendas físicas mediante un diagrama tipo 'flywheel'.</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>¿Y si pudieras construir y lanzar una cuenta de anuncios de Meta completa? Docenas de anuncios de imagen, videos UGC que detienen el scroll, incluso anuncios estilo claymation usando nada mas que tu voz y Claude Code. Sin disenador, sin editor de video, sin VA, y sin tocar el Administrador de anuncios. Estoy a punto de hacer todo esto en vivo en este video, y te voy a dar el sistema exacto que voy a estar usando, gratis. Voy a tomar una foto de producto y convertirla en 30 anuncios de imagen en estilos totalmente distintos sin escribir un solo prompt. Despues te voy a mostrar como clonar cualquier anuncio que hayas visto por ahi, el ganador de un competidor, un anuncio random en tu feed, y reconstruirlo con tu propio producto en segundos. Despues pasamos a video. Te voy a mostrar el flujo de trabajo creativo completo de UGC con IA y como lograr una consistencia de personaje perfecta. Despues te voy a mostrar como podes agregar B-roll, efectos de sonido lo-fi, musica de fondo, voz en off. Todo lo que posiblemente agregarias a un video y tendrias que editar y publicar, lo podes hacer dentro de Claude Code. Sin abrir CapCut, sin Canva, sin Adobe, sin Final Cut Pro. Literalmente estas hablando con Claude como si fuera tu gerente creativo. Incluso voy a tomar un TikTok al azar y mostrarte como puedo recrearlo plano por plano usando uno de mis propios productos. Ademas te voy a mostrar como hacer anuncios estilo animacion que parezcan claymation o estilo Pixar. Y finalmente, te voy a mostrar mi parte favorita de todo este sistema. Lanzar los anuncios a tu cuenta de anuncios real sin tocar el Administrador de anuncios. Claude puede extraer todos los datos de tu cuenta de anuncios y aprender exactamente que esta funcionando. Y no solo eso, sino que puede escanear todos tus anuncios de imagen y video para entender con contexto perfecto de que deberia tratarse cada anuncio, y despues escribirte el copy de anuncio perfecto especifico para cada anuncio individual. Este sistema por si solo te va a ahorrar horas todos los dias y te va a dar el desbloqueo que necesitas para lanzar mas anuncios en tu cuenta hoy mismo. Y lo mejor de todo, esto vive en un repositorio de GitHub gratuito que construi y que podes conseguir en la descripcion de abajo. Si nunca usaste Claude Code y no tenes ni idea de como usar GitHub, no importa. Literalmente lo unico que tenes que hacer es agarrar el link que te dan, tirarlo en Claude Code, y el se encarga de toda la configuracion por vos. Asi que si corres anuncios de Meta o queres correr anuncios de Meta, este video es el cheat code que estabas esperando. Y este podria ser uno de los videos mas importantes que veas en todo el ano. Vamos a entrarle.</t>
+          <t>La estrategia de marca de mil millones de dólares de Vuori. Están corriendo más de 17 anuncios en Meta. Eso es un volumen enorme de creatividades, con formatos como videos de estilo de vida, videos UGC, videos protagonizados por el fundador, demos de producto, imágenes, tomas estéticas de marca, testimonios y contenido nativo de venta suave. No fuerzan la venta, construyen el deseo. Educan, y después mandan a todos directo a la página de producto. Ofertas simples de 20% de descuento en la primera compra, con visuales prolijos, posicionamiento premium y desgloses de la historia de la tela con prueba social. Convierte porque el producto queda clarísimo. Ahora la palanca real: AOV y LTV. No venden un solo producto, venden los conjuntos completos. Tienen remeras y pantalones, opciones para gimnasio y para el día a día, y variantes de talles, calce, colores y estilos. Te gusta una marca para todo. Eso aumenta el tamaño del carrito automáticamente. Después, alta retención, producto de alta calidad, uso diario integrado con email, más ciclos de recompra. Los clientes no compran una sola vez, vuelven una y otra vez. Ahora el retail. Tienen más de cien tiendas propias en todo el mundo y están en Nordstrom, REI y Equinox. No se apuraron. Primero construyeron demanda, después se expandieron a mercados de altos ingresos. Y acá está la jugada real: los anuncios llevan a ventas online. Ese alcance lleva a más reconocimiento de marca. El reconocimiento de marca lleva de vuelta a visitas en tienda, y las tiendas generan lealtad. La lealtad genera recompras directas al consumidor. Ese es el flywheel. Entonces, ¿cuál es la conclusión? Vuori no ganó solo con anuncios, no ganó solo con retail. Ganaron curando todo el sistema junto: volumen creativo, calidad de producto, posicionamiento premium y expansión de retail con un LTV fuerte. Así se construye una marca de mil millones de dólares. Comentá 'playbook' y te mando las cinco etapas que vas a atravesar al construir tu marca.</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano (gorra, anteojos, luz azul/verde de fondo tipo home studio) intercalado con capturas de pantalla de un editor de codigo/chat de Claude Code y ejemplos de anuncios generados. Subtitulos dinamicos con palabras clave resaltadas en blanco sobre negro ('VOICE', 'PERFECT') con icono de forma de onda de audio. Cortes frecuentes entre camara y pantalla, sin locacion mas alla del escritorio/oficina del creador.</t>
+          <t>Formato split-screen típico de este canal de análisis de marcas: mitad inferior es talking head del presentador (remera clara y campera oscura, micrófono profesional visible, fondo neutro) hablando fijo a cámara; mitad superior cambia de contenido según el tema (clip de una mujer grabándose al espejo con el celular, captura de pantalla/screencast de la página de producto de Vuori con talles y colores, y un diagrama animado tipo 'flywheel' con flechas, logo de la marca y etiquetas de texto: Ads, Meta, Online Sales, Awareness, Store visits). Encuadre vertical, sin cortes dentro del talking head, ritmo marcado por los cambios de la mitad superior.</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta hipotetica + promesa de maximo valor ('el video de mas valor que hice'); estructura de lista de capacidades demostradas una por una en vivo (imagen, video, lanzamiento); gatillo de gratuidad y urgencia/FOMO (repo gratis, 'uno de los videos mas importantes que veas este ano') mas reduccion de friccion para quien nunca uso la herramienta.</t>
+          <t>Gancho: cifra grande y marca reconocible en el título/primer segundo ('estrategia de mil millones de dólares de Vuori'). Estructura: desglose enumerado de palancas de negocio (creatividad, AOV/LTV, retail, flywheel) que cierra con una síntesis memorable. Gatillo: autoridad/expertise analítico + números concretos (17+ ads, 20% off, 100+ tiendas) + curiosidad por 'el sistema completo'; CTA de comentario para generar leads.</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>sí, solo necesita camara/mic y grabacion de pantalla, sin equipo de produccion caro.</t>
+          <t>sí + requiere investigar la marca a fondo y armar un diagrama simple tipo flywheel (se puede hacer gratis en Canva), sin necesidad de equipo caro.</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1593,15 +1593,15 @@
     </row>
     <row r="12" ht="88" customHeight="1">
       <c r="A12" s="2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -1628,33 +1628,33 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>34600</v>
+        <v>11400</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.paidsocial/video/7650195193890721038</t>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7657288764053622029</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>En formato 'todo lo que construi', Caleb muestra una serie de automatizaciones armadas con el nuevo modelo Fable 5 de Claude: dashboards de contenido, gestion de su comunidad de Skool, republicado de posts, email marketing, anuncios de Meta y hasta un programador de horarios de guarderia del gimnasio, todo controlado desde el celular.</t>
+          <t>Caleb muestra como, con una skill personalizada de Claude que conecta los MCP de Airtable y Meta Ads, le pidio a Claude que generara y lanzara 500 anuncios (50 creativos x 10 variantes de copy) a su cuenta de Meta en cuestion de minutos, algo que a mano le hubiera llevado una semana.</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Esto es todo lo que construi en las ultimas 24 horas usando el nuevo modelo Fable 5 de Claude. Primero le hice construir este dashboard de contenido. Muestra mi cantidad total de seguidores en todos los canales sociales, la cantidad total de vistas. Aca tengo todos mis distintos canales con sus estadisticas. Un dashboard en vivo de mi contenido en cada canal de las ultimas 48 horas. O graficos increibles que muestran el volumen de publicaciones, la tendencia promedio en tres meses, la tasa de acierto de seguidores por publicacion, que es cuantos de mis videos se vuelven virales, contenido que funciono bien que no republique en otros canales. Toda una base de datos de biblioteca de contenido que muestra las vistas en cada canal donde publico mi contenido, y una vista de todos los acuerdos de marca que hice. Ah si, construi eso desde mi celular. Lo siguiente que tuve que hacer fue auditar mi comunidad de Skool y darme sugerencias sobre como hacer que la seccion de cursos fluya mejor. Asi que en realidad me construyo cursos nuevos, donde descargo todo mi contenido de Skool y volvio a subir todo por mi. Y ahora mismo esta literalmente tomando control de mi navegador en mi Mac Mini y subiendo miniaturas personalizadas a los nuevos cursos que creo para mi. Tambien puede hacer cosas como mandar DMs a la gente que esta por cancelar, crear eventos automaticamente en el calendario del grupo, y publicar automaticamente cosas como grabaciones grupales de Skool y oradores invitados en la seccion de cursos por mi. Todo esto es trabajo que normalmente tendria que pagarle a una VA para hacer, o que me llevaria horas cada semana. Ahora mismo lo tengo trabajando en un nuevo sistema de email para mi, asi que le hice investigar cada proveedor de email que existe y averiguar cuales tenian las mejores integraciones de API. Y va a encargarse de cambiar toda mi infraestructura de email de un proveedor a otro. Tengo a Fable 5 conectado a todos mis canales sociales para que pueda republicar contenido por mi. Asi que aca dije: publique un video en mi Instagram y quiero que lo republiques en TikTok y YouTube Shorts, y lo hizo. Tambien queria que escribiera un texto mas largo para LinkedIn y lo hizo por mi. Esta proxima es una locura. Le hice construir un programador automatico de cuidado infantil para el gimnasio al que voy. El gimnasio al que voy solo tiene como dos lugares de guarderia cada manana, y si no te despertas a las 6 am, simplemente no los conseguis. Asi que Fable 5 puede controlar mi navegador Chrome a las 6 de la manana y seleccionar automaticamente mis horarios preferidos para dejar a mi hijo en el gimnasio. Le hice rastrear todas mis finanzas y conciliar toda mi contabilidad entre lo personal y lo de mi negocio. Lo tengo publicando y creando anuncios para mi y mi cuenta de anuncios sin que yo tenga que entrar al Administrador de anuncios. Voy a crear anuncios tipo claymation y animaciones estilo Pixar. Tengo esta cosa integrada en practicamente cada aspecto de mi vida ahora mismo, tanto en mi negocio como en mi vida personal. Y lo tengo corriendo en esta Mac Mini, asi que literalmente puedo controlarlo desde cualquier lugar, desde mi celular. Lo que significa que si estoy manejando de vuelta a casa y quiero saber como va mi contenido, puedo simplemente hablarle por voz a Claude y me va a decir. O si tengo anuncios nuevos que necesitan publicarse, le puedo pedir que los publique por mi y lo va a hacer. ¿Cual es lo mas genial que construiste hasta ahora? Contame en los comentarios.</t>
+          <t>Dejame mostrarte como podes crear 500 anuncios en cinco minutos usando Claude y Airtable. Ya no hay ninguna razon para que sigas usando el Administrador de anuncios para armar tus anuncios. El ingrediente secreto de todo esto es una skill personalizada que arme, que conecta el MCP oficial de Airtable con el MCP de Meta Ads. Y quedate hasta el final porque te voy a mostrar donde conseguir esa skill al final del video. Paso 1: vas a conectar el MCP de Airtable a Claude. Paso 2: vas a conectar el MCP oficial de Meta a Claude agarrando este link y agregandolo como conector MCP personalizado dentro de Claude. Paso 3: vas a tomar mi skill personalizada y agregarla como skill personalizada de Claude dentro de Claude. ¡Ahora literalmente le podes pedir a Claude que haga cientos de anuncios en tu cuenta de anuncios! Hagamos una demo rapida. Le voy a pedir a Claude que me haga 500 anuncios nuevos promocionando mi comunidad de Skool. Primero voy a subir 45 anuncios de imagen y 5 anuncios de video a la Biblioteca Creativa de Facebook. Ahora Claude puede usar el MCP de Meta para traer todos esos assets a mi base de Airtable. Ahora le voy a pedir a Claude que me escriba 10 variaciones de copy de anuncio para cada uno de esos anuncios usando mis 10 frameworks de copy favoritos. Entonces 50 creativos de anuncio por 10 variaciones de copy da 500 anuncios en total. Ahora le pido a Claude que arme todo esto en una base de Airtable para que yo la revise, y podes ver aca que estan todos en mi Airtable con todas las variantes de copy, el creativo seleccionado, y toda la configuracion preconfigurada. ¡Si! Esto significa que no tenes que desactivar manualmente todas las mejoras creativas automaticas. Ahora lo unico que tengo que hacer es pedirle a Claude que lance estos anuncios a mi cuenta en grupos de 10, y ahi va, despues de unos minutos tengo todos esos anuncios en mi cuenta de anuncios de Meta. Y si hubiera querido armar todos estos anuncios manualmente usando el Administrador de anuncios, probablemente me hubiera llevado una semana entera. [?] Conseguí mi skill, que le da un cerebro completo a tu Claude para que todo este sistema funcione correctamente. Comenta 'airtable' y te mando el link.</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>Talking head en oficina/casa con luces de colores (verde/rosa) y planta de fondo, banner de texto rojo fijo en la parte superior con el titulo 'EVERYTHING IVE BUILT USING FABLE 5', subtitulos dinamicos abajo. Intercalado con grabacion de escritorio/mano senalando un monitor con un dashboard real (seguidores de Facebook, YouTube, X). Cortes entre webcam y pantalla, estilo demo casera.</t>
+          <t>Pantalla dividida: mitad superior alterna capturas de documentacion tecnica del sistema (tablas, principios de funcionamiento) y de la interfaz de Airtable con los anuncios generados; mitad inferior es webcam del creador con gorra, en cuarto con luces de colores. Subtitulos dinamicos, cortes frecuentes entre demo de pantalla y cara para mostrar el proceso paso a paso.</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>Gancho de curiosidad ('todo lo que construi en 24 horas'); estructura de catalogo de casos de uso variados y crecientes en sorpresa (dashboards, cursos, email, guarderia, finanzas, ads); gatillo de pregunta final que invita al comentario y fantasia aspiracional de un asistente todopoderoso que maneja todo el negocio.</t>
+          <t>Gancho de resultado extremo y cuantificado ('500 anuncios en 5 minutos'); estructura clara en pasos numerados (1, 2, 3) reforzada con demo en vivo como prueba; gatillo de reciprocidad (comentar para recibir la skill gratis) apalancado en el dolor de armar anuncios uno por uno a mano.</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>sí, el formato de grabacion es barato, aunque depende de tener ya varios sistemas y negocios digitales armados para poder mostrar tantos casos de uso.</t>
+          <t>sí, el video en si es barato de grabar, aunque construir la demo (conectar MCPs de Airtable y Meta) exige conocimiento tecnico previo.</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1685,27 +1685,27 @@
     </row>
     <row r="13" ht="88" customHeight="1">
       <c r="A13" s="2" t="n">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Mitch Barham (Beardpreneur)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1720,48 +1720,48 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>13400</v>
+        <v>11000</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beardpreneur/video/7634698833859005709</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7598212323538455838</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Mitch (beardpreneur) explica en 4 puntos el nuevo conector MCP de Meta Ads que permite gestionar campanas de Facebook Ads directamente desde Claude o ChatGPT sin necesidad de programar, y ofrece mandar el link a quien comente 'meta'.</t>
+          <t>Chase Chappell analiza la estrategia de anuncios de Facebook de Alex Hormozi (170+ anuncios activos): destaca que sus hooks y segmentación funcionan bien, pero critica que le falta contenido de prueba/conversión (reseñas, antes-después, ofertas) para acompañar todo el funnel.</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Vas a querer guardar esto para despues. Meta acaba de lanzar una actualizacion enorme que te permite manejar tus anuncios de Facebook directamente desde Claude o ChatGPT. Y aca van cuatro cosas que realmente necesitas saber sobre el conector MCP de Meta Ads. 1. No necesitas ser desarrollador para instalarlo. No hace falta configuracion de API ni programar nada. Literalmente solo lo conectas a tu herramienta de IA via MCP y listo. Desconfia del consejo que te da. Probablemente sea bastante parecido a un representante normal de Facebook que te da consejos malos. Pero si va a extraer tus insights reales de rendimiento de campana, datos de catalogo. Asi que la IA puede analizar realmente que esta funcionando y, ya sabes, darte ideas. Pero yo las tomaria con pinzas. Pero ahora tambien podes editar campanas en lenguaje natural en vez de andar clickeando por todos esos menus del Administrador de anuncios. Y le podes decir a la IA que directamente actualice tu conjunto de anuncios, cree una campana nueva, lo que quieras hacer. Por ultimo, funciona a traves de 4 canales. Podes usar tu IA para extraer insights de Meta y compararlos con tus otras plataformas, todo en un solo lugar. Si queres el link para instalar esto dentro de tu IA, deja la palabra 'meta' y te mando el link del MCP para que lo instales con tu Claude o tu ChatGPT.</t>
+          <t>¿La estrategia de anuncios de Facebook de Alex Hormozi convierte en la era del 'ad drama' [?]? Está corriendo más de 170 anuncios de Facebook ahora mismo. Múltiples ángulos únicos, llamados directos (callouts), problema-solución, incluso anuncios simples de imagen que se ven aburridos a propósito. Tiene entre cinco y diez hooks (ganchos) únicos por ángulo, interpelando a su cliente ideal y forzando la autoidentificación. Esa parte funciona. Capta la atención y califica a la audiencia. Pero acá está el problema. Una vez que tiene la atención, no está acelerando lo suficientemente rápido a los compradores a lo largo del recorrido (journey). No hay reseñas, no hay anuncios de beneficios, no hay desgloses de la oferta, no hay pruebas de transformación, no hay antes y después. En 2026 tenés que cubrir cada etapa: atención, prueba, deseo, justificación, conversión y lealtad. Agregá [?] estas distintas creatividades publicitarias únicas para cada paso: reseñas, beneficios, claridad del producto, y resultados reales. Sus más de ciento setenta anuncios podrían convertirse en 17 anuncios funcionando con máxima eficiencia. Eso es hacer 'a drama to' [?] marketing bien hecho. No solo hooks, sino dominación total del recorrido del cliente. Contame qué pensás. ¿Está aprovechando su 'a drama to' [?] al máximo potencial?</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>Formato de pantalla dividida: mitad superior es una captura de una pagina/anuncio oficial de Meta con el titular 'Introducing Meta Ads AI Connectors' y una ilustracion de personas en oficina; mitad inferior es el creador (barba larga, anteojos) hablando a camara sosteniendo un microfono. Subtitulos palabra por palabra quemados en el video, fondo neutro tipo estudio, sin locacion identificable mas alla de un espacio de grabacion cerrado.</t>
+          <t>Encuadre: capturas de Meta Ads Library y gráficos de diseño propio (flowchart, grilla de anuncios) con el creador en recuadro inferior. Subtítulos: etiquetas de texto diseñadas (burbujas moradas: 'WE HAVE AN OFFER FOR YOU', etc.), flechas rojas de énfasis. Cortes: alterna entre captura del Ads Library ('~170 results' para Alex Hormozi), diagrama de flujo animado y grilla de fotos con etiquetas. Gráficos: diagramas hechos a medida (ícono de 'Prospects', logo de Meta), fondo de puntos decorativo. Locación: sin locación física visible, fondo de estudio con micrófono.</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>Gancho de noticia/autoridad ('Meta acaba de lanzar una actualizacion enorme'); estructura numerada de 4 datos clave, facil de seguir y de guardar; gatillo de reciprocidad con CTA claro (comentar la palabra clave para recibir el link), que ademas genera comentarios masivos.</t>
+          <t>Gancho: menciona a una figura reconocida del marketing (Alex Hormozi) en formato de pregunta provocadora sobre si su estrategia realmente funciona, combinando autoridad prestada con la promesa de una crítica polémica. Estructura: formato de auditoría — reconoce qué funciona (hooks, segmentación) y después señala el hueco (falta contenido de conversión) y propone una solución (17 anuncios optimizados cubriendo todo el funnel). Gatillo: crítica contraintuitiva a una celebridad del rubro más pregunta final que invita al debate en comentarios.</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>sí, solo requiere un microfono y la captura de una pagina web oficial, con edicion simple de subtitulos y split-screen.</t>
+          <t>No — exige diseño gráfico personalizado (flowcharts, grillas con etiquetas) además de research en Ad Library, más trabajo que un simple talking-head.</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1777,22 +1777,22 @@
     </row>
     <row r="14" ht="88" customHeight="1">
       <c r="A14" s="2" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1812,48 +1812,48 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12700</v>
+        <v>10900</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7634971114262908190</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7652379900728413471</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell analiza si 'The Absorption Company' (marca de suplementos vinculada a Ian Somerhalder) tiene lo necesario para convertirse en la próxima gran marca, repasando su producto, su sitio web y su estrategia de distribución.</t>
+          <t>Video que enumera el 'stack' de herramientas de inteligencia artificial que, según el creador, usan las marcas de e-commerce de cien millones de dólares para investigar, producir creatividades estilo UGC y lanzar campañas más rápido.</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>¿Es 'The Absorption Company' la próxima gran marca de suplementos? Tienen todos los ingredientes de una marca que va a explotar. Vamos a desglosarlo. Construyeron un producto que realmente se destaca: una formulación limpia con un diferenciador claro. Después construyeron un sitio que convierte en cada gatillo [trigger]: hay etiquetado de producto para guiar a los usuarios, suscripciones para impulsar el LTV [valor de vida del cliente], el sello 'elección de médicos' [?] para dar credibilidad, y desgloses respaldados por ciencia [?] para generar confianza, recomendaciones de expertos, y flujos de compra simples y prolijos. ¿Y la pieza clave? Posicionan el producto como una rutina diaria. Eso es lo que impulsa la retención. Después viene la distribución: están corriendo más de 150 anuncios de Facebook enfocados en problema-solución, educación, desgloses de producto, ciencia y resultados. Y no solo están vendiendo, están convenciendo. Y ahora están escalando en TikTok Shop. Eso significa más contenido, más alcance y más conversiones. Entonces, ¿pueden ser la próxima gran marca? Bueno, si siguen escalando su creatividad, siguen impulsando afiliados y maximizan su LTV, definitivamente están en el camino. Comenten 'growth' y les desgloso el manual completo.</t>
+          <t>El stack de herramientas de IA detrás de las marcas de e-commerce de cien millones de dólares. Claude para armar la estrategia: ganchos, guiones, ofertas y ángulos. Manus para analizar creadores, cuentas publicitarias y brechas de rendimiento. Yuka[?] para automatizar las invitaciones a creadores a gran escala para TikTok Shop. Higgsfield[?] (confirmado por el logo que aparece en pantalla) para convertir ideas estáticas en creatividades de video estilo UGC. Opencl[?] para correr tareas mientras dormís. Y archives[?] para crear anuncios UGC sin depender de creadores. Imaginative para sacar imágenes de anuncios de Meta a gran escala. Así es como las mejores marcas se mueven más rápido. No usan la IA solo para hacer contenido, usan la IA para investigar más rápido, lanzar más rápido, testear más rápido y encontrar ganadores antes que nadie. Comentá 'AI' y te mando el stack exacto.</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>Talking head en recuadro pequeño abajo, foto de producto (tres frascos de suplementos: CoQ10, Berberine, etc.) sobre fondo blanco tipo catálogo, capturas de pantalla del sitio web (sección 'Backed by Experts' con citas de médicos y catálogo de productos en TikTok Shop), campera oscura.</t>
+          <t>Video de ritmo muy acelerado (35 segundos) que intercala capturas/grabaciones de pantalla de herramientas de IA (interfaz de 'Higgsfield' con botón 'Generate' y avatar; una escena tipo video generado por IA con el branding 'MCP x Claude') en la mitad superior, con el presentador (remera negra, fondo claro liso, micrófono de podcast) hablando en la mitad inferior. Título grande en texto blanco sobre franja negra en el frame de apertura, junto a una imagen de referencia.</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta especulativa ('¿es la próxima gran marca?') que invita a quedarse a ver la respuesta; estructura de checklist/desglose (producto, web, distribución) que da sensación de análisis riguroso; menciones de cifras y elementos de credibilidad (150+ anuncios, respaldo de expertos) que dan autoridad; cierre con incentivo para comentar.</t>
+          <t>Gancho: cifra grande ('marcas de cien millones de dólares') + promesa de una lista secreta ('tech stack'). Estructura: listado rápido de herramientas con una función concreta para cada una, ideal para el formato corto (35 segundos). Gatillo: curiosidad (nombres de herramientas de IA nuevas/desconocidas) + autoridad + utilidad práctica inmediata + CTA de comentario ('AI').</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>sí — solo requiere fotos de producto y capturas de pantalla del sitio, sin producción cara.</t>
+          <t>sí + solo necesita grabaciones de pantalla de herramientas freemium/gratuitas y un guion tipo lista, aunque exige estar al tanto de herramientas de IA nuevas.</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1869,32 +1869,32 @@
     </row>
     <row r="15" ht="88" customHeight="1">
       <c r="A15" s="2" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1904,48 +1904,48 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1465</v>
+        <v>9980</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7629795407534591254</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7641243325227339038</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell explica por qué el ROAS que reporta Meta puede estar inflado por solapamiento con otros canales (afiliados, SEO), y muestra en un dashboard cómo distintos modelos de atribución (first click, total impact, last click) de herramientas como Triple Whale o Northbeam dan cifras muy distintas para decidir dónde cortar gasto.</t>
+          <t>Presenta una herramienta de inteligencia artificial que genera automáticamente decenas de anuncios de marca a partir de la URL de un producto, sin diseñadores ni producción.</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Ahora, cuando estás escalando un negocio a través de anuncios pagos [corregido de "paydays", error de reconocimiento], vas a tener un montón de cosas distintas corriendo de fondo: vas a tener email, vas a tener orgánico, vas a tener afiliados. Y lo que suele pasar es que meta, por ejemplo, les va a mostrar tus anuncios a personas que llegaron a tu sitio, digamos, a través de un link de afiliado o por SEO, y como resultado [corregido de "as a resolver"] meta puede sobrereportar, porque está compartiendo las impresiones que se solapan con gente que también vino de un canal distinto, pero como recibieron un anuncio de meta en una ventana de tiempo específica, después se los clasifica como una conversión en meta. Y ven acá, por ejemplo, que meta está reportando un ROAS [corregido de "row s", error de reconocimiento] de 7x, que si solo miraran meta ahora mismo pensarían que es increíble. Si miro, por ejemplo, el first click (primer clic), pueden ver que el ROAS [corregido de "Ross"] en realidad se mide en 2.4. Si voy al impacto total, pueden ver que es 3.69. Y si voy al last click (último clic), va a ser otra cosa completamente distinta a lo que meta está reportando actualmente dentro de Ads Manager. Y ahí está la belleza de usar una herramienta de atribución como Triple Whale [corregido de "triple well"], como Northbeam [corregido de "North Beam"], no importa cuál uses, personalmente yo prefiero Triple Whale. Pero si miran acá, esta cuenta está gastando $274,000 en los últimos 30 días, y pueden ver que somos muy dominantes en Google. Pero si empiezo a mirar estos distintos modelos de atribución y lo desgloso por canal, y entro al canal, puedo mirar la campaña, puedo mirar el rendimiento de los anuncios, y muy rápidamente empezás a encontrar áreas de desperdicio que hay que cortar. Y después empezás a mirar el MER [corregido de "Mer"], entendés cuál tiene que ser tu objetivo de MER, y empezás a optimizar en base a esas métricas. Ahora, si no estás usando herramientas como esta, es muy difícil escalar de forma rentable, porque hay tanto pasando, hay tanto solapamiento, que es muy difícil entender de dónde viene realmente la gente que después convierte, y en realidad no vas a saber qué canal está generando las conversiones.</t>
+          <t>Esta nueva herramienta de IA te crea anuncios ilimitados con un solo prompt. ¿Y la parte que da miedo? Que realmente convierten. Se llama Imaginative [?] (en el título aparece como 'Imaginetive'). Literalmente pegás la URL de tu producto. Después la IA escanea tu sitio web, extrae tus imágenes, extrae tus fuentes tipográficas, copia los colores de tu marca, lee tus reseñas, escanea Reddit buscando a tus competidores, escanea las reseñas de Amazon, y arma todo tu kit de marca automáticamente. Después elegís los formatos de anuncio que querés: anuncios estilo POV, anuncios de Instagram Story, anuncios tipo respuesta de DM, anuncios estilo nota, anuncios de reseña, anuncios de estilo de vida, anuncios de comparación. Y en segundos obtenés de 50 a 100 piezas publicitarias completamente de marca, listas para lanzar. Sin diseñadores, sin Canva, sin Photoshop, sin producciones caras. Y la parte más loca: estos anuncios ya no parecen contenido generado por IA. Algunas de estas marcas están consiguiendo 3x, 5x, hasta 10x de ROAS usándolos, y están escalando una barbaridad. Por eso las marcas de crecimiento más rápido están produciendo cientos de piezas creativas todos los meses. La IA acaba de cambiar la publicidad para siempre. Comentá 'AI' y te mando la herramienta.</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>Sin talking head: tarjeta de texto roja fija ("Why attribution tools are a must when you want to scale ads") sobre una captura/grabación de pantalla de un dashboard de atribución con métricas (porcentajes, montos en dólares, tabla por canal: Google Ads, Meta, Klaviyo, TikTok, Direct). Los tres frames capturados son prácticamente idénticos, lo que sugiere una imagen fija sostenida con narración en off.</t>
+          <t>Talking head/selfie con micrófono, superpuesto por croma sobre capturas de pantalla de una herramienta de generación/análisis de anuncios (interfaz tipo swipe file con 'Feature Breakdown' de una marca de jeans, y panel de resultados de IA con la pieza 'Linen. Relaxed'). Subtítulo grande tipo texto en caja azul con emoji ('Have you heard of this New Ai Tool? 🤔') en uno de los frames. Cortes entre el presentador y las capturas de pantalla de resultados.</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio-alto</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>Gancho de autoridad/urgencia en el título (las herramientas de atribución "son un must" para escalar) reforzado con prueba visual concreta: cifras reales que contrastan el ROAS inflado de Meta contra otros modelos de atribución, generando credibilidad técnica.</t>
+          <t>Gancho de curiosidad directo ('¿escuchaste hablar de esta nueva herramienta de IA?') más promesa de beneficio concreto y algo 'escalofriante' (que convierten de verdad). Detalla un proceso paso a paso fácil de imaginar (pegar URL y todo automático), apela a autoridad con números concretos (3x-10x ROAS, 50-100 creatividades) y cierra con un call-to-action de comentario que dispara engagement.</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: solo necesita una tarjeta de texto y una captura de pantalla de un dashboard (propio o de ejemplo), sin cámara ni edición avanzada.</t>
+          <t>sí + solo requiere grabarse hablando y mostrar capturas de pantalla de la herramienta, sin edición avanzada.</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -1961,32 +1961,32 @@
     </row>
     <row r="16" ht="88" customHeight="1">
       <c r="A16" s="2" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1996,48 +1996,48 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>924</v>
+        <v>9889</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7634126651894287648</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7592305158449827102</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath comparte un tip rápido: cuando una campaña de Meta Ads falla o tira errores raros por bugs de Ads Manager, muchas veces la solución más simple es recrearla desde cero en vez de intentar arreglarla.</t>
+          <t>Chase Chappell describe el estilo creativo híbrido que combina IA (para fondos, motion graphics y transiciones) con talento real filmado en cámara, como estrategia para triplicar el volumen de anuncios sin perder autenticidad.</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Una solución fácil y subestimada para muchas campañas de anuncios de Meta es simplemente recrearla. Ads Manager está lleno de errores (bugs) y es muy común que algo salga mal dentro de tu campaña, que no entregue bien o que directamente deje de entregar. Que aparezcan una serie de errores que en realidad no entendés bien qué significan ni cómo solucionarlos. En lugar de tratar de ajustarla y cambiar cosas para que funcione, a veces es mejor decir: ¿sabés qué? Voy a recrear esto desde cero. Muchas veces eso hace que funcione, que empiece a entregar y a entregar correctamente.</t>
+          <t>Este nuevo estilo creativo se está apoderando del e-commerce ahora mismo. Es IA híbrida con clips reales. Y las marcas están usando IA para manejar todo lo que ralentiza la producción. Fondos, motion graphics, transiciones de escena. La IA construye todo el entorno visual en segundos. Y después mezclan creadores de IA con talento real filmado en cámara. Una parte es IA, pero el resto son caras reales, reacciones reales, historias reales. Esto mantiene el contenido humano para que los espectadores confíen en él, pero le da a la marca más material para trabajar, para cosas que no podrían capturar u obtener de creadores a esa escala. Acá está la estrategia detrás de esto. La IA te da variaciones infinitas para que puedas testear docenas de creadores de IA rápido. El talento real mantiene el rendimiento alto porque nada convierte como la verdadera emoción [?] (en el audio se entiende 'true motion'). La mezcla permite que las marcas tripliquen su producción, bajen costos, y dominen los feeds. Con volumen creativo constante, podés lograr escala sin sacrificar autenticidad. Las marcas que adoptan esto primero están ganando la subasta en Meta y TikTok porque su contenido se siente nativo. Pero tienen de tres a cinco veces la cantidad de anuncios saliendo, algo que estas plataformas aman. Así que si todavía no estás probando este formato híbrido, ya estás atrás. Comentá 'IA' y te muestro cómo hacerlo.</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: plano medio, sentado a una mesa exterior. Subtítulos: palabra por palabra en mayúsculas. Cortes: toma continua, sin gráficos adicionales en los frames vistos. Gráficos: ninguno visible. Locación: exterior, campo/pradera soleada, mesa de picnic, luz natural fuerte, usa lentes de sol.</t>
+          <t>Encuadre: mezcla de captura de pantalla de herramienta de IA (Google Flow), clip UGC real (una madre comprando con sus hijas en un supermercado) y grilla de Meta Ads Library, con el creador en recuadro inferior. Subtítulos: franja roja con texto tipo subtítulo de reseña ('...even bought that...organic berries'). Cortes: varios cortes entre las distintas fuentes de video. Gráficos: ninguno más allá del recuadro PiP y la franja de texto. Locación: sin locación física propia, fondo de estudio con micrófono.</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>Gancho: etiqueta la solución como 'subestimada' y 'fácil', apelando a la curiosidad por un tip de insider. Estructura: problema conocido y frustrante (bugs de Ads Manager) seguido de una solución simple y contraintuitiva (recrear en vez de arreglar). Gatillo: tip práctico e inmediatamente aplicable, de muy bajo esfuerzo para el espectador.</t>
+          <t>Gancho: framing de tendencia emergente ('este nuevo estilo se está apoderando del e-commerce ahora mismo') con emoji de IA. Estructura: identifica la tendencia, explica el mecanismo híbrido (IA + talento real), lista beneficios de producción, muestra prueba (marcas ganando la subasta) y cierra con urgencia ('ya estás atrás'). Gatillo: FOMO de tendencia combinado con un beneficio operativo muy concreto para agencias/marcas (triplicar producción, bajar costos).</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Sí — grabado con celular al aire libre, sin edición ni gráficos adicionales.</t>
+          <t>No — depende de acceso a herramientas de IA de video (Veo/Flow) y de conseguir varios clips reales distintos para mezclar en la edición.</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2053,27 +2053,27 @@
     </row>
     <row r="17" ht="88" customHeight="1">
       <c r="A17" s="2" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Charley T (Disrupter School)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2088,48 +2088,48 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>302</v>
+        <v>8648</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ctthedisrupter/video/7592685803558505742</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7669839443364302110</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Entrevista callejera/de evento en la que el creador aborda a Ben Schreiber, quien dice gastar entre $400.000 y $500.000 mensuales en Meta Ads, y le pide dos tips: usar la métrica "ganancia bruta por transacción" (GPT = AOV − CPA) en vez de solo ROAS, e iterar sobre los creativos ganadores en pequeños pasos (estilo Kaizen).</t>
+          <t>Comparación de las estrategias de marketing de dos marcas de suplementos, Mars Men y Thorne: volumen y formatos de anuncios en Facebook, embudos de venta (quiz vs. página de producto directa) y estrategias de distribución (retail/profesionales de la salud vs. venta directa).</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>Hola, amigo. ¿Cómo te llamás? Hola, soy Ben Schreiber de LaTica Leathers [?] (nombre de marca tal como se transcribió; posiblemente "Latico Leathers"). ¿Cuánto están gastando ahora mismo? En promedio, diría que gastamos entre 400 y 500 mil dólares al mes en anuncios de Meta. Nada, ya sabés, un par de cientos de miles de dólares al mes, un par de millones al año. Sí. Como si nada (casually). Bueno, dejame preguntarte esto: hay mucha gente que no anda tirando casualmente un par de millones al año. Tratando nomás de hacer las cosas bien. ¿Cuál sería un tip o un truco o simplemente algo para alguien que quiere ser mejor mañana? ¿Qué pasa si no llegaron todavía al millón al año y vos estás gastando un par de millones? ¿Qué podrían hacer para mejorar ya mismo? Tengo dos cosas de entrada. Diría que uno, y esto en realidad fue un consejo que vos me diste y que yo agregué a mis columnas de Meta, fue agregar tu GPT, tu ganancia bruta por transacción (gross profit per transaction). Sí, miro eso y me ayudó muchísimo. Es una mejor mirada que el ROAS o el costo por compra. Agreguen eso a sus columnas, y pregúntenle a este tipo si necesitan ayuda para configurarlo. Sí, eso es, por cierto, el AOV (valor promedio de orden) menos el CPA (costo por adquisición). Muy indicativo de cómo está funcionando un anuncio, algo que la mayoría de la gente no mira. Número dos es mirar a tus ganadores, mandárselos a tu equipo de diseño gráfico [?] (transcripto como "graph design team", probable error de "graphic design team") y hacer iteraciones basadas en tu creativo ganador. Tratar de ver si podés ir mejorándolo de a poco y hacerlo todavía mejor. Me encanta eso, viejo. Así que el progreso a través de iteraciones es ir mejorando un poquito. Es Kaizen, un uno por ciento mejor cada día. Eventualmente vas a resolver el problema (crack that nut). Exacto.</t>
+          <t>¿Quién tiene mejor marketing, Mars Men o Thorne? Mars Men está corriendo más de 12 [¿1200?, posible error de transcripción] anuncios activos en Facebook ahora mismo. Eso es una locura total. Están corriendo todos los formatos que te puedas imaginar. Ofertas de 50% de descuento para meter gente en suscripción. Anuncios de antes y después, desgloses de producto, anuncios educativos tipo '8 señales de tal cosa', formato podcast, UGC, ofertas especiales, comparaciones de producto, anuncios explicativos de cómo funciona el producto, qué hace y cuáles son sus beneficios. Y montones de imágenes generadas por IA y básicamente cada tipo de pieza creativa que te puedas imaginar. Thorne solo está corriendo alrededor de 200 anuncios activos en Facebook, con videos, ofertas de suscripción con descuento, UGC, y tomas mayormente centradas en el producto. Se están perdiendo un montón de formatos y ángulos creativos distintos. Mars Men manda a la gente a un funnel de quiz, porque saben que cuanta más información puedan capturar, mejor pueden personalizar la oferta, hacer retargeting, y volver a contactar a la gente para que compre. Una vez que alguien completa ese quiz, lo dirigen a un protocolo personalizado y le dan una oferta de 50% de descuento. Esa página de producto está construida completamente para convertir. Desglosa todo lo que necesitás saber sobre el producto, cómo funciona, los beneficios, y por qué deberías comprarlo. También te incluyen regalos especiales. Porque saben que si pueden aumentar el valor de vida del cliente y lograr una buena relación entre CAC y LTV [?, en el audio 'C to L TV ratio'], se pueden dar el lujo de gastar un montón de plata en anuncios. No es casualidad que Mars Men esté escalando. Thorne manda a la gente directo a la página de producto: tienen algunas fotos de producto, desgloses de producto, dos sabores, y una oferta de suscripción con descuento. Pero les falta mostrar variantes de sabor, les falta educación visual, les faltan montones de imágenes de comparación y desglose de producto, y la mayor parte del sitio es solo texto. Hay muchísimo más que podrían estar haciendo en sus páginas de producto para educar a los clientes, resolver objeciones, y aumentar sus tasas de conversión y sus AOV (ticket promedio). Pero Thorne no se enfoca solo en marketing directo al consumidor. Están aprovechando a profesionales de la salud que recomiendan, prescriben o venden productos Thorne directamente. También están disponibles a través de cientos de retailers distintos. Están en Amazon, están en Fullscript, tienen distribución profesional, usan alianzas de afiliados con otros proveedores de salud, y se asocian con otras marcas que distribuyen y recomiendan sus productos, como Ultrahuman. Esto le permitió a Thorne escalar rápidamente a lo largo de los años a través de la distribución, aprovechando la confianza de los profesionales de la salud, los retailers, los afiliados y otras marcas establecidas. Mars Men solo tiene una presencia de retail más chica, en lugares como GNC. Así que mientras Mars Men construyó un embudo agresivo de respuesta directa, publicidad y conversión, Thorne construyó una red masiva de confianza y distribución. Contame quién pensás que está ganando.</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>Formato "vox pop"/entrevista en vivo en un evento nocturno (bar o fiesta de conferencia), luz ambiente azul/violeta, entrevistador con micrófono pequeño de mano, entrevistado con estética llamativa (pelo teñido azul, barba, camisa blanca). Subtítulos en cajas de fondo celeste/turquesa con texto blanco en mayúscula, por frase (no palabra por palabra). Cámara en mano con leve movimiento, plano medio de dos personas, gente y ruido de fondo visibles.</t>
+          <t>Talking head/selfie con micrófono, superpuesto por croma sobre capturas de pantalla reales de anuncios y páginas de producto de ambas marcas: oferta '50% OFF FOR LIFE' de Mars Men con botellas de producto, desglose de ingredientes de Mars Men, e imagen de 'The Thorne Podcast' con un médico. Formato de comparación lado a lado apoyado en evidencia visual (screenshots), sin gráficos animados propios más allá del recorte por croma.</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Gancho de cifra grande impactante (gasta $400-500 mil dólares AL MES) + formato de entrevista espontánea que genera autenticidad + estructura de "pedile 2 tips a alguien que gasta millones" + gatillo de aspiración y utilidad concreta con una métrica accionable que el espectador puede copiar ya.</t>
+          <t>Gancho de comparación directa entre dos marcas del mismo nicho (formato '¿quién lo hace mejor?') que genera opinión y polémica en los comentarios. Aporta datos concretos (cantidad de anuncios, tipo de funnel, tácticas de retail) que dan autoridad, y cierra pidiendo la opinión del espectador, lo que dispara comentarios y alcance.</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>sí + solo requiere un micrófono de mano/solapa y asistir a eventos de networking para conseguir entrevistados; el valor está en el contenido del entrevistado, no en la producción.</t>
+          <t>sí + solo necesita investigar dos marcas competidoras y grabarse comentando capturas de pantalla de sus anuncios y páginas.</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2145,27 +2145,27 @@
     </row>
     <row r="18" ht="88" customHeight="1">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Venta del servicio</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+        <v>10</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Macie Reed</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2180,48 +2180,48 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>284</v>
+        <v>7591</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maciereedmarketing/video/7665765984271240461</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7666142376062209310</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Macie recuerda a su audiencia que la lista de espera para su Meta Ads Crash Course está abierta, detallando los beneficios de anotarse (acceso anticipado, descuento y un toolkit de Notion gratis).</t>
+          <t>Chase Chappell anuncia una nueva funcion de Meta Ads (Partnership Hub) que permite convertir en anuncios de asociacion paga el contenido que creadores, clientes o influencers ya etiquetaron con la marca, sin necesidad de una produccion nueva.</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Si querés aprender meta ads en 2026 y convertirte en una meta ads manager que pueda ganar una tonelada de dinero y trabajar una fracción del tiempo, este es solo tu recordatorio de que estoy lanzando mi meta ads crash course en la próxima semana más o menos, y mi lista de espera está actualmente abierta y disponible para que te anotes. Entonces cuando te anotás y comprás el Meta Ads Crash Course desde la lista de espera, vas a tener acceso anticipado al lanzamiento del curso, vas a tener un precio con descuento, le voy a meter un super descuento, y voy a sumar contenido extra donde recibís mi meta ads toolkit completamente gratis. Ahora, esto es como un producto viejo que solía ofrecer, no está disponible actualmente en ningún otro lado, así que estoy trayendo de vuelta a un favorito al que todavía nadie más tiene acceso. Así que lo recibís completamente gratis, y básicamente es la Biblia. Es como, si estás en plan 'okay, tengo que entrar y crear una cuenta publicitaria, crear anuncios', simplemente tenés que ir a este, eh, Nash, perdón, Dashboard de Notion, y está todo ahí para vos. Te va a decir exactamente qué hacer, te da inspiración de anuncios, te da swipe files, eh, ideas de hooks, cómo escribir captions convincentes, eh, qué llamados a la acción usar, básicamente todo. Y eso viene junto con mi meta ads crash course, donde voy a estar adentro del Meta Ads Manager guiándote paso a paso exactamente en cómo configurar tu cuenta y tus campañas, y qué hacer y qué realmente no importa tanto al principio, porque meta te tira un montón de boludeces encima. Así que si esto te suena como algo para vos, asegurate de unirte a mi lista de espera. El link para hacerlo está en la parte de arriba de mi perfil, así que andá a hacerlo ahora.</t>
+          <t>Meta Ads acaba de lanzar una de las actualizaciones mas locas para las marcas. Ahora podes correr anuncios con contenido de personas que ya etiquetaron tu producto. Eso significa que si un creador, cliente o influencer alguna vez publico sobre tu marca y te etiqueto, ahora podes convertir ese contenido en un anuncio de asociacion paga (paid partnership ad) al instante. Asi es como funciona: anda a Partnership Hub, hace clic en contenido, y Meta literalmente te va a mostrar las publicaciones que presentaron tu producto en un video o imagen. Ahora podes ver quien lo publico, podes ver si tenes los derechos de uso o no. Y si todavia no tenes los derechos, simplemente haces clic en solicitar directamente al creador, y una vez que lo aprueba, podes lanzar exactamente esa publicacion como un anuncio de asociacion paga dentro del Administrador de Anuncios de Meta. Esto es enorme porque la mayoria de las marcas estan constantemente tratando de crear anuncios nuevos desde cero. Pero ahora podes revisar todo tu historial de contenido etiquetado y convertir publicaciones existentes en anuncios. Publicaciones de clientes, videos de creadores, contenido de influencers, etiquetas de producto, menciones organicas: todo eso se convierte en un potencial anuncio de asociacion paga. Esta es una de las oportunidades creativas mas faciles de aprovechar en Meta ahora mismo. No necesitas esperar una produccion nueva. No necesitas dar briefing a 50 creadores nuevos. No necesitas adivinar que se siente nativo ahora mismo. Podes encontrar contenido que literalmente ya existe, solicitar los derechos y empezar a testear. Las marcas que se muevan mas rapido en esto van a tener una ventaja enorme en volumen creativo, porque el juego en 2027 no es solo tener mejores anuncios, es tener mas angulos, mas formatos, mas creadores y mas contenido. Comenta 'partnership' y te muestro exactamente como funciona la estrategia.</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical en dormitorio con luz cálida anaranjada de fondo, campera de jean, sin mic visible en los frames capturados; segundo y tercer frame muestran otro ángulo con cuadros de fondo (parecen láminas de peces/naturaleza). Subtítulos blancos simples quemados en el video. Formato promocional directo sin gráficos de apoyo adicionales ni cortes de escena marcados en los frames vistos.</t>
+          <t>Formato de superposicion: grabacion de pantalla del Administrador de Anuncios de Meta (Partnership Hub, buscador de productos, estado de elegibilidad del contenido) ocupando la mitad superior, con Chase hablando a camara en la mitad inferior con microfono de podcast sobre fondo liso. Se agregan anotaciones a mano en rojo (circulos y subrayados) sobre la interfaz para senalar donde hacer clic. Un frame usa tipografia grande sobre fondo de puntos con texto tachado ('New Shoot', 'Brief 50 Creators') para reforzar el mensaje hablado.</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>Gancho: identificación directa con la audiencia objetivo ('si querés aprender meta ads y ganar mucho dinero trabajando poco'). Estructura: oferta clara con beneficios listados uno a uno (acceso anticipado, descuento, bonus gratis). Gatillo: urgencia y escasez ('lanzo la próxima semana', 'nadie más tiene acceso a esto todavía'), apalancando el interés generado por los episodios educativos previos de la serie.</t>
+          <t>Gancho de urgencia/novedad ('Meta ads just dropped... craziest updates'); estructura tutorial de 'asi funciona' paso a paso que da valor inmediato; gatillo de oportunidad de bajo esfuerzo ('lowest hanging creative opportunity') mas urgencia competitiva (quien se mueve mas rapido gana volumen) y CTA de comentario para generar leads.</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: es un video de venta simple, solo cámara y buena luz ambiente, sin producción adicional.</t>
+          <t>si, solo necesita una cuenta de Meta Ads Manager, grabacion de pantalla gratuita y un microfono basico.</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
     </row>
     <row r="19" ht="88" customHeight="1">
       <c r="A19" s="2" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Dara Denney</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2272,48 +2272,48 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>250</v>
+        <v>7101</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7665463418513673479</t>
+          <t>https://www.tiktok.com/@daradenney/video/7650514495403543838</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde recomienda usar funciones de investigación profunda de IA (Claude, Gemini, GPT, Perplexity, Manus) para escanear Reddit, comentarios de YouTube y bibliotecas de anuncios de competidores y así nunca quedarse sin ángulos de anuncios nuevos.</t>
+          <t>Recapitulación desde el evento Conversations 2026 de Meta en Londres, donde una estratega creativa explica el lanzamiento de los agentes de IA para negocios de WhatsApp/Meta, que pueden vender y cerrar ventas directamente en el chat -incluso agente a agente- y cómo eso cambia el rol de la publicidad.</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>[el transcript comienza abruptamente, posible corte al inicio del clip, ver nota] ...ángulos, vas a tener que inventar ángulos nuevos cada semana. Normalmente vas a poder encontrar una porción importante de ángulos de anuncios solo con hacer este ejercicio muy simple. Y honestamente, hoy en día, algunas de las mejores formas de encontrar ángulos es usar investigación con IA. Podés ir a Claude, a Gemini, a GPT, Perplexity [?] ("Proplexity" en el original), Manus, y cada uno de estos modelos típicamente tiene una función de investigación profunda (deep research) o alguna variación, que te permite rastrear la web en busca de información específica. Y le podés preguntar: "mirá, tengo este producto. Este es mi nivel de conciencia (awareness level). Este es mi deseo. Esta es mi sofisticación de mercado. Me estoy quedando sin ángulos de anuncios. Estos son los distintos ángulos de anuncios que ya encontré. Quiero que investigues en Reddit, comentarios de YouTube, bibliotecas de anuncios de la competencia. Y a partir de eso, necesito que me ayudes a armar una lista de ángulos de anuncios completamente nuevos que todavía no haya probado."</t>
+          <t>No quiero sonar alarmista, pero en el futuro muy cercano no le vamos a estar vendiendo solo a humanos. Insertá el chiste. Le vamos a estar vendiendo a agentes. Entonces, si sos estratega creativo o dueño de un negocio, y estás viendo esta noticia que salió de Londres la semana pasada del evento Conversations de Meta, y estás pensando 'ah, esto es solo un tema de WhatsApp'. Incorrecto. Meta acaba de lanzar sus agentes de IA para negocios, que también van a llegar pronto a Instagram. Esto no va a ser solo un chat que responde preguntas frecuentes o un mini competidor de chat: puede recomendar productos de tu catálogo, reservar turnos, e incluso cerrar la venta, y hasta comunicarse por notas de voz. Las aerolíneas ya la están rompiendo con esta estrategia. Marcas de consumo masivo, marcas de indumentaria. Pero lo que más me llamó la atención, especialmente como estadounidense, donde admito que muchos de mis clientes hoy no están usando anuncios de WhatsApp, fue cuando el director de marketing de Meta subió al escenario y dijo que muchas de las conversaciones que están pasando en WhatsApp con los clientes no son solo de agente a cliente. Son de agente a agente. Dio un ejemplo buenísimo de una empresa de alquiler de autos, donde notaron que los agentes de las personas están efectivamente cerrando la venta final con los agentes de IA de negocios de Meta. Como alguien que hace más de una década que hace publicidad en Meta, esto me parece verdaderamente fascinante, porque el librito de jugadas solía ser: mostrás el anuncio, vas a la landing page, cerrás la venta. Pero ahora, cada vez más, vamos a empezar a ver que pasa de anuncio a chat a venta, y también vamos a tener la venta y compra real de esos productos a través de todos nuestros agentes. Entonces, como estratega creativa, así es como me estoy preparando para esto: tengo un interés recién descubierto en los anuncios de clic para enviar mensaje. Los voy a estar estudiando en serio las próximas semanas, para entender si hay una diferencia entre el creador ganador para anuncios de clic a mensaje versus el librito de jugadas habitual del negocio. Y también voy a estar viendo cómo se manejan esas conversaciones por parte de los agentes de IA de Meta. Tengo muchísima curiosidad por ver qué marcas se mueven primero acá. Creo que hay una ventaja competitiva enorme en este momento. Y para la gente que tiene negocios de infoproductos como yo, pienso: esto es buenísimo, porque una gran parte de la venta pasa por el DM. Y sobre todo, como estratega creativa, realmente me pregunto qué va a pasar ahora con el brief. ¿Cuál va a ser el rol real de la pieza creativa del anuncio de acá en adelante? Si el embudo ahora es anuncio-chat-venta, ¿nuestra estrategia creativa va a ir todavía más hacia la parte alta del embudo? Que ha sido la tendencia en los últimos meses. Bueno, un montón de gracias a Meta por invitarme a Conversations la semana pasada. La onda fue muy distinta a la del Performance Summit. Y tengo que decir que salí de ese evento pensando muchísimo sobre el futuro de la publicidad. Y, la verdad, no puedo esperar, pero tengo mucha curiosidad por escuchar qué piensan ustedes de todo esto.</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto, mismo living/oficina, sin gráficos superpuestos en los frames revisados (1, 3 y 5) — solo subtítulos bold blancos sobre el video. Formato más simple y directo, sin cortes a pantallas ni inserts visibles en esos frames.</t>
+          <t>Mezcla de b-roll grabado en vivo en el evento Conversations 2026 de Meta en Londres (mujer de pie frente a una pantalla/backdrop del evento con micrófono de mano tipo entrevista) con selfie video grabado en otro momento/lugar (interior tipo living/oficina, luz natural), misma protagonista (pelo pelirrojo, blusa rosa satinada, chaleco verde oliva, aros). No se observan subtítulos incrustados en los frames muestreados.</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Gancho directo de solución a un problema recurrente (quedarse sin ángulos); estructura breve de tip único y accionable (usar deep research de varias IAs); gatillo de utilidad inmediata y bajo esfuerzo de consumo, video de solo 54 segundos.</t>
+          <t>Gancho: afirmación provocadora sobre el futuro ('le vamos a vender a agentes de IA, no a humanos') que genera intriga y hasta un poco de alarma. Estructura: contexto del anuncio de Meta, ejemplo concreto (alquiler de autos con venta agente-a-agente), y plan de acción personal de la creadora. Gatillo: primicia/exclusividad (asistió al evento real de Meta), autoridad (más de una década en pauta de Meta), curiosidad por una tendencia disruptiva; cierra con pregunta abierta para generar comentarios.</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>sí, es el más simple del lote: solo cámara y un tip hablado, sin gráficos ni edición extra.</t>
+          <t>no + depende de tener acceso a un evento exclusivo de la industria para conseguir la primicia informativa que arma el gancho, aunque la grabación en sí (selfie) es de bajo costo.</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2329,15 +2329,15 @@
     </row>
     <row r="20" ht="88" customHeight="1">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2364,33 +2364,33 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>11700</v>
+        <v>7051</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7636037201276505374</t>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7631323413780385038</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell compara las estrategias de marketing de dos marcas de ropa deportiva, Rhone y Ten Thousand, analizando sus embudos de venta, presencia en retail y enfoque creativo (rendimiento a corto plazo vs. construcción de marca a largo plazo).</t>
+          <t>Caleb prueba ChatGPT Image 2.0 recien lanzado y, en una seguidilla rapida de ejemplos, muestra como usarlo para anuncios: clonar un anuncio existente con su propio producto, cambiar texto, poner a una influencer en distintas escenas, generar headshots profesionales y crear una infografia compleja con busqueda web integrada.</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>¿De quién es mejor el marketing, de Rhone o de Ten Thousand? Ambas marcas corren alrededor de 120 anuncios en Meta. Así que esto no se trata de volumen, se trata de cómo convierten la atención en ingresos. Rhone manda el tráfico directo a la página de producto. Ten Thousand manda el tráfico a la página de colección. Rhone elige un camino más rápido, con mayor intención y conversiones más directas. Pero acá es donde se pone interesante: el flujo de colección de Ten Thousand no es una debilidad, es una jugada de marca. Están dejando que los clientes exploren múltiples productos y múltiples puntos de entrada. Esto tiene más chances de encontrar el ajuste perfecto, y de hecho puede aumentar su AOV [ticket promedio] si la experiencia está bien calibrada. Ahora sumemos el retail: Rhone tiene más de 20 tiendas. Ten Thousand tiene cero. Rhone tiene presencia física. La confianza se construye offline, lo cual sin dudas ayuda a las conversiones online. Pero Ten Thousand es totalmente digital, lo que significa que cada dólar está obligado a rendir. Sin red de contención del retail. Es un juego distinto, y definitivamente es una presión distinta. Ahora miremos la estrategia creativa: Rhone apuesta a su rendimiento con UGC, ofertas de respuesta directa, conversiones rápidas. Ten Thousand apuesta a su marca con visuales prolijos, posicionamiento premium, un marketing menos agresivo y una percepción más controlada de quiénes son. Entonces, ¿qué está pasando realmente acá? Rhone está optimizando para ingresos inmediatos. Ten Thousand está optimizando para valor de marca a largo plazo. Entonces, ¿quién creen que está ganando? Cuéntenme abajo.</t>
+          <t>A Nano Banana lo acaban de destronar oficialmente. ChatGPT Image 2.0 acaba de lanzarse y algunos de estos casos de uso son una locura. Asi es como podes usarlo para anuncios en redes sociales. Bueno, primero le di esta imagen de un anuncio que vi por ahi de un suplemento de colageno. Le di este producto ficticio de un suplemento de colageno y le dije que recreara el anuncio con mi producto. Miren que perfecto tradujo ese texto a esta imagen. Ahora, ¿y si quiero cambiar la palabra 'works' por 'slaps'? Hecho. O este anuncio con mi version del producto hecho con mi oferta. ¿O que tal si quiero una influencer usando esta gorra y sosteniendo esta mezcla de electrolitos? ¡Listo! ¿Y si la quiero sentada en su sillon? ¿O cepillandose los dientes? ¿O acostada en la cama? ¿O que tal si la quiero mostrar en esta escena dentro de un auto? Hecho. O puedo subir ocho fotos mias y que me genere una foto de perfil profesional. O una foto lifestyle. ¿Pero y si quiero estar usando este buzo de Sub Pop que uso todo el tiempo? Hecho. ¿Si quiero ser invitado en un podcast? Hecho. ¿Y si me gusta este anuncio pero quiero cambiar el texto del letterboard? Hecho. ¿O si me gusta este anuncio pero quiero que sea mi producto? ¿Como esta gorra? Hecho. Jaja, ¿o si quiero mostrar una foto de unboxing de este producto? Hecho. Este nuevo modelo de imagenes realmente piensa, lo que significa que le podes dar un prompt muy generico y te va a dar un resultado realmente bueno. Y ni hablar de que puede buscar en internet para conseguir mas contexto sobre lo que le estas pidiendo. Como ahora mismo, le estoy pidiendo que cree una infografia compleja explicando los anuncios de Meta y la actualizacion Andromeda [?] y como funciona en conjunto con GEM y Lattice [?]. Y pueden ver que esta pensando y buscando en internet informacion sobre estos temas. Y aca esta. Esto realmente esta bastante solido. ¿Que opinan? ¿Esto tambien es mejor que Nano Banana? Cuentenme en los comentarios.</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>Talking head en recuadro pequeño abajo, clip de video de marca con overlay de texto (escena de tren/subte con logo cruzado y crédito 'Creative Director &amp; Co-Founder'), captura de pantalla del carrito de compra de Ten Thousand con anotación roja, captura de comentarios de Instagram de la cuenta de Rhone con recuadros rojos resaltando respuestas, campera oscura.</t>
+          <t>Mezcla de talking head en primer plano (gorra, anteojos, luz roja/verde de fondo) con capturas de un monitor de escritorio y de un celular mostrando la interfaz de ChatGPT generando imagenes en tiempo real. Banner de texto rojo fijo con el titular ('CHATGPT IMAGE 2 JUST DROPPED AND ITS BETTER THAN NANO BANANA') en la parte superior de casi todos los frames, subtitulos dinamicos abajo. Formato demo tipo 'mira lo que hace esta IA' con ritmo rapido de ejemplos.</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>Formato de comparación cabeza a cabeza que invita a 'elegir un bando'; estructura por variable (tráfico, retail, creatividad) fácil de seguir; conclusión con dos filosofías claras y opuestas (ingresos inmediatos vs. valor de marca a largo plazo) que deja algo memorable; cierre con pregunta de opinión.</t>
+          <t>Gancho de comparacion/controversia con un producto viral ya conocido ('¿mejor que Nano Banana?'); estructura de rafaga de ejemplos con 'hecho/listo' repetido que genera ritmo y sorpresa creciente; gatillo de pregunta final que invita a comentar/debatir, mas la novedad de la herramienta recien lanzada.</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>sí — solo necesita capturas de pantalla y clips públicos de las marcas, sin producción propia cara.</t>
+          <t>sí, solo necesita una suscripcion a la herramienta de IA y grabacion de pantalla/webcam, sin edicion compleja.</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2421,27 +2421,27 @@
     </row>
     <row r="21" ht="88" customHeight="1">
       <c r="A21" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Caleb Kruse (Mr. Paid Social)</t>
+          <t>Mitch Barham (Beardpreneur)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2456,48 +2456,48 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>11400</v>
+        <v>5708</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.paidsocial/video/7657288764053622029</t>
+          <t>https://www.tiktok.com/@beardpreneur/video/7628243140423470349</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Caleb muestra como, con una skill personalizada de Claude que conecta los MCP de Airtable y Meta Ads, le pidio a Claude que generara y lanzara 500 anuncios (50 creativos x 10 variantes de copy) a su cuenta de Meta en cuestion de minutos, algo que a mano le hubiera llevado una semana.</t>
+          <t>Fragmento breve, con pinta de recorte de un podcast o transmision en vivo, donde Mitch da su opinion sobre la frecuencia publicitaria: dice que casi no le importa y que todo se reduce a los resultados; si un ad set 'evergreen' se agota, prefiere duplicarlo y refrescar la audiencia antes que matar la creatividad.</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>Dejame mostrarte como podes crear 500 anuncios en cinco minutos usando Claude y Airtable. Ya no hay ninguna razon para que sigas usando el Administrador de anuncios para armar tus anuncios. El ingrediente secreto de todo esto es una skill personalizada que arme, que conecta el MCP oficial de Airtable con el MCP de Meta Ads. Y quedate hasta el final porque te voy a mostrar donde conseguir esa skill al final del video. Paso 1: vas a conectar el MCP de Airtable a Claude. Paso 2: vas a conectar el MCP oficial de Meta a Claude agarrando este link y agregandolo como conector MCP personalizado dentro de Claude. Paso 3: vas a tomar mi skill personalizada y agregarla como skill personalizada de Claude dentro de Claude. ¡Ahora literalmente le podes pedir a Claude que haga cientos de anuncios en tu cuenta de anuncios! Hagamos una demo rapida. Le voy a pedir a Claude que me haga 500 anuncios nuevos promocionando mi comunidad de Skool. Primero voy a subir 45 anuncios de imagen y 5 anuncios de video a la Biblioteca Creativa de Facebook. Ahora Claude puede usar el MCP de Meta para traer todos esos assets a mi base de Airtable. Ahora le voy a pedir a Claude que me escriba 10 variaciones de copy de anuncio para cada uno de esos anuncios usando mis 10 frameworks de copy favoritos. Entonces 50 creativos de anuncio por 10 variaciones de copy da 500 anuncios en total. Ahora le pido a Claude que arme todo esto en una base de Airtable para que yo la revise, y podes ver aca que estan todos en mi Airtable con todas las variantes de copy, el creativo seleccionado, y toda la configuracion preconfigurada. ¡Si! Esto significa que no tenes que desactivar manualmente todas las mejoras creativas automaticas. Ahora lo unico que tengo que hacer es pedirle a Claude que lance estos anuncios a mi cuenta en grupos de 10, y ahi va, despues de unos minutos tengo todos esos anuncios en mi cuenta de anuncios de Meta. Y si hubiera querido armar todos estos anuncios manualmente usando el Administrador de anuncios, probablemente me hubiera llevado una semana entera. [?] Conseguí mi skill, que le da un cerebro completo a tu Claude para que todo este sistema funcione correctamente. Comenta 'airtable' y te mando el link.</t>
+          <t>La frecuencia. Me importa y no me importa la frecuencia. Aun asi, o sea, volvemos a lo mismo. Es como, me importa pero no me importa. Es como una de las ultimas cosas que voy a mirar. La verdad es que todo se reduce a los resultados. Tipo, che, esto se esta cayendo. No esta funcionando. Estos anuncios la estaban rompiendo. ¿Okay? Dependiendo de la industria, del nicho, lo que hay que hacer es duplicar y refrescar la audiencia. Literalmente hice eso con un conjunto de anuncios de un fotografo de bodas el otro dia, donde era como, esto siempre funciona. Son evergreen, siempre funcionan. Entonces tipo, bueno, duplica el conjunto de anuncios y reinicialo, y veamos que pasa. Y por lo general vuelve a agarrar ritmo justo donde habia quedado.</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>Pantalla dividida: mitad superior alterna capturas de documentacion tecnica del sistema (tablas, principios de funcionamiento) y de la interfaz de Airtable con los anuncios generados; mitad inferior es webcam del creador con gorra, en cuarto con luces de colores. Subtitulos dinamicos, cortes frecuentes entre demo de pantalla y cara para mostrar el proceso paso a paso.</t>
+          <t>Arranca con un pequeno recuadro de video de esquinas redondeadas sobre un fondo animado de particulas/glow (plantilla tipo 'highlight' de clip automatico), despues corta a la imagen de camara web a pantalla completa. El poster de fondo ('NOBODY CARES, WORK HARDER') aparece espejado/invertido en varios frames, senal de grabacion sin corregir el volteo de la webcam. Subtitulos palabra por palabra, sin cortes de pantalla ni graficos: es talking head puro, con pinta de recorte de un video mas largo.</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>Gancho de resultado extremo y cuantificado ('500 anuncios en 5 minutos'); estructura clara en pasos numerados (1, 2, 3) reforzada con demo en vivo como prueba; gatillo de reciprocidad (comentar para recibir la skill gratis) apalancado en el dolor de armar anuncios uno por uno a mano.</t>
+          <t>Gancho de opinion contraintuitiva sobre un tema tecnico muy discutido en el nicho (la frecuencia del anuncio); estructura breve de anecdota real y concreta (el fotografo de bodas) que aporta credibilidad; gatillo de autoridad por experiencia practica, en un clip corto (36s) facil de consumir entero.</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
-          <t>sí, el video en si es barato de grabar, aunque construir la demo (conectar MCPs de Airtable y Meta) exige conocimiento tecnico previo.</t>
+          <t>sí, es literalmente una camara fija sin edicion ni graficos, el formato mas barato del lote (ideal para recortar contenido largo como un podcast).</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2513,27 +2513,27 @@
     </row>
     <row r="22" ht="88" customHeight="1">
       <c r="A22" s="2" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2548,33 +2548,33 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>7591</v>
+        <v>5173</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7666142376062209310</t>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7664714637417532685</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell anuncia una nueva funcion de Meta Ads (Partnership Hub) que permite convertir en anuncios de asociacion paga el contenido que creadores, clientes o influencers ya etiquetaron con la marca, sin necesidad de una produccion nueva.</t>
+          <t>Caleb cuenta como usa una Mac Mini corriendo Claude Code para automatizar buena parte de su negocio: una app de iPhone controlada por voz, campanas de email, un dashboard de contenido, scraping de anuncios/contenido viral hacia Airtable y el lanzamiento de una promo de aniversario en su cuenta de Meta, todo gestionado desde la cama a las 6am.</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Meta Ads acaba de lanzar una de las actualizaciones mas locas para las marcas. Ahora podes correr anuncios con contenido de personas que ya etiquetaron tu producto. Eso significa que si un creador, cliente o influencer alguna vez publico sobre tu marca y te etiqueto, ahora podes convertir ese contenido en un anuncio de asociacion paga (paid partnership ad) al instante. Asi es como funciona: anda a Partnership Hub, hace clic en contenido, y Meta literalmente te va a mostrar las publicaciones que presentaron tu producto en un video o imagen. Ahora podes ver quien lo publico, podes ver si tenes los derechos de uso o no. Y si todavia no tenes los derechos, simplemente haces clic en solicitar directamente al creador, y una vez que lo aprueba, podes lanzar exactamente esa publicacion como un anuncio de asociacion paga dentro del Administrador de Anuncios de Meta. Esto es enorme porque la mayoria de las marcas estan constantemente tratando de crear anuncios nuevos desde cero. Pero ahora podes revisar todo tu historial de contenido etiquetado y convertir publicaciones existentes en anuncios. Publicaciones de clientes, videos de creadores, contenido de influencers, etiquetas de producto, menciones organicas: todo eso se convierte en un potencial anuncio de asociacion paga. Esta es una de las oportunidades creativas mas faciles de aprovechar en Meta ahora mismo. No necesitas esperar una produccion nueva. No necesitas dar briefing a 50 creadores nuevos. No necesitas adivinar que se siente nativo ahora mismo. Podes encontrar contenido que literalmente ya existe, solicitar los derechos y empezar a testear. Las marcas que se muevan mas rapido en esto van a tener una ventaja enorme en volumen creativo, porque el juego en 2027 no es solo tener mejores anuncios, es tener mas angulos, mas formatos, mas creadores y mas contenido. Comenta 'partnership' y te muestro exactamente como funciona la estrategia.</t>
+          <t>Pense que todo el hype de comprar una Mac Mini para correr tus agentes de IA era una pavada, hasta que compre una. Me di cuenta de que podes hacer un monton de cosas con ella. Te garantizo que el 99% de los tech bros de IA la estan usando solo para correr cosas como OpenClaw [?] o Hermes, pero no creo que ni siquiera haga falta meterse con eso. Probablemente el caso de uso mas loco que le estoy dando ahora mismo es que hice que Claude Code me construyera una app que me permite controlarlo con mi voz desde mi iPhone, desde cualquier lugar. Literalmente la estoy construyendo ahora mismo usando Xcode y uso esta app en mi iPhone. Si algo se rompe, le puedo escribir a Claude Code desde la app para que arregle la app. Automaticamente sube la app a mi telefono por mi. Tengo todo un entorno de desarrollo sin siquiera tener que saber lo que estoy haciendo, porque todo corre siempre en esta Mac Mini. Puedo estar literalmente en cualquier parte del mundo y darle tareas para que haga. Esta manana le hice armar toda una campana de lanzamiento por email para la venta de aniversario de mi comunidad de Skool que estoy corriendo ahora mismo, y literalmente entro a mi proveedor de email Flodesk y controlo el navegador para armarme los flujos de email, segmentarlos, y enviarlos en el orden en que yo queria que se enviaran. Tengo otra instancia corriendo un dashboard que rastrea todo mi contenido hacia una base de datos tipo biblioteca gigante y me da insights todos los dias. A lo largo del dia, la tengo peinando mi Instagram en busca de piezas de contenido organico viral y anuncios que ve por ahi. Y tira todos esos anuncios a esta base de Airtable donde tiene un gasto estimado y los likes. Tambien tira todas esas piezas de contenido organico, cuantas vistas consiguio cada contenido, junto con la transcripcion completa y una explicacion de por que se volvio viral en primer lugar. [?] Con esta Mac Mini arme esta venta de aniversario en mi cuenta de anuncios de Meta, que ya tiene una venta registrada hoy. Hice esto desde mi cama a las 6 de la manana. Hay muchisimos mas casos de uso para esto, pero lo unico que puedo decir es que tener esta configuracion ahora me permite basicamente tener una VA que controla todo mi negocio de punta a punta. Tiene contexto completo de todo lo que hice con ella alguna vez. Se pone mas inteligente cuanto mas la uso. Les voy a mostrar a la gente como arme esto en mi comunidad de Skool, que esta con 70% de descuento ahora mismo por mi aniversario. Asi que si queres el link para eso, comenta 'skool' y te lo mando.</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>Formato de superposicion: grabacion de pantalla del Administrador de Anuncios de Meta (Partnership Hub, buscador de productos, estado de elegibilidad del contenido) ocupando la mitad superior, con Chase hablando a camara en la mitad inferior con microfono de podcast sobre fondo liso. Se agregan anotaciones a mano en rojo (circulos y subrayados) sobre la interfaz para senalar donde hacer clic. Un frame usa tipografia grande sobre fondo de puntos con texto tachado ('New Shoot', 'Brief 50 Creators') para reforzar el mensaje hablado.</t>
+          <t>Talking head en primer plano con iluminacion de colores (violeta/rosa) y planta de fondo, subtitulos dinamicos quemados, intercalado con capturas de pantalla de un dashboard/Airtable mostrando datos reales, incluyendo un frame donde un dedo senala la pantalla mientras explica por que un contenido se volvio viral. Ritmo tipo 'day in the life' con pruebas visuales de cada automatizacion mencionada.</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>Gancho de urgencia/novedad ('Meta ads just dropped... craziest updates'); estructura tutorial de 'asi funciona' paso a paso que da valor inmediato; gatillo de oportunidad de bajo esfuerzo ('lowest hanging creative opportunity') mas urgencia competitiva (quien se mueve mas rapido gana volumen) y CTA de comentario para generar leads.</t>
+          <t>Gancho de escepticismo convertido en creencia ('pense que era una pavada hasta que...'); estructura tipo 'day in the life' que encadena casos de uso cada vez mas sorprendentes; gatillo de urgencia y oferta (descuento de aniversario del 70%) mas CTA claro para comentar y recibir el link.</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>si, solo necesita una cuenta de Meta Ads Manager, grabacion de pantalla gratuita y un microfono basico.</t>
+          <t>no del todo, requiere tener ya armado un ecosistema de negocio (Mac Mini, Airtable, Skool, automatizaciones) para poder mostrar casos de uso reales, aunque la grabacion en si sea barata.</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
     </row>
     <row r="23" ht="88" customHeight="1">
       <c r="A23" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Caleb Kruse (Mr. Paid Social)</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2640,33 +2640,33 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="J23" s="6" t="n">
-        <v>7051</v>
+        <v>5119</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.paidsocial/video/7631323413780385038</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7664540572052442390</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Caleb prueba ChatGPT Image 2.0 recien lanzado y, en una seguidilla rapida de ejemplos, muestra como usarlo para anuncios: clonar un anuncio existente con su propio producto, cambiar texto, poner a una influencer en distintas escenas, generar headshots profesionales y crear una infografia compleja con busqueda web integrada.</t>
+          <t>Video corto que explica que la razón número uno por la que fallan los anuncios de Meta no es el algoritmo sino una oferta que no está lo suficientemente diferenciada frente a alternativas más baratas como Amazon.</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>A Nano Banana lo acaban de destronar oficialmente. ChatGPT Image 2.0 acaba de lanzarse y algunos de estos casos de uso son una locura. Asi es como podes usarlo para anuncios en redes sociales. Bueno, primero le di esta imagen de un anuncio que vi por ahi de un suplemento de colageno. Le di este producto ficticio de un suplemento de colageno y le dije que recreara el anuncio con mi producto. Miren que perfecto tradujo ese texto a esta imagen. Ahora, ¿y si quiero cambiar la palabra 'works' por 'slaps'? Hecho. O este anuncio con mi version del producto hecho con mi oferta. ¿O que tal si quiero una influencer usando esta gorra y sosteniendo esta mezcla de electrolitos? ¡Listo! ¿Y si la quiero sentada en su sillon? ¿O cepillandose los dientes? ¿O acostada en la cama? ¿O que tal si la quiero mostrar en esta escena dentro de un auto? Hecho. O puedo subir ocho fotos mias y que me genere una foto de perfil profesional. O una foto lifestyle. ¿Pero y si quiero estar usando este buzo de Sub Pop que uso todo el tiempo? Hecho. ¿Si quiero ser invitado en un podcast? Hecho. ¿Y si me gusta este anuncio pero quiero cambiar el texto del letterboard? Hecho. ¿O si me gusta este anuncio pero quiero que sea mi producto? ¿Como esta gorra? Hecho. Jaja, ¿o si quiero mostrar una foto de unboxing de este producto? Hecho. Este nuevo modelo de imagenes realmente piensa, lo que significa que le podes dar un prompt muy generico y te va a dar un resultado realmente bueno. Y ni hablar de que puede buscar en internet para conseguir mas contexto sobre lo que le estas pidiendo. Como ahora mismo, le estoy pidiendo que cree una infografia compleja explicando los anuncios de Meta y la actualizacion Andromeda [?] y como funciona en conjunto con GEM y Lattice [?]. Y pueden ver que esta pensando y buscando en internet informacion sobre estos temas. Y aca esta. Esto realmente esta bastante solido. ¿Que opinan? ¿Esto tambien es mejor que Nano Banana? Cuentenme en los comentarios.</t>
+          <t>¿Cuál es la razón número uno por la que fallan los anuncios de Meta? La razón número uno por la que fallan los anuncios de Meta es que la oferta no es lo suficientemente buena. Y lo que quiero decir específicamente con eso es que la gente no quiere comprar tu producto al precio al que lo estás ofreciendo. Tuve tantas conversaciones con gente que está corriendo anuncios de Meta y me dice 'ay, mis anuncios no venden', y yo les digo 'esperá, dame dos segundos'. Y ahí entrás a Amazon, buscás su producto, y decís 'mirá, tu mismo producto, 20% más barato, con envío para el día siguiente'. Por eso no está funcionando: tenés que tener algo diferenciado. Y ellos dicen 'ah, bueno'. Es como, sí: construí una marca, o inventá algo genuinamente único, o hacé publicidad solo a nivel local y dominá ese mercado. Tenés que tener un diferencial, si no, no va a funcionar.</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>Mezcla de talking head en primer plano (gorra, anteojos, luz roja/verde de fondo) con capturas de un monitor de escritorio y de un celular mostrando la interfaz de ChatGPT generando imagenes en tiempo real. Banner de texto rojo fijo con el titular ('CHATGPT IMAGE 2 JUST DROPPED AND ITS BETTER THAN NANO BANANA') en la parte superior de casi todos los frames, subtitulos dinamicos abajo. Formato demo tipo 'mira lo que hace esta IA' con ritmo rapido de ejemplos.</t>
+          <t>Escena grabada en exteriores junto al mar (aparenta ser una terraza o cubierta de un evento tipo conferencia, con almohadones a rayas naranjas y vista a una marina/montañas), con un hombre (pelo oscuro, polo blanco) conversando/hablando a cámara en distintos primeros planos, gesticulando con la mano cerca de la cabeza. Subtítulos incrustados sincronizados con el guion ('that Meta Ads fail', 'aren't selling', 'It's like yeah.'), sin gráficos adicionales.</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>Gancho de comparacion/controversia con un producto viral ya conocido ('¿mejor que Nano Banana?'); estructura de rafaga de ejemplos con 'hecho/listo' repetido que genera ritmo y sorpresa creciente; gatillo de pregunta final que invita a comentar/debatir, mas la novedad de la herramienta recien lanzada.</t>
+          <t>Gancho: pregunta directa y muy buscada ('¿cuál es la razón número uno por la que fallan los anuncios de Meta?'). Estructura: respuesta directa, ejemplo conversacional relatable (comparación con Amazon), y consejos prácticos de diferenciación. Gatillo: utilidad práctica inmediata + autoridad (experiencia con clientes reales) + desmiente una creencia común ('no es el algoritmo').</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>sí, solo necesita una suscripcion a la herramienta de IA y grabacion de pantalla/webcam, sin edicion compleja.</t>
+          <t>sí + es solo una conversación/opinión grabada en cualquier lugar con luz natural y subtítulos automáticos, cero edición compleja.</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
     </row>
     <row r="24" ht="88" customHeight="1">
       <c r="A24" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Mitch Barham (Beardpreneur)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2732,48 +2732,48 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="J24" s="6" t="n">
-        <v>5119</v>
+        <v>4859</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7664540572052442390</t>
+          <t>https://www.tiktok.com/@beardpreneur/video/7652781295931624718</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Video corto que explica que la razón número uno por la que fallan los anuncios de Meta no es el algoritmo sino una oferta que no está lo suficientemente diferenciada frente a alternativas más baratas como Amazon.</t>
+          <t>Mitch explica por que, con Advantage+ dominando la entrega de anuncios en Meta, la segmentacion manual ya casi no importa: el verdadero 'targeting' ahora lo hace la creatividad (copy, imagen, video), al punto de poder nombrar explicitamente a la audiencia en la primera linea del anuncio.</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>¿Cuál es la razón número uno por la que fallan los anuncios de Meta? La razón número uno por la que fallan los anuncios de Meta es que la oferta no es lo suficientemente buena. Y lo que quiero decir específicamente con eso es que la gente no quiere comprar tu producto al precio al que lo estás ofreciendo. Tuve tantas conversaciones con gente que está corriendo anuncios de Meta y me dice 'ay, mis anuncios no venden', y yo les digo 'esperá, dame dos segundos'. Y ahí entrás a Amazon, buscás su producto, y decís 'mirá, tu mismo producto, 20% más barato, con envío para el día siguiente'. Por eso no está funcionando: tenés que tener algo diferenciado. Y ellos dicen 'ah, bueno'. Es como, sí: construí una marca, o inventá algo genuinamente único, o hacé publicidad solo a nivel local y dominá ese mercado. Tenés que tener un diferencial, si no, no va a funcionar.</t>
+          <t>Mira, la cosa es que tu segmentacion ya no importa. La creatividad lo hace todo. Y se que eso confunde a todo el mundo porque piensan '¿que carajo?'. Y te lo voy a explicar. Mira, en los ultimos seis meses, en realidad como 7, 8 meses, el... el algoritmo de Meta, todos tus anuncios, cambio drasticamente con todo el mundo siendo empujado hacia campanas de ventas Advantage Plus. Advantage Plus leads, campanas, tus audiencias Advantage Plus. No me importa si volves a intereses manuales, igual estas dentro de Advantage Plus. Va a salirse de cualquier parametro que le des. Ni siquiera lo usa realmente como una sugerencia para tu creatividad. Tu copy de anuncio, tu imagen y tus videos son los que hacen la segmentacion. Podes llegar incluso a nombrarlos explicitamente en la primera linea. Entonces, digamos que vendes productos para mascotas. 'Hola, duenos de mascotas, ¿tenes una mascota?'. Todos esos son creativos de apertura y ganchos de apertura que el sistema lee, conoce, interpreta, y despues le sirve tu anuncio a la gente correcta. Es alucinante. Pero esto es lo que hacemos con todos nuestros clientes y la estamos rompiendo por completo.</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>Escena grabada en exteriores junto al mar (aparenta ser una terraza o cubierta de un evento tipo conferencia, con almohadones a rayas naranjas y vista a una marina/montañas), con un hombre (pelo oscuro, polo blanco) conversando/hablando a cámara en distintos primeros planos, gesticulando con la mano cerca de la cabeza. Subtítulos incrustados sincronizados con el guion ('that Meta Ads fail', 'aren't selling', 'It's like yeah.'), sin gráficos adicionales.</t>
+          <t>Talking head a media distancia (se ve el torso, gesticula con las manos), con un poster de fondo con frases motivacionales en letras grandes que aparece espejado/invertido en algunos frames (senal de flip horizontal no corregido). Titular gancho en texto blanco sobre fondo negro en el primer frame ('Ads On Facebook Failing? This is The Cause and Fix'), subtitulos dinamicos con palabras clave resaltadas en rosa/magenta. Toma continua sin cortes a pantalla ni graficos.</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>Gancho: pregunta directa y muy buscada ('¿cuál es la razón número uno por la que fallan los anuncios de Meta?'). Estructura: respuesta directa, ejemplo conversacional relatable (comparación con Amazon), y consejos prácticos de diferenciación. Gatillo: utilidad práctica inmediata + autoridad (experiencia con clientes reales) + desmiente una creencia común ('no es el algoritmo').</t>
+          <t>Gancho de afirmacion contraintuitiva y polemica ('el targeting esta muerto'); estructura de explicacion causal ('te lo voy a explicar') con ejemplo concreto y accionable (nombrar a la audiencia en la primera linea del copy); gatillo de autoridad/prueba social al cerrar con 'esto es lo que hacemos con nuestros clientes y la rompemos'.</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>sí + es solo una conversación/opinión grabada en cualquier lugar con luz natural y subtítulos automáticos, cero edición compleja.</t>
+          <t>sí, es solo una camara fija y opinion hablada, sin edicion ni graficos, uno de los formatos mas baratos de replicar.</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       <c r="C25" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -2889,7 +2889,7 @@
       <c r="C26" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -2981,7 +2981,7 @@
       <c r="C27" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -3065,32 +3065,32 @@
     </row>
     <row r="28" ht="88" customHeight="1">
       <c r="A28" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Solución de un problema</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Fácil</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Mitch Barham (Beardpreneur)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3100,48 +3100,48 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>310</v>
+        <v>4294</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7665695408898706710</t>
+          <t>https://www.tiktok.com/@beardpreneur/video/7670313706110209294</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath lista cinco errores comunes que arruinan una cuenta de anuncios de Meta: matar anuncios por emociones, escalar demasiado rapido, solo testear variaciones superficiales, depender de una sola creatividad y copiar anuncios de la competencia.</t>
+          <t>Mitch cuestiona el panico generalizado por la caida de conversiones en Facebook Ads mostrando graficos reales de una cuenta de cliente que correlacionan las caidas de gasto/rendimiento en Meta con caidas simultaneas en Google Ads, y concluye que el verdadero motivo es un cambio en el comportamiento del consumidor (mas investigacion antes de comprar).</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Cinco formas de arruinar tu cuenta de anuncios de Meta. Numero uno: matar anuncios basandote en emociones. Una pequena caida no significa que tu anuncio este muerto, espera al menos una semana. Numero dos: escalar demasiado rapido. Pasar de 50 dolares por dia a 500 dolares de la noche a la manana no es escalar, es una receta para el desastre. Vas a resetear la fase de aprendizaje y disparar tus CPA. Numero tres: solo testear variaciones. Si tu anuncio ya esta fracasando y cambias la paleta de colores, no va a pasar nada significativo. Anda mas profundo y testea distintos hooks, distintas emociones, distintas ofertas. Numero cuatro: dejar que una sola creatividad sostenga toda la cuenta. Si no tenes nada preparado para cuando la fatiga publicitaria finalmente aparezca y la audiencia deje de comprar, tus ventas se van a desplomar. Numero cinco: copiar los anuncios de tu competencia de forma identica, uno a uno. Realmente no conoces sus margenes de negocio, su oferta, su proceso ni su backend. Toma inspiracion, pero mantenete unico.</t>
+          <t>Las conversiones de los anuncios de Facebook vienen cayendo de forma sostenida. Y todo el mundo esta entrando en panico y diciendo 'ay dios mio, los anuncios de Facebook no funcionan'. Y Andromeda, GEM y Lattice [?] como que 'ah, es el fin del mundo'. Aca esta la cosa, esto no cuenta toda la historia. Hay una correlacion entre los anuncios de Facebook, los anuncios de Google y los anuncios de Bing. Y te lo voy a mostrar. Tengo dos graficos aca. Uno es un grafico personalizado del gasto en anuncios de un cliente. Bien, estoy mirando un periodo de dos meses, y aca estan las conversiones de Google, y podes ver subidas y bajadas. Pero vas a ver aca, el 2 de marzo, Google cayo. Y mira eso, los anuncios de Facebook cayeron al mismo tiempo. Despues empieza a subir de nuevo y Google hace lo mismo. Despues, el 17 de marzo, Google empieza a caer de nuevo hacia este pozo mas grande. Mira lo que paso aca. El 16 de marzo, el gasto de Facebook bajo hasta el punto de que el 29 de marzo cayo practicamente a cero. Tuvimos que apagar todo. Y mira eso, el 25 de marzo. Y despues se quedo ahi. Y despues, a medida que el gasto subio, podes notar que la tendencia va para arriba. Entonces, todo esto para decir que, basicamente, lo que estas viendo es que el comportamiento del consumidor cambio por completo. No es que 'se cocinen' [?] con tu anuncio de Facebook y vayan directo a comprar. Se siguen 'cocinando', pero despues van a investigar. Van a ver si sos legitimo. Como son tus resenas. Estan tardando mas en comprar. La plata ya no es gratis. Eso es lo que esta pasando.</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>Toma unica a camara, estilo selfie, al aire libre en un campo/pastizal con cielo despejado, musculosa casual; solo subtitulos blancos que siguen el audio, sin graficos adicionales ni cortes de edicion visibles.</t>
+          <t>Talking head con un grafico de datos superpuesto de fondo ('CVR and CTR have moved in opposite directions on Meta', lineas roja/azul), despues corta a grabacion de pantalla real de un dashboard de anuncios mostrando gasto y conversiones dia por dia con zoom en los numeros. Subtitulos dinamicos. Combina opinion hablada con evidencia de datos reales en pantalla, sin graficos animados propios.</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>Gancho de aversion a la perdida ('your ad account is bleeding money'); estructura de lista numerada de errores, facil de seguir y de aplicar como checklist; gatillo de miedo/urgencia a estar cometiendo un error sin saberlo.</t>
+          <t>Gancho de problema urgente y ampliamente sentido en el nicho (conversiones cayendo, panico generalizado); estructura de 'esto no es lo que parece' respaldada con evidencia grafica propia (datos de cliente real); gatillo de autoridad basada en datos y cierre con un insight accionable sobre comportamiento del consumidor.</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>si, es el formato mas simple del lote: una sola toma a camara al aire libre con subtitulos.</t>
+          <t>sí, requiere tener datos reales de cuentas de clientes para mostrar como prueba, pero la grabacion en si (camara + captura de pantalla) es de bajo costo.</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3157,27 +3157,27 @@
     </row>
     <row r="29" ht="88" customHeight="1">
       <c r="A29" s="2" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Mitch Barham (Beardpreneur)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3192,48 +3192,48 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4294</v>
+        <v>4168</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beardpreneur/video/7670313706110209294</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7613406587423673631</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Mitch cuestiona el panico generalizado por la caida de conversiones en Facebook Ads mostrando graficos reales de una cuenta de cliente que correlacionan las caidas de gasto/rendimiento en Meta con caidas simultaneas en Google Ads, y concluye que el verdadero motivo es un cambio en el comportamiento del consumidor (mas investigacion antes de comprar).</t>
+          <t>Chase Chappell presenta una herramienta de inteligencia creativa que permite buscar los anuncios de cualquier competidor, ver cuáles llevan más tiempo corriendo (señal de que convierten) y guardar los mejores patrones en un swipe file.</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>Las conversiones de los anuncios de Facebook vienen cayendo de forma sostenida. Y todo el mundo esta entrando en panico y diciendo 'ay dios mio, los anuncios de Facebook no funcionan'. Y Andromeda, GEM y Lattice [?] como que 'ah, es el fin del mundo'. Aca esta la cosa, esto no cuenta toda la historia. Hay una correlacion entre los anuncios de Facebook, los anuncios de Google y los anuncios de Bing. Y te lo voy a mostrar. Tengo dos graficos aca. Uno es un grafico personalizado del gasto en anuncios de un cliente. Bien, estoy mirando un periodo de dos meses, y aca estan las conversiones de Google, y podes ver subidas y bajadas. Pero vas a ver aca, el 2 de marzo, Google cayo. Y mira eso, los anuncios de Facebook cayeron al mismo tiempo. Despues empieza a subir de nuevo y Google hace lo mismo. Despues, el 17 de marzo, Google empieza a caer de nuevo hacia este pozo mas grande. Mira lo que paso aca. El 16 de marzo, el gasto de Facebook bajo hasta el punto de que el 29 de marzo cayo practicamente a cero. Tuvimos que apagar todo. Y mira eso, el 25 de marzo. Y despues se quedo ahi. Y despues, a medida que el gasto subio, podes notar que la tendencia va para arriba. Entonces, todo esto para decir que, basicamente, lo que estas viendo es que el comportamiento del consumidor cambio por completo. No es que 'se cocinen' [?] con tu anuncio de Facebook y vayan directo a comprar. Se siguen 'cocinando', pero despues van a investigar. Van a ver si sos legitimo. Como son tus resenas. Estan tardando mas en comprar. La plata ya no es gratis. Eso es lo que esta pasando.</t>
+          <t>La herramienta creativa detrás de tus marcas favoritas. Si estás corriendo anuncios pagos en 2026, ya sabés esto: lo creativo es el cuello de botella. Meta ya no premia un solo anuncio ganador. Premia volumen, variación y formatos. Ahí es donde entra esta herramienta. Te permite buscar cualquier competidor y ver al instante qué anuncios llevan más tiempo corriendo. Eso importa porque los anuncios no se quedan activos a menos que estén convirtiendo. Podés desglosar eso: hooks, ángulos, formatos de anuncio, videos estilo UGC, estructuras de oferta, y después guardar todo en un swipe file (archivo de referencia) que tu equipo realmente pueda usar. No hay que adivinar, no hay agotamiento creativo, y no hay que empezar de cero. Así es como los mejores media buyers (compradores de medios) se mantienen adelante. No solo testean más rápido, roban patrones que ya están comprobados que funcionan. Si querés mejores anuncios, un CAC (costo de adquisición de cliente) más bajo, y creatividades que realmente escalen, necesitás mejor inteligencia creativa. Comentá 'tool' y te la mando.</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>Talking head con un grafico de datos superpuesto de fondo ('CVR and CTR have moved in opposite directions on Meta', lineas roja/azul), despues corta a grabacion de pantalla real de un dashboard de anuncios mostrando gasto y conversiones dia por dia con zoom en los numeros. Subtitulos dinamicos. Combina opinion hablada con evidencia de datos reales en pantalla, sin graficos animados propios.</t>
+          <t>Encuadre: capturas de pantalla de Meta Ads Library (búsqueda de marcas como 'alphalete', ficha de anuncio individual, grilla de resultados) con el creador en recuadro inferior. Subtítulos: ninguno quemado aparte de la interfaz misma. Cortes: entre distintas pantallas del Ads Library. Gráficos: flecha roja señalando el dato '741D' (741 días activo) como prueba de que un anuncio convierte. Locación: sin locación física, fondo de estudio con micrófono.</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>Gancho de problema urgente y ampliamente sentido en el nicho (conversiones cayendo, panico generalizado); estructura de 'esto no es lo que parece' respaldada con evidencia grafica propia (datos de cliente real); gatillo de autoridad basada en datos y cierre con un insight accionable sobre comportamiento del consumidor.</t>
+          <t>Gancho: apela a autoridad indirecta ('la herramienta detrás de tus marcas favoritas'). Estructura: plantea el problema del momento (lo creativo es el cuello de botella, Meta premia volumen), presenta el mecanismo de la herramienta, muestra prueba concreta en pantalla (un anuncio corriendo hace 741 días) y promete un resultado usable (swipe file). Gatillo: dato duro y verificable (741 días) que vuelve tangible una promesa abstracta, sumado al CTA por palabra clave.</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>sí, requiere tener datos reales de cuentas de clientes para mostrar como prueba, pero la grabacion en si (camara + captura de pantalla) es de bajo costo.</t>
+          <t>Sí, con matices — el research se hace en Meta Ads Library, que es gratis; solo hace falta grabación de pantalla y una flecha de énfasis.</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       <c r="C30" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Solución de un problema</t>
         </is>
@@ -3341,27 +3341,27 @@
     </row>
     <row r="31" ht="88" customHeight="1">
       <c r="A31" s="2" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Caleb Kruse (Mr. Paid Social)</t>
+          <t>Dara Denney</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3376,48 +3376,48 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>3701</v>
+        <v>4094</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.paidsocial/video/7627237636427549966</t>
+          <t>https://www.tiktok.com/@daradenney/video/7667945190090394911</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Video tipo listado que muestra 15 ejemplos de anuncios generados con la IA de video Seedance 2.0 (probadores de ropa, recorridos inmobiliarios, entrevistas callejeras, unboxing, ASMR, etc.) para promocionar el uso de esta herramienta en la creación de creativos publicitarios.</t>
+          <t>Dara Denney muestra cómo automatizó por completo el reporte mensual de rendimiento creativo de su agencia usando ChatGPT, Codex y una conexión directa a la API de Meta Ads, reduciendo el tiempo de armado de 3-4 horas a 20-30 minutos.</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t>Acá tienen 15 usos increíbles para Seedance 2 [corregido de "C Dance 2", error de reconocimiento] y cómo podés usarlo en tu publicidad. Voy a ir bastante rápido, así que asegurate de guardar este video para no perderlo. Número uno, anuncios estilo podcast. Este es el producto para vos. Es como un shot de espresso para tu cuenta de anuncios. Número dos, videos de prueba de outfits (probadores de ropa). Número 3, videos de recorrido inmobiliario (real estate walkthrough). Bienvenidos a esta casa de estilo medio siglo de 1969 en el codiciado barrio de Lake Wilderness. El nivel principal cuenta con un... Número 4, anuncios de entrevistas callejeras (street interview). Hola a todos, hoy le estamos preguntando a la gente qué piensan de Mr. Paid Social. ¿Qué piensan ustedes, chicas, de Mr. Paid Social? Creo que es realmente innovador. No creo que su segmentación (targeting) sea tan efectiva como podría ser. Escuché que es... Número 5, anuncios de producto cinematográficos. Número 6, anuncios estilo nota adhesiva (post-it). Número 7, anuncios estilo time lapse. Número 8, anuncios de showcase de unboxing de producto. ¡Hermano, por fin llegaron! ¡Mirá esto! Los detalles son una locura. El azul resalta en la parte de atrás. ¡Dale! Número 9, anuncios de probador de producto. Gimnasios. Terminé de probar estos. Número 10, videos de cosmética. Prueba de humectante. Bueno, en realidad es dewy/luminoso [corregido de "Dewey"]. Número 11, anuncios de destacado de característica (feature call-out). Si solo pudiera usar una gorra por el resto de mi vida, sería esta. Sin dudas. Corderoy de tres tonos, parche tejido, y esta correa ajustable para que le quede a cualquiera. Número 11 [así en el original, se repite el número — probablemente debería ser "12" [?]], anuncios de showcase de app. Esta app es increíble. Tiene tantas funciones que hacen que estudiar sea mucho más fácil. Número 13, anuncios estilo caricatura (cartoon). Las enfermedades cardíacas son la causa número uno de muerte en hombres. Número 14, videos de IA con pantalla verde (green screen). Todo dentro de la comunidad AI Ad Alchemist [?, nombre de comunidad poco claro en el audio]. Acá es donde podés venir a aprovechar la IA y la automatización para finalmente escalar tu app [?, posiblemente "tus anuncios/ads"]. Número 15, videos ASMR. Ay, dios mío, mirá eso. Nunca habíamos visto un modelo tan bueno haciendo anuncios de IA. Y si querés el link para probarlo, está en mi perfil. De estos 15 ejemplos, asegurate de seguirme porque hago mucho contenido mostrando cómo llevar tu media buying al siguiente nivel con IA.</t>
+          <t>Este flujo de trabajo con ChatGPT significa que nunca más voy a tener que hacer reportes creativos a mano, especialmente ahora que ChatGPT, Work y Codex están todos en el mismo lugar. A fin de cada mes armamos un reporte de rendimiento creativo para todos nuestros clientes. Cubre de todo: métricas del negocio mes a mes, desglose de productos, aprendizajes creativos. Pero nos llevaba entre tres y cuatro horas armar cada uno por marca. Así que acá les cuento cómo automaticé esto por completo usando ChatGPT, bajando el tiempo total de armado del deck a 20 minutos. Primero usé GPT 5.6 [?] en ChatGPT, le mostré ejemplos de nuestros reportes viejos y le di contexto adicional sobre lo que quería lograr. Ahí armamos un plan para construir una app en Codex. Después armé una "plugin skill" (habilidad conectada) que ayudara a darle vida a los decks exactamente en el formato que yo quería. Y finalmente conecté Codex directamente a Meta Ads a través de una llamada a la API de Meta for Developers, para poder conseguir los datos más precisos posibles. Antes estaba haciendo malabares con múltiples fuentes de datos y visualizaciones, pero ahora todo se hace a través de ChatGPT, Work y Codex. Ahora tenemos esto como tareas programadas para cada marca, y directamente nos avisa por Slack cada vez que un reporte está listo para los últimos retoques. Entonces ahora, cada mes, a ChatGPT se le avisa cuando es momento de generar un reporte nuevo. Ahí consulta la "plugin skill" que desarrollé, para saber de qué cliente se trata y en qué formato quiero la presentación, y después, usando Codex, se conecta directamente a Meta Ads para conseguir los datos más precisos. Yo solo dedico entre 20 y 30 minutos a agregar los insights que solo yo puedo aportar, pero el 90% del trabajo pesado quedó completamente resuelto por ChatGPT. Así que si sos una mujer en "spam" [?] que quiere automatizar por completo su reporte de Meta Ads, asegurate de descargar la app de escritorio de ChatGPT.</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>Grabación de pantalla de una computadora reproduciendo la interfaz de la herramienta de IA Seedance 2.0 (se ve el panel de generación con el prompt de texto y botones "Remix / Upscale / Extend / More") intercalada con clips de ejemplo generados por IA (mujer hablando a cámara estilo podcast con micrófono, una casa en el bosque tipo cabaña, un teléfono mostrando una app). Texto gráfico fijo en rojo/blanco con borde negro "SEEDANCE 2.0 JUST DROPPED / Here's 15 ad examples" superpuesto durante todo el video. Formato vertical con el video del ejemplo enmarcado dentro de la captura de pantalla más grande.</t>
+          <t>Collage con múltiples capas: talking head (mujer sentada en escritorio de madera con laptop, remera verde, micrófono de podcast, decoración con lámpara verde y cuadros de fondo) combinado con capturas de pantalla superpuestas de la interfaz de ChatGPT y de documentos/planes de trabajo. Subtítulos progresivos con algún efecto de tachado sobre el texto. Edición con varias capas visuales (screen recording + cámara).</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>Gancho de curiosidad/reto en el título ("¿podés notar que es 100% IA?") que invita a comentar, combinado con estructura de listicle numerado (15 ejemplos) que promete valor denso y variado; el pedido explícito de guardar el video genera retención y señal de guardado al algoritmo.</t>
+          <t>Promesa de resultado fuerte al inicio ("nunca más voy a tener que hacer reportes a mano"), reforzada con cifra de tiempo ahorrado (de 3-4 horas a 20 minutos). Estructura de tutorial paso a paso de la automatización, herramienta por herramienta, con capturas de pantalla como evidencia. El gatillo es el ahorro de tiempo cuantificado combinado con un tutorial técnico con prueba visual y asociación a una marca (contenido patrocinado, autoridad).</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: cualquiera con acceso a Seedance 2.0 (u otra IA de video similar) y una pantalla para grabar puede replicar el formato listicle sin filmar nada propio.</t>
+          <t>no — requiere herramientas pagas (ChatGPT Work, Codex, API de Meta) y conocimiento técnico para armar el flujo que se muestra.</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3433,27 +3433,27 @@
     </row>
     <row r="32" ht="88" customHeight="1">
       <c r="A32" s="2" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3468,48 +3468,48 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>2827</v>
+        <v>3940</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7621602508879727904</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7635737398961245462</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath anuncia que los anuncios en Threads, antes exclusivos de EE.UU., ahora se lanzaron globalmente, sumando nuevos formatos (carrusel, catálogo, apps) para alcanzar a los más de 400 millones de usuarios activos mensuales de la plataforma.</t>
+          <t>Matt Bell comparte, sobre un grafico fijo con voz en off, un insight de sus ultimas 90 dias en cuentas de anuncios: las creatividades estaticas estan empezando a convertir mejor que el video, posiblemente por la desconfianza creciente hacia contenido generado con IA y las voces genericas de UGC.</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Tengo una noticia importante en cuanto a los anuncios en Threads. Antes, los anuncios en Threads solo se mostraban en Estados Unidos, pero ahora se lanzaron a nivel global. Así que si no estás en Estados Unidos, es probable que empieces a ver anuncios en Threads en breve. También tenemos ahora más formatos de anuncio que podemos usar en esa plataforma. Así que en lugar de solo anuncios básicos de feed, ahora también podemos correr anuncios carrusel, anuncios de catálogo, anuncios de apps. Así que tenemos más flexibilidad como anunciantes para alcanzar a los más de 400 millones de usuarios activos mensuales que hay actualmente en Threads.</t>
+          <t>Y lo que les puedo decir ahora mismo es que, en todas las cuentas de anuncios en las que estuve trabajando en los ultimos 90 dias, lo estatico esta empezando a rendir mejor que el video. Creo que lo que esta pasando es que hay demasiadas marcas haciendo contenido de IA malo, y muchos consumidores estan empezando a desconfiar de si el creativo que estan viendo fue generado por IA. Entonces, en mi opinion, creo que esta empezando a haber una falta de confianza con los creadores de video. Y encima de eso, muchas marcas estan yendo directamente con esta voz generica de influencer, tipo el creador UGC estandar, que no esta convirtiendo tan bien comparado con lo estatico. Esa es la tendencia que estoy viendo. Pero de cualquier manera, tenes que tener variacion aca.</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: plano medio sentado, formato podcast con micrófono. Subtítulos: palabra por palabra en mayúsculas, con una palabra clave ('ON') resaltada en azul. Cortes: toma continua. Gráficos: solo el color del subtítulo. Locación: interior tipo cocina/comedor con reloj de pared y planta de fondo.</t>
+          <t>Video practicamente estatico: los tres frames muestreados (1, 3 y 5) son identicos, una sola imagen/grafico fijo con dos titulares en banners rojos ('Static Meta ads seem to be doing better on average than video right now' / 'Is this because of AI?') sobre una captura de pantalla de datos comparando video, estatico y carrusel. No hay talking head visible ni cortes; la voz en off es la unica fuente de dinamismo, sin locacion identificable (imagen tipo escritorio/Mac).</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>Gancho: anuncio de 'noticia importante' sobre una plataforma específica, genera expectativa inmediata. Estructura: qué cambió (alcance global), qué hay de nuevo (formatos de anuncio), por qué importa (tamaño de audiencia alcanzable). Gatillo: la noticia posiciona al creador como fuente actualizada y confiable, lo que favorece que se guarde/comparta como referencia.</t>
+          <t>Gancho de dato de tendencia contraintuitivo y accionable para el nicho (estatico rinde mejor que video); estructura breve de opinion mas hipotesis (desconfianza hacia la IA); gatillo de pregunta polemica para generar debate en comentarios ('¿es por la IA?'), todo en un clip muy corto (39s).</t>
         </is>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>Sí — mismo setup casero simple (mic + sala) que otros videos del mismo creador.</t>
+          <t>sí, es practicamente solo un grafico de texto fijo con voz en off, el formato mas barato posible de producir.</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3525,32 +3525,32 @@
     </row>
     <row r="33" ht="88" customHeight="1">
       <c r="A33" s="2" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3560,33 +3560,33 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>2420</v>
+        <v>3915</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7631128226135411986</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7646124046270074134</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Maddi presenta un framework de 5 pasos para el 'anuncio de misión/visión' en marcas de moda y joyería: gancho de identidad, mostrar el oficio (craft), conectar con la vida real de la clienta, prueba social y cierre en un único producto hero.</t>
+          <t>Matt Bell explica, mostrando datos reales de una cuenta de Meta Ads y de la herramienta de atribucion Triple Whale, por que guiarse solo por el ROI que reporta cada plataforma es enganoso, y como usar distintos modelos de atribucion (primer clic, ultimo clic, lineal, etc.) para saber que esta generando ingresos de verdad.</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Hay un formato de anuncio al que siempre vuelvo con prácticamente todos mis clientes de moda y de joyería, literalmente casi todos los clientes con los que trabajo, y sigue funcionando muy bien dentro de la cuenta de anuncios. Y como dije, con cada cliente para el que lo armo, se convierte en uno de los anuncios que más tiempo dura corriendo, recibe mucho presupuesto, y por lo general consigue un CPA realmente bueno. Pero lo más importante es que construye marca, y yo lo llamo el anuncio de misión o visión. Y creo que para las marcas de moda y de joyería específicamente esto está subestimado, y no es un video testimonial, no está vendiendo el producto, está mostrando el porqué detrás de la marca. Ahora, cada vez que armé esto, seguí una estructura específica que les voy a mostrar paso a paso. Y como mencioné, siguiendo este formato, sigue ganando dentro de la cuenta de anuncios. Así que acá está el framework. Tiene cinco secciones y, como dije, sigo exactamente esta fórmula cada vez. El paso 1 es el gancho de identidad. Abrís con para quién es esto, no con el producto, no con una oferta. Nombrás a la persona específica; esto está hecho específicamente para ella. Si no es esa persona específica, querés que siga scrolleando. El número 2 es revelar el oficio/la manufactura (craft), no el producto, el craft. Puede ser la costura, la tela, el calce, la fabricación; esto no se debería ver nunca en una foto de producto típica de e-commerce. Estás diciendo que realmente nos importa cómo hicimos esto y el porqué detrás de por qué lo hicimos, o de este calce específico. Por eso la gente se va a quedar y va a seguir mirando. Y después, en el framework, el número 3 es el "por qué" (the why). Acá querés conectar el producto con la vida real de ella. Y no estoy hablando de styling versátil, "perfecto para cualquier ocasión". Quiero que te pongas tan específico en ese momento puntual que ella se sienta realmente vista y entienda: sí, en ese momento específico de mi vida, soy yo usando ese producto específico. Después el número 4 es, por supuesto, la prueba social. Necesitamos esto: pueden ser reseñas, fotos de UGC (contenido generado por usuarios), cuántas unidades vendiste. Cualquier cosa que genere confianza con tu audiencia es lo que queremos aportar acá. Y por supuesto, el número 5 es cerrar con ese producto, un solo producto hero (estrella). No "mirá nuestra colección", nombrá ese producto hero para que quede grabado en su cabeza. Entonces, como mencioné, la razón por la que este formato sigue ganando es porque hace algo que la mayoría del contenido pago no hace: hace que la clienta se sienta vista antes de pedirle que haga una compra.</t>
+          <t>Si mirás esta cuenta de anuncios ahora mismo, podes ver que el ROI promedio para este periodo es 2x. ¿Okay? Y la mayoria de la gente va a mirar esto y va a tomar decisiones en base al ROI que se esta reportando. Entonces capaz miran esa campana que esta teniendo un ROI de 3x ahora mismo y piensan 'esta bien, la voy a dejar corriendo'. Y obviamente van a mirar las campanas con ROI mas bajo y las van a apagar. El problema que tenes es que la forma en que META reporta los datos ahora mismo, y todos estos otros canales de anuncios, es de una manera muy dificil de rastrear. Toda tu estrategia entera tiene que estar dictada en base a tu MER. Ahora, esto de aca es Triple Whale. Y Triple Whale es esta herramienta que te permite mirar distintos modelos de atribucion, en lo que vamos a entrar en un segundo, y tambien te da la capacidad de crear estos dashboards muy lindos donde podes conseguir estas metricas y rastrearlas. Ahora, tambien hay otras herramientas ademas de Triple Whale. Un par de ejemplos serian Northbeam, TrueROAS [?]. A estas se las llama herramientas de atribucion. Entonces si entras aca donde dice 'atribucion', tenes estos distintos modelos de atribucion aca. Y algo de esto se explica solo, pero basicamente, si voy a 'primer clic' ahora mismo, lo que me va a mostrar son mis resultados de la gente que hizo clic desde el anuncio y compro ahi. En otras palabras, ¿que canal te esta trayendo el mejor trafico de conversion? Despues, si voy a 'ultimo clic', eso me va a mostrar a la gente que vio un anuncio, digamos en Facebook, pero despues, 3 dias mas tarde, vio un anuncio en Google Display y convirtio como resultado del Google Display, entonces esa seria una conversion de ultimo clic. Y despues tambien tenes lineal, pagado y aprendizaje en todo [?], y atribucion triple. Estas son basicamente la version de Triple Whale de tratar de calcular cual es el riesgo usando su propio modelo. Y creo que involucra IA y un monton de otras cosas, pero basicamente te da una vision bastante buena de que es lo que realmente esta generando tus ingresos.</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano (más cerrado que en otros videos de la misma cuenta), fondo blanco con logo "MADE." en la pared, título fijo tipo banner blanco con borde negro arriba ("This Ad Format KEEPS Performing... Here's How To Do It"), aire acondicionado visible detrás. Mismo encuadre estático en los tres frames revisados, sin cortes evidentes de cámara.</t>
+          <t>Grabacion de pantalla de principio a fin en los frames analizados: primero un dashboard de Meta Ads (tabla con gasto, CPM, alcance, frecuencia, CTR), despues el dashboard de Triple Whale con metricas reales (Net Profit, ROAS, MER, Net Margin, Web Analytics). Banner de texto blanco fijo en la parte superior con el titulo del video. No aparece el creador a camara en los frames muestreados, solo voz en off narrando los datos en pantalla.</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>Gancho de curiosidad/autoridad ("este formato SIGUE funcionando... así se hace") combinado con promesa de framework numerado y accionable (5 pasos) que da estructura fácil de recordar, y cierre con una frase citable ("hace sentir vista a la clienta antes de pedirle que compre").</t>
+          <t>Gancho de problema tecnico relevante para el nicho (el ROI que ves esta enganando tus decisiones); estructura educativa apoyada en demo con datos y herramientas profesionales reales (autoridad/expertise); formato de mini-tutorial que ademas puede generar leads para la agencia del creador.</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: es un video educativo de talking head con guion estructurado, replicable con celular, buena luz y un fondo prolijo.</t>
+          <t>no del todo, exige acceso a cuentas de anuncios reales con datos y una suscripcion paga a herramientas de atribucion como Triple Whale.</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -3617,17 +3617,17 @@
     </row>
     <row r="34" ht="88" customHeight="1">
       <c r="A34" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Mitch Barham (Beardpreneur)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3652,33 +3652,33 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1960</v>
+        <v>3813</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7667312448218615062</t>
+          <t>https://www.tiktok.com/@beardpreneur/video/7654413458217209101</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath compara las estrategias publicitarias y de sitio web de dos marcas de joyería (Crafted vs. Sonuchi [?]), analizando sus anuncios en la Biblioteca de Anuncios de Meta, la variedad creativa y la experiencia de compra online, y concluye que Crafted es mejor.</t>
+          <t>En formato de respuesta a un comentario, Mitch usa una infografia de embudo (arriba/medio/abajo del funnel) para explicar que la mayoria de las cuentas arrancan pidiendo la venta demasiado pronto, y que al escalar a presupuestos de 6 cifras multiples por mes hay que volver a llenar la parte alta del embudo con contenido de awareness.</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>¿El marketing de quién es mejor, Crafted o Sonuchi [?]? Bueno, Sonuchi está corriendo 87 anuncios de Meta. Tienen una variedad decente de imágenes acá. Sin embargo, sus anuncios en video son todos muy parecidos. Hacen pequeñas iteraciones sobre distintas piezas creativas, y ese formato probablemente les funcione bien. Pero podrían pasar al siguiente nivel incluyendo formatos completamente nuevos. Pensá en reseñas UGC, unboxings. Ahora, Crafted: 130 anuncios de Meta, mucho mejor. Tienen imágenes estáticas en distintos formatos y videos que muestran el producto en acción en diferentes situaciones. Esto es fantástico porque encaja con su eslogan, que es 'crafted to last' [hecho para durar]. También experimentaron con más formatos, lo cual está bien. Sobre el sitio web: está buenísimo. Te dan un descuento misterioso apenas hacés clic. Eso me gusta mucho. También hay reseñas, garantías de calidad por todos lados. La página principal de Sonuchi también te tira un pop-up de oferta, pero no es un misterio: es un simple descuento de 10 libras. Curiosamente, sí tienen fotos de Lamine Yamal usando sus joyas, pero está escondido dentro del sitio web. Tenés que esforzarte bastante para encontrarlo. Si tenés a una de las estrellas más grandes del fútbol usando tus productos, tendrías que estar gritándolo a los cuatro vientos. Las dos marcas son buenas, pero Crafted le gana a esta. Su testeo creativo es más sofisticado, el storytelling de su producto es más ajustado y su sitio tiene menos fricción. ¿Están de acuerdo? Cuéntenme abajo en los comentarios.</t>
+          <t>Asi que, tecnicamente, todos estamos usando mal los anuncios de Facebook. Mira, durante anos todo fue conversiones, conversiones, conversiones. O leads, leads, leads. Cuando en realidad, la parte alta del embudo deberia ser algo como tu engagement, tus reproducciones de video, tu contenido de redes sociales, o el objetivo de 'ver contenido'. Olvidate del trafico. Pero ahi estas calentando a la gente. Pero todos arrancamos aca, en el medio del embudo, con consideracion e intencion, y directamente vamos a lo 'a la mierda, compren nuestras cosas'. ¿Que estas haciendo? Compra nuestras cosas. Registrate ahora mismo, y despues se lo metemos por la garganta con un presupuesto chico. Si, arranca aca. ¿Por que no? No hace falta estar arriba. Cuando empezamos a gastar multiples 6 cifras por mes, tenemos que llenar la parte de arriba del embudo, que es a lo que se referia el tipo que respondio a mi video. A esto le decimos 'Tippy Top' (la puntita de arriba). Estamos llenando el balde aca arriba, moviendolos hacia aca, y finalmente hacia abajo, la parte baja del embudo, donde el anuncio es estrictamente nada mas que 'che, vengan a comprar nuestras cosas'. El problema es que entrenamos a todo el mundo para ir siempre directo a la yugular y querer la venta ya. Esto no funciona. Es como intentar casarte con alguien de una asi de rapido, en vez de salir con esa persona y dejar que realmente te conozca, para despues decirle 'che, ¿queres comprar nuestras cosas?'.</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>Formato 'reacción/análisis' con inserciones gráficas cambiantes en picture-in-picture: frame 1 muestra una interfaz tipo Biblioteca de Anuncios de Meta ('Active', 'Library ID', plataformas) con miniatura de video de ropa; frame 3 muestra un primer plano de una pulsera/cadena dorada en una muñeca con texto de marca ('HEAT PROOF situations'); frame 5 muestra una foto del futbolista Lamine Yamal con cadenas y su nombre en texto. En los tres, el presentador (remera polo gris) aparece más chico abajo hablando, fondo blanco liso. Subtítulos blancos en negrita. Varios cortes con distintas capturas de pantalla.</t>
+          <t>Formato de respuesta a comentario (incluye la burbuja del comentario original: 'Did you just say TOFU is middle of funnel?'), con una infografia de embudo de marketing (TOP OF FUNNEL azul, MIDDLE OF FUNNEL verde, BOTTOM OF FUNNEL amarillo, cada uno con iconos de sus acciones tipicas) superpuesta detras/alrededor del presentador durante todo el video. Talking head con gestos de mano marcados, subtitulos dinamicos con palabras clave resaltadas en rosa/magenta.</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>Gancho: formato versus directo ('¿el marketing de quién es mejor?') que invita a opinar. Estructura: comparación punto por punto de anuncios y sitio web de dos marcas competidoras, veredicto final y pregunta para generar comentarios. Gatillo: formato comparativo/polémica leve entre marcas + curiosidad + cierre con pregunta que dispara engagement.</t>
+          <t>Gancho de afirmacion polemica y validadora ('todos lo estamos haciendo mal'); estructura de respuesta a un comentario que aprovecha una conversacion previa como prueba de engagement/autoridad, combinada con una infografia clara que ensena un framework (TOFU/MOFU/BOFU) mientras habla; gatillo de identificacion para cuentas grandes que ya sienten ese dolor, reforzado con lenguaje directo y coloquial.</t>
         </is>
       </c>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>sí, mismo formato reacción/análisis mostrando capturas de pantalla (Ads Library, sitio web) con cámara casera, sin producción cara.</t>
+          <t>sí, la infografia requiere algo de diseno previo pero es reutilizable, y el resto es solo camara y opinion hablada.</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -3709,15 +3709,15 @@
     </row>
     <row r="35" ht="88" customHeight="1">
       <c r="A35" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3744,33 +3744,33 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1848</v>
+        <v>3701</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7650905074020977942</t>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7627237636427549966</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Dos marketineros (Ben Heath y un colega) reaccionan a un comercial de Adidas con estrellas como Beckham, Zidane y Messi, elogiando su producción. Después revisan la Biblioteca de Anuncios de Meta y descubren que Adidas no está pautando esa pieza como anuncio pago, algo que consideran una oportunidad desperdiciada.</t>
+          <t>Video tipo listado que muestra 15 ejemplos de anuncios generados con la IA de video Seedance 2.0 (probadores de ropa, recorridos inmobiliarios, entrevistas callejeras, unboxing, ASMR, etc.) para promocionar el uso de esta herramienta en la creación de creativos publicitarios.</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>Es una demostración de poder una locura de parte de Adidas, ese anuncio. Tener a tantos nombres [famosos] y gastar tanta plata en eso... o sea, debe haber costado una fortuna absoluta. Yo de soccer no sé nada, de fútbol sí que sé algo [?]. Se siente como si estuvieras viendo una película o una serie de TV. Escuchá, hermano, tengo un equipo, son de fiar. Bueno, ya vamos en camino. Estamos en el auto ahora. Gracias. Es casi como que no es realmente un anuncio. No es realmente una pieza de contenido diseñada para vender algo. Es más como una pieza de entretenimiento en la que metieron su marca. La verdad, uno dice: 'guau, qué paciencia' [?]... los superás [?] (fragmento poco claro por la transcripción automática). Me hace sentir viejo que 1996 sea como si fuera hace una eternidad. Ja ja ja ja ja ja. ¿Ese es Beckham? ¿Tienen a alguien todavía mejor? [?] Sí, un David Beckham con cara de joven, y también un Zinedine Zidane joven. En esta parte es como: 'nosotros estamos a cargo de este espacio'. Bueno, te voy a ser sincero: puede que le haya dicho al que posiblemente sea el mejor jugador del planeta que yo podía terminar esto hoy. Definitivamente podrías recortar eso y usarlo en un formato más publicitario, para ser un poco más directo a la hora de promocionar cosas. Entonces, ¿cumplí o cumplí? ¿Y después ponen a Messi al final? Es un video de cinco minutos y él no aparece hasta el minuto 4:30 o algo así. Che, vos sos mi plan B. Es muy competitivo contra Nike, el gran rival. Sí, sin dudas es así. Así que si voy a ver qué están haciendo con esto en Adidas Football, porque podrían estar usando... no tienen ningún anuncio corriendo. Eso me parece una locura. Adidas Football tiene 26,4 millones de seguidores en su página de Facebook y 34,7 millones en Instagram. Y no estar corriendo ningún anuncio... para cualquier gestor de anuncios sería el sueño poder manejar esa cuenta, porque sería tan fácil generar resultados tan buenos con esa audiencia. Y no les han hecho publicidad a esa audiencia [?]. Sería como tirarle a peces en un barril [algo súper fácil] correr anuncios para esa audiencia en esas cuentas. Bueno, en Adidas Originals sí están corriendo anuncios: tienen 440 [?] corriendo en todas las ubicaciones. No es tanto para una marca de ese tamaño. Ya puedo ver diferentes idiomas. Bueno, esta es como la cuenta principal de Adidas. Me sorprende muchísimo que no estén corriendo variaciones de esa pieza creativa como anuncios, ni ningún anuncio en Adidas Football, pero acá sí están corriendo anuncios. 690 sería mucho para muchas empresas; para Adidas, para nada. Seguramente podrían hacer mucho más ahí. Y estuvimos revisando y no logramos encontrar que usen ese contenido en ningún anuncio activo. Hay que tener en cuenta que ese contenido obviamente fue creado pensando en el Mundial, y tiene como cuatro semanas. Estamos ahora a como 10 días [del Mundial], grabando esto desde el Mundial. Y no están usando esa pieza en formato pago. Eso parece una oportunidad desperdiciada, tirada ahí nomás. Se la perdieron. Sobre todo considerando cuánto habrán gastado en armar eso: les debe haber costado millones producirlo, sobre todo con todos esos nombres. Probablemente decenas de millones. Sí, sería muy fácil usar eso para vender productos. Claro, que es exactamente lo que Adidas quiere hacer.</t>
+          <t>Acá tienen 15 usos increíbles para Seedance 2 [corregido de "C Dance 2", error de reconocimiento] y cómo podés usarlo en tu publicidad. Voy a ir bastante rápido, así que asegurate de guardar este video para no perderlo. Número uno, anuncios estilo podcast. Este es el producto para vos. Es como un shot de espresso para tu cuenta de anuncios. Número dos, videos de prueba de outfits (probadores de ropa). Número 3, videos de recorrido inmobiliario (real estate walkthrough). Bienvenidos a esta casa de estilo medio siglo de 1969 en el codiciado barrio de Lake Wilderness. El nivel principal cuenta con un... Número 4, anuncios de entrevistas callejeras (street interview). Hola a todos, hoy le estamos preguntando a la gente qué piensan de Mr. Paid Social. ¿Qué piensan ustedes, chicas, de Mr. Paid Social? Creo que es realmente innovador. No creo que su segmentación (targeting) sea tan efectiva como podría ser. Escuché que es... Número 5, anuncios de producto cinematográficos. Número 6, anuncios estilo nota adhesiva (post-it). Número 7, anuncios estilo time lapse. Número 8, anuncios de showcase de unboxing de producto. ¡Hermano, por fin llegaron! ¡Mirá esto! Los detalles son una locura. El azul resalta en la parte de atrás. ¡Dale! Número 9, anuncios de probador de producto. Gimnasios. Terminé de probar estos. Número 10, videos de cosmética. Prueba de humectante. Bueno, en realidad es dewy/luminoso [corregido de "Dewey"]. Número 11, anuncios de destacado de característica (feature call-out). Si solo pudiera usar una gorra por el resto de mi vida, sería esta. Sin dudas. Corderoy de tres tonos, parche tejido, y esta correa ajustable para que le quede a cualquiera. Número 11 [así en el original, se repite el número — probablemente debería ser "12" [?]], anuncios de showcase de app. Esta app es increíble. Tiene tantas funciones que hacen que estudiar sea mucho más fácil. Número 13, anuncios estilo caricatura (cartoon). Las enfermedades cardíacas son la causa número uno de muerte en hombres. Número 14, videos de IA con pantalla verde (green screen). Todo dentro de la comunidad AI Ad Alchemist [?, nombre de comunidad poco claro en el audio]. Acá es donde podés venir a aprovechar la IA y la automatización para finalmente escalar tu app [?, posiblemente "tus anuncios/ads"]. Número 15, videos ASMR. Ay, dios mío, mirá eso. Nunca habíamos visto un modelo tan bueno haciendo anuncios de IA. Y si querés el link para probarlo, está en mi perfil. De estos 15 ejemplos, asegurate de seguirme porque hago mucho contenido mostrando cómo llevar tu media buying al siguiente nivel con IA.</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>Formato de dos personas hablando (uno con polo bordó) sentadas en un living con chimenea de fondo, en composición de pantalla dividida: mitad de arriba los dos reaccionando, mitad de abajo el clip del anuncio de Adidas que están comentando (formato duet/reacción). Más adelante corta a una captura de pantalla (screen recording) de la Meta Ads Library mostrando la búsqueda 'adidas' y sus resultados. Subtítulos blancos en minúscula, negrita, sincronizados palabra por palabra.</t>
+          <t>Grabación de pantalla de una computadora reproduciendo la interfaz de la herramienta de IA Seedance 2.0 (se ve el panel de generación con el prompt de texto y botones "Remix / Upscale / Extend / More") intercalada con clips de ejemplo generados por IA (mujer hablando a cámara estilo podcast con micrófono, una casa en el bosque tipo cabaña, un teléfono mostrando una app). Texto gráfico fijo en rojo/blanco con borde negro "SEEDANCE 2.0 JUST DROPPED / Here's 15 ad examples" superpuesto durante todo el video. Formato vertical con el video del ejemplo enmarcado dentro de la captura de pantalla más grande.</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Arranca directo reaccionando a un anuncio de alto impacto con celebridades (gancho de curiosidad + nombres famosos), sigue una estructura de análisis (calidad creativa y luego chequeo de datos reales en la Ads Library), y el gatillo es la revelación sorprendente de que Adidas no está pautando esa pieza pese a haber costado millones, sumado a la autoridad de mostrar data concreta.</t>
+          <t>Gancho de curiosidad/reto en el título ("¿podés notar que es 100% IA?") que invita a comentar, combinado con estructura de listicle numerado (15 ejemplos) que promete valor denso y variado; el pedido explícito de guardar el video genera retención y señal de guardado al algoritmo.</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Sí, pero requiere conocimientos de marketing y acceso a la Ads Library; la edición a pantalla dividida es sencilla de lograr con apps gratuitas.</t>
+          <t>sí, nota: cualquiera con acceso a Seedance 2.0 (u otra IA de video similar) y una pantalla para grabar puede replicar el formato listicle sin filmar nada propio.</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -3801,27 +3801,27 @@
     </row>
     <row r="36" ht="88" customHeight="1">
       <c r="A36" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3836,48 +3836,48 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1540</v>
+        <v>3692</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7667313471880547606</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7650235356842986775</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>En una entrevista al aire libre, Ben Heath cuenta cuánto gasta realmente en publicidad paga para su propia agencia y explica que el límite no es la demanda sino la capacidad de atender más clientes.</t>
+          <t>Matt Bell explica cómo usa Claude (IA de Anthropic) para analizar reportes de campañas pagas de Meta y Google, detectando por ejemplo caídas de conversión causadas por tráfico de afiliados.</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>¿Cuánto gastás en tu propia publicidad? Probablemente mucho menos de lo que la gente piensa, porque tengo, para el mundo de los anuncios de Meta, una base orgánica de seguidores muy grande. Casi siempre estamos limitados por la capacidad de entrega de nuestras distintas ofertas, más que por la demanda. Tenemos un ciclo que se repite: en algún momento generamos algo de capacidad extra en la agencia, prendemos los anuncios, gastamos como 5.000 dólares, y enseguida llegamos al límite de capacidad, entonces los apagamos de nuevo. Así que, la verdad, rara vez gastamos más de, digamos, 10 o 15 mil dólares en un mes. Podríamos gastar mucho más que eso si tuviéramos la capacidad para entregar, pero muchas veces no la tenemos. Y tenemos muy claro que preferimos decirle que no a un cliente, o al menos todavía no, y mantener un servicio de alta calidad, en vez de simplemente meter a la mayor cantidad de gente posible por la puerta.</t>
+          <t>Vengo usando mucho Claude para ayudarme a analizar las campañas de anuncios pagos que estoy corriendo últimamente, y se volvió extremadamente valioso, porque lo que puedo hacer es sacar muchos reportes distintos de distintos canales y después cargárselos a Claude, darle contexto y hacerle las preguntas correctas, lo cual me ayuda a dirigir las campañas y los canales en la dirección correcta. Así que acá, por ejemplo, hay capturas de pantalla de un chat que tuve con Claude para una marca que venía teniendo problemas con la tasa de conversión, que estaba bajando, y tienen afiliados que están mandando un poco más de tráfico del que deberían, y eso está impactando en las campañas de meta ads. Entonces estamos tratando de entender por qué está pasando esto, qué tenemos que sacar, y como estos chicos no están usando nada como Triple Whale [?, en el audio "Triple L"] o Hyros [?, en el audio "high rise"], en realidad no tenemos nada con modelos de atribución ni con el solapamiento (overlap). Así que lo que hago acá es entrar a GA4 y exportar un archivo CSV que muestra el rendimiento del tráfico por campaña UTM y por fuente UTM, y después cargo información sobre meta, y exporto distintas tablas de meta: a nivel de campaña, a nivel de anuncios, incluso algo de la creatividad del anuncio. Y exportamos métricas como costo por clic, click through, CPMs; saco reportes de si el CPM subió o bajó en los últimos 12 meses. Y cuando empezás a juntar toda esta información, puede ser un poco difícil armar un análisis sólido que explique qué está pasando o qué no está pasando. Y ahí es donde entra Claude, porque podés cargarle todo esto. Y una vez que ya armó ese contexto, podés empezar a hacerle preguntas para tratar de entender qué está pasando. Y como pueden ver, Claude es realmente bueno para visualizar estos datos a lo largo del tiempo. Entonces acá podemos ver, por ejemplo, cómo se ve la convergencia [?, posiblemente "conversión"] a lo largo del tiempo con Google para esta campaña específica que estamos corriendo. Lo podemos comparar con Facebook y podemos hacer un montón de otras cosas más. Y esa es la belleza de usar IA en media buying. Yo no hago que la IA corra ninguna de las campañas ni las configure, pero la estoy usando ahora para analizar toda esta información. Y está llegando a un punto en el que, al final de cada semana, voy a empezar a cargarle reportes específicos a Claude, que después me va a dar un resumen de qué está pasando.</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>Entrevista entre dos personas sentadas en sillas plegables de camping, encuadre de perfil (no miran a cámara, se miran entre ellos), fondo de pared de chapa corrugada y piso de ripio. Edición con corte a pantalla dividida (los dos hablando a la vez) y a planos individuales. Subtítulos blancos negrita sincronizados. Vestimenta casual (polo, remera), luz solar dura de exterior.</t>
+          <t>Sin talking head: fondo negro con título fijo en texto blanco ("How I'm using Claude with media buying"); debajo se muestra una captura de pantalla real de un chat/reporte sobre fondo blanco, y en un frame posterior se agrega un gráfico de líneas comparando canales. Se ve la barra de dock de macOS abajo, lo que sugiere una grabación de pantalla o edición simple tipo diapositivas con voz en off, sin subtítulos incrustados visibles en los frames capturados.</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>Pregunta directa como gancho (¿cuánto gastás en tus propios anuncios?), respuesta contraintuitiva con cifras reales como estructura, y el gatillo es la transparencia/autoridad de un experto compartiendo números concretos de su propio negocio.</t>
+          <t>Gancho de autoridad práctica ("cómo uso Claude para analizar campañas") sobre un dolor común del rubro (atribución confusa, afiliados inflando resultados), reforzado con prueba real (capturas de un chat/reporte real) en estructura de caso de uso paso a paso.</t>
         </is>
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Sí, es una entrevista informal grabada con poco equipo; el gancho son las cifras compartidas, no la producción.</t>
+          <t>sí, nota: solo requiere capturas de pantalla propias, una cuenta de Claude y una grabación de pantalla o edición básica de texto, sin cámara ni locación.</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -3893,32 +3893,32 @@
     </row>
     <row r="37" ht="88" customHeight="1">
       <c r="A37" s="2" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Venta del servicio</t>
+        <v>24</v>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Información</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Dara Denney</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3928,48 +3928,48 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>269</v>
+        <v>3681</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7637927133989440775</t>
+          <t>https://www.tiktok.com/@daradenney/video/7636400068785966367</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde cuenta el caso de un evento en vivo que generó más de $2 millones en 24 horas gracias a anuncios de Facebook que llenaron la sala, desglosando asistentes, tasa de cierre y costos del evento.</t>
+          <t>Dara Denney predice que los anuncios que muestran una conversación genuina (FaceTime, webinars, llamadas de coaching) van a ser la próxima tendencia creativa en Meta Ads porque son casi imposibles de imitar con IA, y presenta Riverside como herramienta para filmarlos.</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>Ahora tuve la oportunidad de asociarme con varios eventos locales y masterminds, todos los cuales tenían varios miles de personas en asistencia, gracias al poder de los anuncios de Facebook. Ahora estamos hablando de salas que recaudaron y vendieron más de dos millones de dólares en 24 horas, solo de la gente presente. En la sala misma, unas 900 personas presentes, más o menos [?] ("gave retake" en el original, probablemente "give or take"). Nuestro cliente terminó ofreciendo un producto de $10,000 que tiene. De esa sala, cerca del 20%, más o menos [?], convirtieron un poco más. Así que estos son los números reales: 217 personas terminaron cerrando esta oferta de $10,000, lo cual son $2.17 millones, sumado a los casi medio millón de dólares en venta de entradas. Ahora, en total costó — cuando digo "nosotros" me refiero a nuestro cliente — cerca de medio millón de dólares en gasto publicitario, más el equipo del evento y material, etcétera. Entonces el costo del evento fue de cerca de medio millón de dólares para organizar y montar este evento y llenar la sala, para después vender. Si contás la venta de entradas, cerca de 2.5 a 2.6 millones de dólares en productos vendidos durante este evento. Así que, de nuevo, un evento muy rentable visto de esa manera.</t>
+          <t>Esta nueva tendencia creativa va a dominar los anuncios de Meta en los próximos 90 días. Pero no les voy a mentir, es muy difícil de replicar con IA. Así que les voy a mostrar cómo Riverside puede ayudar. En el primer trimestre de 2026, las animaciones con IA, este... [?], los "hooks" (ganchos) y los anuncios de controversia eran el tipo de tendencia creativa que dominaba todos los feeds de los estrategas creativos y todas las cuentas publicitarias. Pero con este auge del contenido hecho con IA, también empezamos a ver la necesidad de eventos, de contenido largo y de conversación genuina. Mi corazonada es que los creativos publicitarios que muestran una conversación real van a ser lo próximo que haga escalar las cuentas publicitarias. Así que, obviamente, podés hacer una conversación entre dos personas en persona, o por FaceTime, o clips de un webinar online o de una llamada grupal de coaching. Vi que esto está explotando en contenido orgánico, y creo que le va a ir muy bien en anuncios porque es prácticamente imposible de falsificar. Esa va a ser la diferencia en lo que funciona, ¿no? Lo que es difícil de replicar con IA, que es la conversación genuina. Ahora, este tipo de contenido en particular es muy difícil de filmar, porque en realidad no podés grabar la pantalla de una llamada de FaceTime. Hasta probé filmar una de estas por Google Meet, que es un embole total porque solo te filma a uno de los dos a la vez. Si la hubiéramos filmado con Riverside, habría sido mucho más fácil. Cada persona se graba localmente en una pista separada en 4K, lo que significa que los problemas de wifi no van a afectar la calidad. Y si estás haciendo una llamada larga o un webinar, su edición de "magic clips" también genera clips automáticamente que podés editar fácilmente, para poder sacar contenido a la calle mucho, mucho más rápido. Así que tengo curiosidad: ¿ya probaste anuncios que muestren una conversación genuina? Comentá "Riverside" y te mando más detalles.</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto, webcam fija en el mismo living/oficina con planta y cuadro, micrófono de brazo. Subtítulos blancos simples. Un breve inserto gráfico de ícono de perfil con notificación en rojo ("705") sobre fondo negro, posiblemente a modo de intro. Edición mínima, sin gráficos de datos pese a hablar de cifras.</t>
+          <t>Talking head (mujer pelirroja, sweater, micrófono inalámbrico con espuma) en un ambiente hogareño (espejo, estantería de fondo). Incluye un segmento tipo "duet"/simulación de videollamada con pantalla dividida (ventana pequeña de ella arriba, otra mujer simulando una llamada de FaceTime abajo con un globo de texto simulado) para ilustrar el concepto, y un gráfico con el logo "RIVERSIDE" superpuesto sobre la imagen. Subtítulos progresivos.</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>bajo</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Gancho de resultado extremo y concreto ("$2 millones en 24 horas"); estructura de desglose numérico paso a paso que aporta credibilidad; gatillo de aspiración/prueba social con caso real de cliente.</t>
+          <t>Predicción de tendencia con plazo concreto ("esto va a dominar en 90 días") combinada con tensión ("es muy difícil de replicar con IA"). Estructura de contexto de tendencias pasadas, hipótesis propia, demostración práctica del problema (dificultad de grabar un FaceTime) y solución/producto (Riverside), cerrando con un llamado a la acción interactivo en comentarios. El gatillo combina predicción de tendencia, demostración del problema real y solución concreta.</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>sí, solo cámara y micrófono, historia y cifras propias; casi sin edición.</t>
+          <t>sí en el guion (predicción + problema + solución), aunque la demo tipo "duet"/simulación de videollamada exige un poco más de edición y una segunda persona.</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -3985,27 +3985,27 @@
     </row>
     <row r="38" ht="88" customHeight="1">
       <c r="A38" s="2" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Mitch Barham (Beardpreneur)</t>
+          <t>Chase Chappell</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4020,48 +4020,48 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3813</v>
+        <v>3637</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@beardpreneur/video/7654413458217209101</t>
+          <t>https://www.tiktok.com/@chase_chappell/video/7670568658346790174</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>En formato de respuesta a un comentario, Mitch usa una infografia de embudo (arriba/medio/abajo del funnel) para explicar que la mayoria de las cuentas arrancan pidiendo la venta demasiado pronto, y que al escalar a presupuestos de 6 cifras multiples por mes hay que volver a llenar la parte alta del embudo con contenido de awareness.</t>
+          <t>Chase Chappell compara, punto por punto, cómo operan las marcas de e-commerce que facturan 100 mil dólares al mes contra las que facturan 1 millón: cantidad de anuncios activos, diversidad creativa, cadencia de lanzamiento, métricas que miran, optimización de la landing page y segmentación por buyer persona, cerrando con un llamado a comentar para recibir un lead magnet.</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>Asi que, tecnicamente, todos estamos usando mal los anuncios de Facebook. Mira, durante anos todo fue conversiones, conversiones, conversiones. O leads, leads, leads. Cuando en realidad, la parte alta del embudo deberia ser algo como tu engagement, tus reproducciones de video, tu contenido de redes sociales, o el objetivo de 'ver contenido'. Olvidate del trafico. Pero ahi estas calentando a la gente. Pero todos arrancamos aca, en el medio del embudo, con consideracion e intencion, y directamente vamos a lo 'a la mierda, compren nuestras cosas'. ¿Que estas haciendo? Compra nuestras cosas. Registrate ahora mismo, y despues se lo metemos por la garganta con un presupuesto chico. Si, arranca aca. ¿Por que no? No hace falta estar arriba. Cuando empezamos a gastar multiples 6 cifras por mes, tenemos que llenar la parte de arriba del embudo, que es a lo que se referia el tipo que respondio a mi video. A esto le decimos 'Tippy Top' (la puntita de arriba). Estamos llenando el balde aca arriba, moviendolos hacia aca, y finalmente hacia abajo, la parte baja del embudo, donde el anuncio es estrictamente nada mas que 'che, vengan a comprar nuestras cosas'. El problema es que entrenamos a todo el mundo para ir siempre directo a la yugular y querer la venta ya. Esto no funciona. Es como intentar casarte con alguien de una asi de rapido, en vez de salir con esa persona y dejar que realmente te conozca, para despues decirle 'che, ¿queres comprar nuestras cosas?'.</t>
+          <t>Marcas de 100 mil al mes versus marcas de 1 millón de dólares al mes: acá está la diferencia. Las marcas de 100 mil al mes solo corren de 30 a 50 anuncios activos; una marca de un millón de dólares al mes corre de 300 a 750 anuncios activos. Las marcas de 100 mil al mes se enfocan en unos pocos formatos básicos, mayormente tomas de producto, videos simples y ofertas directas. Una marca de un millón al mes está corriendo cada formato que te puedas imaginar: anuncios de UGC (contenido generado por usuarios), anuncios de colaboración paga, demos de producto destacando beneficios, reseñas de clientes, comparaciones, videos del fundador, contenido educativo, antes y después, con diferentes ganchos, ángulos, creadores y ofertas. Construyen diversidad creativa en toda la cuenta publicitaria. La marca de 100 mil al mes lanza pocas creatividades por mes; la marca de un millón al mes lanza anuncios nuevos todas las semanas, a veces más de 50 creatividades nuevas por vez, porque saben que el volumen de creatividades es lo que les permite seguir escalando sin que el rendimiento caiga o sin llegar a la fatiga publicitaria. La marca de 100 mil al mes solo mira el ROI inmediato; la marca de un millón al mes está obsesionada con los ratios de [?LTV, en el original dice 'CTV'], las suscripciones, los compradores recurrentes y el AOV (valor promedio de pedido). Saben que si logran que cada cliente valga más, se pueden dar el lujo de gastar más para adquirirlo, y por eso están escalando. La marca de 100 mil al mes casi no se enfoca en la optimización de la tasa de conversión, y mandan el tráfico a una página de producto básica con la esperanza de que la gente compre; la marca de un millón al mes manda el tráfico a PDPs (páginas de producto) y landing pages para clientes totalmente desarrolladas. Responden todas las objeciones del comprador, explican el producto, muestran pruebas, ofrecen suscripciones, y hacen que la decisión de compra se sienta obvia. La marca de 100 mil al mes se enfoca en un solo avatar de cliente; la marca de un millón al mes construye anuncios para cada persona a la que le puedan llegar a vender: mamás, atletas, médicos, profesionales ocupados, gente con problemas digestivos, gente que intenta bajar de peso, gente que intenta dormir mejor. Cada persona tiene su propio gancho, creatividad, punto de dolor y oferta. Esa es la verdadera diferencia. La marca de 100 mil al mes corre anuncios; la marca de un millón al mes construye todo un sistema de creatividad y conversión. Comentá 'ads' y te mando los mejores anuncios para correr en 2027.</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>Formato de respuesta a comentario (incluye la burbuja del comentario original: 'Did you just say TOFU is middle of funnel?'), con una infografia de embudo de marketing (TOP OF FUNNEL azul, MIDDLE OF FUNNEL verde, BOTTOM OF FUNNEL amarillo, cada uno con iconos de sus acciones tipicas) superpuesta detras/alrededor del presentador durante todo el video. Talking head con gestos de mano marcados, subtitulos dinamicos con palabras clave resaltadas en rosa/magenta.</t>
+          <t>Formato con capturas de pantalla como B-roll: Meta Ads Library de la marca AG1 con un círculo rojo dibujado sobre '~630 results', primer plano de un producto (bolsa de AG1), captura de pantalla de un checkout con planes de suscripción (NZ$), presentador en la parte inferior de cada plano hablando a cámara con micrófono, subtítulos blancos, estructura con múltiples cortes alternando entre B-roll/capturas y talking head.</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>Gancho de afirmacion polemica y validadora ('todos lo estamos haciendo mal'); estructura de respuesta a un comentario que aprovecha una conversacion previa como prueba de engagement/autoridad, combinada con una infografia clara que ensena un framework (TOFU/MOFU/BOFU) mientras habla; gatillo de identificacion para cuentas grandes que ya sienten ese dolor, reforzado con lenguaje directo y coloquial.</t>
+          <t>Gancho: comparación aspiracional con emoji de shock ('$100K vs $1M, así de diferente'). Estructura: seis comparaciones paralelas en el mismo formato (X hace esto, Y hace esto otro) que aceleran el ritmo y facilitan la retención -&gt; cierre con CTA de comentario para lead magnet. Gatillo: aspiración de escalar a $1M + FOMO + prueba con marca real y evidencia visual (AG1 en Meta Ads Library) + CTA de bajo esfuerzo que además genera engagement/alcance.</t>
         </is>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
-          <t>sí, la infografia requiere algo de diseno previo pero es reutilizable, y el resto es solo camara y opinion hablada.</t>
+          <t>no/medio + Requiere investigación previa en Meta Ads Library y grabación de pantalla de sitios de la competencia, bastante más tiempo de preproducción que un talking head simple.</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       <c r="C39" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Solución de un problema</t>
         </is>
@@ -4169,15 +4169,15 @@
     </row>
     <row r="40" ht="88" customHeight="1">
       <c r="A40" s="2" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4204,33 +4204,33 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1463</v>
+        <v>2827</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7666767722230959367</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7621602508879727904</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Maddi propone 3 tipos de creatividad para marcas 'desire first' (que venden deseo/estilo de vida): anuncio de deseo (top of funnel), anuncio de fundador/marca (middle of funnel) y anuncio de prueba social (bottom of funnel), como ejemplo de diversificación real de contenido.</t>
+          <t>Ben Heath anuncia que los anuncios en Threads, antes exclusivos de EE.UU., ahora se lanzaron globalmente, sumando nuevos formatos (carrusel, catálogo, apps) para alcanzar a los más de 400 millones de usuarios activos mensuales de la plataforma.</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>Si yo estuviera manejando una cuenta de anuncios para una marca "desire first" (que vende primero el deseo), acá hay 3 tipos de creatividad que lanzaría, y ninguno es otra toma de marca o de producto (product shop). El primero es un anuncio de deseo (desire ad). Esto vende el estilo de vida, no el producto. Pensá en un "fit check" o cuando una chica se prueba un outfit y le encanta cómo se ve. El deseo es lo que realmente gana el clic. Esto es tu top of funnel. El segundo es el anuncio de fundador o de marca. Puede ser hablando a cámara, puede ser b-roll con voz en off. Esto es el porqué detrás de la marca, la historia detrás de ese producto específico, o incluso la decisión que casi no tomaste. La gente no compra por lógica, compra por creencia. Esto es lo que construye confianza, y eso es tu middle of funnel. El tercero son tus anuncios de prueba social. Gente real, escenarios reales. Pensá en ese cumplido no solicitado, o en ese mensaje de una amiga que dice "¿de dónde sacaste eso?". La historia que ella publicó sin etiquetar tu marca. La prueba es lo que cierra a la gente que el deseo trajo. Y por supuesto, esto es tu bottom of funnel. Así que pueden ver tres formatos, tres etapas del funnel. Eso es diversificación, no tres versiones de una toma de producto. Así que recuerden: el deseo gana el clic, la marca construye la confianza, y la prueba lo cierra. Y necesitás las tres.</t>
+          <t>Tengo una noticia importante en cuanto a los anuncios en Threads. Antes, los anuncios en Threads solo se mostraban en Estados Unidos, pero ahora se lanzaron a nivel global. Así que si no estás en Estados Unidos, es probable que empieces a ver anuncios en Threads en breve. También tenemos ahora más formatos de anuncio que podemos usar en esa plataforma. Así que en lugar de solo anuncios básicos de feed, ahora también podemos correr anuncios carrusel, anuncios de catálogo, anuncios de apps. Así que tenemos más flexibilidad como anunciantes para alcanzar a los más de 400 millones de usuarios activos mensuales que hay actualmente en Threads.</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>Combina talking head (mujer sentada en sillón claro, top con texto animado en rojo tipo "are" superpuesto) con clips de ejemplo/B-roll de una marca real (se ve un video borroso con boceto de moda de fondo y watermark de TikTok "@zimmermann") y tarjetas de texto grandes tipo tipografía editorial ("PROOF is what closes the") sobre fondo color crema. Más variedad de recursos visuales (cortes a ejemplos + tipografía grande) que otros videos de la cuenta.</t>
+          <t>Encuadre: plano medio sentado, formato podcast con micrófono. Subtítulos: palabra por palabra en mayúsculas, con una palabra clave ('ON') resaltada en azul. Cortes: toma continua. Gráficos: solo el color del subtítulo. Locación: interior tipo cocina/comedor con reloj de pared y planta de fondo.</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>Gancho de utilidad segmentada (dirigido específicamente a marcas "desire first") con framework simple de 3 tipos ligado a las 3 etapas del funnel, fácil de recordar, reforzado con un cierre tipo mantra ("el deseo gana el clic, la marca construye confianza, la prueba cierra") que funciona como frase citable.</t>
+          <t>Gancho: anuncio de 'noticia importante' sobre una plataforma específica, genera expectativa inmediata. Estructura: qué cambió (alcance global), qué hay de nuevo (formatos de anuncio), por qué importa (tamaño de audiencia alcanzable). Gatillo: la noticia posiciona al creador como fuente actualizada y confiable, lo que favorece que se guarde/comparta como referencia.</t>
         </is>
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: la base es talking head con guion claro; usar clips de ejemplo de otras marcas como ilustración es opcional y de bajo costo.</t>
+          <t>Sí — mismo setup casero simple (mic + sala) que otros videos del mismo creador.</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4261,22 +4261,22 @@
     </row>
     <row r="41" ht="88" customHeight="1">
       <c r="A41" s="2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -4296,48 +4296,48 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1333</v>
+        <v>2569</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7618955944449297696</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7624497738855583008</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath explica cómo cambian las campañas de Meta Ads según el presupuesto diario invertido: $10, $100, $1.000 y $10.000 al día, y qué debería priorizar el anunciante en cada nivel.</t>
+          <t>En formato de entrevista, Ben Heath responde cual es el error mas comun de los anunciantes en Meta Ads: no dejar en paz las campanas y tocarlas constantemente, lo que impide salir de la fase de aprendizaje y lleva a decisiones basadas en ruido en vez de datos.</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>Así se ven los anuncios de Meta con $10 al día, $100 al día, $1.000 al día y $10.000 al día. Con $10 al día, solo estás tratando de conseguir una prueba de concepto. ¿Realmente podés generar ventas? ¿Realmente podés generar leads con las campañas publicitarias que produjiste? Con $100 al día, Meta está empezando a aprender. Estás empezando a generar algunas conversiones. Podés hacer un poco de testeo. Es poco probable que sea un impulsor significativo de los ingresos de tu negocio, pero ya tenés impulso (momentum). Con $1.000 al día, necesitás sistematizar el proceso. Estás escalando lo que funciona. Estás rotando los creativos regularmente, y estás tomando decisiones basadas en datos. Con $10.000 al día, necesitás una máquina de producción de creativos publicitarios. Necesitás estar agregando constantemente anuncios de testimonios de clientes [?] (transcripto como "Clyde testimonial ads", probable error de reconocimiento de "client testimonial ads"), anuncios de partnership (alianzas) y creativos hechos internamente (in-house). También sueles enfocarte, en este nivel, en la incrementalidad y en exprimir todo lo que puedas de tus campañas publicitarias. Y ahora ya sabés...</t>
+          <t>¿Cual es el error mas grande que ves que comete la gente en las campanas de anuncios de Meta? El error mas comun que veo que comete la gente en las cuentas de anuncios de Meta va a ser que la gente no puede dejar sus cuentas de anuncios en paz. Ajustando y testeando constantemente y metiendo un anuncio aca. Cuando hacen eso, nunca salen de la fase de aprendizaje. Nunca le dan tiempo a Meta para estabilizar las campanas. Ven resultados increiblemente volatiles. Le atribuyen mal los resultados a los cambios que acaban de hacer. Y puede no tener nada que ver con eso. Podria ser que de todas formas ibas a tener un buen dia o un mal dia. Entonces no estan tomando decisiones basadas en datos. Estan mucho mejor si simplemente le dan mas tiempo a las cosas, se dan un cronograma de optimizacion y dicen 'solo voy a ajustar mis campanas una vez cada siete dias, o una vez cada 10 dias', algo asi.</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>Talking head a cámara fija, plano medio, en interior con fondo neutro (pared blanca/gris con panel geométrico tipo estudio). Viste polo bordó. Grandes overlays de texto con las cifras en dólares (naranja, amarillo, verde) en la esquina superior izquierda que cambian según el tramo del que habla, más subtítulos en mayúscula blanca centrados en la parte baja, sincronizados por palabra/frase. Un solo plano, sin cortes de cámara ni b-roll adicional.</t>
+          <t>Toma continua a camara en interior sencillo (paredes blancas, cuadro enmarcado, planta), microfono de podcast visible sobre la mesa; subtitulos blancos que siguen el audio palabra por palabra, sin graficos adicionales; formato de pregunta y respuesta tipo entrevista/podcast.</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>Gancho de curiosidad numérico ("así se ven los anuncios con distintos presupuestos") + estructura de lista clara en 4 escalones crecientes + gatillo de autodiagnóstico práctico: el espectador identifica en qué nivel de gasto está y qué debería hacer a continuación.</t>
+          <t>Gancho de pregunta directa ('What's the biggest mistake...?') que promete un error concreto a evitar; estructura de explicacion causa-efecto (tocar demasiado, nunca sale de fase de aprendizaje, decisiones mal atribuidas) con solucion accionable al final (ajustar cada 7-10 dias); gatillo de autoridad conversacional: se siente como consejo genuino de experto en vez de anuncio.</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>sí + con celular, micrófono de solapa y un editor con texto animado alcanza; no requiere locación especial ni equipo caro.</t>
+          <t>si, solo requiere una camara, un microfono y responder una pregunta con criterio propio.</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4353,17 +4353,17 @@
     </row>
     <row r="42" ht="88" customHeight="1">
       <c r="A42" s="2" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Información</t>
+        <v>27</v>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4388,33 +4388,33 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1219</v>
+        <v>2569</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7626399562290171168</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7645570700857724167</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath explica una estrategia para construir marca (no solo generar ventas) usando Meta Ads, combinando anuncios protagonizados por el fundador con anuncios de partnership con creadores e influencers.</t>
+          <t>Maddi (agencia MADE.) cuenta el caso de una marca de moda de ticket alto (AOV 300-600 USD) a la que ayudaron a pasar de perder dinero en adquisición de clientes nuevos a duplicar esos ingresos, cambiando el tipo de contenido creativo y la estructura de campañas en Meta.</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>Así es como construís una marca con los anuncios de Meta. La mayoría de los negocios usan los anuncios de Meta para generar leads y ventas, y eso tiene sentido, pero si lo hacés de forma inteligente, también podés construir una marca al mismo tiempo si usás una combinación de anuncios protagonizados por el fundador (founder-led ads) y anuncios de partnership, donde te asociás con creadores e influencers para promocionar tus productos y servicios en tu nombre. Si te asociás con la gente correcta y le acertás al tono, los valores que tu público objetivo asocia con esos creadores e influencers pueden trasladarse a tu marca con el tiempo.</t>
+          <t>Gastamos $20,000 para generar $100,000 para esta marca de moda, y les voy a mostrar exactamente qué hicimos para lograrlo. Esta clienta de moda realmente tenía una base de clientes leales. Generaban compras recurrentes, pero la adquisición de clientes nuevos específicamente a través de meta ads les estaba haciendo perder dinero. Además, sus productos van, digamos, de 300 a 600 dólares de AOV (ticket promedio). Entonces pedirle a un cliente nuevo que se comprometa con una compra de ese tamaño siendo una marca desconocida es muy difícil. La marca solo había corrido imágenes de campaña o contenido de e-commerce, nada que mostrara el estilo de vida o a la mujer de todos los días. Como sabemos, la moda es una compra aspiracional, y el consumidor quiere ver momentos que representen su vida real, donde las prendas realmente se estén usando. De la misma manera, con contenido de styling en un producto de precio alto, empezamos a mostrar más contenido de versatilidad: la misma parte de arriba con distintas partes de abajo, el vestido combinado de formas muy distintas. Suena lógico, pero esta marca solo estaba explotando ese único pilar de contenido de campaña y de e-commerce. La agencia anterior en realidad nunca usó exclusiones [corregido de "explosions"/"explosiones", error de reconocimiento] en su campaña, lo cual hizo que meta se pusiera muy vago/perezoso. En nuestra campaña de prospección, ajustamos bien esas exclusiones para lograr que meta se enfocara fuera de los clientes tibios o existentes, ya que solo tenían drops (lanzamientos) y no recurrencia de los más vendidos (best sellers). Armamos esto como una campaña CBO múltiple, con distintos ad sets por categoría de producto, y dejamos que meta intentara encontrar los productos ganadores y también las creatividades ganadoras. Si encontrábamos creatividades ganadoras o productos ganadores, los separábamos en su propia campaña y la corríamos con presupuesto para ayudarlos a agotar stock. Su marca siempre fue ganadora, pero su estrategia de anuncios simplemente estaba frenando su verdadero crecimiento. No solo logramos esto en pocas semanas, sino que durante los primeros seis meses trabajando juntos, de hecho duplicamos sus ingresos de clientes nuevos.</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: plano medio, con cambio de ángulo entre frames (perfil en uno, frontal en otro), lo que sugiere cortes de cámara. Subtítulos: palabra por palabra en mayúsculas. Cortes: salto entre distintos ángulos de cámara (jump cuts). Gráficos: captura de un anuncio real de Meta (perfil 'Ben Heath', texto 'I gave recently...', botón 'Learn more') insertada como prueba. Locación: living con sofá, lámpara y caballete de arte de fondo.</t>
+          <t>Talking head en formato entrevista/testimonio: mujer sentada en sillón color crema, fondo liso beige, plano medio fijo, sin cortes de cámara visibles en los frames revisados. Subtítulos incrustados en dos estilos: un titular manuscrito ("loyal customer base") arriba, y captions estilo palabra por palabra abajo en la parte inferior del video.</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>Gancho: promesa directa en la primera frase ('así es como construís una marca'). Estructura: reencuadre de la creencia común (los anuncios solo sirven para leads/ventas) hacia una posibilidad menos obvia (construir marca), seguida del método concreto (founder-led + partnership ads) y el mecanismo (transferencia de valores). Gatillo: muestra su propio anuncio real como prueba social/autoridad.</t>
+          <t>Gancho numérico fuerte en el título ($20,000 invertidos → $100,000 generados) que promete un caso de éxito cuantificado, con estructura de diagnóstico/qué cambiamos/resultado tipo case study y cifras reales que dan autoridad y curiosidad por el "cómo".</t>
         </is>
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>Sí — hablar a cámara en un living con un solo screenshot de anuncio como apoyo visual, sin edición compleja.</t>
+          <t>sí, nota: solo requiere una persona hablando a cámara con buena luz y un fondo prolijo, sin locación ni equipo caro.</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -4445,15 +4445,15 @@
     </row>
     <row r="43" ht="88" customHeight="1">
       <c r="A43" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
+        <v>84</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -4480,33 +4480,33 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1052</v>
+        <v>2420</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7641896333955058977</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7631128226135411986</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath explica un método de cuatro pasos, totalmente gratis, para espiar qué anuncios de Meta están corriendo los competidores usando la Biblioteca de Anuncios.</t>
+          <t>Maddi presenta un framework de 5 pasos para el 'anuncio de misión/visión' en marcas de moda y joyería: gancho de identidad, mostrar el oficio (craft), conectar con la vida real de la clienta, prueba social y cierre en un único producto hero.</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>Acá tenés un método de cuatro pasos para espiar gratis los anuncios de Meta de tus competidores. Paso 1, muy simple: andá a la Biblioteca de Anuncios [Ads Library], una herramienta completamente gratuita. Paso 2: buscá a tus competidores; podés ver exactamente qué anuncios están corriendo. Paso 3: ordená por impresiones, de mayor a menor. Esto es importante: ahora podés ver no solo los anuncios que están corriendo tus competidores, sino cuáles están recibiendo más inversión. Si combinás eso con los anuncios que llevan más tiempo corriendo, también podés ver cuándo se lanzó un anuncio por primera vez. Esos son tus ganadores: son los que probablemente les están dando los mejores resultados a tus competidores, y esos son los que en el Paso 4 vas a querer tomar como modelo. Te recomiendo que te bases en varios competidores distintos, no en uno solo. Y si querés ver un tutorial completo y a fondo sobre la Biblioteca de Anuncios, tengo uno que podés encontrar en mi canal de YouTube.</t>
+          <t>Hay un formato de anuncio al que siempre vuelvo con prácticamente todos mis clientes de moda y de joyería, literalmente casi todos los clientes con los que trabajo, y sigue funcionando muy bien dentro de la cuenta de anuncios. Y como dije, con cada cliente para el que lo armo, se convierte en uno de los anuncios que más tiempo dura corriendo, recibe mucho presupuesto, y por lo general consigue un CPA realmente bueno. Pero lo más importante es que construye marca, y yo lo llamo el anuncio de misión o visión. Y creo que para las marcas de moda y de joyería específicamente esto está subestimado, y no es un video testimonial, no está vendiendo el producto, está mostrando el porqué detrás de la marca. Ahora, cada vez que armé esto, seguí una estructura específica que les voy a mostrar paso a paso. Y como mencioné, siguiendo este formato, sigue ganando dentro de la cuenta de anuncios. Así que acá está el framework. Tiene cinco secciones y, como dije, sigo exactamente esta fórmula cada vez. El paso 1 es el gancho de identidad. Abrís con para quién es esto, no con el producto, no con una oferta. Nombrás a la persona específica; esto está hecho específicamente para ella. Si no es esa persona específica, querés que siga scrolleando. El número 2 es revelar el oficio/la manufactura (craft), no el producto, el craft. Puede ser la costura, la tela, el calce, la fabricación; esto no se debería ver nunca en una foto de producto típica de e-commerce. Estás diciendo que realmente nos importa cómo hicimos esto y el porqué detrás de por qué lo hicimos, o de este calce específico. Por eso la gente se va a quedar y va a seguir mirando. Y después, en el framework, el número 3 es el "por qué" (the why). Acá querés conectar el producto con la vida real de ella. Y no estoy hablando de styling versátil, "perfecto para cualquier ocasión". Quiero que te pongas tan específico en ese momento puntual que ella se sienta realmente vista y entienda: sí, en ese momento específico de mi vida, soy yo usando ese producto específico. Después el número 4 es, por supuesto, la prueba social. Necesitamos esto: pueden ser reseñas, fotos de UGC (contenido generado por usuarios), cuántas unidades vendiste. Cualquier cosa que genere confianza con tu audiencia es lo que queremos aportar acá. Y por supuesto, el número 5 es cerrar con ese producto, un solo producto hero (estrella). No "mirá nuestra colección", nombrá ese producto hero para que quede grabado en su cabeza. Entonces, como mencioné, la razón por la que este formato sigue ganando es porque hace algo que la mayoría del contenido pago no hace: hace que la clienta se sienta vista antes de pedirle que haga una compra.</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>Arranca con una tarjeta de título diseñada (fondo tipo hormigón con trazos de marcador rojo) con el texto 'Top Secret: Methods to spy on competitors Meta Ads'. Corta a talking head sentado a una mesa, pared clara con cuadros de fondo, polo oscuro con micrófono clip. Subtítulos en mayúsculas, blancos y negrita (estilo distinto al de otros videos del mismo creador), estructurados como pasos numerados.</t>
+          <t>Talking head en primer plano (más cerrado que en otros videos de la misma cuenta), fondo blanco con logo "MADE." en la pared, título fijo tipo banner blanco con borde negro arriba ("This Ad Format KEEPS Performing... Here's How To Do It"), aire acondicionado visible detrás. Mismo encuadre estático en los tres frames revisados, sin cortes evidentes de cámara.</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>Portada 'top secret' como gancho de curiosidad, estructura tipo tutorial en 4 pasos fácil de seguir, y el gatillo es la promesa de valor gratuito y accionable (espiar a la competencia sin pagar nada).</t>
+          <t>Gancho de curiosidad/autoridad ("este formato SIGUE funcionando... así se hace") combinado con promesa de framework numerado y accionable (5 pasos) que da estructura fácil de recordar, y cierre con una frase citable ("hace sentir vista a la clienta antes de pedirle que compre").</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>Sí, solo necesita una tarjeta de título simple y hablar a cámara siguiendo una estructura de pasos.</t>
+          <t>sí, nota: es un video educativo de talking head con guion estructurado, replicable con celular, buena luz y un fondo prolijo.</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
     </row>
     <row r="44" ht="88" customHeight="1">
       <c r="A44" s="2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4572,33 +4572,33 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>965</v>
+        <v>2311</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7603330394024365344</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7641134699745643783</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath explica cómo estructurar una secuencia de anuncios de Meta que "cuente una historia": primero valor, luego demostración del producto, después testimonio, y por último anuncios de venta directa con llamado a la acción.</t>
+          <t>Maddi audita una cuenta de Meta Ads que gasta $300,000/mes y detalla tres errores principales: frecuencia demasiado alta, falta de un criterio único de testeo (CBO/ABO) por campaña, y cadencia de creatividades insuficiente.</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>Así es como contás una historia con los anuncios de Meta. Podés configurar tus anuncios para que se entreguen en una secuencia y así educar a tu audiencia de la manera que quieras. Por ejemplo, si estoy vendiendo una oferta de alto ticket (precio alto), voy a empezar entregando valor. Después voy a demostrar cómo funciona el producto o servicio. Luego voy a seguir eso con un testimonio, y después voy a incluir anuncios más orientados a la venta con llamados a la acción (call to actions). Ahora ya sabés eso.</t>
+          <t>Acabo de auditar una cuenta de anuncios que gasta $300,000 en meta ads, y estos son los principales errores que están matando la cuenta. Número uno es la frecuencia. Para una cuenta de este tamaño esperaríamos una frecuencia de alrededor de 2, pero al desglosar cada anuncio individual, el 80% tenía una frecuencia de dos o más, lo que significa que no estaban introduciendo conceptos nuevos que mejoraran el top of funnel ni yendo detrás de alcance neto nuevo (net new reach), que es súper importante. Queremos asegurarnos de que nuestra cuenta de anuncios tenga suficientes creatividades con una frecuencia de 1.5 o menos, para ampliar nuestro alcance neto nuevo. El número 2 es la forma en que estaban testeando, ya sea CBO o ABO. Esto puede marcar una diferencia real en toda tu cuenta, pero dentro de sus campañas tenían activos (assets) divididos por producto, activos divididos por persona (audiencia) y activos divididos por creatividad. Tenés que elegir uno y mantenerlo dentro de esa campaña específica para poder realmente diseccionar los resultados que estás recibiendo. Número tres es nuestra cadencia de creatividades. Para una cuenta que gasta esto, esperaríamos lanzamientos (drops) semanales dentro de la cuenta de anuncios, y querríamos al menos entre 10 y 15 creatividades, si no más, para tener no solo volumen de creatividades sino también diversificación de creatividades. Esta cuenta solo estaba agregando en sprints quincenales, lo cual simplemente no alcanza para una cuenta que gasta esto.</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>Talking head en interior tipo living/hogar, con una planta y un televisor de fondo, luz natural suave, polo celeste. Subtítulos palabra por palabra en blanco/negrita centrados; en un momento se superpone la captura de pantalla de una publicación real con comentarios/reseñas como ejemplo visual. Un solo plano fijo, sin cortes de cámara.</t>
+          <t>Talking head en primer plano, saco blanco/crema, fondo blanco con logo "MADE." detrás, título fijo blanco con borde negro arriba ("I Just Audited A Meta Account Spending $300,000 p/m"). Encuadre y locación prácticamente idénticos en los tres frames, sin cortes visibles.</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>Gancho directo de promesa de método ("así se cuenta una historia con anuncios de Meta") + estructura de framework en 4 pasos fácil de recordar (valor → demo → testimonio → venta) + gatillo de utilidad y aplicabilidad inmediata para cualquier negocio de alto ticket.</t>
+          <t>Gancho de cifra alta y autoridad ("auditoría de una cuenta de $300k/mes") combinado con formato listicle de errores numerados que promete valor práctico inmediato y aplicable a cualquier cuenta, generando FOMO de estar cometiendo los mismos errores.</t>
         </is>
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>sí + solo hace falta cámara casera, subtítulos automáticos y una captura de pantalla de ejemplo como apoyo visual.</t>
+          <t>sí, nota: video de opinión/consejo a cámara sin locación especial, replicable con celular y buena luz; el valor está en el conocimiento del tema, no en la producción.</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -4629,17 +4629,17 @@
     </row>
     <row r="45" ht="88" customHeight="1">
       <c r="A45" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -4664,33 +4664,33 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>919</v>
+        <v>2081</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7626005293658361121</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7644104846248774920</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath contrasta el comportamiento de los anunciantes principiantes (reactivos, atados emocionalmente al ROAS diario) con el de los profesionales (más pacientes, dispuestos a sacrificar ROAS a corto plazo para lograr escala).</t>
+          <t>Maddi explica por qué escalar el anuncio 'top' de una cuenta puede ser un error si en realidad es un anuncio de retargeting disfrazado de ganador, y cómo detectarlo revisando la frecuencia en ventanas de 7, 14 y 30 días.</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>¿Cuál es la mayor diferencia entre los anunciantes de Meta pro y los principiantes? Los anunciantes principiantes son demasiado reactivos y están emocionalmente atados a sus campañas. He visto a muchos anunciantes principiantes cuyo estado de ánimo y bienestar general está totalmente dictado por cuál fue su retorno de la inversión publicitaria (ROAS) ese día hasta el momento. Los anunciantes pro entienden que las cosas llevan más tiempo. Le dan más estabilidad a las cosas. También juegan el juego de otra manera: los anunciantes profesionales muchas veces van a sacrificar el retorno de la inversión publicitaria a corto plazo a cambio de escala. Eso puede significar pagar más por adquirir un cliente, no menos. Pero sabiendo que lo recuperás en el valor de vida del cliente (LTV), lo recuperás en referidos, porque tu producto o servicio es tan bueno. Así que, muchas veces, los mejores anunciantes no logran los mejores números de retorno de la inversión publicitaria, pero muy seguido operan a la mayor escala.</t>
+          <t>Acabo de hacerme cargo de una cuenta que gasta $50,000 por mes en meta, y este fue el error más grande que vi, y realmente el error más grande que estoy viendo que comete todo el mundo en su cuenta de anuncios: escalar un anuncio que no debería escalarse. Déjenme mostrarles exactamente a qué me refiero. Cuando miran su anuncio top, capaz miran cuál es su CPA y cuántas compras están generando, y piensan "fantástico, voy a escalar esto", ya sea dentro de este ad set o en una campaña separada, una campaña de escalado. Pero lo que la gente no llega a mirar es la frecuencia de ese anuncio, porque puede estar disfrazado de anuncio de bottom of funnel que está teniendo un CPA excelente, excelentes resultados, y pensás "bueno, si lo saco solo o lo escalo más, va a dar estos mismos resultados". Pero la razón por la que este anuncio está funcionando tan bien es por la creatividad de top of funnel que lo está alimentando, y en realidad está disfrazado de anuncio top pero en realidad es un anuncio de retargeting. Entonces yo miraría un período de 7 días, y si el anuncio ya está por encima de 2, 2.5, 3, obviamente tenés un anuncio de retargeting, y después mirando incluso los 14 y los 30 días, si esos números se ven aún más altos, entonces esto es un anuncio de retargeting y no debería escalarse. Definitivamente debería replicarse e iterarse, porque por supuesto necesitamos estos anuncios dentro del ad set [corregido de "answer set", error de reconocimiento], pero no debería ser uno que se escale de forma aislada (en silo) ni en general.</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: plano medio/primer plano, formato podcast con micrófono profesional en cuadro. Subtítulos: palabra por palabra en mayúsculas. Cortes: toma continua. Gráficos: ninguno. Locación: interior tipo cocina/comedor, luz natural de ventana, lámpara colgante.</t>
+          <t>Talking head en primer plano, fondo blanco liso, campera/saco beige, título fijo arriba ("Stop Scaling The Wrong Meta Ad"), mismo plano estático en los tres frames revisados.</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Gancho: formato de comparación identitaria ('principiante VS pro'), que engancha porque el espectador quiere saber en cuál categoría cae. Estructura: lista de contrastes de comportamiento que escala hacia una conclusión contraintuitiva. Gatillo: remate inesperado (los mejores anunciantes no tienen el mejor ROAS, sino la mayor escala), que invita a repensar una métrica que todos vigilan obsesivamente.</t>
+          <t>Gancho de alerta sobre un error común ("dejá de escalar el anuncio equivocado") que genera urgencia y autoridad (cuenta real de $50k/mes), explicando un concepto contraintuitivo (el anuncio "ganador" puede ser en realidad retargeting) con un método numérico concreto para verificarlo.</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
-          <t>Sí — solo requiere un micrófono decente y una habitación con buena luz natural.</t>
+          <t>sí, nota: contenido 100% de guion/consejo a cámara, sin locación ni edición compleja, requiere solo conocimiento del tema.</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -4721,17 +4721,17 @@
     </row>
     <row r="46" ht="88" customHeight="1">
       <c r="A46" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Macie Reed</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4756,33 +4756,33 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>846</v>
+        <v>2063</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maciereedmarketing/video/7659974291945049357</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7650270956841143560</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Tercer episodio de la serie educativa 'Meta Ads Must Haves' de Macie, donde explica los seis objetivos de campaña de Meta Ads y por qué en la práctica ella solo usa leads y ventas.</t>
+          <t>Maddi cuenta el caso de una cuenta de Meta Ads de $200,000/mes con campañas fragmentadas y solapadas (mismas audiencias/targeting) heredadas de la agencia anterior, y cómo consolidarlas para mejorar la 'densidad de señal' y bajar el MER.</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>Bienvenidos a Meta Ads Must Haves episodio 3, donde en esta serie les enseño toda la información fundamental que necesitan saber sobre meta ads para que puedan convertirse en un meta ads manager y ganar una tonelada de dinero trabajando una fracción del tiempo. En el episodio anterior prometí que les iba a explicar cuáles son los diferentes objetivos a nivel de campaña. Así que de eso exactamente vamos a hablar hoy. Quédense hasta el final de este video porque voy a compartir los dos objetivos que son realmente los únicos que les tienen que importar. Ahora, tienen seis objetivos diferentes para elegir en su campaña, y todos cumplen una función distinta. Como resumen rápido, estos son los tres [?] objetivos que pueden elegir: reconocimiento (awareness), tráfico, interacción (engagement), leads, promoción de aplicaciones, y ventas. Ahora, todos estos objetivos cubren desde el tope del embudo, audiencias frías totalmente nuevas, la mitad del embudo, gente a la que están nutriendo y que va conociendo su marca, y después el fondo del embudo, que es donde idealmente esperan hacerlos cruzar esa barrera y llegar hasta la compra. Entonces, primero, en la parte más alta del embudo, tenemos reconocimiento. Y esto es básicamente decirle a meta ads: che, poné mi anuncio frente a la mayor cantidad de ojos y personas posible. Acá vamos por alcance e impresiones. Esto es genial para una empresa nueva que recién está lanzando y que todavía nadie conoce. El segundo objetivo es tráfico. Esto es decirle a meta ads: quiero que la gente haga clic en este anuncio y vaya a un destino determinado. Entonces nos enfocamos principalmente en clics en el enlace, vistas de landing page, y visitas al perfil de Instagram. El tercer objetivo va a ser interacción. Acá es donde queremos que la gente le dé like a nuestros anuncios, comente nuestros anuncios, o siga nuestras redes sociales. Básicamente estamos tratando de generar conversación. El cuarto objetivo son los leads. Este va a ser su objetivo de generación de leads, es decir, quieren recolectar emails para hacer crecer su lista de correo. El quinto objetivo es bastante de nicho, es la promoción de aplicaciones. Esto obviamente solo es relevante para quienes tienen una app en la App Store. Así que, honestamente, nunca usé este. Y por último, pero no menos importante, tenemos la campaña de ventas. Esto es lo que se usa para ir directo a la yugular y lograr que la gente compre un producto. Ahora, en mis cuatro años siendo ads manager, en realidad solo uso leads y ventas. Siendo ventas el principal. Porque como administradora de publicidad de e-commerce D2C (directo al consumidor), eso es lo que nos importa. Queremos que entren ventas e ingresos. Entonces lo principal que priorizo en absolutamente todas las cuentas de mis clientes va a ser un objetivo de ventas. Y después a veces lo voy a combinar con el objetivo de leads, asumiendo que alguien está gestionando el email marketing. Si recién se están iniciando en meta ads, yo realmente solo me enfocaría en estos dos, los objetivos de leads y de ventas. No hace falta preocuparse por ninguno de los otros. Son demasiado de tope de embudo como para realmente generar impacto o mover la aguja para las marcas de e-commerce. Si les gusta este tipo de contenido y quieren aprender más sobre cómo administrar meta ads, asegúrense de seguirme porque recién estamos arrancando esta serie.</t>
+          <t>¿La fragmentación está matando tu cuenta de anuncios? Recién nos hicimos cargo de una cuenta de anuncios que gasta $200,000 por mes en meta ads. Y lo primero que notamos fue que esta marca y su agencia anterior estaban creando campañas literalmente porque sí, sin ningún motivo real. No había ningún factor que identificara por qué se armó esta campaña, cuál era la diferenciación entre una y otra. Y en su mayoría las campañas se superponían con similitudes de creatividad, los mismos tipos de persona (audiencia), básicamente el mismo targeting, lo cual en mi opinión hacía que su frecuencia subiera y también que su CPA fuera bastante alto. Sabemos que meta premia la densidad de señal, es decir, quiere tener toda la señal posible dentro de esa única campaña para poder brillar; eso es después de Andromeda [actualización del algoritmo de Meta]. Entonces cuando nos hicimos cargo de esta cuenta, no cortamos todo de una, porque eso también puede ser peligroso. Pero vimos cómo podíamos consolidar lo que estaba ganando en ciertos activos (assets) dentro de otros activos, y buscamos reducir las campañas y los activos dentro de la cuenta. Ahora, por supuesto, su MER [corregido de "Mir", error de reconocimiento] bajó, porque no están compitiendo contra sí mismos en estas campañas. Meta sabe a quién ir a buscar, y consolidaron y crearon una señal excelente para que meta la use.</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical en dormitorio/living con buena luz cálida (lámpara), decoración de fondo (cuadro, planta), micrófono de solapa, sin cortes de escena visibles. Se superpone a pantalla completa una captura del panel real de Meta Ads Manager 'Choose a campaign objective' como recurso visual de apoyo. Subtítulos grandes tipo caption animado quemados palabra por palabra en cada frase clave.</t>
+          <t>Talking head en primer plano, top oscuro, fondo blanco liso, título fijo arriba ("Stop Creating New Campaigns In Meta") y subtítulos incrustados palabra por palabra en la parte inferior (se leen fragmentos como "we just took over an ad account spending $200,000 per month" y "same persona types, really the same targeting"). Mismo plano estático en los tres frames.</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>Gancho: promesa de valor concreto y directo ('los dos objetivos que son los únicos que les importan'). Estructura: formato educativo numerado tipo episodio de serie/curso que lista los seis objetivos de forma clara. Gatillo: autoridad (4 años de experiencia) y aspiracional (ganar mucho dinero trabajando poco), más el gancho de continuidad para el próximo episodio.</t>
+          <t>Gancho de pregunta retórica/alarma ("¿la fragmentación está matando tu cuenta?") sobre una cifra grande ($200k/mes) que da autoridad, con estructura diagnóstico-causa-solución que enseña un concepto técnico (densidad de señal / MER) de forma aplicable.</t>
         </is>
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo cámara frontal de celular, mic de solapa económico y capturas de pantalla propias del Ads Manager.</t>
+          <t>sí, nota: video de consejo a cámara con subtítulos dinámicos, replicable con celular y una app de edición de captions gratuita.</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -4813,32 +4813,32 @@
     </row>
     <row r="47" ht="88" customHeight="1">
       <c r="A47" s="2" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>Venta del servicio</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+        <v>31</v>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4848,48 +4848,48 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2569</v>
+        <v>1971</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7645570700857724167</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7646443420076068118</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Maddi (agencia MADE.) cuenta el caso de una marca de moda de ticket alto (AOV 300-600 USD) a la que ayudaron a pasar de perder dinero en adquisición de clientes nuevos a duplicar esos ingresos, cambiando el tipo de contenido creativo y la estructura de campañas en Meta.</t>
+          <t>Matt Bell comenta una tendencia que observa en sus cuentas de Meta Ads: el contenido estático está empezando a superar en rendimiento al video y al UGC generado con IA, por la creciente desconfianza de los consumidores hacia contenido con IA y voces genéricas de influencer.</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>Gastamos $20,000 para generar $100,000 para esta marca de moda, y les voy a mostrar exactamente qué hicimos para lograrlo. Esta clienta de moda realmente tenía una base de clientes leales. Generaban compras recurrentes, pero la adquisición de clientes nuevos específicamente a través de meta ads les estaba haciendo perder dinero. Además, sus productos van, digamos, de 300 a 600 dólares de AOV (ticket promedio). Entonces pedirle a un cliente nuevo que se comprometa con una compra de ese tamaño siendo una marca desconocida es muy difícil. La marca solo había corrido imágenes de campaña o contenido de e-commerce, nada que mostrara el estilo de vida o a la mujer de todos los días. Como sabemos, la moda es una compra aspiracional, y el consumidor quiere ver momentos que representen su vida real, donde las prendas realmente se estén usando. De la misma manera, con contenido de styling en un producto de precio alto, empezamos a mostrar más contenido de versatilidad: la misma parte de arriba con distintas partes de abajo, el vestido combinado de formas muy distintas. Suena lógico, pero esta marca solo estaba explotando ese único pilar de contenido de campaña y de e-commerce. La agencia anterior en realidad nunca usó exclusiones [corregido de "explosions"/"explosiones", error de reconocimiento] en su campaña, lo cual hizo que meta se pusiera muy vago/perezoso. En nuestra campaña de prospección, ajustamos bien esas exclusiones para lograr que meta se enfocara fuera de los clientes tibios o existentes, ya que solo tenían drops (lanzamientos) y no recurrencia de los más vendidos (best sellers). Armamos esto como una campaña CBO múltiple, con distintos ad sets por categoría de producto, y dejamos que meta intentara encontrar los productos ganadores y también las creatividades ganadoras. Si encontrábamos creatividades ganadoras o productos ganadores, los separábamos en su propia campaña y la corríamos con presupuesto para ayudarlos a agotar stock. Su marca siempre fue ganadora, pero su estrategia de anuncios simplemente estaba frenando su verdadero crecimiento. No solo logramos esto en pocas semanas, sino que durante los primeros seis meses trabajando juntos, de hecho duplicamos sus ingresos de clientes nuevos.</t>
+          <t>Lo que les puedo decir ahora mismo es que, en todas las cuentas de anuncios en las que estuve trabajando en los últimos 90 días, lo estático (static/imagen) está empezando a rendir mejor que el video. Creo que lo que está pasando es que hay demasiadas marcas haciendo mal contenido de IA, y muchos consumidores se están volviendo escépticos sobre si la creatividad que están viendo fue generada por IA. Entonces, en mi opinión, creo que está empezando a haber una falta de confianza con la creatividad en video [corregido de "video craves", error de reconocimiento]. Y encima de eso, muchas marcas están yendo directamente con esa voz genérica de influencer, como el típico creador de UGC estándar, que no está convirtiendo tan bien comparado con lo estático. Esa es la tendencia que estoy viendo. Pero de cualquier manera, tienen que tener variación acá. Deberían probar carruseles, estático, video, y ver qué les está funcionando a ustedes, en lugar de hacer solo estático.</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>Talking head en formato entrevista/testimonio: mujer sentada en sillón color crema, fondo liso beige, plano medio fijo, sin cortes de cámara visibles en los frames revisados. Subtítulos incrustados en dos estilos: un titular manuscrito ("loyal customer base") arriba, y captions estilo palabra por palabra abajo en la parte inferior del video.</t>
+          <t>Sin talking head: tarjeta de texto roja fija ("Static is beginning to out perform video and AI UGC and every other type of creative...") sobre una captura/grabación de pantalla de escritorio Mac con tres recuadros (Video, otro tipo poco legible, Carrusel) y texto pequeño ilegible. Los tres frames capturados son prácticamente idénticos, lo que sugiere una sola imagen fija sostenida con narración en off en vez de video en movimiento.</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>Gancho numérico fuerte en el título ($20,000 invertidos → $100,000 generados) que promete un caso de éxito cuantificado, con estructura de diagnóstico/qué cambiamos/resultado tipo case study y cifras reales que dan autoridad y curiosidad por el "cómo".</t>
+          <t>Gancho de pregunta/tendencia contraintuitiva en el título ("¿alguien más nota que lo estático supera al video?") que interpela directamente a colegas del rubro, en formato corto de opinión/hot take de autoridad que invita al debate en comentarios.</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: solo requiere una persona hablando a cámara con buena luz y un fondo prolijo, sin locación ni equipo caro.</t>
+          <t>sí, nota: solo necesita una tarjeta de texto con opinión y una captura de pantalla de fondo, sin cámara ni edición avanzada.</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -4905,17 +4905,17 @@
     </row>
     <row r="48" ht="88" customHeight="1">
       <c r="A48" s="2" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4940,33 +4940,33 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>2311</v>
+        <v>1960</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7641134699745643783</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7667312448218615062</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Maddi audita una cuenta de Meta Ads que gasta $300,000/mes y detalla tres errores principales: frecuencia demasiado alta, falta de un criterio único de testeo (CBO/ABO) por campaña, y cadencia de creatividades insuficiente.</t>
+          <t>Ben Heath compara las estrategias publicitarias y de sitio web de dos marcas de joyería (Crafted vs. Sonuchi [?]), analizando sus anuncios en la Biblioteca de Anuncios de Meta, la variedad creativa y la experiencia de compra online, y concluye que Crafted es mejor.</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>Acabo de auditar una cuenta de anuncios que gasta $300,000 en meta ads, y estos son los principales errores que están matando la cuenta. Número uno es la frecuencia. Para una cuenta de este tamaño esperaríamos una frecuencia de alrededor de 2, pero al desglosar cada anuncio individual, el 80% tenía una frecuencia de dos o más, lo que significa que no estaban introduciendo conceptos nuevos que mejoraran el top of funnel ni yendo detrás de alcance neto nuevo (net new reach), que es súper importante. Queremos asegurarnos de que nuestra cuenta de anuncios tenga suficientes creatividades con una frecuencia de 1.5 o menos, para ampliar nuestro alcance neto nuevo. El número 2 es la forma en que estaban testeando, ya sea CBO o ABO. Esto puede marcar una diferencia real en toda tu cuenta, pero dentro de sus campañas tenían activos (assets) divididos por producto, activos divididos por persona (audiencia) y activos divididos por creatividad. Tenés que elegir uno y mantenerlo dentro de esa campaña específica para poder realmente diseccionar los resultados que estás recibiendo. Número tres es nuestra cadencia de creatividades. Para una cuenta que gasta esto, esperaríamos lanzamientos (drops) semanales dentro de la cuenta de anuncios, y querríamos al menos entre 10 y 15 creatividades, si no más, para tener no solo volumen de creatividades sino también diversificación de creatividades. Esta cuenta solo estaba agregando en sprints quincenales, lo cual simplemente no alcanza para una cuenta que gasta esto.</t>
+          <t>¿El marketing de quién es mejor, Crafted o Sonuchi [?]? Bueno, Sonuchi está corriendo 87 anuncios de Meta. Tienen una variedad decente de imágenes acá. Sin embargo, sus anuncios en video son todos muy parecidos. Hacen pequeñas iteraciones sobre distintas piezas creativas, y ese formato probablemente les funcione bien. Pero podrían pasar al siguiente nivel incluyendo formatos completamente nuevos. Pensá en reseñas UGC, unboxings. Ahora, Crafted: 130 anuncios de Meta, mucho mejor. Tienen imágenes estáticas en distintos formatos y videos que muestran el producto en acción en diferentes situaciones. Esto es fantástico porque encaja con su eslogan, que es 'crafted to last' [hecho para durar]. También experimentaron con más formatos, lo cual está bien. Sobre el sitio web: está buenísimo. Te dan un descuento misterioso apenas hacés clic. Eso me gusta mucho. También hay reseñas, garantías de calidad por todos lados. La página principal de Sonuchi también te tira un pop-up de oferta, pero no es un misterio: es un simple descuento de 10 libras. Curiosamente, sí tienen fotos de Lamine Yamal usando sus joyas, pero está escondido dentro del sitio web. Tenés que esforzarte bastante para encontrarlo. Si tenés a una de las estrellas más grandes del fútbol usando tus productos, tendrías que estar gritándolo a los cuatro vientos. Las dos marcas son buenas, pero Crafted le gana a esta. Su testeo creativo es más sofisticado, el storytelling de su producto es más ajustado y su sitio tiene menos fricción. ¿Están de acuerdo? Cuéntenme abajo en los comentarios.</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano, saco blanco/crema, fondo blanco con logo "MADE." detrás, título fijo blanco con borde negro arriba ("I Just Audited A Meta Account Spending $300,000 p/m"). Encuadre y locación prácticamente idénticos en los tres frames, sin cortes visibles.</t>
+          <t>Formato 'reacción/análisis' con inserciones gráficas cambiantes en picture-in-picture: frame 1 muestra una interfaz tipo Biblioteca de Anuncios de Meta ('Active', 'Library ID', plataformas) con miniatura de video de ropa; frame 3 muestra un primer plano de una pulsera/cadena dorada en una muñeca con texto de marca ('HEAT PROOF situations'); frame 5 muestra una foto del futbolista Lamine Yamal con cadenas y su nombre en texto. En los tres, el presentador (remera polo gris) aparece más chico abajo hablando, fondo blanco liso. Subtítulos blancos en negrita. Varios cortes con distintas capturas de pantalla.</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>Gancho de cifra alta y autoridad ("auditoría de una cuenta de $300k/mes") combinado con formato listicle de errores numerados que promete valor práctico inmediato y aplicable a cualquier cuenta, generando FOMO de estar cometiendo los mismos errores.</t>
+          <t>Gancho: formato versus directo ('¿el marketing de quién es mejor?') que invita a opinar. Estructura: comparación punto por punto de anuncios y sitio web de dos marcas competidoras, veredicto final y pregunta para generar comentarios. Gatillo: formato comparativo/polémica leve entre marcas + curiosidad + cierre con pregunta que dispara engagement.</t>
         </is>
       </c>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: video de opinión/consejo a cámara sin locación especial, replicable con celular y buena luz; el valor está en el conocimiento del tema, no en la producción.</t>
+          <t>sí, mismo formato reacción/análisis mostrando capturas de pantalla (Ads Library, sitio web) con cámara casera, sin producción cara.</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -4997,22 +4997,22 @@
     </row>
     <row r="49" ht="88" customHeight="1">
       <c r="A49" s="2" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -5032,48 +5032,48 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>2081</v>
+        <v>1957</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7644104846248774920</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7625510355711642887</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Maddi explica por qué escalar el anuncio 'top' de una cuenta puede ser un error si en realidad es un anuncio de retargeting disfrazado de ganador, y cómo detectarlo revisando la frecuencia en ventanas de 7, 14 y 30 días.</t>
+          <t>Clip promocional del episodio 1 del podcast 'Marketing MADE.' que explica el concepto de 'Entity ID' de Meta: cómo el algoritmo asigna una misma huella digital a creatividades visualmente similares, haciendo que compitan entre sí y no reciban aprendizaje fresco.</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>Acabo de hacerme cargo de una cuenta que gasta $50,000 por mes en meta, y este fue el error más grande que vi, y realmente el error más grande que estoy viendo que comete todo el mundo en su cuenta de anuncios: escalar un anuncio que no debería escalarse. Déjenme mostrarles exactamente a qué me refiero. Cuando miran su anuncio top, capaz miran cuál es su CPA y cuántas compras están generando, y piensan "fantástico, voy a escalar esto", ya sea dentro de este ad set o en una campaña separada, una campaña de escalado. Pero lo que la gente no llega a mirar es la frecuencia de ese anuncio, porque puede estar disfrazado de anuncio de bottom of funnel que está teniendo un CPA excelente, excelentes resultados, y pensás "bueno, si lo saco solo o lo escalo más, va a dar estos mismos resultados". Pero la razón por la que este anuncio está funcionando tan bien es por la creatividad de top of funnel que lo está alimentando, y en realidad está disfrazado de anuncio top pero en realidad es un anuncio de retargeting. Entonces yo miraría un período de 7 días, y si el anuncio ya está por encima de 2, 2.5, 3, obviamente tenés un anuncio de retargeting, y después mirando incluso los 14 y los 30 días, si esos números se ven aún más altos, entonces esto es un anuncio de retargeting y no debería escalarse. Definitivamente debería replicarse e iterarse, porque por supuesto necesitamos estos anuncios dentro del ad set [corregido de "answer set", error de reconocimiento], pero no debería ser uno que se escale de forma aislada (en silo) ni en general.</t>
+          <t>Meta tiene algo que se llama Entity ID (ID de entidad). Básicamente se le asigna una huella digital (fingerprint) a tu creatividad según cómo se ve visualmente, no según cómo la nombraste ni cuántas veces la subiste a la cuenta de anuncios. Si dos anuncios se ven parecidos para el algoritmo —digamos que tienen la misma iluminación, el mismo modelo, el mismo tratamiento estético, el mismo formato— se les asigna el mismo Entity ID. Básicamente, se les asigna la misma huella digital. Y esto es lo que pasa: comparten el mismo historial de rendimiento, comparten las mismas expectativas de entrega, compiten literalmente por el mismo pool de audiencia. Y cualquier versión nueva que subas no tiene oportunidad de un aprendizaje renovado (refresh), porque en realidad ya viene prejuzgada según todo lo que aprendió de los otros anuncios que se ven parecidos.</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano, fondo blanco liso, campera/saco beige, título fijo arriba ("Stop Scaling The Wrong Meta Ad"), mismo plano estático en los tres frames revisados.</t>
+          <t>Formato podcast con talking head, fondo de estudio con paneles geométricos iluminados en rosa/púrpura/azul, micrófono de brazo visible en primer plano, plano medio, sin subtítulos visibles en los frames capturados. Estética mucho más elaborada que los otros videos de la misma cuenta, que suelen usar fondo liso.</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Gancho de alerta sobre un error común ("dejá de escalar el anuncio equivocado") que genera urgencia y autoridad (cuenta real de $50k/mes), explicando un concepto contraintuitivo (el anuncio "ganador" puede ser en realidad retargeting) con un método numérico concreto para verificarlo.</t>
+          <t>Gancho de concepto técnico poco conocido ("Entity ID") que promete revelar cómo funciona realmente el algoritmo de Meta, apelando a la curiosidad de anunciantes avanzados, en formato de fragmento de podcast que también sirve de promoción cruzada de contenido nuevo de la marca.</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: contenido 100% de guion/consejo a cámara, sin locación ni edición compleja, requiere solo conocimiento del tema.</t>
+          <t>no, nota: requiere un set de podcast con iluminación de color y equipo de grabación dedicado, más costoso que los videos de un solo plano con fondo liso de la misma cuenta.</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5089,15 +5089,15 @@
     </row>
     <row r="50" ht="88" customHeight="1">
       <c r="A50" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
+        <v>33</v>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -5109,12 +5109,12 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Macie Reed</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5124,33 +5124,33 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>826</v>
+        <v>1848</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maciereedmarketing/video/7667600871445761294</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7650905074020977942</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Sexto episodio de la serie donde Macie explica los cuatro formatos de anuncio disponibles en Meta Ads Manager (video, imagen, carrusel, catálogo) y cierra promocionando la lista de espera de su curso.</t>
+          <t>Dos marketineros (Ben Heath y un colega) reaccionan a un comercial de Adidas con estrellas como Beckham, Zidane y Messi, elogiando su producción. Después revisan la Biblioteca de Anuncios de Meta y descubren que Adidas no está pautando esa pieza como anuncio pago, algo que consideran una oportunidad desperdiciada.</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>Bienvenidos de nuevo a Meta ads Must Haves episodio 6, donde en esta serie les estoy enseñando todo lo que necesitan saber sobre meta ads para que puedan convertirse en un meta ads manager, ganar una tonelada de dinero, y trabajar una fracción del tiempo. Si no están al día con la serie, asegúrense de volver a mi perfil y ver los videos anteriores. Pero en el episodio de hoy vamos a hablar sobre los formatos de anuncio. Hay cuatro tipos diferentes de formatos de anuncio, y hay un momento y un lugar diferente para usarlos según distintos propósitos. Pero por ahora, empecemos a mapear los cuatro tipos. Primero y principal, tenemos video. Esto es bastante directo. Es básicamente lo que están viendo ahora mismo. Un video en Instagram o Facebook. Estos van a ser anuncios estilo UGC de alguien hablando a cámara, de unboxing, o entrevistas callejeras. Después tenemos imágenes, que se explica bastante solo. Es una foto de producto o algún tipo de foto que tiene un titular, o tal vez señala características, o es un 'nosotros versus ellos'. Tercero son los anuncios carrusel. Estos son los anuncios por los que uno se desliza en el feed, o aparecen como múltiples diapositivas en una historia. Y estos son realmente geniales si tenés múltiples productos o querés mostrar múltiples ángulos de tu producto, o simplemente destacar diferentes USPs (propuestas de venta únicas). Y por último, pero no menos importante, tenemos el anuncio de catálogo. El anuncio de catálogo es un anuncio dinámico que en realidad conectás directamente a tu cuenta de Shopify, y toma toda la información de tu producto directamente de tu sitio web. Entonces toma la imagen de tu producto, el título de tu producto, los precios, todas esas cosas buenas. Así que básicamente autocompleta el anuncio por vos, y después todo lo que tenés que hacer es entrar y completar un titular y una descripción. Eso es esencialmente todo. Ahora, es muy importante que tengan estos cuatro tipos de formatos dentro de su cuenta publicitaria, simplemente porque a meta le gusta tener más con qué trabajar. Y si le das más diversidad, va a estar muy contento con vos y te va a recompensar. Si les gusta la serie, entonces les va a encantar mi Meta Ads Crash Course, que es un curso de meta ads amigable para principiantes. Y la lista de espera para eso cierra en solo un par de días. Entonces si están interesados en aprender meta ads como principiantes totales, o tal vez ya entraron un par de veces y simplemente no logran entender cómo hacerlo funcionar, mi meta ads crash course va a ser perfecto para ustedes. Y cuando se unan a mi lista de espera, van a tener acceso anticipado antes que todos los demás. Van a obtener mi curso de 47 dólares por 27 dólares. Además les voy a sumar mi Meta Ads Toolkit totalmente gratis. ¿Quieren unirse a la lista de espera? Vayan a la parte de arriba de mi perfil. Está disponible en mi bio.</t>
+          <t>Es una demostración de poder una locura de parte de Adidas, ese anuncio. Tener a tantos nombres [famosos] y gastar tanta plata en eso... o sea, debe haber costado una fortuna absoluta. Yo de soccer no sé nada, de fútbol sí que sé algo [?]. Se siente como si estuvieras viendo una película o una serie de TV. Escuchá, hermano, tengo un equipo, son de fiar. Bueno, ya vamos en camino. Estamos en el auto ahora. Gracias. Es casi como que no es realmente un anuncio. No es realmente una pieza de contenido diseñada para vender algo. Es más como una pieza de entretenimiento en la que metieron su marca. La verdad, uno dice: 'guau, qué paciencia' [?]... los superás [?] (fragmento poco claro por la transcripción automática). Me hace sentir viejo que 1996 sea como si fuera hace una eternidad. Ja ja ja ja ja ja. ¿Ese es Beckham? ¿Tienen a alguien todavía mejor? [?] Sí, un David Beckham con cara de joven, y también un Zinedine Zidane joven. En esta parte es como: 'nosotros estamos a cargo de este espacio'. Bueno, te voy a ser sincero: puede que le haya dicho al que posiblemente sea el mejor jugador del planeta que yo podía terminar esto hoy. Definitivamente podrías recortar eso y usarlo en un formato más publicitario, para ser un poco más directo a la hora de promocionar cosas. Entonces, ¿cumplí o cumplí? ¿Y después ponen a Messi al final? Es un video de cinco minutos y él no aparece hasta el minuto 4:30 o algo así. Che, vos sos mi plan B. Es muy competitivo contra Nike, el gran rival. Sí, sin dudas es así. Así que si voy a ver qué están haciendo con esto en Adidas Football, porque podrían estar usando... no tienen ningún anuncio corriendo. Eso me parece una locura. Adidas Football tiene 26,4 millones de seguidores en su página de Facebook y 34,7 millones en Instagram. Y no estar corriendo ningún anuncio... para cualquier gestor de anuncios sería el sueño poder manejar esa cuenta, porque sería tan fácil generar resultados tan buenos con esa audiencia. Y no les han hecho publicidad a esa audiencia [?]. Sería como tirarle a peces en un barril [algo súper fácil] correr anuncios para esa audiencia en esas cuentas. Bueno, en Adidas Originals sí están corriendo anuncios: tienen 440 [?] corriendo en todas las ubicaciones. No es tanto para una marca de ese tamaño. Ya puedo ver diferentes idiomas. Bueno, esta es como la cuenta principal de Adidas. Me sorprende muchísimo que no estén corriendo variaciones de esa pieza creativa como anuncios, ni ningún anuncio en Adidas Football, pero acá sí están corriendo anuncios. 690 sería mucho para muchas empresas; para Adidas, para nada. Seguramente podrían hacer mucho más ahí. Y estuvimos revisando y no logramos encontrar que usen ese contenido en ningún anuncio activo. Hay que tener en cuenta que ese contenido obviamente fue creado pensando en el Mundial, y tiene como cuatro semanas. Estamos ahora a como 10 días [del Mundial], grabando esto desde el Mundial. Y no están usando esa pieza en formato pago. Eso parece una oportunidad desperdiciada, tirada ahí nomás. Se la perdieron. Sobre todo considerando cuánto habrán gastado en armar eso: les debe haber costado millones producirlo, sobre todo con todos esos nombres. Probablemente decenas de millones. Sí, sería muy fácil usar eso para vender productos. Claro, que es exactamente lo que Adidas quiere hacer.</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical, sentada en sillón con manta blanca, sosteniendo una taza (elemento casual/lifestyle), mic de solapa, misma locación de dormitorio/living en los tres frames sin cortes visibles. Se superpone a pantalla completa una captura/mockup de un anuncio real de Instagram (imagen de producto con botón 'Follow' y 'Shop now') como ejemplo visual de un formato. Subtítulos tipo caption animado quemados en el video.</t>
+          <t>Formato de dos personas hablando (uno con polo bordó) sentadas en un living con chimenea de fondo, en composición de pantalla dividida: mitad de arriba los dos reaccionando, mitad de abajo el clip del anuncio de Adidas que están comentando (formato duet/reacción). Más adelante corta a una captura de pantalla (screen recording) de la Meta Ads Library mostrando la búsqueda 'adidas' y sus resultados. Subtítulos blancos en minúscula, negrita, sincronizados palabra por palabra.</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>Gancho: continuidad de serie educativa numerada que ya tiene audiencia fidelizada. Estructura: lista clara y ordenada de los '4 formatos' fácil de seguir y guardar. Gatillo: urgencia/escasez al final (lista de espera de curso que cierra en días, con descuento y bonus gratis).</t>
+          <t>Arranca directo reaccionando a un anuncio de alto impacto con celebridades (gancho de curiosidad + nombres famosos), sigue una estructura de análisis (calidad creativa y luego chequeo de datos reales en la Ads Library), y el gatillo es la revelación sorprendente de que Adidas no está pautando esa pieza pese a haber costado millones, sumado a la autoridad de mostrar data concreta.</t>
         </is>
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo cámara de celular y ejemplos de anuncios reales tomados de la propia plataforma como referencia visual.</t>
+          <t>Sí, pero requiere conocimientos de marketing y acceso a la Ads Library; la edición a pantalla dividida es sencilla de lograr con apps gratuitas.</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -5181,27 +5181,27 @@
     </row>
     <row r="51" ht="88" customHeight="1">
       <c r="A51" s="2" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+        <v>34</v>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5216,48 +5216,48 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>813</v>
+        <v>1614</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7661251520700222742</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7642466201179884822</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath reacciona y puntua con 8 sobre 10 un anuncio de Meta de la marca de ropa YoungLA, que usa una colaboracion con celebridades/influencers y una oferta por tiempo limitado.</t>
+          <t>Matt Bell explica la estrategia de 'partnership ads' (whitelisting) en Meta: contactar masivamente a microcreadores (de cientos a 10,000 seguidores) para correr anuncios pagos publicados directamente desde sus cuentas, generando prueba social, awareness y contenido auténtico acumulativo.</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>Entonces se muestra a Marlon de entrada: es el encaje perfecto para el publico objetivo de Young LA. Eso esta bueno. Me gusta. Despues lo sigue con otras celebridades e influencers. Es un buen truco de retencion. Muchos cortes rapidos. Genera intriga sobre la colaboracion de una manera divertida, mostrando en cierto modo a la gente interactuando con los personajes. Me gusta eso. Y despues termina con 'tiempo limitado'. La oferta especifica que es por esta colaboracion, eso es importante, y consigo que mas gente actue. Muestra que hay un reloj corriendo de verdad. Tienen que actuar ahora. Ocho de diez.</t>
+          <t>Esta estrategia de meta ads nos está dando un crecimiento compuesto explosivo. Básicamente se trata de usar partnerships (asociaciones) en meta, que es cuando vas y buscás un montón de creadores de contenido o influencers y publicás en partnership con esas personas. Así que agarré esta captura de Google, y pueden ver acá, por ejemplo, en este anuncio de belleza, tenés el nombre del creador de contenido y después dice "con" (with), y después la marca. Y lo que estamos haciendo ahora mismo en algunas de estas marcas es contactar masivamente a microcreadores de contenido que se parecen a los clientes. O sea, no son gente que ya tiene muchos seguidores. Normalmente tienen desde un par de cientos hasta quizás 10,000 seguidores como máximo en Instagram. Y lo que hacemos es conseguir un buen volumen de gente hablando sobre el producto o servicio. Y después corremos lo que se llaman anuncios de partnership de meta. Algunos le dicen "whitelist ads" (anuncios de whitelisting). Entonces lo que hacemos es tener una campaña ahora mismo que tiene todos estos distintos anuncios de partnership. Básicamente es una campaña, un ad set. Y podés incluso hacerlo con targeting abierto/amplio (open broad), o podés usar exclusiones. Yo prefiero usar exclusiones porque esto funciona muy bien con el top of funnel. Y normalmente tenemos entre 5 y 25 anuncios dependiendo de cuánto presupuesto tengas. Y simplemente vas empujando a todos estos distintos creadores que están hablando de tu producto, pero corriendo los anuncios con ellos. Entonces básicamente parece una marca distinta en vez de solo ser tu marca. Y donde esto empieza a compensarse/multiplicarse (compound) es que, con el tiempo, terminás teniendo un par de cientos de creadores que publicaron sobre vos. Entonces cuando la gente busca tu marca, su contenido aparece. Tenés más prueba social, tenés creatividad publicitaria. Y obviamente estás construyendo reconocimiento (awareness) a través de su audiencia, porque ellos también están publicando sobre vos. Y en mi experiencia hasta ahora, lo que mejor funcionó es enfocarse en estos microcreadores de contenido, enfocarse en gente que se parece a tus clientes. No son creadores de contenido profesionales, no son influencers. Y ese estilo de contenido auténtico que conseguís de este tipo de persona está funcionando muy bien como anuncio. De nuevo, esta estrategia simplemente implica literalmente contactar gente, ofreciéndoles algún tipo de incentivo. Tal vez hacés una tarifa fija por posteo más producto gratis, o afiliación, lo que sea. Y a cambio, querés poder correr anuncios de partnership donde podés correr anuncios a través de su página, con esta creatividad. Eso es lo que está funcionando extremadamente bien ahora mismo en un par de marcas de e-commerce con las que estoy trabajando.</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>Formato de resena: Ben sentado en un living (silla de madera, planta, chimenea de fondo) sosteniendo el celular con el anuncio original reproduciendose en una ventana superpuesta con controles de pausa; titulo grande en la parte superior ('$300M Ad Expert Reviews Young LA') y etiquetas de seccion que van cambiando ('Target Audience Fit', 'Pacing &amp; Engagement', 'Urgency &amp; Clear Value Proposition') sincronizadas con lo que dice.</t>
+          <t>Sin talking head propio: tarjeta de texto roja con título ("New Meta Ads Strategy For Explosive Compounding Growth") sobre capturas de pantalla de dos posts reales (Instagram y Facebook) de un partnership ad de belleza ("kaiblue with lakeur_beauty"), y una segunda tarjeta de texto con instrucción concreta ("Put all of the partner ads into one campaign/shopping campaign, use exclusions"). Formato slideshow de imágenes fijas con narración en off; se ve el dock de un iPhone/iPad abajo.</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Gancho de autoridad numerica ('$300M Ad Expert') mas formato de 'resena' que genera curiosidad; estructura de checklist de criterios que ensena mientras entretiene, cerrando con una puntuacion numerica facil de recordar y compartir; gatillo de aprendizaje a partir de un ejemplo real de una marca conocida.</t>
+          <t>Gancho de superlativo ("una de las mejores estrategias que estoy corriendo ahora") con promesa de crecimiento compuesto/explosivo, explicando paso a paso una táctica poco conocida (whitelisting con microcreadores) respaldada con un ejemplo visual real que da sensación de información privilegiada.</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>si, solo necesita un celular, una app que permita superponer video (por ejemplo CapCut) y comentar el anuncio de otra marca.</t>
+          <t>sí, nota: no requiere producción propia, solo capturas de pantalla de ejemplo y narración en off; el costo real está en el trabajo de outreach a creadores, no en el video en sí.</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -5273,15 +5273,15 @@
     </row>
     <row r="52" ht="88" customHeight="1">
       <c r="A52" s="2" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -5308,33 +5308,33 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
-        <v>803</v>
+        <v>1540</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7665377118192176406</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7667313471880547606</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath resena un anuncio de Bose y lo puntua con 0 sobre 10 porque el video muestra a una mujer preparando una ensalada y nunca conecta claramente con el parlante que se supone que vende.</t>
+          <t>En una entrevista al aire libre, Ben Heath cuenta cuánto gasta realmente en publicidad paga para su propia agencia y explica que el límite no es la demanda sino la capacidad de atender más clientes.</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>'Hagamos mi ensalada de verano favorita de durazno grillado y burrata, inspirada en el Soundlink Flex de Bose en color Sunset Peach.' Bueno, esto es un anuncio de Bose. ¿Por que esta hablando de hacer una ensalada? 'Elegi una variedad...' Este anuncio entero es una senora mostrandonos como hacer una ensalada. ¿Como es que eso vende productos de audio? ¿Quien en Bose aprobo esto [?, en el original 'Who would Bose approve this', frase con orden gramatical inusual]? Cero de diez.</t>
+          <t>¿Cuánto gastás en tu propia publicidad? Probablemente mucho menos de lo que la gente piensa, porque tengo, para el mundo de los anuncios de Meta, una base orgánica de seguidores muy grande. Casi siempre estamos limitados por la capacidad de entrega de nuestras distintas ofertas, más que por la demanda. Tenemos un ciclo que se repite: en algún momento generamos algo de capacidad extra en la agencia, prendemos los anuncios, gastamos como 5.000 dólares, y enseguida llegamos al límite de capacidad, entonces los apagamos de nuevo. Así que, la verdad, rara vez gastamos más de, digamos, 10 o 15 mil dólares en un mes. Podríamos gastar mucho más que eso si tuviéramos la capacidad para entregar, pero muchas veces no la tenemos. Y tenemos muy claro que preferimos decirle que no a un cliente, o al menos todavía no, y mantener un servicio de alta calidad, en vez de simplemente meter a la mayor cantidad de gente posible por la puerta.</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>Mismo formato de resena que la fila 204: Ben en el mismo living con el celular mostrando el anuncio original de Bose superpuesto (escena de cocina con duraznos, tomates y un producto rojo sobre la mesada); titulo '$300M Ad Expert Reviews Bose Ad', etiquetas de seccion ('The Visual Hook', 'Confusing by Design') que acompanan la critica.</t>
+          <t>Entrevista entre dos personas sentadas en sillas plegables de camping, encuadre de perfil (no miran a cámara, se miran entre ellos), fondo de pared de chapa corrugada y piso de ripio. Edición con corte a pantalla dividida (los dos hablando a la vez) y a planos individuales. Subtítulos blancos negrita sincronizados. Vestimenta casual (polo, remera), luz solar dura de exterior.</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>Gancho de indignacion e incredulidad ('Why is she talking about making a salad?'); estructura de resena negativa que genera controversia y comentarios; gatillo de 'fail' de una marca grande, que produce curiosidad morbosa y validacion social ('¿quien aprobo esto?').</t>
+          <t>Pregunta directa como gancho (¿cuánto gastás en tus propios anuncios?), respuesta contraintuitiva con cifras reales como estructura, y el gatillo es la transparencia/autoridad de un experto compartiendo números concretos de su propio negocio.</t>
         </is>
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>si, mismo formato replicable que la fila 204, sin costo adicional mas alla de encontrar un anuncio ajeno para comentar.</t>
+          <t>Sí, es una entrevista informal grabada con poco equipo; el gancho son las cifras compartidas, no la producción.</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
@@ -5365,17 +5365,17 @@
     </row>
     <row r="53" ht="88" customHeight="1">
       <c r="A53" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Macie Reed</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -5400,33 +5400,33 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
-        <v>583</v>
+        <v>1485</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maciereedmarketing/video/7658140615288311053</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7633738600223411464</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>Primer episodio de la serie 'Meta Ads Must Haves' de Macie, donde explica la diferencia fundamental entre publicidad 'push' (redes sociales/Meta) y 'pull' (búsqueda/Google) para quienes recién arrancan en meta ads.</t>
+          <t>Maddi resume los errores más comunes que encontró auditando cinco cuentas de Meta Ads de marcas de moda/joyería ($50k-$300k/mes): creatividad sin sistema, falta real de diversificación de contenido más allá de fotos de campaña, y destinos de post-clic mal elegidos.</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>Bienvenidos a Meta Ads Must Haves episodio 1, donde en esta serie les voy a explicar toda la información fundamental que necesitan saber sobre Meta Ads para poder convertirse en un meta ads manager. Ahora, probablemente estén pensando: Macie, ¿por qué querría convertirme en un meta ads manager? Y me alegra mucho que preguntes. Meta ads en realidad es un oficio digital muy bien pago, lo que significa que podés trabajar desde cualquier lugar. Mientras tengas wifi y una notebook, podés ganar una tonelada de dinero, dejar tu trabajo de 9 a 5, y trabajar una fracción del tiempo, básicamente dándote libertad total de tiempo, ubicación y dinero. Puedo dar fe de esto porque es lo que yo hago. Entonces, para arrancar la serie, realmente quiero sentar las bases de qué son exactamente los meta ads. Los meta ads son los anuncios que la gente ve en su feed de Facebook e Instagram. Y estos se les muestran a las personas en base a su interés, comportamientos, datos demográficos, o proximidad a ciertas cosas. Entonces la forma en que me gusta pensarlo es que cuando pienso en publicidad digital en general, la categorizo en dos grupos separados, ¿no? Tenemos paid social (redes de pago) y tenemos paid search (búsqueda de pago). Paid social van a ser las plataformas de redes sociales: Instagram, TikTok, Pinterest, YouTube. Y paid search básicamente va a ser Google. Entonces entre estas dos tenemos un método de empuje (push) versus uno de atracción (pull). Empuje significa que estás empujando tu contenido hacia gente completamente nueva, audiencias frías. Y eso es exactamente lo que hace paid social. ¿No? Entonces, ¿cuántas veces estuviste scrolleando en Instagram y te topaste con un producto del que nunca habías escuchado en tu vida, y resuelve un problema que ni sabías que tenías? Ese es el poder de paid social. Y resulta que meta es la plataforma de paid social más grande. Mientras que, por el contrario, Google es una plataforma de atracción (pull). Está atrayendo a gente que ya está buscando activamente su producto, su industria, o el problema que están tratando de resolver. Si les gusta la serie, asegúrense de seguirme para que puedan ver el episodio 2, donde voy a hablar sobre la estructura fundamental de meta ads.</t>
+          <t>Solo esta semana audité alrededor de cinco marcas de moda, joyería y accesorios en meta, que gastan entre $50,000 y unos $300,000 por mes. Y los errores, o digamos los problemas que estoy encontrando, son bastante similares entre estas cuentas, así que pensé en compartirlos con ustedes. El número 1 es que hay un gran impulso por el volumen de creatividades, con lo cual estoy totalmente de acuerdo, pero tiene que haber algo de orden en cómo estamos volcando las creatividades a la cuenta. Ahora mismo siento que, para muchas marcas, es como "hagamos toda esta creatividad y metámosla en un ad set a ver qué pasa". Y en realidad no hay ningún sistema detrás. No hay un razonamiento de si esto debería ser un ad set nuevo, porque esencialmente es un ángulo nuevo, o es un posicionamiento nuevo de la marca, y si en realidad deberíamos testearlo aparte de las otras creatividades que estamos haciendo. Por ejemplo, tuvimos una marca que ponía sus creatividades de regalo (gifting) para un producto específico junto con sus creatividades del día a día, y eso simplemente confunde al algoritmo sobre a quién ir a buscar. Creo que todo el mundo habla de diversificación de creatividades, pero igual sigo sin ver suficiente de eso. Para muchas de estas marcas premium, dentro de la cuenta de anuncios es solo contenido de campaña (fotos de shooting), lo cual sí tiene su lugar, pero, como ya lo mencioné un millón de veces, es solo una parte pequeña de tu estrategia de marca; hay un límite de cuánto meta va a identificar eso como un anuncio nuevo. Así que hay que pensar en cómo cubrir tus pilares [de contenido]. Ya sea contenido de creadores de UGC, contenido de clientas, contenido de regalos, videos de unboxing mostrando las prendas en un perchero. ¿Cómo podés crear distintos estilos de contenido que no sean solo tu shooting de campaña? Y el número 3 [nota: en el guion no se nombra explícitamente un "número 2"; el bloque anterior sobre diversificación funcionaría como tal [?]] en realidad no tiene que ver específicamente con el anuncio en sí, sino con el post-clic, que es realmente importante discutir. Hacemos mucho testeo con marcas de moda y de joyería, y con todas las marcas con las que trabajamos, sobre cuál es el destino correcto para mandar a la gente después de un clic. Y aunque no lo crean, esto realmente varía según el cliente y su tipo de nicho. Así que no hay un enfoque único para todos. Pero muchas de las cosas que estaba viendo eran mandarlos a la home, lo cual no es para nada lo correcto para una marca de moda, o mandarlos potencialmente a una página de colección cuando una página de producto podría tener una tasa de conversión más alta, o a veces mandarlos a una página de producto cuando la página de colección podría rendir mejor en conversión. Así que hay que diseccionar bien a dónde están yendo los anuncios después del clic para ayudar a mejorar los resultados del anuncio. Así que estos son los grandes errores. Asegúrense de no estar cometiéndolos, y si quieren una auditoría gratis de meta [corregido de "free meta order", error de reconocimiento], la ofrezco en el link de mi bio.</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical en dormitorio/living con decoración fija de fondo (lámpara, cuadro parcialmente visible tipo 'Overthinkers Club', póster, planta), campera de jean, micrófono de solapa, sin cortes de escena. Arranca con un gráfico de título de la serie en amarillo tipo sticker ('META ADS MUST HAVES Episode 1'). Subtítulos animados quemados palabra por palabra/frase corta, con gestos de mano para enfatizar.</t>
+          <t>Talking head en primer plano, top negro, fondo blanco con logo "MADE." detrás, título fijo arriba ("Meta Ad Mistakes I'm Seeing Right Now"), mismo encuadre estático en los tres frames, formato idéntico al resto de los videos de la cuenta.</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>Gancho: promesa aspiracional de estilo de vida (oficio digital bien pago, libertad de tiempo y ubicación). Estructura: episodio 1 de una serie educativa que sienta las bases conceptuales antes de avanzar, generando hábito de seguimiento. Gatillo: autoridad personal ('puedo dar fe de esto porque es lo que yo hago') y curiosidad por el próximo episodio.</t>
+          <t>Gancho de autoridad reciente y volumen ("esta semana auditué 5 cuentas de $50k-$300k") con formato listicle de errores numerados que genera identificación/FOMO en el espectador, cerrando con CTA de lead magnet (auditoría gratis).</t>
         </is>
       </c>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo celular, mic de solapa y buena luz de living/dormitorio, sin edición avanzada.</t>
+          <t>sí, nota: video de consejo a cámara sin locación especial, replicable con celular y buena luz; el valor está en la experiencia/casos reales citados.</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
@@ -5457,27 +5457,27 @@
     </row>
     <row r="54" ht="88" customHeight="1">
       <c r="A54" s="2" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -5492,48 +5492,48 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="J54" s="6" t="n">
-        <v>573</v>
+        <v>1465</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7642638640090336545</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7629795407534591254</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath ensena, paso a paso, como crear una metrica personalizada de 'hook rate' (tasa de retencion del gancho) dentro del Administrador de Anuncios de Meta.</t>
+          <t>Matt Bell explica por qué el ROAS que reporta Meta puede estar inflado por solapamiento con otros canales (afiliados, SEO), y muestra en un dashboard cómo distintos modelos de atribución (first click, total impact, last click) de herramientas como Triple Whale o Northbeam dan cifras muy distintas para decidir dónde cortar gasto.</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>Como analizar tus hooks de anuncios de Meta: aca tenes un proceso de cinco pasos. Paso 1: anda al Administrador de Anuncios y hace clic en Columnas. Paso 2: seleccioná personalizar columnas. Paso 3: desplazate hacia abajo y crea una metrica personalizada. Paso 4: nombrala 'hook rate'. Paso 5: configura la formula: tu hook rate es las reproducciones de video de 3 segundos dividido las impresiones. Despues hace clic en guardar y va a aparecer junto a cualquier anuncio de video que tengas en tu cuenta de anuncios.</t>
+          <t>Ahora, cuando estás escalando un negocio a través de anuncios pagos [corregido de "paydays", error de reconocimiento], vas a tener un montón de cosas distintas corriendo de fondo: vas a tener email, vas a tener orgánico, vas a tener afiliados. Y lo que suele pasar es que meta, por ejemplo, les va a mostrar tus anuncios a personas que llegaron a tu sitio, digamos, a través de un link de afiliado o por SEO, y como resultado [corregido de "as a resolver"] meta puede sobrereportar, porque está compartiendo las impresiones que se solapan con gente que también vino de un canal distinto, pero como recibieron un anuncio de meta en una ventana de tiempo específica, después se los clasifica como una conversión en meta. Y ven acá, por ejemplo, que meta está reportando un ROAS [corregido de "row s", error de reconocimiento] de 7x, que si solo miraran meta ahora mismo pensarían que es increíble. Si miro, por ejemplo, el first click (primer clic), pueden ver que el ROAS [corregido de "Ross"] en realidad se mide en 2.4. Si voy al impacto total, pueden ver que es 3.69. Y si voy al last click (último clic), va a ser otra cosa completamente distinta a lo que meta está reportando actualmente dentro de Ads Manager. Y ahí está la belleza de usar una herramienta de atribución como Triple Whale [corregido de "triple well"], como Northbeam [corregido de "North Beam"], no importa cuál uses, personalmente yo prefiero Triple Whale. Pero si miran acá, esta cuenta está gastando $274,000 en los últimos 30 días, y pueden ver que somos muy dominantes en Google. Pero si empiezo a mirar estos distintos modelos de atribución y lo desgloso por canal, y entro al canal, puedo mirar la campaña, puedo mirar el rendimiento de los anuncios, y muy rápidamente empezás a encontrar áreas de desperdicio que hay que cortar. Y después empezás a mirar el MER [corregido de "Mer"], entendés cuál tiene que ser tu objetivo de MER, y empezás a optimizar en base a esas métricas. Ahora, si no estás usando herramientas como esta, es muy difícil escalar de forma rentable, porque hay tanto pasando, hay tanto solapamiento, que es muy difícil entender de dónde viene realmente la gente que después convierte, y en realidad no vas a saber qué canal está generando las conversiones.</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>Arranca con Ben a camara con el titulo superpuesto ('How to analyse your Meta Ad hooks'); despues el video se divide en dos: arriba Ben hablando en formato pequeno con vineta, abajo grabacion de pantalla del Administrador de Anuncios (panel de Personalizar columnas, creacion de metrica personalizada) con subtitulos de palabra clave ('scroll', 'views').</t>
+          <t>Sin talking head: tarjeta de texto roja fija ("Why attribution tools are a must when you want to scale ads") sobre una captura/grabación de pantalla de un dashboard de atribución con métricas (porcentajes, montos en dólares, tabla por canal: Google Ads, Meta, Klaviyo, TikTok, Direct). Los tres frames capturados son prácticamente idénticos, lo que sugiere una imagen fija sostenida con narración en off.</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>Gancho de tutorial claro con promesa de proceso ('a five step process'); estructura numerada (paso 1 a 5) facil de seguir y de guardar; gatillo de utilidad practica inmediata para cualquier anunciante.</t>
+          <t>Gancho de autoridad/urgencia en el título (las herramientas de atribución "son un must" para escalar) reforzado con prueba visual concreta: cifras reales que contrastan el ROAS inflado de Meta contra otros modelos de atribución, generando credibilidad técnica.</t>
         </is>
       </c>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>si, solo requiere grabar la pantalla del Administrador de Anuncios y explicar los pasos a camara.</t>
+          <t>sí, nota: solo necesita una tarjeta de texto y una captura de pantalla de un dashboard (propio o de ejemplo), sin cámara ni edición avanzada.</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -5549,15 +5549,15 @@
     </row>
     <row r="55" ht="88" customHeight="1">
       <c r="A55" s="2" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -5569,12 +5569,12 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Macie Reed</t>
+          <t>MADE Marketing (Maddi)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -5584,33 +5584,33 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>466</v>
+        <v>1463</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maciereedmarketing/video/7664783404147150094</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7666767722230959367</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Cuarto episodio de la serie donde Macie explica las dos decisiones clave de presupuesto en Meta Ads (diario vs. de por vida, y presupuesto a nivel de campaña vs. de conjunto de anuncios) y cierra promocionando la lista de espera de su curso.</t>
+          <t>Maddi propone 3 tipos de creatividad para marcas 'desire first' (que venden deseo/estilo de vida): anuncio de deseo (top of funnel), anuncio de fundador/marca (middle of funnel) y anuncio de prueba social (bottom of funnel), como ejemplo de diversificación real de contenido.</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr">
         <is>
-          <t>Bienvenidos de nuevo a Meta Ads Must-Haves episodio 4, donde en esta serie les estoy enseñando todo lo que necesitan saber sobre Meta Ads para que puedan convertirse en un Meta Ads manager y ganar una tonelada de dinero y trabajar una fracción del tiempo. En el episodio de hoy vamos a hablar sobre presupuestos, porque hay dos decisiones que tenés que tomar cuando se trata de presupuesto. La primera decisión es si querés hacer un presupuesto diario versus uno de por vida (lifetime). Diario significa: che Meta, tenés tal cantidad de dinero que quiero que gastes todos los días indefinidamente hasta que te diga lo contrario. Y presupuesto de por vida significa: che, tenés esta suma total de dinero que necesito que gastes entre tal fecha y tal fecha. Y una vez que se gastó el dinero o pasó esa última fecha, entonces apagás la campaña. Generalmente les recomiendo a todos hacer presupuesto diario porque podés controlar manualmente tu presupuesto mucho más fácil y extender la vida de una campaña todo el tiempo que necesites. Después, la segunda decisión que tenés que tomar es dónde querés determinar tu presupuesto. En un episodio anterior mencioné que puede ser a nivel de campaña o a nivel de conjunto de anuncios (ad set). A nivel de campaña, básicamente le estás diciendo: che Meta, tenés tal cantidad de dinero que quiero que gastes todos los días dividido entre mis conjuntos de anuncios como te parezca mejor para conseguirme el mejor retorno de mi inversión publicitaria. Mientras que tal vez en realidad necesitás testear diferentes elementos dentro de tu anuncio. Entonces necesitás limitar tu variable de gasto y hacer que cada conjunto de anuncios gaste la misma cantidad. En ese caso, vas a hacer una optimización de presupuesto a nivel de conjunto de anuncios y decir: che, quiero $30 para este conjunto de anuncios todos los días, 30 para este, y 30 para este otro. Y eso es esencialmente la idea general de cómo determinar tu presupuesto. Muchos de ustedes están disfrutando esta serie y en realidad me estuvieron pidiendo un curso. Así que estoy trabajando en un meta ads crash course que va a ser un curso de meta ads amigable para principiantes. Y mientras trabajo en construir esto, en realidad ya abrí mi lista de espera. Entonces si se unen a mi lista de espera, tienen acceso anticipado, precio con descuento, y voy a compartir contenido extra.</t>
+          <t>Si yo estuviera manejando una cuenta de anuncios para una marca "desire first" (que vende primero el deseo), acá hay 3 tipos de creatividad que lanzaría, y ninguno es otra toma de marca o de producto (product shop). El primero es un anuncio de deseo (desire ad). Esto vende el estilo de vida, no el producto. Pensá en un "fit check" o cuando una chica se prueba un outfit y le encanta cómo se ve. El deseo es lo que realmente gana el clic. Esto es tu top of funnel. El segundo es el anuncio de fundador o de marca. Puede ser hablando a cámara, puede ser b-roll con voz en off. Esto es el porqué detrás de la marca, la historia detrás de ese producto específico, o incluso la decisión que casi no tomaste. La gente no compra por lógica, compra por creencia. Esto es lo que construye confianza, y eso es tu middle of funnel. El tercero son tus anuncios de prueba social. Gente real, escenarios reales. Pensá en ese cumplido no solicitado, o en ese mensaje de una amiga que dice "¿de dónde sacaste eso?". La historia que ella publicó sin etiquetar tu marca. La prueba es lo que cierra a la gente que el deseo trajo. Y por supuesto, esto es tu bottom of funnel. Así que pueden ver tres formatos, tres etapas del funnel. Eso es diversificación, no tres versiones de una toma de producto. Así que recuerden: el deseo gana el clic, la marca construye la confianza, y la prueba lo cierra. Y necesitás las tres.</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical, mismo tipo de set/decoración que otros episodios de la serie (pared clara, cómoda, lámpara, cuadro, planta), esta vez con sweater a rayas y sosteniendo una taza. Subtítulos automáticos animados palabra por palabra, con al menos un error tipográfico visible en pantalla ('A FRADTION' en vez de 'a fraction'). Sin gráficos de apoyo adicionales en los frames vistos, sin cortes de escena.</t>
+          <t>Combina talking head (mujer sentada en sillón claro, top con texto animado en rojo tipo "are" superpuesto) con clips de ejemplo/B-roll de una marca real (se ve un video borroso con boceto de moda de fondo y watermark de TikTok "@zimmermann") y tarjetas de texto grandes tipo tipografía editorial ("PROOF is what closes the") sobre fondo color crema. Más variedad de recursos visuales (cortes a ejemplos + tipografía grande) que otros videos de la cuenta.</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Gancho: continuidad de la serie educativa numerada que ya construyó audiencia en episodios previos. Estructura: 'dos decisiones' de presupuesto explicadas de forma clara y aplicable de inmediato. Gatillo: urgencia comercial al cierre (lista de espera con acceso anticipado y descuento) que capitaliza el interés generado por el contenido educativo gratuito.</t>
+          <t>Gancho de utilidad segmentada (dirigido específicamente a marcas "desire first") con framework simple de 3 tipos ligado a las 3 etapas del funnel, fácil de recordar, reforzado con un cierre tipo mantra ("el deseo gana el clic, la marca construye confianza, la prueba cierra") que funciona como frase citable.</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: mismo formato de bajo costo que el resto de la serie, solo celular y mic de solapa.</t>
+          <t>sí, nota: la base es talking head con guion claro; usar clips de ejemplo de otras marcas como ilustración es opcional y de bajo costo.</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
@@ -5641,17 +5641,17 @@
     </row>
     <row r="56" ht="88" customHeight="1">
       <c r="A56" s="2" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Solución de un problema</t>
+        <v>88</v>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -5676,33 +5676,33 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>2063</v>
+        <v>1378</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7650270956841143560</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7629597512055147784</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Maddi cuenta el caso de una cuenta de Meta Ads de $200,000/mes con campañas fragmentadas y solapadas (mismas audiencias/targeting) heredadas de la agencia anterior, y cómo consolidarlas para mejorar la 'densidad de señal' y bajar el MER.</t>
+          <t>Maddi, de la agencia MADE Marketing, cuenta en modo 'detrás de escena' cómo triplicaron los ingresos de una marca de moda en 45 días, mostrando el dashboard de ventas real y explicando su estrategia de un solo producto ganador, diversificación creativa semanal y anuncios de misión de marca.</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>¿La fragmentación está matando tu cuenta de anuncios? Recién nos hicimos cargo de una cuenta de anuncios que gasta $200,000 por mes en meta ads. Y lo primero que notamos fue que esta marca y su agencia anterior estaban creando campañas literalmente porque sí, sin ningún motivo real. No había ningún factor que identificara por qué se armó esta campaña, cuál era la diferenciación entre una y otra. Y en su mayoría las campañas se superponían con similitudes de creatividad, los mismos tipos de persona (audiencia), básicamente el mismo targeting, lo cual en mi opinión hacía que su frecuencia subiera y también que su CPA fuera bastante alto. Sabemos que meta premia la densidad de señal, es decir, quiere tener toda la señal posible dentro de esa única campaña para poder brillar; eso es después de Andromeda [actualización del algoritmo de Meta]. Entonces cuando nos hicimos cargo de esta cuenta, no cortamos todo de una, porque eso también puede ser peligroso. Pero vimos cómo podíamos consolidar lo que estaba ganando en ciertos activos (assets) dentro de otros activos, y buscamos reducir las campañas y los activos dentro de la cuenta. Ahora, por supuesto, su MER [corregido de "Mir", error de reconocimiento] bajó, porque no están compitiendo contra sí mismos en estas campañas. Meta sabe a quién ir a buscar, y consolidaron y crearon una señal excelente para que meta la use.</t>
+          <t>Cómo logramos resultados como este en probablemente unos 45 días trabajando con esta marca de moda. Ahora mismo esta semana están en [?] alrededor de 7, y lo hemos ido mejorando semana a semana, lo cual también es muy emocionante de ver dentro de la cuenta. Lo más importante que hicimos cuando empezamos a trabajar con esta clienta fue recortar mucho su oferta de productos. Nos enfocamos en lo que estaba funcionando con los anuncios de marcas de moda. Si tenés productos que vendés continuamente y podés encontrar un best seller, literalmente podés obtener resultados como este vendiendo un solo producto; en este caso es literalmente un solo producto, enfocándonos en eso y realmente creando un producto viral en Meta Ads. Lo siguiente que hicimos fue subir contenido nuevo de forma consistente cada semana, y no estamos haciendo volúmenes descabellados, es muy manejable para esta clienta, pero realmente nos enfocamos semana a semana en la diversificación creativa. Entonces cada pieza de contenido es muy intencional en base a las ventas que estamos viendo fuera de la plataforma, porque esto viene en una variedad de colores, y analizamos cada pieza de contenido que subimos asegurándonos de que sea muy distinta a la última que publicamos, y que todo cuente una historia coherente. Lo tercero que hicimos, que creo que muchas marcas de moda no hacen, es que nos enfocamos mucho en anuncios de visión y misión de marca. La razón real por la que esta marca fue fundada. Creo que la gente se olvida de esto en una marca de moda. Piensan que la gente compra solo porque le gusta la prenda. Pero creo que cuando pueden ver la intención o los aspectos intencionales, eh, las razones por las que eligieron la tela o por qué fundaron la marca o los bocetos y todo esto, realmente atrae a la gente y genera esa confianza mucho más rápido. Así que esas fueron las principales cosas en las que nos enfocamos en los últimos 45 días para aumentar los ingresos de esto. Y estoy muy emocionada de ver a esta marca escalar más.</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano, top oscuro, fondo blanco liso, título fijo arriba ("Stop Creating New Campaigns In Meta") y subtítulos incrustados palabra por palabra en la parte inferior (se leen fragmentos como "we just took over an ad account spending $200,000 per month" y "same persona types, really the same targeting"). Mismo plano estático en los tres frames.</t>
+          <t>Talking head vertical en selfie, cara en primer plano con micrófono de solapa, misma locación de fondo claro en los tres frames sin cortes visibles. Se superpone de forma fija una captura de pantalla de un dashboard de ventas (gráfico 'Gross sales' / 'Total sales over time') en la parte superior del cuadro. Subtítulo grande en negrita tipo título ('How We Tripled This Fashion's Brand Revenue In 45 Days') quemado como hook inicial.</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="Q56" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta retórica/alarma ("¿la fragmentación está matando tu cuenta?") sobre una cifra grande ($200k/mes) que da autoridad, con estructura diagnóstico-causa-solución que enseña un concepto técnico (densidad de señal / MER) de forma aplicable.</t>
+          <t>Gancho: cifra de resultado concreto y verificable con captura real del dashboard ('triplicamos los ingresos en 45 días'). Estructura: relato de 'las 3 cosas que hicimos' (producto único, diversificación creativa semanal, anuncios de misión de marca). Gatillo: prueba social/autoridad (datos reales en pantalla) que genera confianza y curiosidad sobre el método replicable.</t>
         </is>
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: video de consejo a cámara con subtítulos dinámicos, replicable con celular y una app de edición de captions gratuita.</t>
+          <t>sí + nota: solo necesita una persona hablando a cámara con micrófono y una captura de pantalla de resultados reales, sin edición compleja.</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -5733,17 +5733,17 @@
     </row>
     <row r="57" ht="88" customHeight="1">
       <c r="A57" s="2" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Solución de un problema</t>
+        <v>37</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -5768,33 +5768,33 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>1485</v>
+        <v>1338</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7633738600223411464</t>
+          <t>https://www.tiktok.com/@madecreativeco/video/7641559635861736712</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Maddi resume los errores más comunes que encontró auditando cinco cuentas de Meta Ads de marcas de moda/joyería ($50k-$300k/mes): creatividad sin sistema, falta real de diversificación de contenido más allá de fotos de campaña, y destinos de post-clic mal elegidos.</t>
+          <t>Maddi (MADE Marketing) muestra su proceso al incorporar una nueva marca de 2 millones de dólares mensuales a la agencia, explicando el documento de research que usa para auditar los anuncios ganadores y armar el calendario creativo antes de tocar la cuenta publicitaria.</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>Solo esta semana audité alrededor de cinco marcas de moda, joyería y accesorios en meta, que gastan entre $50,000 y unos $300,000 por mes. Y los errores, o digamos los problemas que estoy encontrando, son bastante similares entre estas cuentas, así que pensé en compartirlos con ustedes. El número 1 es que hay un gran impulso por el volumen de creatividades, con lo cual estoy totalmente de acuerdo, pero tiene que haber algo de orden en cómo estamos volcando las creatividades a la cuenta. Ahora mismo siento que, para muchas marcas, es como "hagamos toda esta creatividad y metámosla en un ad set a ver qué pasa". Y en realidad no hay ningún sistema detrás. No hay un razonamiento de si esto debería ser un ad set nuevo, porque esencialmente es un ángulo nuevo, o es un posicionamiento nuevo de la marca, y si en realidad deberíamos testearlo aparte de las otras creatividades que estamos haciendo. Por ejemplo, tuvimos una marca que ponía sus creatividades de regalo (gifting) para un producto específico junto con sus creatividades del día a día, y eso simplemente confunde al algoritmo sobre a quién ir a buscar. Creo que todo el mundo habla de diversificación de creatividades, pero igual sigo sin ver suficiente de eso. Para muchas de estas marcas premium, dentro de la cuenta de anuncios es solo contenido de campaña (fotos de shooting), lo cual sí tiene su lugar, pero, como ya lo mencioné un millón de veces, es solo una parte pequeña de tu estrategia de marca; hay un límite de cuánto meta va a identificar eso como un anuncio nuevo. Así que hay que pensar en cómo cubrir tus pilares [de contenido]. Ya sea contenido de creadores de UGC, contenido de clientas, contenido de regalos, videos de unboxing mostrando las prendas en un perchero. ¿Cómo podés crear distintos estilos de contenido que no sean solo tu shooting de campaña? Y el número 3 [nota: en el guion no se nombra explícitamente un "número 2"; el bloque anterior sobre diversificación funcionaría como tal [?]] en realidad no tiene que ver específicamente con el anuncio en sí, sino con el post-clic, que es realmente importante discutir. Hacemos mucho testeo con marcas de moda y de joyería, y con todas las marcas con las que trabajamos, sobre cuál es el destino correcto para mandar a la gente después de un clic. Y aunque no lo crean, esto realmente varía según el cliente y su tipo de nicho. Así que no hay un enfoque único para todos. Pero muchas de las cosas que estaba viendo eran mandarlos a la home, lo cual no es para nada lo correcto para una marca de moda, o mandarlos potencialmente a una página de colección cuando una página de producto podría tener una tasa de conversión más alta, o a veces mandarlos a una página de producto cuando la página de colección podría rendir mejor en conversión. Así que hay que diseccionar bien a dónde están yendo los anuncios después del clic para ayudar a mejorar los resultados del anuncio. Así que estos son los grandes errores. Asegúrense de no estar cometiéndolos, y si quieren una auditoría gratis de meta [corregido de "free meta order", error de reconocimiento], la ofrezco en el link de mi bio.</t>
+          <t>Estoy trabajando en un flujo de trabajo creativo para una marca que factura 2 millones de dólares al mes, y pensé en mostrarles detrás de cámaras cómo empieza el proceso. Esta marca básicamente contrató a MADE, o a mí, para ser la conexión entre su equipo creativo interno y también su agencia de compra de medios. Entonces, aunque nosotros también hacemos la compra de medios, a veces las marcas nos contratan más como estrategas creativos fraccionales o servicios de CMO fraccional para cerrar las brechas entre, eh, los equipos internos y externos. Entonces mi trabajo es mejorar el flujo de trabajo creativo y ponerlo en marcha, también mejorar los resultados de su creatividad y ayudar donde sea posible a mejorar los resultados de la compra de medios. Entonces lo primero que hago es completar este documento que repasa los últimos 30 días: cuáles son sus anuncios ganadores y sus potenciales, como ganadores o algo así como sus ganadores, y lo que esto me ayuda a identificar son básicamente las cosas centrales que estoy viendo, o sea, los públicos objetivo (personas), los gatillos emocionales, qué tipo de contenido es. ¿Son solo estáticos o videos? ¿Es un solo estilo de creativo publicitario? ¿Cuál es la estructura? ¿Cuál es el tipo de producción? Y después entro obviamente en los resultados acá, que en realidad no les voy a mostrar porque ahí tenemos resultados, pero miro obviamente el CPA, el ROAS [?], el hook, el hold, el CTR saliente (outbound), los insights de frecuencia, y cuáles creo que serían los próximos pasos lógicos. Después empiezo a armar como un flujo semanal de cómo se vería con los equipos en términos de lunes a viernes, y entonces, ¿cuál es mi primer objetivo para esta clienta? Vamos a empezar con 10 creativos nuevos como mínimo por semana, y lo fui desglosando en: bueno, ¿cómo se verían las iteraciones? ¿Cuántas iteraciones quiero tener y cuántos conceptos completamente nuevos? Y voy desglosando esto, eh, por personas o tipos de producto, y después empiezo a mapear esto en un calendario. Ahora, obviamente mis iteraciones acá van a ser un poco más reactivas, pero me gusta tener mis iteraciones planeadas con al menos 2 semanas de anticipación, y después mi plan mensual queda totalmente definido en términos de mis conceptos completamente nuevos, en base a mi investigación de lo que está funcionando, eh, o lo que no está funcionando, y qué oportunidades puedo ver en las personas, pero también en el producto. También tengo esta especie de Matriz de Personas, que básicamente me dice cuáles creo que son las más fuertes para enfocarme, eh, así como cuáles pilares de contenido son nuestra prioridad, porque no los tenemos en la cuenta en este momento. Ahora, llevo trabajando con esta marca 3 semanas y todavía ni toqué un anuncio, porque esta parte es tan importante para realmente entender la cuenta publicitaria y empezar a mapear tu cadencia semanal, para que puedas tener éxito con tu testeo creativo.</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano, top negro, fondo blanco con logo "MADE." detrás, título fijo arriba ("Meta Ad Mistakes I'm Seeing Right Now"), mismo encuadre estático en los tres frames, formato idéntico al resto de los videos de la cuenta.</t>
+          <t>Talking head en oficina (pared de vidrio, escritorio, monitor de computadora) intercalado con capturas de pantalla grabadas de una hoja de cálculo de Google Sheets (el documento de flujo de trabajo creativo), con zoom y el dedo señalando celdas. Subtítulo grande en negrita en la intro; sin cortes de cámara adicionales, formato 'screen recording' + presentadora hablando.</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>Gancho de autoridad reciente y volumen ("esta semana auditué 5 cuentas de $50k-$300k") con formato listicle de errores numerados que genera identificación/FOMO en el espectador, cerrando con CTA de lead magnet (auditoría gratis).</t>
+          <t>Gancho: cifra grande y exclusiva ('marca de 2 millones de dólares al mes') más promesa de contenido 'detrás de escena'. Estructura: proceso paso a paso mostrando el documento real de auditoría creativa y el armado del calendario. Gatillo: autoridad/prueba social y curiosidad por ver documentos internos reales de una agencia que trabaja con marcas grandes.</t>
         </is>
       </c>
       <c r="R57" s="5" t="inlineStr">
         <is>
-          <t>sí, nota: video de consejo a cámara sin locación especial, replicable con celular y buena luz; el valor está en la experiencia/casos reales citados.</t>
+          <t>sí + nota: solo requiere grabar la pantalla de una hoja de cálculo propia y hablar a cámara, sin edición avanzada.</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
@@ -5825,15 +5825,15 @@
     </row>
     <row r="58" ht="88" customHeight="1">
       <c r="A58" s="2" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+        <v>89</v>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -5860,33 +5860,33 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>375</v>
+        <v>1333</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7662343318533082390</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7618955944449297696</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath enumera a los saltos, en formato de lista rapida, una serie de factores y metricas de Meta Ads calificandolos como importantes o no importantes (segun se ve en pantalla: segmentacion por interes, ajustes de presupuesto diario, calidad de audio, entre otros).</t>
+          <t>Ben Heath explica cómo cambian las campañas de Meta Ads según el presupuesto diario invertido: $10, $100, $1.000 y $10.000 al día, y qué debería priorizar el anunciante en cada nivel.</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>Extremadamente importante, no importante, muy importante, medio importante, ya no importante, importante, importante de nuevo, no importante, no muy importante, muy importante, muy importante, no tan importante como la gente cree, muy importante, medio importante, no importante mientras lo evites, no importante, no importante mientras no sea un problema, altamente importante.</t>
+          <t>Así se ven los anuncios de Meta con $10 al día, $100 al día, $1.000 al día y $10.000 al día. Con $10 al día, solo estás tratando de conseguir una prueba de concepto. ¿Realmente podés generar ventas? ¿Realmente podés generar leads con las campañas publicitarias que produjiste? Con $100 al día, Meta está empezando a aprender. Estás empezando a generar algunas conversiones. Podés hacer un poco de testeo. Es poco probable que sea un impulsor significativo de los ingresos de tu negocio, pero ya tenés impulso (momentum). Con $1.000 al día, necesitás sistematizar el proceso. Estás escalando lo que funciona. Estás rotando los creativos regularmente, y estás tomando decisiones basadas en datos. Con $10.000 al día, necesitás una máquina de producción de creativos publicitarios. Necesitás estar agregando constantemente anuncios de testimonios de clientes [?] (transcripto como "Clyde testimonial ads", probable error de reconocimiento de "client testimonial ads"), anuncios de partnership (alianzas) y creativos hechos internamente (in-house). También sueles enfocarte, en este nivel, en la incrementalidad y en exprimir todo lo que puedas de tus campañas publicitarias. Y ahora ya sabés...</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>Video en primer plano tipo selfie al aire libre (azotea/edificio, cielo despejado); cada corte muestra una etiqueta grafica distinta con el nombre del factor (por ejemplo 'IBT / Interest-based targeting', 'DBA / Daily budget adjustments', 'Audio quality') en distintos estilos de texto y color; ritmo de edicion muy rapido dado que en 23 segundos se listan cerca de 19 items. Nota: la transcripcion de audio es solo la secuencia de calificaciones, sin el nombre del item; la asociacion item-calificacion se ve unicamente en el video.</t>
+          <t>Talking head a cámara fija, plano medio, en interior con fondo neutro (pared blanca/gris con panel geométrico tipo estudio). Viste polo bordó. Grandes overlays de texto con las cifras en dólares (naranja, amarillo, verde) en la esquina superior izquierda que cambian según el tramo del que habla, más subtítulos en mayúscula blanca centrados en la parte baja, sincronizados por palabra/frase. Un solo plano, sin cortes de cámara ni b-roll adicional.</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>Formato de lista rapida tipo 'importante vs no importante' que genera intriga constante sobre que sigue; estructura repetitiva que facilita el scroll-stop por su ritmo; gatillo de curiosidad y autoevaluacion (el espectador chequea mentalmente si esta haciendo bien o mal cada punto).</t>
+          <t>Gancho de curiosidad numérico ("así se ven los anuncios con distintos presupuestos") + estructura de lista clara en 4 escalones crecientes + gatillo de autodiagnóstico práctico: el espectador identifica en qué nivel de gasto está y qué debería hacer a continuación.</t>
         </is>
       </c>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>si, es un video selfie con textos superpuestos, sin necesidad de edicion avanzada mas alla de las etiquetas.</t>
+          <t>sí + con celular, micrófono de solapa y un editor con texto animado alcanza; no requiere locación especial ni equipo caro.</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
     </row>
     <row r="59" ht="88" customHeight="1">
       <c r="A59" s="2" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>Solución de un problema</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -5952,33 +5952,33 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
-        <v>333</v>
+        <v>1240</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7632740460217322759</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7623388351776787744</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde comparte una lista numerada de hooks (ganchos de apertura) para anuncios de Facebook y UGC que, según él, ya están probados y funcionan de forma repetida para escalar cuentas publicitarias.</t>
+          <t>Ben Heath explica cómo seguir logrando resultados con Meta Ads después de la actualización del algoritmo Andromeda. Su consejo es reemplazar la regla de tener 20+ creatividades por empezar con solo 4 conceptos realmente distintos y después iterar sobre los detalles.</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
         <is>
-          <t>Si estás buscando una lista de hooks para anuncios de Facebook, o tal vez simplemente hooks de UGC que puedas reutilizar, que ya fueron testeados y que están comprobados que funcionan una y otra vez y escalan en una cuenta publicitaria, entonces este video es para vos. Número uno: 'público objetivo, no te duermas con esto' (target audience do not sleep on this). Ese es un gancho increíble para nombrar una audiencia específica. Entonces podrías decir algo como, ya sabés, 'dueños de negocios de e-commerce, no se duerman con esto', o 'dueños de agencias no se duerman con esto', o 'si sos un hombre de más de 35 años y estás sufriendo este problema, no te duermas con esto', ¿no? Realmente podés nombrar y ser muy específico. Número dos: '¿escuchaste mucho sobre X?'. Este generalmente es genial para crear curiosidad al principio de un anuncio, ¿no? Genera como una especie de FOMO [?] ('debería haber escuchado sobre esto hasta ahora'), ¿no? Número tres: 'la mayoría de las personas no saben cómo hacer X', que de nuevo, crea exclusividad. Es como que te sentís excluido si no sabés sobre esta cosa. 'Probé este truco (hack) de X para que vos no tengas que hacerlo'. Uno increíble, ¿okay? 'Te voy a compartir algo muy personal'. Eso también crea una historia, crea esta relación con la audiencia. 'Este truco me cambió la vida'. Muy similar, número cuatro: 'dejá de hacer esto', que básicamente ese es casi como un gancho de clickbait. Simplemente invita al usuario a seguir mirando el anuncio para enterarse de: ¿qué es esto? ¿De qué estás hablando?, ¿no?</t>
+          <t>¿Es posible seguir teniendo éxito con los anuncios de Meta después de la actualización Andromeda? Porque ahora mismo el consejo es que necesitás tener 20 o más creatividades publicitarias distintas activas en todo momento. Y para la mayoría de los negocios, eso es difícil de lograr. Así que acá va una forma diferente de abordarlo. No empieces con 20. Empezá con 4. Cuatro conceptos genuinamente diferentes. Puede ser un ángulo distinto, un formato distinto, un enfoque distinto. Eso va a ser suficiente para que Meta vea diversidad creativa. Y una vez que encontrás algo que funciona, podés empezar a testear los detalles más finos. Eso podría ser distintos hooks (ganchos), distintos overlays (superposiciones de texto/gráficos), blanco y negro versus color en tus imágenes estáticas o tus videos. Estructurá tus pruebas para que Andromeda no ignore tus variaciones. No necesitás 20 anuncios al azar. Necesitás fuerte diversidad arriba, precisión por debajo. Y así es como ganás después de Andromeda.</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical con fondo oscuro/neutro tipo oficina o estudio (silla de escritorio visible, planta), mic de mesa tipo streaming, sin cortes de escena entre los frames vistos. Se agrega un gráfico numerado tipo 'badge' amarillo con ícono de gancho/anzuelo para marcar cada punto de la lista (visible en el frame del punto 2). Subtítulos blancos simples quemados en el video.</t>
+          <t>Encuadre: plano medio fijo, cámara a la altura de los ojos, vertical. Subtítulos: palabra por palabra en mayúsculas, con 'META' resaltado en azul. Cortes: toma continua, sin cortes de cámara visibles. Gráficos: inserto de 4 tarjetas verdes con signos de pregunta que representan los '4 conceptos'. Locación: living/oficina en casa, con planta y estufa de leña de fondo.</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Gancho: promesa de utilidad inmediata tipo 'lista de recursos listos para usar' (hooks ya probados). Estructura: lista numerada fácil de guardar y aplicar directamente en la propia cuenta. Gatillo: utilidad práctica y autoridad (afirma que estos hooks 'escalan' cuentas reales), lo que invita a guardar el video como referencia.</t>
+          <t>Gancho: pregunta directa sobre si todavía se puede tener éxito tras un cambio de algoritmo reciente (Andromeda), apela a la ansiedad/incertidumbre del anunciante. Estructura: contraste entre el consejo 'oficial' (20 creatividades) y su propuesta alternativa (4 conceptos), con explicación del mecanismo y ejemplos concretos de qué variar. Gatillo: recomendación contraintuitiva y accionable con un número específico, posiciona al creador como quien tiene una lectura más inteligente que el consenso general.</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo cámara, mic de mesa económico y un gráfico simple de número superpuesto, editable en apps gratuitas.</t>
+          <t>Sí — solo requiere cámara/celular y un gráfico simple (tarjetas con signos de pregunta), sin equipo profesional.</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -6009,32 +6009,32 @@
     </row>
     <row r="60" ht="88" customHeight="1">
       <c r="A60" s="2" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -6044,48 +6044,48 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>304</v>
+        <v>1236</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7634298092455480584</t>
+          <t>https://www.tiktok.com/@officialmattbell/video/7648727626592406806</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde muestra cómo generó con IA (Google Veo 3) un video-hook para un cliente de productos blanqueadores de dientes, compartiendo el prompt exacto que usó y el resultado final en pantalla dividida.</t>
+          <t>Matt Bell comparte en pantalla los resultados reales de una campaña ASC (Advantage+ Shopping) de Meta que está funcionando bien para una marca de e-commerce, mostrando métricas de alcance, frecuencia y costo por conversión.</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>Como ven, este hook de acá fue generado enteramente usando IA. Ya no necesitás esperar para conseguir stock footage, o tal vez si sos un marketer que recibe assets de un cliente, todo lo que necesitás ahora es la nueva herramienta de video Veo 3 de Google para generar todo el stock footage y b-roll que necesites. Podés usar esto de dos formas diferentes. Podés usarlo simplemente para generar b-roll y metraje, como te voy a mostrar en este video, o también podés hacer que la gente hable. Entonces acá lo que le puse [al prompt] fue: crear un video de una mujer hermosa de 23 años, pelirroja, con maquillaje suave y pelo ondulado, mirándose a sí misma en el espejo del baño. El baño es de un estilo escandinavo [?] moderno y prolijo. El ángulo de cámara está justo detrás de su hombro. Está sonriendo suavemente [?]. Se está cepillando los dientes y hay un líquido color púrpura en código hexadecimal [?]. Y después le puse un líquido de código de color hexadecimal X goteando de su boca. Mi objetivo acá es que uno de nuestros clientes en realidad vende productos blanqueadores de dientes, que en realidad son de color amarillo. Y entonces por eso quería crear algo que fuera como shockeante. Si silencio el video acá y le doy play, pueden ver que empieza a cepillarse los dientes, pero se pone un poco raro en cierto punto, ¿no? Se puede ver como que ahora, por alguna razón, se está cepillando la cara. Y entonces pensé: bueno, ahora lo que queremos hacer acá es, ya saben, una vez que termina, apoya el cepillo de dientes sobre la mesada. Se suponía que solo se iba a cepillar los dientes, no toda la cara. Y entonces reproduje esto acá. Fue un poco raro al principio porque, de nuevo, se metía más hacia el interior de su mejilla, pero de ahí en adelante se veía, ya saben, mejor hacia el final. Así que de hecho usamos parte de ese clip. Esto es, de nuevo, una forma muy simple de mostrarles cómo usarlo. Y entonces, ¿no?, pueden ver que este del lado izquierdo es todo de Veo [?]. Bueno. Pero es el tipo de cosa que cuando la ves en tu feed, decís '¿qué mierda es eso?', ¿no? Y ese es el objetivo con esto. Ese es el objetivo, conseguir un hook fuerte. Es como esa misma imagen acá arriba, pero también hicimos otra acá, que es como simplemente dientes más amarillentos y como dientes grandes mostrándose acá en el medio, que de nuevo, es el tipo de cosa que ves en tu feed y decís '¿qué es eso?'. Y entonces si mirás algunos de estos otros ejemplos, que tienen una tasa de hook súper, súper alta, como 91%, 67%, 75%, todos esos como 'wow, ¿qué es eso?', ese tipo de hook. Que es lo que estamos tratando de hacer más, utilizando Veo 3 hoy en día.</t>
+          <t>Quiero darles una actualización porque estoy usando campañas ASC ahora mismo, campañas de compras Advantage+, y en realidad están funcionando muy bien. Básicamente es una campaña abierta y amplia que usa optimización de presupuesto de campaña (CBO). Y en ese conjunto de anuncios tengo alrededor de 15 creativos. Y quiero mostrarles las métricas principales de los últimos 30 días acá. Como pueden ver, tuvimos un alcance de un millón de personas, que es bastante fuerte, pero la frecuencia es de 4x. Entonces naturalmente está haciendo retargeting de gente dentro de esta campaña. Y solo para darles más contexto, tengo otras campañas corriendo, que oculté acá, pero básicamente tengo una campaña de tope de embudo corriendo con exclusiones de quienes ya interactuaron con los anuncios y también visitaron el sitio web de esta marca. Y después tengo otra campaña que hace retargeting a clientes existentes, retargeting de tráfico y retargeting de interacción. Y esta es la campaña dominante en términos de gasto publicitario. Pueden ver que tuvimos 4.300 compras acá. Estamos usando cualquier creativo que haya funcionado bien, ya sea orgánicamente o en una campaña estándar de tope de embudo. Entonces, usualmente en esta cuenta, si estuvimos testeando un conjunto de anuncios que tuvo 20 o más conversiones a un costo razonable o mejor que el promedio, entonces duplicamos ese anuncio y lo corremos dentro de esta ASC. Esta es la única marca con la que estoy probando esto por ahora. Usualmente esta marca paga alrededor de $25 por conversión. Ahora mismo está en $18, y podría bajar más optimizando el creativo. Ahora, si vieron mis otros videos, sabrán que en realidad no fui fanático de ASC por un tiempo. Dejé de usarla porque encontré mucha evidencia que sugería que ya no eran confiables. Pero en este caso, hemos estado empujando fuerte una campaña de tope de embudo que está consiguiendo mucho tráfico nuevo. Entonces no me preocupa tanto esta relación de alcance a frecuencia. Y parece estar funcionando bastante bien. De hecho la vengo corriendo desde hace bastante tiempo. Pueden ver que tuvimos 21.000 compras de por vida, una frecuencia de por vida de [?] x, un CPA de $17,65 con casi $400.000 de gasto. Entonces recomendaría probar una campaña ASC, especialmente si sos de e-commerce y tenés múltiples SKUs y múltiples creativos. Probablemente solo haría esto cuando ya tengas una estructura de tope de embudo y fondo de embudo, y después agregues esto encima. Tenés que estar atento a esta frecuencia. Tenés que cuidarte del solapamiento de subastas (auction overlap). Pero como pueden ver, hay muchos datos acá y en Triple Whale [?] que respaldan que esta campaña está funcionando, y voy a seguir trabajando para seguir escalándola.</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>Talking head en estudio/oficina con fondo oscuro y planta, mic de mesa, sin cortes en la primera parte. A mitad de video pasa a formato de pantalla dividida (split screen) mostrando debajo del presentador el resultado del video generado por IA (dos clips de una mujer cepillándose los dientes con líquido violeta, y un soporte de cepillos de dientes). Subtítulos blancos simples quemados. El propio video generado por IA funciona como el 'hook' de ejemplo que se está explicando.</t>
+          <t>Es prácticamente solo una grabación/captura de pantalla del panel de Meta Ads Manager en tema oscuro, con las métricas reales de la cuenta (Resultados, Alcance, Frecuencia, Costo por resultado, Presupuesto, Gasto, Impresiones, CPM); no aparece el presentador en cámara en los frames vistos, es voz en off narrando sobre el dashboard. Un cintillo de texto rojo fijo en la parte superior funciona de hook ('New insight on ASC Meta campaigns performing well'); se ve el dock de iOS en la parte inferior, sugiriendo una grabación de pantalla de dispositivo móvil pegada en formato vertical. Sin cortes de escena, sin gráficos adicionales, locación no aplica (solo pantalla).</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>Gancho: intriga visual inmediata ('este hook fue generado enteramente con IA'). Estructura: caso práctico paso a paso, mostrando el prompt exacto usado y el resultado, más el dato de tasas de hook reales (91%, 67%, 75%). Gatillo: curiosidad/asombro por lo inusual ('qué mierda es eso') combinado con utilidad de tutorial replicable.</t>
+          <t>Gancho: actualización de un profesional compartiendo datos en vivo de su propia cuenta ('quiero darles una actualización'). Estructura: recorrido por cifras reales concretas (alcance, frecuencia, CPA, gasto total) que sirve de evidencia paso a paso. Gatillo: autoridad y transparencia (muestra números reales, incluso admite que antes dudaba de ASC), lo que genera confianza y comentarios de otros media buyers.</t>
         </is>
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>sí, con nota: requiere acceso a una herramienta de IA generativa de video de pago/créditos (Google Veo 3), pero no equipo de filmación caro.</t>
+          <t>sí + nota: solo necesita grabar la pantalla del Ads Manager propio y narrar, cero producción adicional.</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -6101,15 +6101,15 @@
     </row>
     <row r="61" ht="88" customHeight="1">
       <c r="A61" s="2" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+        <v>91</v>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -6121,12 +6121,12 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -6136,33 +6136,33 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>295</v>
+        <v>1219</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7629809400877681927</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7626399562290171168</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde resume en 58 segundos su framework completo para arrancar y escalar una cuenta de Meta ads, desde definir buyer personas y espiar competidores hasta la regla de optimización a los 7 días.</t>
+          <t>Ben Heath explica una estrategia para construir marca (no solo generar ventas) usando Meta Ads, combinando anuncios protagonizados por el fundador con anuncios de partnership con creadores e influencers.</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr">
         <is>
-          <t>Gasté cerca de $10 millones de dólares en anuncios de Facebook tan solo en los últimos seis meses; denme 58 segundos y les muestro exactamente cómo arrancar y escalar tu cuenta de meta ads. Entendé que en esta era post-'end of meta' [?] (frase poco clara en el audio original, posiblemente referida a la era posterior a los cambios de privacidad de iOS14/Meta) todo se trata de los creativos. Lo primero que haría si fuera vos es definir tres ICPs objetivo, o sea tres personas (buyer personas) únicas y diferentes que tengas. A partir de ahí, listaría los tres a cinco principales deseos y puntos de dolor que tiene cada una de ellas. Y después, a partir de ahí, lo que haría es encontrar competidores que estén anunciando para exactamente el mismo ICP, y robarles ('snipearles') sus anuncios estáticos de mayor duración en el tiempo, para después poder replicarlos para mi ICP y sus puntos de dolor. Después voy a ir al ads manager, crear una sola campaña y fijar mi presupuesto diario como una campaña CBO (optimización de presupuesto de campaña) para superar mi objetivo de KPI multiplicado por la cantidad de anuncios que quiero lanzar. Voy a crear un conjunto de anuncios por cada creativo que quiera lanzar, y configurar mi segmentación como ubicación automática, y programar que esos anuncios salgan en vivo a medianoche. Después voy a dejar que esto corra durante siete días. Y a los siete días voy a volver a revisar la cuenta, eliminar todo lo que no esté funcionando, y si la campaña en general es rentable, la voy a escalar un 20 por ciento, en base a que los últimos siete días demuestren ser rentables.</t>
+          <t>Así es como construís una marca con los anuncios de Meta. La mayoría de los negocios usan los anuncios de Meta para generar leads y ventas, y eso tiene sentido, pero si lo hacés de forma inteligente, también podés construir una marca al mismo tiempo si usás una combinación de anuncios protagonizados por el fundador (founder-led ads) y anuncios de partnership, donde te asociás con creadores e influencers para promocionar tus productos y servicios en tu nombre. Si te asociás con la gente correcta y le acertás al tono, los valores que tu público objetivo asocia con esos creadores e influencers pueden trasladarse a tu marca con el tiempo.</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical en estudio/oficina con fondo oscuro, silla tipo gamer, planta, mic de mesa, sin cortes de escena visibles ni gráficos adicionales más allá del texto de título. Texto de título grande en verde neón ('$10M Ad Strategy in 58 Seconds') al inicio a modo de gancho visual. Subtítulos blancos simples palabra por palabra, ritmo acelerado acorde a la promesa de brevedad.</t>
+          <t>Encuadre: plano medio, con cambio de ángulo entre frames (perfil en uno, frontal en otro), lo que sugiere cortes de cámara. Subtítulos: palabra por palabra en mayúsculas. Cortes: salto entre distintos ángulos de cámara (jump cuts). Gráficos: captura de un anuncio real de Meta (perfil 'Ben Heath', texto 'I gave recently...', botón 'Learn more') insertada como prueba. Locación: living con sofá, lámpara y caballete de arte de fondo.</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Gancho: autoridad y cifra grande impactante ('gasté casi $10 millones') combinada con promesa de brevedad/eficiencia ('58 segundos'). Estructura: framework completo comprimido en pasos secuenciales (personas, competidores, estructura de campaña, regla de 7 días). Gatillo: urgencia y autoridad que invita a guardar el video como referencia rápida.</t>
+          <t>Gancho: promesa directa en la primera frase ('así es como construís una marca'). Estructura: reencuadre de la creencia común (los anuncios solo sirven para leads/ventas) hacia una posibilidad menos obvia (construir marca), seguida del método concreto (founder-led + partnership ads) y el mecanismo (transferencia de valores). Gatillo: muestra su propio anuncio real como prueba social/autoridad.</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo cámara, mic de mesa y un texto de título simple; el valor está en el conocimiento compartido, no en la producción.</t>
+          <t>Sí — hablar a cámara en un living con un solo screenshot de anuncio como apoyo visual, sin edición compleja.</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -6193,15 +6193,15 @@
     </row>
     <row r="62" ht="88" customHeight="1">
       <c r="A62" s="2" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -6228,33 +6228,33 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>285</v>
+        <v>1052</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7662722851530689814</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7641896333955058977</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath analiza un anuncio de Meta de Athletic Greens (AG1) protagonizado por Hugh Jackman y lo puntua 9 sobre 10, destacando la demo de producto, el uso del actor y el giro de la llamada telefonica como 'pattern interrupt'.</t>
+          <t>Ben Heath explica un método de cuatro pasos, totalmente gratis, para espiar qué anuncios de Meta están corriendo los competidores usando la Biblioteca de Anuncios.</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>Pensa en todas las cosas que AG1 reemplaza, es una decision obvia (no brainer). Bueno, empieza [?, en el original 'strange with product demo', probable error de reconocimiento por 'starts with product demo'] con una demo de producto, despues un corte rapido a Hugh Jackman. Me gusta eso, no hay nada malo ahi. Los negocios chicos pueden hacer esto tambien al 100%, dicho sea de paso. Solo necesitas trabajar con influencers de menor nivel. 'No necesitas pastillas para esto. Polvo es para eso [?, en el original 'Power is for that', probable error de reconocimiento por 'Powder is for that']. Cuando podes tener todo en una sola cucharada.' La narrativa es fuerte, tener a sus vecinos como repitiendo todo lo que dice realmente transmite la idea de que ama el producto. Tambien es entretenido, tipo, es gracioso, va a mantener tu atencion. Me encanta esta parte de la llamada telefonica. Es una interrupcion de patron (pattern interrupt) realmente grande, abre un nuevo loop. Va a mantener al espectador enganchado, viendolo hasta el final del anuncio. Este es un muy buen anuncio. Le doy un nueve de 10.</t>
+          <t>Acá tenés un método de cuatro pasos para espiar gratis los anuncios de Meta de tus competidores. Paso 1, muy simple: andá a la Biblioteca de Anuncios [Ads Library], una herramienta completamente gratuita. Paso 2: buscá a tus competidores; podés ver exactamente qué anuncios están corriendo. Paso 3: ordená por impresiones, de mayor a menor. Esto es importante: ahora podés ver no solo los anuncios que están corriendo tus competidores, sino cuáles están recibiendo más inversión. Si combinás eso con los anuncios que llevan más tiempo corriendo, también podés ver cuándo se lanzó un anuncio por primera vez. Esos son tus ganadores: son los que probablemente les están dando los mejores resultados a tus competidores, y esos son los que en el Paso 4 vas a querer tomar como modelo. Te recomiendo que te bases en varios competidores distintos, no en uno solo. Y si querés ver un tutorial completo y a fondo sobre la Biblioteca de Anuncios, tengo uno que podés encontrar en mi canal de YouTube.</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>Mismo formato de resena que las filas 204/205/212: Ben con el celular mostrando el anuncio original superpuesto (video con Hugh Jackman, escena de cocina/mesa con dos personas), esta vez sentado en un living distinto con planta y estanteria de fondo; etiquetas de seccion superpuestas (por ejemplo 'Immediate Demo &amp; Influencer Pairing') acompanan la critica.</t>
+          <t>Arranca con una tarjeta de título diseñada (fondo tipo hormigón con trazos de marcador rojo) con el texto 'Top Secret: Methods to spy on competitors Meta Ads'. Corta a talking head sentado a una mesa, pared clara con cuadros de fondo, polo oscuro con micrófono clip. Subtítulos en mayúsculas, blancos y negrita (estilo distinto al de otros videos del mismo creador), estructurados como pasos numerados.</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>Gancho de reconocimiento de celebridad (Hugh Jackman) mas formato de resena de alta puntuacion que funciona como caso de estudio a imitar; estructura de desglose punto por punto de que funciona; gatillo de aprendizaje aspiracional al analizar un anuncio exitoso de una marca grande.</t>
+          <t>Portada 'top secret' como gancho de curiosidad, estructura tipo tutorial en 4 pasos fácil de seguir, y el gatillo es la promesa de valor gratuito y accionable (espiar a la competencia sin pagar nada).</t>
         </is>
       </c>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>si, mismo formato de resena replicable con celular y superposicion de video.</t>
+          <t>Sí, solo necesita una tarjeta de título simple y hablar a cámara siguiendo una estructura de pasos.</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -6285,15 +6285,15 @@
     </row>
     <row r="63" ht="88" customHeight="1">
       <c r="A63" s="2" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+        <v>92</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -6320,33 +6320,33 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>276</v>
+        <v>965</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7628347207007128840</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7603330394024365344</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde explica que el KPI "tiempo hasta el lead" (time to lead) es el más importante para negocios de generación de leads, y que responder en menos de 5 minutos tras el opt-in aumenta significativamente las reservas.</t>
+          <t>Ben Heath explica cómo estructurar una secuencia de anuncios de Meta que "cuente una historia": primero valor, luego demostración del producto, después testimonio, y por último anuncios de venta directa con llamado a la acción.</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>Si no sabés cómo generar confianza, o más específicamente, cómo lograr que tomen acción, eso va a arruinar el rendimiento de tus anuncios de Facebook. El error más grande que veo que comete la gente es que no respetan el KPI de "tiempo hasta el lead" que deberían respetar, ¿okay? Es probablemente la métrica más importante que necesitás rastrear con tu negocio de infoproductos, agencia de anuncios legal [?], o cualquier tipo de negocio de publicidad basado en generación de leads necesita rastrear el tiempo hasta el lead: cuánto tardó antes de que alguien de tu equipo se pusiera en contacto con esa persona. Okay, así que te sorprendería la cantidad de gente que hace esto mal — es como que esperan unas horas, o un día, o dos días, o esperan bastante tiempo después de que alguien se registró (opt-in) para tomar acción. Y entonces el KPI general acá es probablemente mucho más corto de lo que pensás. Así que imaginate — se supone que esto es un reloj acá — pero son 5 minutos máximo. Si podés respetar este plazo, vas a aumentar significativamente la cantidad de reservas (bookings) que conseguís.</t>
+          <t>Así es como contás una historia con los anuncios de Meta. Podés configurar tus anuncios para que se entreguen en una secuencia y así educar a tu audiencia de la manera que quieras. Por ejemplo, si estoy vendiendo una oferta de alto ticket (precio alto), voy a empezar entregando valor. Después voy a demostrar cómo funciona el producto o servicio. Luego voy a seguir eso con un testimonio, y después voy a incluir anuncios más orientados a la venta con llamados a la acción (call to actions). Ahora ya sabés eso.</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>Plano vertical medio de busto, cámara fija tipo webcam, en living/oficina hogareña con planta y cuadro de fondo, micrófono de brazo visible. Subtítulos grandes bold con una palabra clave resaltada en verde. Corta a un segundo bloque en pantalla dividida con capturas de pantalla de formularios de opt-in con círculos y flechas dibujados a mano, y a un tercer bloque con notas escritas a mano en una libreta (diagrama del tiempo de respuesta).</t>
+          <t>Talking head en interior tipo living/hogar, con una planta y un televisor de fondo, luz natural suave, polo celeste. Subtítulos palabra por palabra en blanco/negrita centrados; en un momento se superpone la captura de pantalla de una publicación real con comentarios/reseñas como ejemplo visual. Un solo plano fijo, sin cortes de cámara.</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Gancho de error/miedo ("esto va a arruinar tu rendimiento en Facebook Ads"); estructura de problema → métrica desconocida → número concreto y accionable (5 minutos); gatillo de autoridad + utilidad inmediata aplicable ya.</t>
+          <t>Gancho directo de promesa de método ("así se cuenta una historia con anuncios de Meta") + estructura de framework en 4 pasos fácil de recordar (valor → demo → testimonio → venta) + gatillo de utilidad y aplicabilidad inmediata para cualquier negocio de alto ticket.</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>sí, solo requiere cámara de celular/webcam, micrófono básico y notas a mano; no hay edición compleja.</t>
+          <t>sí + solo hace falta cámara casera, subtítulos automáticos y una captura de pantalla de ejemplo como apoyo visual.</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
@@ -6377,32 +6377,32 @@
     </row>
     <row r="64" ht="88" customHeight="1">
       <c r="A64" s="2" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -6412,48 +6412,48 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>256</v>
+        <v>924</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7636521756043250952</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7634126651894287648</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde presenta un método para crear ángulos de anuncios de Facebook a partir de investigación de datos propios y de mercado, transformando patrones de clientes en declaraciones de deseo ("quiero...") y ejemplificándolo con un producto de salud cardíaca.</t>
+          <t>Ben Heath comparte un tip rápido: cuando una campaña de Meta Ads falla o tira errores raros por bugs de Ads Manager, muchas veces la solución más simple es recrearla desde cero en vez de intentar arreglarla.</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>Quiero mostrarte una nueva forma de crear ángulos de anuncios para Facebook. Podés investigar datos propios (own data) o datos de mercado (market data). Los datos propios serían cualquier cosa que le pertenezca a tu negocio: reseñas de clientes, el administrador de anuncios (ads manager) — ahí revisás cualquier anuncio anterior que hayas corrido, cuál fue su rendimiento —, revisás encuestas post-compra, comentarios en redes sociales. Datos de mercado es cuando revisás las reseñas de tus competidores en su sitio web, en Amazon. Pero lo que eventualmente querés hacer es transformar estos patrones en declaraciones de "quiero" (I want to). "Quiero saber que mi corazón está realmente sano." Acá agregás un par de razones, "para poder..." ("so I can"). ¿Cuál es la verdadera razón por la que alguien quiere tener un corazón sano? Bueno, a partir de ahí, quieren prevenir un ataque cardíaco repentino. ¿Por qué? Bueno, quieren prevenir un ataque cardíaco para poder seguir manteniendo a su familia. ¿Por qué? Para poder cumplir su propósito como protector. Entonces es como ir cada vez más profundo — es como pelar una cebolla. ¿Cómo se ve transformar este deseo en un ángulo de anuncio? Hay un montón de formas en las que este deseo se puede manifestar. "La promesa de la graduación": un padre mira a su hija pequeña en la obra de teatro de la escuela primaria, que se imagina hacia adelante [?] ("Ford" en el original, probablemente "forward") hasta su graduación universitaria, con voz en off: "¿Vas a estar ahí para sus grandes momentos? Nuestro escaneo cardíaco con IA ayuda a asegurar que sí." "La rutina matutina": un ejecutivo de unos 50 años haciendo su rutina matutina, despidiéndose de su esposa con un beso, etcétera, agarrando su portafolio, ajustándose la corbata. Después se muestran los resultados de su escaneo cardíaco en el teléfono, dándole la confianza para enfrentar otro día. "Tranquilidad en solo 15 minutos." "El constructor de legado": un dueño de negocio trabajando hasta tarde, mirando fotos de las familias de sus empleados en su escritorio. "Ahora es solo tu familia la que cuenta contigo. Conocé el estado de salud de tu corazón hoy." Los deseos de mercado masivo son un primer paso para poder crear un anuncio. Mucha gente se queda ahí y después sufre el síndrome de la página en blanco.</t>
+          <t>Una solución fácil y subestimada para muchas campañas de anuncios de Meta es simplemente recrearla. Ads Manager está lleno de errores (bugs) y es muy común que algo salga mal dentro de tu campaña, que no entregue bien o que directamente deje de entregar. Que aparezcan una serie de errores que en realidad no entendés bien qué significan ni cómo solucionarlos. En lugar de tratar de ajustarla y cambiar cosas para que funcione, a veces es mejor decir: ¿sabés qué? Voy a recrear esto desde cero. Muchas veces eso hace que funcione, que empiece a entregar y a entregar correctamente.</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto en el mismo setup casero con planta y cuadro de fondo. Subtítulos bold. Pantalla dividida con gráficos tipo diagrama de flujo y tablas (aparentemente de un documento o presentación) que enumeran el proceso de investigación y ejemplos de ángulos de anuncio con guiones escritos; el gráfico llega a mostrar un cuarto ángulo ("The Weekend Dad") que no se alcanza a narrar en el tramo de transcript disponible.</t>
+          <t>Encuadre: plano medio, sentado a una mesa exterior. Subtítulos: palabra por palabra en mayúsculas. Cortes: toma continua, sin gráficos adicionales en los frames vistos. Gráficos: ninguno visible. Locación: exterior, campo/pradera soleada, mesa de picnic, luz natural fuerte, usa lentes de sol.</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>Gancho de promesa de método nuevo; estructura de framework paso a paso (datos propios/mercado → declaraciones de deseo → ángulos) con ejemplo aplicado completo; gatillo de utilidad + curiosidad por ver el marco aplicado a un caso real.</t>
+          <t>Gancho: etiqueta la solución como 'subestimada' y 'fácil', apelando a la curiosidad por un tip de insider. Estructura: problema conocido y frustrante (bugs de Ads Manager) seguido de una solución simple y contraintuitiva (recrear en vez de arreglar). Gatillo: tip práctico e inmediatamente aplicable, de muy bajo esfuerzo para el espectador.</t>
         </is>
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>sí, necesita armar un documento o slide con el framework, sin herramientas costosas.</t>
+          <t>Sí — grabado con celular al aire libre, sin edición ni gráficos adicionales.</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
     </row>
     <row r="65" ht="88" customHeight="1">
       <c r="A65" s="2" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+        <v>94</v>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -6504,48 +6504,48 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>72700</v>
+        <v>919</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7603828023187492126</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7626005293658361121</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell cuenta el caso de la marca Haus, que usa datos de TikTok Shop para identificar al 1% de creadores top, los suma a una comunidad de contenido y produce miles de anuncios de partnership, lo que según el video la llevó de 1 a 10 millones de dólares en un mes.</t>
+          <t>Ben Heath contrasta el comportamiento de los anunciantes principiantes (reactivos, atados emocionalmente al ROAS diario) con el de los profesionales (más pacientes, dispuestos a sacrificar ROAS a corto plazo para lograr escala).</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
         <is>
-          <t>Esta marca se está apoderando de internet con UGC. Haus construyó un sistema usando datos de TikTok Shop en los que ya confían. Identifican al 1% superior de creadores que generan más ventas. Después los pasan a una comunidad de contenido armada para escalar. Esa misma comunidad produce creatividades sin parar para los anuncios de Meta. Ahora mismo están corriendo más de 11.000 anuncios de 'paid partnership club' [?] pagados. Eso significa testeo constante, iteración constante, y ganadores nuevos todo el tiempo. Esta estrategia está funcionando ahora mismo. En 2026. Y es la misma estrategia que los hizo escalar de un millón a diez millones de dólares en un solo mes. No en un año, no en un trimestre. En un mes. Datos de UGC, escala de comunidad. Ese es el nuevo playbook. Comentá 'UGC' y te mando la estrategia completa.</t>
+          <t>¿Cuál es la mayor diferencia entre los anunciantes de Meta pro y los principiantes? Los anunciantes principiantes son demasiado reactivos y están emocionalmente atados a sus campañas. He visto a muchos anunciantes principiantes cuyo estado de ánimo y bienestar general está totalmente dictado por cuál fue su retorno de la inversión publicitaria (ROAS) ese día hasta el momento. Los anunciantes pro entienden que las cosas llevan más tiempo. Le dan más estabilidad a las cosas. También juegan el juego de otra manera: los anunciantes profesionales muchas veces van a sacrificar el retorno de la inversión publicitaria a corto plazo a cambio de escala. Eso puede significar pagar más por adquirir un cliente, no menos. Pero sabiendo que lo recuperás en el valor de vida del cliente (LTV), lo recuperás en referidos, porque tu producto o servicio es tan bueno. Así que, muchas veces, los mejores anunciantes no logran los mejores números de retorno de la inversión publicitaria, pero muy seguido operan a la mayor escala.</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: múltiples capas de video superpuestas (PiP dentro de PiP): clip selfie del fundador de la marca arriba, presentador de podcast hablando a un micrófono abajo. Subtítulos: etiqueta de texto tipo 'Haus Founder' con flecha roja señalando al fundador. Cortes: alterna entre el clip del fundador, capturas de Meta Ads Library y un dashboard de analítica con gráfico de ventas. Gráficos: flechas rojas de énfasis, capturas con métricas reales ('~11,000 results', '$10.9M Total sales', '107.9K%'). Locación: interior tipo living con micrófono de podcast.</t>
+          <t>Encuadre: plano medio/primer plano, formato podcast con micrófono profesional en cuadro. Subtítulos: palabra por palabra en mayúsculas. Cortes: toma continua. Gráficos: ninguno. Locación: interior tipo cocina/comedor, luz natural de ventana, lámpara colgante.</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Gancho: afirmación de caso de éxito extremo ('esta marca se está apoderando de internet'). Estructura: formato de case study (quién, qué hicieron, prueba con capturas reales, resultado numérico). Gatillo: cifra específica y extrema (de 1 a 10 millones de dólares en un mes, no en un año) reforzada con capturas de pantalla reales como prueba social, más CTA con palabra clave.</t>
+          <t>Gancho: formato de comparación identitaria ('principiante VS pro'), que engancha porque el espectador quiere saber en cuál categoría cae. Estructura: lista de contrastes de comportamiento que escala hacia una conclusión contraintuitiva. Gatillo: remate inesperado (los mejores anunciantes no tienen el mejor ROAS, sino la mayor escala), que invita a repensar una métrica que todos vigilan obsesivamente.</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>No — depende de tener un caso de éxito real con datos de ventas documentados y varias capas de video (PiP, capturas, dashboard) editadas juntas.</t>
+          <t>Sí — solo requiere un micrófono decente y una habitación con buena luz natural.</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
@@ -6561,32 +6561,32 @@
     </row>
     <row r="66" ht="88" customHeight="1">
       <c r="A66" s="2" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -6596,48 +6596,48 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="J66" s="6" t="n">
-        <v>29000</v>
+        <v>896</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7624241425068166431</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7636364743753649440</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell anuncia que Meta eliminara los pagos con tarjeta de credito para cuentas de anuncios de alto gasto a partir del 1 de abril, obligando a usar debito bancario o facturacion mensual, y advierte sobre el impacto en el flujo de caja de las marcas.</t>
+          <t>Ben Heath responde, en formato de preguntas y respuestas, cual es la mejor optimizacion de campana en Meta Ads entre leads, vistas de landing page o ventas, y cuando conviene elegir cada una.</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t>¿Escuchaste sobre esta nueva actualizacion de META? META acaba de hacer un movimiento que la mayoria de los anunciantes estan pasando completamente por alto. Estan eliminando silenciosamente los pagos con tarjeta de credito, especificamente para cuentas de anuncios de alto gasto. A partir del 1 de abril, o cambias a debito bancario o facturacion mensual, o tus anuncios se detienen. Se acabaron los puntos de la tarjeta. ¿Por que? Porque META ya no quiere pagar de 2 a 3% en comisiones de tarjeta de credito. Esto es una jugada de margen por parte de Meta. Pero es mas grande que eso. Estan ajustando el control sobre el flujo de caja, la verificacion de cuentas, y quien realmente puede escalar. A los anunciantes mas chicos, por ahora no los afecta [?, en el original 'They're on touch for now', probable error de reconocimiento por 'They're untouched for now'], pero a los grandes anunciantes: ahora estan jugando con las reglas de Meta, y aca es donde se pone real. Ahora estas pagando nominas, haciendo pedidos de inventario, y pagando una factura enorme de Meta a fin de mes, todo al mismo tiempo, sin colchon, sin demora, sin margen de maniobra. Esto no es una actualizacion de facturacion. Esto es una prueba de estres de flujo de caja. Las plataformas se estan poniendo mas estrictas y el juego se esta poniendo mas dificil. Asi que la pregunta real es: ¿puede tu negocio realmente sostener el flujo de caja?</t>
+          <t>¿Cual es la mejor optimizacion? ¿Leads, vistas de landing page o ventas? Definitivamente no vistas de landing page. Y entre las otras dos, realmente depende de tu negocio. Entonces, te conviene ir con ventas si podes rastrear la conversion de compra, cuando alguien efectivamente hace una compra. Eh, particularmente si hay valores diferentes, y podes optimizar para compras de mayor valor. Personas que gastan mas cuando compran en tu tienda online, por ejemplo. Si no podes rastrear eso directamente, es decir, si hay un paso intermedio (la gente agenda una cotizacion gratis, una llamada o una consulta o algo asi), entonces te conviene mas ir con leads.</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>Produccion mas elaborada: combina un clip de video/cine de stock (hombre con anteojos de sol de perfil en un auto) con el logo de Meta superpuesto como gancho visual; sigue con un infografico a medida comparando linea de tiempo 'antes' (pago con tarjeta, periodo de 60 dias) vs 'despues' (facturacion, periodo de 30 dias) con emojis y flechas; cierra con un grafico simulando un estado de cuenta/factura de Meta ('Ads on Reels $50,000') con signos de exclamacion, y Chase hablando a camara con microfono de podcast sobre fondo negro.</t>
+          <t>Toma continua al aire libre (silla puf sobre pasto, luz natural), Ben con anteojos de sol y ropa casual; subtitulos grandes en negrita que resaltan palabra por palabra lo que dice; pequenos iconos (personas, flecha, documento, apreton de manos) en las esquinas superiores, posiblemente indicando el tema o el formato de una entrevista/podcast reciclado como clip corto.</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta mas novedad ('Have you heard of this new META update?'); estructura de que-por que-que implica con evidencia visual (linea de tiempo, factura simulada) que hace tangible un cambio abstracto de facturacion; gatillo de ansiedad financiera ('cash flow stress test') relevante para cualquier negocio que dependa de Meta Ads.</t>
+          <t>Pregunta directa como gancho ('What's the best optimization?'); respuesta corta, clara y accionable en menos de 31 segundos; gatillo de utilidad practica inmediata para cualquiera que gestione campanas.</t>
         </is>
       </c>
       <c r="R66" s="5" t="inlineStr">
         <is>
-          <t>no, requiere metraje de stock/cine con licencia y al menos dos piezas de diseno grafico a medida (linea de tiempo y factura simulada), mas tiempo de edicion que el resto del lote.</t>
+          <t>si, es una respuesta corta a camara con subtitulos, sin edicion compleja.</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
@@ -6653,27 +6653,27 @@
     </row>
     <row r="67" ht="88" customHeight="1">
       <c r="A67" s="2" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+        <v>41</v>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Macie Reed</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -6688,48 +6688,48 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>28900</v>
+        <v>846</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7612660537196907806</t>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7659974291945049357</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell presenta una herramienta que permite 'copiar' el anuncio de cualquier competidor y obtener la plantilla creativa exacta (estructura, hook, formato, CTA) para recrearlo en minutos para la propia marca.</t>
+          <t>Tercer episodio de la serie educativa 'Meta Ads Must Haves' de Macie, donde explica los seis objetivos de campaña de Meta Ads y por qué en la práctica ella solo usa leads y ventas.</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t>Esta herramienta creativa cambia las reglas del juego. Si estás corriendo anuncios pagos ahora mismo, esto es una estrategia al límite de lo injusto. Con esta herramienta, literalmente podés 'swipear' (copiar) el anuncio de cualquier competidor y conseguir la plantilla creativa exacta para recrearlo. No es inspiración. No hay que adivinar la estructura y el formato real, ya sea un anuncio de reseña con beneficios, antes y después, testimonios de UGC, o anuncios basados en problema-solución. Ves qué formato están usando, cómo está armado el hook (gancho), dónde aparece la prueba, cómo está ubicado el CTA (llamado a la acción), y después literalmente te dan un botón de 'recrear' para tu marca en minutos. Así es como las marcas top se mueven más rápido que todas las demás. No están reinventando los anuncios, están replicando lo que ya funciona hoy y desplegándolo a escala. Ayuda a bajar la fatiga creativa, a testear más rápido, y a tener más anuncios ganadores. Así que si sos una marca seria escalando en 2026, este es el tipo de ventaja (leverage) que necesitás. Comentá 'creative' y te mando la herramienta.</t>
+          <t>Bienvenidos a Meta Ads Must Haves episodio 3, donde en esta serie les enseño toda la información fundamental que necesitan saber sobre meta ads para que puedan convertirse en un meta ads manager y ganar una tonelada de dinero trabajando una fracción del tiempo. En el episodio anterior prometí que les iba a explicar cuáles son los diferentes objetivos a nivel de campaña. Así que de eso exactamente vamos a hablar hoy. Quédense hasta el final de este video porque voy a compartir los dos objetivos que son realmente los únicos que les tienen que importar. Ahora, tienen seis objetivos diferentes para elegir en su campaña, y todos cumplen una función distinta. Como resumen rápido, estos son los tres [?] objetivos que pueden elegir: reconocimiento (awareness), tráfico, interacción (engagement), leads, promoción de aplicaciones, y ventas. Ahora, todos estos objetivos cubren desde el tope del embudo, audiencias frías totalmente nuevas, la mitad del embudo, gente a la que están nutriendo y que va conociendo su marca, y después el fondo del embudo, que es donde idealmente esperan hacerlos cruzar esa barrera y llegar hasta la compra. Entonces, primero, en la parte más alta del embudo, tenemos reconocimiento. Y esto es básicamente decirle a meta ads: che, poné mi anuncio frente a la mayor cantidad de ojos y personas posible. Acá vamos por alcance e impresiones. Esto es genial para una empresa nueva que recién está lanzando y que todavía nadie conoce. El segundo objetivo es tráfico. Esto es decirle a meta ads: quiero que la gente haga clic en este anuncio y vaya a un destino determinado. Entonces nos enfocamos principalmente en clics en el enlace, vistas de landing page, y visitas al perfil de Instagram. El tercer objetivo va a ser interacción. Acá es donde queremos que la gente le dé like a nuestros anuncios, comente nuestros anuncios, o siga nuestras redes sociales. Básicamente estamos tratando de generar conversación. El cuarto objetivo son los leads. Este va a ser su objetivo de generación de leads, es decir, quieren recolectar emails para hacer crecer su lista de correo. El quinto objetivo es bastante de nicho, es la promoción de aplicaciones. Esto obviamente solo es relevante para quienes tienen una app en la App Store. Así que, honestamente, nunca usé este. Y por último, pero no menos importante, tenemos la campaña de ventas. Esto es lo que se usa para ir directo a la yugular y lograr que la gente compre un producto. Ahora, en mis cuatro años siendo ads manager, en realidad solo uso leads y ventas. Siendo ventas el principal. Porque como administradora de publicidad de e-commerce D2C (directo al consumidor), eso es lo que nos importa. Queremos que entren ventas e ingresos. Entonces lo principal que priorizo en absolutamente todas las cuentas de mis clientes va a ser un objetivo de ventas. Y después a veces lo voy a combinar con el objetivo de leads, asumiendo que alguien está gestionando el email marketing. Si recién se están iniciando en meta ads, yo realmente solo me enfocaría en estos dos, los objetivos de leads y de ventas. No hace falta preocuparse por ninguno de los otros. Son demasiado de tope de embudo como para realmente generar impacto o mover la aguja para las marcas de e-commerce. Si les gusta este tipo de contenido y quieren aprender más sobre cómo administrar meta ads, asegúrense de seguirme porque recién estamos arrancando esta serie.</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: grabación de pantalla de una herramienta de plantillas publicitarias con el creador en recuadro inferior hablando a micrófono. Subtítulos: texto grande tipo 'hook' superpuesto ('Have you heard of this Meta Ad Creative Tool?'), y en otro frame texto de ejemplo de copy de anuncio en franjas blancas. Cortes: cambia entre distintas pantallas de la herramienta (dashboard de inicio, ejemplo de anuncio UGC de sábanas, menú de categorías/filtros). Gráficos: parte del nombre/logo de la marca de la herramienta aparece borroneado. Locación: sin locación física, foco en pantalla con fondo de estudio.</t>
+          <t>Talking head vertical en dormitorio/living con buena luz cálida (lámpara), decoración de fondo (cuadro, planta), micrófono de solapa, sin cortes de escena visibles. Se superpone a pantalla completa una captura del panel real de Meta Ads Manager 'Choose a campaign objective' como recurso visual de apoyo. Subtítulos grandes tipo caption animado quemados palabra por palabra en cada frase clave.</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Gancho: pregunta retórica con etiqueta de 'game changer' y emoji, apunta a la curiosidad sobre una herramienta desconocida. Estructura: promesa fuerte ('estrategia al límite de lo injusto'), demostración en pantalla del mecanismo, beneficios (menos fatiga creativa, testeo más rápido) y apela a la exclusividad ('así se mueven las marcas top'). Gatillo: combinación de FOMO más utilidad muy concreta (botón de 'recrear') más curiosidad por el nombre de la herramienta, que aparece parcialmente oculto.</t>
+          <t>Gancho: promesa de valor concreto y directo ('los dos objetivos que son los únicos que les importan'). Estructura: formato educativo numerado tipo episodio de serie/curso que lista los seis objetivos de forma clara. Gatillo: autoridad (4 años de experiencia) y aspiracional (ganar mucho dinero trabajando poco), más el gancho de continuidad para el próximo episodio.</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>Sí, con matices — el formato (webcam + grabación de pantalla) es económico, pero requiere acceso a la herramienta de plantillas mostrada (probablemente paga).</t>
+          <t>sí + nota: solo cámara frontal de celular, mic de solapa económico y capturas de pantalla propias del Ads Manager.</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
@@ -6745,32 +6745,32 @@
     </row>
     <row r="68" ht="88" customHeight="1">
       <c r="A68" s="2" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Venta del servicio</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+        <v>42</v>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -6780,48 +6780,48 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1378</v>
+        <v>845</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7629597512055147784</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7669060115953192194</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Maddi, de la agencia MADE Marketing, cuenta en modo 'detrás de escena' cómo triplicaron los ingresos de una marca de moda en 45 días, mostrando el dashboard de ventas real y explicando su estrategia de un solo producto ganador, diversificación creativa semanal y anuncios de misión de marca.</t>
+          <t>Ben Heath compara la estrategia de marketing de Olipop contra la de Poppi (competidoras de soda prebiótica): cantidad de anuncios activos, oferta, colaboraciones de marca y experiencia de compra en el sitio web, concluyendo que Olipop convierte mejor y Poppi conecta mejor culturalmente.</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr">
         <is>
-          <t>Cómo logramos resultados como este en probablemente unos 45 días trabajando con esta marca de moda. Ahora mismo esta semana están en [?] alrededor de 7, y lo hemos ido mejorando semana a semana, lo cual también es muy emocionante de ver dentro de la cuenta. Lo más importante que hicimos cuando empezamos a trabajar con esta clienta fue recortar mucho su oferta de productos. Nos enfocamos en lo que estaba funcionando con los anuncios de marcas de moda. Si tenés productos que vendés continuamente y podés encontrar un best seller, literalmente podés obtener resultados como este vendiendo un solo producto; en este caso es literalmente un solo producto, enfocándonos en eso y realmente creando un producto viral en Meta Ads. Lo siguiente que hicimos fue subir contenido nuevo de forma consistente cada semana, y no estamos haciendo volúmenes descabellados, es muy manejable para esta clienta, pero realmente nos enfocamos semana a semana en la diversificación creativa. Entonces cada pieza de contenido es muy intencional en base a las ventas que estamos viendo fuera de la plataforma, porque esto viene en una variedad de colores, y analizamos cada pieza de contenido que subimos asegurándonos de que sea muy distinta a la última que publicamos, y que todo cuente una historia coherente. Lo tercero que hicimos, que creo que muchas marcas de moda no hacen, es que nos enfocamos mucho en anuncios de visión y misión de marca. La razón real por la que esta marca fue fundada. Creo que la gente se olvida de esto en una marca de moda. Piensan que la gente compra solo porque le gusta la prenda. Pero creo que cuando pueden ver la intención o los aspectos intencionales, eh, las razones por las que eligieron la tela o por qué fundaron la marca o los bocetos y todo esto, realmente atrae a la gente y genera esa confianza mucho más rápido. Así que esas fueron las principales cosas en las que nos enfocamos en los últimos 45 días para aumentar los ingresos de esto. Y estoy muy emocionada de ver a esta marca escalar más.</t>
+          <t>¿Quién es mejor en marketing, Poppy u Olipop? Bueno, Olipop está corriendo 40 anuncios de Meta con imágenes centradas en el producto y videos centrados en los beneficios. Y lo particular es que crearon su propio jingle que usan en los anuncios, lo cual es bastante interesante. Lo que les falta es una oferta fuerte que empuje a la gente a comprar. Ahora comparemos eso con Poppy, que está corriendo 180 anuncios de Meta. Destacan ofertas interesantes de entrada. Poppy también se está apoyando fuerte en su colaboración reciente con Love Island, lo que hace que se sientan más como una marca dentro de la cultura. Y mirando el sitio web de Poppy, es hermoso. Abre con ofertas y una variedad de productos. Pero su menú de tienda es torpe y no empujan combos de venta directa al consumidor, una oportunidad enorme desperdiciada. Mientras tanto, el sitio web de Olipop sí empuja combos DTC (venta directa al consumidor) y empuja suscripciones, y las empuja de inmediato. Su página de producto está diseñada para reducir la fricción e impulsar más ventas. Mucho mejor. Olipop es la máquina de DTC mejor construida. Entonces tienen un sitio web más ajustado, un empuje de suscripciones [?] más fuerte, una creatividad más consistente. Poppy es la mejor marca cultural: una operación publicitaria más grande, alianzas más audaces, un posicionamiento de estilo de vida más profundo. Entonces Olipop te muestra cómo convertir. Poppy te muestra cómo importar (tener relevancia cultural). Las mejores marcas DTC hacen ambas cosas.</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>Talking head vertical en selfie, cara en primer plano con micrófono de solapa, misma locación de fondo claro en los tres frames sin cortes visibles. Se superpone de forma fija una captura de pantalla de un dashboard de ventas (gráfico 'Gross sales' / 'Total sales over time') en la parte superior del cuadro. Subtítulo grande en negrita tipo título ('How We Tripled This Fashion's Brand Revenue In 45 Days') quemado como hook inicial.</t>
+          <t>Imágenes de producto compuestas: presentador sosteniendo dos latas de Olipop contra fondo turquesa tipo estudio/croma, luego un vaso de Poppi con fondo de playa y sello 'Limited Edition Love Island', luego captura de pantalla del sitio web de Olipop con sus sabores, presentador siempre en la mitad inferior del cuadro hablando a cámara, subtítulos blancos, múltiples cortes entre gráficos/fotos de producto y talking head.</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>Gancho: cifra de resultado concreto y verificable con captura real del dashboard ('triplicamos los ingresos en 45 días'). Estructura: relato de 'las 3 cosas que hicimos' (producto único, diversificación creativa semanal, anuncios de misión de marca). Gatillo: prueba social/autoridad (datos reales en pantalla) que genera confianza y curiosidad sobre el método replicable.</t>
+          <t>Gancho: pregunta de opinión/rivalidad entre dos marcas conocidas ('¿quién es mejor?'). Estructura: comparación punto por punto (anuncios, oferta, colaboraciones, sitio web) con evidencia visual real (capturas, fotos de producto) -&gt; síntesis final memorable ('uno muestra cómo convertir, el otro cómo importar'). Gatillo: rivalidad/curiosidad + caso de estudio de marcas reales reconocibles + conclusión citable.</t>
         </is>
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo necesita una persona hablando a cámara con micrófono y una captura de pantalla de resultados reales, sin edición compleja.</t>
+          <t>no/medio + Requiere fondo tipo croma/compuesto, fotos de producto de calidad y capturas de sitios de la competencia, más trabajo de edición que el resto del lote.</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -6837,22 +6837,22 @@
     </row>
     <row r="69" ht="88" customHeight="1">
       <c r="A69" s="2" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -6872,33 +6872,33 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1240</v>
+        <v>832</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7623388351776787744</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7648656606674062614</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath explica cómo seguir logrando resultados con Meta Ads después de la actualización del algoritmo Andromeda. Su consejo es reemplazar la regla de tener 20+ creatividades por empezar con solo 4 conceptos realmente distintos y después iterar sobre los detalles.</t>
+          <t>Ben Heath, filmado en un evento de Meta en Silicon Valley, explica en lenguaje simple terminos tecnicos de publicidad: ROAS, incrementalidad, CPM, CTR, CPC, retargeting, CAC y AOV.</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr">
         <is>
-          <t>¿Es posible seguir teniendo éxito con los anuncios de Meta después de la actualización Andromeda? Porque ahora mismo el consejo es que necesitás tener 20 o más creatividades publicitarias distintas activas en todo momento. Y para la mayoría de los negocios, eso es difícil de lograr. Así que acá va una forma diferente de abordarlo. No empieces con 20. Empezá con 4. Cuatro conceptos genuinamente diferentes. Puede ser un ángulo distinto, un formato distinto, un enfoque distinto. Eso va a ser suficiente para que Meta vea diversidad creativa. Y una vez que encontrás algo que funciona, podés empezar a testear los detalles más finos. Eso podría ser distintos hooks (ganchos), distintos overlays (superposiciones de texto/gráficos), blanco y negro versus color en tus imágenes estáticas o tus videos. Estructurá tus pruebas para que Andromeda no ignore tus variaciones. No necesitás 20 anuncios al azar. Necesitás fuerte diversidad arriba, precisión por debajo. Y así es como ganás después de Andromeda.</t>
+          <t>Meta me llevo a Silicon Valley y acabo de estar en una sala con mas de 1.000 anunciantes que gastan decenas de miles de millones en anuncios de Meta cada ano. Escuche mucha jerga, asi que hoy te la voy a desglosar y explicar que significa en realidad. Empecemos con ROAS, que es retorno sobre la inversion publicitaria (return on ad spend), y eso simplemente mide lo que gastaste en anuncios versus lo que recuperaste. La incrementalidad mide lo que tus anuncios generaron para tu negocio que no hubieras conseguido si no hubieras estado corriendo anuncios en primer lugar. La incrementalidad es el 'uplift' (el aumento incremental). El CPM [?, transcripto como 'Ppm', probable error de reconocimiento], que es el costo por mil impresiones. Es la metrica que se usa tipicamente para medir el costo de la publicidad. Si quisieras comparar plataformas publicitarias o distintas ubicaciones, usarias el CPM. CTR significa tasa de clics (click through rate), que mide el porcentaje de gente que hizo clic en tu anuncio versus la gente que lo vio. Para anuncios de Meta, una buena tasa de clics normalmente seria algo por encima del 1%. Si superas el 2%, normalmente estas haciendo un trabajo muy bueno. CPC significa costo por clic y mide simplemente cuanto estas pagando por cada clic en tu anuncio. Retargeting es poner anuncios frente a personas que ya interactuaron con tu negocio: pueden ser personas que visitaron tu sitio web, personas en una lista de email, incluso personas que te compraron anteriormente. CAC significa costo de adquisicion de cliente (cost to acquire a customer). Una de las metricas mas importantes en publicidad paga, honestamente, en todo el marketing, es el AOV, que es el valor promedio de la orden (average order value). Cuando la gente entra a tu sitio web y compra. Cuanto mas alto el AOV, mejor.</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: plano medio fijo, cámara a la altura de los ojos, vertical. Subtítulos: palabra por palabra en mayúsculas, con 'META' resaltado en azul. Cortes: toma continua, sin cortes de cámara visibles. Gráficos: inserto de 4 tarjetas verdes con signos de pregunta que representan los '4 conceptos'. Locación: living/oficina en casa, con planta y estufa de leña de fondo.</t>
+          <t>Arranca con metraje real del escenario de una conferencia de Meta (pantalla gigante con el mensaje 'Ushering in the next era of shoppable experiences', panel de oradoras) para dar contexto y autoridad; despues corta a Ben hablando a camara al aire libre en el predio del evento, con la credencial/lanyard visible y remera roja; subtitulos en mayusculas siguen palabra por palabra lo que dice.</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Gancho: pregunta directa sobre si todavía se puede tener éxito tras un cambio de algoritmo reciente (Andromeda), apela a la ansiedad/incertidumbre del anunciante. Estructura: contraste entre el consejo 'oficial' (20 creatividades) y su propuesta alternativa (4 conceptos), con explicación del mecanismo y ejemplos concretos de qué variar. Gatillo: recomendación contraintuitiva y accionable con un número específico, posiciona al creador como quien tiene una lectura más inteligente que el consenso general.</t>
+          <t>Gancho de autoridad y exclusividad ('Meta flew me out to Silicon Valley... 1,000 advertisers that spend tens of billions'); estructura de diccionario/glosario facil de seguir y de guardar ('save this'); gatillo educativo que resuelve confusion de jerga para audiencia principiante e intermedia.</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>Sí — solo requiere cámara/celular y un gráfico simple (tarjetas con signos de pregunta), sin equipo profesional.</t>
+          <t>no del todo, depende de haber sido invitado a un evento real de Meta para el gancho de autoridad, aunque el glosario en si se podria grabar en cualquier lado.</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -6929,17 +6929,17 @@
     </row>
     <row r="70" ht="88" customHeight="1">
       <c r="A70" s="2" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>BitBranding</t>
+          <t>Macie Reed</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -6964,33 +6964,33 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="J70" s="6" t="n">
-        <v>274</v>
+        <v>826</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bitbranding/video/7658448519593725215</t>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7667600871445761294</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>BitBranding argumenta que la forma tradicional de escalar anuncios de Facebook (duplicar campañas, apilar intereses) ya no funciona porque el algoritmo de Meta ya no necesita segmentación manual, y que la clave está en tener una oferta rentable y conocer bien los números.</t>
+          <t>Sexto episodio de la serie donde Macie explica los cuatro formatos de anuncio disponibles en Meta Ads Manager (video, imagen, carrusel, catálogo) y cierra promocionando la lista de espera de su curso.</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t>Estás escalando tus anuncios de Facebook mal, y puedo probarlo. La mayoría de las marcas de ropa que están escalando anuncios ahora mismo lo hacen duplicando campañas, tocando presupuestos, probando nuevas audiencias, y cada una de esas acciones te está costando dinero. Los gurús en internet están enseñando un sistema que funcionaba hace tres años, hace cinco años: duplicá el ad set, probá en amplio (broad), escalá el ganador, corré una campaña de testeo, y si no funciona, debe ser tu creativo. No — el problema es el método. Meta ya no necesita que le digas quién es tu cliente. El algoritmo de Meta es más inteligente que cualquier stack de intereses [?] ("Interstac" en el original) que vayas a armar. Lo que Meta necesita de vos es una oferta rentable y paciencia. Quienes puedan gastar más para adquirir un cliente siempre van a ganar — creo que es una cita de Dan Kennedy —, que básicamente dice que si conocés tan bien tus números que podés gastar más que tus competidores para adquirir un cliente, vas a conseguir ese cliente. Y mientras puedas hacerlo de forma rentable a largo plazo, vas a seguir ganando. Pero solo podés gastar más cuando realmente conocés esos números. Y ahí es donde empezamos.</t>
+          <t>Bienvenidos de nuevo a Meta ads Must Haves episodio 6, donde en esta serie les estoy enseñando todo lo que necesitan saber sobre meta ads para que puedan convertirse en un meta ads manager, ganar una tonelada de dinero, y trabajar una fracción del tiempo. Si no están al día con la serie, asegúrense de volver a mi perfil y ver los videos anteriores. Pero en el episodio de hoy vamos a hablar sobre los formatos de anuncio. Hay cuatro tipos diferentes de formatos de anuncio, y hay un momento y un lugar diferente para usarlos según distintos propósitos. Pero por ahora, empecemos a mapear los cuatro tipos. Primero y principal, tenemos video. Esto es bastante directo. Es básicamente lo que están viendo ahora mismo. Un video en Instagram o Facebook. Estos van a ser anuncios estilo UGC de alguien hablando a cámara, de unboxing, o entrevistas callejeras. Después tenemos imágenes, que se explica bastante solo. Es una foto de producto o algún tipo de foto que tiene un titular, o tal vez señala características, o es un 'nosotros versus ellos'. Tercero son los anuncios carrusel. Estos son los anuncios por los que uno se desliza en el feed, o aparecen como múltiples diapositivas en una historia. Y estos son realmente geniales si tenés múltiples productos o querés mostrar múltiples ángulos de tu producto, o simplemente destacar diferentes USPs (propuestas de venta únicas). Y por último, pero no menos importante, tenemos el anuncio de catálogo. El anuncio de catálogo es un anuncio dinámico que en realidad conectás directamente a tu cuenta de Shopify, y toma toda la información de tu producto directamente de tu sitio web. Entonces toma la imagen de tu producto, el título de tu producto, los precios, todas esas cosas buenas. Así que básicamente autocompleta el anuncio por vos, y después todo lo que tenés que hacer es entrar y completar un titular y una descripción. Eso es esencialmente todo. Ahora, es muy importante que tengan estos cuatro tipos de formatos dentro de su cuenta publicitaria, simplemente porque a meta le gusta tener más con qué trabajar. Y si le das más diversidad, va a estar muy contento con vos y te va a recompensar. Si les gusta la serie, entonces les va a encantar mi Meta Ads Crash Course, que es un curso de meta ads amigable para principiantes. Y la lista de espera para eso cierra en solo un par de días. Entonces si están interesados en aprender meta ads como principiantes totales, o tal vez ya entraron un par de veces y simplemente no logran entender cómo hacerlo funcionar, mi meta ads crash course va a ser perfecto para ustedes. Y cuando se unan a mi lista de espera, van a tener acceso anticipado antes que todos los demás. Van a obtener mi curso de 47 dólares por 27 dólares. Además les voy a sumar mi Meta Ads Toolkit totalmente gratis. ¿Quieren unirse a la lista de espera? Vayan a la parte de arriba de mi perfil. Está disponible en mi bio.</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>Plano medio frontal en el mismo fondo oscuro liso, gorra al revés y anteojos. Subtítulos bold blancos. Incluye una transición con motion blur/barras naranjas estilo glitch entre tomas, y una placa de texto grande sobre fondo teal oscuro ("KNOW THOSE NUMBERS") a modo de énfasis.</t>
+          <t>Talking head vertical, sentada en sillón con manta blanca, sosteniendo una taza (elemento casual/lifestyle), mic de solapa, misma locación de dormitorio/living en los tres frames sin cortes visibles. Se superpone a pantalla completa una captura/mockup de un anuncio real de Instagram (imagen de producto con botón 'Follow' y 'Shop now') como ejemplo visual de un formato. Subtítulos tipo caption animado quemados en el video.</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>Gancho contrarian/polémico ("lo estás haciendo mal y puedo probarlo") que ataca la sabiduría convencional de "gurús"; estructura mito vs. verdad con cita de autoridad (Dan Kennedy); gatillo de disonancia cognitiva + promesa de método superior.</t>
+          <t>Gancho: continuidad de serie educativa numerada que ya tiene audiencia fidelizada. Estructura: lista clara y ordenada de los '4 formatos' fácil de seguir y guardar. Gatillo: urgencia/escasez al final (lista de espera de curso que cierra en días, con descuento y bonus gratis).</t>
         </is>
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
-          <t>sí, el formato es talking head con cortes/transición simple y una placa de texto, alcanzable con un editor de video básico.</t>
+          <t>sí + nota: solo cámara de celular y ejemplos de anuncios reales tomados de la propia plataforma como referencia visual.</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -7021,15 +7021,15 @@
     </row>
     <row r="71" ht="88" customHeight="1">
       <c r="A71" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+        <v>45</v>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -7041,12 +7041,12 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -7060,29 +7060,29 @@
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>249</v>
+        <v>813</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7661753639463177490</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7661251520700222742</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde explica el concepto de sofisticación de mercado (5 niveles) y cómo determina qué tipo de oferta y mensaje publicitario en frío conviene usar, usando su propia agencia de Facebook ads para HVAC y el mercado de IA como ejemplos.</t>
+          <t>Ben Heath reacciona y puntua con 8 sobre 10 un anuncio de Meta de la marca de ropa YoungLA, que usa una colaboracion con celebridades/influencers y una oferta por tiempo limitado.</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr">
         <is>
-          <t>Tu sofisticación de mercado va a dictar el tipo de oferta y también el tipo de anuncio que vas a querer hacer con tu cuenta de anuncios de Facebook. Si ignorás completamente este concepto, esto podría ser la diferencia entre una cuenta que escala o que fracasa. ¿Cuántas otras empresas similares a la tuya ya lanzaron productos similares, o intentaron resolver problemas similares a los tuyos, o hicieron ofertas similares al mismo mercado al que estás intentando apuntar ahora mismo? Por lo tanto, esto dicta qué tipo de ofertas o posicionamiento vas a querer tomar con tu negocio. Como vas a ver, nivel uno: nacimiento de un mercado, simplemente hacé cualquier afirmación (claim). Podés decir cualquier cosa. Y voy a armar un ejemplo con vos a lo largo de este video. Entonces, el nivel uno acá va a ser — y voy a usar mi agencia como ejemplo. Vamos al nivel uno. Y lo que voy a decir es "llevo campañas de Facebook ads", como ejemplo, voy a inventar un ejemplo acá, "para negocios de HVAC (climatización)". Bien. Esto es lo que funcionaría en un mensaje publicitario en frío (cold advertising) para un mercado nuevo. Tené en cuenta que acá no estoy hablando de publicidad a una audiencia cálida (warm audience). No estoy hablando de publicidad a una lista que ya tenés, a referidos, a amigos y familia. Me estoy refiriendo puramente a lo que significa hacer marketing a gente que no tiene ni idea de quién sos. Por lo tanto, un mercado frío (cold market). Eso sería llamadas en frío, email en frío, anuncios en frío — entonces Facebook ads, TikTok ads, Google ads. Y por lo tanto, si este es un mercado nuevo, podés hacer cualquier afirmación, lo que significa que puedo simplemente salir y decir "che, llevo Facebook ads para empresas de HVAC" y tendría un flujo de clientes llenando mi calendario queriendo trabajar conmigo, porque piensan "quiero hacer Facebook ads". Si sabés algo de este rubro, sabés que definitivamente no estamos en un nivel uno. Esto típicamente pasa cuando se abre un mercado o categoría completamente nueva. Por ejemplo, la IA. La IA ahora mismo es uno de los espacios o categorías nuevas que hay. La mayoría de las ofertas en el mercado de la IA no han sido explotadas tanto todavía. De hecho, estaba viendo un video hace poco de Dan Martel, que hablaba de cómo solo el 5% de toda la población de la Tierra ha pagado realmente para usar IA hasta ahora, lo que significa que la mayoría de la gente ni siquiera usa la IA de forma profesional.</t>
+          <t>Entonces se muestra a Marlon de entrada: es el encaje perfecto para el publico objetivo de Young LA. Eso esta bueno. Me gusta. Despues lo sigue con otras celebridades e influencers. Es un buen truco de retencion. Muchos cortes rapidos. Genera intriga sobre la colaboracion de una manera divertida, mostrando en cierto modo a la gente interactuando con los personajes. Me gusta eso. Y despues termina con 'tiempo limitado'. La oferta especifica que es por esta colaboracion, eso es importante, y consigo que mas gente actue. Muestra que hay un reloj corriendo de verdad. Tienen que actuar ahora. Ocho de diez.</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto en el mismo setup. Subtítulos bold. Pantalla dividida con una imagen de referencia (gráfico de niveles de sofisticación de mercado, estilo diagrama de marketing clásico) y notas manuscritas superpuestas debajo (fórmulas conceptuales y ejemplo del nicho HVAC), repetida de forma casi idéntica entre frame 3 y frame 5.</t>
+          <t>Formato de resena: Ben sentado en un living (silla de madera, planta, chimenea de fondo) sosteniendo el celular con el anuncio original reproduciendose en una ventana superpuesta con controles de pausa; titulo grande en la parte superior ('$300M Ad Expert Reviews Young LA') y etiquetas de seccion que van cambiando ('Target Audience Fit', 'Pacing &amp; Engagement', 'Urgency &amp; Clear Value Proposition') sincronizadas con lo que dice.</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Gancho de consecuencia alta ("la diferencia entre escalar o fracasar"); estructura educativa con marco teórico conocido (niveles de sofisticación) aplicado a un ejemplo propio y a un caso de actualidad (IA); gatillo de autoridad + aplicabilidad a la propia cuenta del espectador.</t>
+          <t>Gancho de autoridad numerica ('$300M Ad Expert') mas formato de 'resena' que genera curiosidad; estructura de checklist de criterios que ensena mientras entretiene, cerrando con una puntuacion numerica facil de recordar y compartir; gatillo de aprendizaje a partir de un ejemplo real de una marca conocida.</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
-          <t>sí, necesita solo una imagen de referencia (buscable/reutilizable) y notas a mano encima.</t>
+          <t>si, solo necesita un celular, una app que permita superponer video (por ejemplo CapCut) y comentar el anuncio de otra marca.</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
@@ -7113,15 +7113,15 @@
     </row>
     <row r="72" ht="88" customHeight="1">
       <c r="A72" s="2" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
+        <v>46</v>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
@@ -7148,33 +7148,33 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="J72" s="6" t="n">
-        <v>242</v>
+        <v>803</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7663560014900038934</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665377118192176406</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath resena un anuncio de Meta de Huel (puntuacion 8 sobre 10), destacando el gancho verbal en forma de pregunta, la ubicacion autentica tipo detras de escena en un deposito y el ritmo rapido de edicion.</t>
+          <t>Ben Heath resena un anuncio de Bose y lo puntua con 0 sobre 10 porque el video muestra a una mujer preparando una ensalada y nunca conecta claramente con el parlante que se supone que vende.</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>¿Es bueno Huel [?, en el original 'fuel', probable error de reconocimiento del nombre de marca] para bajar de peso? Entonces arranca con la pregunta, uno de mis tipos favoritos de hooks verbales [?, en el original 'herbal hooks', corregido por 'verbal hooks' segun coincide con el grafico en pantalla], genera mucha curiosidad y tambien ayuda a encuadrar una objecion y superarla temprano. Nos hacen esta pregunta tantas veces que en realidad lanzamos un producto nuevo. Esta ambientado en un deposito, tiene como una onda de detras de camara [?, en el original 'behind the scenes field', probable error de reconocimiento por 'behind the scenes feel'], muy autentico, me gusta eso. Tiene 200 calorias, 20 gramos de proteina, nutricion adecuada, todo por solo una libra la comida. Estan respondiendo la pregunta enumerando beneficios. Hicieron todo eso en 10 segundos, lo cual es muy ajustado, esta muy bueno. Elimina mucha incertidumbre. Entonces, si te costo mantener la constancia para bajar de peso, esto esta hecho para eso. Y ves que hay muchos cortes, movimiento constante, excelente para la atencion. Tambien me gusta bastante el estilo POV. Le doy un ocho de 10.</t>
+          <t>'Hagamos mi ensalada de verano favorita de durazno grillado y burrata, inspirada en el Soundlink Flex de Bose en color Sunset Peach.' Bueno, esto es un anuncio de Bose. ¿Por que esta hablando de hacer una ensalada? 'Elegi una variedad...' Este anuncio entero es una senora mostrandonos como hacer una ensalada. ¿Como es que eso vende productos de audio? ¿Quien en Bose aprobo esto [?, en el original 'Who would Bose approve this', frase con orden gramatical inusual]? Cero de diez.</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>Mismo formato de resena que el resto del lote: Ben con el celular mostrando el anuncio original superpuesto en un recuadro (cajas en un deposito con un globo de chat simulando la pregunta, botella y caja de Huel); etiquetas de seccion ('Verbal Hook', 'Authentic Location') que acompanan el analisis; titulo '$300M Ad Expert Reviews Huel'.</t>
+          <t>Mismo formato de resena que la fila 204: Ben en el mismo living con el celular mostrando el anuncio original de Bose superpuesto (escena de cocina con duraznos, tomates y un producto rojo sobre la mesada); titulo '$300M Ad Expert Reviews Bose Ad', etiquetas de seccion ('The Visual Hook', 'Confusing by Design') que acompanan la critica.</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>Gancho de pregunta directa (¿Es bueno Huel para bajar de peso?) senalado por el propio Ben como tecnica replicable; estructura de resena con criterios claros (hook, ubicacion, ritmo) que educa mientras entretiene; gatillo de autoridad mas aprendizaje por ejemplo.</t>
+          <t>Gancho de indignacion e incredulidad ('Why is she talking about making a salad?'); estructura de resena negativa que genera controversia y comentarios; gatillo de 'fail' de una marca grande, que produce curiosidad morbosa y validacion social ('¿quien aprobo esto?').</t>
         </is>
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>si, mismo formato de resena de bajo costo: solo celular y superposicion de video.</t>
+          <t>si, mismo formato replicable que la fila 204, sin costo adicional mas alla de encontrar un anuncio ajeno para comentar.</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -7205,32 +7205,32 @@
     </row>
     <row r="73" ht="88" customHeight="1">
       <c r="A73" s="2" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Difícil</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Mary-Anne Da'Marzo</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -7240,48 +7240,48 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J73" s="6" t="n">
-        <v>232</v>
+        <v>748</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7664708959932108050</t>
+          <t>https://www.tiktok.com/@maryannedamarzo/video/7669759222082440470</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde muestra cómo un mismo producto (coaching de pérdida de peso) puede anunciarse con tres ángulos completamente distintos según la objeción del público —sin gimnasio/equipo, odio al cardio, falta de tiempo por trabajo—, manteniendo el mismo deseo central.</t>
+          <t>Un video de motion graphics que plantea si se puede reemplazar todo el sistema de Meta ads con IA, mostrando en 4 pasos cómo conectar Claude a la cuenta de Meta Ads para analizar resultados, diagnosticar problemas y generar nuevas variantes creativas.</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr">
         <is>
-          <t>Los ángulos son una variable en tu anuncio que puede cambiar el mensaje por completo, en términos de qué decís. Cuando vas a pescar y usás una carnada, ¿no? Vas a cambiar la carnada según el tipo de pez que querés rastrear, o según el tipo de pez que querés atrapar, o según el tipo de día, o a veces incluso la hora del día o las estaciones — vas a cambiar esa carnada. Acá, lo que hice es: esos son tres ángulos completamente distintos que podría usar dentro de mis anuncios de Facebook. Todos son "conscientes de la solución" (solution aware). Todos son sobre un producto para bajar de peso. Todos apuntan a la misma audiencia, pero hablan de objeciones distintas de formas distintas. Este es para alguien que tiene la objeción de "ah, mierda, no puedo hacerlo, no tengo gimnasio" — bueno, "sin gimnasio". "No tengo ningún equipo en casa" — "sin equipo". Y, saben, "solo toma 20 minutos al día" — entonces "no tengo tiempo, 20 minutos al día, genial". ¿Ves? Entonces yo típicamente soy consciente de que si quiero bajar de peso — soy "consciente de la solución" —, podría necesitar un gimnasio, podría necesitar equipo. Ah, esto es distinto: "sin gimnasio, sin equipo". Ahora, para la gente que odia el cardio [?] ("weight cardio" en el original, corregido por sentido a "hate cardio"), típicamente, de nuevo, soy consciente de la solución, sé que podría bajar de peso, podría hacer cardio, no quiero hacerlo, odio la mierda del cardio. Entonces pienso, "sabés qué, no lo voy a hacer". Pero es como, "che, mirá, si odiás el cardio, prestá atención". Okay, interesante, ese soy yo. Después el tercero: "sé que podría hacer dieta, pero va a ser difícil preparar las comidas, va a ser difícil encajarlo en mi horario, estoy ocupado, tengo un negocio, semanas de 60 horas de trabajo" — okay, "demasiado ocupado para hacer dieta, esto es para semanas de 60 horas de trabajo". Interesante. Tres ángulos completamente distintos. Pero, de nuevo, el mismo deseo central de bajar de peso, el mismo programa de coaching fitness. Ahora, seguimos hablándole a la misma solución para nuestra audiencia, pero simplemente cambiamos el ángulo, lo que significa que estamos mirando el mismo producto pero desde ángulos distintos, como vemos acá, distintas formas de enmarcar el mismo producto.</t>
+          <t>¿Es posible reemplazar todo tu sistema de meta ads con IA? Lo probé con Claude y la nueva alianza de Meta recientemente. Así es como funciona. Paso 1: conectar Claude. Meta ahora le permite a Claude conectarse directamente a tu cuenta de meta ads usando conectores de IA. Paso 2: extraer insights. Pedile a Claude que analice el ROAS, las tasas de clics (CTR), el costo por impresión, y las tendencias de conversión en todas las campañas automáticamente. Paso 3: diagnosticar los problemas. Claude identifica gasto desperdiciado, creativos débiles, picos de frecuencia, y problemas de entrega en segundos. Paso 4: generar campañas. Puede duplicar los recursos ganadores y crear nuevas variaciones creativas de testeo automáticamente. La IA acelera la ejecución masivamente, pero la estrategia y el posicionamiento son tan importantes. Si le acertás a esa parte, podés escalar con IA muy bien. Seguime para más contenido educativo de IA y marketing de e-commerce.</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto en el setup habitual. Subtítulos bold ("the bait"). Pantalla dividida con una tabla de referencia sobre tamaños/ángulos de toma cinematográficos (aparentemente un gráfico reutilizado por el juego de palabras con "ángulos") y notas manuscritas con los tres ángulos de copy concretos del ejemplo (sin gimnasio, odio al cardio, 60 horas de trabajo).</t>
+          <t>Fondo de color sólido violeta/azul editado en post-producción (no es una locación real/cámara fija), con estructura de 'pasos' numerados. Se superponen capturas de pantalla (logo de Meta Ads con flecha hacia el logo de Claude, un chat de Claude, un documento tipo Notion con copy de anuncio) y textos grandes en tipografía animada tipo motion graphics ('TRENDS', 'NEW CREATIVE') que remarcan cada paso. La presentadora aparece en la parte inferior del cuadro con blazer blanco y micrófono, formato mitad gráfico/mitad presentadora, sin locación física visible.</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Gancho de analogía simple y memorable (carnada de pesca); estructura de ejemplo triple aplicado al mismo producto/audiencia mostrando la técnica en acción; gatillo de claridad conceptual + aplicabilidad inmediata al propio negocio del espectador.</t>
+          <t>Gancho: pregunta directa sobre una tendencia de actualidad (IA + Meta ads, alianza nueva con Claude). Estructura: framework claro en 4 pasos numerados, fácil de seguir en un video corto (49 seg). Gatillo: curiosidad/FOMO tecnológico por una herramienta nueva, reforzado por la autoridad de quien dice haberlo probado ella misma.</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
-          <t>sí, mismo formato de notas a mano; el gráfico de referencia sobre ángulos de cámara es opcional/decorativo.</t>
+          <t>sí, con nota: requiere edición de motion graphics (fondo de color, overlays animados, capturas de pantalla) con una app gratuita tipo CapCut; exige más tiempo de edición que un talking head simple, pero no equipo profesional.</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
@@ -7297,32 +7297,32 @@
     </row>
     <row r="74" ht="88" customHeight="1">
       <c r="A74" s="2" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -7332,33 +7332,33 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="J74" s="6" t="n">
-        <v>11500</v>
+        <v>715</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7639758395595099422</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665700523940629782</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Video de análisis de marca que desglosa la estrategia publicitaria y de retail de Vuori, la marca de indumentaria deportiva valuada en mil millones de dólares, explicando su volumen creativo, su juego de AOV/LTV y su expansión a tiendas físicas mediante un diagrama tipo 'flywheel'.</t>
+          <t>Ben Heath argumenta que la mayoria de las cuentas de anuncios que fallan no tienen un problema creativo sino un problema de oferta, y explica que auditar (precio, garantia, propuesta de valor, urgencia) antes de tocar los anuncios.</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>La estrategia de marca de mil millones de dólares de Vuori. Están corriendo más de 17 anuncios en Meta. Eso es un volumen enorme de creatividades, con formatos como videos de estilo de vida, videos UGC, videos protagonizados por el fundador, demos de producto, imágenes, tomas estéticas de marca, testimonios y contenido nativo de venta suave. No fuerzan la venta, construyen el deseo. Educan, y después mandan a todos directo a la página de producto. Ofertas simples de 20% de descuento en la primera compra, con visuales prolijos, posicionamiento premium y desgloses de la historia de la tela con prueba social. Convierte porque el producto queda clarísimo. Ahora la palanca real: AOV y LTV. No venden un solo producto, venden los conjuntos completos. Tienen remeras y pantalones, opciones para gimnasio y para el día a día, y variantes de talles, calce, colores y estilos. Te gusta una marca para todo. Eso aumenta el tamaño del carrito automáticamente. Después, alta retención, producto de alta calidad, uso diario integrado con email, más ciclos de recompra. Los clientes no compran una sola vez, vuelven una y otra vez. Ahora el retail. Tienen más de cien tiendas propias en todo el mundo y están en Nordstrom, REI y Equinox. No se apuraron. Primero construyeron demanda, después se expandieron a mercados de altos ingresos. Y acá está la jugada real: los anuncios llevan a ventas online. Ese alcance lleva a más reconocimiento de marca. El reconocimiento de marca lleva de vuelta a visitas en tienda, y las tiendas generan lealtad. La lealtad genera recompras directas al consumidor. Ese es el flywheel. Entonces, ¿cuál es la conclusión? Vuori no ganó solo con anuncios, no ganó solo con retail. Ganaron curando todo el sistema junto: volumen creativo, calidad de producto, posicionamiento premium y expansión de retail con un LTV fuerte. Así se construye una marca de mil millones de dólares. Comentá 'playbook' y te mando las cinco etapas que vas a atravesar al construir tu marca.</t>
+          <t>'Probamos un monton de anuncios distintos. Ninguno funciona. Meta simplemente no funciona para nuestro negocio.' Antes de dar el briefing creativo, auditamos la oferta. ¿El precio es competitivo? ¿La reversion de riesgo es lo suficientemente fuerte? ¿La propuesta de valor es lo suficientemente clara en menos de 5 segundos? Una creatividad debil puede ocultar una oferta fuerte. Una creatividad fuerte no puede salvar una oferta debil. La mayoria de las cuentas de anuncios que fracasan no fracasan por los anuncios. Fracasan porque la oferta no es lo suficientemente buena. Una gran oferta casi se vende sola. El anuncio solo necesita comunicarla con claridad. Cuando miramos una cuenta de anuncios nueva, miramos la oferta antes de mirar la estructura de la cuenta. ¿Cual es la garantia? ¿Cual es la friccion para comprar? ¿Hay una razon convincente para comprar hoy en vez de despues? Un descuento del 20% no es una gran oferta. Una gran oferta es un intercambio de valor completo que hace que la decision se sienta obvia (no brainer). Vimos cuentas mas que duplicar sus ingresos no cambiando un solo anuncio, sino reestructurando la oferta, agregando un bono, ajustando una garantia, creando urgencia real en vez de fabricada. Arregla la oferta primero.</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>Formato split-screen típico de este canal de análisis de marcas: mitad inferior es talking head del presentador (remera clara y campera oscura, micrófono profesional visible, fondo neutro) hablando fijo a cámara; mitad superior cambia de contenido según el tema (clip de una mujer grabándose al espejo con el celular, captura de pantalla/screencast de la página de producto de Vuori con talles y colores, y un diagrama animado tipo 'flywheel' con flechas, logo de la marca y etiquetas de texto: Ads, Meta, Online Sales, Awareness, Store visits). Encuadre vertical, sin cortes dentro del talking head, ritmo marcado por los cambios de la mitad superior.</t>
+          <t>Efecto visual de 'triple clon': el mismo presentador aparece tres veces sentado en el mismo sillon, con remeras de distinto color (roja, gris, verde) y etiquetas 'BEGINNER', 'INTERMEDIATE', 'EXPERT' sobre cada uno; interior luminoso tipo living moderno con planta y cuadro; subtitulos en blanco siguen el audio.</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>Gancho: cifra grande y marca reconocible en el título/primer segundo ('estrategia de mil millones de dólares de Vuori'). Estructura: desglose enumerado de palancas de negocio (creatividad, AOV/LTV, retail, flywheel) que cierra con una síntesis memorable. Gatillo: autoridad/expertise analítico + números concretos (17+ ads, 20% off, 100+ tiendas) + curiosidad por 'el sistema completo'; CTA de comentario para generar leads.</t>
+          <t>Gancho visual de patron interrumpido (verse triplicado) que detiene el scroll antes de escuchar una palabra; gancho verbal contraintuitivo ('no tienen un problema creativo, tienen un problema de oferta'); estructura de framework de auditoria con checklist accionable y prueba social (cuentas que duplicaron ingresos); gatillo de autoridad mas curiosidad.</t>
         </is>
       </c>
       <c r="R74" s="5" t="inlineStr">
         <is>
-          <t>sí + requiere investigar la marca a fondo y armar un diagrama simple tipo flywheel (se puede hacer gratis en Canva), sin necesidad de equipo caro.</t>
+          <t>no del todo, el efecto de clonarse en video requiere camara fija y edicion para alinear las tres tomas (o una app especifica); el contenido en si es replicable sin el efecto.</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
@@ -7389,27 +7389,27 @@
     </row>
     <row r="75" ht="88" customHeight="1">
       <c r="A75" s="2" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Macie Reed</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -7424,48 +7424,48 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="J75" s="6" t="n">
-        <v>11000</v>
+        <v>583</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7598212323538455838</t>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7658140615288311053</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell analiza la estrategia de anuncios de Facebook de Alex Hormozi (170+ anuncios activos): destaca que sus hooks y segmentación funcionan bien, pero critica que le falta contenido de prueba/conversión (reseñas, antes-después, ofertas) para acompañar todo el funnel.</t>
+          <t>Primer episodio de la serie 'Meta Ads Must Haves' de Macie, donde explica la diferencia fundamental entre publicidad 'push' (redes sociales/Meta) y 'pull' (búsqueda/Google) para quienes recién arrancan en meta ads.</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t>¿La estrategia de anuncios de Facebook de Alex Hormozi convierte en la era del 'ad drama' [?]? Está corriendo más de 170 anuncios de Facebook ahora mismo. Múltiples ángulos únicos, llamados directos (callouts), problema-solución, incluso anuncios simples de imagen que se ven aburridos a propósito. Tiene entre cinco y diez hooks (ganchos) únicos por ángulo, interpelando a su cliente ideal y forzando la autoidentificación. Esa parte funciona. Capta la atención y califica a la audiencia. Pero acá está el problema. Una vez que tiene la atención, no está acelerando lo suficientemente rápido a los compradores a lo largo del recorrido (journey). No hay reseñas, no hay anuncios de beneficios, no hay desgloses de la oferta, no hay pruebas de transformación, no hay antes y después. En 2026 tenés que cubrir cada etapa: atención, prueba, deseo, justificación, conversión y lealtad. Agregá [?] estas distintas creatividades publicitarias únicas para cada paso: reseñas, beneficios, claridad del producto, y resultados reales. Sus más de ciento setenta anuncios podrían convertirse en 17 anuncios funcionando con máxima eficiencia. Eso es hacer 'a drama to' [?] marketing bien hecho. No solo hooks, sino dominación total del recorrido del cliente. Contame qué pensás. ¿Está aprovechando su 'a drama to' [?] al máximo potencial?</t>
+          <t>Bienvenidos a Meta Ads Must Haves episodio 1, donde en esta serie les voy a explicar toda la información fundamental que necesitan saber sobre Meta Ads para poder convertirse en un meta ads manager. Ahora, probablemente estén pensando: Macie, ¿por qué querría convertirme en un meta ads manager? Y me alegra mucho que preguntes. Meta ads en realidad es un oficio digital muy bien pago, lo que significa que podés trabajar desde cualquier lugar. Mientras tengas wifi y una notebook, podés ganar una tonelada de dinero, dejar tu trabajo de 9 a 5, y trabajar una fracción del tiempo, básicamente dándote libertad total de tiempo, ubicación y dinero. Puedo dar fe de esto porque es lo que yo hago. Entonces, para arrancar la serie, realmente quiero sentar las bases de qué son exactamente los meta ads. Los meta ads son los anuncios que la gente ve en su feed de Facebook e Instagram. Y estos se les muestran a las personas en base a su interés, comportamientos, datos demográficos, o proximidad a ciertas cosas. Entonces la forma en que me gusta pensarlo es que cuando pienso en publicidad digital en general, la categorizo en dos grupos separados, ¿no? Tenemos paid social (redes de pago) y tenemos paid search (búsqueda de pago). Paid social van a ser las plataformas de redes sociales: Instagram, TikTok, Pinterest, YouTube. Y paid search básicamente va a ser Google. Entonces entre estas dos tenemos un método de empuje (push) versus uno de atracción (pull). Empuje significa que estás empujando tu contenido hacia gente completamente nueva, audiencias frías. Y eso es exactamente lo que hace paid social. ¿No? Entonces, ¿cuántas veces estuviste scrolleando en Instagram y te topaste con un producto del que nunca habías escuchado en tu vida, y resuelve un problema que ni sabías que tenías? Ese es el poder de paid social. Y resulta que meta es la plataforma de paid social más grande. Mientras que, por el contrario, Google es una plataforma de atracción (pull). Está atrayendo a gente que ya está buscando activamente su producto, su industria, o el problema que están tratando de resolver. Si les gusta la serie, asegúrense de seguirme para que puedan ver el episodio 2, donde voy a hablar sobre la estructura fundamental de meta ads.</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: capturas de Meta Ads Library y gráficos de diseño propio (flowchart, grilla de anuncios) con el creador en recuadro inferior. Subtítulos: etiquetas de texto diseñadas (burbujas moradas: 'WE HAVE AN OFFER FOR YOU', etc.), flechas rojas de énfasis. Cortes: alterna entre captura del Ads Library ('~170 results' para Alex Hormozi), diagrama de flujo animado y grilla de fotos con etiquetas. Gráficos: diagramas hechos a medida (ícono de 'Prospects', logo de Meta), fondo de puntos decorativo. Locación: sin locación física visible, fondo de estudio con micrófono.</t>
+          <t>Talking head vertical en dormitorio/living con decoración fija de fondo (lámpara, cuadro parcialmente visible tipo 'Overthinkers Club', póster, planta), campera de jean, micrófono de solapa, sin cortes de escena. Arranca con un gráfico de título de la serie en amarillo tipo sticker ('META ADS MUST HAVES Episode 1'). Subtítulos animados quemados palabra por palabra/frase corta, con gestos de mano para enfatizar.</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Gancho: menciona a una figura reconocida del marketing (Alex Hormozi) en formato de pregunta provocadora sobre si su estrategia realmente funciona, combinando autoridad prestada con la promesa de una crítica polémica. Estructura: formato de auditoría — reconoce qué funciona (hooks, segmentación) y después señala el hueco (falta contenido de conversión) y propone una solución (17 anuncios optimizados cubriendo todo el funnel). Gatillo: crítica contraintuitiva a una celebridad del rubro más pregunta final que invita al debate en comentarios.</t>
+          <t>Gancho: promesa aspiracional de estilo de vida (oficio digital bien pago, libertad de tiempo y ubicación). Estructura: episodio 1 de una serie educativa que sienta las bases conceptuales antes de avanzar, generando hábito de seguimiento. Gatillo: autoridad personal ('puedo dar fe de esto porque es lo que yo hago') y curiosidad por el próximo episodio.</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr">
         <is>
-          <t>No — exige diseño gráfico personalizado (flowcharts, grillas con etiquetas) además de research en Ad Library, más trabajo que un simple talking-head.</t>
+          <t>sí + nota: solo celular, mic de solapa y buena luz de living/dormitorio, sin edición avanzada.</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
@@ -7481,32 +7481,32 @@
     </row>
     <row r="76" ht="88" customHeight="1">
       <c r="A76" s="2" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -7516,48 +7516,48 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J76" s="6" t="n">
-        <v>10900</v>
+        <v>573</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7652379900728413471</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7642638640090336545</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Video que enumera el 'stack' de herramientas de inteligencia artificial que, según el creador, usan las marcas de e-commerce de cien millones de dólares para investigar, producir creatividades estilo UGC y lanzar campañas más rápido.</t>
+          <t>Ben Heath ensena, paso a paso, como crear una metrica personalizada de 'hook rate' (tasa de retencion del gancho) dentro del Administrador de Anuncios de Meta.</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
-          <t>El stack de herramientas de IA detrás de las marcas de e-commerce de cien millones de dólares. Claude para armar la estrategia: ganchos, guiones, ofertas y ángulos. Manus para analizar creadores, cuentas publicitarias y brechas de rendimiento. Yuka[?] para automatizar las invitaciones a creadores a gran escala para TikTok Shop. Higgsfield[?] (confirmado por el logo que aparece en pantalla) para convertir ideas estáticas en creatividades de video estilo UGC. Opencl[?] para correr tareas mientras dormís. Y archives[?] para crear anuncios UGC sin depender de creadores. Imaginative para sacar imágenes de anuncios de Meta a gran escala. Así es como las mejores marcas se mueven más rápido. No usan la IA solo para hacer contenido, usan la IA para investigar más rápido, lanzar más rápido, testear más rápido y encontrar ganadores antes que nadie. Comentá 'AI' y te mando el stack exacto.</t>
+          <t>Como analizar tus hooks de anuncios de Meta: aca tenes un proceso de cinco pasos. Paso 1: anda al Administrador de Anuncios y hace clic en Columnas. Paso 2: seleccioná personalizar columnas. Paso 3: desplazate hacia abajo y crea una metrica personalizada. Paso 4: nombrala 'hook rate'. Paso 5: configura la formula: tu hook rate es las reproducciones de video de 3 segundos dividido las impresiones. Despues hace clic en guardar y va a aparecer junto a cualquier anuncio de video que tengas en tu cuenta de anuncios.</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>Video de ritmo muy acelerado (35 segundos) que intercala capturas/grabaciones de pantalla de herramientas de IA (interfaz de 'Higgsfield' con botón 'Generate' y avatar; una escena tipo video generado por IA con el branding 'MCP x Claude') en la mitad superior, con el presentador (remera negra, fondo claro liso, micrófono de podcast) hablando en la mitad inferior. Título grande en texto blanco sobre franja negra en el frame de apertura, junto a una imagen de referencia.</t>
+          <t>Arranca con Ben a camara con el titulo superpuesto ('How to analyse your Meta Ad hooks'); despues el video se divide en dos: arriba Ben hablando en formato pequeno con vineta, abajo grabacion de pantalla del Administrador de Anuncios (panel de Personalizar columnas, creacion de metrica personalizada) con subtitulos de palabra clave ('scroll', 'views').</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>Gancho: cifra grande ('marcas de cien millones de dólares') + promesa de una lista secreta ('tech stack'). Estructura: listado rápido de herramientas con una función concreta para cada una, ideal para el formato corto (35 segundos). Gatillo: curiosidad (nombres de herramientas de IA nuevas/desconocidas) + autoridad + utilidad práctica inmediata + CTA de comentario ('AI').</t>
+          <t>Gancho de tutorial claro con promesa de proceso ('a five step process'); estructura numerada (paso 1 a 5) facil de seguir y de guardar; gatillo de utilidad practica inmediata para cualquier anunciante.</t>
         </is>
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
-          <t>sí + solo necesita grabaciones de pantalla de herramientas freemium/gratuitas y un guion tipo lista, aunque exige estar al tanto de herramientas de IA nuevas.</t>
+          <t>si, solo requiere grabar la pantalla del Administrador de Anuncios y explicar los pasos a camara.</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -7573,27 +7573,27 @@
     </row>
     <row r="77" ht="88" customHeight="1">
       <c r="A77" s="2" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Macie Reed</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -7608,48 +7608,48 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="J77" s="6" t="n">
-        <v>9980</v>
+        <v>466</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7641243325227339038</t>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7664783404147150094</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>Presenta una herramienta de inteligencia artificial que genera automáticamente decenas de anuncios de marca a partir de la URL de un producto, sin diseñadores ni producción.</t>
+          <t>Cuarto episodio de la serie donde Macie explica las dos decisiones clave de presupuesto en Meta Ads (diario vs. de por vida, y presupuesto a nivel de campaña vs. de conjunto de anuncios) y cierra promocionando la lista de espera de su curso.</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>Esta nueva herramienta de IA te crea anuncios ilimitados con un solo prompt. ¿Y la parte que da miedo? Que realmente convierten. Se llama Imaginative [?] (en el título aparece como 'Imaginetive'). Literalmente pegás la URL de tu producto. Después la IA escanea tu sitio web, extrae tus imágenes, extrae tus fuentes tipográficas, copia los colores de tu marca, lee tus reseñas, escanea Reddit buscando a tus competidores, escanea las reseñas de Amazon, y arma todo tu kit de marca automáticamente. Después elegís los formatos de anuncio que querés: anuncios estilo POV, anuncios de Instagram Story, anuncios tipo respuesta de DM, anuncios estilo nota, anuncios de reseña, anuncios de estilo de vida, anuncios de comparación. Y en segundos obtenés de 50 a 100 piezas publicitarias completamente de marca, listas para lanzar. Sin diseñadores, sin Canva, sin Photoshop, sin producciones caras. Y la parte más loca: estos anuncios ya no parecen contenido generado por IA. Algunas de estas marcas están consiguiendo 3x, 5x, hasta 10x de ROAS usándolos, y están escalando una barbaridad. Por eso las marcas de crecimiento más rápido están produciendo cientos de piezas creativas todos los meses. La IA acaba de cambiar la publicidad para siempre. Comentá 'AI' y te mando la herramienta.</t>
+          <t>Bienvenidos de nuevo a Meta Ads Must-Haves episodio 4, donde en esta serie les estoy enseñando todo lo que necesitan saber sobre Meta Ads para que puedan convertirse en un Meta Ads manager y ganar una tonelada de dinero y trabajar una fracción del tiempo. En el episodio de hoy vamos a hablar sobre presupuestos, porque hay dos decisiones que tenés que tomar cuando se trata de presupuesto. La primera decisión es si querés hacer un presupuesto diario versus uno de por vida (lifetime). Diario significa: che Meta, tenés tal cantidad de dinero que quiero que gastes todos los días indefinidamente hasta que te diga lo contrario. Y presupuesto de por vida significa: che, tenés esta suma total de dinero que necesito que gastes entre tal fecha y tal fecha. Y una vez que se gastó el dinero o pasó esa última fecha, entonces apagás la campaña. Generalmente les recomiendo a todos hacer presupuesto diario porque podés controlar manualmente tu presupuesto mucho más fácil y extender la vida de una campaña todo el tiempo que necesites. Después, la segunda decisión que tenés que tomar es dónde querés determinar tu presupuesto. En un episodio anterior mencioné que puede ser a nivel de campaña o a nivel de conjunto de anuncios (ad set). A nivel de campaña, básicamente le estás diciendo: che Meta, tenés tal cantidad de dinero que quiero que gastes todos los días dividido entre mis conjuntos de anuncios como te parezca mejor para conseguirme el mejor retorno de mi inversión publicitaria. Mientras que tal vez en realidad necesitás testear diferentes elementos dentro de tu anuncio. Entonces necesitás limitar tu variable de gasto y hacer que cada conjunto de anuncios gaste la misma cantidad. En ese caso, vas a hacer una optimización de presupuesto a nivel de conjunto de anuncios y decir: che, quiero $30 para este conjunto de anuncios todos los días, 30 para este, y 30 para este otro. Y eso es esencialmente la idea general de cómo determinar tu presupuesto. Muchos de ustedes están disfrutando esta serie y en realidad me estuvieron pidiendo un curso. Así que estoy trabajando en un meta ads crash course que va a ser un curso de meta ads amigable para principiantes. Y mientras trabajo en construir esto, en realidad ya abrí mi lista de espera. Entonces si se unen a mi lista de espera, tienen acceso anticipado, precio con descuento, y voy a compartir contenido extra.</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>Talking head/selfie con micrófono, superpuesto por croma sobre capturas de pantalla de una herramienta de generación/análisis de anuncios (interfaz tipo swipe file con 'Feature Breakdown' de una marca de jeans, y panel de resultados de IA con la pieza 'Linen. Relaxed'). Subtítulo grande tipo texto en caja azul con emoji ('Have you heard of this New Ai Tool? 🤔') en uno de los frames. Cortes entre el presentador y las capturas de pantalla de resultados.</t>
+          <t>Talking head vertical, mismo tipo de set/decoración que otros episodios de la serie (pared clara, cómoda, lámpara, cuadro, planta), esta vez con sweater a rayas y sosteniendo una taza. Subtítulos automáticos animados palabra por palabra, con al menos un error tipográfico visible en pantalla ('A FRADTION' en vez de 'a fraction'). Sin gráficos de apoyo adicionales en los frames vistos, sin cortes de escena.</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>medio-alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Gancho de curiosidad directo ('¿escuchaste hablar de esta nueva herramienta de IA?') más promesa de beneficio concreto y algo 'escalofriante' (que convierten de verdad). Detalla un proceso paso a paso fácil de imaginar (pegar URL y todo automático), apela a autoridad con números concretos (3x-10x ROAS, 50-100 creatividades) y cierra con un call-to-action de comentario que dispara engagement.</t>
+          <t>Gancho: continuidad de la serie educativa numerada que ya construyó audiencia en episodios previos. Estructura: 'dos decisiones' de presupuesto explicadas de forma clara y aplicable de inmediato. Gatillo: urgencia comercial al cierre (lista de espera con acceso anticipado y descuento) que capitaliza el interés generado por el contenido educativo gratuito.</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr">
         <is>
-          <t>sí + solo requiere grabarse hablando y mostrar capturas de pantalla de la herramienta, sin edición avanzada.</t>
+          <t>sí + nota: mismo formato de bajo costo que el resto de la serie, solo celular y mic de solapa.</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
@@ -7665,32 +7665,32 @@
     </row>
     <row r="78" ht="88" customHeight="1">
       <c r="A78" s="2" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
+        <v>52</v>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -7700,48 +7700,48 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="J78" s="6" t="n">
-        <v>9889</v>
+        <v>382</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7592305158449827102</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7644916873481555202</t>
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell describe el estilo creativo híbrido que combina IA (para fondos, motion graphics y transiciones) con talento real filmado en cámara, como estrategia para triplicar el volumen de anuncios sin perder autenticidad.</t>
+          <t>Segunda pieza del glosario de Ben Heath grabado en el evento de Meta en Silicon Valley (marcado como Parte 1 en pantalla): explica reach, impresiones, tasa de conversion, audiencias similares (lookalike), el pixel de Meta y UGC.</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
         <is>
-          <t>Este nuevo estilo creativo se está apoderando del e-commerce ahora mismo. Es IA híbrida con clips reales. Y las marcas están usando IA para manejar todo lo que ralentiza la producción. Fondos, motion graphics, transiciones de escena. La IA construye todo el entorno visual en segundos. Y después mezclan creadores de IA con talento real filmado en cámara. Una parte es IA, pero el resto son caras reales, reacciones reales, historias reales. Esto mantiene el contenido humano para que los espectadores confíen en él, pero le da a la marca más material para trabajar, para cosas que no podrían capturar u obtener de creadores a esa escala. Acá está la estrategia detrás de esto. La IA te da variaciones infinitas para que puedas testear docenas de creadores de IA rápido. El talento real mantiene el rendimiento alto porque nada convierte como la verdadera emoción [?] (en el audio se entiende 'true motion'). La mezcla permite que las marcas tripliquen su producción, bajen costos, y dominen los feeds. Con volumen creativo constante, podés lograr escala sin sacrificar autenticidad. Las marcas que adoptan esto primero están ganando la subasta en Meta y TikTok porque su contenido se siente nativo. Pero tienen de tres a cinco veces la cantidad de anuncios saliendo, algo que estas plataformas aman. Así que si todavía no estás probando este formato híbrido, ya estás atrás. Comentá 'IA' y te muestro cómo hacerlo.</t>
+          <t>Meta me llevo a Silicon Valley y acabo de estar en una sala con mas de mil anunciantes que gastan decenas de miles de millones en anuncios de Meta cada ano. Escuche mucha jerga, asi que hoy te la voy a desglosar y explicar que significa en realidad. Reach (alcance) es simplemente a cuanta gente se le mostraron tus anuncios. Impresiones es cuantas veces se vieron tus anuncios. Es distinto del alcance porque la misma persona puede ver tus anuncios multiples veces. La tasa de conversion tipicamente se refiere al porcentaje de gente que convirtio despues de hacer clic en uno de tus anuncios. Audiencia similar (Lookalike Audience), que es un grupo de personas muy parecidas a otro grupo de personas. Subis una lista de clientes a Meta y le decis 'creame una audiencia similar'. Meta va a analizar los datos y va a crear una audiencia de personas parecidas a ellos, a las que quizas quieras apuntar. El Pixel de Meta, que es un codigo que pones en tu sitio web que te permite rastrear las acciones que hace la gente despues de hacer clic en tu anuncio, asi podes ver que paginas miraron, si compraron o se convirtieron en lead. Esa informacion se retroalimenta a tu cuenta de anuncios de Meta, lo que permite que tus campanas optimicen correctamente y consigas mas de las acciones que queres conseguir. UGC, que es contenido generado por el usuario, es cuando la gente explica su experiencia con un producto o servicio, hace recomendaciones, demuestra las caracteristicas. Mi version favorita de UGC es trabajar con creadores e influencers. Su poder para detener el scroll realmente ayuda a mejorar el rendimiento, y ademas su recomendacion tiene peso, asi que las tasas de conversion tambien son mas altas.</t>
         </is>
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: mezcla de captura de pantalla de herramienta de IA (Google Flow), clip UGC real (una madre comprando con sus hijas en un supermercado) y grilla de Meta Ads Library, con el creador en recuadro inferior. Subtítulos: franja roja con texto tipo subtítulo de reseña ('...even bought that...organic berries'). Cortes: varios cortes entre las distintas fuentes de video. Gráficos: ninguno más allá del recuadro PiP y la franja de texto. Locación: sin locación física propia, fondo de estudio con micrófono.</t>
+          <t>Mismo set que la fila 203 (mismo dia y lugar): Ben al aire libre en el predio del evento con credencial/lanyard y remera roja, edificio y cielo despejado de fondo; subtitulos en mayusculas siguiendo el audio palabra por palabra; titulo superpuesto '$300M Meta Ad expert breaks down the jargon (Part 1)'.</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q78" s="5" t="inlineStr">
         <is>
-          <t>Gancho: framing de tendencia emergente ('este nuevo estilo se está apoderando del e-commerce ahora mismo') con emoji de IA. Estructura: identifica la tendencia, explica el mecanismo híbrido (IA + talento real), lista beneficios de producción, muestra prueba (marcas ganando la subasta) y cierra con urgencia ('ya estás atrás'). Gatillo: FOMO de tendencia combinado con un beneficio operativo muy concreto para agencias/marcas (triplicar producción, bajar costos).</t>
+          <t>Mismo gancho de autoridad y exclusividad que la fila 203 (invitacion de Meta a Silicon Valley); estructura de glosario facil de guardar ('Save this'); gatillo educativo de simplificar jerga tecnica para audiencia de marketing.</t>
         </is>
       </c>
       <c r="R78" s="5" t="inlineStr">
         <is>
-          <t>No — depende de acceso a herramientas de IA de video (Veo/Flow) y de conseguir varios clips reales distintos para mezclar en la edición.</t>
+          <t>no del todo, depende del acceso al evento real para el gancho de autoridad, aunque el glosario en si es replicable en cualquier locacion.</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -7757,32 +7757,32 @@
     </row>
     <row r="79" ht="88" customHeight="1">
       <c r="A79" s="2" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
+        <v>53</v>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -7792,48 +7792,48 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="J79" s="6" t="n">
-        <v>8648</v>
+        <v>375</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7669839443364302110</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7662343318533082390</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>Comparación de las estrategias de marketing de dos marcas de suplementos, Mars Men y Thorne: volumen y formatos de anuncios en Facebook, embudos de venta (quiz vs. página de producto directa) y estrategias de distribución (retail/profesionales de la salud vs. venta directa).</t>
+          <t>Ben Heath enumera a los saltos, en formato de lista rapida, una serie de factores y metricas de Meta Ads calificandolos como importantes o no importantes (segun se ve en pantalla: segmentacion por interes, ajustes de presupuesto diario, calidad de audio, entre otros).</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr">
         <is>
-          <t>¿Quién tiene mejor marketing, Mars Men o Thorne? Mars Men está corriendo más de 12 [¿1200?, posible error de transcripción] anuncios activos en Facebook ahora mismo. Eso es una locura total. Están corriendo todos los formatos que te puedas imaginar. Ofertas de 50% de descuento para meter gente en suscripción. Anuncios de antes y después, desgloses de producto, anuncios educativos tipo '8 señales de tal cosa', formato podcast, UGC, ofertas especiales, comparaciones de producto, anuncios explicativos de cómo funciona el producto, qué hace y cuáles son sus beneficios. Y montones de imágenes generadas por IA y básicamente cada tipo de pieza creativa que te puedas imaginar. Thorne solo está corriendo alrededor de 200 anuncios activos en Facebook, con videos, ofertas de suscripción con descuento, UGC, y tomas mayormente centradas en el producto. Se están perdiendo un montón de formatos y ángulos creativos distintos. Mars Men manda a la gente a un funnel de quiz, porque saben que cuanta más información puedan capturar, mejor pueden personalizar la oferta, hacer retargeting, y volver a contactar a la gente para que compre. Una vez que alguien completa ese quiz, lo dirigen a un protocolo personalizado y le dan una oferta de 50% de descuento. Esa página de producto está construida completamente para convertir. Desglosa todo lo que necesitás saber sobre el producto, cómo funciona, los beneficios, y por qué deberías comprarlo. También te incluyen regalos especiales. Porque saben que si pueden aumentar el valor de vida del cliente y lograr una buena relación entre CAC y LTV [?, en el audio 'C to L TV ratio'], se pueden dar el lujo de gastar un montón de plata en anuncios. No es casualidad que Mars Men esté escalando. Thorne manda a la gente directo a la página de producto: tienen algunas fotos de producto, desgloses de producto, dos sabores, y una oferta de suscripción con descuento. Pero les falta mostrar variantes de sabor, les falta educación visual, les faltan montones de imágenes de comparación y desglose de producto, y la mayor parte del sitio es solo texto. Hay muchísimo más que podrían estar haciendo en sus páginas de producto para educar a los clientes, resolver objeciones, y aumentar sus tasas de conversión y sus AOV (ticket promedio). Pero Thorne no se enfoca solo en marketing directo al consumidor. Están aprovechando a profesionales de la salud que recomiendan, prescriben o venden productos Thorne directamente. También están disponibles a través de cientos de retailers distintos. Están en Amazon, están en Fullscript, tienen distribución profesional, usan alianzas de afiliados con otros proveedores de salud, y se asocian con otras marcas que distribuyen y recomiendan sus productos, como Ultrahuman. Esto le permitió a Thorne escalar rápidamente a lo largo de los años a través de la distribución, aprovechando la confianza de los profesionales de la salud, los retailers, los afiliados y otras marcas establecidas. Mars Men solo tiene una presencia de retail más chica, en lugares como GNC. Así que mientras Mars Men construyó un embudo agresivo de respuesta directa, publicidad y conversión, Thorne construyó una red masiva de confianza y distribución. Contame quién pensás que está ganando.</t>
+          <t>Extremadamente importante, no importante, muy importante, medio importante, ya no importante, importante, importante de nuevo, no importante, no muy importante, muy importante, muy importante, no tan importante como la gente cree, muy importante, medio importante, no importante mientras lo evites, no importante, no importante mientras no sea un problema, altamente importante.</t>
         </is>
       </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
-          <t>Talking head/selfie con micrófono, superpuesto por croma sobre capturas de pantalla reales de anuncios y páginas de producto de ambas marcas: oferta '50% OFF FOR LIFE' de Mars Men con botellas de producto, desglose de ingredientes de Mars Men, e imagen de 'The Thorne Podcast' con un médico. Formato de comparación lado a lado apoyado en evidencia visual (screenshots), sin gráficos animados propios más allá del recorte por croma.</t>
+          <t>Video en primer plano tipo selfie al aire libre (azotea/edificio, cielo despejado); cada corte muestra una etiqueta grafica distinta con el nombre del factor (por ejemplo 'IBT / Interest-based targeting', 'DBA / Daily budget adjustments', 'Audio quality') en distintos estilos de texto y color; ritmo de edicion muy rapido dado que en 23 segundos se listan cerca de 19 items. Nota: la transcripcion de audio es solo la secuencia de calificaciones, sin el nombre del item; la asociacion item-calificacion se ve unicamente en el video.</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Gancho de comparación directa entre dos marcas del mismo nicho (formato '¿quién lo hace mejor?') que genera opinión y polémica en los comentarios. Aporta datos concretos (cantidad de anuncios, tipo de funnel, tácticas de retail) que dan autoridad, y cierra pidiendo la opinión del espectador, lo que dispara comentarios y alcance.</t>
+          <t>Formato de lista rapida tipo 'importante vs no importante' que genera intriga constante sobre que sigue; estructura repetitiva que facilita el scroll-stop por su ritmo; gatillo de curiosidad y autoevaluacion (el espectador chequea mentalmente si esta haciendo bien o mal cada punto).</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr">
         <is>
-          <t>sí + solo necesita investigar dos marcas competidoras y grabarse comentando capturas de pantalla de sus anuncios y páginas.</t>
+          <t>si, es un video selfie con textos superpuestos, sin necesidad de edicion avanzada mas alla de las etiquetas.</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
     </row>
     <row r="80" ht="88" customHeight="1">
       <c r="A80" s="2" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
+        <v>95</v>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Dara Denney</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -7884,33 +7884,33 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="J80" s="6" t="n">
-        <v>7101</v>
+        <v>333</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daradenney/video/7650514495403543838</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7632740460217322759</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Recapitulación desde el evento Conversations 2026 de Meta en Londres, donde una estratega creativa explica el lanzamiento de los agentes de IA para negocios de WhatsApp/Meta, que pueden vender y cerrar ventas directamente en el chat -incluso agente a agente- y cómo eso cambia el rol de la publicidad.</t>
+          <t>Justin Lalonde comparte una lista numerada de hooks (ganchos de apertura) para anuncios de Facebook y UGC que, según él, ya están probados y funcionan de forma repetida para escalar cuentas publicitarias.</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
         <is>
-          <t>No quiero sonar alarmista, pero en el futuro muy cercano no le vamos a estar vendiendo solo a humanos. Insertá el chiste. Le vamos a estar vendiendo a agentes. Entonces, si sos estratega creativo o dueño de un negocio, y estás viendo esta noticia que salió de Londres la semana pasada del evento Conversations de Meta, y estás pensando 'ah, esto es solo un tema de WhatsApp'. Incorrecto. Meta acaba de lanzar sus agentes de IA para negocios, que también van a llegar pronto a Instagram. Esto no va a ser solo un chat que responde preguntas frecuentes o un mini competidor de chat: puede recomendar productos de tu catálogo, reservar turnos, e incluso cerrar la venta, y hasta comunicarse por notas de voz. Las aerolíneas ya la están rompiendo con esta estrategia. Marcas de consumo masivo, marcas de indumentaria. Pero lo que más me llamó la atención, especialmente como estadounidense, donde admito que muchos de mis clientes hoy no están usando anuncios de WhatsApp, fue cuando el director de marketing de Meta subió al escenario y dijo que muchas de las conversaciones que están pasando en WhatsApp con los clientes no son solo de agente a cliente. Son de agente a agente. Dio un ejemplo buenísimo de una empresa de alquiler de autos, donde notaron que los agentes de las personas están efectivamente cerrando la venta final con los agentes de IA de negocios de Meta. Como alguien que hace más de una década que hace publicidad en Meta, esto me parece verdaderamente fascinante, porque el librito de jugadas solía ser: mostrás el anuncio, vas a la landing page, cerrás la venta. Pero ahora, cada vez más, vamos a empezar a ver que pasa de anuncio a chat a venta, y también vamos a tener la venta y compra real de esos productos a través de todos nuestros agentes. Entonces, como estratega creativa, así es como me estoy preparando para esto: tengo un interés recién descubierto en los anuncios de clic para enviar mensaje. Los voy a estar estudiando en serio las próximas semanas, para entender si hay una diferencia entre el creador ganador para anuncios de clic a mensaje versus el librito de jugadas habitual del negocio. Y también voy a estar viendo cómo se manejan esas conversaciones por parte de los agentes de IA de Meta. Tengo muchísima curiosidad por ver qué marcas se mueven primero acá. Creo que hay una ventaja competitiva enorme en este momento. Y para la gente que tiene negocios de infoproductos como yo, pienso: esto es buenísimo, porque una gran parte de la venta pasa por el DM. Y sobre todo, como estratega creativa, realmente me pregunto qué va a pasar ahora con el brief. ¿Cuál va a ser el rol real de la pieza creativa del anuncio de acá en adelante? Si el embudo ahora es anuncio-chat-venta, ¿nuestra estrategia creativa va a ir todavía más hacia la parte alta del embudo? Que ha sido la tendencia en los últimos meses. Bueno, un montón de gracias a Meta por invitarme a Conversations la semana pasada. La onda fue muy distinta a la del Performance Summit. Y tengo que decir que salí de ese evento pensando muchísimo sobre el futuro de la publicidad. Y, la verdad, no puedo esperar, pero tengo mucha curiosidad por escuchar qué piensan ustedes de todo esto.</t>
+          <t>Si estás buscando una lista de hooks para anuncios de Facebook, o tal vez simplemente hooks de UGC que puedas reutilizar, que ya fueron testeados y que están comprobados que funcionan una y otra vez y escalan en una cuenta publicitaria, entonces este video es para vos. Número uno: 'público objetivo, no te duermas con esto' (target audience do not sleep on this). Ese es un gancho increíble para nombrar una audiencia específica. Entonces podrías decir algo como, ya sabés, 'dueños de negocios de e-commerce, no se duerman con esto', o 'dueños de agencias no se duerman con esto', o 'si sos un hombre de más de 35 años y estás sufriendo este problema, no te duermas con esto', ¿no? Realmente podés nombrar y ser muy específico. Número dos: '¿escuchaste mucho sobre X?'. Este generalmente es genial para crear curiosidad al principio de un anuncio, ¿no? Genera como una especie de FOMO [?] ('debería haber escuchado sobre esto hasta ahora'), ¿no? Número tres: 'la mayoría de las personas no saben cómo hacer X', que de nuevo, crea exclusividad. Es como que te sentís excluido si no sabés sobre esta cosa. 'Probé este truco (hack) de X para que vos no tengas que hacerlo'. Uno increíble, ¿okay? 'Te voy a compartir algo muy personal'. Eso también crea una historia, crea esta relación con la audiencia. 'Este truco me cambió la vida'. Muy similar, número cuatro: 'dejá de hacer esto', que básicamente ese es casi como un gancho de clickbait. Simplemente invita al usuario a seguir mirando el anuncio para enterarse de: ¿qué es esto? ¿De qué estás hablando?, ¿no?</t>
         </is>
       </c>
       <c r="O80" s="5" t="inlineStr">
         <is>
-          <t>Mezcla de b-roll grabado en vivo en el evento Conversations 2026 de Meta en Londres (mujer de pie frente a una pantalla/backdrop del evento con micrófono de mano tipo entrevista) con selfie video grabado en otro momento/lugar (interior tipo living/oficina, luz natural), misma protagonista (pelo pelirrojo, blusa rosa satinada, chaleco verde oliva, aros). No se observan subtítulos incrustados en los frames muestreados.</t>
+          <t>Talking head vertical con fondo oscuro/neutro tipo oficina o estudio (silla de escritorio visible, planta), mic de mesa tipo streaming, sin cortes de escena entre los frames vistos. Se agrega un gráfico numerado tipo 'badge' amarillo con ícono de gancho/anzuelo para marcar cada punto de la lista (visible en el frame del punto 2). Subtítulos blancos simples quemados en el video.</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
-          <t>Gancho: afirmación provocadora sobre el futuro ('le vamos a vender a agentes de IA, no a humanos') que genera intriga y hasta un poco de alarma. Estructura: contexto del anuncio de Meta, ejemplo concreto (alquiler de autos con venta agente-a-agente), y plan de acción personal de la creadora. Gatillo: primicia/exclusividad (asistió al evento real de Meta), autoridad (más de una década en pauta de Meta), curiosidad por una tendencia disruptiva; cierra con pregunta abierta para generar comentarios.</t>
+          <t>Gancho: promesa de utilidad inmediata tipo 'lista de recursos listos para usar' (hooks ya probados). Estructura: lista numerada fácil de guardar y aplicar directamente en la propia cuenta. Gatillo: utilidad práctica y autoridad (afirma que estos hooks 'escalan' cuentas reales), lo que invita a guardar el video como referencia.</t>
         </is>
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
-          <t>no + depende de tener acceso a un evento exclusivo de la industria para conseguir la primicia informativa que arma el gancho, aunque la grabación en sí (selfie) es de bajo costo.</t>
+          <t>sí + nota: solo cámara, mic de mesa económico y un gráfico simple de número superpuesto, editable en apps gratuitas.</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
     </row>
     <row r="81" ht="88" customHeight="1">
       <c r="A81" s="2" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Solución de un problema</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -7976,48 +7976,48 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="J81" s="6" t="n">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7670633794583448840</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665695408898706710</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde señala que con presupuestos chicos ($50-100/día) los anunciantes suelen pelear simultáneamente contra tres problemas (mala oferta, malos creativos, mala landing page) y confunden el síntoma —tener que producir demasiados creativos— con la causa real.</t>
+          <t>Ben Heath lista cinco errores comunes que arruinan una cuenta de anuncios de Meta: matar anuncios por emociones, escalar demasiado rapido, solo testear variaciones superficiales, depender de una sola creatividad y copiar anuncios de la competencia.</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr">
         <is>
-          <t>Cuando recién empezás a correr anuncios, puede que no te des cuenta de esto cuando estás gastando un presupuesto muy chico, como 50 a 100 dólares por día, pero podrías estar peleando contra los tres problemas simultáneamente. A veces tenés una mala oferta y tenés que producir una cantidad significativa de creativos porque todavía no sos muy bueno haciendo creativos, y tampoco tenés el tipo correcto de landing page, y por lo tanto lo que termina pasando es que estás peleando en los tres frentes sin realmente saberlo. Sentís que estás dando vueltas en círculos y siempre tenés que estar produciendo nuevos creativos para tratar de superar los malos creativos, la mala oferta y la mala landing page. Así que uno de los síntomas acá de tener un problema de los de arriba típicamente va a ser "demasiados creativos". Okay, o sea, que tenés que producir tantos creativos todo el tiempo porque sentís que "justo mis anuncios se siguen muriendo, nada funciona" — o funciona por muy poco tiempo. Esto usualmente significa que una de esas tres cosas tiene un problema. Okay, entonces si tenés malos creativos, obviamente vas a tener que producir más creativos con la esperanza de encontrar uno bueno, porque eso es como buscar una aguja en un pajar. Mala oferta significa que, de nuevo, tus creativos van a tener que sobrecompensar por la oferta siendo mala. Mala landing page, de nuevo, significa que tenés que sobrecompensar haciendo muchísimo más volumen de creativos, porque tienen que mandarte gente súper "cálida" (warm) a tu landing page, o si no, simplemente no van a convertir.</t>
+          <t>Cinco formas de arruinar tu cuenta de anuncios de Meta. Numero uno: matar anuncios basandote en emociones. Una pequena caida no significa que tu anuncio este muerto, espera al menos una semana. Numero dos: escalar demasiado rapido. Pasar de 50 dolares por dia a 500 dolares de la noche a la manana no es escalar, es una receta para el desastre. Vas a resetear la fase de aprendizaje y disparar tus CPA. Numero tres: solo testear variaciones. Si tu anuncio ya esta fracasando y cambias la paleta de colores, no va a pasar nada significativo. Anda mas profundo y testea distintos hooks, distintas emociones, distintas ofertas. Numero cuatro: dejar que una sola creatividad sostenga toda la cuenta. Si no tenes nada preparado para cuando la fatiga publicitaria finalmente aparezca y la audiencia deje de comprar, tus ventas se van a desplomar. Numero cinco: copiar los anuncios de tu competencia de forma identica, uno a uno. Realmente no conoces sus margenes de negocio, su oferta, su proceso ni su backend. Toma inspiracion, pero mantenete unico.</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto. Subtítulos con cifras destacadas en dorado ("$50 — $100 a día"). Pantalla dividida con lo que parece ser una grabación de pantalla de una app de notas del celular (se ve reloj/batería en la captura) con cálculos y un diagrama de flujo escritos a mano (Oferta → Creativos → Landing Page, más síntomas listados).</t>
+          <t>Toma unica a camara, estilo selfie, al aire libre en un campo/pastizal con cielo despejado, musculosa casual; solo subtitulos blancos que siguen el audio, sin graficos adicionales ni cortes de edicion visibles.</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Gancho de insight/reencuadre ("tu problema podría no ser uno solo"); estructura de diagnóstico de síntoma vs. causa con tres frentes posibles; gatillo de identificación ("me pasa a mí") para anunciantes de bajo presupuesto.</t>
+          <t>Gancho de aversion a la perdida ('your ad account is bleeding money'); estructura de lista numerada de errores, facil de seguir y de aplicar como checklist; gatillo de miedo/urgencia a estar cometiendo un error sin saberlo.</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr">
         <is>
-          <t>sí, celular con app de notas, cámara y micrófono básico alcanzan para replicarlo.</t>
+          <t>si, es el formato mas simple del lote: una sola toma a camara al aire libre con subtitulos.</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
@@ -8033,17 +8033,17 @@
     </row>
     <row r="82" ht="88" customHeight="1">
       <c r="A82" s="2" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -8068,33 +8068,33 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="J82" s="6" t="n">
-        <v>242</v>
+        <v>304</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7640890960645295378</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7634298092455480584</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde cuenta que perdió un cliente grande tras recomendarle matar su funnel de anuncios, y explica las señales para decidir entre relanzar creativos ganadores anteriores, hacer A/B testing incremental del funnel, o cambiar el VSL/webinar por completo.</t>
+          <t>Justin Lalonde muestra cómo generó con IA (Google Veo 3) un video-hook para un cliente de productos blanqueadores de dientes, compartiendo el prompt exacto que usó y el resultado final en pantalla dividida.</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr">
         <is>
-          <t>Acabo de perder un retainer de cliente de múltiples seis cifras porque le dije que matara todo su funnel [?] ("because they told them" en el original, corregido por sentido — probablemente "porque yo le dije") — ahora te cuento por qué lo volvería a hacer. Desde la perspectiva de un media buyer, o de una agencia, o incluso de un marketer, diría que lo que está en juego es que podés convertirte en una agencia muy rápido que simplemente no puede entregar resultados, cuando la verdad es simplemente que te tocaron cartas malas y tenés que poder cambiar esas cartas y hacerte cargo de la situación. Así que algunas de las señales acá — y una de las primeras — es cuando muchos de tus "ganadores" (winners) actuales están muriendo. Lo que vas a querer hacer, y lo que vas a querer probar, es relanzar viejos ganadores. Si estos vuelven a mover la aguja, decimos "okay, no, esto probablemente es solo un problema de creativos, nuestro stack de creativos actual simplemente no sirve, necesitamos reformular los creativos". Pero lo que a veces termina pasando — y en el caso específico del cliente que mencioné en la introducción — es que relanzar viejos ganadores no funcionó por mucho tiempo. Empezó a pasar que, si mirás el gráfico, esos resultados repuntaban un poco y después iban bajando lentamente otra vez. Entonces, el A/B testing del funnel es cuando vas a hacer cambios pequeños, mejoras incrementales pequeñas — por ejemplo, probar titulares (headlines), después la página de opt-in o sin página de opt-in como ejemplo, después empezás a avanzar hacia conversión y optimización. Voy a poner acá algo como Microsoft Clarity, que instalarías en tu landing page, y después empezás a probar cosas como: ¿deberían mover el botón más arriba? ¿La gente siquiera hace scroll hasta la sección de testimonios? ¿La gente lee las reseñas o no? ¿Lee la descripción? — empezás a mirar todos los detalles pequeños de tu landing page para intentar arreglarla. Otras cosas que podés hacer acá es, si estás corriendo un VSL como ejemplo, cambiar el VSL — voy a poner "VSL webinar" como cambio — esto en realidad te puede devolver a resultados bastante decentes, como "okay, genial, mi funnel no está tan mal, solo necesitaba unos ajustes".</t>
+          <t>Como ven, este hook de acá fue generado enteramente usando IA. Ya no necesitás esperar para conseguir stock footage, o tal vez si sos un marketer que recibe assets de un cliente, todo lo que necesitás ahora es la nueva herramienta de video Veo 3 de Google para generar todo el stock footage y b-roll que necesites. Podés usar esto de dos formas diferentes. Podés usarlo simplemente para generar b-roll y metraje, como te voy a mostrar en este video, o también podés hacer que la gente hable. Entonces acá lo que le puse [al prompt] fue: crear un video de una mujer hermosa de 23 años, pelirroja, con maquillaje suave y pelo ondulado, mirándose a sí misma en el espejo del baño. El baño es de un estilo escandinavo [?] moderno y prolijo. El ángulo de cámara está justo detrás de su hombro. Está sonriendo suavemente [?]. Se está cepillando los dientes y hay un líquido color púrpura en código hexadecimal [?]. Y después le puse un líquido de código de color hexadecimal X goteando de su boca. Mi objetivo acá es que uno de nuestros clientes en realidad vende productos blanqueadores de dientes, que en realidad son de color amarillo. Y entonces por eso quería crear algo que fuera como shockeante. Si silencio el video acá y le doy play, pueden ver que empieza a cepillarse los dientes, pero se pone un poco raro en cierto punto, ¿no? Se puede ver como que ahora, por alguna razón, se está cepillando la cara. Y entonces pensé: bueno, ahora lo que queremos hacer acá es, ya saben, una vez que termina, apoya el cepillo de dientes sobre la mesada. Se suponía que solo se iba a cepillar los dientes, no toda la cara. Y entonces reproduje esto acá. Fue un poco raro al principio porque, de nuevo, se metía más hacia el interior de su mejilla, pero de ahí en adelante se veía, ya saben, mejor hacia el final. Así que de hecho usamos parte de ese clip. Esto es, de nuevo, una forma muy simple de mostrarles cómo usarlo. Y entonces, ¿no?, pueden ver que este del lado izquierdo es todo de Veo [?]. Bueno. Pero es el tipo de cosa que cuando la ves en tu feed, decís '¿qué mierda es eso?', ¿no? Y ese es el objetivo con esto. Ese es el objetivo, conseguir un hook fuerte. Es como esa misma imagen acá arriba, pero también hicimos otra acá, que es como simplemente dientes más amarillentos y como dientes grandes mostrándose acá en el medio, que de nuevo, es el tipo de cosa que ves en tu feed y decís '¿qué es eso?'. Y entonces si mirás algunos de estos otros ejemplos, que tienen una tasa de hook súper, súper alta, como 91%, 67%, 75%, todos esos como 'wow, ¿qué es eso?', ese tipo de hook. Que es lo que estamos tratando de hacer más, utilizando Veo 3 hoy en día.</t>
         </is>
       </c>
       <c r="O82" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto en el setup habitual. Subtítulos bold, algunos frames sin gráfico adicional. Pantalla dividida con una libreta donde va escribiendo a mano (aparentemente en vivo) una lista numerada de señales para matar un funnel y pasos de A/B testing, construyéndose progresivamente en sincronía con el relato hablado.</t>
+          <t>Talking head en estudio/oficina con fondo oscuro y planta, mic de mesa, sin cortes en la primera parte. A mitad de video pasa a formato de pantalla dividida (split screen) mostrando debajo del presentador el resultado del video generado por IA (dos clips de una mujer cepillándose los dientes con líquido violeta, y un soporte de cepillos de dientes). Subtítulos blancos simples quemados. El propio video generado por IA funciona como el 'hook' de ejemplo que se está explicando.</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="Q82" s="5" t="inlineStr">
         <is>
-          <t>Gancho de vulnerabilidad/pérdida concreta ("perdí un cliente de 6 cifras") + postura contraintuitiva ("lo haría de nuevo"); estructura narrativa de caso real con señales de decisión enumeradas; gatillo de storytelling + utilidad práctica tipo checklist implícito.</t>
+          <t>Gancho: intriga visual inmediata ('este hook fue generado enteramente con IA'). Estructura: caso práctico paso a paso, mostrando el prompt exacto usado y el resultado, más el dato de tasas de hook reales (91%, 67%, 75%). Gatillo: curiosidad/asombro por lo inusual ('qué mierda es eso') combinado con utilidad de tutorial replicable.</t>
         </is>
       </c>
       <c r="R82" s="5" t="inlineStr">
         <is>
-          <t>sí, formato de libreta/notas a mano en vivo, mismo setup casero de siempre.</t>
+          <t>sí, con nota: requiere acceso a una herramienta de IA generativa de video de pago/créditos (Google Veo 3), pero no equipo de filmación caro.</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
@@ -8125,27 +8125,27 @@
     </row>
     <row r="83" ht="88" customHeight="1">
       <c r="A83" s="2" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Charley T (Disrupter School)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -8160,48 +8160,48 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="J83" s="6" t="n">
-        <v>231400</v>
+        <v>302</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7618214625120767262</t>
+          <t>https://www.tiktok.com/@ctthedisrupter/video/7592685803558505742</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell presenta cómo conectar la herramienta de IA Manus a Meta Ads Manager para detectar la fatiga de creatividades en tiempo real y automatizar el contacto con creadores de UGC vía Instagram, armando lo que llama un 'motor de adquisición autooptimizante'.</t>
+          <t>Entrevista callejera/de evento en la que el creador aborda a Ben Schreiber, quien dice gastar entre $400.000 y $500.000 mensuales en Meta Ads, y le pide dos tips: usar la métrica "ganancia bruta por transacción" (GPT = AOV − CPA) en vez de solo ROAS, e iterar sobre los creativos ganadores en pequeños pasos (estilo Kaizen).</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr">
         <is>
-          <t>Meta acaba de cambiar el marketing con IA para siempre. Acaban de adquirir Manus AI y ahora la podés sincronizar directamente con Meta Ads. Esto es automatización de IA a nivel de toma de decisiones. Acá está exactamente cómo funciona. Primero, conectás Manus AI a Meta Ads Manager, permitiéndole ver los datos de tu cuenta publicitaria en tiempo real. Segundo, le podés preguntar qué creatividades se están fatigando y te dice exactamente cuándo está cayendo la atención, cuándo la frecuencia se está disparando, y justo antes de que el rendimiento de tu cuenta esté por caer. Así sabés exactamente cuándo renovar tu contenido publicitario. Pero acá es donde se pone una locura. Podés configurar el agente de IA para que automatice por vos el contacto con creadores. Imaginate un bot potenciado por Meta contactando creadores de UGC por vos en Instagram, haciéndoles la propuesta, haciendo seguimiento, registrando las respuestas, organizando las entregas, y alimentando automáticamente esas creatividades nuevas de vuelta a tu cuenta publicitaria justo en el momento exacto en que más importa. Eso significa que tu pipeline creativo nunca se va a secar. Y se acabó el adivinar cuándo cambiar los anuncios, se acabó correr desesperado por contenido nuevo, y se acabaron los cuellos de botella creativos que matan la escala. Esto no es solo una herramienta de IA para reportes. Esto es un motor de adquisición autooptimizante. IA vigilando tus anuncios, IA prediciendo la fatiga, IA consiguiendo nuevos creadores, e IA manteniendo tu cuenta fresca. Si entendés de anuncios de Meta, sabés que lo creativo es el cuello de botella. Esto va a cambiar todo. Comentá 'Manus' y te doy el desglose exacto de cómo podés aprovecharlo antes que todos los demás.</t>
+          <t>Hola, amigo. ¿Cómo te llamás? Hola, soy Ben Schreiber de LaTica Leathers [?] (nombre de marca tal como se transcribió; posiblemente "Latico Leathers"). ¿Cuánto están gastando ahora mismo? En promedio, diría que gastamos entre 400 y 500 mil dólares al mes en anuncios de Meta. Nada, ya sabés, un par de cientos de miles de dólares al mes, un par de millones al año. Sí. Como si nada (casually). Bueno, dejame preguntarte esto: hay mucha gente que no anda tirando casualmente un par de millones al año. Tratando nomás de hacer las cosas bien. ¿Cuál sería un tip o un truco o simplemente algo para alguien que quiere ser mejor mañana? ¿Qué pasa si no llegaron todavía al millón al año y vos estás gastando un par de millones? ¿Qué podrían hacer para mejorar ya mismo? Tengo dos cosas de entrada. Diría que uno, y esto en realidad fue un consejo que vos me diste y que yo agregué a mis columnas de Meta, fue agregar tu GPT, tu ganancia bruta por transacción (gross profit per transaction). Sí, miro eso y me ayudó muchísimo. Es una mejor mirada que el ROAS o el costo por compra. Agreguen eso a sus columnas, y pregúntenle a este tipo si necesitan ayuda para configurarlo. Sí, eso es, por cierto, el AOV (valor promedio de orden) menos el CPA (costo por adquisición). Muy indicativo de cómo está funcionando un anuncio, algo que la mayoría de la gente no mira. Número dos es mirar a tus ganadores, mandárselos a tu equipo de diseño gráfico [?] (transcripto como "graph design team", probable error de "graphic design team") y hacer iteraciones basadas en tu creativo ganador. Tratar de ver si podés ir mejorándolo de a poco y hacerlo todavía mejor. Me encanta eso, viejo. Así que el progreso a través de iteraciones es ir mejorando un poquito. Es Kaizen, un uno por ciento mejor cada día. Eventualmente vas a resolver el problema (crack that nut). Exacto.</t>
         </is>
       </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: grabación de pantalla (screen recording) en modo oscuro con la cara del creador en un recuadro (PiP) en la parte inferior, formato podcast con micrófono. Subtítulos: no hay subtítulos quemados; el texto en pantalla es la interfaz de la app. Cortes: cortes entre distintas pantallas de la herramienta (menú de conectores, chat de la IA, dashboard). Gráficos: flechas rojas de énfasis dibujadas sobre la interfaz para guiar la mirada (se confirma en pantalla el nombre real de la herramienta, 'Manus 1.6 Lite'). Locación: fondo oscuro tipo estudio, sin locación física identificable.</t>
+          <t>Formato "vox pop"/entrevista en vivo en un evento nocturno (bar o fiesta de conferencia), luz ambiente azul/violeta, entrevistador con micrófono pequeño de mano, entrevistado con estética llamativa (pelo teñido azul, barba, camisa blanca). Subtítulos en cajas de fondo celeste/turquesa con texto blanco en mayúscula, por frase (no palabra por palabra). Cámara en mano con leve movimiento, plano medio de dos personas, gente y ruido de fondo visibles.</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Gancho: afirmación exagerada de 'noticia' ('Meta acaba de cambiar el marketing con IA para siempre'), con emoji en el título. Estructura: anuncio de novedad, explicación paso a paso del mecanismo, escalada de expectativa ('acá es donde se pone una locura') y reencuadre ambicioso (no es una herramienta de reportes, es un motor de adquisición). Gatillo: FOMO por ser early adopter más un CTA con palabra clave en comentarios que dispara el algoritmo por engagement.</t>
+          <t>Gancho de cifra grande impactante (gasta $400-500 mil dólares AL MES) + formato de entrevista espontánea que genera autenticidad + estructura de "pedile 2 tips a alguien que gasta millones" + gatillo de aspiración y utilidad concreta con una métrica accionable que el espectador puede copiar ya.</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr">
         <is>
-          <t>Sí, con matices — el formato (webcam + grabación de pantalla + flechas) es de bajo presupuesto, pero depende de tener acceso a la herramienta de IA mostrada y de estar atento a la novedad justo cuando es tendencia.</t>
+          <t>sí + solo requiere un micrófono de mano/solapa y asistir a eventos de networking para conseguir entrevistados; el valor está en el contenido del entrevistado, no en la producción.</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
@@ -8217,32 +8217,32 @@
     </row>
     <row r="84" ht="88" customHeight="1">
       <c r="A84" s="2" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
+        <v>98</v>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Caleb Kruse (Mr. Paid Social)</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -8252,33 +8252,33 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="J84" s="6" t="n">
-        <v>5173</v>
+        <v>295</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mr.paidsocial/video/7664714637417532685</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7629809400877681927</t>
         </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>Caleb cuenta como usa una Mac Mini corriendo Claude Code para automatizar buena parte de su negocio: una app de iPhone controlada por voz, campanas de email, un dashboard de contenido, scraping de anuncios/contenido viral hacia Airtable y el lanzamiento de una promo de aniversario en su cuenta de Meta, todo gestionado desde la cama a las 6am.</t>
+          <t>Justin Lalonde resume en 58 segundos su framework completo para arrancar y escalar una cuenta de Meta ads, desde definir buyer personas y espiar competidores hasta la regla de optimización a los 7 días.</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr">
         <is>
-          <t>Pense que todo el hype de comprar una Mac Mini para correr tus agentes de IA era una pavada, hasta que compre una. Me di cuenta de que podes hacer un monton de cosas con ella. Te garantizo que el 99% de los tech bros de IA la estan usando solo para correr cosas como OpenClaw [?] o Hermes, pero no creo que ni siquiera haga falta meterse con eso. Probablemente el caso de uso mas loco que le estoy dando ahora mismo es que hice que Claude Code me construyera una app que me permite controlarlo con mi voz desde mi iPhone, desde cualquier lugar. Literalmente la estoy construyendo ahora mismo usando Xcode y uso esta app en mi iPhone. Si algo se rompe, le puedo escribir a Claude Code desde la app para que arregle la app. Automaticamente sube la app a mi telefono por mi. Tengo todo un entorno de desarrollo sin siquiera tener que saber lo que estoy haciendo, porque todo corre siempre en esta Mac Mini. Puedo estar literalmente en cualquier parte del mundo y darle tareas para que haga. Esta manana le hice armar toda una campana de lanzamiento por email para la venta de aniversario de mi comunidad de Skool que estoy corriendo ahora mismo, y literalmente entro a mi proveedor de email Flodesk y controlo el navegador para armarme los flujos de email, segmentarlos, y enviarlos en el orden en que yo queria que se enviaran. Tengo otra instancia corriendo un dashboard que rastrea todo mi contenido hacia una base de datos tipo biblioteca gigante y me da insights todos los dias. A lo largo del dia, la tengo peinando mi Instagram en busca de piezas de contenido organico viral y anuncios que ve por ahi. Y tira todos esos anuncios a esta base de Airtable donde tiene un gasto estimado y los likes. Tambien tira todas esas piezas de contenido organico, cuantas vistas consiguio cada contenido, junto con la transcripcion completa y una explicacion de por que se volvio viral en primer lugar. [?] Con esta Mac Mini arme esta venta de aniversario en mi cuenta de anuncios de Meta, que ya tiene una venta registrada hoy. Hice esto desde mi cama a las 6 de la manana. Hay muchisimos mas casos de uso para esto, pero lo unico que puedo decir es que tener esta configuracion ahora me permite basicamente tener una VA que controla todo mi negocio de punta a punta. Tiene contexto completo de todo lo que hice con ella alguna vez. Se pone mas inteligente cuanto mas la uso. Les voy a mostrar a la gente como arme esto en mi comunidad de Skool, que esta con 70% de descuento ahora mismo por mi aniversario. Asi que si queres el link para eso, comenta 'skool' y te lo mando.</t>
+          <t>Gasté cerca de $10 millones de dólares en anuncios de Facebook tan solo en los últimos seis meses; denme 58 segundos y les muestro exactamente cómo arrancar y escalar tu cuenta de meta ads. Entendé que en esta era post-'end of meta' [?] (frase poco clara en el audio original, posiblemente referida a la era posterior a los cambios de privacidad de iOS14/Meta) todo se trata de los creativos. Lo primero que haría si fuera vos es definir tres ICPs objetivo, o sea tres personas (buyer personas) únicas y diferentes que tengas. A partir de ahí, listaría los tres a cinco principales deseos y puntos de dolor que tiene cada una de ellas. Y después, a partir de ahí, lo que haría es encontrar competidores que estén anunciando para exactamente el mismo ICP, y robarles ('snipearles') sus anuncios estáticos de mayor duración en el tiempo, para después poder replicarlos para mi ICP y sus puntos de dolor. Después voy a ir al ads manager, crear una sola campaña y fijar mi presupuesto diario como una campaña CBO (optimización de presupuesto de campaña) para superar mi objetivo de KPI multiplicado por la cantidad de anuncios que quiero lanzar. Voy a crear un conjunto de anuncios por cada creativo que quiera lanzar, y configurar mi segmentación como ubicación automática, y programar que esos anuncios salgan en vivo a medianoche. Después voy a dejar que esto corra durante siete días. Y a los siete días voy a volver a revisar la cuenta, eliminar todo lo que no esté funcionando, y si la campaña en general es rentable, la voy a escalar un 20 por ciento, en base a que los últimos siete días demuestren ser rentables.</t>
         </is>
       </c>
       <c r="O84" s="5" t="inlineStr">
         <is>
-          <t>Talking head en primer plano con iluminacion de colores (violeta/rosa) y planta de fondo, subtitulos dinamicos quemados, intercalado con capturas de pantalla de un dashboard/Airtable mostrando datos reales, incluyendo un frame donde un dedo senala la pantalla mientras explica por que un contenido se volvio viral. Ritmo tipo 'day in the life' con pruebas visuales de cada automatizacion mencionada.</t>
+          <t>Talking head vertical en estudio/oficina con fondo oscuro, silla tipo gamer, planta, mic de mesa, sin cortes de escena visibles ni gráficos adicionales más allá del texto de título. Texto de título grande en verde neón ('$10M Ad Strategy in 58 Seconds') al inicio a modo de gancho visual. Subtítulos blancos simples palabra por palabra, ritmo acelerado acorde a la promesa de brevedad.</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="Q84" s="5" t="inlineStr">
         <is>
-          <t>Gancho de escepticismo convertido en creencia ('pense que era una pavada hasta que...'); estructura tipo 'day in the life' que encadena casos de uso cada vez mas sorprendentes; gatillo de urgencia y oferta (descuento de aniversario del 70%) mas CTA claro para comentar y recibir el link.</t>
+          <t>Gancho: autoridad y cifra grande impactante ('gasté casi $10 millones') combinada con promesa de brevedad/eficiencia ('58 segundos'). Estructura: framework completo comprimido en pasos secuenciales (personas, competidores, estructura de campaña, regla de 7 días). Gatillo: urgencia y autoridad que invita a guardar el video como referencia rápida.</t>
         </is>
       </c>
       <c r="R84" s="5" t="inlineStr">
         <is>
-          <t>no del todo, requiere tener ya armado un ecosistema de negocio (Mac Mini, Airtable, Skool, automatizaciones) para poder mostrar casos de uso reales, aunque la grabacion en si sea barata.</t>
+          <t>sí + nota: solo cámara, mic de mesa y un texto de título simple; el valor está en el conocimiento compartido, no en la producción.</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
@@ -8309,32 +8309,32 @@
     </row>
     <row r="85" ht="88" customHeight="1">
       <c r="A85" s="2" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
+        <v>55</v>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -8344,48 +8344,48 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="J85" s="6" t="n">
-        <v>4168</v>
+        <v>285</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7613406587423673631</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7662722851530689814</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell presenta una herramienta de inteligencia creativa que permite buscar los anuncios de cualquier competidor, ver cuáles llevan más tiempo corriendo (señal de que convierten) y guardar los mejores patrones en un swipe file.</t>
+          <t>Ben Heath analiza un anuncio de Meta de Athletic Greens (AG1) protagonizado por Hugh Jackman y lo puntua 9 sobre 10, destacando la demo de producto, el uso del actor y el giro de la llamada telefonica como 'pattern interrupt'.</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
         <is>
-          <t>La herramienta creativa detrás de tus marcas favoritas. Si estás corriendo anuncios pagos en 2026, ya sabés esto: lo creativo es el cuello de botella. Meta ya no premia un solo anuncio ganador. Premia volumen, variación y formatos. Ahí es donde entra esta herramienta. Te permite buscar cualquier competidor y ver al instante qué anuncios llevan más tiempo corriendo. Eso importa porque los anuncios no se quedan activos a menos que estén convirtiendo. Podés desglosar eso: hooks, ángulos, formatos de anuncio, videos estilo UGC, estructuras de oferta, y después guardar todo en un swipe file (archivo de referencia) que tu equipo realmente pueda usar. No hay que adivinar, no hay agotamiento creativo, y no hay que empezar de cero. Así es como los mejores media buyers (compradores de medios) se mantienen adelante. No solo testean más rápido, roban patrones que ya están comprobados que funcionan. Si querés mejores anuncios, un CAC (costo de adquisición de cliente) más bajo, y creatividades que realmente escalen, necesitás mejor inteligencia creativa. Comentá 'tool' y te la mando.</t>
+          <t>Pensa en todas las cosas que AG1 reemplaza, es una decision obvia (no brainer). Bueno, empieza [?, en el original 'strange with product demo', probable error de reconocimiento por 'starts with product demo'] con una demo de producto, despues un corte rapido a Hugh Jackman. Me gusta eso, no hay nada malo ahi. Los negocios chicos pueden hacer esto tambien al 100%, dicho sea de paso. Solo necesitas trabajar con influencers de menor nivel. 'No necesitas pastillas para esto. Polvo es para eso [?, en el original 'Power is for that', probable error de reconocimiento por 'Powder is for that']. Cuando podes tener todo en una sola cucharada.' La narrativa es fuerte, tener a sus vecinos como repitiendo todo lo que dice realmente transmite la idea de que ama el producto. Tambien es entretenido, tipo, es gracioso, va a mantener tu atencion. Me encanta esta parte de la llamada telefonica. Es una interrupcion de patron (pattern interrupt) realmente grande, abre un nuevo loop. Va a mantener al espectador enganchado, viendolo hasta el final del anuncio. Este es un muy buen anuncio. Le doy un nueve de 10.</t>
         </is>
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>Encuadre: capturas de pantalla de Meta Ads Library (búsqueda de marcas como 'alphalete', ficha de anuncio individual, grilla de resultados) con el creador en recuadro inferior. Subtítulos: ninguno quemado aparte de la interfaz misma. Cortes: entre distintas pantallas del Ads Library. Gráficos: flecha roja señalando el dato '741D' (741 días activo) como prueba de que un anuncio convierte. Locación: sin locación física, fondo de estudio con micrófono.</t>
+          <t>Mismo formato de resena que las filas 204/205/212: Ben con el celular mostrando el anuncio original superpuesto (video con Hugh Jackman, escena de cocina/mesa con dos personas), esta vez sentado en un living distinto con planta y estanteria de fondo; etiquetas de seccion superpuestas (por ejemplo 'Immediate Demo &amp; Influencer Pairing') acompanan la critica.</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Gancho: apela a autoridad indirecta ('la herramienta detrás de tus marcas favoritas'). Estructura: plantea el problema del momento (lo creativo es el cuello de botella, Meta premia volumen), presenta el mecanismo de la herramienta, muestra prueba concreta en pantalla (un anuncio corriendo hace 741 días) y promete un resultado usable (swipe file). Gatillo: dato duro y verificable (741 días) que vuelve tangible una promesa abstracta, sumado al CTA por palabra clave.</t>
+          <t>Gancho de reconocimiento de celebridad (Hugh Jackman) mas formato de resena de alta puntuacion que funciona como caso de estudio a imitar; estructura de desglose punto por punto de que funciona; gatillo de aprendizaje aspiracional al analizar un anuncio exitoso de una marca grande.</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr">
         <is>
-          <t>Sí, con matices — el research se hace en Meta Ads Library, que es gratis; solo hace falta grabación de pantalla y una flecha de énfasis.</t>
+          <t>si, mismo formato de resena replicable con celular y superposicion de video.</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
@@ -8401,27 +8401,27 @@
     </row>
     <row r="86" ht="88" customHeight="1">
       <c r="A86" s="2" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+        <v>56</v>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Dara Denney</t>
+          <t>Macie Reed</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -8436,48 +8436,48 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="J86" s="6" t="n">
-        <v>4094</v>
+        <v>284</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daradenney/video/7667945190090394911</t>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7665765984271240461</t>
         </is>
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>Dara Denney muestra cómo automatizó por completo el reporte mensual de rendimiento creativo de su agencia usando ChatGPT, Codex y una conexión directa a la API de Meta Ads, reduciendo el tiempo de armado de 3-4 horas a 20-30 minutos.</t>
+          <t>Macie recuerda a su audiencia que la lista de espera para su Meta Ads Crash Course está abierta, detallando los beneficios de anotarse (acceso anticipado, descuento y un toolkit de Notion gratis).</t>
         </is>
       </c>
       <c r="N86" s="5" t="inlineStr">
         <is>
-          <t>Este flujo de trabajo con ChatGPT significa que nunca más voy a tener que hacer reportes creativos a mano, especialmente ahora que ChatGPT, Work y Codex están todos en el mismo lugar. A fin de cada mes armamos un reporte de rendimiento creativo para todos nuestros clientes. Cubre de todo: métricas del negocio mes a mes, desglose de productos, aprendizajes creativos. Pero nos llevaba entre tres y cuatro horas armar cada uno por marca. Así que acá les cuento cómo automaticé esto por completo usando ChatGPT, bajando el tiempo total de armado del deck a 20 minutos. Primero usé GPT 5.6 [?] en ChatGPT, le mostré ejemplos de nuestros reportes viejos y le di contexto adicional sobre lo que quería lograr. Ahí armamos un plan para construir una app en Codex. Después armé una "plugin skill" (habilidad conectada) que ayudara a darle vida a los decks exactamente en el formato que yo quería. Y finalmente conecté Codex directamente a Meta Ads a través de una llamada a la API de Meta for Developers, para poder conseguir los datos más precisos posibles. Antes estaba haciendo malabares con múltiples fuentes de datos y visualizaciones, pero ahora todo se hace a través de ChatGPT, Work y Codex. Ahora tenemos esto como tareas programadas para cada marca, y directamente nos avisa por Slack cada vez que un reporte está listo para los últimos retoques. Entonces ahora, cada mes, a ChatGPT se le avisa cuando es momento de generar un reporte nuevo. Ahí consulta la "plugin skill" que desarrollé, para saber de qué cliente se trata y en qué formato quiero la presentación, y después, usando Codex, se conecta directamente a Meta Ads para conseguir los datos más precisos. Yo solo dedico entre 20 y 30 minutos a agregar los insights que solo yo puedo aportar, pero el 90% del trabajo pesado quedó completamente resuelto por ChatGPT. Así que si sos una mujer en "spam" [?] que quiere automatizar por completo su reporte de Meta Ads, asegurate de descargar la app de escritorio de ChatGPT.</t>
+          <t>Si querés aprender meta ads en 2026 y convertirte en una meta ads manager que pueda ganar una tonelada de dinero y trabajar una fracción del tiempo, este es solo tu recordatorio de que estoy lanzando mi meta ads crash course en la próxima semana más o menos, y mi lista de espera está actualmente abierta y disponible para que te anotes. Entonces cuando te anotás y comprás el Meta Ads Crash Course desde la lista de espera, vas a tener acceso anticipado al lanzamiento del curso, vas a tener un precio con descuento, le voy a meter un super descuento, y voy a sumar contenido extra donde recibís mi meta ads toolkit completamente gratis. Ahora, esto es como un producto viejo que solía ofrecer, no está disponible actualmente en ningún otro lado, así que estoy trayendo de vuelta a un favorito al que todavía nadie más tiene acceso. Así que lo recibís completamente gratis, y básicamente es la Biblia. Es como, si estás en plan 'okay, tengo que entrar y crear una cuenta publicitaria, crear anuncios', simplemente tenés que ir a este, eh, Nash, perdón, Dashboard de Notion, y está todo ahí para vos. Te va a decir exactamente qué hacer, te da inspiración de anuncios, te da swipe files, eh, ideas de hooks, cómo escribir captions convincentes, eh, qué llamados a la acción usar, básicamente todo. Y eso viene junto con mi meta ads crash course, donde voy a estar adentro del Meta Ads Manager guiándote paso a paso exactamente en cómo configurar tu cuenta y tus campañas, y qué hacer y qué realmente no importa tanto al principio, porque meta te tira un montón de boludeces encima. Así que si esto te suena como algo para vos, asegurate de unirte a mi lista de espera. El link para hacerlo está en la parte de arriba de mi perfil, así que andá a hacerlo ahora.</t>
         </is>
       </c>
       <c r="O86" s="5" t="inlineStr">
         <is>
-          <t>Collage con múltiples capas: talking head (mujer sentada en escritorio de madera con laptop, remera verde, micrófono de podcast, decoración con lámpara verde y cuadros de fondo) combinado con capturas de pantalla superpuestas de la interfaz de ChatGPT y de documentos/planes de trabajo. Subtítulos progresivos con algún efecto de tachado sobre el texto. Edición con varias capas visuales (screen recording + cámara).</t>
+          <t>Talking head vertical en dormitorio con luz cálida anaranjada de fondo, campera de jean, sin mic visible en los frames capturados; segundo y tercer frame muestran otro ángulo con cuadros de fondo (parecen láminas de peces/naturaleza). Subtítulos blancos simples quemados en el video. Formato promocional directo sin gráficos de apoyo adicionales ni cortes de escena marcados en los frames vistos.</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
-          <t>Promesa de resultado fuerte al inicio ("nunca más voy a tener que hacer reportes a mano"), reforzada con cifra de tiempo ahorrado (de 3-4 horas a 20 minutos). Estructura de tutorial paso a paso de la automatización, herramienta por herramienta, con capturas de pantalla como evidencia. El gatillo es el ahorro de tiempo cuantificado combinado con un tutorial técnico con prueba visual y asociación a una marca (contenido patrocinado, autoridad).</t>
+          <t>Gancho: identificación directa con la audiencia objetivo ('si querés aprender meta ads y ganar mucho dinero trabajando poco'). Estructura: oferta clara con beneficios listados uno a uno (acceso anticipado, descuento, bonus gratis). Gatillo: urgencia y escasez ('lanzo la próxima semana', 'nadie más tiene acceso a esto todavía'), apalancando el interés generado por los episodios educativos previos de la serie.</t>
         </is>
       </c>
       <c r="R86" s="5" t="inlineStr">
         <is>
-          <t>no — requiere herramientas pagas (ChatGPT Work, Codex, API de Meta) y conocimiento técnico para armar el flujo que se muestra.</t>
+          <t>sí + nota: es un video de venta simple, solo cámara y buena luz ambiente, sin producción adicional.</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
@@ -8493,32 +8493,32 @@
     </row>
     <row r="87" ht="88" customHeight="1">
       <c r="A87" s="2" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
+        <v>57</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Solución de un problema</t>
         </is>
       </c>
-      <c r="E87" s="11" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>BitBranding</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -8528,33 +8528,33 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J87" s="6" t="n">
-        <v>3915</v>
+        <v>278</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@officialmattbell/video/7646124046270074134</t>
+          <t>https://www.tiktok.com/@bitbranding/video/7638775568783133982</t>
         </is>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>Matt Bell explica, mostrando datos reales de una cuenta de Meta Ads y de la herramienta de atribucion Triple Whale, por que guiarse solo por el ROI que reporta cada plataforma es enganoso, y como usar distintos modelos de atribucion (primer clic, ultimo clic, lineal, etc.) para saber que esta generando ingresos de verdad.</t>
+          <t>BitBranding argumenta que los anuncios de Facebook que fallan no es un problema de presupuesto sino del algoritmo que cambió, y presenta cómo usan Claude en todo su proceso de anuncios, cerrando con el resultado de una campaña real de $4.800 de gasto diario y ROAS 5x.</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t>Si mirás esta cuenta de anuncios ahora mismo, podes ver que el ROI promedio para este periodo es 2x. ¿Okay? Y la mayoria de la gente va a mirar esto y va a tomar decisiones en base al ROI que se esta reportando. Entonces capaz miran esa campana que esta teniendo un ROI de 3x ahora mismo y piensan 'esta bien, la voy a dejar corriendo'. Y obviamente van a mirar las campanas con ROI mas bajo y las van a apagar. El problema que tenes es que la forma en que META reporta los datos ahora mismo, y todos estos otros canales de anuncios, es de una manera muy dificil de rastrear. Toda tu estrategia entera tiene que estar dictada en base a tu MER. Ahora, esto de aca es Triple Whale. Y Triple Whale es esta herramienta que te permite mirar distintos modelos de atribucion, en lo que vamos a entrar en un segundo, y tambien te da la capacidad de crear estos dashboards muy lindos donde podes conseguir estas metricas y rastrearlas. Ahora, tambien hay otras herramientas ademas de Triple Whale. Un par de ejemplos serian Northbeam, TrueROAS [?]. A estas se las llama herramientas de atribucion. Entonces si entras aca donde dice 'atribucion', tenes estos distintos modelos de atribucion aca. Y algo de esto se explica solo, pero basicamente, si voy a 'primer clic' ahora mismo, lo que me va a mostrar son mis resultados de la gente que hizo clic desde el anuncio y compro ahi. En otras palabras, ¿que canal te esta trayendo el mejor trafico de conversion? Despues, si voy a 'ultimo clic', eso me va a mostrar a la gente que vio un anuncio, digamos en Facebook, pero despues, 3 dias mas tarde, vio un anuncio en Google Display y convirtio como resultado del Google Display, entonces esa seria una conversion de ultimo clic. Y despues tambien tenes lineal, pagado y aprendizaje en todo [?], y atribucion triple. Estas son basicamente la version de Triple Whale de tratar de calcular cual es el riesgo usando su propio modelo. Y creo que involucra IA y un monton de otras cosas, pero basicamente te da una vision bastante buena de que es lo que realmente esta generando tus ingresos.</t>
+          <t>La brecha entre las marcas que están ganando en Facebook ads y las que están perdiendo dinero nunca fue tan amplia [corregido de 'wiped']. Las marcas que están perdiendo siguen haciéndolo a la vieja usanza. Apilamiento de intereses (interest stacking), topes de puja (bid caps), 12 conjuntos de anuncios diferentes, tratando manualmente de ser más listos que un algoritmo que tiene más datos que toda la gente de su equipo combinada. Y acá está la cosa: no es que sean malos en esto, es que el algoritmo cambió. Meta cambió más en los últimos 18 meses que en los cinco años anteriores, y la mayoría de las marcas no se enteraron. Las marcas que descubran cómo alimentar al algoritmo con mejores insumos ahora mismo van a dominar su categoría. Las que no, van a seguir preguntándose por qué su costo por compra sigue subiendo. Ahora, si estás gastando dinero en anuncios de Facebook y no estás viendo el retorno que esperabas, te puedo asegurar ahora mismo que no son los insumos, no es tu presupuesto. Entonces en este video les voy a mostrar exactamente cómo podemos usar Claude en todo nuestro proceso de anuncios de Facebook, desde saber a quién le estamos vendiendo, hasta escribir el guion, el creativo, hasta armar el brief de campaña antes de siquiera abrir el ads manager. Vale la pena armar esta campaña. Déjenme mostrarles el resultado final antes de entrar en cómo la construimos. Entonces esta es una campaña ahora mismo con $4.800 de gasto diario, gastamos $136.000 en los últimos 30 días, que sé que para algunas personas no es una locura, pero con un ROAS de 5x [corregido de '5x row as'] no está nada mal.</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>Grabacion de pantalla de principio a fin en los frames analizados: primero un dashboard de Meta Ads (tabla con gasto, CPM, alcance, frecuencia, CTR), despues el dashboard de Triple Whale con metricas reales (Net Profit, ROAS, MER, Net Margin, Web Analytics). Banner de texto blanco fijo en la parte superior con el titulo del video. No aparece el creador a camara en los frames muestreados, solo voz en off narrando los datos en pantalla.</t>
+          <t>Talking head en estudio con fondo oscuro/gris, gorra puesta al revés, remera con texto de merch ('Love Your Neighbor'), mic no visible en cuadro. Se intercala al menos un slide de fondo sólido azul grisáceo con frases clave en tipografía blanca grande tipo motion graphics (sin cara), a modo de corte visual entre segmentos del guion. Subtítulos blancos quemados en los segmentos con cara.</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Gancho de problema tecnico relevante para el nicho (el ROI que ves esta enganando tus decisiones); estructura educativa apoyada en demo con datos y herramientas profesionales reales (autoridad/expertise); formato de mini-tutorial que ademas puede generar leads para la agencia del creador.</t>
+          <t>Gancho: negación/contraintuitivo directo ('tus anuncios no fallan por el presupuesto') que reencuadra el problema. Estructura: contraste 'los que ganan vs. los que pierden' seguido de caso real con cifras de campaña (gasto diario, gasto en 30 días, ROAS). Gatillo: urgencia/FOMO por el cambio de algoritmo, reforzado con CTA de comentario para desbloquear el video completo (mencionado en la descripción del posteo).</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
-          <t>no del todo, exige acceso a cuentas de anuncios reales con datos y una suscripcion paga a herramientas de atribucion como Triple Whale.</t>
+          <t>no del todo + nota: combina talking head con slides de motion graphics editadas, lo que exige más tiempo de edición que un video simple a cámara.</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
     </row>
     <row r="88" ht="88" customHeight="1">
       <c r="A88" s="2" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+        <v>99</v>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Dara Denney</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -8620,48 +8620,48 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="J88" s="6" t="n">
-        <v>3681</v>
+        <v>276</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@daradenney/video/7636400068785966367</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7628347207007128840</t>
         </is>
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>Dara Denney predice que los anuncios que muestran una conversación genuina (FaceTime, webinars, llamadas de coaching) van a ser la próxima tendencia creativa en Meta Ads porque son casi imposibles de imitar con IA, y presenta Riverside como herramienta para filmarlos.</t>
+          <t>Justin Lalonde explica que el KPI "tiempo hasta el lead" (time to lead) es el más importante para negocios de generación de leads, y que responder en menos de 5 minutos tras el opt-in aumenta significativamente las reservas.</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t>Esta nueva tendencia creativa va a dominar los anuncios de Meta en los próximos 90 días. Pero no les voy a mentir, es muy difícil de replicar con IA. Así que les voy a mostrar cómo Riverside puede ayudar. En el primer trimestre de 2026, las animaciones con IA, este... [?], los "hooks" (ganchos) y los anuncios de controversia eran el tipo de tendencia creativa que dominaba todos los feeds de los estrategas creativos y todas las cuentas publicitarias. Pero con este auge del contenido hecho con IA, también empezamos a ver la necesidad de eventos, de contenido largo y de conversación genuina. Mi corazonada es que los creativos publicitarios que muestran una conversación real van a ser lo próximo que haga escalar las cuentas publicitarias. Así que, obviamente, podés hacer una conversación entre dos personas en persona, o por FaceTime, o clips de un webinar online o de una llamada grupal de coaching. Vi que esto está explotando en contenido orgánico, y creo que le va a ir muy bien en anuncios porque es prácticamente imposible de falsificar. Esa va a ser la diferencia en lo que funciona, ¿no? Lo que es difícil de replicar con IA, que es la conversación genuina. Ahora, este tipo de contenido en particular es muy difícil de filmar, porque en realidad no podés grabar la pantalla de una llamada de FaceTime. Hasta probé filmar una de estas por Google Meet, que es un embole total porque solo te filma a uno de los dos a la vez. Si la hubiéramos filmado con Riverside, habría sido mucho más fácil. Cada persona se graba localmente en una pista separada en 4K, lo que significa que los problemas de wifi no van a afectar la calidad. Y si estás haciendo una llamada larga o un webinar, su edición de "magic clips" también genera clips automáticamente que podés editar fácilmente, para poder sacar contenido a la calle mucho, mucho más rápido. Así que tengo curiosidad: ¿ya probaste anuncios que muestren una conversación genuina? Comentá "Riverside" y te mando más detalles.</t>
+          <t>Si no sabés cómo generar confianza, o más específicamente, cómo lograr que tomen acción, eso va a arruinar el rendimiento de tus anuncios de Facebook. El error más grande que veo que comete la gente es que no respetan el KPI de "tiempo hasta el lead" que deberían respetar, ¿okay? Es probablemente la métrica más importante que necesitás rastrear con tu negocio de infoproductos, agencia de anuncios legal [?], o cualquier tipo de negocio de publicidad basado en generación de leads necesita rastrear el tiempo hasta el lead: cuánto tardó antes de que alguien de tu equipo se pusiera en contacto con esa persona. Okay, así que te sorprendería la cantidad de gente que hace esto mal — es como que esperan unas horas, o un día, o dos días, o esperan bastante tiempo después de que alguien se registró (opt-in) para tomar acción. Y entonces el KPI general acá es probablemente mucho más corto de lo que pensás. Así que imaginate — se supone que esto es un reloj acá — pero son 5 minutos máximo. Si podés respetar este plazo, vas a aumentar significativamente la cantidad de reservas (bookings) que conseguís.</t>
         </is>
       </c>
       <c r="O88" s="5" t="inlineStr">
         <is>
-          <t>Talking head (mujer pelirroja, sweater, micrófono inalámbrico con espuma) en un ambiente hogareño (espejo, estantería de fondo). Incluye un segmento tipo "duet"/simulación de videollamada con pantalla dividida (ventana pequeña de ella arriba, otra mujer simulando una llamada de FaceTime abajo con un globo de texto simulado) para ilustrar el concepto, y un gráfico con el logo "RIVERSIDE" superpuesto sobre la imagen. Subtítulos progresivos.</t>
+          <t>Plano vertical medio de busto, cámara fija tipo webcam, en living/oficina hogareña con planta y cuadro de fondo, micrófono de brazo visible. Subtítulos grandes bold con una palabra clave resaltada en verde. Corta a un segundo bloque en pantalla dividida con capturas de pantalla de formularios de opt-in con círculos y flechas dibujados a mano, y a un tercer bloque con notas escritas a mano en una libreta (diagrama del tiempo de respuesta).</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
-          <t>Predicción de tendencia con plazo concreto ("esto va a dominar en 90 días") combinada con tensión ("es muy difícil de replicar con IA"). Estructura de contexto de tendencias pasadas, hipótesis propia, demostración práctica del problema (dificultad de grabar un FaceTime) y solución/producto (Riverside), cerrando con un llamado a la acción interactivo en comentarios. El gatillo combina predicción de tendencia, demostración del problema real y solución concreta.</t>
+          <t>Gancho de error/miedo ("esto va a arruinar tu rendimiento en Facebook Ads"); estructura de problema → métrica desconocida → número concreto y accionable (5 minutos); gatillo de autoridad + utilidad inmediata aplicable ya.</t>
         </is>
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
-          <t>sí en el guion (predicción + problema + solución), aunque la demo tipo "duet"/simulación de videollamada exige un poco más de edición y una segunda persona.</t>
+          <t>sí, solo requiere cámara de celular/webcam, micrófono básico y notas a mano; no hay edición compleja.</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
@@ -8677,27 +8677,27 @@
     </row>
     <row r="89" ht="88" customHeight="1">
       <c r="A89" s="2" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell</t>
+          <t>BitBranding</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -8712,33 +8712,33 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="J89" s="6" t="n">
-        <v>3637</v>
+        <v>275</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@chase_chappell/video/7670568658346790174</t>
+          <t>https://www.tiktok.com/@bitbranding/video/7633975768598449439</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>Chase Chappell compara, punto por punto, cómo operan las marcas de e-commerce que facturan 100 mil dólares al mes contra las que facturan 1 millón: cantidad de anuncios activos, diversidad creativa, cadencia de lanzamiento, métricas que miran, optimización de la landing page y segmentación por buyer persona, cerrando con un llamado a comentar para recibir un lead magnet.</t>
+          <t>BitBranding analiza por qué las marcas de ropa pierden dinero con sus anuncios pese a usar IA, centrándose en la retención de hook en los primeros 3 segundos y en cómo usar Claude para generar copys de anuncios a partir de reseñas reales de clientes.</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t>Marcas de 100 mil al mes versus marcas de 1 millón de dólares al mes: acá está la diferencia. Las marcas de 100 mil al mes solo corren de 30 a 50 anuncios activos; una marca de un millón de dólares al mes corre de 300 a 750 anuncios activos. Las marcas de 100 mil al mes se enfocan en unos pocos formatos básicos, mayormente tomas de producto, videos simples y ofertas directas. Una marca de un millón al mes está corriendo cada formato que te puedas imaginar: anuncios de UGC (contenido generado por usuarios), anuncios de colaboración paga, demos de producto destacando beneficios, reseñas de clientes, comparaciones, videos del fundador, contenido educativo, antes y después, con diferentes ganchos, ángulos, creadores y ofertas. Construyen diversidad creativa en toda la cuenta publicitaria. La marca de 100 mil al mes lanza pocas creatividades por mes; la marca de un millón al mes lanza anuncios nuevos todas las semanas, a veces más de 50 creatividades nuevas por vez, porque saben que el volumen de creatividades es lo que les permite seguir escalando sin que el rendimiento caiga o sin llegar a la fatiga publicitaria. La marca de 100 mil al mes solo mira el ROI inmediato; la marca de un millón al mes está obsesionada con los ratios de [?LTV, en el original dice 'CTV'], las suscripciones, los compradores recurrentes y el AOV (valor promedio de pedido). Saben que si logran que cada cliente valga más, se pueden dar el lujo de gastar más para adquirirlo, y por eso están escalando. La marca de 100 mil al mes casi no se enfoca en la optimización de la tasa de conversión, y mandan el tráfico a una página de producto básica con la esperanza de que la gente compre; la marca de un millón al mes manda el tráfico a PDPs (páginas de producto) y landing pages para clientes totalmente desarrolladas. Responden todas las objeciones del comprador, explican el producto, muestran pruebas, ofrecen suscripciones, y hacen que la decisión de compra se sienta obvia. La marca de 100 mil al mes se enfoca en un solo avatar de cliente; la marca de un millón al mes construye anuncios para cada persona a la que le puedan llegar a vender: mamás, atletas, médicos, profesionales ocupados, gente con problemas digestivos, gente que intenta bajar de peso, gente que intenta dormir mejor. Cada persona tiene su propio gancho, creatividad, punto de dolor y oferta. Esa es la verdadera diferencia. La marca de 100 mil al mes corre anuncios; la marca de un millón al mes construye todo un sistema de creatividad y conversión. Comentá 'ads' y te mando los mejores anuncios para correr en 2027.</t>
+          <t>Acá es donde la mayoría de las marcas de ropa todavía pierden dinero, incluso con un buen prompt [?] ("grape prompt" en el original, probablemente error de reconocimiento por "great prompt"). El watch time (tiempo de visualización) de tus anuncios — Facebook lo llama el "thruplay" —, es una de las señales más importantes que usa meta [?] para decidir a quién mostrarle tus anuncios. La clave para crear anuncios que frenen el scroll en los primeros tres segundos: la retención de hook promedio está por debajo del 20%, lo que significa que literalmente el 80% de la gente se va después de unos tres a cinco segundos. Ahora, una buena retención de hook es del 30 al 40%, y los hooks atípicos (outliers) superan el 50%. Y los anuncios en la categoría de outliers reciben una distribución exponencialmente más barata de parte de meta. Okay, entonces siempre decimos, ¿qué es mejor, una foto o un video? Y normalmente digo que ambos son en realidad muy buenos. Sin embargo, si podés crear un video muy bueno, un video siempre le va a ganar a una imagen. Lo que pasa es que la mayoría de la gente no puede crear contenido en video que realmente conecte con su audiencia. Así que tomé 10 anuncios generados con IA y analicé qué pasó en los primeros tres segundos de cada uno. Dejame guiarte por los patrones acá. Los anuncios que mejor funcionaron abrían con una frase que rompía el "scroll mental" del espectador, el patrón de "scroll mental". Ejemplo: "esta buzo/hoodie me hizo llegar tarde al trabajo y no me arrepiento de nada". Suficientemente raro como para detenerte, suficientemente identificable como para hacerte seguir leyendo. Y los anuncios más fuertes usaban las palabras exactas que nuestros clientes usaban en reseñas, DMs y comentarios, no lenguaje de marketing. Okay, entonces Claude [?] (transcripto como "Cloud") sacó a la superficie ese lenguaje al instante cuando le dimos reseñas de clientes en bruto. La IA generó la segunda versión cuando le pedimos que fuera específica y humana. El tráfico frío necesita curiosidad y un llamado a la acción (call to action). Retargeting — metámonos en la locura del retargeting de meta. Técnicamente, si un anuncio se muestra más de una vez, ya es retargeting, pero podés crear contenido dirigido a alguien que está más avanzado en tu funnel versus una audiencia completamente fría. Pero el retargeting necesita urgencia y un llamado a la acción. Claude [?] produjo cinco variaciones de cada uno al instante cuando especificamos la etapa del funnel en el prompt. Solo esto redujo nuestro tiempo de creación de anuncios en un 60%.</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
         <is>
-          <t>Formato con capturas de pantalla como B-roll: Meta Ads Library de la marca AG1 con un círculo rojo dibujado sobre '~630 results', primer plano de un producto (bolsa de AG1), captura de pantalla de un checkout con planes de suscripción (NZ$), presentador en la parte inferior de cada plano hablando a cámara con micrófono, subtítulos blancos, estructura con múltiples cortes alternando entre B-roll/capturas y talking head.</t>
+          <t>Plano medio/primer plano frontal, locación con pared oscura lisa (sin fondo de living), gorra al revés. Subtítulos blancos bold centrados. Usa stickers/íconos animados superpuestos (logo de Meta con ícono de señal wifi, ícono de chip de IA con "x10"). Corta a una placa gráfica de fondo color teal con íconos ilustrados (semáforo, cerebro) y texto grande estilo poster ("needs"/"curiosity"). Edición tipo agencia/marca con identidad visual propia.</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>Gancho: comparación aspiracional con emoji de shock ('$100K vs $1M, así de diferente'). Estructura: seis comparaciones paralelas en el mismo formato (X hace esto, Y hace esto otro) que aceleran el ritmo y facilitan la retención -&gt; cierre con CTA de comentario para lead magnet. Gatillo: aspiración de escalar a $1M + FOMO + prueba con marca real y evidencia visual (AG1 en Meta Ads Library) + CTA de bajo esfuerzo que además genera engagement/alcance.</t>
+          <t>Gancho de urgencia con cifra impactante ("tenés 3 segundos... 80% se va"); estructura de mini-caso de estudio (10 anuncios analizados) con patrones concretos y ejemplo de copy real; gatillo de curiosidad + prueba social/autoridad de datos, más CTA de comentario para entregar contenido extra.</t>
         </is>
       </c>
       <c r="R89" s="5" t="inlineStr">
         <is>
-          <t>no/medio + Requiere investigación previa en Meta Ads Library y grabación de pantalla de sitios de la competencia, bastante más tiempo de preproducción que un talking head simple.</t>
+          <t>no del todo, el contenido en sí es replicable pero los stickers/íconos animados y la placa gráfica de marca requieren edición y diseño más avanzados.</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
@@ -8769,32 +8769,32 @@
     </row>
     <row r="90" ht="88" customHeight="1">
       <c r="A90" s="2" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>BitBranding</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>EE.UU.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -8804,48 +8804,48 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="J90" s="6" t="n">
-        <v>1957</v>
+        <v>274</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7625510355711642887</t>
+          <t>https://www.tiktok.com/@bitbranding/video/7658448519593725215</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>Clip promocional del episodio 1 del podcast 'Marketing MADE.' que explica el concepto de 'Entity ID' de Meta: cómo el algoritmo asigna una misma huella digital a creatividades visualmente similares, haciendo que compitan entre sí y no reciban aprendizaje fresco.</t>
+          <t>BitBranding argumenta que la forma tradicional de escalar anuncios de Facebook (duplicar campañas, apilar intereses) ya no funciona porque el algoritmo de Meta ya no necesita segmentación manual, y que la clave está en tener una oferta rentable y conocer bien los números.</t>
         </is>
       </c>
       <c r="N90" s="5" t="inlineStr">
         <is>
-          <t>Meta tiene algo que se llama Entity ID (ID de entidad). Básicamente se le asigna una huella digital (fingerprint) a tu creatividad según cómo se ve visualmente, no según cómo la nombraste ni cuántas veces la subiste a la cuenta de anuncios. Si dos anuncios se ven parecidos para el algoritmo —digamos que tienen la misma iluminación, el mismo modelo, el mismo tratamiento estético, el mismo formato— se les asigna el mismo Entity ID. Básicamente, se les asigna la misma huella digital. Y esto es lo que pasa: comparten el mismo historial de rendimiento, comparten las mismas expectativas de entrega, compiten literalmente por el mismo pool de audiencia. Y cualquier versión nueva que subas no tiene oportunidad de un aprendizaje renovado (refresh), porque en realidad ya viene prejuzgada según todo lo que aprendió de los otros anuncios que se ven parecidos.</t>
+          <t>Estás escalando tus anuncios de Facebook mal, y puedo probarlo. La mayoría de las marcas de ropa que están escalando anuncios ahora mismo lo hacen duplicando campañas, tocando presupuestos, probando nuevas audiencias, y cada una de esas acciones te está costando dinero. Los gurús en internet están enseñando un sistema que funcionaba hace tres años, hace cinco años: duplicá el ad set, probá en amplio (broad), escalá el ganador, corré una campaña de testeo, y si no funciona, debe ser tu creativo. No — el problema es el método. Meta ya no necesita que le digas quién es tu cliente. El algoritmo de Meta es más inteligente que cualquier stack de intereses [?] ("Interstac" en el original) que vayas a armar. Lo que Meta necesita de vos es una oferta rentable y paciencia. Quienes puedan gastar más para adquirir un cliente siempre van a ganar — creo que es una cita de Dan Kennedy —, que básicamente dice que si conocés tan bien tus números que podés gastar más que tus competidores para adquirir un cliente, vas a conseguir ese cliente. Y mientras puedas hacerlo de forma rentable a largo plazo, vas a seguir ganando. Pero solo podés gastar más cuando realmente conocés esos números. Y ahí es donde empezamos.</t>
         </is>
       </c>
       <c r="O90" s="5" t="inlineStr">
         <is>
-          <t>Formato podcast con talking head, fondo de estudio con paneles geométricos iluminados en rosa/púrpura/azul, micrófono de brazo visible en primer plano, plano medio, sin subtítulos visibles en los frames capturados. Estética mucho más elaborada que los otros videos de la misma cuenta, que suelen usar fondo liso.</t>
+          <t>Plano medio frontal en el mismo fondo oscuro liso, gorra al revés y anteojos. Subtítulos bold blancos. Incluye una transición con motion blur/barras naranjas estilo glitch entre tomas, y una placa de texto grande sobre fondo teal oscuro ("KNOW THOSE NUMBERS") a modo de énfasis.</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q90" s="5" t="inlineStr">
         <is>
-          <t>Gancho de concepto técnico poco conocido ("Entity ID") que promete revelar cómo funciona realmente el algoritmo de Meta, apelando a la curiosidad de anunciantes avanzados, en formato de fragmento de podcast que también sirve de promoción cruzada de contenido nuevo de la marca.</t>
+          <t>Gancho contrarian/polémico ("lo estás haciendo mal y puedo probarlo") que ataca la sabiduría convencional de "gurús"; estructura mito vs. verdad con cita de autoridad (Dan Kennedy); gatillo de disonancia cognitiva + promesa de método superior.</t>
         </is>
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
-          <t>no, nota: requiere un set de podcast con iluminación de color y equipo de grabación dedicado, más costoso que los videos de un solo plano con fondo liso de la misma cuenta.</t>
+          <t>sí, el formato es talking head con cortes/transición simple y una placa de texto, alcanzable con un editor de video básico.</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
@@ -8861,32 +8861,32 @@
     </row>
     <row r="91" ht="88" customHeight="1">
       <c r="A91" s="2" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
+        <v>59</v>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
         <is>
           <t>Venta del servicio</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Media</t>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>MADE Marketing (Maddi)</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -8896,48 +8896,48 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="J91" s="6" t="n">
-        <v>1338</v>
+        <v>269</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@madecreativeco/video/7641559635861736712</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7637927133989440775</t>
         </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>Maddi (MADE Marketing) muestra su proceso al incorporar una nueva marca de 2 millones de dólares mensuales a la agencia, explicando el documento de research que usa para auditar los anuncios ganadores y armar el calendario creativo antes de tocar la cuenta publicitaria.</t>
+          <t>Justin Lalonde cuenta el caso de un evento en vivo que generó más de $2 millones en 24 horas gracias a anuncios de Facebook que llenaron la sala, desglosando asistentes, tasa de cierre y costos del evento.</t>
         </is>
       </c>
       <c r="N91" s="5" t="inlineStr">
         <is>
-          <t>Estoy trabajando en un flujo de trabajo creativo para una marca que factura 2 millones de dólares al mes, y pensé en mostrarles detrás de cámaras cómo empieza el proceso. Esta marca básicamente contrató a MADE, o a mí, para ser la conexión entre su equipo creativo interno y también su agencia de compra de medios. Entonces, aunque nosotros también hacemos la compra de medios, a veces las marcas nos contratan más como estrategas creativos fraccionales o servicios de CMO fraccional para cerrar las brechas entre, eh, los equipos internos y externos. Entonces mi trabajo es mejorar el flujo de trabajo creativo y ponerlo en marcha, también mejorar los resultados de su creatividad y ayudar donde sea posible a mejorar los resultados de la compra de medios. Entonces lo primero que hago es completar este documento que repasa los últimos 30 días: cuáles son sus anuncios ganadores y sus potenciales, como ganadores o algo así como sus ganadores, y lo que esto me ayuda a identificar son básicamente las cosas centrales que estoy viendo, o sea, los públicos objetivo (personas), los gatillos emocionales, qué tipo de contenido es. ¿Son solo estáticos o videos? ¿Es un solo estilo de creativo publicitario? ¿Cuál es la estructura? ¿Cuál es el tipo de producción? Y después entro obviamente en los resultados acá, que en realidad no les voy a mostrar porque ahí tenemos resultados, pero miro obviamente el CPA, el ROAS [?], el hook, el hold, el CTR saliente (outbound), los insights de frecuencia, y cuáles creo que serían los próximos pasos lógicos. Después empiezo a armar como un flujo semanal de cómo se vería con los equipos en términos de lunes a viernes, y entonces, ¿cuál es mi primer objetivo para esta clienta? Vamos a empezar con 10 creativos nuevos como mínimo por semana, y lo fui desglosando en: bueno, ¿cómo se verían las iteraciones? ¿Cuántas iteraciones quiero tener y cuántos conceptos completamente nuevos? Y voy desglosando esto, eh, por personas o tipos de producto, y después empiezo a mapear esto en un calendario. Ahora, obviamente mis iteraciones acá van a ser un poco más reactivas, pero me gusta tener mis iteraciones planeadas con al menos 2 semanas de anticipación, y después mi plan mensual queda totalmente definido en términos de mis conceptos completamente nuevos, en base a mi investigación de lo que está funcionando, eh, o lo que no está funcionando, y qué oportunidades puedo ver en las personas, pero también en el producto. También tengo esta especie de Matriz de Personas, que básicamente me dice cuáles creo que son las más fuertes para enfocarme, eh, así como cuáles pilares de contenido son nuestra prioridad, porque no los tenemos en la cuenta en este momento. Ahora, llevo trabajando con esta marca 3 semanas y todavía ni toqué un anuncio, porque esta parte es tan importante para realmente entender la cuenta publicitaria y empezar a mapear tu cadencia semanal, para que puedas tener éxito con tu testeo creativo.</t>
+          <t>Ahora tuve la oportunidad de asociarme con varios eventos locales y masterminds, todos los cuales tenían varios miles de personas en asistencia, gracias al poder de los anuncios de Facebook. Ahora estamos hablando de salas que recaudaron y vendieron más de dos millones de dólares en 24 horas, solo de la gente presente. En la sala misma, unas 900 personas presentes, más o menos [?] ("gave retake" en el original, probablemente "give or take"). Nuestro cliente terminó ofreciendo un producto de $10,000 que tiene. De esa sala, cerca del 20%, más o menos [?], convirtieron un poco más. Así que estos son los números reales: 217 personas terminaron cerrando esta oferta de $10,000, lo cual son $2.17 millones, sumado a los casi medio millón de dólares en venta de entradas. Ahora, en total costó — cuando digo "nosotros" me refiero a nuestro cliente — cerca de medio millón de dólares en gasto publicitario, más el equipo del evento y material, etcétera. Entonces el costo del evento fue de cerca de medio millón de dólares para organizar y montar este evento y llenar la sala, para después vender. Si contás la venta de entradas, cerca de 2.5 a 2.6 millones de dólares en productos vendidos durante este evento. Así que, de nuevo, un evento muy rentable visto de esa manera.</t>
         </is>
       </c>
       <c r="O91" s="5" t="inlineStr">
         <is>
-          <t>Talking head en oficina (pared de vidrio, escritorio, monitor de computadora) intercalado con capturas de pantalla grabadas de una hoja de cálculo de Google Sheets (el documento de flujo de trabajo creativo), con zoom y el dedo señalando celdas. Subtítulo grande en negrita en la intro; sin cortes de cámara adicionales, formato 'screen recording' + presentadora hablando.</t>
+          <t>Plano medio de busto, webcam fija en el mismo living/oficina con planta y cuadro, micrófono de brazo. Subtítulos blancos simples. Un breve inserto gráfico de ícono de perfil con notificación en rojo ("705") sobre fondo negro, posiblemente a modo de intro. Edición mínima, sin gráficos de datos pese a hablar de cifras.</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>Gancho: cifra grande y exclusiva ('marca de 2 millones de dólares al mes') más promesa de contenido 'detrás de escena'. Estructura: proceso paso a paso mostrando el documento real de auditoría creativa y el armado del calendario. Gatillo: autoridad/prueba social y curiosidad por ver documentos internos reales de una agencia que trabaja con marcas grandes.</t>
+          <t>Gancho de resultado extremo y concreto ("$2 millones en 24 horas"); estructura de desglose numérico paso a paso que aporta credibilidad; gatillo de aspiración/prueba social con caso real de cliente.</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr">
         <is>
-          <t>sí + nota: solo requiere grabar la pantalla de una hoja de cálculo propia y hablar a cámara, sin edición avanzada.</t>
+          <t>sí, solo cámara y micrófono, historia y cifras propias; casi sin edición.</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
@@ -8953,32 +8953,32 @@
     </row>
     <row r="92" ht="88" customHeight="1">
       <c r="A92" s="2" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -8988,33 +8988,33 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J92" s="6" t="n">
-        <v>845</v>
+        <v>261</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7669060115953192194</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7642454739313102098</t>
         </is>
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath compara la estrategia de marketing de Olipop contra la de Poppi (competidoras de soda prebiótica): cantidad de anuncios activos, oferta, colaboraciones de marca y experiencia de compra en el sitio web, concluyendo que Olipop convierte mejor y Poppi conecta mejor culturalmente.</t>
+          <t>Justin Lalonde explica que Meta lanzó su propio servidor MCP oficial para conectar cuentas de anuncios con IA (como Claude) de forma segura, y muestra paso a paso cómo instalarlo y usarlo para modificar presupuestos por chat.</t>
         </is>
       </c>
       <c r="N92" s="5" t="inlineStr">
         <is>
-          <t>¿Quién es mejor en marketing, Poppy u Olipop? Bueno, Olipop está corriendo 40 anuncios de Meta con imágenes centradas en el producto y videos centrados en los beneficios. Y lo particular es que crearon su propio jingle que usan en los anuncios, lo cual es bastante interesante. Lo que les falta es una oferta fuerte que empuje a la gente a comprar. Ahora comparemos eso con Poppy, que está corriendo 180 anuncios de Meta. Destacan ofertas interesantes de entrada. Poppy también se está apoyando fuerte en su colaboración reciente con Love Island, lo que hace que se sientan más como una marca dentro de la cultura. Y mirando el sitio web de Poppy, es hermoso. Abre con ofertas y una variedad de productos. Pero su menú de tienda es torpe y no empujan combos de venta directa al consumidor, una oportunidad enorme desperdiciada. Mientras tanto, el sitio web de Olipop sí empuja combos DTC (venta directa al consumidor) y empuja suscripciones, y las empuja de inmediato. Su página de producto está diseñada para reducir la fricción e impulsar más ventas. Mucho mejor. Olipop es la máquina de DTC mejor construida. Entonces tienen un sitio web más ajustado, un empuje de suscripciones [?] más fuerte, una creatividad más consistente. Poppy es la mejor marca cultural: una operación publicitaria más grande, alianzas más audaces, un posicionamiento de estilo de vida más profundo. Entonces Olipop te muestra cómo convertir. Poppy te muestra cómo importar (tener relevancia cultural). Las mejores marcas DTC hacen ambas cosas.</t>
+          <t>Ha habido muchos reportes en el ambiente sobre perfiles de Facebook que quedaron completamente eliminados/baneados [?] ("nuked" en el original) por conectar un MCP a sus cuentas de anuncios. Eso era antes — ahora Meta lanzó oficialmente su propio servidor MCP, permitiéndote conectar tus cuentas de anuncios de forma segura con herramientas como Claude. Lo que vas a hacer es descargar Claude Desktop. Después vas a ir a la esquina inferior izquierda y hacer clic en configuración (settings). Después vas a ir a conectores (connectors). Desde ahí vas a hacer clic en "agregar un conector personalizado" (add a custom connector). Le vas a poner de nombre "meta ads" acá. Ahora, este es el único MCP oficial de Meta. Okay, entonces una vez que lo tengas puesto, podés simplemente hacer clic en "agregar". Como podés ver, una vez agregado vas a ver el ícono de Facebook y ahora vas a tener un botón que dice "conectar" (connect). Así que vamos a hacer clic en eso, y ahí se va a abrir tu perfil de Facebook. Te va a preguntar si sos la persona correcta. Decís que sí. Ahora te va a preguntar si querés otorgar [?] ("often" en el original, probablemente "grant") acceso a todos los negocios actuales y futuros, o solo a los negocios actuales. Yo voy a elegir "todos los actuales y futuros" para efectos de este video. Después vas a darle a continuar, y ahí vamos a hacer clic en guardar acá. Ahora nos aparece una pantalla de éxito, y listo. Ya tenemos nuestro configurador de meta ads. Desde el punto de vista de reportes y preguntas, en mi experiencia es en realidad un MCP muy sólido. Acá hay otra cosa que podés hacer con este MCP: por ejemplo, le dije "che, quiero que aumentes el gasto publicitario del ad set dcd32 en $2 extra por día, dado que esta es una campaña ABO [?]" ("adio" en el original). Entonces me dijo "confirmación rápida: este ad set acá, el presupuesto actualmente es de 1875 por día, lo voy a poner en 2075 por día. La cuenta de anuncios es esta, y el ID del ad set es este. Por favor confirmá." Y yo le dije que sí, y listo — "hecho, dcd32 ahora está en 2075 por día".</t>
         </is>
       </c>
       <c r="O92" s="5" t="inlineStr">
         <is>
-          <t>Imágenes de producto compuestas: presentador sosteniendo dos latas de Olipop contra fondo turquesa tipo estudio/croma, luego un vaso de Poppi con fondo de playa y sello 'Limited Edition Love Island', luego captura de pantalla del sitio web de Olipop con sus sabores, presentador siempre en la mitad inferior del cuadro hablando a cámara, subtítulos blancos, múltiples cortes entre gráficos/fotos de producto y talking head.</t>
+          <t>Plano medio, presentador con blazer, iluminación más cálida/producida que otros videos del mismo canal. Subtítulos bold. Gran parte del video es grabación de pantalla (screen recording) de Mac mostrando la app de Claude Desktop: configuración, conectores, y luego el chat con la confirmación de cambio de presupuesto del MCP de Meta, en formato pantalla dividida.</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="Q92" s="5" t="inlineStr">
         <is>
-          <t>Gancho: pregunta de opinión/rivalidad entre dos marcas conocidas ('¿quién es mejor?'). Estructura: comparación punto por punto (anuncios, oferta, colaboraciones, sitio web) con evidencia visual real (capturas, fotos de producto) -&gt; síntesis final memorable ('uno muestra cómo convertir, el otro cómo importar'). Gatillo: rivalidad/curiosidad + caso de estudio de marcas reales reconocibles + conclusión citable.</t>
+          <t>Gancho de miedo/alerta ("Facebook está baneando cuentas") que capitaliza un tema de actualidad (bans por MCP no oficiales); estructura tutorial paso a paso con capturas reales; gatillo de urgencia + utilidad práctica inmediata sobre una herramienta nueva de IA aplicada a ads.</t>
         </is>
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
-          <t>no/medio + Requiere fondo tipo croma/compuesto, fotos de producto de calidad y capturas de sitios de la competencia, más trabajo de edición que el resto del lote.</t>
+          <t>sí, requiere grabación de pantalla (gratis con herramientas nativas) y narración; sin equipo especial más allá del que ya usa el canal.</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
@@ -9045,32 +9045,32 @@
     </row>
     <row r="93" ht="88" customHeight="1">
       <c r="A93" s="2" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E93" s="11" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -9080,48 +9080,48 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="J93" s="6" t="n">
-        <v>832</v>
+        <v>260</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7648656606674062614</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7644680332192533778</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath, filmado en un evento de Meta en Silicon Valley, explica en lenguaje simple terminos tecnicos de publicidad: ROAS, incrementalidad, CPM, CTR, CPC, retargeting, CAC y AOV.</t>
+          <t>Justin Lalonde muestra casos de uso reales del MCP de Meta con Claude: pedir resúmenes de campañas activas, marcar ad sets que superan un umbral de gasto/costo por resultado, y recibir recomendaciones de qué ad sets escalar según 30 días de datos.</t>
         </is>
       </c>
       <c r="N93" s="5" t="inlineStr">
         <is>
-          <t>Meta me llevo a Silicon Valley y acabo de estar en una sala con mas de 1.000 anunciantes que gastan decenas de miles de millones en anuncios de Meta cada ano. Escuche mucha jerga, asi que hoy te la voy a desglosar y explicar que significa en realidad. Empecemos con ROAS, que es retorno sobre la inversion publicitaria (return on ad spend), y eso simplemente mide lo que gastaste en anuncios versus lo que recuperaste. La incrementalidad mide lo que tus anuncios generaron para tu negocio que no hubieras conseguido si no hubieras estado corriendo anuncios en primer lugar. La incrementalidad es el 'uplift' (el aumento incremental). El CPM [?, transcripto como 'Ppm', probable error de reconocimiento], que es el costo por mil impresiones. Es la metrica que se usa tipicamente para medir el costo de la publicidad. Si quisieras comparar plataformas publicitarias o distintas ubicaciones, usarias el CPM. CTR significa tasa de clics (click through rate), que mide el porcentaje de gente que hizo clic en tu anuncio versus la gente que lo vio. Para anuncios de Meta, una buena tasa de clics normalmente seria algo por encima del 1%. Si superas el 2%, normalmente estas haciendo un trabajo muy bueno. CPC significa costo por clic y mide simplemente cuanto estas pagando por cada clic en tu anuncio. Retargeting es poner anuncios frente a personas que ya interactuaron con tu negocio: pueden ser personas que visitaron tu sitio web, personas en una lista de email, incluso personas que te compraron anteriormente. CAC significa costo de adquisicion de cliente (cost to acquire a customer). Una de las metricas mas importantes en publicidad paga, honestamente, en todo el marketing, es el AOV, que es el valor promedio de la orden (average order value). Cuando la gente entra a tu sitio web y compra. Cuanto mas alto el AOV, mejor.</t>
+          <t>Recientemente mostré en el canal cómo conectar Claude a tu cuenta de anuncios de Meta usando su MCP. Ahora, en este video quiero mostrarte exactamente qué podés hacer con él, en distintos casos de uso de este nuevo MCP. Uno de los primeros formatos (prompts) que quiero compartir con vos es el siguiente: "Dame un resumen de 7 días [?]" ("70 summary" en el original) "de todas mis campañas activas, marcá cualquiera que esté gastando más de X con [CPR/ROAS ?] por debajo de Y" — podés cambiar eso según el tipo de cuenta. En este caso, lo que voy a hacer es ir específicamente por esta campaña. Así que voy a copiar el nombre de esta campaña y voy a decir "marcá cualquier cosa que gaste más de $150 con costo por resultado, digamos, por encima de un tercio, en esta campaña". Y esto es lo que me dio: "Okay, genial, revisé cada cuenta de anuncios o campaña de anuncios que tenés dentro de esta cuenta para campañas activas, este es el monto de gasto, acá están los resultados generales por campaña". Decía algo así como "mirá, hay un ad set que efectivamente supera ambos umbrales acá, gastó $144, que está cerca de tu límite de 150 — no estoy seguro por qué lo mencioné pero bueno, es lo suficientemente cerca —, el costo por resultado es de 130 o más. Hay este que tiene un resultado a 144. Así que este es el único outlier que tenés acá". Ahora, lo que podría hacer desde ahí es simplemente decir "che, apagá DCT 70 J" — que ya había sido apagado. Ahora, el siguiente prompt que le di a este Claude [?] ("clot" en el original) con el que estoy conversando en el hilo es "mostrame los anuncios que hayan alcanzado mi objetivo de costo por resultado de $100 durante siete días consecutivos dentro de mi campaña de team schedules, y recomendame cuáles escalar y cuánto". Y me dijo, "bueno, en realidad todavía no llegaste a eso". Aun así, me dio un análisis de costo por resultado de 30 días acá. Así que se fue un poco más atrás para darme cuáles ad sets habían tenido el mejor rendimiento ahí — como cuántos días tuvieron conversiones en este ciclo de 30 días. Entonces acá decía algo como "si yo fuera vos, escalaría DCT 64 J; DCT 32 va a ser el segundo que más escalaría acá; después DCT 70, DCT 24 y después DCT 84 acá".</t>
         </is>
       </c>
       <c r="O93" s="5" t="inlineStr">
         <is>
-          <t>Arranca con metraje real del escenario de una conferencia de Meta (pantalla gigante con el mensaje 'Ushering in the next era of shoppable experiences', panel de oradoras) para dar contexto y autoridad; despues corta a Ben hablando a camara al aire libre en el predio del evento, con la credencial/lanyard visible y remera roja; subtitulos en mayusculas siguen palabra por palabra lo que dice.</t>
+          <t>Plano medio de busto, cabello rizado, mismo tipo de setup cálido del canal. Subtítulos bold. Pantalla dividida extensa con capturas de las respuestas de texto de Claude (tablas de resumen de campañas de 7 días, análisis de costo por resultado a 30 días con recomendaciones de escalado). Formato tutorial denso en texto/datos.</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>alto</t>
         </is>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Gancho de autoridad y exclusividad ('Meta flew me out to Silicon Valley... 1,000 advertisers that spend tens of billions'); estructura de diccionario/glosario facil de seguir y de guardar ('save this'); gatillo educativo que resuelve confusion de jerga para audiencia principiante e intermedia.</t>
+          <t>Gancho de continuidad de serie ("ya mostré cómo conectar... ahora te muestro qué hacer con esto"); estructura de casos de uso concretos con prompts copiables y resultados reales mostrados en pantalla; gatillo de utilidad práctica + demostración de ahorro de tiempo/dinero.</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr">
         <is>
-          <t>no del todo, depende de haber sido invitado a un evento real de Meta para el gancho de autoridad, aunque el glosario en si se podria grabar en cualquier lado.</t>
+          <t>sí, mismo requisito que el video anterior: grabación de pantalla del chat de IA más narración, reproducible por cualquiera con acceso al MCP.</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
@@ -9137,32 +9137,32 @@
     </row>
     <row r="94" ht="88" customHeight="1">
       <c r="A94" s="2" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+        <v>62</v>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Mary-Anne Da'Marzo</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -9172,48 +9172,48 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="J94" s="6" t="n">
-        <v>748</v>
+        <v>256</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@maryannedamarzo/video/7669759222082440470</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7636521756043250952</t>
         </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>Un video de motion graphics que plantea si se puede reemplazar todo el sistema de Meta ads con IA, mostrando en 4 pasos cómo conectar Claude a la cuenta de Meta Ads para analizar resultados, diagnosticar problemas y generar nuevas variantes creativas.</t>
+          <t>Justin Lalonde presenta un método para crear ángulos de anuncios de Facebook a partir de investigación de datos propios y de mercado, transformando patrones de clientes en declaraciones de deseo ("quiero...") y ejemplificándolo con un producto de salud cardíaca.</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t>¿Es posible reemplazar todo tu sistema de meta ads con IA? Lo probé con Claude y la nueva alianza de Meta recientemente. Así es como funciona. Paso 1: conectar Claude. Meta ahora le permite a Claude conectarse directamente a tu cuenta de meta ads usando conectores de IA. Paso 2: extraer insights. Pedile a Claude que analice el ROAS, las tasas de clics (CTR), el costo por impresión, y las tendencias de conversión en todas las campañas automáticamente. Paso 3: diagnosticar los problemas. Claude identifica gasto desperdiciado, creativos débiles, picos de frecuencia, y problemas de entrega en segundos. Paso 4: generar campañas. Puede duplicar los recursos ganadores y crear nuevas variaciones creativas de testeo automáticamente. La IA acelera la ejecución masivamente, pero la estrategia y el posicionamiento son tan importantes. Si le acertás a esa parte, podés escalar con IA muy bien. Seguime para más contenido educativo de IA y marketing de e-commerce.</t>
+          <t>Quiero mostrarte una nueva forma de crear ángulos de anuncios para Facebook. Podés investigar datos propios (own data) o datos de mercado (market data). Los datos propios serían cualquier cosa que le pertenezca a tu negocio: reseñas de clientes, el administrador de anuncios (ads manager) — ahí revisás cualquier anuncio anterior que hayas corrido, cuál fue su rendimiento —, revisás encuestas post-compra, comentarios en redes sociales. Datos de mercado es cuando revisás las reseñas de tus competidores en su sitio web, en Amazon. Pero lo que eventualmente querés hacer es transformar estos patrones en declaraciones de "quiero" (I want to). "Quiero saber que mi corazón está realmente sano." Acá agregás un par de razones, "para poder..." ("so I can"). ¿Cuál es la verdadera razón por la que alguien quiere tener un corazón sano? Bueno, a partir de ahí, quieren prevenir un ataque cardíaco repentino. ¿Por qué? Bueno, quieren prevenir un ataque cardíaco para poder seguir manteniendo a su familia. ¿Por qué? Para poder cumplir su propósito como protector. Entonces es como ir cada vez más profundo — es como pelar una cebolla. ¿Cómo se ve transformar este deseo en un ángulo de anuncio? Hay un montón de formas en las que este deseo se puede manifestar. "La promesa de la graduación": un padre mira a su hija pequeña en la obra de teatro de la escuela primaria, que se imagina hacia adelante [?] ("Ford" en el original, probablemente "forward") hasta su graduación universitaria, con voz en off: "¿Vas a estar ahí para sus grandes momentos? Nuestro escaneo cardíaco con IA ayuda a asegurar que sí." "La rutina matutina": un ejecutivo de unos 50 años haciendo su rutina matutina, despidiéndose de su esposa con un beso, etcétera, agarrando su portafolio, ajustándose la corbata. Después se muestran los resultados de su escaneo cardíaco en el teléfono, dándole la confianza para enfrentar otro día. "Tranquilidad en solo 15 minutos." "El constructor de legado": un dueño de negocio trabajando hasta tarde, mirando fotos de las familias de sus empleados en su escritorio. "Ahora es solo tu familia la que cuenta contigo. Conocé el estado de salud de tu corazón hoy." Los deseos de mercado masivo son un primer paso para poder crear un anuncio. Mucha gente se queda ahí y después sufre el síndrome de la página en blanco.</t>
         </is>
       </c>
       <c r="O94" s="5" t="inlineStr">
         <is>
-          <t>Fondo de color sólido violeta/azul editado en post-producción (no es una locación real/cámara fija), con estructura de 'pasos' numerados. Se superponen capturas de pantalla (logo de Meta Ads con flecha hacia el logo de Claude, un chat de Claude, un documento tipo Notion con copy de anuncio) y textos grandes en tipografía animada tipo motion graphics ('TRENDS', 'NEW CREATIVE') que remarcan cada paso. La presentadora aparece en la parte inferior del cuadro con blazer blanco y micrófono, formato mitad gráfico/mitad presentadora, sin locación física visible.</t>
+          <t>Plano medio de busto en el mismo setup casero con planta y cuadro de fondo. Subtítulos bold. Pantalla dividida con gráficos tipo diagrama de flujo y tablas (aparentemente de un documento o presentación) que enumeran el proceso de investigación y ejemplos de ángulos de anuncio con guiones escritos; el gráfico llega a mostrar un cuarto ángulo ("The Weekend Dad") que no se alcanza a narrar en el tramo de transcript disponible.</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q94" s="5" t="inlineStr">
         <is>
-          <t>Gancho: pregunta directa sobre una tendencia de actualidad (IA + Meta ads, alianza nueva con Claude). Estructura: framework claro en 4 pasos numerados, fácil de seguir en un video corto (49 seg). Gatillo: curiosidad/FOMO tecnológico por una herramienta nueva, reforzado por la autoridad de quien dice haberlo probado ella misma.</t>
+          <t>Gancho de promesa de método nuevo; estructura de framework paso a paso (datos propios/mercado → declaraciones de deseo → ángulos) con ejemplo aplicado completo; gatillo de utilidad + curiosidad por ver el marco aplicado a un caso real.</t>
         </is>
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
-          <t>sí, con nota: requiere edición de motion graphics (fondo de color, overlays animados, capturas de pantalla) con una app gratuita tipo CapCut; exige más tiempo de edición que un talking head simple, pero no equipo profesional.</t>
+          <t>sí, necesita armar un documento o slide con el framework, sin herramientas costosas.</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
@@ -9229,32 +9229,32 @@
     </row>
     <row r="95" ht="88" customHeight="1">
       <c r="A95" s="2" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -9264,48 +9264,48 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="J95" s="6" t="n">
-        <v>715</v>
+        <v>250</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7665700523940629782</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7665463418513673479</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath argumenta que la mayoria de las cuentas de anuncios que fallan no tienen un problema creativo sino un problema de oferta, y explica que auditar (precio, garantia, propuesta de valor, urgencia) antes de tocar los anuncios.</t>
+          <t>Justin Lalonde recomienda usar funciones de investigación profunda de IA (Claude, Gemini, GPT, Perplexity, Manus) para escanear Reddit, comentarios de YouTube y bibliotecas de anuncios de competidores y así nunca quedarse sin ángulos de anuncios nuevos.</t>
         </is>
       </c>
       <c r="N95" s="5" t="inlineStr">
         <is>
-          <t>'Probamos un monton de anuncios distintos. Ninguno funciona. Meta simplemente no funciona para nuestro negocio.' Antes de dar el briefing creativo, auditamos la oferta. ¿El precio es competitivo? ¿La reversion de riesgo es lo suficientemente fuerte? ¿La propuesta de valor es lo suficientemente clara en menos de 5 segundos? Una creatividad debil puede ocultar una oferta fuerte. Una creatividad fuerte no puede salvar una oferta debil. La mayoria de las cuentas de anuncios que fracasan no fracasan por los anuncios. Fracasan porque la oferta no es lo suficientemente buena. Una gran oferta casi se vende sola. El anuncio solo necesita comunicarla con claridad. Cuando miramos una cuenta de anuncios nueva, miramos la oferta antes de mirar la estructura de la cuenta. ¿Cual es la garantia? ¿Cual es la friccion para comprar? ¿Hay una razon convincente para comprar hoy en vez de despues? Un descuento del 20% no es una gran oferta. Una gran oferta es un intercambio de valor completo que hace que la decision se sienta obvia (no brainer). Vimos cuentas mas que duplicar sus ingresos no cambiando un solo anuncio, sino reestructurando la oferta, agregando un bono, ajustando una garantia, creando urgencia real en vez de fabricada. Arregla la oferta primero.</t>
+          <t>[el transcript comienza abruptamente, posible corte al inicio del clip, ver nota] ...ángulos, vas a tener que inventar ángulos nuevos cada semana. Normalmente vas a poder encontrar una porción importante de ángulos de anuncios solo con hacer este ejercicio muy simple. Y honestamente, hoy en día, algunas de las mejores formas de encontrar ángulos es usar investigación con IA. Podés ir a Claude, a Gemini, a GPT, Perplexity [?] ("Proplexity" en el original), Manus, y cada uno de estos modelos típicamente tiene una función de investigación profunda (deep research) o alguna variación, que te permite rastrear la web en busca de información específica. Y le podés preguntar: "mirá, tengo este producto. Este es mi nivel de conciencia (awareness level). Este es mi deseo. Esta es mi sofisticación de mercado. Me estoy quedando sin ángulos de anuncios. Estos son los distintos ángulos de anuncios que ya encontré. Quiero que investigues en Reddit, comentarios de YouTube, bibliotecas de anuncios de la competencia. Y a partir de eso, necesito que me ayudes a armar una lista de ángulos de anuncios completamente nuevos que todavía no haya probado."</t>
         </is>
       </c>
       <c r="O95" s="5" t="inlineStr">
         <is>
-          <t>Efecto visual de 'triple clon': el mismo presentador aparece tres veces sentado en el mismo sillon, con remeras de distinto color (roja, gris, verde) y etiquetas 'BEGINNER', 'INTERMEDIATE', 'EXPERT' sobre cada uno; interior luminoso tipo living moderno con planta y cuadro; subtitulos en blanco siguen el audio.</t>
+          <t>Plano medio de busto, mismo living/oficina, sin gráficos superpuestos en los frames revisados (1, 3 y 5) — solo subtítulos bold blancos sobre el video. Formato más simple y directo, sin cortes a pantallas ni inserts visibles en esos frames.</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>bajo</t>
         </is>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Gancho visual de patron interrumpido (verse triplicado) que detiene el scroll antes de escuchar una palabra; gancho verbal contraintuitivo ('no tienen un problema creativo, tienen un problema de oferta'); estructura de framework de auditoria con checklist accionable y prueba social (cuentas que duplicaron ingresos); gatillo de autoridad mas curiosidad.</t>
+          <t>Gancho directo de solución a un problema recurrente (quedarse sin ángulos); estructura breve de tip único y accionable (usar deep research de varias IAs); gatillo de utilidad inmediata y bajo esfuerzo de consumo, video de solo 54 segundos.</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr">
         <is>
-          <t>no del todo, el efecto de clonarse en video requiere camara fija y edicion para alinear las tres tomas (o una app especifica); el contenido en si es replicable sin el efecto.</t>
+          <t>sí, es el más simple del lote: solo cámara y un tip hablado, sin gráficos ni edición extra.</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
@@ -9321,32 +9321,32 @@
     </row>
     <row r="96" ht="88" customHeight="1">
       <c r="A96" s="2" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Ben Heath</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -9356,33 +9356,33 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="J96" s="6" t="n">
-        <v>382</v>
+        <v>249</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@benheathmarketing/video/7644916873481555202</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7661753639463177490</t>
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
-          <t>Segunda pieza del glosario de Ben Heath grabado en el evento de Meta en Silicon Valley (marcado como Parte 1 en pantalla): explica reach, impresiones, tasa de conversion, audiencias similares (lookalike), el pixel de Meta y UGC.</t>
+          <t>Justin Lalonde explica el concepto de sofisticación de mercado (5 niveles) y cómo determina qué tipo de oferta y mensaje publicitario en frío conviene usar, usando su propia agencia de Facebook ads para HVAC y el mercado de IA como ejemplos.</t>
         </is>
       </c>
       <c r="N96" s="5" t="inlineStr">
         <is>
-          <t>Meta me llevo a Silicon Valley y acabo de estar en una sala con mas de mil anunciantes que gastan decenas de miles de millones en anuncios de Meta cada ano. Escuche mucha jerga, asi que hoy te la voy a desglosar y explicar que significa en realidad. Reach (alcance) es simplemente a cuanta gente se le mostraron tus anuncios. Impresiones es cuantas veces se vieron tus anuncios. Es distinto del alcance porque la misma persona puede ver tus anuncios multiples veces. La tasa de conversion tipicamente se refiere al porcentaje de gente que convirtio despues de hacer clic en uno de tus anuncios. Audiencia similar (Lookalike Audience), que es un grupo de personas muy parecidas a otro grupo de personas. Subis una lista de clientes a Meta y le decis 'creame una audiencia similar'. Meta va a analizar los datos y va a crear una audiencia de personas parecidas a ellos, a las que quizas quieras apuntar. El Pixel de Meta, que es un codigo que pones en tu sitio web que te permite rastrear las acciones que hace la gente despues de hacer clic en tu anuncio, asi podes ver que paginas miraron, si compraron o se convirtieron en lead. Esa informacion se retroalimenta a tu cuenta de anuncios de Meta, lo que permite que tus campanas optimicen correctamente y consigas mas de las acciones que queres conseguir. UGC, que es contenido generado por el usuario, es cuando la gente explica su experiencia con un producto o servicio, hace recomendaciones, demuestra las caracteristicas. Mi version favorita de UGC es trabajar con creadores e influencers. Su poder para detener el scroll realmente ayuda a mejorar el rendimiento, y ademas su recomendacion tiene peso, asi que las tasas de conversion tambien son mas altas.</t>
+          <t>Tu sofisticación de mercado va a dictar el tipo de oferta y también el tipo de anuncio que vas a querer hacer con tu cuenta de anuncios de Facebook. Si ignorás completamente este concepto, esto podría ser la diferencia entre una cuenta que escala o que fracasa. ¿Cuántas otras empresas similares a la tuya ya lanzaron productos similares, o intentaron resolver problemas similares a los tuyos, o hicieron ofertas similares al mismo mercado al que estás intentando apuntar ahora mismo? Por lo tanto, esto dicta qué tipo de ofertas o posicionamiento vas a querer tomar con tu negocio. Como vas a ver, nivel uno: nacimiento de un mercado, simplemente hacé cualquier afirmación (claim). Podés decir cualquier cosa. Y voy a armar un ejemplo con vos a lo largo de este video. Entonces, el nivel uno acá va a ser — y voy a usar mi agencia como ejemplo. Vamos al nivel uno. Y lo que voy a decir es "llevo campañas de Facebook ads", como ejemplo, voy a inventar un ejemplo acá, "para negocios de HVAC (climatización)". Bien. Esto es lo que funcionaría en un mensaje publicitario en frío (cold advertising) para un mercado nuevo. Tené en cuenta que acá no estoy hablando de publicidad a una audiencia cálida (warm audience). No estoy hablando de publicidad a una lista que ya tenés, a referidos, a amigos y familia. Me estoy refiriendo puramente a lo que significa hacer marketing a gente que no tiene ni idea de quién sos. Por lo tanto, un mercado frío (cold market). Eso sería llamadas en frío, email en frío, anuncios en frío — entonces Facebook ads, TikTok ads, Google ads. Y por lo tanto, si este es un mercado nuevo, podés hacer cualquier afirmación, lo que significa que puedo simplemente salir y decir "che, llevo Facebook ads para empresas de HVAC" y tendría un flujo de clientes llenando mi calendario queriendo trabajar conmigo, porque piensan "quiero hacer Facebook ads". Si sabés algo de este rubro, sabés que definitivamente no estamos en un nivel uno. Esto típicamente pasa cuando se abre un mercado o categoría completamente nueva. Por ejemplo, la IA. La IA ahora mismo es uno de los espacios o categorías nuevas que hay. La mayoría de las ofertas en el mercado de la IA no han sido explotadas tanto todavía. De hecho, estaba viendo un video hace poco de Dan Martel, que hablaba de cómo solo el 5% de toda la población de la Tierra ha pagado realmente para usar IA hasta ahora, lo que significa que la mayoría de la gente ni siquiera usa la IA de forma profesional.</t>
         </is>
       </c>
       <c r="O96" s="5" t="inlineStr">
         <is>
-          <t>Mismo set que la fila 203 (mismo dia y lugar): Ben al aire libre en el predio del evento con credencial/lanyard y remera roja, edificio y cielo despejado de fondo; subtitulos en mayusculas siguiendo el audio palabra por palabra; titulo superpuesto '$300M Meta Ad expert breaks down the jargon (Part 1)'.</t>
+          <t>Plano medio de busto en el mismo setup. Subtítulos bold. Pantalla dividida con una imagen de referencia (gráfico de niveles de sofisticación de mercado, estilo diagrama de marketing clásico) y notas manuscritas superpuestas debajo (fórmulas conceptuales y ejemplo del nicho HVAC), repetida de forma casi idéntica entre frame 3 y frame 5.</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
-          <t>Mismo gancho de autoridad y exclusividad que la fila 203 (invitacion de Meta a Silicon Valley); estructura de glosario facil de guardar ('Save this'); gatillo educativo de simplificar jerga tecnica para audiencia de marketing.</t>
+          <t>Gancho de consecuencia alta ("la diferencia entre escalar o fracasar"); estructura educativa con marco teórico conocido (niveles de sofisticación) aplicado a un ejemplo propio y a un caso de actualidad (IA); gatillo de autoridad + aplicabilidad a la propia cuenta del espectador.</t>
         </is>
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
-          <t>no del todo, depende del acceso al evento real para el gancho de autoridad, aunque el glosario en si es replicable en cualquier locacion.</t>
+          <t>sí, necesita solo una imagen de referencia (buscable/reutilizable) y notas a mano encima.</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
@@ -9413,32 +9413,32 @@
     </row>
     <row r="97" ht="88" customHeight="1">
       <c r="A97" s="2" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Solución de un problema</t>
         </is>
       </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>BitBranding</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -9448,33 +9448,33 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="J97" s="6" t="n">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bitbranding/video/7638775568783133982</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7670633794583448840</t>
         </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>BitBranding argumenta que los anuncios de Facebook que fallan no es un problema de presupuesto sino del algoritmo que cambió, y presenta cómo usan Claude en todo su proceso de anuncios, cerrando con el resultado de una campaña real de $4.800 de gasto diario y ROAS 5x.</t>
+          <t>Justin Lalonde señala que con presupuestos chicos ($50-100/día) los anunciantes suelen pelear simultáneamente contra tres problemas (mala oferta, malos creativos, mala landing page) y confunden el síntoma —tener que producir demasiados creativos— con la causa real.</t>
         </is>
       </c>
       <c r="N97" s="5" t="inlineStr">
         <is>
-          <t>La brecha entre las marcas que están ganando en Facebook ads y las que están perdiendo dinero nunca fue tan amplia [corregido de 'wiped']. Las marcas que están perdiendo siguen haciéndolo a la vieja usanza. Apilamiento de intereses (interest stacking), topes de puja (bid caps), 12 conjuntos de anuncios diferentes, tratando manualmente de ser más listos que un algoritmo que tiene más datos que toda la gente de su equipo combinada. Y acá está la cosa: no es que sean malos en esto, es que el algoritmo cambió. Meta cambió más en los últimos 18 meses que en los cinco años anteriores, y la mayoría de las marcas no se enteraron. Las marcas que descubran cómo alimentar al algoritmo con mejores insumos ahora mismo van a dominar su categoría. Las que no, van a seguir preguntándose por qué su costo por compra sigue subiendo. Ahora, si estás gastando dinero en anuncios de Facebook y no estás viendo el retorno que esperabas, te puedo asegurar ahora mismo que no son los insumos, no es tu presupuesto. Entonces en este video les voy a mostrar exactamente cómo podemos usar Claude en todo nuestro proceso de anuncios de Facebook, desde saber a quién le estamos vendiendo, hasta escribir el guion, el creativo, hasta armar el brief de campaña antes de siquiera abrir el ads manager. Vale la pena armar esta campaña. Déjenme mostrarles el resultado final antes de entrar en cómo la construimos. Entonces esta es una campaña ahora mismo con $4.800 de gasto diario, gastamos $136.000 en los últimos 30 días, que sé que para algunas personas no es una locura, pero con un ROAS de 5x [corregido de '5x row as'] no está nada mal.</t>
+          <t>Cuando recién empezás a correr anuncios, puede que no te des cuenta de esto cuando estás gastando un presupuesto muy chico, como 50 a 100 dólares por día, pero podrías estar peleando contra los tres problemas simultáneamente. A veces tenés una mala oferta y tenés que producir una cantidad significativa de creativos porque todavía no sos muy bueno haciendo creativos, y tampoco tenés el tipo correcto de landing page, y por lo tanto lo que termina pasando es que estás peleando en los tres frentes sin realmente saberlo. Sentís que estás dando vueltas en círculos y siempre tenés que estar produciendo nuevos creativos para tratar de superar los malos creativos, la mala oferta y la mala landing page. Así que uno de los síntomas acá de tener un problema de los de arriba típicamente va a ser "demasiados creativos". Okay, o sea, que tenés que producir tantos creativos todo el tiempo porque sentís que "justo mis anuncios se siguen muriendo, nada funciona" — o funciona por muy poco tiempo. Esto usualmente significa que una de esas tres cosas tiene un problema. Okay, entonces si tenés malos creativos, obviamente vas a tener que producir más creativos con la esperanza de encontrar uno bueno, porque eso es como buscar una aguja en un pajar. Mala oferta significa que, de nuevo, tus creativos van a tener que sobrecompensar por la oferta siendo mala. Mala landing page, de nuevo, significa que tenés que sobrecompensar haciendo muchísimo más volumen de creativos, porque tienen que mandarte gente súper "cálida" (warm) a tu landing page, o si no, simplemente no van a convertir.</t>
         </is>
       </c>
       <c r="O97" s="5" t="inlineStr">
         <is>
-          <t>Talking head en estudio con fondo oscuro/gris, gorra puesta al revés, remera con texto de merch ('Love Your Neighbor'), mic no visible en cuadro. Se intercala al menos un slide de fondo sólido azul grisáceo con frases clave en tipografía blanca grande tipo motion graphics (sin cara), a modo de corte visual entre segmentos del guion. Subtítulos blancos quemados en los segmentos con cara.</t>
+          <t>Plano medio de busto. Subtítulos con cifras destacadas en dorado ("$50 — $100 a día"). Pantalla dividida con lo que parece ser una grabación de pantalla de una app de notas del celular (se ve reloj/batería en la captura) con cálculos y un diagrama de flujo escritos a mano (Oferta → Creativos → Landing Page, más síntomas listados).</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Gancho: negación/contraintuitivo directo ('tus anuncios no fallan por el presupuesto') que reencuadra el problema. Estructura: contraste 'los que ganan vs. los que pierden' seguido de caso real con cifras de campaña (gasto diario, gasto en 30 días, ROAS). Gatillo: urgencia/FOMO por el cambio de algoritmo, reforzado con CTA de comentario para desbloquear el video completo (mencionado en la descripción del posteo).</t>
+          <t>Gancho de insight/reencuadre ("tu problema podría no ser uno solo"); estructura de diagnóstico de síntoma vs. causa con tres frentes posibles; gatillo de identificación ("me pasa a mí") para anunciantes de bajo presupuesto.</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr">
         <is>
-          <t>no del todo + nota: combina talking head con slides de motion graphics editadas, lo que exige más tiempo de edición que un video simple a cámara.</t>
+          <t>sí, celular con app de notas, cámara y micrófono básico alcanzan para replicarlo.</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
@@ -9505,32 +9505,32 @@
     </row>
     <row r="98" ht="88" customHeight="1">
       <c r="A98" s="2" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde</t>
+          <t>Ben Heath</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -9540,48 +9540,48 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="J98" s="6" t="n">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7642454739313102098</t>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7663560014900038934</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde explica que Meta lanzó su propio servidor MCP oficial para conectar cuentas de anuncios con IA (como Claude) de forma segura, y muestra paso a paso cómo instalarlo y usarlo para modificar presupuestos por chat.</t>
+          <t>Ben Heath resena un anuncio de Meta de Huel (puntuacion 8 sobre 10), destacando el gancho verbal en forma de pregunta, la ubicacion autentica tipo detras de escena en un deposito y el ritmo rapido de edicion.</t>
         </is>
       </c>
       <c r="N98" s="5" t="inlineStr">
         <is>
-          <t>Ha habido muchos reportes en el ambiente sobre perfiles de Facebook que quedaron completamente eliminados/baneados [?] ("nuked" en el original) por conectar un MCP a sus cuentas de anuncios. Eso era antes — ahora Meta lanzó oficialmente su propio servidor MCP, permitiéndote conectar tus cuentas de anuncios de forma segura con herramientas como Claude. Lo que vas a hacer es descargar Claude Desktop. Después vas a ir a la esquina inferior izquierda y hacer clic en configuración (settings). Después vas a ir a conectores (connectors). Desde ahí vas a hacer clic en "agregar un conector personalizado" (add a custom connector). Le vas a poner de nombre "meta ads" acá. Ahora, este es el único MCP oficial de Meta. Okay, entonces una vez que lo tengas puesto, podés simplemente hacer clic en "agregar". Como podés ver, una vez agregado vas a ver el ícono de Facebook y ahora vas a tener un botón que dice "conectar" (connect). Así que vamos a hacer clic en eso, y ahí se va a abrir tu perfil de Facebook. Te va a preguntar si sos la persona correcta. Decís que sí. Ahora te va a preguntar si querés otorgar [?] ("often" en el original, probablemente "grant") acceso a todos los negocios actuales y futuros, o solo a los negocios actuales. Yo voy a elegir "todos los actuales y futuros" para efectos de este video. Después vas a darle a continuar, y ahí vamos a hacer clic en guardar acá. Ahora nos aparece una pantalla de éxito, y listo. Ya tenemos nuestro configurador de meta ads. Desde el punto de vista de reportes y preguntas, en mi experiencia es en realidad un MCP muy sólido. Acá hay otra cosa que podés hacer con este MCP: por ejemplo, le dije "che, quiero que aumentes el gasto publicitario del ad set dcd32 en $2 extra por día, dado que esta es una campaña ABO [?]" ("adio" en el original). Entonces me dijo "confirmación rápida: este ad set acá, el presupuesto actualmente es de 1875 por día, lo voy a poner en 2075 por día. La cuenta de anuncios es esta, y el ID del ad set es este. Por favor confirmá." Y yo le dije que sí, y listo — "hecho, dcd32 ahora está en 2075 por día".</t>
+          <t>¿Es bueno Huel [?, en el original 'fuel', probable error de reconocimiento del nombre de marca] para bajar de peso? Entonces arranca con la pregunta, uno de mis tipos favoritos de hooks verbales [?, en el original 'herbal hooks', corregido por 'verbal hooks' segun coincide con el grafico en pantalla], genera mucha curiosidad y tambien ayuda a encuadrar una objecion y superarla temprano. Nos hacen esta pregunta tantas veces que en realidad lanzamos un producto nuevo. Esta ambientado en un deposito, tiene como una onda de detras de camara [?, en el original 'behind the scenes field', probable error de reconocimiento por 'behind the scenes feel'], muy autentico, me gusta eso. Tiene 200 calorias, 20 gramos de proteina, nutricion adecuada, todo por solo una libra la comida. Estan respondiendo la pregunta enumerando beneficios. Hicieron todo eso en 10 segundos, lo cual es muy ajustado, esta muy bueno. Elimina mucha incertidumbre. Entonces, si te costo mantener la constancia para bajar de peso, esto esta hecho para eso. Y ves que hay muchos cortes, movimiento constante, excelente para la atencion. Tambien me gusta bastante el estilo POV. Le doy un ocho de 10.</t>
         </is>
       </c>
       <c r="O98" s="5" t="inlineStr">
         <is>
-          <t>Plano medio, presentador con blazer, iluminación más cálida/producida que otros videos del mismo canal. Subtítulos bold. Gran parte del video es grabación de pantalla (screen recording) de Mac mostrando la app de Claude Desktop: configuración, conectores, y luego el chat con la confirmación de cambio de presupuesto del MCP de Meta, en formato pantalla dividida.</t>
+          <t>Mismo formato de resena que el resto del lote: Ben con el celular mostrando el anuncio original superpuesto en un recuadro (cajas en un deposito con un globo de chat simulando la pregunta, botella y caja de Huel); etiquetas de seccion ('Verbal Hook', 'Authentic Location') que acompanan el analisis; titulo '$300M Ad Expert Reviews Huel'.</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
-          <t>Gancho de miedo/alerta ("Facebook está baneando cuentas") que capitaliza un tema de actualidad (bans por MCP no oficiales); estructura tutorial paso a paso con capturas reales; gatillo de urgencia + utilidad práctica inmediata sobre una herramienta nueva de IA aplicada a ads.</t>
+          <t>Gancho de pregunta directa (¿Es bueno Huel para bajar de peso?) senalado por el propio Ben como tecnica replicable; estructura de resena con criterios claros (hook, ubicacion, ritmo) que educa mientras entretiene; gatillo de autoridad mas aprendizaje por ejemplo.</t>
         </is>
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
-          <t>sí, requiere grabación de pantalla (gratis con herramientas nativas) y narración; sin equipo especial más allá del que ya usa el canal.</t>
+          <t>si, mismo formato de resena de bajo costo: solo celular y superposicion de video.</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
@@ -9597,22 +9597,22 @@
     </row>
     <row r="99" ht="88" customHeight="1">
       <c r="A99" s="2" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Información</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -9632,48 +9632,48 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J99" s="6" t="n">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justnlalonde/video/7644680332192533778</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7640890960645295378</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>Justin Lalonde muestra casos de uso reales del MCP de Meta con Claude: pedir resúmenes de campañas activas, marcar ad sets que superan un umbral de gasto/costo por resultado, y recibir recomendaciones de qué ad sets escalar según 30 días de datos.</t>
+          <t>Justin Lalonde cuenta que perdió un cliente grande tras recomendarle matar su funnel de anuncios, y explica las señales para decidir entre relanzar creativos ganadores anteriores, hacer A/B testing incremental del funnel, o cambiar el VSL/webinar por completo.</t>
         </is>
       </c>
       <c r="N99" s="5" t="inlineStr">
         <is>
-          <t>Recientemente mostré en el canal cómo conectar Claude a tu cuenta de anuncios de Meta usando su MCP. Ahora, en este video quiero mostrarte exactamente qué podés hacer con él, en distintos casos de uso de este nuevo MCP. Uno de los primeros formatos (prompts) que quiero compartir con vos es el siguiente: "Dame un resumen de 7 días [?]" ("70 summary" en el original) "de todas mis campañas activas, marcá cualquiera que esté gastando más de X con [CPR/ROAS ?] por debajo de Y" — podés cambiar eso según el tipo de cuenta. En este caso, lo que voy a hacer es ir específicamente por esta campaña. Así que voy a copiar el nombre de esta campaña y voy a decir "marcá cualquier cosa que gaste más de $150 con costo por resultado, digamos, por encima de un tercio, en esta campaña". Y esto es lo que me dio: "Okay, genial, revisé cada cuenta de anuncios o campaña de anuncios que tenés dentro de esta cuenta para campañas activas, este es el monto de gasto, acá están los resultados generales por campaña". Decía algo así como "mirá, hay un ad set que efectivamente supera ambos umbrales acá, gastó $144, que está cerca de tu límite de 150 — no estoy seguro por qué lo mencioné pero bueno, es lo suficientemente cerca —, el costo por resultado es de 130 o más. Hay este que tiene un resultado a 144. Así que este es el único outlier que tenés acá". Ahora, lo que podría hacer desde ahí es simplemente decir "che, apagá DCT 70 J" — que ya había sido apagado. Ahora, el siguiente prompt que le di a este Claude [?] ("clot" en el original) con el que estoy conversando en el hilo es "mostrame los anuncios que hayan alcanzado mi objetivo de costo por resultado de $100 durante siete días consecutivos dentro de mi campaña de team schedules, y recomendame cuáles escalar y cuánto". Y me dijo, "bueno, en realidad todavía no llegaste a eso". Aun así, me dio un análisis de costo por resultado de 30 días acá. Así que se fue un poco más atrás para darme cuáles ad sets habían tenido el mejor rendimiento ahí — como cuántos días tuvieron conversiones en este ciclo de 30 días. Entonces acá decía algo como "si yo fuera vos, escalaría DCT 64 J; DCT 32 va a ser el segundo que más escalaría acá; después DCT 70, DCT 24 y después DCT 84 acá".</t>
+          <t>Acabo de perder un retainer de cliente de múltiples seis cifras porque le dije que matara todo su funnel [?] ("because they told them" en el original, corregido por sentido — probablemente "porque yo le dije") — ahora te cuento por qué lo volvería a hacer. Desde la perspectiva de un media buyer, o de una agencia, o incluso de un marketer, diría que lo que está en juego es que podés convertirte en una agencia muy rápido que simplemente no puede entregar resultados, cuando la verdad es simplemente que te tocaron cartas malas y tenés que poder cambiar esas cartas y hacerte cargo de la situación. Así que algunas de las señales acá — y una de las primeras — es cuando muchos de tus "ganadores" (winners) actuales están muriendo. Lo que vas a querer hacer, y lo que vas a querer probar, es relanzar viejos ganadores. Si estos vuelven a mover la aguja, decimos "okay, no, esto probablemente es solo un problema de creativos, nuestro stack de creativos actual simplemente no sirve, necesitamos reformular los creativos". Pero lo que a veces termina pasando — y en el caso específico del cliente que mencioné en la introducción — es que relanzar viejos ganadores no funcionó por mucho tiempo. Empezó a pasar que, si mirás el gráfico, esos resultados repuntaban un poco y después iban bajando lentamente otra vez. Entonces, el A/B testing del funnel es cuando vas a hacer cambios pequeños, mejoras incrementales pequeñas — por ejemplo, probar titulares (headlines), después la página de opt-in o sin página de opt-in como ejemplo, después empezás a avanzar hacia conversión y optimización. Voy a poner acá algo como Microsoft Clarity, que instalarías en tu landing page, y después empezás a probar cosas como: ¿deberían mover el botón más arriba? ¿La gente siquiera hace scroll hasta la sección de testimonios? ¿La gente lee las reseñas o no? ¿Lee la descripción? — empezás a mirar todos los detalles pequeños de tu landing page para intentar arreglarla. Otras cosas que podés hacer acá es, si estás corriendo un VSL como ejemplo, cambiar el VSL — voy a poner "VSL webinar" como cambio — esto en realidad te puede devolver a resultados bastante decentes, como "okay, genial, mi funnel no está tan mal, solo necesitaba unos ajustes".</t>
         </is>
       </c>
       <c r="O99" s="5" t="inlineStr">
         <is>
-          <t>Plano medio de busto, cabello rizado, mismo tipo de setup cálido del canal. Subtítulos bold. Pantalla dividida extensa con capturas de las respuestas de texto de Claude (tablas de resumen de campañas de 7 días, análisis de costo por resultado a 30 días con recomendaciones de escalado). Formato tutorial denso en texto/datos.</t>
+          <t>Plano medio de busto en el setup habitual. Subtítulos bold, algunos frames sin gráfico adicional. Pantalla dividida con una libreta donde va escribiendo a mano (aparentemente en vivo) una lista numerada de señales para matar un funnel y pasos de A/B testing, construyéndose progresivamente en sincronía con el relato hablado.</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Gancho de continuidad de serie ("ya mostré cómo conectar... ahora te muestro qué hacer con esto"); estructura de casos de uso concretos con prompts copiables y resultados reales mostrados en pantalla; gatillo de utilidad práctica + demostración de ahorro de tiempo/dinero.</t>
+          <t>Gancho de vulnerabilidad/pérdida concreta ("perdí un cliente de 6 cifras") + postura contraintuitiva ("lo haría de nuevo"); estructura narrativa de caso real con señales de decisión enumeradas; gatillo de storytelling + utilidad práctica tipo checklist implícito.</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr">
         <is>
-          <t>sí, mismo requisito que el video anterior: grabación de pantalla del chat de IA más narración, reproducible por cualquiera con acceso al MCP.</t>
+          <t>sí, formato de libreta/notas a mano en vivo, mismo setup casero de siempre.</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
@@ -9697,12 +9697,12 @@
       <c r="C100" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Información</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Difícil</t>
         </is>
@@ -9781,32 +9781,32 @@
     </row>
     <row r="101" ht="88" customHeight="1">
       <c r="A101" s="2" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Solución de un problema</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>Difícil</t>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>BitBranding</t>
+          <t>Justin Lalonde</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>EE.UU.</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -9816,48 +9816,48 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="J101" s="6" t="n">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bitbranding/video/7633975768598449439</t>
+          <t>https://www.tiktok.com/@justnlalonde/video/7664708959932108050</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>BitBranding analiza por qué las marcas de ropa pierden dinero con sus anuncios pese a usar IA, centrándose en la retención de hook en los primeros 3 segundos y en cómo usar Claude para generar copys de anuncios a partir de reseñas reales de clientes.</t>
+          <t>Justin Lalonde muestra cómo un mismo producto (coaching de pérdida de peso) puede anunciarse con tres ángulos completamente distintos según la objeción del público —sin gimnasio/equipo, odio al cardio, falta de tiempo por trabajo—, manteniendo el mismo deseo central.</t>
         </is>
       </c>
       <c r="N101" s="5" t="inlineStr">
         <is>
-          <t>Acá es donde la mayoría de las marcas de ropa todavía pierden dinero, incluso con un buen prompt [?] ("grape prompt" en el original, probablemente error de reconocimiento por "great prompt"). El watch time (tiempo de visualización) de tus anuncios — Facebook lo llama el "thruplay" —, es una de las señales más importantes que usa meta [?] para decidir a quién mostrarle tus anuncios. La clave para crear anuncios que frenen el scroll en los primeros tres segundos: la retención de hook promedio está por debajo del 20%, lo que significa que literalmente el 80% de la gente se va después de unos tres a cinco segundos. Ahora, una buena retención de hook es del 30 al 40%, y los hooks atípicos (outliers) superan el 50%. Y los anuncios en la categoría de outliers reciben una distribución exponencialmente más barata de parte de meta. Okay, entonces siempre decimos, ¿qué es mejor, una foto o un video? Y normalmente digo que ambos son en realidad muy buenos. Sin embargo, si podés crear un video muy bueno, un video siempre le va a ganar a una imagen. Lo que pasa es que la mayoría de la gente no puede crear contenido en video que realmente conecte con su audiencia. Así que tomé 10 anuncios generados con IA y analicé qué pasó en los primeros tres segundos de cada uno. Dejame guiarte por los patrones acá. Los anuncios que mejor funcionaron abrían con una frase que rompía el "scroll mental" del espectador, el patrón de "scroll mental". Ejemplo: "esta buzo/hoodie me hizo llegar tarde al trabajo y no me arrepiento de nada". Suficientemente raro como para detenerte, suficientemente identificable como para hacerte seguir leyendo. Y los anuncios más fuertes usaban las palabras exactas que nuestros clientes usaban en reseñas, DMs y comentarios, no lenguaje de marketing. Okay, entonces Claude [?] (transcripto como "Cloud") sacó a la superficie ese lenguaje al instante cuando le dimos reseñas de clientes en bruto. La IA generó la segunda versión cuando le pedimos que fuera específica y humana. El tráfico frío necesita curiosidad y un llamado a la acción (call to action). Retargeting — metámonos en la locura del retargeting de meta. Técnicamente, si un anuncio se muestra más de una vez, ya es retargeting, pero podés crear contenido dirigido a alguien que está más avanzado en tu funnel versus una audiencia completamente fría. Pero el retargeting necesita urgencia y un llamado a la acción. Claude [?] produjo cinco variaciones de cada uno al instante cuando especificamos la etapa del funnel en el prompt. Solo esto redujo nuestro tiempo de creación de anuncios en un 60%.</t>
+          <t>Los ángulos son una variable en tu anuncio que puede cambiar el mensaje por completo, en términos de qué decís. Cuando vas a pescar y usás una carnada, ¿no? Vas a cambiar la carnada según el tipo de pez que querés rastrear, o según el tipo de pez que querés atrapar, o según el tipo de día, o a veces incluso la hora del día o las estaciones — vas a cambiar esa carnada. Acá, lo que hice es: esos son tres ángulos completamente distintos que podría usar dentro de mis anuncios de Facebook. Todos son "conscientes de la solución" (solution aware). Todos son sobre un producto para bajar de peso. Todos apuntan a la misma audiencia, pero hablan de objeciones distintas de formas distintas. Este es para alguien que tiene la objeción de "ah, mierda, no puedo hacerlo, no tengo gimnasio" — bueno, "sin gimnasio". "No tengo ningún equipo en casa" — "sin equipo". Y, saben, "solo toma 20 minutos al día" — entonces "no tengo tiempo, 20 minutos al día, genial". ¿Ves? Entonces yo típicamente soy consciente de que si quiero bajar de peso — soy "consciente de la solución" —, podría necesitar un gimnasio, podría necesitar equipo. Ah, esto es distinto: "sin gimnasio, sin equipo". Ahora, para la gente que odia el cardio [?] ("weight cardio" en el original, corregido por sentido a "hate cardio"), típicamente, de nuevo, soy consciente de la solución, sé que podría bajar de peso, podría hacer cardio, no quiero hacerlo, odio la mierda del cardio. Entonces pienso, "sabés qué, no lo voy a hacer". Pero es como, "che, mirá, si odiás el cardio, prestá atención". Okay, interesante, ese soy yo. Después el tercero: "sé que podría hacer dieta, pero va a ser difícil preparar las comidas, va a ser difícil encajarlo en mi horario, estoy ocupado, tengo un negocio, semanas de 60 horas de trabajo" — okay, "demasiado ocupado para hacer dieta, esto es para semanas de 60 horas de trabajo". Interesante. Tres ángulos completamente distintos. Pero, de nuevo, el mismo deseo central de bajar de peso, el mismo programa de coaching fitness. Ahora, seguimos hablándole a la misma solución para nuestra audiencia, pero simplemente cambiamos el ángulo, lo que significa que estamos mirando el mismo producto pero desde ángulos distintos, como vemos acá, distintas formas de enmarcar el mismo producto.</t>
         </is>
       </c>
       <c r="O101" s="5" t="inlineStr">
         <is>
-          <t>Plano medio/primer plano frontal, locación con pared oscura lisa (sin fondo de living), gorra al revés. Subtítulos blancos bold centrados. Usa stickers/íconos animados superpuestos (logo de Meta con ícono de señal wifi, ícono de chip de IA con "x10"). Corta a una placa gráfica de fondo color teal con íconos ilustrados (semáforo, cerebro) y texto grande estilo poster ("needs"/"curiosity"). Edición tipo agencia/marca con identidad visual propia.</t>
+          <t>Plano medio de busto en el setup habitual. Subtítulos bold ("the bait"). Pantalla dividida con una tabla de referencia sobre tamaños/ángulos de toma cinematográficos (aparentemente un gráfico reutilizado por el juego de palabras con "ángulos") y notas manuscritas con los tres ángulos de copy concretos del ejemplo (sin gimnasio, odio al cardio, 60 horas de trabajo).</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Gancho de urgencia con cifra impactante ("tenés 3 segundos... 80% se va"); estructura de mini-caso de estudio (10 anuncios analizados) con patrones concretos y ejemplo de copy real; gatillo de curiosidad + prueba social/autoridad de datos, más CTA de comentario para entregar contenido extra.</t>
+          <t>Gancho de analogía simple y memorable (carnada de pesca); estructura de ejemplo triple aplicado al mismo producto/audiencia mostrando la técnica en acción; gatillo de claridad conceptual + aplicabilidad inmediata al propio negocio del espectador.</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr">
         <is>
-          <t>no del todo, el contenido en sí es replicable pero los stickers/íconos animados y la placa gráfica de marca requieren edición y diseño más avanzados.</t>
+          <t>sí, mismo formato de notas a mano; el gráfico de referencia sobre ángulos de cámara es opcional/decorativo.</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Matt Bell</t>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -10175,7 +10175,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Caleb Kruse (Mr. Paid Social)</t>
+          <t>Matt Bell</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -10235,7 +10235,7 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Charley T (Disrupter School)</t>
+          <t>Mary-Anne Da'Marzo</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
@@ -10245,7 +10245,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Mary-Anne Da'Marzo</t>
+          <t>Charley T (Disrupter School)</t>
         </is>
       </c>
       <c r="B33" s="15" t="n">

--- a/top_100_reels_meta_ads_guiones.xlsx
+++ b/top_100_reels_meta_ads_guiones.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Top 100 Meta Ads" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen y método" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bonus marketing general" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Guiones para tu negocio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top 100 Meta Ads" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen y método" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Bonus marketing general" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +62,14 @@
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +111,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -179,6 +191,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,8 +560,4878 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J112"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Formato</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t># por vistas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Día sugerido</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Basado en (creador)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Link del original</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Vistas del original</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GUION ADAPTADO A TU NEGOCIO (listo para grabar)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de edición necesaria</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Qué se adaptó</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Demo de herramienta/IA — 18 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="100" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7618214625120767262</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>231400</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Esto puede cambiarte cómo manejás tus anuncios para siempre. Ahora podés conectar una IA directo a la cuenta de anuncios de tu concesionaria o tu estudio. Así funciona: primero, la IA ve en tiempo real los datos de tu cuenta. Segundo, le preguntás qué anuncios se están cansando, y te dice cuándo está bajando la atención y cuándo te va a subir el costo por consulta, antes de que pase. Así sabés el momento justo para cambiar el anuncio. Pero acá viene lo fuerte: le podés pedir que directamente te arme cinco ideas de anuncios nuevos basadas en los que mejor funcionaron el último mes, listas para grabar. Se terminó adivinar cuándo cambiar el anuncio, se terminó quedarte sin ideas a último momento. No es una herramienta que te tira un reporte más, es una IA que te cuida la cuenta en piloto automático. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de pantalla en modo oscuro simulando un chat de IA conectado al Administrador de anuncios, con Gonzalo en recuadro (PiP) abajo hablando a micrófono; subtítulos bold; flechas de énfasis dibujadas sobre la interfaz; cortes entre 2 o 3 pantallas distintas.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de anuncio de novedad más mecanismo paso a paso y reencuadre ambicioso; cambié el contacto automático a creadores UGC por generación automática de ideas de anuncios para concesionarias y estudios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7647588481862012174</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>47400</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>¿Te imaginás tener la cuenta de anuncios completa de tu estudio armada en una sola tarde, sin depender de un diseñador ni de un community manager? Te lo muestro. Agarro los datos del estudio -especialidad, zona, tipo de casos que quieren atraer- y con inteligencia artificial genero veinte variantes de anuncio: testimonios, preguntas frecuentes, el momento en que se ganó un caso. Después reviso qué está funcionando en la cuenta real y ajusto el texto de cada anuncio para esa especialidad puntual. Lo que antes llevaba una semana entera, ahora lo tengo armado en un par de horas. Esto es lo que hago todos los días para estudios y concesionarias que quieren dejar de depender de que alguien 'los recomiende' y empezar a tener consultas todas las semanas. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre vertical medio plano tipo escritorio/oficina; subtítulos dinámicos quemados con 1-2 palabras clave resaltadas; 4-5 cortes entre cámara y capturas de pantalla del Ads Manager/Meta Business Suite mostrando los anuncios generados; sin b-roll; música de fondo suave y baja.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho hipotético y la demo de capacidades encadenadas del original, cambiando el ecommerce genérico por el armado completo de una cuenta de anuncios para un estudio jurídico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7650195193890721038</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>34600</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Esto es todo lo que armé esta semana con inteligencia artificial para las cuentas de mis clientes. Primero, un tablero que muestra cuántas consultas generó cada campaña, separadas por estudio y por concesionaria, para que cada dueño vea en tiempo real cuánto le cuesta cada consulta real. Después, hice que contestara sola los comentarios más comunes de los anuncios -precio, zona, si atienden tal tema- para no perder ni un lead a la noche. Le pedí que armara un resumen semanal en criollo, sin jerga de marketing, para mandarle al cliente por WhatsApp los lunes. Y lo más loco: todas las mañanas revisa si algún anuncio se disparó en costo y me avisa antes de que se coma el presupuesto del mes. Todo esto corriendo solo, mientras yo estoy en otra reunión. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre vertical medio plano con banner de texto fijo arriba con el título; subtítulos dinámicos; cortes hacia capturas de pantalla de una planilla/dashboard con métricas de clientes (consultas por campaña); sin b-roll adicional; música up-tempo de fondo baja.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de catálogo de casos de uso cada vez más sorprendentes, cambiando automatizaciones personales (guardería, finanzas) por tareas de gestión de cuentas de clientes reales del rubro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7612660537196907806</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>28900</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Esta herramienta es gratis y casi nadie en tu rubro la usa: la biblioteca de anuncios de Meta. Buscás el nombre de cualquier estudio jurídico o concesionaria de tu ciudad, y ves todos los anuncios que están corriendo ahora mismo. No es para copiar el anuncio tal cual, es para robar la estructura: qué gancho usan, si muestran el precio, si arrancan con una pregunta o con el producto, dónde meten el botón de WhatsApp. El dato clave: si un anuncio lleva meses corriendo igual, es porque les está funcionando, si no ya lo hubieran bajado. Agarrás esa estructura y la aplicás con tu marca, tu precio, tu servicio. Así se mueven los que más facturan en tu rubro: no inventan de cero, usan lo que ya funciona. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de pantalla en vivo de la Biblioteca de Anuncios de Meta buscando un rubro y ciudad reales, con Gonzalo en recuadro inferior hablando a micrófono; subtítulos bold; círculos o flechas señalando gancho, precio y botón de WhatsApp en los anuncios mostrados.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de 'herramienta que cambia las reglas' con demo en pantalla enfocada en robar estructura, no copy; cambié una herramienta paga no verificable por la Biblioteca de Anuncios de Meta, real y gratuita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7641243325227339038</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>9980</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Hay una herramienta nueva que arma anuncios para autos usados sin que yo escriba un solo texto, y lo incómodo es lo bien que están quedando. Le cargo el modelo, el precio y la financiación, escanea las fotos, copia los colores de la marca y arma el kit completo sola. Elijo el formato -comparativa de cuotas, testimonio, pregunta frecuente respondida- y en minutos tengo veinte piezas para probar, sin fotógrafo ni producción cara. Ya no se notan hechas por una máquina, parecen armadas por el vendedor de toda la vida del local. Por eso las cuentas que más crecen prueban veinte variantes por mes, no una sola. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro chico superpuesto (o cortes) sobre capturas de pantalla de la herramienta/plantilla de generación de anuncios; subtítulo destacado en caja de color en el frame de apertura; subtítulos dinámicos; cortes entre cara y piezas generadas; sin b-roll; música de fondo.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de curiosidad sobre una herramienta nueva más el proceso paso a paso, cambiando la marca genérica de ecommerce por una concesionaria y el gatillo de 'da miedo' por 'incómodamente bien hechos'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7592305158449827102</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>9889</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Cada vez más concesionarias están grabando un solo auto bien filmado y usando inteligencia artificial para armar el resto: cambian el fondo, cambian el texto, arman hasta la escena de un cliente probando el auto, todo a partir de ese mismo video base. Así, en el tiempo que antes te llevaba producir un anuncio, ahora salen diez variantes distintas. Y como la base sigue siendo real —el auto, el vendedor, el cliente contento— el anuncio no pierde autenticidad. Las que ya lo están haciendo le están ganando la pulseada a la competencia en Meta, porque suben contenido nuevo cada semana mientras el resto repite la misma foto de siempre hace meses. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: presentador en recuadro chico abajo, capturas de pantalla (foto real de un auto + versión editada) ocupando el resto de la pantalla. Subtítulos quemados en una franja de color. 3-4 cortes entre fuentes (foto original, versión con fondo cambiado, anuncio final). Sin gráficos adicionales. Música de fondo suave tipo tendencia, volumen bajo.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de tendencia emergente y la estructura mecanismo-beneficios-prueba; se cambió el ejemplo de e-commerce con IA por concesionarias que combinan autos reales con ediciones asistidas por IA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7631323413780385038</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>7051</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Estas son las nuevas herramientas de imagen con IA, y para anuncios cambian todo. Miren esto. Le subí la foto de un 0km de la concesionaria y le pedí que lo ponga en la ruta al atardecer. Listo. Le pedí que cambie el cartel de 'financiación' por '12 cuotas sin interés'. Hecho. Subí la foto de un cliente saliendo con las llaves en la mano y le pedí tres fondos distintos para no repetir siempre la misma imagen en los anuncios. Listo. Y a un estudio jurídico le armé cuatro variantes del mismo anuncio de consulta gratis, cambiando color y texto, en dos minutos. Esto no reemplaza tener fotos reales de tu local o tu agencia, pero te ahorra la mitad del laburo de armar variantes para testear en Meta. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: presentador en primer plano alternando con captura de pantalla de celular o compu mostrando la imagen generándose. Título fijo arriba en franja de color con el gancho. Subtítulos dinámicos abajo. Cortes rápidos cada 3-4 segundos entre ejemplo y ejemplo. Sin b-roll. Música de fondo rítmica y baja para acompañar el ritmo de ejemplos.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Se mantuvo la ráfaga de ejemplos con 'listo/hecho' repetido y el ritmo creciente de sorpresa; se reemplazaron los ejemplos de suplementos e influencers por generación de imágenes para autos 0km y anuncios de estudios jurídicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7664714637417532685</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>5173</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Pensé que todo esto de manejar cuentas con inteligencia artificial era puro humo, hasta que empecé a usarlo en serio. Armé un sistema que arranca solo cada mañana: revisa la cuenta de cada estudio y cada concesionaria, y me avisa qué anuncio subió de costo. Contesta los comentarios más comunes -precio, zona, horarios- antes de que yo prenda la computadora. A la tarde arma tres variantes nuevas para el cliente que peor viene esa semana, usando lo que mejor funcionó en cuentas del mismo rubro. Y los domingos me deja armado el informe de cada cliente, listo para mandar el lunes. Esta mañana, tomando mate, ya tenía una cuenta optimizada antes de las ocho. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en primer plano con subtítulos dinámicos quemados; cortes hacia capturas de pantalla de un dashboard o planilla de seguimiento de clientes; ritmo tipo 'día en la vida' con 4-5 cortes marcando cada tarea; música de fondo suave.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura 'día en la vida' de escepticismo convertido en creencia con casos de uso crecientes, cambiando automatizaciones personales por tareas diarias de gestión de cuentas de clientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7649829734410505485</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>4574</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Tengo una biblioteca con más de treinta plantillas de anuncios ya probadas -testimonio, comparación de cuotas, antes y después de un caso- y un sistema que las combina con los datos de cada cliente para generar los anuncios. Cargo el modelo de auto o el tipo de caso que quiero promocionar, y el sistema cruza eso con cada plantilla. Hagamos la prueba: una concesionaria me pidió anuncios para tres modelos distintos, y en un par de minutos tengo treinta piezas, resultado de cruzar los tres modelos con diez plantillas cada uno, listas para revisar antes de subir. Antes armaba cada anuncio de cero, plantilla por plantilla. Ahora combino lo que ya sé que funciona con los datos de cada cuenta nueva, y multiplico la cantidad de piezas sin multiplicar el tiempo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida: arriba capturas de la planilla/librería de plantillas y ejemplos de piezas generadas para el cliente; abajo webcam; subtítulos dinámicos; corte marcando cada paso del proceso; sin b-roll; música mínima de fondo.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de velocidad y resultado con demo de plantillas combinadas en tiempo real, cambiando la gorra propia del creador por pedidos reales de un cliente concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7613406587423673631</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4168</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Esta es la herramienta con la que las concesionarias que más venden en Meta espían a la competencia. Si corrés anuncios en 2026 ya lo sabés: lo que te frena no es el presupuesto, es no tener ideas nuevas para grabar. Con esta herramienta buscás a cualquier concesionaria o estudio de la zona y ves al instante qué anuncios llevan más tiempo activos. Y eso importa, porque un anuncio no sigue dando vueltas semanas si no le está trayendo consultas al dueño. Podés ver el gancho que usan, si es foto o video, y guardarte los mejores en una carpeta de referencia para tu propio negocio. No hace falta reinventar la rueda: hace falta ver qué ya funciona en tu rubro y adaptarlo a tu ciudad. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: capturas de pantalla de una herramienta de espionaje de anuncios con el presentador en recuadro chico abajo. Cortes entre pantalla de búsqueda, ficha de anuncio y resultados. Gráfico: flecha o círculo señalando el dato de días activo como prueba. Sin b-roll ni locación propia. Sin música o muy baja de fondo.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Se mantuvo el gancho de autoridad indirecta y la prueba con un dato duro en pantalla; se cambió el CTA por palabra clave por el CTA estándar de categoría y los ejemplos pasaron a ser concesionarias y estudios locales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="100" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7667945190090394911</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>4094</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Este flujo con inteligencia artificial hizo que nunca más tenga que armar a mano el informe mensual de mis clientes. A fin de cada mes armamos un reporte para cada estudio y cada concesionaria: cuántas consultas entraron, qué anuncio funcionó mejor, cuánto bajó el costo por consulta. Antes nos llevaba tres o cuatro horas armar cada uno. Te cuento cómo lo automaticé y lo bajé a veinte minutos. Primero entrené a la inteligencia artificial con informes viejos nuestros, para que aprenda el formato exacto que uso. Después la conecté directo a la cuenta de anuncios de cada cliente, para sacar los números más precisos sin copiar y pegar nada. Ahora, todos los meses, se genera solo el reporte de cada cliente, y yo dedico veinte minutos a agregar el análisis que solo yo puedo dar, mientras el noventa por ciento del trabajo pesado ya está resuelto. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en escritorio combinado con capturas de pantalla superpuestas de la interfaz de IA y de los informes de clientes; subtítulos progresivos con alguna palabra destacada; edición en capas (cámara más grabación de pantalla); sin b-roll adicional.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la promesa de resultado con cifra de tiempo ahorrado y la estructura de tutorial paso a paso con capturas como evidencia, cambiando el reporte creativo de ecommerce por el informe mensual de consultas para estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7627237636427549966</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>3701</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Estos son los formatos de anuncio en video que están funcionando ahora con IA, y se hacen en minutos. Uno: recorrido del auto, como si fueras el cliente subiendo y mostrando el interior. Dos: entrevista corta en la vereda de la concesionaria preguntando qué busca la gente en un 0km. Tres: testimonio armado con voz de cliente real sobre imágenes generadas del auto en distintos escenarios. Cuatro: comparación lado a lado de cuotas, antes y después. Cinco: el abogado respondiendo a cámara la pregunta más común que le hacen por WhatsApp. Seis: un caso resuelto contado como historia corta, sin nombres. Con estos seis formatos ya tenés variedad para no repetir siempre el mismo anuncio. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de pantalla de un generador de video con IA intercalada con clips de ejemplo (recorrido de auto, entrevista callejera, testimonio). Texto fijo arriba con el título de la lista. Formato vertical, cortes cada 3-5 segundos por ejemplo. Música de fondo con ritmo constante tipo trend.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de listado rápido numerado de formatos de anuncio en video generados con IA; se redujo de 15 a 6 ejemplos y se cambiaron los rubros a concesionarias y estudios jurídicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="100" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7650235356842986775</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3692</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Vengo usando bastante la inteligencia artificial para analizar las cuentas de mis clientes, y se volvió clave porque puedo sacar los reportes de varias campañas, cargárselos y hacerle las preguntas justas. Por ejemplo, tenía una concesionaria con la tasa de consultas cayendo, y resultó que estaban recibiendo mensajes de gente de otras provincias que nunca iba a viajar a comprar el auto, porque el anuncio no tenía bien filtrada la zona. Exporto los datos de Meta, campaña por campaña, costo por clic, alcance y consultas de cada semana, y se lo cargo. Ahí le pregunto qué está pasando, y me ayuda a comparar el rendimiento a lo largo del tiempo, cruzando eso con los cambios de segmentación. No hago que la inteligencia artificial toque la cuenta ni configure nada, la uso solo para analizar. Cada semana le cargo el reporte y me arma un resumen de qué cambió. Mandame ANUNCIO por DM.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Sin talking head: fondo con título fijo en texto blanco, debajo captura de pantalla real de un chat de IA con el reporte, en un frame posterior un gráfico de líneas comparando canales; voz en off narrando; subtítulos mínimos o ausentes.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de autoridad práctica con capturas reales y estructura de caso de uso paso a paso, cambiando el análisis de tráfico de afiliados de ecommerce por la detección de tráfico mal segmentado en una concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7636400068785966367</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>3681</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Esta tendencia creativa va a explotar en las cuentas de estudios y concesionarias en los próximos meses, y no es fácil de fingir con inteligencia artificial. Hasta ahora todo era foto del auto, foto del escritorio, testimonio armado. Lo que empieza a andar mejor es mostrar una conversación real: un cliente contándole al abogado su problema, o alguien preguntando por un auto y el vendedor respondiendo ahí mismo, sin guion. Se puede grabar en el local, por videollamada, o en una consulta real con el cliente que dio el ok. Funciona porque es casi imposible de imitar con IA, se nota cuando es de verdad. Grabarlo bien no es tan fácil: una videollamada común se ve con la calidad de wifi de cada uno, y a veces enfoca a una sola persona. Yo grabo cada lado por separado con el celular y después edito para que parezca una charla fluida. Es más laburo, pero es contenido que no se puede fabricar. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en oficina o local; segmento tipo videollamada simulada con pantalla dividida (una persona arriba, la otra abajo) para mostrar el problema de grabar una conversación real; subtítulos progresivos; sin gráficos de marca de terceros.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la predicción de tendencia con plazo concreto y la demo del problema de grabar una conversación real en pantalla dividida, cambiando el ejemplo de coaching/webinars y la marca patrocinante por conversaciones reales entre abogado-cliente o vendedor-comprador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Mary-Anne Da'Marzo</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryannedamarzo/video/7669759222082440470</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>748</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>¿Se puede reemplazar la gestión de tus anuncios con inteligencia artificial? Lo probé esta semana conectando Claude a la cuenta de Meta Ads de un estudio jurídico. Mirá los cuatro pasos. Uno: conectás la cuenta de anuncios a la IA. Dos: le pedís que te muestre cuánto te está costando cada consulta y qué campaña está gastando de más. Tres: la IA te dice en segundos por qué no están entrando consultas, si es la segmentación, el video o la audiencia. Cuatro: le pedís que arme variantes nuevas del anuncio para probar. La herramienta acelera muchísimo el trabajo, pero si no entendés el rubro del cliente, la IA sola no te consigue ni un caso ni una venta de auto más. La estrategia la sigue poniendo una persona. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Fondo de color sólido con motion graphics de texto animado para cada paso numerado (1 a 4); capturas simuladas de un chat de IA y del Administrador de Anuncios superpuestas; presentador en recuadro chico en la parte inferior; subtítulos quemados. Requiere edición de motion graphics o una plantilla prearmada.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de 4 pasos numerados y el gancho '¿se puede reemplazar todo con IA?'; cambié el ejemplo genérico de e-commerce y ROAS por un estudio jurídico y métricas de costo por consulta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7634298092455480584</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>304</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Este gancho que están viendo del lado derecho lo generé enteramente con inteligencia artificial, para una concesionaria. Ya no hace falta tener el auto ahí filmando ni pagar una producción para probar una idea. Le pedí a la herramienta: mostrame un 0km rojo entrando de noche a un showroom vacío, con las luces del techo prendiéndose una por una a medida que avanza. Miren el resultado. Lo uso para testear ideas de gancho antes de gastar en filmación real: si esta versión hecha con IA logra que la gente se quede mirando, ahí sí vale la pena salir a filmar el auto posta. Me ahorra la plata de producción en las ideas que no iban a funcionar. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio en estudio/oficina con fondo oscuro, mic de mesa, primera mitad sin cortes; pasa a pantalla dividida mostrando el clip generado por IA al lado del presentador; subtítulos blancos simples quemados; requiere generar antes 1 clip corto con una herramienta de IA de video usando el prompt del auto.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de demo con prompt de IA más resultado en pantalla dividida y el gancho de intriga visual, y cambié el producto de blanqueador dental por un video de auto 0km generado con IA para una concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="100" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7642454739313102098</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>261</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Anduvieron circulando denuncias de cuentas de Facebook baneadas por conectar herramientas de IA de terceros. Eso quedó atrás: Meta ahora tiene su propio conector oficial para usar con Claude, de forma segura. Te muestro cómo se hace. Abrís Claude Desktop, vas a configuración, después a conectores, y agregás uno nuevo. Buscás el de Meta Ads, el oficial, le das conectar, entrás con tu Facebook, confirmás que sos vos, y elegís si le das acceso a las cuentas actuales o también a las futuras. Guardás y ya quedó conectado. Con esto, le pedí: 'subime cinco mil pesos por día el presupuesto del conjunto de anuncios de la concesionaria', y me contestó: 'confirmo, este conjunto está en veinte mil por día, lo paso a veinticinco mil, ¿confirmás?'. Le dije que sí, y en segundos quedó hecho, sin entrar al Administrador de Anuncios. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio del presentador con buena iluminación; gran parte del video en grabación de pantalla de Claude Desktop (configuración &gt; conectores &gt; conexión) y el chat con la confirmación del cambio de presupuesto, en formato pantalla dividida. Subtítulos bold quemados.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de noticia más tutorial paso a paso con capturas reales del conector oficial de Meta; cambié la cuenta genérica por una concesionaria y las cifras del presupuesto a pesos argentinos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="100" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7644680332192533778</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>260</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>La semana pasada te mostré cómo conecto una IA a la cuenta de mis clientes. Hoy te muestro para qué la uso todos los días. Esta es la cuenta de un estudio jurídico que llevamos. Le pido a la IA: 'resumime el gasto de los últimos siete días y marcame cualquier conjunto de anuncios que esté gastando más de quince mil pesos con costo por consulta arriba de tres mil'. En segundos me tira: 'este gastó dieciocho mil, costo por consulta cuatro mil doscientos, es el único que se pasó'. Lo pauso ahí mismo, antes de seguir quemando plata. Después le pregunto cuáles anuncios vienen con costo por consulta bajo el objetivo hace siete días seguidos, para saber cuáles escalar, y me arma un ranking. Esto antes me llevaba media hora de planilla. Ahora, dos minutos. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto, cámara fija; subtítulos bold quemados; sin b-roll; insertar 2 o 3 capturas simuladas de un chat de IA (tablas con montos y costo por consulta) en pantalla dividida o recuadro; corte simple entre el habla y las capturas.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de casos de uso con prompts copiables y resultados mostrados en pantalla; cambié la cuenta genérica de Facebook Ads por la cuenta real de un estudio jurídico con métricas de costo por consulta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Explicación con gráfico/pizarra — 15 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7639758395595099422</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>11500</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>La estrategia con la que una concesionaria pasó a vender cuarenta autos por mes con Meta Ads. Corren diez anuncios distintos: testimonios retirando el auto, comparativas de cuotas, y el dueño hablando a cámara. No fuerzan la venta, generan confianza y mandan todo a WhatsApp. La palanca real: no venden un auto, venden el service y la financiación de después, así que cada cliente vuelve y factura más con el tiempo. Y arman el círculo: el anuncio genera reconocimiento en el barrio, el reconocimiento lleva gente al local, la visita genera boca en boca, y el boca en boca baja el costo por consulta en Meta. Ese círculo completo es lo que hace crecer la cuenta, no un anuncio suelto. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Split-screen vertical: mitad inferior talking head fijo sin cortes; mitad superior con diagrama circular animado (Anuncio → Reconocimiento → Visita al local → Boca en boca → Consulta) hecho en Canva/Keynote con flechas y logo, más 1-2 capturas de Ads Manager o WhatsApp intercaladas; subtítulos dinámicos; música de fondo sutil.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de cifra grande más la lógica de 'flywheel' que cierra en síntesis memorable, cambiando la marca de indumentaria por una concesionaria y el diagrama por anuncio-reconocimiento-visita-boca en boca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="100" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7670085042210688269</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>4294</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Vamos a la estructura que uso para escalar una cuenta de concesionaria. Estas son mis campañas ganadoras, y siempre separo en dos: una con presupuesto optimizado a nivel de campaña para las piezas de foto, y otra para las de video. En vez de fijar el presupuesto anuncio por anuncio, le doy un mínimo diario a cada campaña completa y dejo que el sistema reparta solo. Con esa estructura, en una concesionaria mediana estoy multiplicando por tres la cantidad de consultas que entraban antes, sin tocar el presupuesto total, solo cambiando cómo está organizado. Y si cada consulta nueva se traduce en un turno, y cada tres o cuatro turnos en un auto vendido, ahí es donde se nota la diferencia real. Así arranco cada cuenta que quiere crecer en serio. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en plano medio sosteniendo una hoja o cartulina blanca con un diagrama dibujado a mano (cajas de campañas, flechas) que se va completando en distintos cortes; subtítulos progresivos palabra por palabra; sin b-roll adicional; sin música o mínima.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de entrar directo en tema con diagrama a mano y la explicación de estructura de campañas paso a paso, cambiando el ejemplo de ecommerce por la organización de campañas de foto y video de una concesionaria con métricas de consultas y autos vendidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="100" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7635737398961245462</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>3940</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Lo que puedo decir de las cuentas en las que vengo trabajando estos últimos noventa días es que las piezas estáticas están empezando a rendir mejor que el video, en varios estudios y concesionarias. Creo que pasa esto: hay tantos anuncios con avatares de inteligencia artificial y voces genéricas de locutor que la gente empezó a desconfiar apenas los escucha. Entonces una foto simple del abogado con un testimonio escrito, o una foto del auto con el precio y la cuota bien grande, está convirtiendo mejor que un video armado con IA. Esa es la tendencia que estoy viendo. Igual, la recomendación sigue siendo la misma: hay que variar formatos, no apostar todo a uno solo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Video prácticamente estático: una sola imagen o gráfico fijo con dos titulares en banners de color superpuestos sobre una captura comparando video vs. estático; sin talking head ni cortes; voz en off; subtítulos quemados sobre el gráfico.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de dato de tendencia contraintuitivo sin talking head y con hipótesis breve, cambiando el rendimiento estático-vs-video de ecommerce por el de cuentas de estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="100" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Mitch Barham (Beardpreneur)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@beardpreneur/video/7654413458217209101</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>3813</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Técnicamente, la mayoría de los estudios y concesionarias usan mal los anuncios de Meta. Durante años fue todo 'consultanos ya', directo a pedir el contacto. En realidad, la parte de arriba del embudo debería ser contenido más liviano: un video del abogado explicando un derecho, o de la concesionaria mostrando el local, algo que genere interacción, no la venta directa. Pero todos arrancan en la mitad, directo a 'escribinos ahora', y con presupuesto chico eso sale carísimo. Cuando un cliente ya factura fuerte y quiere escalar en serio, ahí sí hay que llenar la parte de arriba: contenido que genere confianza antes de pedir nada, para después bajar a la consulta. El problema es que entrenamos a todo el mundo a ir directo a pedir la venta ya, y eso, a partir de cierto tamaño de cuenta, deja de funcionar. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Formato respuesta a comentario, con la burbuja del comentario original en pantalla; infografía de embudo (arriba, medio, abajo) superpuesta durante todo el video; talking head con gestos marcados; subtítulos dinámicos con palabras clave resaltadas.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de afirmación polémica en formato respuesta a comentario con infografía de embudo, cambiando el ejemplo de escalado de ecommerce por el de cuentas de estudios y concesionarias que ya facturan fuerte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7629795407534591254</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>1465</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Cuando estás gastando en Meta, tenés que tener cuidado con un numerito: el resultado que te muestra el Administrador de anuncios. Por ejemplo, te puede mostrar quince consultas en la semana, pero si le preguntás a cada cliente cómo te encontró, la mitad te va a decir que primero te buscó en Google, o que un amigo le pasó tu contacto, y recién ahí vio el anuncio. Meta se atribuye esa consulta igual. Si tenés una concesionaria o un estudio, no mires solo lo que dice el administrador de anuncios: preguntale a cada cliente nuevo cómo llegó hasta vos y anotalo en una planilla simple. En un mes vas a tener el número real, no el que infla la plataforma. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Sin cámara: tarjeta de texto fija con el gancho, sobre una captura o grilla simple armada en Canva o Sheets mostrando la comparación de números. Narración en off. Imagen fija sostenida, sin cortes ni música.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el formato sin cámara de tarjeta de texto sobre un gráfico fijo con narración en off explicando una métrica inflada; se cambió el ROAS de e-commerce por consultas de concesionaria o estudio atribuidas de más a Meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="100" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7618955944449297696</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1333</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Te cuento qué podés esperar de una cuenta de Meta Ads según cuánto gastás por día, para que no te frustres esperando algo que ese presupuesto todavía no da. Con 5 dólares diarios, apenas estás probando si el anuncio funciona, no esperes muchas consultas todavía. Con 15 dólares, el sistema ya empieza a aprender quién es tu cliente y ahí aparecen las primeras consultas reales. Con 40 dólares, podés tener resultados constantes, pero necesitás rotar el anuncio cada par de semanas. Y con 100 dólares para arriba, ya no alcanza un solo anuncio bueno: necesitás contenido nuevo todo el tiempo, testimonios, casos, autos distintos. Fijate en qué escalón estás vos. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: plano medio fijo, fondo neutro. Overlay de texto grande con la cifra en dólares arriba a la izquierda, cambia de color en cada tramo. Subtítulos en mayúscula abajo. Un solo plano, sin cortes ni b-roll ni música.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Se copió la estructura de escalones de presupuesto con overlay numérico y autodiagnóstico; se ajustaron los montos a escala de negocio local y los resultados esperados a consultas y ventas de autos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="100" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7623388351776787744</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>1240</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>¿Se puede seguir consiguiendo consultas con Meta Ads después de las últimas actualizaciones del algoritmo? Circula el consejo de tener veinte piezas publicitarias distintas dando vueltas todo el tiempo, algo que para un estudio chico o una concesionaria de barrio es directamente imposible de sostener. Acá va otra forma de encararlo: en vez de perseguir esa cifra, enfocate en tener cuatro ideas que sean de verdad distintas entre sí, no la misma foto con otro texto arriba. Por ejemplo: el abogado hablando a cámara, un testimonio de cliente, una foto del expediente resuelto, y una pregunta frecuente respondida en texto. Con esas cuatro variantes ya le mostrás al sistema que hay diversidad de verdad, y ahí sí, cuando una empiece a funcionar mejor, ajustás detalles más finos como el gancho o el color. Mandame ANUNCIO por DM y te ayudo a armar tus cuatro ideas.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: plano medio fijo, vertical. Subtítulos palabra por palabra con una palabra clave resaltada en color. Inserto gráfico simple de 4 tarjetas o recuadros numerados representando las 4 ideas. Toma continua, sin cortes de cámara ni música.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de pregunta sobre si se puede seguir funcionando tras una actualización de algoritmo y la propuesta de priorizar pocas piezas realmente distintas antes que muchas parecidas; se adaptaron los ejemplos de variantes creativas a estudios jurídicos y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="100" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7628347207007128840</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>276</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Si no hacés esto, estás tirando a la basura la mitad de las consultas que te generan tus anuncios. El error más grande que veo en estudios y concesionarias es no respetar el tiempo de respuesta. Es la métrica más importante y casi nadie la mide: cuánto tarda tu equipo en contestarle a alguien que dejó sus datos en el formulario o te escribió por WhatsApp. Te sorprendería cuánta gente responde recién a las horas, o al otro día. El número que importa, imaginate un cronómetro corriendo, son 5 minutos. Si contestás dentro de los primeros 5 minutos después de que alguien pregunta, la cantidad de consultas que se convierten en turnos o en ventas de auto sube muchísimo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Plano vertical medio tipo webcam; subtítulos grandes en negrita con la palabra clave resaltada en verde; 3 bloques con cortes: 1) talking head, 2) pantalla dividida con captura de un formulario o chat de WhatsApp con círculos y flechas dibujadas a mano, 3) notas escritas a mano en un cuaderno con diagrama del tiempo de respuesta.</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Mantuve el gancho de error/miedo y la estructura de problema, métrica desconocida y número concreto de 5 minutos con el mismo recurso de diagrama a mano, y cambié 'opt-in' por consultas de WhatsApp o formulario en estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>BitBranding</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bitbranding/video/7633975768598449439</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Acá es donde la mayoría de las concesionarias pierden plata, aunque ya usen IA para armar sus anuncios. Lo que más pesa para que Meta te muestre barato es cuánto se queda mirando la gente tu video, sobre todo los primeros tres segundos. La retención de gancho promedio está por debajo del 20 por ciento: 8 de cada 10 se van a los tres segundos. Un buen gancho retiene entre 30 y 40, los que superan el 50 son los que Meta reparte más barato. Analicé los anuncios que mejor funcionaron para clientes concesionarias: arrancan con algo raro pero identificable, y usan las palabras exactas que los clientes escriben en los comentarios y en Google, no lenguaje de folleto. Le paso esas reseñas reales a la IA y le pido que arme el copy con ese lenguaje. Me bajó a la mitad el tiempo que tardo en armar cada anuncio. Mandame ANUNCIO por DM si querés uno así para tu concesionaria.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio/primer plano con pared oscura lisa de fondo; subtítulos blancos bold centrados; alternar talking head con placas gráficas de fondo de color con íconos ilustrados y texto grande estilo poster (ej. 'necesidad'/'curiosidad'); agregar 2-3 stickers o íconos animados superpuestos (Meta, IA); requiere edición tipo motion graphics.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el dato de retención de gancho en los primeros 3 segundos y el mecanismo de usar IA con reseñas reales de clientes para generar el copy, y cambié el rubro de indumentaria por concesionarias con CTA de pedir revisión del anuncio por DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="100" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7636521756043250952</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Te muestro cómo sacar ángulos de anuncios que no se te ocurrieron nunca. Podés mirar datos propios —reseñas, comentarios, qué preguntan cuando llaman— o datos de mercado —qué dice la gente de la competencia—. La posta es convertir eso en una frase que empiece con 'quiero'. Ejemplo, un cliente de concesionaria: 'quiero cambiar el auto viejo'. ¿Para qué? 'Para no gastarme la guita en el mecánico cada dos meses'. ¿Para qué más? 'Para llevar tranquilo a mis hijos al colegio sin miedo a que se rompa en la ruta'. Ahí está el deseo real: no es el auto, es la tranquilidad de padre. Con eso armás el anuncio: un papá dejando a sus hijos en la escuela, voz en off: '¿tu auto te va a fallar el día que menos podés?'. Eso vende más que cualquier folleto de cuotas. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto; subtítulos bold; insertar un gráfico simple tipo flujo (dato propio/mercado → frase 'quiero... para poder...' → ángulo) hecho a mano o en Canva; opcional una imagen de stock de un padre con auto o colegio; sin b-roll propio necesario.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Mantuve la técnica de 'pelar la cebolla' con frases 'quiero... para poder...' y el framework de datos propios/mercado; cambié el ejemplo de salud cardíaca por un comprador de auto en una concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="100" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7661753639463177490</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>249</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Esto puede ser la diferencia entre una cuenta que escala y una que fracasa: cuánta gente ya vio una oferta como la tuya. Si sos el primero en tu rubro en anunciarte en Meta, podés decir cualquier cosa y funciona: 'vendo autos usados con financiación', listo, la gente reacciona. Pero si sos una concesionaria en una ciudad donde ya hay diez anunciando lo mismo, esa frase no mueve un carajo. Ahí tenés que diferenciarte: no es 'vendo autos', es 'te entregamos el auto en 48 horas con la financiación aprobada por WhatsApp, sin pisar el banco'. Pasa lo mismo con estudios jurídicos: si ya viste veinte abogados anunciando 'consulta gratis', esa oferta se quemó, necesitás algo puntual como 'te decimos en 24 horas si tenés caso, o no te cobramos nada'. Cuanto más saturado está tu rubro, más específico tenés que ser. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto; subtítulos bold; insertar gráfico tipo escalera o tabla de niveles (dibujado a mano o en Canva) con los ejemplos de estudio jurídico y concesionaria escritos abajo; sin b-roll necesario.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Conservé el marco teórico de niveles de sofisticación de mercado aplicado a un ejemplo propio; lo apliqué a concesionarias y estudios jurídicos saturados de ofertas genéricas en vez de HVAC e IA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="100" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7670633794583448840</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>244</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Si estás gastando poca plata en Meta Ads, tipo cinco o diez mil pesos por día, puede que estés peleando tres batallas a la vez sin darte cuenta. Capaz tenés mala oferta, no sabés hacer buenos creativos, y encima cuando te escriben por WhatsApp tardás horas en contestar. Ahí peleás en los tres frentes juntos. La señal es que sentís que necesitás anuncios nuevos todo el tiempo, porque 'no funciona nada' o funciona dos días y se muere. Con malos creativos, tenés que probar un montón para encontrar uno bueno, como buscar una aguja en un pajar. Con mala oferta, tus creativos tienen que sobrecompensar. Y con mala atención por WhatsApp, no importa cuántos anuncios hagas, esa gente se enfría antes de comprar o pedir el turno. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto; subtítulos con las cifras de presupuesto destacadas en color; insertar captura tipo notas del celular con el diagrama escrito a mano 'Oferta → Creativos → Atención WhatsApp' y la lista de síntomas, simulando escritura en vivo.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el diagnóstico de tres frentes simultáneos (oferta, creativo, conversión) y el síntoma de 'necesito más creativos'; cambié la landing page por la atención por WhatsApp, cuello de botella típico de comercios locales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="100" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7640890960645295378</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Una vez perdí un cliente de una concesionaria grande porque le dije que frenáramos toda la campaña y arrancáramos de cero. Lo volvería a hacer. Te cuento las señales para saber si tenés que tirar todo o solo ajustar. Primera señal: los anuncios que siempre te funcionaban ahora se mueren rápido. Ahí probás relanzar esos mismos ganadores; si funcionan de nuevo, era solo cansancio de creativos, fácil de resolver. Pero si los relanzás y a la semana caen otra vez, el problema es más profundo: probás cambios chicos, el título, si mandás al WhatsApp o a un formulario, cómo contestás el primer mensaje. Si ni así repunta, tenés que cambiar la oferta entera: no es lo mismo 'consulta gratis' que 'te digo en el momento cuánto te dan por tu usado'. A veces el problema no es el anuncio, es lo que estás ofreciendo. Si no sabés en cuál de las tres estás, mandame ANUNCIO por DM.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto; subtítulos bold; insertar libreta o notas del celular donde se escribe (real o simulado) una lista numerada de señales, construyéndose en sincro con el relato; sin gráficos adicionales.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de storytelling de pérdida de cliente con postura contraintuitiva y las tres señales de diagnóstico; cambié el ejemplo a una concesionaria y las variables a WhatsApp/oferta en vez de landing page/VSL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="100" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7667680685058182408</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Hay algo que tenés que entender antes de escribir cualquier anuncio en Meta: vos no inventás el deseo, solo lo canalizás. Un deseo es una frase que arranca con 'quiero'. Ejemplo: 'quiero que este juicio se termine de una vez'. Eso ya lo está pensando tu cliente potencial ahora mismo, vos no se lo metiste en la cabeza. Tu trabajo es como una lupa: agarrás ese deseo que ya existe en un montón de gente y lo enfocás hacia tu estudio o tu concesionaria. El deseo está ahí, dando vueltas como el sol. Tu anuncio no crea nada nuevo, solo pone el foco. Por eso cuando un abogado me dice 'no sé qué poner en el anuncio', le digo: dejá de inventar, andá a buscar qué es lo que la gente ya quiere resolver, y hablale directo a eso. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto; apertura opcional de 2 segundos con placa de texto simple sobre fondo oscuro ('Deseo Humano'); subtítulos bold; insertar notas manuscritas 'quiero... para poder...' y, opcional, una imagen de stock de lupa y sol.</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Mantuve el concepto de deseo humano y la metáfora del sol/lupa (canalizar, no crear el deseo); cambié el ejemplo de bajar de peso por resolver un juicio o no quedar varado con el auto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="100" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7664708959932108050</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Los ángulos son lo que cambia el mensaje de tu anuncio sin cambiar el producto. Es como pescar: no usás la misma carnada para todos los peces. Mirá, mismo estudio, mismo servicio de accidentes de tránsito, tres ángulos distintos. Uno, para el que piensa 'no tengo plata para pagar un abogado': 'no cobramos nada hasta que cobres vos'. Dos, para el que piensa 'esto me va a llevar años': 'te decimos en 48 horas si tenés caso'. Tres, para el que piensa 'ya me cagó un abogado antes': 'te mostramos cada paso por WhatsApp, sin sorpresas'. Es el mismo servicio, el mismo cliente ideal, pero atacás tres miedos distintos. En vez de un anuncio genérico, tenés tres carnadas distintas tirando en la misma cuenta. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto; subtítulos bold; insertar notas manuscritas mostrando los tres ángulos uno por uno a medida que se nombran; sin b-roll ni capturas de pantalla.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Mantuve la analogía de pesca y la estructura de tres ángulos distintos para el mismo producto y audiencia; cambié bajar de peso por un servicio de accidentes de tránsito con tres objeciones típicas de un estudio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Auditoría/análisis de cuenta — 12 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="100" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7634971114262908190</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>12700</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>¿Esta concesionaria tiene lo que hace falta para vender más autos con Meta Ads? Le audité la cuenta y te cuento qué encontré. Primero, la oferta: no venden 'autos', venden la cuota más baja de la zona con entrega en 48 horas. Segundo, el embudo: cada anuncio manda directo a WhatsApp, y un vendedor responde en menos de cinco minutos, no a un formulario que nadie completa. Tercero, la cuenta: quince anuncios activos, mezclando modelo por modelo y testimonios de clientes reales. No están solo publicando, están filtrando quién escribe. ¿Alcanza esto para ser la concesionaria que más vende de la zona? Si suman más video y bajan el tiempo de respuesta, están en el camino. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro chico abajo, pantalla completa arriba con capturas del Ads Manager o del chat de WhatsApp Business de la concesionaria (datos sensibles difuminados); subtítulos dinámicos; 3 cortes, uno por cada punto del checklist (oferta, embudo, cuenta); sin música o mínima.</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de pregunta especulativa y el desglose tipo checklist (oferta, embudo, cuenta), cambiando el análisis de una marca de suplementos por la auditoría de una concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="100" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7636037201276505374</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>11700</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>El Estudio A y el Estudio B corren casi la misma cantidad de anuncios en Meta, pero llevan la consulta por caminos totalmente distintos. El Estudio A manda todo el tráfico directo a WhatsApp: el que hace clic, en diez segundos ya está escribiendo. El Estudio B manda a un formulario que filtra mejor: pide zona y tipo de problema antes de que el abogado atienda. Sumale esto: el Estudio A apuesta a la urgencia, casos de accidentes, respuesta rápida. El Estudio B apuesta a la marca, videos institucionales, un abogado que explica derechos en cámara. Uno optimiza la consulta de hoy, el otro que en seis meses lo elijan antes de buscar en Google. ¿Cuál te parece que gana a largo plazo? Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro chico abajo; capturas de pantalla arriba alternando entre las dos cuentas de anuncios o los dos chats de WhatsApp, con flechas/círculos rojos marcando diferencias; subtítulos dinámicos; corte por cada variable comparada (tráfico, oferta, creatividad); sin b-roll.</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de comparación cabeza a cabeza por variables con cierre de dos filosofías opuestas, cambiando indumentaria deportiva por dos estudios jurídicos con embudos distintos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="100" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7598212323538455838</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>¿La estrategia de anuncios del estudio jurídico más grande de tu ciudad realmente convierte? Tiene más de 30 anuncios corriendo ahora mismo, con ganchos distintos para cada tipo de caso, hasta anuncios simples de foto que parecen aburridos a propósito. Esa parte la tienen resuelta: separan bien a quién le hablan. El problema es lo que pasa después: una vez que te llamaron la atención, no aceleran al que está por decidir. No hay testimonios, no hay casos resueltos mostrados, nada que saque la duda de si realmente ganan juicios. Necesitás cubrir todo el recorrido: atención, prueba y recién ahí conversión. Si sumaran testimonios reales y resultados de casos anteriores, esos 30 anuncios dispersos podrían convertirse en 8 funcionando mejor. No es tener más ganchos, es acompañar todo el camino hasta que el cliente se decide. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Gonzalo a cámara con micrófono tipo podcast; insertar captura simulada de la Biblioteca de Anuncios de Meta (grilla genérica con 'X resultados' visible, sin nombrar cuenta real); etiquetas de texto destacando frases clave; flechas de énfasis; subtítulos bold.</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Copié el formato de auditoría que reconoce lo que funciona y señala el hueco de contenido de conversión; cambié a Alex Hormozi por un estudio jurídico genérico sin nombrar a nadie real para no hacer afirmaciones sobre una cuenta ajena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="100" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7669839443364302110</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>8648</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Comparé las cuentas de anuncios de dos estudios jurídicos de la misma ciudad, y las estrategias no podrían ser más distintas. El Estudio Uno tiene veinte anuncios activos: casos ganados, honorarios, testimonios. El Estudio Dos corre apenas cuatro, siempre el mismo formato. El Uno manda a un formulario corto que filtra zona y tipo de problema antes de mostrar el WhatsApp. El Dos manda directo al WhatsApp sin filtrar nada, y el abogado termina perdiendo media hora por día con gente que no calificaba. Pero el Dos tiene algo que el otro no: una red de contadores y escribanos que le derivan casos todos los meses. Uno construyó una máquina de captar consultas frías, el otro una red de confianza. ¿Cuál aguanta mejor si sube el costo de la publicidad? Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en recuadro sobre capturas de pantalla de las dos cuentas (formulario vs. WhatsApp directo) mostradas lado a lado o alternadas; subtítulos dinámicos; 4-5 cortes, uno por punto de comparación; sin música o mínima.</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de comparación extensa por embudo y distribución, cambiando suplementos por dos estudios jurídicos, uno con formulario filtro y otro con red de derivación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="100" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7631951563140959519</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>4643</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Armemos el mapa de anuncios para un estudio de abogados que recién arranca en Meta. Usé inteligencia artificial para analizar todos los comentarios y mensajes que les llegaron en el último año. Encontré dos cosas clave: la gente no sabe si le conviene ir a juicio o llegar a un acuerdo, y no sabe cuánto cuesta la consulta. La estrategia tiene que atacar eso. Primero, una serie de videos cortos contando casos reales resueltos, sin nombres, mostrando que el estudio gana casos de verdad. Eso saca la duda de si el abogado sirve o no. Segundo, un anuncio bien directo que diga cuánto cuesta la primera consulta, porque esa incertidumbre es lo que frena el mensaje. Con esas dos piezas ya cubrís el mayor freno antes de pedirle a alguien que escriba. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: selfie en interior, formato vertical, mitad superior con una captura o mockup (por ejemplo mensajes o reseñas), mitad inferior cara hablando. Subtítulos en pantalla. Plano fijo, sin cortes de cámara. Sin música.</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de 'mapa de ruta' en dos ejes numerados basados en análisis de datos reales; se cambió la marca de skincare de una influencer por un estudio de abogados y sus consultas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="100" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Mitch Barham (Beardpreneur)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@beardpreneur/video/7670313706110209294</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>4294</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Las consultas por Meta le vienen cayendo a un montón de estudios y concesionarias, y todo el mundo entra en pánico pensando que los anuncios dejaron de funcionar. Pero eso no cuenta toda la historia. Tengo acá el gráfico de un cliente, dos meses de datos. Mirá esto: el 3 de julio las búsquedas en Google del estudio caen, y fijate, las consultas por Meta caen exactamente el mismo día. Después las búsquedas se recuperan, y las consultas por Meta hacen lo mismo, casi calcadas. O sea que el anuncio no dejó de funcionar: la gente lo ve, pero antes de escribir busca el estudio en Google, mira reseñas, compara. Antes escribían directo al ver el anuncio, ahora se toman dos o tres días más investigando. No es que Meta se rompió, cambió el comportamiento del que busca abogado o busca auto. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Talking head con un gráfico de datos superpuesto de fondo, corte a grabación de pantalla real de un dashboard o planilla mostrando consultas día por día con zoom en los números; subtítulos dinámicos; sin música o mínima.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de 'esto no es lo que parece' con evidencia gráfica de datos reales de una cuenta de cliente, cambiando la correlación Meta-Google de un ecommerce por la correlación entre búsquedas y consultas de un estudio o concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7641134699745643783</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>2311</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Le acabo de auditar la cuenta a una concesionaria grande, de las que más facturan en su zona, y encontré tres errores que le están costando consultas todos los días. Uno: la frecuencia. Al abrir anuncio por anuncio, ocho de cada diez ya le repetían la misma pieza tres veces o más a la misma gente, en vez de salir a buscar gente nueva que todavía no vio nada de la marca. Dos: cómo estaban armadas las campañas. Dentro de la misma campaña mezclaban anuncios separados por modelo, otros por zona, y otros por tipo de pieza. Tenés que elegir un solo criterio por campaña, si no es imposible saber qué es lo que realmente funciona. Tres: la cadencia de piezas nuevas. Para una cuenta de este tamaño esperás piezas nuevas cada semana; acá solo sumaban cada quince días, y así es imposible no quemar la audiencia. Mandame ANUNCIO por DM.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en primer plano, fondo liso con logo de la agencia, título fijo arriba con la escala de la cuenta auditada; mismo plano estático sin cortes de cámara visibles.</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el formato de auditoría con errores numerados y cifra de escala como autoridad, cambiando la cuenta de ecommerce por una concesionaria grande con problemas de frecuencia, estructura de campañas y cadencia de piezas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="100" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7644104846248774920</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>2081</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Tomé una cuenta nueva la semana pasada, una concesionaria con bastante presupuesto en Meta, y encontré el error que veo en casi todas las cuentas: escalar el anuncio equivocado. Mirás tu anuncio 'top', el de mejor costo por consulta, y pensás 'meto más plata acá'. Pero casi nadie mira la frecuencia de ese anuncio, porque puede estar disfrazado de anuncio que capta gente nueva cuando en realidad es puro retargeting: le aparece una y otra vez a la misma gente que ya estaba por escribir igual. Fijate la frecuencia en una ventana de siete días: si ya pasó de dos, dos y medio, es retargeting. Mirá también los catorce y los treinta días, y si sigue subiendo, confirmás que ese anuncio no suma gente nueva, solo le insiste a la que ya casi estaba lista. Mantenelo, lo necesitás en la cuenta, pero el que hay que escalar es el de arriba, el que lo alimenta. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en primer plano, fondo liso, título fijo arriba, mismo plano estático sin cortes de cámara.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de alerta sobre un error común con método numérico de verificación por ventanas de frecuencia, cambiando la cuenta de ecommerce por una concesionaria donde el anuncio 'top' resultaba ser retargeting disfrazado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="100" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7650270956841143560</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>2063</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>¿Puede la fragmentación ser lo que te está subiendo el costo por consulta? Tomamos una concesionaria que ya venía gastando fuerte en Meta con otra agencia, y lo primero que encontramos fue un quilombo de campañas creadas sin ningún criterio: nadie podía explicar por qué existía cada una ni en qué se diferenciaba de la de al lado. La mayoría se superponían, mismo público, mismo tipo de pieza, compitiendo entre ellas dentro de la misma cuenta, y eso le subía la frecuencia y el costo por consulta. Meta funciona mejor cuando toda la señal de una audiencia está junta en un solo lugar, no repartida en diez campañas parecidas. No cortamos todo de un saque, porque ahí también podés perder lo que sí venía funcionando, pero sí consolidamos lo que estaba ganando y bajamos la cantidad de piezas activas. El costo por consulta bajó, porque las campañas dejaron de competir entre sí por el mismo público. Mandame ANUNCIO por DM.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en primer plano, fondo liso, título fijo arriba, subtítulos incrustados palabra por palabra; mismo plano estático sin cortes.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de pregunta retórica/alarma con estructura diagnóstico-causa-solución, cambiando la cuenta de ecommerce fragmentada por una concesionaria con campañas superpuestas heredadas de otra agencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="100" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7633738600223411464</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>1485</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Esta semana pasé por cinco cuentas de Meta Ads de estudios jurídicos y concesionarias, y los mismos errores se repiten en casi todas. Uno: suben diez anuncios al mismo conjunto sin ningún criterio, mezclan promoción de 0km con contenido de post-venta, y confunden al algoritmo sobre a quién mostrarle qué. Dos: todo el contenido es la misma foto del auto en la vereda o la misma placa en la puerta, sin testimonios ni videos del día a día. Tres: el botón manda a la home del sitio en vez de ir directo a WhatsApp, y ahí se pierde la mitad de las consultas. Fijate si tu cuenta tiene alguno de estos tres. Mandame ANUNCIO por DM y te cuento cuál puede estar pasando en la tuya.</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: primer plano, fondo liso con logo de la agencia, banner de texto fijo arriba con el título. Subtítulos abajo. Plano fijo, sin cortes ni capturas de pantalla. Sin música.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Se copió el gancho de autoridad reciente por volumen de cuentas revisadas con listado numerado de errores; se cambiaron los rubros de moda/joyería a estudios jurídicos y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7648727626592406806</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>1236</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Te quiero mostrar algo que está funcionando bien ahora mismo en la cuenta de una concesionaria que manejo: la campaña de remarketing. Le vuelve a aparecer el anuncio a toda la gente que entró al catálogo de autos en la web o escribió por Instagram y no cerró. En el Ads Manager, últimos 30 días: alcance de 18 mil personas, frecuencia de 3 veces, y el costo por cada turno agendado bajó a 4.500 pesos, contra los 9.000 que costaba con la campaña abierta a todo el mundo. La clave es que no le hablás a un desconocido, le hablás a alguien que ya miró un auto puntual y se fue sin decidir. Si tenés una concesionaria o un estudio con tráfico a la web o mensajes que se enfrían, armar una campaña apuntada solo a esa gente es de las cosas más rentables que podés hacer. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Sin aparecer en cámara: grabación de pantalla del Ads Manager real con las métricas (alcance, frecuencia, costo por resultado, gasto); cintillo de texto rojo fijo arriba como gancho; narración en off; sin cortes de escena; sin música.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de compartir en pantalla métricas reales de una campaña que está funcionando con una lección aplicable; cambié la campaña ASC de e-commerce por una campaña de remarketing a gente que consultó y no cerró en una concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="100" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665700523940629782</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>715</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>'Probamos un montón de anuncios, ninguno funciona, Meta no funciona para mi estudio.' Antes de tocar el anuncio, reviso la oferta. ¿La consulta es gratis? ¿Eso se entiende en los primeros cinco segundos? ¿Por qué alguien te tiene que escribir a vos y no al estudio de la otra cuadra? Podés tener el video mejor filmado del mundo, que si la oferta no engancha, no sirve de nada. Con una oferta realmente buena, hasta un video grabado con el celular sin editar genera consultas. La mayoría de las cuentas que no generan consultas no fallan por el video, fallan porque nunca quedó claro qué ofrecés ni por qué hoy y no después. Vi estudios y concesionarias duplicar las consultas solo ordenando la oferta: consulta sin cargo, plazo claro, sin letra chica. Arreglá la oferta primero. Mandame ANUNCIO por DM y te digo qué le falta al tuyo.</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Efecto de multiplicación en cámara (2-3 clones del presentador con remeras distintas) si hay tiempo de posproducción, o alternativa simple: plano fijo único medio primer plano en oficina. Subtítulos blancos quemados. Opcional: insertar 2-3 segundos con una lista en pantalla tipo checklist de auditoría (precio, garantía, urgencia).</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho contraintuitivo 'el problema no es el anuncio, es la oferta' y el framework de auditar antes de la creatividad; cambié los ejemplos a estudios jurídicos y concesionarias auditando su oferta de consulta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Opinión a cámara — 12 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="100" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7664540572052442390</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>5119</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>¿Cuál es la razón número uno por la que fracasan los anuncios de Meta de una concesionaria? El problema no es el algoritmo, es que no tenés nada que te distinga del resto. Y con eso digo específicamente que la gente no encuentra ningún motivo para comprarte el auto a vos y no al de la concesionaria de la otra cuadra. Tuve esta conversación mil veces: el dueño me dice 'mis anuncios no venden', y yo le digo 'esperá, dejame ver'. Busco el mismo modelo en otra concesionaria de la zona, y encuentro la misma financiación, a veces mejor. Por eso no funciona: no hay ningún motivo para elegirte a vos en particular. Necesitás algo propio: una entrega más rápida, un service incluido, algo que el resto no ofrezca. Si no, no importa cuánto gastes en anuncios, no va a funcionar. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Talking head simple en primer plano (oficina o exterior), sin capturas de pantalla ni gráficos; subtítulos dinámicos sincronizados; sin cortes a otra fuente, como mucho 1-2 cambios de plano dentro del mismo talking head; sin música o mínima; producción fácil.</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de pregunta directa con respuesta que desmiente una creencia común y el ejemplo conversacional, cambiando la comparación con Amazon por la comparación entre concesionarias de la misma zona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="100" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Mitch Barham (Beardpreneur)</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@beardpreneur/video/7652781295931624718</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>4859</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Mirá, en Meta ya no hace falta afinar tanto la segmentación manual. El filtro real lo hace la creatividad. Sé que esto confunde a todo el mundo, te explico. Desde hace un tiempo el sistema empuja todo hacia las campañas automáticas, esas donde vos ya casi no elegís a quién le mostrás el anuncio. Por más que pongas intereses específicos, igual lo va a mostrar a quien el sistema decida. Entonces, ¿quién filtra a la audiencia correcta? El texto y la imagen. Podés nombrar directamente a quién le hablás en la primera línea: '¿Buscás cambiar el auto y te preocupa la cuota?', en vez de un anuncio genérico. Ese texto es el que filtra, no la segmentación de atrás. Esto es lo que hacemos con cada cliente, y por eso entran consultas más calificadas. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en plano medio, fondo simple de oficina, toma continua sin cortes a pantalla ni gráficos; subtítulos dinámicos con 1-2 palabras clave resaltadas en color; sin b-roll; sin música o mínima.</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la afirmación contraintuitiva sobre segmentación con ejemplo accionable de primera línea de copy, cambiando el ejemplo de mascotas por uno de concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="100" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7660541148682849567</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>2874</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>La estrategia de anuncios que necesitás si tenés un estudio o una concesionaria en 2027. La mayoría todavía usa la vieja: encuentra un anuncio que funciona y hace diez variaciones calcadas, después no entiende por qué de golpe deja de rendir. La nueva no es más variaciones, es más diversidad real: formatos distintos para cada momento, contenido que genere confianza antes de vender, el abogado explicando un derecho, el vendedor mostrando el local, testimonios reales, comparaciones de cuota, y recién ahí el anuncio de 'consultanos ahora'. Divido la producción en tres partes: un tercio contenido grabado por el mismo estudio o concesionaria, un tercio testimonios reales de clientes, y un tercio piezas con inteligencia artificial para probar rápido. La idea ya no es apostar todo a un anuncio ganador, es que el sistema reparta el presupuesto entre varias piezas. Dejá de buscar el anuncio ganador único, armá un sistema que siga generando ganadores. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Clips de ejemplo (testimonio, foto del local o del estudio) en la mitad superior, presentador hablando a cámara con micrófono abajo; texto en pantalla acompañando palabras clave; subtítulos dinámicos; varios cortes entre b-roll y talking head.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho contraintuitivo contra la práctica común y el framework numérico accionable de 33/33/33, cambiando la producción creativa de ecommerce por la de un estudio o concesionaria repartida entre contenido propio, testimonios y piezas con IA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="100" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7626399562290171168</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>1219</v>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Así construye marca un estudio de abogados con Meta Ads, no solo consultas. La mayoría de los estudios usan los anuncios nada más para conseguir consultas, y está bien, pero si lo hacés bien, además construís marca. ¿Cómo? Combinando dos tipos de anuncios: uno donde el abogado titular habla directo a cámara y explica un tema legal con calma, y otro de recomendación, donde un cliente real, con su nombre y su cara, cuenta en veinte segundos cómo lo ayudaste con su caso. Si elegís bien a qué clientes mostrar y no suena actuado, la confianza que la gente le tiene a esa persona se traslada al estudio con el tiempo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio hablando a cámara con 2 ángulos para cortar tipo jump cut (perfil y frontal); subtítulos palabra por palabra en mayúsculas; insertar 1 captura de un anuncio real (propio o de un cliente) con testimonio como prueba; sin b-roll; música suave de fondo opcional; locación oficina/estudio.</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de reencuadre (los anuncios no son solo para leads) y la estructura de 2 tipos de anuncios más el mecanismo de transferencia de confianza, y cambié el ejemplo de founder+influencer por abogado titular más testimonio de cliente real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="100" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7634126651894287648</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>924</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Antes de gastar horas renegando porque una campaña de Meta Ads de tu estudio o tu concesionaria que venía funcionando bien de golpe dejó de traer consultas, o te tira errores que no entendés, probá esto: borrala entera y armala de nuevo desde cero. El Administrador de Anuncios se cuelga todo el tiempo, y muchas veces no metiste la pata vos ni tu agencia, es el sistema. En vez de perder la tarde tocando presupuesto, público y ubicaciones tratando de revivirla, creá una campaña nueva, calcada a la anterior. Nueve de cada diez veces con eso alcanza para que vuelva a entregar bien. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio, toma continua sin cortes, interior o exterior simple; subtítulos palabra por palabra en mayúsculas; sin gráficos ni capturas; sin b-roll; sin música necesaria.</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de 'tip subestimado' y la estructura de problema técnico seguido de solución simple y contraintuitiva, y cambié el contexto genérico por campañas de estudios y concesionarias con CTA de guardar el video.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="100" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Macie Reed</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7658140615288311053</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>583</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Si tenés un estudio jurídico o una concesionaria y estás por invertir en publicidad, primero entendé esto: hay dos formas de hacer publicidad digital y son opuestas. Google es búsqueda: le mostrás tu anuncio a alguien que ya está buscando activamente un abogado o un auto usado. Meta es al revés: le aparecés a alguien que ni sabía que tenía ese problema, que capaz ni pensaba en cambiar el auto hasta que vio tu video en el feed. Por eso en Meta el anuncio tiene que generar el interés desde cero, no alcanza con esperar que alguien te busque. Cuando entendés esta diferencia, dejás de decir 'invertí y no funcionó' sin saber para qué sirve cada plataforma. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Talking head vertical, plano medio fijo en oficina o estudio propio, sin cortes de escena. Subtítulos animados palabra por palabra. Placa de texto simple opcional (lupa vs. feed) al mencionar la diferencia Google/Meta.</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de 'episodio educativo' que sienta las bases conceptuales (push vs pull) y el tono de autoridad personal; cambié el destinatario de 'quien quiere ser meta ads manager' a 'dueño de estudio jurídico o concesionaria que va a invertir'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="100" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Macie Reed</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7664783404147150094</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>466</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Si invertís en Meta Ads para tu estudio o tu concesionaria, hay dos decisiones de presupuesto que conviene que entiendas. Primera: presupuesto diario o de por vida. Diario es 'gastá tal monto todos los días hasta nuevo aviso'. De por vida es 'gastá este total entre esta fecha y esta otra, y después se apaga solo'. Para la mayoría de los negocios locales conviene el diario, porque lo podés ajustar según cómo vengan las consultas esa semana. Segunda decisión: dónde se reparte esa plata, a nivel de toda la campaña o de cada anuncio. A nivel de campaña, Meta reparte solo buscando el mejor resultado. A nivel de anuncio, vos fijás cuánto gasta cada pieza, útil para comparar piezas distintas parejo. Esto te sirve para hacerle las preguntas correctas a quien te maneja la cuenta. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Talking head vertical, plano fijo en oficina o escritorio, sin cortes de escena, subtítulos automáticos quemados. Sin gráficos de apoyo, formato simple y económico de producir.</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de 'las dos decisiones de presupuesto' explicadas en talking head sin cortes; cambié el cierre de venta de curso por el CTA de seguir la cuenta y los ejemplos al rubro jurídico y automotor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="100" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7644916873481555202</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>382</v>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Estuve toda la semana metido en cuentas de estudios jurídicos y concesionarias, y me di cuenta de que a la mayoría de los dueños nadie les explicó la jerga básica. Te la traduzco. Alcance: a cuánta gente distinta le apareció tu anuncio. Impresiones: cuántas veces se mostró en total, porque la misma persona lo puede ver varias veces. Tasa de conversión: de los que hicieron clic, qué porcentaje terminó escribiéndote o pidiendo un turno. Público similar: le subís a Meta tu lista de clientes y arma una audiencia nueva parecida a ellos. El píxel: un código en tu web que le avisa a Meta qué hace la gente después del clic, para que aprenda a quién mostrarle el anuncio. La próxima vez que alguien te tire estos términos, ya sabés de qué te hablan. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Selfie o cámara en mano en exterior (vereda, cochera) o en la oficina, plano medio; subtítulos en mayúsculas quemados; título superpuesto tipo 'Glosario de Meta Ads'. Sin gráficos adicionales.</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato glosario en talking head al aire libre con subtítulos en mayúsculas; cambié los términos de ejemplo (lookalike, píxel, UGC) por casos con consultas y turnos de estudios jurídicos y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="100" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Macie Reed</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7665765984271240461</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Si tenés un estudio jurídico o una concesionaria y estás gastando en Meta Ads sin saber si te está sirviendo, este es tu cachetazo de realidad. La mayoría de las cuentas que reviso tienen la misma falla: están pagando por me gusta y alcance, no por consultas ni turnos. Te reviso tu cuenta gratis: te digo cuánto te está costando cada consulta hoy, si tu segmentación tiene sentido para tu zona, y qué anuncio está gastando plata sin traerte nada. No es una charla genérica de marketing, es mirar tu cuenta real, tus números reales, y decirte si conviene seguir así o cambiar algo ya. Esto lo hago gratis, sin compromiso, así que no tenés nada que perder salvo seguir gastando a ciegas. Escribime AUDITORÍA por mensaje y te reviso la cuenta gratis.</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Talking head vertical en oficina propia, luz cálida, sin cortes de escena; subtítulos blancos simples quemados; sin gráficos adicionales, formato promocional directo igual de simple que el original.</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de identificación directa con la audiencia y la estructura de oferta clara con beneficios listados; cambié la venta de un curso con lista de espera por la oferta real de Gonzalo de auditoría gratuita de cuenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="100" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>BitBranding</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bitbranding/video/7638775568783133982</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>La diferencia entre los estudios y concesionarias que consiguen consultas con Meta Ads y los que tiran la plata nunca fue tan grande. Los que pierden siguen haciendo lo de hace tres años: armar quince públicos a mano, tocar el presupuesto todos los días, tratar de ser más vivo que el algoritmo. No es que lo hagan mal, es que el algoritmo cambió. Meta hoy necesita menos segmentación manual y más información clara sobre quién te compra. Los que entiendan esto van a dominar su zona. Los que no, van a seguir preguntándose por qué cada consulta sale más cara. Un caso real: una concesionaria que llevamos, gastando cuarenta mil pesos por día, cerró el mes con ciento diez turnos de prueba de manejo agendados, sin tocar el presupuesto de golpe, solo ordenando la segmentación y el mensaje. Guardá este video si te suena conocido.</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Talking head en oficina con fondo simple; se intercala una placa de texto de fondo sólido con una frase clave ('EL ALGORITMO CAMBIÓ') a modo de corte visual entre segmentos; subtítulos blancos quemados en los segmentos con cara.</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el contraste 'los que ganan vs los que pierden' y el cierre con cifras de un caso real de campaña; cambié el ejemplo de e-commerce y Claude por un caso de concesionaria con turnos de prueba de manejo agendados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="100" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>BitBranding</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bitbranding/video/7658448519593725215</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Estás escalando mal tu cuenta de Meta Ads, y te lo puedo probar. La mayoría de las concesionarias que suben presupuesto lo hacen duplicando campañas, tocando el gasto todos los días, probando quince públicos distintos, y cada movimiento te cuesta plata. Es la fórmula de hace cinco años: duplicá el conjunto, probá amplio, escalá el que gana, y si no funciona, la culpa es del anuncio. No. El problema es el método. Meta ya no necesita que vos armes públicos a mano, el algoritmo entiende mejor que vos. Lo que necesita de tu parte es una oferta con margen y paciencia para dejarlo aprender. Hay una regla vieja del marketing: gana el que puede pagar más por conseguir un cliente. Si sabés cuánto te deja realmente un caso o la venta de un auto, podés gastar más que el de al lado y seguir ganando. Pero solo si conocés esos números. Guardá este video.</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio frontal en oficina o showroom, fondo simple; subtítulos bold blancos quemados; una placa de texto grande con frase de énfasis ('CONOCÉ TUS NÚMEROS') a modo de corte entre segmentos.</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho contrarian 'lo estás haciendo mal' y la estructura mito vs verdad con cita de autoridad del marketing; cambié el ejemplo de marcas de ropa por concesionarias y 'cliente' por casos o ventas de auto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="100" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7665463418513673479</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Si laburás con anuncios, en algún momento se te van a acabar las ideas de qué decir, te vas a quedar sin ángulos nuevos cada semana. Lo que yo hago hoy es usar la IA para investigar. Le entro a Claude o a ChatGPT y le digo: 'tengo un estudio de abogados que lleva casos de accidentes de tránsito, ya usé estos ángulos: urgencia, plata que te deben, miedo a hacer el trámite solo. Buscame en Google, en foros y en las páginas de otros estudios qué preguntas hace la gente sobre accidentes, y armame cinco ángulos nuevos que todavía no probé.' En dos minutos tenés una lista que antes te llevaba una tarde entera de brainstorming. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto, cámara fija, toma única sin cortes a pantalla ni gráficos; solo subtítulos bold blancos quemados; edición mínima, solo recorte de silencios.</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el tip único y directo de usar IA de investigación profunda para encontrar ángulos nuevos; cambié el ejemplo genérico de producto por un estudio de abogados especializado en accidentes de tránsito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Lista de tips o errores — 11 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="100" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Mitch Barham (Beardpreneur)</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@beardpreneur/video/7634698833859005709</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>13400</v>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Guardate esto. Te cuento cuatro cosas que tenés que saber si vas a usar inteligencia artificial para meter mano en tus anuncios de Meta. Uno: no necesitás saber programar, hoy cualquier IA como Claude o ChatGPT te puede leer los números de tu cuenta si sabés pedírselo bien. Dos: desconfiá de los consejos genéricos que te tira, no conoce tu rubro, ni tu ciudad, ni cuánto vale un cliente para vos, así que todo lo que te sugiera, revisalo con criterio. Tres: te sirve para ahorrar tiempo, no para reemplazar la estrategia: que te resuma qué conjunto de anuncios está gastando de más, buenísimo; que decida sola qué apagar, no tanto. Cuatro: te ayuda a entender los números, pero el que tiene que entender tu negocio y tu cliente ideal seguís siendo vos. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida: mitad superior gráfico simple de texto con los cuatro puntos apareciendo uno por uno (tipo lista en Canva), mitad inferior Gonzalo hablando a cámara con micrófono; subtítulos palabra por palabra quemados; fondo neutro de estudio.</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Mantuve el formato de lista numerada de cuatro puntos con gancho de 'guardá esto'; cambié el anuncio de un producto específico de Meta por consejos generales y verificables sobre usar IA en la propia cuenta de anuncios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="100" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7652379900728413471</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>10900</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Los errores que veo repetidos en casi todas las cuentas de anuncios de estudios jurídicos que audito. Uno: mandan el anuncio a un formulario en vez de a WhatsApp, y pierden la mitad de las consultas en el camino. Dos: usan foto de la fachada del estudio en vez de mostrar al abogado hablando de un caso real. Tres: no separan las campañas por especialidad, mezclan familia, laboral y penal en el mismo anuncio y confunden al sistema. Cuatro: apagan la campaña a la semana porque 'no vendió', cuando recién ahí Meta está aprendiendo a quién mostrárselo. Cinco: nunca miran el costo por consulta, solo miran cuánto gastaron. Así se van clientes por errores que se arreglan en una tarde. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre vertical con talking head en recuadro chico; arriba texto grande numerado (1 a 5) con un ícono simple por error; ritmo rápido, 3-4 segundos por punto; subtítulos dinámicos; no requiere capturas reales de Ads Manager, alcanza con gráficos de texto; música up-tempo de fondo.</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el ritmo acelerado de lista con una función por ítem, cambiando el listado de herramientas de IA por un listado de errores frecuentes en cuentas de estudios jurídicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="100" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7670568658346790174</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>3637</v>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Estudio que recibe cinco consultas por mes versus estudio que recibe cien: así de distinta es la cuenta de anuncios. El chico corre uno o dos anuncios, siempre la misma foto de la fachada. El grande tiene quince piezas activas a la vez: testimonios, casos ganados, el abogado explicando un tema puntual. El chico renueva una pieza cada dos meses; el grande cada dos semanas, para no quemar la audiencia. El chico solo mira cuánto gastó; el grande mira cuánto le cuesta cada consulta real y cuántas terminan en caso firmado. El chico manda todo a un formulario genérico; el grande manda directo a WhatsApp con el problema ya precargado, para que el abogado sepa de qué se trata antes de responder. Esa es la diferencia real: uno corre anuncios, el otro armó un sistema completo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Capturas de pantalla como B-roll: Meta Ads Library del estudio o concesionaria grande con círculo rojo marcando la cantidad de anuncios activos, captura del chat de WhatsApp con el problema precargado; presentador hablando a cámara abajo; subtítulos blancos; cortes alternando B-roll y talking head.</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de comparaciones paralelas en el mismo formato con evidencia real de Meta Ads Library, cambiando marcas de ecommerce por un estudio o concesionaria chica versus una grande de la misma ciudad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="100" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7631128226135411986</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>2420</v>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Hay un formato de anuncio que uso con casi todos mis clientes de estudios jurídicos: el anuncio de propósito, en 5 partes. Uno: gancho de identidad, arrancás nombrando a quién es esto, 'si te echaron sin indemnización', no arrancás hablando del estudio. Dos: mostrás el oficio, cómo arman el caso, no el resultado final. Tres: conectás con el momento real de esa persona, no un genérico 'te ayudamos con lo que necesites'. Cuatro: prueba social, casos ganados, años en tribunales. Cinco: cerrás con una sola acción, escribir por WhatsApp. Y por eso funciona: el que lo ve piensa 'esto me está hablando a mí', y ahí recién le pedís que te escriba. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: primer plano cerrado, fondo liso con logo de la agencia detrás. Banner de texto fijo arriba con el título del video. Subtítulos abajo. Plano fijo sin cortes de cámara. Sin música.</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Se copió el framework de 5 pasos numerados para un anuncio de propósito y el cierre con frase citable; se adaptó de moda/joyería a estudios jurídicos con ejemplos de casos e indemnización.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="100" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7666767722230959367</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>1463</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Si yo manejara los anuncios de tu estudio o tu concesionaria, lanzaría 3 tipos de anuncio, y ninguno es la típica foto del local con el teléfono. El primero: el anuncio de resultado, mostrás lo que la persona quiere lograr, no el trámite. El auto andando en la ruta un domingo, o la tranquilidad de resolver el problema. Eso engancha al que todavía ni te conoce. El segundo: el anuncio del dueño, vos o el abogado a cámara contando por qué eligieron este trabajo o un caso que los marcó. Ahí la gente empieza a confiar en el tuyo, no en cualquier estudio. El tercero: el anuncio de prueba, el cliente real contando cómo le fue, el WhatsApp de alguien agradeciendo. Eso cierra a los que el primero enganchó. Memorizate esto: el resultado genera el clic, el dueño genera confianza, el cliente real cierra la venta. Necesitás los tres. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Hablás a cámara explicando los 3 tipos; cortás a 2-3 ejemplos reales (auto en ruta, vos o el abogado a cámara, mensaje de WhatsApp de un cliente) mientras nombrás cada uno; tarjeta de texto grande con cada categoría; subtítulos quemados.</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el framework de 3 tipos de anuncio ligados a las etapas del funnel con cierre tipo mantra; cambié los ejemplos de moda/lifestyle por resultado-deseo, dueño/abogado y testimonio real de estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="100" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Macie Reed</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7659974291945049357</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>846</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>En Meta Ads tenés 6 objetivos de campaña para elegir, y quiero que sepas cuáles son y cuáles son los únicos 2 que importan si tenés un estudio o una concesionaria. Están reconocimiento, que solo busca que te vean muchas personas; tráfico, que busca clics a tu página; interacción, que busca likes y comentarios; y promoción de la app, que no te sirve para nada si no tenés una aplicación. Y después están los dos que sí importan: leads, para juntar datos de gente interesada, y ventas o conversión, para que directamente agenden un turno o pidan un presupuesto. En cuatro años laburando cuentas de estudios y concesionarias, prácticamente todo el presupuesto lo pongo en esos dos. Los otros cuatro sirven para marcas grandes que solo quieren que las conozcan, no para un negocio que necesita que suene el teléfono este mes. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Hablás a cámara en plano vertical; insertás a pantalla completa una captura real del panel de objetivos de campaña de Ads Manager mientras nombrás cada uno; subtítulos tipo caption animado.</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de listar todos los objetivos de campaña y revelar que en la práctica solo dos importan; cambié el contexto de e-commerce D2C por estudios y concesionarias que necesitan que suene el teléfono.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="100" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7648656606674062614</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>832</v>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Te traduzco la jerga que seguro escuchaste si alguna vez hablaste con alguien de marketing y no entendiste nada. CPM es lo que cuesta que mil personas vean tu anuncio. CTR es el porcentaje de gente que, después de verlo, hace clic. CPC es cuánto pagás por cada uno de esos clics. Retargeting es volver a impactar con un anuncio a alguien que ya entró a tu página o te escribió y no cerró. Costo por consulta es cuánto te sale, en plata, cada persona que te escribe pidiendo turno o presupuesto. Y el que más te tiene que importar como dueño de estudio o concesionaria es el costo por cliente: cuánto gastaste en total para que una consulta se convierta en un caso firmado o en un auto vendido. La próxima vez que alguien te hable en código, ya vas a entender de qué te está hablando. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Hablás a cámara, encuadre fijo, sin cortes de escena adicionales; subtítulos en mayúscula sincronizados; ritmo de glosario (término, pausa breve, definición); sin música o muy baja.</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato glosario que traduce jerga publicitaria en criollo; cambié términos orientados a e-commerce como el AOV por costo por consulta y costo por cliente, relevantes para estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="100" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Macie Reed</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maciereedmarketing/video/7667600871445761294</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>826</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>En Meta Ads tenés 4 formatos de anuncio, y como estudio o concesionaria te conviene usar los cuatro. El primero es video: el abogado hablando a cámara, o el auto andando por la ruta. El segundo es imagen: una foto del auto con el precio bien grande, o una placa con el resultado de un caso. El tercero es carrusel, varias fotos que se deslizan: perfecto si tenés 4 o 5 autos en stock para mostrar, o distintos servicios del estudio en cada tarjeta. Y el cuarto es catálogo, especialmente para concesionaria, porque conectás el listado de autos que ya tenés cargado y Meta arma solo un anuncio por cada uno, con su foto y su precio, sin que tengas que armar nada a mano. Cuantos más de estos cuatro formatos uses, más variedad le das a Meta para encontrar quién te va a consultar. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Hablás a cámara en plano vertical; insertás a pantalla completa 1 captura de ejemplo por formato (foto de auto con precio, carrusel, anuncio de catálogo); subtítulos tipo caption animado; sin cortes de escena extra.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de listar los 4 formatos de anuncio disponibles en Meta; cambié los ejemplos de e-commerce por autos en stock, placas de casos ganados y videos de auto en ruta, y saqué la promoción de curso porque Gonzalo no vende uno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="100" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7662343318533082390</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Horario de atención en el anuncio: importante. Responder el DM en menos de cinco minutos: extremadamente importante. Poner un descuento del diez por ciento: no tan importante como creés. Que el dueño hable a cámara en vez de un locutor: muy importante. Subtítulos en el video: importante. Postear todos los días en el feed: no importante. Sacarle diez fotos al mismo auto desde el mismo ángulo: no importante. Mostrar el precio en el video: muy importante. Tener la matrícula o el cartel del estudio visible: medio importante. Cambiar el anuncio cada dos días porque 'ya lo vieron': no importante, y te sale carísimo. Responder rápido: lo más importante de toda la lista. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Selfie en exterior o en el local, plano medio, cortes rápidos (jump cuts) entre cada ítem, un rótulo gráfico grande por ítem con su nombre; ritmo ágil; sin b-roll adicional, todo grabado en una sola sesión con los cortes hechos en edición.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de lista rápida 'importante / no importante' con cortes ágiles y un rótulo gráfico por ítem; cambié los factores genéricos de ads por hábitos concretos de atención y anuncios del rubro jurídico y automotor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="100" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7632740460217322759</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>333</v>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Si tenés un estudio de abogados o una concesionaria y vas a grabar tus propios anuncios, guardate estos tres ganchos. Uno: nombrá directo a tu público. Por ejemplo: 'si tenés una concesionaria y hace dos meses que no vendés un auto, escuchame un segundo'. Dos: generá curiosidad con una pregunta rara. '¿Sabías que Meta le muestra menos anuncios a los abogados que hacen esto?'. Tres: creá exclusividad. 'Casi ningún estudio jurídico en Argentina configura esto en sus anuncios, y por eso pierden consultas'. Con estos tres arrancás a grabar hoy mismo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Plano vertical medio, fondo oscuro/neutro tipo oficina, mic de mesa, sin cortes de escena; subtítulos blancos simples quemados; agregar gráfico tipo badge numerado (1, 2, 3) por cada gancho de la lista; sin b-roll.</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de lista numerada de ganchos con el mecanismo de nombrar audiencia, curiosidad y exclusividad, y escribí ejemplos totalmente nuevos para estudios de abogados y concesionarias en vez de e-commerce o agencias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="100" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665695408898706710</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Cinco formas de fundir la plata en Meta Ads si tenés un estudio o una concesionaria. Uno: apagar el anuncio a las cuarenta y ocho horas porque no vino ninguna consulta, esperá al menos una semana. Dos: subir el presupuesto de golpe. Pasar de tres mil a treinta mil pesos por día de un saque no es escalar, es resetear el aprendizaje y pagar más caro cada consulta. Tres: si el anuncio no funciona, cambiarle solo la foto. El problema casi nunca es la imagen, es el mensaje: probá otra oferta, otro gancho. Cuatro: tener un solo anuncio corriendo todo el mes, porque cuando se gasta, tus consultas se caen de un día para el otro. Cinco: copiar el anuncio de la concesionaria de al lado tal cual, sin conocer su stock ni su margen. Tomá ideas, pero armá el tuyo. Guardá este video antes de tocar tu próxima campaña.</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Toma única a cámara, estilo selfie, en exterior o en el local (vereda, showroom, entrada del estudio), sin cortes de escena; solo subtítulos blancos quemados siguiendo el audio, sin gráficos adicionales.</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de lista numerada de 5 errores en toma única sin cortes y el gancho de miedo a 'fundir la plata'; cambié los ejemplos de e-commerce por errores típicos de estudios jurídicos y concesionarias con montos en pesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Tutorial o screencast — 7 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="100" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Kruse (Mr. Paid Social)</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mr.paidsocial/video/7657288764053622029</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Te muestro cómo armo treinta variantes de anuncio para un estudio jurídico en diez minutos, sin escribir cada texto a mano. Paso uno: cargo en una planilla los datos del estudio, especialidad, zona, y los tres tipos de caso que más le convienen. Paso dos: le pido a la inteligencia artificial que arme diez ganchos distintos para cada tipo de caso, con el lenguaje que usa la gente cuando busca un abogado, no el lenguaje que usa el abogado. Paso tres: reviso esas variantes, elijo las mejores diez y las subo directo a la cuenta de anuncios. Lo que antes me llevaba un día entero escribiendo copy uno por uno, ahora lo tengo armado antes del mediodía. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida o pantalla completa con recuadro webcam chico; capturas paso a paso de la planilla de generación de copy y del Ads Manager al subir los anuncios; texto en pantalla marcando 'Paso 1 / Paso 2 / Paso 3'; subtítulos dinámicos; corte en cada cambio de paso; sin b-roll ni música (o mínima).</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la estructura de pasos numerados con demo en vivo como prueba, cambiando la generación de 500 anuncios genéricos por la generación de copy para un estudio jurídico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="100" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7646124046270074134</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>3915</v>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Si mirás el Ads Manager de esta concesionaria, el retorno que te muestra es el doble de la inversión. Y la mayoría toma decisiones solo mirando ese número: 'esta campaña rinde tres a uno, la dejo prendida', 'esta rinde uno a uno, la apago'. El problema es que Meta reporta con una ventana de atribución re corta, y no ve todo el recorrido real del cliente. Por eso en las cuentas grandes sumo una planilla de seguimiento aparte, donde cada consulta que entra queda anotada con la fecha del primer contacto y la fecha de la venta o el caso firmado. Ahí lo podés mirar de dos formas: por primer contacto, qué anuncio trajo a la persona la primera vez, o por último contacto, el anuncio que vio justo antes de decidirse. Muchas veces el anuncio que 'cierra' no es el mismo que generó la consulta, y si mirás solo el número de Meta, terminás apagando la campaña que en realidad hacía todo el trabajo de arriba. Mandame ANUNCIO por DM.</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Grabación de pantalla de principio a fin: primero el Ads Manager (gasto, alcance, CTR), después una planilla propia con las consultas por fecha de primer y último contacto; banner de texto fijo arriba con el título; voz en off, sin talking head.</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de problema técnico sobre el ROI engañoso con demo en pantalla de dos modelos de atribución, cambiando la herramienta de ecommerce por una planilla de seguimiento propia de consultas de estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="100" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7642466201179884822</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>1614</v>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Esta es la estrategia que más resultados me está dando ahora con estudios y concesionarias: en vez de un solo video prolijo del dueño, junto testimonios cortos de clientes reales. Le pido a cada cliente que quedó conforme, ganó el juicio o se llevó el auto, que grabe 15 segundos con el celular contando su experiencia, sin guion. Con 5 o 6 de esos armo varios anuncios distintos y los corro todos juntos en la misma campaña. Cada mes sumo 2 o 3 testimonios nuevos. Ahí es donde se nota la diferencia: a los seis meses tenés 20 o 30 clientes reales hablando de tu estudio o tu concesionaria dando vueltas en internet, y cuando alguien te busca, encuentra prueba social por todos lados, no un solo video armado. Esto funciona mejor que cualquier anuncio hiperproducido porque es gente común, no un actor. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Sin aparecer en cámara: 2-3 capturas de pantalla reales de testimonios de clientes en Instagram/Facebook en formato slideshow, tarjeta de texto superpuesta con la instrucción clave, narración en off, subtítulos quemados.</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el esqueleto de estrategia que compone con el tiempo usando voces de gente común en vez de una sola pieza pulida; cambié el whitelisting con microcreadores de e-commerce por testimonios cortos de clientes y casos reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="100" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7641896333955058977</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Te paso un método de 4 pasos, totalmente gratis, para ver qué anuncios está corriendo la concesionaria o el estudio de la competencia. Paso uno: entrá a la Biblioteca de Anuncios de Meta, es gratis y la encontrás buscándola en Google. Paso dos: buscá el nombre de tu competencia y ahí nomás vas a ver todos los anuncios que tiene activos en este momento. Paso tres: fijate hace cuánto está corriendo cada uno. Si un anuncio lleva semanas o meses activo sin que lo bajen, es porque le está funcionando, porque nadie sostiene un anuncio que no da resultado. Paso cuatro: agarrá la idea de esos anuncios que se sostienen en el tiempo, la oferta, el gancho, y usala como base para pensar los tuyos, no para copiar posta, sino para no arrancar de cero. Hacé esto con dos o tres competidores, no con uno solo. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Tarjeta de título al inicio; hablás a cámara sentado, encuadre fijo, sin cortes de escena adicionales; subtítulos en mayúscula negrita marcando cada paso (Paso 1 a 4).</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el método gratuito de 4 pasos con la Biblioteca de Anuncios de Meta para espiar competencia; cambié el ejemplo de marca genérica por estudios y concesionarias que compiten entre sí en la misma ciudad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="100" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7603330394024365344</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>965</v>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Así armás una secuencia de anuncios para vender autos en Meta, en vez de tirar todo junto. Podés configurar que tus anuncios se muestren en un orden específico y así vas educando al posible comprador paso a paso. Si vendés un modelo caro, arrancá mostrando valor: un tip para elegir bien la financiación. Después mostrás el auto en detalle, un video recorriendo el interior y el baúl. Le sigue un testimonio corto de un cliente que ya se lo llevó, mostrando la patente nueva. Y recién ahí metés el anuncio de venta directa: 'stock disponible, coordiná tu turno para probarlo'. Armar la secuencia así hace que la gente llegue mucho más caliente al anuncio de venta. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Plano fijo hablando a cámara, un solo ángulo, sin cortes de cámara; subtítulos blanco/negrita centrados palabra por palabra; insertar 1 captura de pantalla de un posteo real (foto de auto con comentarios) en el momento del testimonio; sin b-roll adicional; locación oficina o showroom con luz natural.</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el framework de 4 pasos (valor, demo, testimonio, venta) y el insert de captura como prueba, y cambié la oferta genérica de alto ticket por una secuencia de venta de autos en una concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="100" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7642638640090336545</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>573</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Te enseño a armar en el Administrador de Anuncios la métrica que en realidad le importa a un estudio jurídico o una concesionaria: el costo por consulta. Paso uno: entrá al Administrador de Anuncios y hacé clic en Columnas. Paso dos: elegí personalizar columnas. Paso tres: bajá hasta el final y creá una métrica personalizada. Paso cuatro: ponele de nombre 'costo por consulta'. Paso cinco: armá la fórmula, dinero gastado dividido mensajes o llamados iniciados. Guardás, y esa columna te va a aparecer al lado de cada anuncio que estés corriendo. Ahí dejás de mirar 'me gusta' y empezás a mirar cuánto te sale cada consulta real. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Arranca con el presentador a cámara con título superpuesto; después pantalla dividida (recuadro chico con el presentador arriba, grabación de pantalla del Administrador de Anuncios abajo: Columnas &gt; Personalizar columnas &gt; crear métrica). Subtítulos con palabras clave resaltadas.</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura tutorial de 5 pasos numerados y la mecánica de pantalla dividida cámara más Ads Manager; cambié la métrica de 'hook rate' por 'costo por consulta', más relevante para el nicho de Gonzalo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="100" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7629809400877681927</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Gestioné más de 200 millones de pesos en anuncios para estudios y concesionarias este año. Dame 40 segundos y te muestro cómo armar tu cuenta de Meta Ads desde cero. Primero, definí bien a quién le hablás: no es lo mismo alguien que busca un abogado para un despido que alguien que busca uno para un divorcio, armá dos o tres perfiles distintos y anotá qué le preocupa a cada uno. Después, fijate qué están publicando otros estudios o concesionarias de tu zona, y usá esas ideas para tus propios anuncios, adaptadas a vos. Armá una sola campaña, con un conjunto de anuncios por cada video que quieras probar, y dejala correr sin tocar nada durante siete días. Recién ahí entrás, apagás lo que no funcionó, y si en general dio ganancia, le subís el presupuesto un 20 por ciento. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Plano vertical medio, fondo de oficina/estudio, un solo ángulo sin cortes de cámara; subtítulos blancos palabra por palabra a ritmo rápido; agregar texto de título grande y llamativo al inicio con la cifra/gancho (ej. color verde neón); sin b-roll.</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de cifra grande más promesa de brevedad y el framework en pasos (definir a quién le hablás, mirar la competencia, estructura de campaña, regla de revisión a los 7 días), y adapté ejemplos y montos a pesos argentinos para estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Reseña de anuncios reales — 7 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="100" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7667312448218615062</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>1960</v>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>¿Quién tiene mejor estrategia de anuncios, la concesionaria del centro o la de la ruta? Miré lo que están corriendo las dos. La del centro tiene 3 anuncios activos, todos con la misma foto del salón vacío y el teléfono en la descripción, nada más. La de la ruta tiene 14 anuncios corriendo: autos filmados andando, el vendedor mostrando un service, y en cada uno un botón directo para agendar una prueba de manejo por WhatsApp. Encima, cuando le escribís por Instagram, el primer mensaje ya te pregunta qué auto estás buscando y te ofrece turno para el finde. La del centro recién te contesta al otro día. Las dos tienen buenos autos, pero la de la ruta se lleva la venta porque le sacó toda la fricción al proceso. ¿Viste alguna diferencia parecida entre dos negocios de tu rubro? Contame en los comentarios. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: vos hablando en la mitad inferior del cuadro; arriba insertás 3-4 capturas de pantalla del Instagram/Facebook de las dos concesionarias que comparás, cortando cada vez que nombrás una; subtítulos blancos en negrita quemados; sin música.</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de comparar dos marcas competidoras punto por punto y cerrar con una pregunta a la audiencia; cambié las marcas de joyería por dos concesionarias locales y sus métricas por turnos y velocidad de respuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="100" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7650905074020977942</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>1848</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Miren este comercial que hizo una concesionaria acá en Argentina: dron, autos en la ruta, música épica, debe haber costado una fortuna. Como pieza audiovisual, es un golazo. Ahora, fui a fijarme si lo estaban corriendo como anuncio pago en Instagram y Facebook, y no, nada, cero anuncios activos. Esa página tiene casi 40 mil seguidores, y gastaron esa plata en producción para subirlo una sola vez y listo. Eso es tirar la plata de otra forma: no en anuncios malos, sino en no convertir en anuncio algo que ya pagaron carísimo. Con esa misma pieza, bien recortada y con un botón de agendar prueba de manejo, podrían estar generando turnos ahora mismo. Si tenés un video así guardado en la compu sin usarlo como anuncio, estás dejando plata arriba de la mesa. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: vos a cámara con el comercial reproduciéndose en una ventana chica superpuesta; corte a captura de pantalla de la Biblioteca de Anuncios de Meta buscando el nombre de la concesionaria; subtítulos blancos negrita sincronizados; sin música.</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el mecanismo de reaccionar a una pieza cara y descubrir que no se está pautando pese al alcance de la página; cambié el comercial de Adidas con celebridades por un comercial local de concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="100" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7669060115953192194</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>845</v>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>¿Quién labura mejor sus redes, el estudio jurídico A o el estudio B? El estudio A tiene pocos seguidores, pero cada posteo termina con 'escribinos y te decimos si tenés caso', directo, sin vueltas, y así junta consultas todas las semanas. El estudio B tiene mil seguidores más, buena fama en el barrio, hasta salió una vez en el diario local, pero mirás sus últimos veinte posteos y ninguno te dice qué hacer si necesitás un abogado ya. El A convierte mejor: te deja clarísimo el paso siguiente. El B construye mejor reputación: cuando preguntás en el barrio, lo recomiendan. La verdad es que el estudio que más crece es el que hace las dos cosas: construye nombre y en cada posteo te dice exactamente cómo consultar. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Hablás a cámara (o desde la oficina); cortás a 2 capturas de pantalla del Instagram de los dos estudios que comparás; subtítulos blancos quemados; cierre con la frase final en texto grande en pantalla.</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la comparación de dos marcas donde una convierte mejor y la otra construye mejor marca, cerrando con que las mejores hacen ambas cosas; cambié las marcas de soda por dos estudios jurídicos locales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="100" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7661251520700222742</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>813</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Miren este anuncio de una concesionaria que me pasaron para revisar. Arranca mostrando el auto en movimiento, no parado en el playón: eso engancha. Encaje con el público: bien, porque el auto que eligieron es justo el que más buscan las familias de la zona, no el más caro del stock. Ritmo: los primeros 3 segundos ya muestran el auto, no hay logo ni música de intro perdiendo tiempo, eso está buenísimo. Ahora la oferta: dicen 'financiación especial este mes', pero no dicen hasta cuándo. Ahí pierden la urgencia: si no le ponés una fecha límite, la gente lo deja pasar. Le pondría fecha, un botón de agendar prueba de manejo, y listo. Con eso, se lo lleva de un 6 a un 9. Así como está, hoy, le doy un 7. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Vos sentado mostrando el anuncio real reproduciéndose en una ventana superpuesta en el celular; título grande arriba con el puntaje final; etiquetas de criterio apareciendo sincronizadas (Encaje de público, Ritmo, Urgencia/Oferta); subtítulos quemados.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de reseña de un anuncio real con criterios puntuales y nota final; cambié la marca de ropa YoungLA por un anuncio de concesionaria, evaluando encaje de público, ritmo y urgencia de la oferta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="100" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7665377118192176406</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>803</v>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Vi un anuncio de una concesionaria acá en Argentina y te juro que le pongo cero sobre diez. Arranca con el vendedor limpiando el capot de un auto en cámara lenta, con música tranquila de fondo. Quince segundos así. Después aparece el logo. Nada de precio, nada de modelo, nada de por qué tenés que ir a esa agencia y no a la de al lado. ¿Quién aprobó que esto sea el anuncio? Un anuncio no es para mostrar que tenés los autos limpios, es para que alguien agarre el teléfono y pida un turno para verlo. Si tu video no genera una consulta en los primeros cinco segundos, no sirve, por más lindo que quede. Cero sobre diez. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: plano medio, celular en mano estilo selfie o cámara fija en living/oficina. Pantalla dividida o inserto con un clip b-roll genérico (auto siendo limpiado) simulando el anuncio criticado. Subtítulos quemados palabra por palabra. Rótulo de puntaje '0/10' al cierre. Sin gráficos complejos.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de reseña con puntaje y el gancho de indignación 'quién aprobó esto'; cambié la marca (Bose) y la escena de la ensalada por un anuncio genérico inventado de concesionaria mostrando autos limpios sin ninguna llamada a la acción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="100" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7662722851530689814</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Vi un anuncio de un estudio de abogados y le pongo nueve sobre diez. Arranca directo mostrando el problema: 'te chocaron el auto y la aseguradora te ofrece la mitad de lo que corresponde'. A los tres segundos, corte seco a un teléfono sonando y el abogado atendiendo en cámara: 'hola, sí, yo te ayudo con eso'. Esa llamada es una interrupción de patrón buenísima, te agarra desprevenido. Después explica en criollo qué hace el estudio y cierra con el dato concreto: 'la consulta no tiene costo, escribime'. Sin música rara, sin efectos, veinte segundos. Mostró el problema real del cliente, cortó justo cuando bajaba la atención, y cerró con una acción clara. Cualquier estudio o concesionaria puede grabar esto con el celular. Nueve sobre diez. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Mismo formato reseña que la fila 46: el presentador con el celular en mano mostrando (pantalla dividida o superpuesta) el anuncio comentado; rótulos de sección tipo 'el gancho' / 'la interrupción de patrón' / 'el cierre'; subtítulos quemados.</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de reseña positiva con puntaje y el elogio al 'pattern interrupt' de la llamada telefónica; cambié la marca (AG1 con Hugh Jackman) por un anuncio genérico inventado de estudio jurídico con el mismo recurso de corte a llamada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="100" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7663560014900038934</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>¿Te venció la garantía y no sabés si conviene arreglar el auto o cambiarlo? Así arranca un anuncio real que encontré de una concesionaria, con pregunta, uno de los mejores ganchos que existen: genera curiosidad y ataca de entrada la excusa típica del cliente. Está grabado en el taller, entre los autos que están arreglando, nada de estudio armado, eso le da autenticidad, se nota que no es actuado. En los primeros ocho segundos ya te dice: financiación en 24 horas, entrega inmediata, sin vueltas. Están respondiendo la pregunta con beneficios concretos, rapidísimo. Después hay corte, corte, corte cada dos segundos, así que nunca te aburrís. Le pongo un ocho: gancho de pregunta, ubicación real y ritmo, todo lo que tiene que tener un anuncio de rubro automotor. Le faltó mostrar el precio en pantalla, ahí perdió un punto. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Formato reseña: Gonzalo con el celular en mano mostrando un anuncio enmarcado en un recuadro tipo pantalla de teléfono; etiquetas de texto superpuestas ('Gancho de pregunta', 'Ubicación real') en sincro con el análisis; subtítulos bold; cortes rápidos acompañando el ritmo del anuncio mostrado.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Copié el formato de reseña con etiquetas de sección y puntaje del uno al diez; reemplacé el anuncio de Huel por un anuncio ficticio de concesionaria con gancho de pregunta y locación real en el taller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Noticia/actualización de Meta — 5 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="100" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Noticia/actualización de Meta</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7624241425068166431</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>¿Sabés realmente cómo te cobra Meta cuando tu cuenta empieza a gastar fuerte? Muchos dueños de concesionaria no se enteran hasta que les pasa: a medida que tu cuenta gasta más, Meta te empieza a facturar con más frecuencia y en montos más grandes. Antes pagabas cuando el ciclo se cumplía cada tanto. Cuando la cuenta crece, te descuenta automático apenas se llega al umbral, a veces sin que lo notes. Esto no es un tema de puntos de la tarjeta, es un tema de flujo de caja: estás pagando sueldos, pagando stock, y de repente te cae un débito grande de Meta el mismo día. Si no dejás un colchón en la cuenta conectada, te quedás con la pauta pausada justo cuando más entraban consultas. La pregunta real es: ¿tu negocio aguanta ese golpe de caja o no? Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Gonzalo a cámara con micrófono sobre fondo neutro; subtítulos bold; insertar gráfico simple tipo línea de tiempo comparando 'antes' vs 'ahora' de la facturación (dos recuadros y una flecha en Canva); opcional clip de stock de 2 segundos con el logo de Meta como apertura.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de pregunta más novedad y el gatillo de ansiedad por flujo de caja con contraste antes/después; cambié la política específica no verificable por el mecanismo real y conocido de facturación automática de Meta al crecer el gasto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="100" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Noticia/actualización de Meta</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7666142376062209310</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>7591</v>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Meta sumó algo grande para los negocios que venden por WhatsApp: ahora los anuncios de clic a WhatsApp pueden mostrar el catálogo completo dentro del chat, antes de que la persona escriba una palabra. Armás el catálogo con tus autos o tus servicios, lo conectás al anuncio, y cuando alguien hace clic ya ve fotos y precios sin que el vendedor mande nada a mano. Para una concesionaria esto es oro: en vez de tipear modelo por modelo en cada consulta, la persona ya llega mirando el auto que le interesa. No hace falta producir nada nuevo, solo conectar lo que ya tenés. Las cuentas que se muevan primero con esto van a recibir consultas más calificadas mientras el resto sigue mandando fotos una por una. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Pantalla dividida: arriba grabación de pantalla del Ads Manager o del catálogo con anotaciones a mano en rojo (círculos/flechas) marcando dónde hacer clic; abajo talking head; frame de apertura con texto grande sobre la novedad; subtítulos dinámicos; música mínima.</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de urgencia/novedad sobre una función de Meta con explicación paso a paso de cómo funciona, cambiando el contenido etiquetado por creadores por catálogo dentro de anuncios de clic a WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="100" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Noticia/actualización de Meta</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Dara Denney</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@daradenney/video/7650514495403543838</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>7101</v>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>No quiero sonar exagerado, pero pronto el que responda primero por WhatsApp no va a ser una persona, va a ser una inteligencia artificial. Si sos dueño de un estudio o de una concesionaria y pensás que esto no te afecta, te cuento por qué sí. Ya hay negocios usando IA conectada a WhatsApp que responde precio, agenda el turno, y recién ahí deriva al vendedor o al abogado. Una concesionaria con la que trabajo bajó el tiempo de primera respuesta de dos horas a veinte segundos, a cualquier hora del día. Como agencia ya estoy armando estos flujos para mis clientes, antes de que sea algo que tiene todo el mundo. El que se mueve primero acá no compite por precio, compite por velocidad de respuesta. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Talking head estilo selfie en oficina o auto, encuadre vertical medio plano, sin necesidad de b-roll de evento; subtítulos dinámicos (agregados, ya que el original no tenía); sin cortes a pantalla; música de fondo sutil.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó la afirmación provocadora sobre el futuro más el ejemplo concreto y el plan de acción personal, cambiando agentes de WhatsApp para aerolíneas por respuesta automática a consultas de estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="100" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Noticia/actualización de Meta</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7621602508879727904</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>2827</v>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Dato que capaz no sabías sobre Meta: hoy podés poner el botón de enviar mensaje por WhatsApp directo en cualquier anuncio, sin que la persona tenga que buscar tu perfil o llenar un formulario. Muchos estudios y concesionarias todavía usan el botón que manda a la página web, y ahí se pierde la mitad de las consultas, porque la gente prefiere escribir antes que llenar un formulario. Armar el anuncio con el botón de WhatsApp directo te saca ese paso de encima: el que ve el anuncio te escribe al toque. Si tu anuncio todavía manda a un formulario largo o a la home, cambialo esta semana. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: plano medio sentado con micrófono, toma continua sin cortes. Subtítulos palabra por palabra en mayúsculas con una palabra clave resaltada en color. Sin gráficos ni capturas de pantalla. Sin música.</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el formato de dato/novedad sobre Meta con estructura qué-es, por-qué-importa, qué-hacer; se reemplazó la noticia real sobre Threads por un recordatorio sobre el botón de WhatsApp en anuncios aplicado a abogados y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="100" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Noticia/actualización de Meta</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Matt Bell</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@officialmattbell/video/7646443420076068118</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>1971</v>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Esto lo vengo viendo en TODAS las cuentas que manejo, tanto de estudios de abogados como de concesionarias: los anuncios grabados simple, con el celular y sin edición de lujo, le están ganando por goleada a los que están hiper producidos o hechos con inteligencia artificial. ¿Por qué pasa esto? Porque la gente ya aprendió a detectar cuando algo es puro marketing armado, y desconfía un poco. En cambio, cuando ve al abogado hablando como habla siempre en su estudio, o al vendedor mostrando el auto parado en el playón un sábado a la tarde, le cree más y consulta más. Ojo, esto no significa que dejen de invertir en producción linda: prueben las dos cosas y midan cuál les trae más consultas. Pero si todavía no probaron algo simple y real, seguramente estén dejando consultas arriba de la mesa. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Sin aparecer en cámara: captura o grabación fija de pantalla del Ads Manager de fondo, cintillo de texto rojo fijo arriba con la idea principal, narración en off, subtítulos quemados, sin cortes de escena, sin música o muy de fondo.</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de tendencia contraintuitiva sin cámara basada en datos agregados de varias cuentas; cambié el insight de estático-vs-video por autenticidad casera vs. producción/IA en estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Clip de podcast — 5 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="100" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Mitch Barham (Beardpreneur)</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@beardpreneur/video/7628243140423470349</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>5708</v>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Te voy a decir algo que capaz no esperás: la frecuencia del anuncio, ese número que tanto preocupa, es de las últimas cosas que miro. Al final todo se reduce a los resultados. Si el anuncio te sigue trayendo consultas, no lo toques por más que ese número esté alto. El otro día tenía un anuncio de un estudio de abogados que venía funcionando hace meses, consultas todas las semanas. Cuando bajó el rendimiento, no lo maté: lo dupliqué y le renové el público, y volvió a agarrar ritmo en un par de días. Con las concesionarias pasa igual: ese anuncio del 0km que siempre convierte, cuando se cansa, alcanza con duplicarlo y ampliar el público. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: cámara fija en primer plano, alcanza con el celular apoyado. Subtítulos palabra por palabra. Sin cortes de pantalla ni gráficos, es hablar a cámara de punta a punta. Sin música, la voz lleva el video.</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Se copió el gancho de opinión contraintuitiva sobre un tema técnico con una anécdota corta como prueba; se cambió el ejemplo del fotógrafo de bodas por un estudio jurídico y una concesionaria con anuncios evergreen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="100" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Abuvala</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theraviabuvala/video/7667260311375744269</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>4136</v>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Todas las plataformas, Meta, Google, todas, tienen una atribución pésima. Te van a mostrar un costo por consulta bajísimo, pero ese número no cuenta cuántas de esas consultas en realidad nunca contestaron el WhatsApp, o pidieron turno y no vinieron. Por eso a mis clientes les armo un seguimiento aparte: anoto en una planilla simple cada consulta que entra, con la campaña de origen, si se convirtió en turno, y si el turno terminó en caso firmado o auto vendido. Eso no te lo da nunca el Ads Manager solo. Así dejo de mirar cuántos clics tuve y empiezo a mirar, anuncio por anuncio, cuál me trae el cliente que realmente firma o compra, no el que solo pregunta y desaparece. Mandame ANUNCIO por DM.</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Formato podcast/estudio: plano medio con micrófono de brazo tipo boom y estantería de fondo; mitad inferior de pantalla con gráfico simple tipo pizarra mostrando costo real por consulta vs. el reportado; subtítulos blancos palabra por palabra.</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de acusación contra la atribución nativa y la estructura problema-cifra-solución con herramienta propia, cambiando el costo por lead de ecommerce por el costo real por consulta de un estudio o concesionaria con seguimiento aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="100" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7625510355711642887</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>1957</v>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Hay algo que le pasa a un montón de dueños de concesionaria sin que se den cuenta, y tiene que ver con cómo el sistema de Meta clasifica tus anuncios. Si subís cinco anuncios distintos pero todos son la misma foto del auto en la vereda con el mismo cartel, para el algoritmo son básicamente el mismo anuncio. Les asigna el mismo historial, compiten entre ellos por el mismo público, y ninguno recibe aprendizaje fresco. Por eso muchas veces el dueño dice 'subí cinco anuncios nuevos y no cambió nada', y en realidad para Meta nunca fueron anuncios nuevos, solo cambió la foto pero no el ángulo. Lo que hay que cambiar de verdad es el formato: una vez video, una vez testimonio, una vez foto del taller. Recién ahí Meta lo empieza a tratar como algo distinto. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: plano medio en formato podcast con micrófono de brazo. Fondo con luces de color opcional para una estética más elaborada, un fondo liso también funciona. Subtítulos recomendados. Plano fijo, sin cortes ni gráficos.</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho de concepto técnico poco conocido explicado en tono de revelación; se aplicó el mismo concepto de Meta agrupando creatividades parecidas a fotos repetidas de autos en anuncios de concesionaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="100" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7626005293658361121</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>919</v>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>¿Cuál es la diferencia real entre un abogado que recién arranca con Meta Ads y uno que ya lo tiene aceitado? El que arranca es puro nervio: mira el costo por consulta todos los días, y si un día le sale más caro, quiere frenar todo. El que ya lo tiene aceitado sabe que esto se mide en meses, no en un mal día. Y encima juega distinto: muchas veces prefiere pagar más por cada consulta si eso le trae casos de mejor calidad, porque un solo caso bueno le paga el mes entero de publicidad. Por eso los estudios que más facturan casi nunca tienen el costo por consulta más bajo. Tienen la agenda más llena. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio/primer plano estilo podcast con micrófono profesional en cuadro, toma continua sin cortes; subtítulos palabra por palabra en mayúsculas; sin gráficos ni capturas; locación interior tipo oficina o cocina con luz natural.</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de comparación identitaria (principiante versus pro) y el remate contraintuitivo sobre la métrica, y cambié ROAS/escala por costo por consulta y calidad de casos en un estudio de abogados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="100" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Clip de podcast</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7636364743753649440</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>896</v>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>¿Cuál es el mejor objetivo para las campañas de un abogado o una concesionaria: mensajes, clics al link o llamadas? Clics al link, ni loco. Entre mensajes y llamadas depende de cómo cerrás vos las consultas. Si la gente te termina escribiendo por WhatsApp para sacar un turno, andá con el objetivo de mensajes. Si lo que más te funciona es que te llamen directo, usá el objetivo de llamadas. Lo que no tiene sentido es optimizar para que miren tu página, eso no te llena la agenda. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Toma continua corta, encuadre fijo (oficina o exterior); subtítulos grandes palabra por palabra; sin cortes; sin música; menos de 30 segundos de largo.</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de pregunta y respuesta directa y corta sobre el mejor objetivo de campaña; cambié landing page/ventas de e-commerce por mensajes/llamadas, que es como realmente convierten estudios y concesionarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Caso de cliente — 5 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="100" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Caso de cliente</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Chase Chappell</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chase_chappell/video/7603828023187492126</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>72700</v>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Este estudio de abogados se está comiendo a la competencia de su ciudad. Armaron un sistema simple: cada consulta que entra por Meta se contesta en menos de cinco minutos, las 24 horas, sea sábado o domingo a la noche. Las consultas que antes se perdían por tardar en contestar, ahora se convierten en casos. Ahora mismo tienen 12 anuncios distintos corriendo, probando ángulos todo el tiempo. Eso significa testeo constante y casos nuevos todos los meses. Esta estrategia la estamos usando ahora, en 2026, y es la misma que llevó a este estudio de 8 a 35 consultas por mes en 60 días. No en un año. En dos meses. Velocidad de respuesta más anuncios constantes, ese es el combo que funciona. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Formato podcast: Gonzalo a cámara con micrófono; insertar capturas simuladas de métricas (gráfico simple de consultas por mes) con cifras destacadas y flechas rojas; subtítulos bold; corte entre el clip principal y las capturas de prueba.</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>Copié el formato de caso de estudio con cifra extrema de crecimiento en poco tiempo como prueba; cambié ventas de e-commerce en un mes por consultas de un estudio jurídico multiplicadas por la velocidad de respuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="100" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Caso de cliente</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7645570700857724167</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Invertimos dos millones de pesos para generarle veinte a esta concesionaria, y te cuento qué cambiamos. La clienta ya tenía compradores fieles que volvían por el service, pero atraer gente nueva por Meta le hacía perder plata. Sus autos arrancan en un valor alto, y pedirle a un desconocido esa compra es difícil. La cuenta solo tenía fotos de catálogo, nada que mostrara la experiencia real: la entrega, la familia con el auto nuevo. Sumamos ese contenido, más testimonios de por qué la eligieron a ella y no a otra. La agencia anterior nunca había excluido a los clientes existentes de la campaña de captación, y el sistema competía contra sí mismo. Armamos bien esas exclusiones para que el presupuesto vaya solo detrás de gente nueva, y cuando un modelo funcionaba mejor, lo separamos en su propia campaña. El producto siempre fue bueno, lo que frenaba el crecimiento era la estrategia. En seis meses, duplicamos los clientes nuevos que entraban por Meta. Escribime AUDITORÍA por mensaje y te reviso la cuenta gratis.</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Talking head formato entrevista/testimonio, plano medio fijo, fondo liso, sin cortes de cámara; subtítulos incrustados en dos estilos: titular manuscrito arriba y captions palabra por palabra abajo.</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Se tomó el gancho numérico de inversión versus resultado con estructura de diagnóstico-cambio-resultado tipo caso de éxito, cambiando la marca de moda de ticket alto por una concesionaria que perdía plata en captación de clientes nuevos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="100" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Caso de cliente</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7629597512055147784</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>1378</v>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Así triplicamos las consultas de un estudio de abogados en dos meses. Arrancamos recortando lo que promocionaban: en vez de anunciar seis áreas distintas del derecho, nos enfocamos solo en despidos, que era donde más ganaban los casos. Segundo, subimos contenido nuevo cada semana, nada exagerado, pero siempre distinto: una semana un caso resuelto, la otra una duda común respondida a cámara. Tercero, metimos un anuncio contando por qué el abogado eligió esta rama, la historia real detrás del estudio, y ese fue el que más consultas trajo de todos. En esos dos meses pasamos de tres consultas por semana a diez. Si querés que hagamos esto con tu estudio o tu concesionaria, escribime AUDITORÍA por mensaje y te reviso la cuenta gratis.</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: selfie vertical con micrófono de solapa, plano fijo sin cortes. Superposición fija arriba con la captura de un gráfico simple armado en Sheets o Canva. Subtítulo grande tipo título quemado al inicio. Sin música.</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>Se mantuvo el gancho de resultado concreto con prueba visual y la estructura de 'las 3 cosas que hicimos'; se cambió la marca de moda por un estudio de abogados y el CTA pasó a ofrecer la auditoría gratis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="100" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Caso de cliente</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>MADE Marketing (Maddi)</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@madecreativeco/video/7641559635861736712</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>1338</v>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Estoy por arrancar a trabajar con una concesionaria que gasta casi 3 millones de pesos por mes en Meta Ads, y quiero mostrarte cómo empiezo antes de tocar un solo anuncio. Lo primero que hago es un relevamiento de los últimos 30 días de la cuenta: qué anuncios generaron turnos de verdad, cuáles solo dieron likes, cuánto está costando cada consulta y cada venta. Con eso armo una planilla simple: qué está funcionando, qué público responde mejor, qué autos o servicios tienen demanda y todavía no se están mostrando. Recién ahí planifico un calendario de anuncios nuevos, semana por semana. Llevo casi dos semanas con esta cuenta y todavía no cambié ni un solo anuncio, porque entender bien qué está pasando antes de tocar nada es lo que después hace que la plata en Ads vuelva en ventas. Si querés que revise así tu cuenta, escribime AUDITORÍA por mensaje y te reviso la cuenta gratis.</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Hablás a cámara en la oficina; cortás a grabación de pantalla de tu planilla real de auditoría con zoom sobre las columnas clave (anuncios, costo por consulta, público); sin cortes de escena extra; subtítulo grande solo en la intro.</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el gancho de cifra grande de facturación de un cliente real y el proceso de auditoría antes de tocar la cuenta; cambié la marca de e-commerce por una concesionaria y el documento de research por un relevamiento de turnos y costo por consulta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="100" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Caso de cliente</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Venta del servicio</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Justin Lalonde</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@justnlalonde/video/7637927133989440775</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>269</v>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Te cuento un caso real de una concesionaria que llevamos. En treinta días, invirtieron doscientos mil pesos en Meta Ads. Salieron ciento ochenta consultas por WhatsApp de gente interesada en ver autos. De esas, cuarenta y dos sacaron turno para venir al showroom, y de esas visitas, catorce terminaron comprando un auto ese mismo mes. Si cada auto les deja de margen ochenta mil pesos, catorce ventas son más de un millón de pesos de ganancia con doscientos mil invertidos en anuncios. No fue un golpe de suerte: fue segmentar bien la zona, mostrar el stock real y responder rápido cada consulta. Así de concreto puede ser Meta Ads bien armado para un negocio como el tuyo. Escribime AUDITORÍA por mensaje y te reviso la cuenta gratis.</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Plano medio de busto, cámara fija tipo webcam en oficina propia, micrófono de solapa o de brazo; subtítulos blancos simples; placa de texto opcional con los números clave del caso (inversión, consultas, ventas). Edición mínima.</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Tomé la estructura de desglose numérico paso a paso de un caso real como prueba social; cambié el evento en vivo de 2 millones de dólares por un caso de concesionaria con consultas, turnos y ventas de autos en pesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>FORMATO: Entrevista/vox-pop — 3 videos en el top 100 (cuanto más se repite, más está funcionando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="100" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista/vox-pop</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Solución de un problema</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7624497738855583008</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>2569</v>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>¿Cuál es el error más grande que ves en las cuentas de Meta Ads de comercios locales? El más común es que el dueño no se aguanta las ganas de meter mano todos los días: cambia el texto, apaga el anuncio, prueba otra foto. Y cuando hace eso, la campaña nunca termina de aprender quién es el cliente ideal. Los resultados se vuelven un desastre: un día tres consultas, al otro día cero, y el dueño piensa que fue por el cambio que hizo, cuando en realidad son así de volátiles los primeros días. Lo que le digo siempre a mis clientes, ya sean concesionarias o estudios de abogados, es: elegí un día fijo, una vez por semana, y ahí revisás y ajustás. El resto de los días, no la toques. Guardá este video para acordarte la próxima vez que quieras tocar la campaña.</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Encuadre: toma continua a cámara, interior simple, micrófono de mesa visible. Subtítulos blancos palabra por palabra. Sin gráficos ni capturas de pantalla. Formato pregunta y respuesta, la pregunta puede ir como texto en pantalla. Sin música.</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Se mantuvo el gancho de pregunta directa y la estructura causa-efecto del error con consejo final concreto; se cambiaron los ejemplos a dueños de concesionarias y estudios de abogados que tocan demasiado sus campañas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="100" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista/vox-pop</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Ben Heath</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@benheathmarketing/video/7667313471880547606</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>1540</v>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>¿Cuánto gastás en publicidad para conseguir clientes para tu propia agencia? Mucho menos de lo que la gente se imagina. Yo no tengo problema de demanda, tengo problema de capacidad: si agarro 15 estudios y concesionarias a la vez, no les puedo dar bola como se merecen. Entonces hago esto: cuando me queda un lugar libre, prendo los anuncios, invierto una semana, junto un par de consultas, sumo uno o dos clientes nuevos, y los apago de nuevo. Hay meses que gasto 20 mil pesos en mi propia publicidad, nada más. Podría gastar diez veces eso y llenarme de clientes, pero prefiero decirle que no a alguien, o hacerlo esperar un mes, antes que agarrar todo lo que entra y bajar la calidad del servicio. Seguime que subo esto todos los días.</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Formato entrevista: un socio o empleado pregunta y vos respondés; encuadre de perfil sentados los dos (oficina o exterior con luz natural); corte a tu plano individual para la respuesta larga; subtítulos blancos negrita sincronizados.</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de pregunta directa sobre gasto publicitario propio con respuesta contraintuitiva de 'menos de lo que creés porque el límite es la capacidad, no la demanda'; cambié la agencia genérica por la de Gonzalo con estudios y concesionarias como clientes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="100" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Entrevista/vox-pop</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Charley T (Disrupter School)</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ctthedisrupter/video/7592685803558505742</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Che, ¿cómo te llamás? Hola, soy Martín, tengo una concesionaria acá en Rosario. ¿Cuánto invertís en Meta Ads por mes? Unos 700 mil pesos. La mayoría de las concesionarias no llega ni a la mitad de eso. ¿Qué consejo le darías a alguien que recién arranca? Dos cosas. Uno: dejá de mirar solo cuánto te cuesta cada consulta, mirá cuánta plata te queda por auto vendido, descontando lo que gastaste en conseguir a ese cliente. Esa es la cuenta que importa. Y dos: agarrá el anuncio que mejor te funcionó el mes pasado y no lo cambies de una, hacé una versión apenas distinta y probala. Mejorando de a poquito, terminás resolviendo el problema. Seguime que subo entrevistas como esta todos los días.</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Cámara en mano, plano medio de 2 personas, formato vox-pop en evento o feria (salón del automóvil o similar), mic de mano; subtítulos en cajas de color por frase, no palabra por palabra; toma corrida con ruido ambiente, sin cortes ni gráficos.</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Tomé el formato de entrevista espontánea con cifra de inversión grande y los 2 tips finales (métrica real de ganancia más iterar sobre el ganador), y cambié al entrevistado por un dueño de concesionaria argentino con montos en pesos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A103:J103"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A63:J63"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId100"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -9978,14 +14864,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="96" customWidth="1" min="2" max="2"/>
@@ -10264,12 +15150,134 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Hoja 'Guiones para tu negocio'</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>100 guiones NUEVOS y originales en español (voseo), adaptados a la venta de servicios de Meta Ads para abogados, concesionarias y negocios locales. Cada uno sigue el esqueleto del video de referencia (gancho, estructura, mecanismo) sin copiar sus frases. Agrupados por formato, ordenados por cuántos videos del top 100 usan ese formato: los formatos más repetidos son los que están funcionando ahora. Incluye tipo de edición mínima por video y conserva el Día sugerido del plan de 12 días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Demo de herramienta/IA</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Explicación con gráfico/pizarra</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Auditoría/análisis de cuenta</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Opinión a cámara</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Lista de tips o errores</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Tutorial o screencast</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Reseña de anuncios reales</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Noticia/actualización de Meta</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Clip de podcast</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Caso de cliente</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Entrevista/vox-pop</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
